--- a/System_Puchase.xlsx
+++ b/System_Puchase.xlsx
@@ -43,7 +43,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -264,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
@@ -308,13 +314,16 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -879,7 +888,9 @@
         </is>
       </c>
       <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
+      <c r="K2" s="29" t="n">
+        <v>2417</v>
+      </c>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
@@ -909,19 +920,21 @@
       <c r="F3" s="8" t="n">
         <v>463</v>
       </c>
-      <c r="G3" s="29" t="n">
+      <c r="G3" s="30" t="n">
         <v>45836</v>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr"/>
-      <c r="J3" s="32" t="n">
+      <c r="I3" s="32" t="inlineStr"/>
+      <c r="J3" s="33" t="n">
         <v>16897</v>
       </c>
-      <c r="K3" s="8" t="n"/>
+      <c r="K3" s="34" t="n">
+        <v>463</v>
+      </c>
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="8" t="n"/>
       <c r="N3" s="8" t="n"/>
@@ -951,21 +964,23 @@
       <c r="F4" s="8" t="n">
         <v>1193</v>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G4" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J4" s="8" t="n"/>
-      <c r="K4" s="8" t="n"/>
+      <c r="K4" s="34" t="n">
+        <v>1193</v>
+      </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
@@ -995,23 +1010,25 @@
       <c r="F5" s="8" t="n">
         <v>341</v>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I5" s="31" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J5" s="32" t="n">
+      <c r="J5" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K5" s="8" t="n"/>
+      <c r="K5" s="34" t="n">
+        <v>341</v>
+      </c>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n"/>
@@ -1041,19 +1058,21 @@
       <c r="F6" s="8" t="n">
         <v>1099</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I6" s="31" t="inlineStr"/>
-      <c r="J6" s="32" t="n">
+      <c r="I6" s="32" t="inlineStr"/>
+      <c r="J6" s="33" t="n">
         <v>23923</v>
       </c>
-      <c r="K6" s="8" t="n"/>
+      <c r="K6" s="34" t="n">
+        <v>1099</v>
+      </c>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n"/>
@@ -1083,19 +1102,21 @@
       <c r="F7" s="8" t="n">
         <v>1138</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="30" t="n">
         <v>45833</v>
       </c>
-      <c r="H7" s="31" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr"/>
-      <c r="J7" s="32" t="n">
+      <c r="I7" s="32" t="inlineStr"/>
+      <c r="J7" s="33" t="n">
         <v>52145</v>
       </c>
-      <c r="K7" s="8" t="n"/>
+      <c r="K7" s="34" t="n">
+        <v>1138</v>
+      </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
@@ -1125,21 +1146,23 @@
       <c r="F8" s="8" t="n">
         <v>1693</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <v>45818</v>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I8" s="31" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t>002402</t>
         </is>
       </c>
       <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
+      <c r="K8" s="34" t="n">
+        <v>1693</v>
+      </c>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n"/>
@@ -1169,23 +1192,25 @@
       <c r="F9" s="8" t="n">
         <v>576</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="30" t="n">
         <v>45853</v>
       </c>
-      <c r="H9" s="30" t="inlineStr">
+      <c r="H9" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I9" s="31" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t>002491</t>
         </is>
       </c>
-      <c r="J9" s="32" t="n">
+      <c r="J9" s="33" t="n">
         <v>27994</v>
       </c>
-      <c r="K9" s="8" t="n"/>
+      <c r="K9" s="34" t="n">
+        <v>576</v>
+      </c>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n"/>
@@ -1215,23 +1240,25 @@
       <c r="F10" s="8" t="n">
         <v>167</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="30" t="n">
         <v>45832</v>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I10" s="31" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>002457</t>
         </is>
       </c>
-      <c r="J10" s="32" t="n">
+      <c r="J10" s="33" t="n">
         <v>26866</v>
       </c>
-      <c r="K10" s="8" t="n"/>
+      <c r="K10" s="34" t="n">
+        <v>167</v>
+      </c>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
@@ -1261,23 +1288,25 @@
       <c r="F11" s="8" t="n">
         <v>274</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I11" s="31" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J11" s="32" t="n">
+      <c r="J11" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K11" s="8" t="n"/>
+      <c r="K11" s="34" t="n">
+        <v>274</v>
+      </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
@@ -1307,19 +1336,21 @@
       <c r="F12" s="8" t="n">
         <v>5551</v>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I12" s="31" t="inlineStr"/>
-      <c r="J12" s="32" t="n">
+      <c r="I12" s="32" t="inlineStr"/>
+      <c r="J12" s="33" t="n">
         <v>23923</v>
       </c>
-      <c r="K12" s="8" t="n"/>
+      <c r="K12" s="34" t="n">
+        <v>5551</v>
+      </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -1383,19 +1414,21 @@
       <c r="F14" s="8" t="n">
         <v>2228</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="30" t="n">
         <v>45833</v>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I14" s="31" t="inlineStr"/>
-      <c r="J14" s="32" t="n">
+      <c r="I14" s="32" t="inlineStr"/>
+      <c r="J14" s="33" t="n">
         <v>52145</v>
       </c>
-      <c r="K14" s="8" t="n"/>
+      <c r="K14" s="34" t="n">
+        <v>2228</v>
+      </c>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
@@ -1425,21 +1458,23 @@
       <c r="F15" s="8" t="n">
         <v>7873</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I15" s="31" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
+      <c r="K15" s="34" t="n">
+        <v>7873</v>
+      </c>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
@@ -1469,21 +1504,23 @@
       <c r="F16" s="8" t="n">
         <v>13488</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="30" t="n">
         <v>45827</v>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I16" s="31" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
         <is>
           <t>002429</t>
         </is>
       </c>
       <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
+      <c r="K16" s="34" t="n">
+        <v>13488</v>
+      </c>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
@@ -1615,21 +1652,23 @@
       <c r="F20" s="8" t="n">
         <v>458</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="H20" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I20" s="31" t="inlineStr">
+      <c r="I20" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
+      <c r="K20" s="34" t="n">
+        <v>458</v>
+      </c>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
@@ -1659,19 +1698,21 @@
       <c r="F21" s="8" t="n">
         <v>623</v>
       </c>
-      <c r="G21" s="30" t="n">
+      <c r="G21" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="H21" s="30" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I21" s="31" t="inlineStr"/>
-      <c r="J21" s="32" t="n">
+      <c r="I21" s="32" t="inlineStr"/>
+      <c r="J21" s="33" t="n">
         <v>23923</v>
       </c>
-      <c r="K21" s="8" t="n"/>
+      <c r="K21" s="34" t="n">
+        <v>623</v>
+      </c>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
@@ -1701,21 +1742,23 @@
       <c r="F22" s="8" t="n">
         <v>5224</v>
       </c>
-      <c r="G22" s="30" t="n">
+      <c r="G22" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H22" s="30" t="inlineStr">
+      <c r="H22" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I22" s="31" t="inlineStr">
+      <c r="I22" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
+      <c r="K22" s="34" t="n">
+        <v>5224</v>
+      </c>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
@@ -1745,19 +1788,21 @@
       <c r="F23" s="8" t="n">
         <v>356</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="30" t="n">
         <v>45808</v>
       </c>
-      <c r="H23" s="30" t="inlineStr">
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I23" s="31" t="inlineStr"/>
-      <c r="J23" s="32" t="n">
+      <c r="I23" s="32" t="inlineStr"/>
+      <c r="J23" s="33" t="n">
         <v>3193</v>
       </c>
-      <c r="K23" s="8" t="n"/>
+      <c r="K23" s="34" t="n">
+        <v>356</v>
+      </c>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n"/>
@@ -1855,21 +1900,23 @@
       <c r="F26" s="12" t="n">
         <v>3567</v>
       </c>
-      <c r="G26" s="33" t="n">
+      <c r="G26" s="35" t="n">
         <v>45868</v>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="35" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I26" s="34" t="inlineStr">
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
       </c>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
+      <c r="K26" s="37" t="n">
+        <v>3567</v>
+      </c>
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
       <c r="N26" s="12" t="n"/>
@@ -1912,10 +1959,12 @@
           <t>002562</t>
         </is>
       </c>
-      <c r="J27" s="35" t="n">
+      <c r="J27" s="38" t="n">
         <v>9492</v>
       </c>
-      <c r="K27" s="4" t="n"/>
+      <c r="K27" s="29" t="n">
+        <v>679</v>
+      </c>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
@@ -1979,23 +2028,25 @@
       <c r="F29" s="8" t="n">
         <v>907</v>
       </c>
-      <c r="G29" s="30" t="n">
+      <c r="G29" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H29" s="30" t="inlineStr">
+      <c r="H29" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I29" s="31" t="inlineStr">
+      <c r="I29" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J29" s="32" t="n">
+      <c r="J29" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K29" s="8" t="n"/>
+      <c r="K29" s="34" t="n">
+        <v>907</v>
+      </c>
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n"/>
@@ -2093,21 +2144,23 @@
       <c r="F32" s="8" t="n">
         <v>609</v>
       </c>
-      <c r="G32" s="30" t="n">
+      <c r="G32" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H32" s="30" t="inlineStr">
+      <c r="H32" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I32" s="31" t="inlineStr">
+      <c r="I32" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
+      <c r="K32" s="34" t="n">
+        <v>609</v>
+      </c>
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n"/>
@@ -2137,17 +2190,19 @@
       <c r="F33" s="8" t="n">
         <v>1197</v>
       </c>
-      <c r="G33" s="29" t="n">
+      <c r="G33" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H33" s="31" t="inlineStr">
+      <c r="H33" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I33" s="31" t="inlineStr"/>
+      <c r="I33" s="32" t="inlineStr"/>
       <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="K33" s="34" t="n">
+        <v>1197</v>
+      </c>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n"/>
@@ -2177,21 +2232,23 @@
       <c r="F34" s="8" t="n">
         <v>2451</v>
       </c>
-      <c r="G34" s="30" t="n">
+      <c r="G34" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H34" s="30" t="inlineStr">
+      <c r="H34" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I34" s="31" t="inlineStr">
+      <c r="I34" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
+      <c r="K34" s="34" t="n">
+        <v>2451</v>
+      </c>
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n"/>
@@ -2221,21 +2278,23 @@
       <c r="F35" s="8" t="n">
         <v>4898</v>
       </c>
-      <c r="G35" s="30" t="n">
+      <c r="G35" s="31" t="n">
         <v>45826</v>
       </c>
-      <c r="H35" s="30" t="inlineStr">
+      <c r="H35" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I35" s="31" t="inlineStr">
+      <c r="I35" s="32" t="inlineStr">
         <is>
           <t>002438</t>
         </is>
       </c>
       <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
+      <c r="K35" s="34" t="n">
+        <v>4898</v>
+      </c>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n"/>
@@ -2265,17 +2324,19 @@
       <c r="F36" s="8" t="n">
         <v>1417</v>
       </c>
-      <c r="G36" s="30" t="n">
+      <c r="G36" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="H36" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I36" s="31" t="inlineStr"/>
+      <c r="I36" s="32" t="inlineStr"/>
       <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
+      <c r="K36" s="34" t="n">
+        <v>1417</v>
+      </c>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n"/>
@@ -2305,21 +2366,23 @@
       <c r="F37" s="8" t="n">
         <v>799</v>
       </c>
-      <c r="G37" s="30" t="n">
+      <c r="G37" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H37" s="30" t="inlineStr">
+      <c r="H37" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I37" s="31" t="inlineStr">
+      <c r="I37" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
+      <c r="K37" s="34" t="n">
+        <v>799</v>
+      </c>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n"/>
@@ -2349,17 +2412,19 @@
       <c r="F38" s="8" t="n">
         <v>547</v>
       </c>
-      <c r="G38" s="29" t="n">
+      <c r="G38" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H38" s="31" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I38" s="31" t="inlineStr"/>
+      <c r="I38" s="32" t="inlineStr"/>
       <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
+      <c r="K38" s="34" t="n">
+        <v>547</v>
+      </c>
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n"/>
@@ -2389,21 +2454,23 @@
       <c r="F39" s="8" t="n">
         <v>531</v>
       </c>
-      <c r="G39" s="30" t="n">
+      <c r="G39" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H39" s="30" t="inlineStr">
+      <c r="H39" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I39" s="31" t="inlineStr">
+      <c r="I39" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
+      <c r="K39" s="34" t="n">
+        <v>531</v>
+      </c>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n"/>
@@ -2433,17 +2500,19 @@
       <c r="F40" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="G40" s="29" t="n">
+      <c r="G40" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H40" s="31" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I40" s="31" t="inlineStr"/>
+      <c r="I40" s="32" t="inlineStr"/>
       <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
+      <c r="K40" s="34" t="n">
+        <v>1986</v>
+      </c>
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n"/>
@@ -2473,17 +2542,19 @@
       <c r="F41" s="8" t="n">
         <v>5294</v>
       </c>
-      <c r="G41" s="30" t="n">
+      <c r="G41" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H41" s="30" t="inlineStr">
+      <c r="H41" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I41" s="31" t="inlineStr"/>
+      <c r="I41" s="32" t="inlineStr"/>
       <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
+      <c r="K41" s="34" t="n">
+        <v>5294</v>
+      </c>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n"/>
@@ -2513,21 +2584,23 @@
       <c r="F42" s="8" t="n">
         <v>433</v>
       </c>
-      <c r="G42" s="30" t="n">
+      <c r="G42" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H42" s="30" t="inlineStr">
+      <c r="H42" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I42" s="31" t="inlineStr">
+      <c r="I42" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
+      <c r="K42" s="34" t="n">
+        <v>433</v>
+      </c>
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n"/>
@@ -2557,17 +2630,19 @@
       <c r="F43" s="8" t="n">
         <v>1048</v>
       </c>
-      <c r="G43" s="29" t="n">
+      <c r="G43" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H43" s="31" t="inlineStr">
+      <c r="H43" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I43" s="31" t="inlineStr"/>
+      <c r="I43" s="32" t="inlineStr"/>
       <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
+      <c r="K43" s="34" t="n">
+        <v>1048</v>
+      </c>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n"/>
@@ -2597,17 +2672,19 @@
       <c r="F44" s="8" t="n">
         <v>634</v>
       </c>
-      <c r="G44" s="29" t="n">
+      <c r="G44" s="30" t="n">
         <v>45811</v>
       </c>
-      <c r="H44" s="31" t="inlineStr">
+      <c r="H44" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I44" s="31" t="inlineStr"/>
+      <c r="I44" s="32" t="inlineStr"/>
       <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
+      <c r="K44" s="34" t="n">
+        <v>634</v>
+      </c>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n"/>
@@ -2637,21 +2714,23 @@
       <c r="F45" s="8" t="n">
         <v>3083</v>
       </c>
-      <c r="G45" s="30" t="n">
+      <c r="G45" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H45" s="30" t="inlineStr">
+      <c r="H45" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I45" s="31" t="inlineStr">
+      <c r="I45" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="K45" s="34" t="n">
+        <v>3083</v>
+      </c>
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n"/>
@@ -2681,17 +2760,19 @@
       <c r="F46" s="8" t="n">
         <v>504</v>
       </c>
-      <c r="G46" s="30" t="n">
+      <c r="G46" s="31" t="n">
         <v>45872</v>
       </c>
-      <c r="H46" s="30" t="inlineStr">
+      <c r="H46" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I46" s="31" t="inlineStr"/>
+      <c r="I46" s="32" t="inlineStr"/>
       <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
+      <c r="K46" s="34" t="n">
+        <v>504</v>
+      </c>
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n"/>
@@ -2721,17 +2802,19 @@
       <c r="F47" s="8" t="n">
         <v>1443</v>
       </c>
-      <c r="G47" s="29" t="n">
+      <c r="G47" s="30" t="n">
         <v>45821</v>
       </c>
-      <c r="H47" s="31" t="inlineStr">
+      <c r="H47" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I47" s="31" t="inlineStr"/>
+      <c r="I47" s="32" t="inlineStr"/>
       <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
+      <c r="K47" s="34" t="n">
+        <v>1443</v>
+      </c>
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n"/>
@@ -2761,17 +2844,19 @@
       <c r="F48" s="8" t="n">
         <v>2071</v>
       </c>
-      <c r="G48" s="29" t="n">
+      <c r="G48" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H48" s="31" t="inlineStr">
+      <c r="H48" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I48" s="31" t="inlineStr"/>
+      <c r="I48" s="32" t="inlineStr"/>
       <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
+      <c r="K48" s="34" t="n">
+        <v>2071</v>
+      </c>
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n"/>
@@ -2801,17 +2886,19 @@
       <c r="F49" s="8" t="n">
         <v>339</v>
       </c>
-      <c r="G49" s="29" t="n">
+      <c r="G49" s="30" t="n">
         <v>45812</v>
       </c>
-      <c r="H49" s="31" t="inlineStr">
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I49" s="31" t="inlineStr"/>
+      <c r="I49" s="32" t="inlineStr"/>
       <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
+      <c r="K49" s="34" t="n">
+        <v>339</v>
+      </c>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n"/>
@@ -2841,17 +2928,19 @@
       <c r="F50" s="8" t="n">
         <v>437</v>
       </c>
-      <c r="G50" s="30" t="n">
+      <c r="G50" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H50" s="30" t="inlineStr">
+      <c r="H50" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I50" s="31" t="inlineStr"/>
+      <c r="I50" s="32" t="inlineStr"/>
       <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
+      <c r="K50" s="34" t="n">
+        <v>437</v>
+      </c>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
@@ -2881,21 +2970,23 @@
       <c r="F51" s="8" t="n">
         <v>6324</v>
       </c>
-      <c r="G51" s="30" t="n">
+      <c r="G51" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H51" s="30" t="inlineStr">
+      <c r="H51" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I51" s="31" t="inlineStr">
+      <c r="I51" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
+      <c r="K51" s="34" t="n">
+        <v>6324</v>
+      </c>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n"/>
@@ -2925,23 +3016,25 @@
       <c r="F52" s="8" t="n">
         <v>3372</v>
       </c>
-      <c r="G52" s="30" t="n">
+      <c r="G52" s="31" t="n">
         <v>45837</v>
       </c>
-      <c r="H52" s="30" t="inlineStr">
+      <c r="H52" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I52" s="31" t="inlineStr">
+      <c r="I52" s="32" t="inlineStr">
         <is>
           <t>002463</t>
         </is>
       </c>
-      <c r="J52" s="32" t="n">
+      <c r="J52" s="33" t="n">
         <v>11958</v>
       </c>
-      <c r="K52" s="8" t="n"/>
+      <c r="K52" s="34" t="n">
+        <v>3372</v>
+      </c>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n"/>
@@ -2971,17 +3064,19 @@
       <c r="F53" s="8" t="n">
         <v>1197</v>
       </c>
-      <c r="G53" s="29" t="n">
+      <c r="G53" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H53" s="31" t="inlineStr">
+      <c r="H53" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I53" s="31" t="inlineStr"/>
+      <c r="I53" s="32" t="inlineStr"/>
       <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
+      <c r="K53" s="34" t="n">
+        <v>1197</v>
+      </c>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n"/>
@@ -3011,17 +3106,19 @@
       <c r="F54" s="8" t="n">
         <v>2178</v>
       </c>
-      <c r="G54" s="29" t="n">
+      <c r="G54" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H54" s="31" t="inlineStr">
+      <c r="H54" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I54" s="31" t="inlineStr"/>
+      <c r="I54" s="32" t="inlineStr"/>
       <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
+      <c r="K54" s="34" t="n">
+        <v>2178</v>
+      </c>
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n"/>
@@ -3051,21 +3148,23 @@
       <c r="F55" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="G55" s="30" t="n">
+      <c r="G55" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H55" s="30" t="inlineStr">
+      <c r="H55" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I55" s="31" t="inlineStr">
+      <c r="I55" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
+      <c r="K55" s="34" t="n">
+        <v>165</v>
+      </c>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n"/>
@@ -3095,17 +3194,19 @@
       <c r="F56" s="8" t="n">
         <v>2296</v>
       </c>
-      <c r="G56" s="29" t="n">
+      <c r="G56" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H56" s="31" t="inlineStr">
+      <c r="H56" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I56" s="31" t="inlineStr"/>
+      <c r="I56" s="32" t="inlineStr"/>
       <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
+      <c r="K56" s="34" t="n">
+        <v>2296</v>
+      </c>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
@@ -3135,17 +3236,19 @@
       <c r="F57" s="8" t="n">
         <v>1796</v>
       </c>
-      <c r="G57" s="29" t="n">
+      <c r="G57" s="30" t="n">
         <v>45819</v>
       </c>
-      <c r="H57" s="31" t="inlineStr">
+      <c r="H57" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I57" s="31" t="inlineStr"/>
+      <c r="I57" s="32" t="inlineStr"/>
       <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
+      <c r="K57" s="34" t="n">
+        <v>1796</v>
+      </c>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n"/>
@@ -3345,21 +3448,23 @@
       <c r="F63" s="8" t="n">
         <v>4577</v>
       </c>
-      <c r="G63" s="30" t="n">
+      <c r="G63" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H63" s="30" t="inlineStr">
+      <c r="H63" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I63" s="31" t="inlineStr">
+      <c r="I63" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
+      <c r="K63" s="34" t="n">
+        <v>4577</v>
+      </c>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n"/>
@@ -3389,17 +3494,19 @@
       <c r="F64" s="8" t="n">
         <v>9499</v>
       </c>
-      <c r="G64" s="30" t="n">
+      <c r="G64" s="31" t="n">
         <v>45854</v>
       </c>
-      <c r="H64" s="30" t="inlineStr">
+      <c r="H64" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I64" s="31" t="inlineStr"/>
+      <c r="I64" s="32" t="inlineStr"/>
       <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
+      <c r="K64" s="34" t="n">
+        <v>9499</v>
+      </c>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
@@ -3497,21 +3604,23 @@
       <c r="F67" s="8" t="n">
         <v>985</v>
       </c>
-      <c r="G67" s="30" t="n">
+      <c r="G67" s="31" t="n">
         <v>45823</v>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H67" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I67" s="31" t="inlineStr">
+      <c r="I67" s="32" t="inlineStr">
         <is>
           <t>002421</t>
         </is>
       </c>
       <c r="J67" s="8" t="n"/>
-      <c r="K67" s="8" t="n"/>
+      <c r="K67" s="34" t="n">
+        <v>985</v>
+      </c>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n"/>
@@ -3541,21 +3650,23 @@
       <c r="F68" s="8" t="n">
         <v>4806</v>
       </c>
-      <c r="G68" s="30" t="n">
+      <c r="G68" s="31" t="n">
         <v>45823</v>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H68" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I68" s="31" t="inlineStr">
+      <c r="I68" s="32" t="inlineStr">
         <is>
           <t>002421</t>
         </is>
       </c>
       <c r="J68" s="8" t="n"/>
-      <c r="K68" s="8" t="n"/>
+      <c r="K68" s="34" t="n">
+        <v>4806</v>
+      </c>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n"/>
@@ -3653,17 +3764,19 @@
       <c r="F71" s="8" t="n">
         <v>2169</v>
       </c>
-      <c r="G71" s="30" t="n">
+      <c r="G71" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H71" s="30" t="inlineStr">
+      <c r="H71" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I71" s="31" t="inlineStr"/>
+      <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="8" t="n"/>
-      <c r="K71" s="8" t="n"/>
+      <c r="K71" s="34" t="n">
+        <v>2169</v>
+      </c>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n"/>
@@ -3693,17 +3806,19 @@
       <c r="F72" s="8" t="n">
         <v>5939</v>
       </c>
-      <c r="G72" s="30" t="n">
+      <c r="G72" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H72" s="30" t="inlineStr">
+      <c r="H72" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I72" s="31" t="inlineStr"/>
+      <c r="I72" s="32" t="inlineStr"/>
       <c r="J72" s="8" t="n"/>
-      <c r="K72" s="8" t="n"/>
+      <c r="K72" s="34" t="n">
+        <v>5939</v>
+      </c>
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n"/>
@@ -3733,17 +3848,19 @@
       <c r="F73" s="8" t="n">
         <v>4565</v>
       </c>
-      <c r="G73" s="29" t="n">
+      <c r="G73" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H73" s="31" t="inlineStr">
+      <c r="H73" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
+      <c r="I73" s="32" t="inlineStr"/>
       <c r="J73" s="8" t="n"/>
-      <c r="K73" s="8" t="n"/>
+      <c r="K73" s="34" t="n">
+        <v>4565</v>
+      </c>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n"/>
@@ -3773,17 +3890,19 @@
       <c r="F74" s="8" t="n">
         <v>3925</v>
       </c>
-      <c r="G74" s="29" t="n">
+      <c r="G74" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H74" s="31" t="inlineStr">
+      <c r="H74" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
+      <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="8" t="n"/>
-      <c r="K74" s="8" t="n"/>
+      <c r="K74" s="34" t="n">
+        <v>3925</v>
+      </c>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n"/>
@@ -3813,17 +3932,19 @@
       <c r="F75" s="8" t="n">
         <v>8180</v>
       </c>
-      <c r="G75" s="29" t="n">
+      <c r="G75" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H75" s="31" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I75" s="31" t="inlineStr"/>
+      <c r="I75" s="32" t="inlineStr"/>
       <c r="J75" s="8" t="n"/>
-      <c r="K75" s="8" t="n"/>
+      <c r="K75" s="34" t="n">
+        <v>8180</v>
+      </c>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="8" t="n"/>
@@ -3887,21 +4008,23 @@
       <c r="F77" s="8" t="n">
         <v>8872</v>
       </c>
-      <c r="G77" s="30" t="n">
+      <c r="G77" s="31" t="n">
         <v>45825</v>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H77" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I77" s="31" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>002425</t>
         </is>
       </c>
       <c r="J77" s="8" t="n"/>
-      <c r="K77" s="8" t="n"/>
+      <c r="K77" s="34" t="n">
+        <v>8872</v>
+      </c>
       <c r="L77" s="8" t="n"/>
       <c r="M77" s="8" t="n"/>
       <c r="N77" s="8" t="n"/>
@@ -3999,21 +4122,23 @@
       <c r="F80" s="8" t="n">
         <v>5056</v>
       </c>
-      <c r="G80" s="30" t="n">
+      <c r="G80" s="31" t="n">
         <v>45834</v>
       </c>
-      <c r="H80" s="30" t="inlineStr">
+      <c r="H80" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I80" s="31" t="inlineStr">
+      <c r="I80" s="32" t="inlineStr">
         <is>
           <t>002458</t>
         </is>
       </c>
       <c r="J80" s="8" t="n"/>
-      <c r="K80" s="8" t="n"/>
+      <c r="K80" s="34" t="n">
+        <v>5055</v>
+      </c>
       <c r="L80" s="8" t="n"/>
       <c r="M80" s="8" t="n"/>
       <c r="N80" s="8" t="n"/>
@@ -4043,21 +4168,23 @@
       <c r="F81" s="8" t="n">
         <v>12192</v>
       </c>
-      <c r="G81" s="30" t="n">
+      <c r="G81" s="31" t="n">
         <v>45835</v>
       </c>
-      <c r="H81" s="30" t="inlineStr">
+      <c r="H81" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr">
         <is>
           <t>002459</t>
         </is>
       </c>
       <c r="J81" s="8" t="n"/>
-      <c r="K81" s="8" t="n"/>
+      <c r="K81" s="34" t="n">
+        <v>12192</v>
+      </c>
       <c r="L81" s="8" t="n"/>
       <c r="M81" s="8" t="n"/>
       <c r="N81" s="8" t="n"/>
@@ -4155,21 +4282,23 @@
       <c r="F84" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="G84" s="30" t="n">
+      <c r="G84" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H84" s="30" t="inlineStr">
+      <c r="H84" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I84" s="31" t="inlineStr">
+      <c r="I84" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
+      <c r="K84" s="34" t="n">
+        <v>699</v>
+      </c>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
       <c r="N84" s="8" t="n"/>
@@ -4267,23 +4396,25 @@
       <c r="F87" s="8" t="n">
         <v>604</v>
       </c>
-      <c r="G87" s="30" t="n">
+      <c r="G87" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H87" s="30" t="inlineStr">
+      <c r="H87" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I87" s="31" t="inlineStr">
+      <c r="I87" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J87" s="32" t="n">
+      <c r="J87" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K87" s="8" t="n"/>
+      <c r="K87" s="34" t="n">
+        <v>604</v>
+      </c>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="8" t="n"/>
       <c r="N87" s="8" t="n"/>
@@ -4313,17 +4444,19 @@
       <c r="F88" s="8" t="n">
         <v>1934</v>
       </c>
-      <c r="G88" s="29" t="n">
+      <c r="G88" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H88" s="31" t="inlineStr">
+      <c r="H88" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I88" s="31" t="inlineStr"/>
+      <c r="I88" s="32" t="inlineStr"/>
       <c r="J88" s="8" t="n"/>
-      <c r="K88" s="8" t="n"/>
+      <c r="K88" s="34" t="n">
+        <v>1934</v>
+      </c>
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="n"/>
       <c r="N88" s="8" t="n"/>
@@ -4353,17 +4486,19 @@
       <c r="F89" s="8" t="n">
         <v>5387</v>
       </c>
-      <c r="G89" s="30" t="n">
+      <c r="G89" s="31" t="n">
         <v>45821</v>
       </c>
-      <c r="H89" s="30" t="inlineStr">
+      <c r="H89" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I89" s="31" t="inlineStr"/>
+      <c r="I89" s="32" t="inlineStr"/>
       <c r="J89" s="8" t="n"/>
-      <c r="K89" s="8" t="n"/>
+      <c r="K89" s="34" t="n">
+        <v>5387</v>
+      </c>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="8" t="n"/>
@@ -4393,17 +4528,19 @@
       <c r="F90" s="8" t="n">
         <v>701</v>
       </c>
-      <c r="G90" s="29" t="n">
+      <c r="G90" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H90" s="31" t="inlineStr">
+      <c r="H90" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I90" s="31" t="inlineStr"/>
+      <c r="I90" s="32" t="inlineStr"/>
       <c r="J90" s="8" t="n"/>
-      <c r="K90" s="8" t="n"/>
+      <c r="K90" s="34" t="n">
+        <v>701</v>
+      </c>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
       <c r="N90" s="8" t="n"/>
@@ -4433,17 +4570,19 @@
       <c r="F91" s="8" t="n">
         <v>1092</v>
       </c>
-      <c r="G91" s="30" t="n">
+      <c r="G91" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H91" s="30" t="inlineStr">
+      <c r="H91" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I91" s="31" t="inlineStr"/>
+      <c r="I91" s="32" t="inlineStr"/>
       <c r="J91" s="8" t="n"/>
-      <c r="K91" s="8" t="n"/>
+      <c r="K91" s="34" t="n">
+        <v>1092</v>
+      </c>
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n"/>
@@ -4473,21 +4612,23 @@
       <c r="F92" s="8" t="n">
         <v>1245</v>
       </c>
-      <c r="G92" s="30" t="n">
+      <c r="G92" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H92" s="30" t="inlineStr">
+      <c r="H92" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I92" s="31" t="inlineStr">
+      <c r="I92" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J92" s="8" t="n"/>
-      <c r="K92" s="8" t="n"/>
+      <c r="K92" s="34" t="n">
+        <v>1245</v>
+      </c>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n"/>
@@ -4619,17 +4760,19 @@
       <c r="F96" s="8" t="n">
         <v>515</v>
       </c>
-      <c r="G96" s="29" t="n">
+      <c r="G96" s="30" t="n">
         <v>45819</v>
       </c>
-      <c r="H96" s="31" t="inlineStr">
+      <c r="H96" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I96" s="31" t="inlineStr"/>
+      <c r="I96" s="32" t="inlineStr"/>
       <c r="J96" s="8" t="n"/>
-      <c r="K96" s="8" t="n"/>
+      <c r="K96" s="34" t="n">
+        <v>515</v>
+      </c>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n"/>
@@ -4659,17 +4802,19 @@
       <c r="F97" s="8" t="n">
         <v>352</v>
       </c>
-      <c r="G97" s="30" t="n">
+      <c r="G97" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H97" s="30" t="inlineStr">
+      <c r="H97" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I97" s="31" t="inlineStr"/>
+      <c r="I97" s="32" t="inlineStr"/>
       <c r="J97" s="8" t="n"/>
-      <c r="K97" s="8" t="n"/>
+      <c r="K97" s="34" t="n">
+        <v>352</v>
+      </c>
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n"/>
@@ -4699,17 +4844,19 @@
       <c r="F98" s="8" t="n">
         <v>715</v>
       </c>
-      <c r="G98" s="29" t="n">
+      <c r="G98" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H98" s="31" t="inlineStr">
+      <c r="H98" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I98" s="31" t="inlineStr"/>
+      <c r="I98" s="32" t="inlineStr"/>
       <c r="J98" s="8" t="n"/>
-      <c r="K98" s="8" t="n"/>
+      <c r="K98" s="34" t="n">
+        <v>715</v>
+      </c>
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n"/>
@@ -4739,17 +4886,19 @@
       <c r="F99" s="8" t="n">
         <v>1736</v>
       </c>
-      <c r="G99" s="29" t="n">
+      <c r="G99" s="30" t="n">
         <v>45819</v>
       </c>
-      <c r="H99" s="31" t="inlineStr">
+      <c r="H99" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I99" s="31" t="inlineStr"/>
+      <c r="I99" s="32" t="inlineStr"/>
       <c r="J99" s="8" t="n"/>
-      <c r="K99" s="8" t="n"/>
+      <c r="K99" s="34" t="n">
+        <v>1736</v>
+      </c>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n"/>
@@ -4779,21 +4928,23 @@
       <c r="F100" s="8" t="n">
         <v>648</v>
       </c>
-      <c r="G100" s="30" t="n">
+      <c r="G100" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H100" s="30" t="inlineStr">
+      <c r="H100" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I100" s="31" t="inlineStr">
+      <c r="I100" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J100" s="8" t="n"/>
-      <c r="K100" s="8" t="n"/>
+      <c r="K100" s="34" t="n">
+        <v>648</v>
+      </c>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n"/>
@@ -4823,21 +4974,23 @@
       <c r="F101" s="8" t="n">
         <v>334</v>
       </c>
-      <c r="G101" s="30" t="n">
+      <c r="G101" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H101" s="30" t="inlineStr">
+      <c r="H101" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I101" s="31" t="inlineStr">
+      <c r="I101" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J101" s="8" t="n"/>
-      <c r="K101" s="8" t="n"/>
+      <c r="K101" s="34" t="n">
+        <v>334</v>
+      </c>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n"/>
@@ -4867,23 +5020,25 @@
       <c r="F102" s="8" t="n">
         <v>313</v>
       </c>
-      <c r="G102" s="30" t="n">
+      <c r="G102" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H102" s="30" t="inlineStr">
+      <c r="H102" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I102" s="31" t="inlineStr">
+      <c r="I102" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J102" s="32" t="n">
+      <c r="J102" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K102" s="8" t="n"/>
+      <c r="K102" s="34" t="n">
+        <v>313</v>
+      </c>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n"/>
@@ -4913,17 +5068,19 @@
       <c r="F103" s="8" t="n">
         <v>2486</v>
       </c>
-      <c r="G103" s="30" t="n">
+      <c r="G103" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H103" s="30" t="inlineStr">
+      <c r="H103" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I103" s="31" t="inlineStr"/>
+      <c r="I103" s="32" t="inlineStr"/>
       <c r="J103" s="8" t="n"/>
-      <c r="K103" s="8" t="n"/>
+      <c r="K103" s="34" t="n">
+        <v>2486</v>
+      </c>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n"/>
@@ -4987,21 +5144,23 @@
       <c r="F105" s="8" t="n">
         <v>2959</v>
       </c>
-      <c r="G105" s="30" t="n">
+      <c r="G105" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H105" s="30" t="inlineStr">
+      <c r="H105" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I105" s="31" t="inlineStr">
+      <c r="I105" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J105" s="8" t="n"/>
-      <c r="K105" s="8" t="n"/>
+      <c r="K105" s="34" t="n">
+        <v>2959</v>
+      </c>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
       <c r="N105" s="8" t="n"/>
@@ -5031,21 +5190,23 @@
       <c r="F106" s="8" t="n">
         <v>2820</v>
       </c>
-      <c r="G106" s="30" t="n">
+      <c r="G106" s="31" t="n">
         <v>45868</v>
       </c>
-      <c r="H106" s="30" t="inlineStr">
+      <c r="H106" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I106" s="31" t="inlineStr">
+      <c r="I106" s="32" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
       </c>
       <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
+      <c r="K106" s="34" t="n">
+        <v>2820</v>
+      </c>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
       <c r="N106" s="8" t="n"/>
@@ -5109,21 +5270,23 @@
       <c r="F108" s="8" t="n">
         <v>2002</v>
       </c>
-      <c r="G108" s="30" t="n">
+      <c r="G108" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H108" s="30" t="inlineStr">
+      <c r="H108" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I108" s="31" t="inlineStr">
+      <c r="I108" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
+      <c r="K108" s="34" t="n">
+        <v>2002</v>
+      </c>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n"/>
@@ -5153,21 +5316,23 @@
       <c r="F109" s="8" t="n">
         <v>9280</v>
       </c>
-      <c r="G109" s="30" t="n">
+      <c r="G109" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H109" s="30" t="inlineStr">
+      <c r="H109" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I109" s="31" t="inlineStr">
+      <c r="I109" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J109" s="8" t="n"/>
-      <c r="K109" s="8" t="n"/>
+      <c r="K109" s="34" t="n">
+        <v>9280</v>
+      </c>
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
       <c r="N109" s="8" t="n"/>
@@ -5231,17 +5396,19 @@
       <c r="F111" s="8" t="n">
         <v>391</v>
       </c>
-      <c r="G111" s="30" t="n">
+      <c r="G111" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H111" s="30" t="inlineStr">
+      <c r="H111" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I111" s="31" t="inlineStr"/>
+      <c r="I111" s="32" t="inlineStr"/>
       <c r="J111" s="8" t="n"/>
-      <c r="K111" s="8" t="n"/>
+      <c r="K111" s="34" t="n">
+        <v>391</v>
+      </c>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
       <c r="N111" s="8" t="n"/>
@@ -5271,21 +5438,23 @@
       <c r="F112" s="8" t="n">
         <v>582</v>
       </c>
-      <c r="G112" s="30" t="n">
+      <c r="G112" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H112" s="30" t="inlineStr">
+      <c r="H112" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I112" s="31" t="inlineStr">
+      <c r="I112" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J112" s="8" t="n"/>
-      <c r="K112" s="8" t="n"/>
+      <c r="K112" s="34" t="n">
+        <v>582</v>
+      </c>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
       <c r="N112" s="8" t="n"/>
@@ -5315,17 +5484,19 @@
       <c r="F113" s="8" t="n">
         <v>818</v>
       </c>
-      <c r="G113" s="30" t="n">
+      <c r="G113" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H113" s="30" t="inlineStr">
+      <c r="H113" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I113" s="31" t="inlineStr"/>
+      <c r="I113" s="32" t="inlineStr"/>
       <c r="J113" s="8" t="n"/>
-      <c r="K113" s="8" t="n"/>
+      <c r="K113" s="34" t="n">
+        <v>818</v>
+      </c>
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
       <c r="N113" s="8" t="n"/>
@@ -5355,17 +5526,19 @@
       <c r="F114" s="8" t="n">
         <v>666</v>
       </c>
-      <c r="G114" s="29" t="n">
+      <c r="G114" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H114" s="31" t="inlineStr">
+      <c r="H114" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I114" s="31" t="inlineStr"/>
+      <c r="I114" s="32" t="inlineStr"/>
       <c r="J114" s="8" t="n"/>
-      <c r="K114" s="8" t="n"/>
+      <c r="K114" s="34" t="n">
+        <v>666</v>
+      </c>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
       <c r="N114" s="8" t="n"/>
@@ -5395,21 +5568,23 @@
       <c r="F115" s="8" t="n">
         <v>1133</v>
       </c>
-      <c r="G115" s="30" t="n">
+      <c r="G115" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H115" s="30" t="inlineStr">
+      <c r="H115" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I115" s="31" t="inlineStr">
+      <c r="I115" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J115" s="8" t="n"/>
-      <c r="K115" s="8" t="n"/>
+      <c r="K115" s="34" t="n">
+        <v>1133</v>
+      </c>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
       <c r="N115" s="8" t="n"/>
@@ -5439,17 +5614,19 @@
       <c r="F116" s="8" t="n">
         <v>262</v>
       </c>
-      <c r="G116" s="30" t="n">
+      <c r="G116" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H116" s="30" t="inlineStr">
+      <c r="H116" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I116" s="31" t="inlineStr"/>
+      <c r="I116" s="32" t="inlineStr"/>
       <c r="J116" s="8" t="n"/>
-      <c r="K116" s="8" t="n"/>
+      <c r="K116" s="34" t="n">
+        <v>262</v>
+      </c>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n"/>
@@ -5479,21 +5656,23 @@
       <c r="F117" s="8" t="n">
         <v>1385</v>
       </c>
-      <c r="G117" s="30" t="n">
+      <c r="G117" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H117" s="30" t="inlineStr">
+      <c r="H117" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I117" s="31" t="inlineStr">
+      <c r="I117" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J117" s="8" t="n"/>
-      <c r="K117" s="8" t="n"/>
+      <c r="K117" s="34" t="n">
+        <v>1385</v>
+      </c>
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
       <c r="N117" s="8" t="n"/>
@@ -5523,17 +5702,19 @@
       <c r="F118" s="8" t="n">
         <v>2297</v>
       </c>
-      <c r="G118" s="29" t="n">
+      <c r="G118" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H118" s="31" t="inlineStr">
+      <c r="H118" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I118" s="31" t="inlineStr"/>
+      <c r="I118" s="32" t="inlineStr"/>
       <c r="J118" s="8" t="n"/>
-      <c r="K118" s="8" t="n"/>
+      <c r="K118" s="34" t="n">
+        <v>2297</v>
+      </c>
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n"/>
@@ -5597,21 +5778,23 @@
       <c r="F120" s="8" t="n">
         <v>3600</v>
       </c>
-      <c r="G120" s="30" t="n">
+      <c r="G120" s="31" t="n">
         <v>45826</v>
       </c>
-      <c r="H120" s="30" t="inlineStr">
+      <c r="H120" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I120" s="31" t="inlineStr">
+      <c r="I120" s="32" t="inlineStr">
         <is>
           <t>002438</t>
         </is>
       </c>
       <c r="J120" s="8" t="n"/>
-      <c r="K120" s="8" t="n"/>
+      <c r="K120" s="34" t="n">
+        <v>3600</v>
+      </c>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n"/>
@@ -5913,17 +6096,19 @@
       <c r="F129" s="8" t="n">
         <v>8737</v>
       </c>
-      <c r="G129" s="29" t="n">
+      <c r="G129" s="30" t="n">
         <v>45829</v>
       </c>
-      <c r="H129" s="31" t="inlineStr">
+      <c r="H129" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I129" s="31" t="inlineStr"/>
+      <c r="I129" s="32" t="inlineStr"/>
       <c r="J129" s="8" t="n"/>
-      <c r="K129" s="8" t="n"/>
+      <c r="K129" s="34" t="n">
+        <v>8737</v>
+      </c>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n"/>
@@ -5953,17 +6138,19 @@
       <c r="F130" s="8" t="n">
         <v>1511</v>
       </c>
-      <c r="G130" s="30" t="n">
+      <c r="G130" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H130" s="30" t="inlineStr">
+      <c r="H130" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I130" s="31" t="inlineStr"/>
+      <c r="I130" s="32" t="inlineStr"/>
       <c r="J130" s="8" t="n"/>
-      <c r="K130" s="8" t="n"/>
+      <c r="K130" s="34" t="n">
+        <v>1511</v>
+      </c>
       <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n"/>
@@ -5993,17 +6180,19 @@
       <c r="F131" s="8" t="n">
         <v>759</v>
       </c>
-      <c r="G131" s="29" t="n">
+      <c r="G131" s="30" t="n">
         <v>45820</v>
       </c>
-      <c r="H131" s="31" t="inlineStr">
+      <c r="H131" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I131" s="31" t="inlineStr"/>
+      <c r="I131" s="32" t="inlineStr"/>
       <c r="J131" s="8" t="n"/>
-      <c r="K131" s="8" t="n"/>
+      <c r="K131" s="34" t="n">
+        <v>759</v>
+      </c>
       <c r="L131" s="8" t="n"/>
       <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n"/>
@@ -6033,21 +6222,23 @@
       <c r="F132" s="8" t="n">
         <v>1711</v>
       </c>
-      <c r="G132" s="30" t="n">
+      <c r="G132" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H132" s="30" t="inlineStr">
+      <c r="H132" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I132" s="31" t="inlineStr">
+      <c r="I132" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J132" s="8" t="n"/>
-      <c r="K132" s="8" t="n"/>
+      <c r="K132" s="34" t="n">
+        <v>1711</v>
+      </c>
       <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n"/>
@@ -6077,21 +6268,23 @@
       <c r="F133" s="8" t="n">
         <v>159</v>
       </c>
-      <c r="G133" s="30" t="n">
+      <c r="G133" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H133" s="30" t="inlineStr">
+      <c r="H133" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I133" s="31" t="inlineStr">
+      <c r="I133" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J133" s="8" t="n"/>
-      <c r="K133" s="8" t="n"/>
+      <c r="K133" s="34" t="n">
+        <v>159</v>
+      </c>
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n"/>
@@ -6121,17 +6314,19 @@
       <c r="F134" s="8" t="n">
         <v>1487</v>
       </c>
-      <c r="G134" s="29" t="n">
+      <c r="G134" s="30" t="n">
         <v>45834</v>
       </c>
-      <c r="H134" s="31" t="inlineStr">
+      <c r="H134" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I134" s="31" t="inlineStr"/>
+      <c r="I134" s="32" t="inlineStr"/>
       <c r="J134" s="8" t="n"/>
-      <c r="K134" s="8" t="n"/>
+      <c r="K134" s="34" t="n">
+        <v>1487</v>
+      </c>
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n"/>
@@ -6161,21 +6356,23 @@
       <c r="F135" s="8" t="n">
         <v>3654</v>
       </c>
-      <c r="G135" s="30" t="n">
+      <c r="G135" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H135" s="30" t="inlineStr">
+      <c r="H135" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I135" s="31" t="inlineStr">
+      <c r="I135" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J135" s="8" t="n"/>
-      <c r="K135" s="8" t="n"/>
+      <c r="K135" s="34" t="n">
+        <v>3654</v>
+      </c>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n"/>
@@ -6239,23 +6436,25 @@
       <c r="F137" s="8" t="n">
         <v>5071</v>
       </c>
-      <c r="G137" s="30" t="n">
+      <c r="G137" s="31" t="n">
         <v>45828</v>
       </c>
-      <c r="H137" s="30" t="inlineStr">
+      <c r="H137" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I137" s="31" t="inlineStr">
+      <c r="I137" s="32" t="inlineStr">
         <is>
           <t>002384</t>
         </is>
       </c>
-      <c r="J137" s="32" t="n">
+      <c r="J137" s="33" t="n">
         <v>25000</v>
       </c>
-      <c r="K137" s="8" t="n"/>
+      <c r="K137" s="34" t="n">
+        <v>272</v>
+      </c>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n"/>
@@ -6319,21 +6518,23 @@
       <c r="F139" s="8" t="n">
         <v>5617</v>
       </c>
-      <c r="G139" s="30" t="n">
+      <c r="G139" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H139" s="30" t="inlineStr">
+      <c r="H139" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I139" s="31" t="inlineStr">
+      <c r="I139" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J139" s="8" t="n"/>
-      <c r="K139" s="8" t="n"/>
+      <c r="K139" s="34" t="n">
+        <v>5617</v>
+      </c>
       <c r="L139" s="8" t="n"/>
       <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n"/>
@@ -6363,21 +6564,23 @@
       <c r="F140" s="8" t="n">
         <v>6371</v>
       </c>
-      <c r="G140" s="30" t="n">
+      <c r="G140" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H140" s="30" t="inlineStr">
+      <c r="H140" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I140" s="31" t="inlineStr">
+      <c r="I140" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J140" s="8" t="n"/>
-      <c r="K140" s="8" t="n"/>
+      <c r="K140" s="34" t="n">
+        <v>6371</v>
+      </c>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n"/>
@@ -6407,17 +6610,19 @@
       <c r="F141" s="8" t="n">
         <v>1168</v>
       </c>
-      <c r="G141" s="29" t="n">
+      <c r="G141" s="30" t="n">
         <v>45822</v>
       </c>
-      <c r="H141" s="31" t="inlineStr">
+      <c r="H141" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I141" s="31" t="inlineStr"/>
+      <c r="I141" s="32" t="inlineStr"/>
       <c r="J141" s="8" t="n"/>
-      <c r="K141" s="8" t="n"/>
+      <c r="K141" s="34" t="n">
+        <v>1168</v>
+      </c>
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n"/>
@@ -6447,23 +6652,25 @@
       <c r="F142" s="8" t="n">
         <v>1752</v>
       </c>
-      <c r="G142" s="29" t="n">
+      <c r="G142" s="30" t="n">
         <v>45828</v>
       </c>
-      <c r="H142" s="31" t="inlineStr">
+      <c r="H142" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I142" s="31" t="inlineStr">
+      <c r="I142" s="32" t="inlineStr">
         <is>
           <t>002384</t>
         </is>
       </c>
-      <c r="J142" s="32" t="n">
+      <c r="J142" s="33" t="n">
         <v>25000</v>
       </c>
-      <c r="K142" s="8" t="n"/>
+      <c r="K142" s="34" t="n">
+        <v>6593</v>
+      </c>
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n"/>
@@ -6493,17 +6700,19 @@
       <c r="F143" s="8" t="n">
         <v>697</v>
       </c>
-      <c r="G143" s="29" t="n">
+      <c r="G143" s="30" t="n">
         <v>45829</v>
       </c>
-      <c r="H143" s="31" t="inlineStr">
+      <c r="H143" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I143" s="31" t="inlineStr"/>
+      <c r="I143" s="32" t="inlineStr"/>
       <c r="J143" s="8" t="n"/>
-      <c r="K143" s="8" t="n"/>
+      <c r="K143" s="34" t="n">
+        <v>697</v>
+      </c>
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n"/>
@@ -6533,17 +6742,19 @@
       <c r="F144" s="8" t="n">
         <v>2312</v>
       </c>
-      <c r="G144" s="29" t="n">
+      <c r="G144" s="30" t="n">
         <v>45829</v>
       </c>
-      <c r="H144" s="31" t="inlineStr">
+      <c r="H144" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I144" s="31" t="inlineStr"/>
+      <c r="I144" s="32" t="inlineStr"/>
       <c r="J144" s="8" t="n"/>
-      <c r="K144" s="8" t="n"/>
+      <c r="K144" s="34" t="n">
+        <v>2042</v>
+      </c>
       <c r="L144" s="8" t="n"/>
       <c r="M144" s="8" t="n"/>
       <c r="N144" s="8" t="n"/>
@@ -6573,21 +6784,23 @@
       <c r="F145" s="8" t="n">
         <v>593</v>
       </c>
-      <c r="G145" s="30" t="n">
+      <c r="G145" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H145" s="30" t="inlineStr">
+      <c r="H145" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I145" s="31" t="inlineStr">
+      <c r="I145" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J145" s="8" t="n"/>
-      <c r="K145" s="8" t="n"/>
+      <c r="K145" s="34" t="n">
+        <v>593</v>
+      </c>
       <c r="L145" s="8" t="n"/>
       <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n"/>
@@ -6617,21 +6830,23 @@
       <c r="F146" s="8" t="n">
         <v>6008</v>
       </c>
-      <c r="G146" s="30" t="n">
+      <c r="G146" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H146" s="30" t="inlineStr">
+      <c r="H146" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I146" s="31" t="inlineStr">
+      <c r="I146" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J146" s="8" t="n"/>
-      <c r="K146" s="8" t="n"/>
+      <c r="K146" s="34" t="n">
+        <v>6008</v>
+      </c>
       <c r="L146" s="8" t="n"/>
       <c r="M146" s="8" t="n"/>
       <c r="N146" s="8" t="n"/>
@@ -6661,17 +6876,19 @@
       <c r="F147" s="8" t="n">
         <v>515</v>
       </c>
-      <c r="G147" s="29" t="n">
+      <c r="G147" s="30" t="n">
         <v>45827</v>
       </c>
-      <c r="H147" s="31" t="inlineStr">
+      <c r="H147" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I147" s="31" t="inlineStr"/>
+      <c r="I147" s="32" t="inlineStr"/>
       <c r="J147" s="8" t="n"/>
-      <c r="K147" s="8" t="n"/>
+      <c r="K147" s="34" t="n">
+        <v>515</v>
+      </c>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n"/>
@@ -6701,21 +6918,23 @@
       <c r="F148" s="8" t="n">
         <v>1753</v>
       </c>
-      <c r="G148" s="30" t="n">
+      <c r="G148" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H148" s="30" t="inlineStr">
+      <c r="H148" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I148" s="31" t="inlineStr">
+      <c r="I148" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J148" s="8" t="n"/>
-      <c r="K148" s="8" t="n"/>
+      <c r="K148" s="34" t="n">
+        <v>1753</v>
+      </c>
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
       <c r="N148" s="8" t="n"/>
@@ -6745,17 +6964,19 @@
       <c r="F149" s="8" t="n">
         <v>796</v>
       </c>
-      <c r="G149" s="29" t="n">
+      <c r="G149" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H149" s="31" t="inlineStr">
+      <c r="H149" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I149" s="31" t="inlineStr"/>
+      <c r="I149" s="32" t="inlineStr"/>
       <c r="J149" s="8" t="n"/>
-      <c r="K149" s="8" t="n"/>
+      <c r="K149" s="34" t="n">
+        <v>796</v>
+      </c>
       <c r="L149" s="8" t="n"/>
       <c r="M149" s="8" t="n"/>
       <c r="N149" s="8" t="n"/>
@@ -6785,17 +7006,19 @@
       <c r="F150" s="8" t="n">
         <v>862</v>
       </c>
-      <c r="G150" s="30" t="n">
+      <c r="G150" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H150" s="30" t="inlineStr">
+      <c r="H150" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I150" s="31" t="inlineStr"/>
+      <c r="I150" s="32" t="inlineStr"/>
       <c r="J150" s="8" t="n"/>
-      <c r="K150" s="8" t="n"/>
+      <c r="K150" s="34" t="n">
+        <v>862</v>
+      </c>
       <c r="L150" s="8" t="n"/>
       <c r="M150" s="8" t="n"/>
       <c r="N150" s="8" t="n"/>
@@ -6859,21 +7082,23 @@
       <c r="F152" s="8" t="n">
         <v>1714</v>
       </c>
-      <c r="G152" s="30" t="n">
+      <c r="G152" s="31" t="n">
         <v>45835</v>
       </c>
-      <c r="H152" s="30" t="inlineStr">
+      <c r="H152" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I152" s="31" t="inlineStr">
+      <c r="I152" s="32" t="inlineStr">
         <is>
           <t>002459</t>
         </is>
       </c>
       <c r="J152" s="8" t="n"/>
-      <c r="K152" s="8" t="n"/>
+      <c r="K152" s="34" t="n">
+        <v>1714</v>
+      </c>
       <c r="L152" s="8" t="n"/>
       <c r="M152" s="8" t="n"/>
       <c r="N152" s="8" t="n"/>
@@ -6971,21 +7196,23 @@
       <c r="F155" s="8" t="n">
         <v>4358</v>
       </c>
-      <c r="G155" s="30" t="n">
+      <c r="G155" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H155" s="30" t="inlineStr">
+      <c r="H155" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I155" s="31" t="inlineStr">
+      <c r="I155" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J155" s="8" t="n"/>
-      <c r="K155" s="8" t="n"/>
+      <c r="K155" s="34" t="n">
+        <v>4358</v>
+      </c>
       <c r="L155" s="8" t="n"/>
       <c r="M155" s="8" t="n"/>
       <c r="N155" s="8" t="n"/>
@@ -7015,17 +7242,19 @@
       <c r="F156" s="8" t="n">
         <v>3717</v>
       </c>
-      <c r="G156" s="30" t="n">
+      <c r="G156" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H156" s="30" t="inlineStr">
+      <c r="H156" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I156" s="31" t="inlineStr"/>
+      <c r="I156" s="32" t="inlineStr"/>
       <c r="J156" s="8" t="n"/>
-      <c r="K156" s="8" t="n"/>
+      <c r="K156" s="34" t="n">
+        <v>3717</v>
+      </c>
       <c r="L156" s="8" t="n"/>
       <c r="M156" s="8" t="n"/>
       <c r="N156" s="8" t="n"/>
@@ -7055,17 +7284,19 @@
       <c r="F157" s="8" t="n">
         <v>738</v>
       </c>
-      <c r="G157" s="29" t="n">
+      <c r="G157" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H157" s="31" t="inlineStr">
+      <c r="H157" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I157" s="31" t="inlineStr"/>
+      <c r="I157" s="32" t="inlineStr"/>
       <c r="J157" s="8" t="n"/>
-      <c r="K157" s="8" t="n"/>
+      <c r="K157" s="34" t="n">
+        <v>738</v>
+      </c>
       <c r="L157" s="8" t="n"/>
       <c r="M157" s="8" t="n"/>
       <c r="N157" s="8" t="n"/>
@@ -7095,17 +7326,19 @@
       <c r="F158" s="8" t="n">
         <v>785</v>
       </c>
-      <c r="G158" s="29" t="n">
+      <c r="G158" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H158" s="31" t="inlineStr">
+      <c r="H158" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I158" s="31" t="inlineStr"/>
+      <c r="I158" s="32" t="inlineStr"/>
       <c r="J158" s="8" t="n"/>
-      <c r="K158" s="8" t="n"/>
+      <c r="K158" s="34" t="n">
+        <v>785</v>
+      </c>
       <c r="L158" s="8" t="n"/>
       <c r="M158" s="8" t="n"/>
       <c r="N158" s="8" t="n"/>
@@ -7135,21 +7368,23 @@
       <c r="F159" s="8" t="n">
         <v>396</v>
       </c>
-      <c r="G159" s="30" t="n">
+      <c r="G159" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H159" s="30" t="inlineStr">
+      <c r="H159" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I159" s="31" t="inlineStr">
+      <c r="I159" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J159" s="8" t="n"/>
-      <c r="K159" s="8" t="n"/>
+      <c r="K159" s="34" t="n">
+        <v>396</v>
+      </c>
       <c r="L159" s="8" t="n"/>
       <c r="M159" s="8" t="n"/>
       <c r="N159" s="8" t="n"/>
@@ -7179,17 +7414,19 @@
       <c r="F160" s="8" t="n">
         <v>2364</v>
       </c>
-      <c r="G160" s="29" t="n">
+      <c r="G160" s="30" t="n">
         <v>45827</v>
       </c>
-      <c r="H160" s="31" t="inlineStr">
+      <c r="H160" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I160" s="31" t="inlineStr"/>
+      <c r="I160" s="32" t="inlineStr"/>
       <c r="J160" s="8" t="n"/>
-      <c r="K160" s="8" t="n"/>
+      <c r="K160" s="34" t="n">
+        <v>2364</v>
+      </c>
       <c r="L160" s="8" t="n"/>
       <c r="M160" s="8" t="n"/>
       <c r="N160" s="8" t="n"/>
@@ -7219,17 +7456,19 @@
       <c r="F161" s="8" t="n">
         <v>5124</v>
       </c>
-      <c r="G161" s="29" t="n">
+      <c r="G161" s="30" t="n">
         <v>45825</v>
       </c>
-      <c r="H161" s="31" t="inlineStr">
+      <c r="H161" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I161" s="31" t="inlineStr"/>
+      <c r="I161" s="32" t="inlineStr"/>
       <c r="J161" s="8" t="n"/>
-      <c r="K161" s="8" t="n"/>
+      <c r="K161" s="34" t="n">
+        <v>5122</v>
+      </c>
       <c r="L161" s="8" t="n"/>
       <c r="M161" s="8" t="n"/>
       <c r="N161" s="8" t="n"/>
@@ -7429,21 +7668,23 @@
       <c r="F167" s="8" t="n">
         <v>3590</v>
       </c>
-      <c r="G167" s="30" t="n">
+      <c r="G167" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H167" s="30" t="inlineStr">
+      <c r="H167" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I167" s="31" t="inlineStr">
+      <c r="I167" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J167" s="8" t="n"/>
-      <c r="K167" s="8" t="n"/>
+      <c r="K167" s="34" t="n">
+        <v>3590</v>
+      </c>
       <c r="L167" s="8" t="n"/>
       <c r="M167" s="8" t="n"/>
       <c r="N167" s="8" t="n"/>
@@ -7473,21 +7714,23 @@
       <c r="F168" s="8" t="n">
         <v>7709</v>
       </c>
-      <c r="G168" s="30" t="n">
+      <c r="G168" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H168" s="30" t="inlineStr">
+      <c r="H168" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I168" s="31" t="inlineStr">
+      <c r="I168" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J168" s="8" t="n"/>
-      <c r="K168" s="8" t="n"/>
+      <c r="K168" s="34" t="n">
+        <v>7709</v>
+      </c>
       <c r="L168" s="8" t="n"/>
       <c r="M168" s="8" t="n"/>
       <c r="N168" s="8" t="n"/>
@@ -7517,17 +7760,19 @@
       <c r="F169" s="8" t="n">
         <v>5281</v>
       </c>
-      <c r="G169" s="29" t="n">
+      <c r="G169" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H169" s="31" t="inlineStr">
+      <c r="H169" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I169" s="31" t="inlineStr"/>
+      <c r="I169" s="32" t="inlineStr"/>
       <c r="J169" s="8" t="n"/>
-      <c r="K169" s="8" t="n"/>
+      <c r="K169" s="34" t="n">
+        <v>5281</v>
+      </c>
       <c r="L169" s="8" t="n"/>
       <c r="M169" s="8" t="n"/>
       <c r="N169" s="8" t="n"/>
@@ -7557,17 +7802,19 @@
       <c r="F170" s="8" t="n">
         <v>943</v>
       </c>
-      <c r="G170" s="30" t="n">
+      <c r="G170" s="31" t="n">
         <v>45832</v>
       </c>
-      <c r="H170" s="30" t="inlineStr">
+      <c r="H170" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I170" s="31" t="inlineStr"/>
+      <c r="I170" s="32" t="inlineStr"/>
       <c r="J170" s="8" t="n"/>
-      <c r="K170" s="8" t="n"/>
+      <c r="K170" s="34" t="n">
+        <v>943</v>
+      </c>
       <c r="L170" s="8" t="n"/>
       <c r="M170" s="8" t="n"/>
       <c r="N170" s="8" t="n"/>
@@ -7597,17 +7844,19 @@
       <c r="F171" s="8" t="n">
         <v>423</v>
       </c>
-      <c r="G171" s="29" t="n">
+      <c r="G171" s="30" t="n">
         <v>45827</v>
       </c>
-      <c r="H171" s="31" t="inlineStr">
+      <c r="H171" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I171" s="31" t="inlineStr"/>
+      <c r="I171" s="32" t="inlineStr"/>
       <c r="J171" s="8" t="n"/>
-      <c r="K171" s="8" t="n"/>
+      <c r="K171" s="34" t="n">
+        <v>423</v>
+      </c>
       <c r="L171" s="8" t="n"/>
       <c r="M171" s="8" t="n"/>
       <c r="N171" s="8" t="n"/>
@@ -7637,21 +7886,23 @@
       <c r="F172" s="8" t="n">
         <v>520</v>
       </c>
-      <c r="G172" s="30" t="n">
+      <c r="G172" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H172" s="30" t="inlineStr">
+      <c r="H172" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I172" s="31" t="inlineStr">
+      <c r="I172" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J172" s="8" t="n"/>
-      <c r="K172" s="8" t="n"/>
+      <c r="K172" s="34" t="n">
+        <v>520</v>
+      </c>
       <c r="L172" s="8" t="n"/>
       <c r="M172" s="8" t="n"/>
       <c r="N172" s="8" t="n"/>
@@ -7681,17 +7932,19 @@
       <c r="F173" s="8" t="n">
         <v>320</v>
       </c>
-      <c r="G173" s="30" t="n">
+      <c r="G173" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H173" s="30" t="inlineStr">
+      <c r="H173" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I173" s="31" t="inlineStr"/>
+      <c r="I173" s="32" t="inlineStr"/>
       <c r="J173" s="8" t="n"/>
-      <c r="K173" s="8" t="n"/>
+      <c r="K173" s="34" t="n">
+        <v>320</v>
+      </c>
       <c r="L173" s="8" t="n"/>
       <c r="M173" s="8" t="n"/>
       <c r="N173" s="8" t="n"/>
@@ -7721,17 +7974,19 @@
       <c r="F174" s="8" t="n">
         <v>178</v>
       </c>
-      <c r="G174" s="29" t="n">
+      <c r="G174" s="30" t="n">
         <v>45839</v>
       </c>
-      <c r="H174" s="31" t="inlineStr">
+      <c r="H174" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I174" s="31" t="inlineStr"/>
+      <c r="I174" s="32" t="inlineStr"/>
       <c r="J174" s="8" t="n"/>
-      <c r="K174" s="8" t="n"/>
+      <c r="K174" s="34" t="n">
+        <v>178</v>
+      </c>
       <c r="L174" s="8" t="n"/>
       <c r="M174" s="8" t="n"/>
       <c r="N174" s="8" t="n"/>
@@ -7795,17 +8050,19 @@
       <c r="F176" s="8" t="n">
         <v>8610</v>
       </c>
-      <c r="G176" s="29" t="n">
+      <c r="G176" s="30" t="n">
         <v>45829</v>
       </c>
-      <c r="H176" s="31" t="inlineStr">
+      <c r="H176" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I176" s="31" t="inlineStr"/>
+      <c r="I176" s="32" t="inlineStr"/>
       <c r="J176" s="8" t="n"/>
-      <c r="K176" s="8" t="n"/>
+      <c r="K176" s="34" t="n">
+        <v>8610</v>
+      </c>
       <c r="L176" s="8" t="n"/>
       <c r="M176" s="8" t="n"/>
       <c r="N176" s="8" t="n"/>
@@ -7835,23 +8092,25 @@
       <c r="F177" s="8" t="n">
         <v>7197</v>
       </c>
-      <c r="G177" s="30" t="n">
+      <c r="G177" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H177" s="30" t="inlineStr">
+      <c r="H177" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I177" s="31" t="inlineStr">
+      <c r="I177" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J177" s="32" t="n">
+      <c r="J177" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K177" s="8" t="n"/>
+      <c r="K177" s="34" t="n">
+        <v>7197</v>
+      </c>
       <c r="L177" s="8" t="n"/>
       <c r="M177" s="8" t="n"/>
       <c r="N177" s="8" t="n"/>
@@ -7881,21 +8140,23 @@
       <c r="F178" s="8" t="n">
         <v>21179</v>
       </c>
-      <c r="G178" s="30" t="n">
+      <c r="G178" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H178" s="30" t="inlineStr">
+      <c r="H178" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I178" s="31" t="inlineStr">
+      <c r="I178" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J178" s="8" t="n"/>
-      <c r="K178" s="8" t="n"/>
+      <c r="K178" s="34" t="n">
+        <v>21179</v>
+      </c>
       <c r="L178" s="8" t="n"/>
       <c r="M178" s="8" t="n"/>
       <c r="N178" s="8" t="n"/>
@@ -8061,17 +8322,19 @@
       <c r="F183" s="8" t="n">
         <v>628</v>
       </c>
-      <c r="G183" s="29" t="n">
+      <c r="G183" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H183" s="31" t="inlineStr">
+      <c r="H183" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I183" s="31" t="inlineStr"/>
+      <c r="I183" s="32" t="inlineStr"/>
       <c r="J183" s="8" t="n"/>
-      <c r="K183" s="8" t="n"/>
+      <c r="K183" s="34" t="n">
+        <v>628</v>
+      </c>
       <c r="L183" s="8" t="n"/>
       <c r="M183" s="8" t="n"/>
       <c r="N183" s="8" t="n"/>
@@ -8101,21 +8364,23 @@
       <c r="F184" s="8" t="n">
         <v>5965</v>
       </c>
-      <c r="G184" s="30" t="n">
+      <c r="G184" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H184" s="30" t="inlineStr">
+      <c r="H184" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I184" s="31" t="inlineStr">
+      <c r="I184" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J184" s="8" t="n"/>
-      <c r="K184" s="8" t="n"/>
+      <c r="K184" s="34" t="n">
+        <v>5965</v>
+      </c>
       <c r="L184" s="8" t="n"/>
       <c r="M184" s="8" t="n"/>
       <c r="N184" s="8" t="n"/>
@@ -8145,21 +8410,23 @@
       <c r="F185" s="8" t="n">
         <v>2312</v>
       </c>
-      <c r="G185" s="30" t="n">
+      <c r="G185" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H185" s="30" t="inlineStr">
+      <c r="H185" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I185" s="31" t="inlineStr">
+      <c r="I185" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J185" s="8" t="n"/>
-      <c r="K185" s="8" t="n"/>
+      <c r="K185" s="34" t="n">
+        <v>2312</v>
+      </c>
       <c r="L185" s="8" t="n"/>
       <c r="M185" s="8" t="n"/>
       <c r="N185" s="8" t="n"/>
@@ -8189,17 +8456,19 @@
       <c r="F186" s="8" t="n">
         <v>1596</v>
       </c>
-      <c r="G186" s="30" t="n">
+      <c r="G186" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H186" s="30" t="inlineStr">
+      <c r="H186" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I186" s="31" t="inlineStr"/>
+      <c r="I186" s="32" t="inlineStr"/>
       <c r="J186" s="8" t="n"/>
-      <c r="K186" s="8" t="n"/>
+      <c r="K186" s="34" t="n">
+        <v>1596</v>
+      </c>
       <c r="L186" s="8" t="n"/>
       <c r="M186" s="8" t="n"/>
       <c r="N186" s="8" t="n"/>
@@ -8229,21 +8498,23 @@
       <c r="F187" s="8" t="n">
         <v>186</v>
       </c>
-      <c r="G187" s="30" t="n">
+      <c r="G187" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H187" s="30" t="inlineStr">
+      <c r="H187" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I187" s="31" t="inlineStr">
+      <c r="I187" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J187" s="8" t="n"/>
-      <c r="K187" s="8" t="n"/>
+      <c r="K187" s="34" t="n">
+        <v>186</v>
+      </c>
       <c r="L187" s="8" t="n"/>
       <c r="M187" s="8" t="n"/>
       <c r="N187" s="8" t="n"/>
@@ -8307,21 +8578,23 @@
       <c r="F189" s="8" t="n">
         <v>2657</v>
       </c>
-      <c r="G189" s="30" t="n">
+      <c r="G189" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H189" s="30" t="inlineStr">
+      <c r="H189" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I189" s="31" t="inlineStr">
+      <c r="I189" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J189" s="8" t="n"/>
-      <c r="K189" s="8" t="n"/>
+      <c r="K189" s="34" t="n">
+        <v>2657</v>
+      </c>
       <c r="L189" s="8" t="n"/>
       <c r="M189" s="8" t="n"/>
       <c r="N189" s="8" t="n"/>
@@ -8385,21 +8658,23 @@
       <c r="F191" s="8" t="n">
         <v>1047</v>
       </c>
-      <c r="G191" s="30" t="n">
+      <c r="G191" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H191" s="30" t="inlineStr">
+      <c r="H191" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I191" s="31" t="inlineStr">
+      <c r="I191" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J191" s="8" t="n"/>
-      <c r="K191" s="8" t="n"/>
+      <c r="K191" s="34" t="n">
+        <v>1047</v>
+      </c>
       <c r="L191" s="8" t="n"/>
       <c r="M191" s="8" t="n"/>
       <c r="N191" s="8" t="n"/>
@@ -8429,17 +8704,19 @@
       <c r="F192" s="8" t="n">
         <v>2157</v>
       </c>
-      <c r="G192" s="29" t="n">
+      <c r="G192" s="30" t="n">
         <v>45831</v>
       </c>
-      <c r="H192" s="31" t="inlineStr">
+      <c r="H192" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I192" s="31" t="inlineStr"/>
+      <c r="I192" s="32" t="inlineStr"/>
       <c r="J192" s="8" t="n"/>
-      <c r="K192" s="8" t="n"/>
+      <c r="K192" s="34" t="n">
+        <v>2157</v>
+      </c>
       <c r="L192" s="8" t="n"/>
       <c r="M192" s="8" t="n"/>
       <c r="N192" s="8" t="n"/>
@@ -8469,17 +8746,19 @@
       <c r="F193" s="8" t="n">
         <v>684</v>
       </c>
-      <c r="G193" s="29" t="n">
+      <c r="G193" s="30" t="n">
         <v>45831</v>
       </c>
-      <c r="H193" s="31" t="inlineStr">
+      <c r="H193" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I193" s="31" t="inlineStr"/>
+      <c r="I193" s="32" t="inlineStr"/>
       <c r="J193" s="8" t="n"/>
-      <c r="K193" s="8" t="n"/>
+      <c r="K193" s="34" t="n">
+        <v>684</v>
+      </c>
       <c r="L193" s="8" t="n"/>
       <c r="M193" s="8" t="n"/>
       <c r="N193" s="8" t="n"/>
@@ -8509,17 +8788,19 @@
       <c r="F194" s="8" t="n">
         <v>2333</v>
       </c>
-      <c r="G194" s="29" t="n">
+      <c r="G194" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H194" s="31" t="inlineStr">
+      <c r="H194" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I194" s="31" t="inlineStr"/>
+      <c r="I194" s="32" t="inlineStr"/>
       <c r="J194" s="8" t="n"/>
-      <c r="K194" s="8" t="n"/>
+      <c r="K194" s="34" t="n">
+        <v>2333</v>
+      </c>
       <c r="L194" s="8" t="n"/>
       <c r="M194" s="8" t="n"/>
       <c r="N194" s="8" t="n"/>
@@ -8549,17 +8830,19 @@
       <c r="F195" s="8" t="n">
         <v>2669</v>
       </c>
-      <c r="G195" s="30" t="n">
+      <c r="G195" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H195" s="30" t="inlineStr">
+      <c r="H195" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I195" s="31" t="inlineStr"/>
+      <c r="I195" s="32" t="inlineStr"/>
       <c r="J195" s="8" t="n"/>
-      <c r="K195" s="8" t="n"/>
+      <c r="K195" s="34" t="n">
+        <v>2669</v>
+      </c>
       <c r="L195" s="8" t="n"/>
       <c r="M195" s="8" t="n"/>
       <c r="N195" s="8" t="n"/>
@@ -8589,17 +8872,19 @@
       <c r="F196" s="8" t="n">
         <v>196</v>
       </c>
-      <c r="G196" s="30" t="n">
+      <c r="G196" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H196" s="30" t="inlineStr">
+      <c r="H196" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I196" s="31" t="inlineStr"/>
+      <c r="I196" s="32" t="inlineStr"/>
       <c r="J196" s="8" t="n"/>
-      <c r="K196" s="8" t="n"/>
+      <c r="K196" s="34" t="n">
+        <v>196</v>
+      </c>
       <c r="L196" s="8" t="n"/>
       <c r="M196" s="8" t="n"/>
       <c r="N196" s="8" t="n"/>
@@ -8629,21 +8914,23 @@
       <c r="F197" s="8" t="n">
         <v>799</v>
       </c>
-      <c r="G197" s="30" t="n">
+      <c r="G197" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H197" s="30" t="inlineStr">
+      <c r="H197" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I197" s="31" t="inlineStr">
+      <c r="I197" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J197" s="8" t="n"/>
-      <c r="K197" s="8" t="n"/>
+      <c r="K197" s="34" t="n">
+        <v>799</v>
+      </c>
       <c r="L197" s="8" t="n"/>
       <c r="M197" s="8" t="n"/>
       <c r="N197" s="8" t="n"/>
@@ -8741,17 +9028,19 @@
       <c r="F200" s="8" t="n">
         <v>1140</v>
       </c>
-      <c r="G200" s="29" t="n">
+      <c r="G200" s="30" t="n">
         <v>45832</v>
       </c>
-      <c r="H200" s="31" t="inlineStr">
+      <c r="H200" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I200" s="31" t="inlineStr"/>
+      <c r="I200" s="32" t="inlineStr"/>
       <c r="J200" s="8" t="n"/>
-      <c r="K200" s="8" t="n"/>
+      <c r="K200" s="34" t="n">
+        <v>1140</v>
+      </c>
       <c r="L200" s="8" t="n"/>
       <c r="M200" s="8" t="n"/>
       <c r="N200" s="8" t="n"/>
@@ -8781,21 +9070,23 @@
       <c r="F201" s="8" t="n">
         <v>4991</v>
       </c>
-      <c r="G201" s="30" t="n">
+      <c r="G201" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H201" s="30" t="inlineStr">
+      <c r="H201" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I201" s="31" t="inlineStr">
+      <c r="I201" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J201" s="8" t="n"/>
-      <c r="K201" s="8" t="n"/>
+      <c r="K201" s="34" t="n">
+        <v>4991</v>
+      </c>
       <c r="L201" s="8" t="n"/>
       <c r="M201" s="8" t="n"/>
       <c r="N201" s="8" t="n"/>
@@ -8825,17 +9116,19 @@
       <c r="F202" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="G202" s="30" t="n">
+      <c r="G202" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H202" s="30" t="inlineStr">
+      <c r="H202" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I202" s="31" t="inlineStr"/>
+      <c r="I202" s="32" t="inlineStr"/>
       <c r="J202" s="8" t="n"/>
-      <c r="K202" s="8" t="n"/>
+      <c r="K202" s="34" t="n">
+        <v>500</v>
+      </c>
       <c r="L202" s="8" t="n"/>
       <c r="M202" s="8" t="n"/>
       <c r="N202" s="8" t="n"/>
@@ -8865,21 +9158,23 @@
       <c r="F203" s="8" t="n">
         <v>357</v>
       </c>
-      <c r="G203" s="30" t="n">
+      <c r="G203" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H203" s="30" t="inlineStr">
+      <c r="H203" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I203" s="31" t="inlineStr">
+      <c r="I203" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J203" s="8" t="n"/>
-      <c r="K203" s="8" t="n"/>
+      <c r="K203" s="34" t="n">
+        <v>357</v>
+      </c>
       <c r="L203" s="8" t="n"/>
       <c r="M203" s="8" t="n"/>
       <c r="N203" s="8" t="n"/>
@@ -8909,17 +9204,19 @@
       <c r="F204" s="8" t="n">
         <v>1382</v>
       </c>
-      <c r="G204" s="29" t="n">
+      <c r="G204" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H204" s="31" t="inlineStr">
+      <c r="H204" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I204" s="31" t="inlineStr"/>
+      <c r="I204" s="32" t="inlineStr"/>
       <c r="J204" s="8" t="n"/>
-      <c r="K204" s="8" t="n"/>
+      <c r="K204" s="34" t="n">
+        <v>1382</v>
+      </c>
       <c r="L204" s="8" t="n"/>
       <c r="M204" s="8" t="n"/>
       <c r="N204" s="8" t="n"/>
@@ -8983,17 +9280,19 @@
       <c r="F206" s="8" t="n">
         <v>2401</v>
       </c>
-      <c r="G206" s="30" t="n">
+      <c r="G206" s="31" t="n">
         <v>45836</v>
       </c>
-      <c r="H206" s="30" t="inlineStr">
+      <c r="H206" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I206" s="31" t="inlineStr"/>
+      <c r="I206" s="32" t="inlineStr"/>
       <c r="J206" s="8" t="n"/>
-      <c r="K206" s="8" t="n"/>
+      <c r="K206" s="34" t="n">
+        <v>2401</v>
+      </c>
       <c r="L206" s="8" t="n"/>
       <c r="M206" s="8" t="n"/>
       <c r="N206" s="8" t="n"/>
@@ -9023,21 +9322,23 @@
       <c r="F207" s="8" t="n">
         <v>724</v>
       </c>
-      <c r="G207" s="30" t="n">
+      <c r="G207" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H207" s="30" t="inlineStr">
+      <c r="H207" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I207" s="31" t="inlineStr">
+      <c r="I207" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J207" s="8" t="n"/>
-      <c r="K207" s="8" t="n"/>
+      <c r="K207" s="34" t="n">
+        <v>724</v>
+      </c>
       <c r="L207" s="8" t="n"/>
       <c r="M207" s="8" t="n"/>
       <c r="N207" s="8" t="n"/>
@@ -9067,21 +9368,23 @@
       <c r="F208" s="8" t="n">
         <v>4730</v>
       </c>
-      <c r="G208" s="30" t="n">
+      <c r="G208" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H208" s="30" t="inlineStr">
+      <c r="H208" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I208" s="31" t="inlineStr">
+      <c r="I208" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J208" s="8" t="n"/>
-      <c r="K208" s="8" t="n"/>
+      <c r="K208" s="34" t="n">
+        <v>4730</v>
+      </c>
       <c r="L208" s="8" t="n"/>
       <c r="M208" s="8" t="n"/>
       <c r="N208" s="8" t="n"/>
@@ -9111,17 +9414,19 @@
       <c r="F209" s="8" t="n">
         <v>1287</v>
       </c>
-      <c r="G209" s="29" t="n">
+      <c r="G209" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H209" s="31" t="inlineStr">
+      <c r="H209" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I209" s="31" t="inlineStr"/>
+      <c r="I209" s="32" t="inlineStr"/>
       <c r="J209" s="8" t="n"/>
-      <c r="K209" s="8" t="n"/>
+      <c r="K209" s="34" t="n">
+        <v>1287</v>
+      </c>
       <c r="L209" s="8" t="n"/>
       <c r="M209" s="8" t="n"/>
       <c r="N209" s="8" t="n"/>
@@ -9151,17 +9456,19 @@
       <c r="F210" s="8" t="n">
         <v>2121</v>
       </c>
-      <c r="G210" s="30" t="n">
+      <c r="G210" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H210" s="30" t="inlineStr">
+      <c r="H210" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I210" s="31" t="inlineStr"/>
+      <c r="I210" s="32" t="inlineStr"/>
       <c r="J210" s="8" t="n"/>
-      <c r="K210" s="8" t="n"/>
+      <c r="K210" s="34" t="n">
+        <v>2121</v>
+      </c>
       <c r="L210" s="8" t="n"/>
       <c r="M210" s="8" t="n"/>
       <c r="N210" s="8" t="n"/>
@@ -9191,23 +9498,25 @@
       <c r="F211" s="8" t="n">
         <v>5448</v>
       </c>
-      <c r="G211" s="30" t="n">
+      <c r="G211" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H211" s="30" t="inlineStr">
+      <c r="H211" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I211" s="31" t="inlineStr">
+      <c r="I211" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J211" s="32" t="n">
+      <c r="J211" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K211" s="8" t="n"/>
+      <c r="K211" s="34" t="n">
+        <v>5448</v>
+      </c>
       <c r="L211" s="8" t="n"/>
       <c r="M211" s="8" t="n"/>
       <c r="N211" s="8" t="n"/>
@@ -9237,17 +9546,19 @@
       <c r="F212" s="8" t="n">
         <v>4435</v>
       </c>
-      <c r="G212" s="29" t="n">
+      <c r="G212" s="30" t="n">
         <v>45824</v>
       </c>
-      <c r="H212" s="31" t="inlineStr">
+      <c r="H212" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I212" s="31" t="inlineStr"/>
+      <c r="I212" s="32" t="inlineStr"/>
       <c r="J212" s="8" t="n"/>
-      <c r="K212" s="8" t="n"/>
+      <c r="K212" s="34" t="n">
+        <v>4435</v>
+      </c>
       <c r="L212" s="8" t="n"/>
       <c r="M212" s="8" t="n"/>
       <c r="N212" s="8" t="n"/>
@@ -9277,17 +9588,19 @@
       <c r="F213" s="8" t="n">
         <v>7211</v>
       </c>
-      <c r="G213" s="29" t="n">
+      <c r="G213" s="30" t="n">
         <v>45833</v>
       </c>
-      <c r="H213" s="31" t="inlineStr">
+      <c r="H213" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I213" s="31" t="inlineStr"/>
+      <c r="I213" s="32" t="inlineStr"/>
       <c r="J213" s="8" t="n"/>
-      <c r="K213" s="8" t="n"/>
+      <c r="K213" s="34" t="n">
+        <v>653</v>
+      </c>
       <c r="L213" s="8" t="n"/>
       <c r="M213" s="8" t="n"/>
       <c r="N213" s="8" t="n"/>
@@ -9453,17 +9766,19 @@
       <c r="F218" s="8" t="n">
         <v>28073</v>
       </c>
-      <c r="G218" s="30" t="n">
+      <c r="G218" s="31" t="n">
         <v>45854</v>
       </c>
-      <c r="H218" s="30" t="inlineStr">
+      <c r="H218" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I218" s="31" t="inlineStr"/>
+      <c r="I218" s="32" t="inlineStr"/>
       <c r="J218" s="8" t="n"/>
-      <c r="K218" s="8" t="n"/>
+      <c r="K218" s="34" t="n">
+        <v>28073</v>
+      </c>
       <c r="L218" s="8" t="n"/>
       <c r="M218" s="8" t="n"/>
       <c r="N218" s="8" t="n"/>
@@ -9493,17 +9808,19 @@
       <c r="F219" s="8" t="n">
         <v>855</v>
       </c>
-      <c r="G219" s="29" t="n">
+      <c r="G219" s="30" t="n">
         <v>45838</v>
       </c>
-      <c r="H219" s="31" t="inlineStr">
+      <c r="H219" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I219" s="31" t="inlineStr"/>
+      <c r="I219" s="32" t="inlineStr"/>
       <c r="J219" s="8" t="n"/>
-      <c r="K219" s="8" t="n"/>
+      <c r="K219" s="34" t="n">
+        <v>855</v>
+      </c>
       <c r="L219" s="8" t="n"/>
       <c r="M219" s="8" t="n"/>
       <c r="N219" s="8" t="n"/>
@@ -9533,17 +9850,19 @@
       <c r="F220" s="8" t="n">
         <v>2858</v>
       </c>
-      <c r="G220" s="29" t="n">
+      <c r="G220" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H220" s="31" t="inlineStr">
+      <c r="H220" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I220" s="31" t="inlineStr"/>
+      <c r="I220" s="32" t="inlineStr"/>
       <c r="J220" s="8" t="n"/>
-      <c r="K220" s="8" t="n"/>
+      <c r="K220" s="34" t="n">
+        <v>2858</v>
+      </c>
       <c r="L220" s="8" t="n"/>
       <c r="M220" s="8" t="n"/>
       <c r="N220" s="8" t="n"/>
@@ -9573,21 +9892,23 @@
       <c r="F221" s="8" t="n">
         <v>1276</v>
       </c>
-      <c r="G221" s="30" t="n">
+      <c r="G221" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H221" s="30" t="inlineStr">
+      <c r="H221" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I221" s="31" t="inlineStr">
+      <c r="I221" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J221" s="8" t="n"/>
-      <c r="K221" s="8" t="n"/>
+      <c r="K221" s="34" t="n">
+        <v>1276</v>
+      </c>
       <c r="L221" s="8" t="n"/>
       <c r="M221" s="8" t="n"/>
       <c r="N221" s="8" t="n"/>
@@ -9617,21 +9938,23 @@
       <c r="F222" s="8" t="n">
         <v>3044</v>
       </c>
-      <c r="G222" s="30" t="n">
+      <c r="G222" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H222" s="30" t="inlineStr">
+      <c r="H222" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I222" s="31" t="inlineStr">
+      <c r="I222" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J222" s="8" t="n"/>
-      <c r="K222" s="8" t="n"/>
+      <c r="K222" s="34" t="n">
+        <v>3044</v>
+      </c>
       <c r="L222" s="8" t="n"/>
       <c r="M222" s="8" t="n"/>
       <c r="N222" s="8" t="n"/>
@@ -9661,17 +9984,19 @@
       <c r="F223" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="G223" s="30" t="n">
+      <c r="G223" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H223" s="30" t="inlineStr">
+      <c r="H223" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I223" s="31" t="inlineStr"/>
+      <c r="I223" s="32" t="inlineStr"/>
       <c r="J223" s="8" t="n"/>
-      <c r="K223" s="8" t="n"/>
+      <c r="K223" s="34" t="n">
+        <v>176</v>
+      </c>
       <c r="L223" s="8" t="n"/>
       <c r="M223" s="8" t="n"/>
       <c r="N223" s="8" t="n"/>
@@ -9905,17 +10230,19 @@
       <c r="F230" s="8" t="n">
         <v>2098</v>
       </c>
-      <c r="G230" s="29" t="n">
+      <c r="G230" s="30" t="n">
         <v>45835</v>
       </c>
-      <c r="H230" s="31" t="inlineStr">
+      <c r="H230" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I230" s="31" t="inlineStr"/>
+      <c r="I230" s="32" t="inlineStr"/>
       <c r="J230" s="8" t="n"/>
-      <c r="K230" s="8" t="n"/>
+      <c r="K230" s="34" t="n">
+        <v>2098</v>
+      </c>
       <c r="L230" s="8" t="n"/>
       <c r="M230" s="8" t="n"/>
       <c r="N230" s="8" t="n"/>
@@ -9945,17 +10272,19 @@
       <c r="F231" s="8" t="n">
         <v>1673</v>
       </c>
-      <c r="G231" s="29" t="n">
+      <c r="G231" s="30" t="n">
         <v>45838</v>
       </c>
-      <c r="H231" s="31" t="inlineStr">
+      <c r="H231" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I231" s="31" t="inlineStr"/>
+      <c r="I231" s="32" t="inlineStr"/>
       <c r="J231" s="8" t="n"/>
-      <c r="K231" s="8" t="n"/>
+      <c r="K231" s="34" t="n">
+        <v>1673</v>
+      </c>
       <c r="L231" s="8" t="n"/>
       <c r="M231" s="8" t="n"/>
       <c r="N231" s="8" t="n"/>
@@ -9985,17 +10314,19 @@
       <c r="F232" s="8" t="n">
         <v>848</v>
       </c>
-      <c r="G232" s="29" t="n">
+      <c r="G232" s="30" t="n">
         <v>45838</v>
       </c>
-      <c r="H232" s="31" t="inlineStr">
+      <c r="H232" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I232" s="31" t="inlineStr"/>
+      <c r="I232" s="32" t="inlineStr"/>
       <c r="J232" s="8" t="n"/>
-      <c r="K232" s="8" t="n"/>
+      <c r="K232" s="34" t="n">
+        <v>848</v>
+      </c>
       <c r="L232" s="8" t="n"/>
       <c r="M232" s="8" t="n"/>
       <c r="N232" s="8" t="n"/>
@@ -10025,17 +10356,19 @@
       <c r="F233" s="8" t="n">
         <v>1455</v>
       </c>
-      <c r="G233" s="29" t="n">
+      <c r="G233" s="30" t="n">
         <v>45835</v>
       </c>
-      <c r="H233" s="31" t="inlineStr">
+      <c r="H233" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I233" s="31" t="inlineStr"/>
+      <c r="I233" s="32" t="inlineStr"/>
       <c r="J233" s="8" t="n"/>
-      <c r="K233" s="8" t="n"/>
+      <c r="K233" s="34" t="n">
+        <v>1455</v>
+      </c>
       <c r="L233" s="8" t="n"/>
       <c r="M233" s="8" t="n"/>
       <c r="N233" s="8" t="n"/>
@@ -10065,21 +10398,23 @@
       <c r="F234" s="8" t="n">
         <v>8252</v>
       </c>
-      <c r="G234" s="30" t="n">
+      <c r="G234" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H234" s="30" t="inlineStr">
+      <c r="H234" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I234" s="31" t="inlineStr">
+      <c r="I234" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J234" s="8" t="n"/>
-      <c r="K234" s="8" t="n"/>
+      <c r="K234" s="34" t="n">
+        <v>4152</v>
+      </c>
       <c r="L234" s="8" t="n"/>
       <c r="M234" s="8" t="n"/>
       <c r="N234" s="8" t="n"/>
@@ -10143,17 +10478,19 @@
       <c r="F236" s="8" t="n">
         <v>6442</v>
       </c>
-      <c r="G236" s="30" t="n">
+      <c r="G236" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H236" s="30" t="inlineStr">
+      <c r="H236" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I236" s="31" t="inlineStr"/>
+      <c r="I236" s="32" t="inlineStr"/>
       <c r="J236" s="8" t="n"/>
-      <c r="K236" s="8" t="n"/>
+      <c r="K236" s="34" t="n">
+        <v>6442</v>
+      </c>
       <c r="L236" s="8" t="n"/>
       <c r="M236" s="8" t="n"/>
       <c r="N236" s="8" t="n"/>
@@ -10183,21 +10520,23 @@
       <c r="F237" s="8" t="n">
         <v>591</v>
       </c>
-      <c r="G237" s="30" t="n">
+      <c r="G237" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H237" s="30" t="inlineStr">
+      <c r="H237" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I237" s="31" t="inlineStr">
+      <c r="I237" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J237" s="8" t="n"/>
-      <c r="K237" s="8" t="n"/>
+      <c r="K237" s="34" t="n">
+        <v>591</v>
+      </c>
       <c r="L237" s="8" t="n"/>
       <c r="M237" s="8" t="n"/>
       <c r="N237" s="8" t="n"/>
@@ -10227,17 +10566,19 @@
       <c r="F238" s="8" t="n">
         <v>376</v>
       </c>
-      <c r="G238" s="30" t="n">
+      <c r="G238" s="31" t="n">
         <v>45872</v>
       </c>
-      <c r="H238" s="30" t="inlineStr">
+      <c r="H238" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I238" s="31" t="inlineStr"/>
+      <c r="I238" s="32" t="inlineStr"/>
       <c r="J238" s="8" t="n"/>
-      <c r="K238" s="8" t="n"/>
+      <c r="K238" s="34" t="n">
+        <v>376</v>
+      </c>
       <c r="L238" s="8" t="n"/>
       <c r="M238" s="8" t="n"/>
       <c r="N238" s="8" t="n"/>
@@ -10267,17 +10608,19 @@
       <c r="F239" s="8" t="n">
         <v>3350</v>
       </c>
-      <c r="G239" s="29" t="n">
+      <c r="G239" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H239" s="31" t="inlineStr">
+      <c r="H239" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I239" s="31" t="inlineStr"/>
+      <c r="I239" s="32" t="inlineStr"/>
       <c r="J239" s="8" t="n"/>
-      <c r="K239" s="8" t="n"/>
+      <c r="K239" s="34" t="n">
+        <v>3350</v>
+      </c>
       <c r="L239" s="8" t="n"/>
       <c r="M239" s="8" t="n"/>
       <c r="N239" s="8" t="n"/>
@@ -10307,19 +10650,21 @@
       <c r="F240" s="8" t="n">
         <v>3159</v>
       </c>
-      <c r="G240" s="30" t="n">
+      <c r="G240" s="31" t="n">
         <v>45883</v>
       </c>
-      <c r="H240" s="30" t="inlineStr">
+      <c r="H240" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I240" s="31" t="inlineStr"/>
-      <c r="J240" s="32" t="n">
+      <c r="I240" s="32" t="inlineStr"/>
+      <c r="J240" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K240" s="8" t="n"/>
+      <c r="K240" s="34" t="n">
+        <v>3159</v>
+      </c>
       <c r="L240" s="8" t="n"/>
       <c r="M240" s="8" t="n"/>
       <c r="N240" s="8" t="n"/>
@@ -10349,17 +10694,19 @@
       <c r="F241" s="8" t="n">
         <v>851</v>
       </c>
-      <c r="G241" s="29" t="n">
+      <c r="G241" s="30" t="n">
         <v>45839</v>
       </c>
-      <c r="H241" s="31" t="inlineStr">
+      <c r="H241" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I241" s="31" t="inlineStr"/>
+      <c r="I241" s="32" t="inlineStr"/>
       <c r="J241" s="8" t="n"/>
-      <c r="K241" s="8" t="n"/>
+      <c r="K241" s="34" t="n">
+        <v>851</v>
+      </c>
       <c r="L241" s="8" t="n"/>
       <c r="M241" s="8" t="n"/>
       <c r="N241" s="8" t="n"/>
@@ -10389,19 +10736,21 @@
       <c r="F242" s="8" t="n">
         <v>1622</v>
       </c>
-      <c r="G242" s="30" t="n">
+      <c r="G242" s="31" t="n">
         <v>45883</v>
       </c>
-      <c r="H242" s="30" t="inlineStr">
+      <c r="H242" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I242" s="31" t="inlineStr"/>
-      <c r="J242" s="32" t="n">
+      <c r="I242" s="32" t="inlineStr"/>
+      <c r="J242" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K242" s="8" t="n"/>
+      <c r="K242" s="34" t="n">
+        <v>1622</v>
+      </c>
       <c r="L242" s="8" t="n"/>
       <c r="M242" s="8" t="n"/>
       <c r="N242" s="8" t="n"/>
@@ -10431,19 +10780,21 @@
       <c r="F243" s="8" t="n">
         <v>2530</v>
       </c>
-      <c r="G243" s="30" t="n">
+      <c r="G243" s="31" t="n">
         <v>45883</v>
       </c>
-      <c r="H243" s="30" t="inlineStr">
+      <c r="H243" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I243" s="31" t="inlineStr"/>
-      <c r="J243" s="32" t="n">
+      <c r="I243" s="32" t="inlineStr"/>
+      <c r="J243" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K243" s="8" t="n"/>
+      <c r="K243" s="34" t="n">
+        <v>2530</v>
+      </c>
       <c r="L243" s="8" t="n"/>
       <c r="M243" s="8" t="n"/>
       <c r="N243" s="8" t="n"/>
@@ -10473,21 +10824,23 @@
       <c r="F244" s="8" t="n">
         <v>238</v>
       </c>
-      <c r="G244" s="30" t="n">
+      <c r="G244" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H244" s="30" t="inlineStr">
+      <c r="H244" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I244" s="31" t="inlineStr">
+      <c r="I244" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J244" s="8" t="n"/>
-      <c r="K244" s="8" t="n"/>
+      <c r="K244" s="34" t="n">
+        <v>238</v>
+      </c>
       <c r="L244" s="8" t="n"/>
       <c r="M244" s="8" t="n"/>
       <c r="N244" s="8" t="n"/>
@@ -10517,17 +10870,19 @@
       <c r="F245" s="8" t="n">
         <v>1966</v>
       </c>
-      <c r="G245" s="29" t="n">
+      <c r="G245" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H245" s="31" t="inlineStr">
+      <c r="H245" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I245" s="31" t="inlineStr"/>
+      <c r="I245" s="32" t="inlineStr"/>
       <c r="J245" s="8" t="n"/>
-      <c r="K245" s="8" t="n"/>
+      <c r="K245" s="34" t="n">
+        <v>1966</v>
+      </c>
       <c r="L245" s="8" t="n"/>
       <c r="M245" s="8" t="n"/>
       <c r="N245" s="8" t="n"/>
@@ -10557,17 +10912,19 @@
       <c r="F246" s="8" t="n">
         <v>1676</v>
       </c>
-      <c r="G246" s="30" t="n">
+      <c r="G246" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H246" s="30" t="inlineStr">
+      <c r="H246" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I246" s="31" t="inlineStr"/>
+      <c r="I246" s="32" t="inlineStr"/>
       <c r="J246" s="8" t="n"/>
-      <c r="K246" s="8" t="n"/>
+      <c r="K246" s="34" t="n">
+        <v>1676</v>
+      </c>
       <c r="L246" s="8" t="n"/>
       <c r="M246" s="8" t="n"/>
       <c r="N246" s="8" t="n"/>
@@ -10597,21 +10954,23 @@
       <c r="F247" s="8" t="n">
         <v>2424</v>
       </c>
-      <c r="G247" s="30" t="n">
+      <c r="G247" s="31" t="n">
         <v>45912</v>
       </c>
-      <c r="H247" s="30" t="inlineStr">
+      <c r="H247" s="31" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I247" s="31" t="inlineStr">
+      <c r="I247" s="32" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
       </c>
       <c r="J247" s="8" t="n"/>
-      <c r="K247" s="8" t="n"/>
+      <c r="K247" s="34" t="n">
+        <v>2424</v>
+      </c>
       <c r="L247" s="8" t="n"/>
       <c r="M247" s="8" t="n"/>
       <c r="N247" s="8" t="n"/>
@@ -10641,17 +11000,19 @@
       <c r="F248" s="8" t="n">
         <v>420</v>
       </c>
-      <c r="G248" s="30" t="n">
+      <c r="G248" s="31" t="n">
         <v>45847</v>
       </c>
-      <c r="H248" s="30" t="inlineStr">
+      <c r="H248" s="31" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I248" s="31" t="inlineStr"/>
+      <c r="I248" s="32" t="inlineStr"/>
       <c r="J248" s="8" t="n"/>
-      <c r="K248" s="8" t="n"/>
+      <c r="K248" s="34" t="n">
+        <v>420</v>
+      </c>
       <c r="L248" s="8" t="n"/>
       <c r="M248" s="8" t="n"/>
       <c r="N248" s="8" t="n"/>
@@ -10681,17 +11042,19 @@
       <c r="F249" s="8" t="n">
         <v>768</v>
       </c>
-      <c r="G249" s="29" t="n">
+      <c r="G249" s="30" t="n">
         <v>45838</v>
       </c>
-      <c r="H249" s="31" t="inlineStr">
+      <c r="H249" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I249" s="31" t="inlineStr"/>
+      <c r="I249" s="32" t="inlineStr"/>
       <c r="J249" s="8" t="n"/>
-      <c r="K249" s="8" t="n"/>
+      <c r="K249" s="34" t="n">
+        <v>768</v>
+      </c>
       <c r="L249" s="8" t="n"/>
       <c r="M249" s="8" t="n"/>
       <c r="N249" s="8" t="n"/>
@@ -10721,17 +11084,19 @@
       <c r="F250" s="8" t="n">
         <v>1375</v>
       </c>
-      <c r="G250" s="29" t="n">
+      <c r="G250" s="30" t="n">
         <v>45838</v>
       </c>
-      <c r="H250" s="31" t="inlineStr">
+      <c r="H250" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I250" s="31" t="inlineStr"/>
+      <c r="I250" s="32" t="inlineStr"/>
       <c r="J250" s="8" t="n"/>
-      <c r="K250" s="8" t="n"/>
+      <c r="K250" s="34" t="n">
+        <v>1375</v>
+      </c>
       <c r="L250" s="8" t="n"/>
       <c r="M250" s="8" t="n"/>
       <c r="N250" s="8" t="n"/>
@@ -10761,17 +11126,19 @@
       <c r="F251" s="8" t="n">
         <v>2363</v>
       </c>
-      <c r="G251" s="29" t="n">
+      <c r="G251" s="30" t="n">
         <v>45838</v>
       </c>
-      <c r="H251" s="31" t="inlineStr">
+      <c r="H251" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I251" s="31" t="inlineStr"/>
+      <c r="I251" s="32" t="inlineStr"/>
       <c r="J251" s="8" t="n"/>
-      <c r="K251" s="8" t="n"/>
+      <c r="K251" s="34" t="n">
+        <v>2363</v>
+      </c>
       <c r="L251" s="8" t="n"/>
       <c r="M251" s="8" t="n"/>
       <c r="N251" s="8" t="n"/>
@@ -10835,21 +11202,23 @@
       <c r="F253" s="12" t="n">
         <v>4733</v>
       </c>
-      <c r="G253" s="33" t="n">
+      <c r="G253" s="35" t="n">
         <v>45915</v>
       </c>
-      <c r="H253" s="33" t="inlineStr">
+      <c r="H253" s="35" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I253" s="34" t="inlineStr">
+      <c r="I253" s="36" t="inlineStr">
         <is>
           <t>002617</t>
         </is>
       </c>
       <c r="J253" s="12" t="n"/>
-      <c r="K253" s="12" t="n"/>
+      <c r="K253" s="37" t="n">
+        <v>4733</v>
+      </c>
       <c r="L253" s="12" t="n"/>
       <c r="M253" s="12" t="n"/>
       <c r="N253" s="12" t="n"/>
@@ -11015,17 +11384,19 @@
       <c r="F258" s="8" t="n">
         <v>4413</v>
       </c>
-      <c r="G258" s="29" t="n">
+      <c r="G258" s="30" t="n">
         <v>45889</v>
       </c>
-      <c r="H258" s="31" t="inlineStr">
+      <c r="H258" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I258" s="31" t="inlineStr"/>
+      <c r="I258" s="32" t="inlineStr"/>
       <c r="J258" s="8" t="n"/>
-      <c r="K258" s="8" t="n"/>
+      <c r="K258" s="34" t="n">
+        <v>4413</v>
+      </c>
       <c r="L258" s="8" t="n"/>
       <c r="M258" s="8" t="n"/>
       <c r="N258" s="8" t="n"/>
@@ -11055,21 +11426,23 @@
       <c r="F259" s="8" t="n">
         <v>1225</v>
       </c>
-      <c r="G259" s="30" t="n">
+      <c r="G259" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H259" s="31" t="inlineStr">
+      <c r="H259" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I259" s="31" t="inlineStr">
+      <c r="I259" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J259" s="8" t="n"/>
-      <c r="K259" s="8" t="n"/>
+      <c r="K259" s="34" t="n">
+        <v>1225</v>
+      </c>
       <c r="L259" s="8" t="n"/>
       <c r="M259" s="8" t="n"/>
       <c r="N259" s="8" t="n"/>
@@ -11099,21 +11472,23 @@
       <c r="F260" s="8" t="n">
         <v>438</v>
       </c>
-      <c r="G260" s="30" t="n">
+      <c r="G260" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H260" s="31" t="inlineStr">
+      <c r="H260" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I260" s="31" t="inlineStr">
+      <c r="I260" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J260" s="8" t="n"/>
-      <c r="K260" s="8" t="n"/>
+      <c r="K260" s="34" t="n">
+        <v>438</v>
+      </c>
       <c r="L260" s="8" t="n"/>
       <c r="M260" s="8" t="n"/>
       <c r="N260" s="8" t="n"/>
@@ -11143,21 +11518,23 @@
       <c r="F261" s="8" t="n">
         <v>13176</v>
       </c>
-      <c r="G261" s="30" t="n">
+      <c r="G261" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H261" s="31" t="inlineStr">
+      <c r="H261" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I261" s="31" t="inlineStr">
+      <c r="I261" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J261" s="8" t="n"/>
-      <c r="K261" s="8" t="n"/>
+      <c r="K261" s="34" t="n">
+        <v>13176</v>
+      </c>
       <c r="L261" s="8" t="n"/>
       <c r="M261" s="8" t="n"/>
       <c r="N261" s="8" t="n"/>
@@ -11187,19 +11564,21 @@
       <c r="F262" s="8" t="n">
         <v>1547</v>
       </c>
-      <c r="G262" s="29" t="n">
+      <c r="G262" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H262" s="31" t="inlineStr">
+      <c r="H262" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I262" s="31" t="inlineStr"/>
-      <c r="J262" s="32" t="n">
+      <c r="I262" s="32" t="inlineStr"/>
+      <c r="J262" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K262" s="8" t="n"/>
+      <c r="K262" s="34" t="n">
+        <v>1547</v>
+      </c>
       <c r="L262" s="8" t="n"/>
       <c r="M262" s="8" t="n"/>
       <c r="N262" s="8" t="n"/>
@@ -11229,17 +11608,19 @@
       <c r="F263" s="8" t="n">
         <v>6103</v>
       </c>
-      <c r="G263" s="29" t="n">
+      <c r="G263" s="30" t="n">
         <v>45839</v>
       </c>
-      <c r="H263" s="31" t="inlineStr">
+      <c r="H263" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I263" s="31" t="inlineStr"/>
+      <c r="I263" s="32" t="inlineStr"/>
       <c r="J263" s="8" t="n"/>
-      <c r="K263" s="8" t="n"/>
+      <c r="K263" s="34" t="n">
+        <v>6099</v>
+      </c>
       <c r="L263" s="8" t="n"/>
       <c r="M263" s="8" t="n"/>
       <c r="N263" s="8" t="n"/>
@@ -11269,17 +11650,19 @@
       <c r="F264" s="8" t="n">
         <v>6054</v>
       </c>
-      <c r="G264" s="29" t="n">
+      <c r="G264" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H264" s="31" t="inlineStr">
+      <c r="H264" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I264" s="31" t="inlineStr"/>
+      <c r="I264" s="32" t="inlineStr"/>
       <c r="J264" s="8" t="n"/>
-      <c r="K264" s="8" t="n"/>
+      <c r="K264" s="34" t="n">
+        <v>6054</v>
+      </c>
       <c r="L264" s="8" t="n"/>
       <c r="M264" s="8" t="n"/>
       <c r="N264" s="8" t="n"/>
@@ -11309,17 +11692,19 @@
       <c r="F265" s="8" t="n">
         <v>5588</v>
       </c>
-      <c r="G265" s="30" t="n">
+      <c r="G265" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H265" s="31" t="inlineStr">
+      <c r="H265" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I265" s="31" t="inlineStr"/>
+      <c r="I265" s="32" t="inlineStr"/>
       <c r="J265" s="8" t="n"/>
-      <c r="K265" s="8" t="n"/>
+      <c r="K265" s="34" t="n">
+        <v>5588</v>
+      </c>
       <c r="L265" s="8" t="n"/>
       <c r="M265" s="8" t="n"/>
       <c r="N265" s="8" t="n"/>
@@ -11417,21 +11802,23 @@
       <c r="F268" s="8" t="n">
         <v>2413</v>
       </c>
-      <c r="G268" s="30" t="n">
+      <c r="G268" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H268" s="31" t="inlineStr">
+      <c r="H268" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I268" s="31" t="inlineStr">
+      <c r="I268" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J268" s="8" t="n"/>
-      <c r="K268" s="8" t="n"/>
+      <c r="K268" s="34" t="n">
+        <v>2413</v>
+      </c>
       <c r="L268" s="8" t="n"/>
       <c r="M268" s="8" t="n"/>
       <c r="N268" s="8" t="n"/>
@@ -11461,21 +11848,23 @@
       <c r="F269" s="8" t="n">
         <v>157</v>
       </c>
-      <c r="G269" s="30" t="n">
+      <c r="G269" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H269" s="31" t="inlineStr">
+      <c r="H269" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I269" s="31" t="inlineStr">
+      <c r="I269" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J269" s="8" t="n"/>
-      <c r="K269" s="8" t="n"/>
+      <c r="K269" s="34" t="n">
+        <v>157</v>
+      </c>
       <c r="L269" s="8" t="n"/>
       <c r="M269" s="8" t="n"/>
       <c r="N269" s="8" t="n"/>
@@ -11505,21 +11894,23 @@
       <c r="F270" s="8" t="n">
         <v>7482</v>
       </c>
-      <c r="G270" s="30" t="n">
+      <c r="G270" s="31" t="n">
         <v>45848</v>
       </c>
-      <c r="H270" s="31" t="inlineStr">
+      <c r="H270" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I270" s="31" t="inlineStr">
+      <c r="I270" s="32" t="inlineStr">
         <is>
           <t>002478</t>
         </is>
       </c>
       <c r="J270" s="8" t="n"/>
-      <c r="K270" s="8" t="n"/>
+      <c r="K270" s="34" t="n">
+        <v>7482</v>
+      </c>
       <c r="L270" s="8" t="n"/>
       <c r="M270" s="8" t="n"/>
       <c r="N270" s="8" t="n"/>
@@ -11617,21 +12008,23 @@
       <c r="F273" s="8" t="n">
         <v>2570</v>
       </c>
-      <c r="G273" s="30" t="n">
+      <c r="G273" s="31" t="n">
         <v>45868</v>
       </c>
-      <c r="H273" s="31" t="inlineStr">
+      <c r="H273" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I273" s="31" t="inlineStr">
+      <c r="I273" s="32" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
       </c>
       <c r="J273" s="8" t="n"/>
-      <c r="K273" s="8" t="n"/>
+      <c r="K273" s="34" t="n">
+        <v>2570</v>
+      </c>
       <c r="L273" s="8" t="n"/>
       <c r="M273" s="8" t="n"/>
       <c r="N273" s="8" t="n"/>
@@ -11695,17 +12088,19 @@
       <c r="F275" s="8" t="n">
         <v>779</v>
       </c>
-      <c r="G275" s="29" t="n">
+      <c r="G275" s="30" t="n">
         <v>45841</v>
       </c>
-      <c r="H275" s="31" t="inlineStr">
+      <c r="H275" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I275" s="31" t="inlineStr"/>
+      <c r="I275" s="32" t="inlineStr"/>
       <c r="J275" s="8" t="n"/>
-      <c r="K275" s="8" t="n"/>
+      <c r="K275" s="34" t="n">
+        <v>779</v>
+      </c>
       <c r="L275" s="8" t="n"/>
       <c r="M275" s="8" t="n"/>
       <c r="N275" s="8" t="n"/>
@@ -11735,21 +12130,23 @@
       <c r="F276" s="8" t="n">
         <v>4884</v>
       </c>
-      <c r="G276" s="30" t="n">
+      <c r="G276" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H276" s="31" t="inlineStr">
+      <c r="H276" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I276" s="31" t="inlineStr">
+      <c r="I276" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J276" s="8" t="n"/>
-      <c r="K276" s="8" t="n"/>
+      <c r="K276" s="34" t="n">
+        <v>4884</v>
+      </c>
       <c r="L276" s="8" t="n"/>
       <c r="M276" s="8" t="n"/>
       <c r="N276" s="8" t="n"/>
@@ -11779,21 +12176,23 @@
       <c r="F277" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="G277" s="30" t="n">
+      <c r="G277" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H277" s="31" t="inlineStr">
+      <c r="H277" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I277" s="31" t="inlineStr">
+      <c r="I277" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J277" s="8" t="n"/>
-      <c r="K277" s="8" t="n"/>
+      <c r="K277" s="34" t="n">
+        <v>146</v>
+      </c>
       <c r="L277" s="8" t="n"/>
       <c r="M277" s="8" t="n"/>
       <c r="N277" s="8" t="n"/>
@@ -11823,17 +12222,19 @@
       <c r="F278" s="8" t="n">
         <v>680</v>
       </c>
-      <c r="G278" s="30" t="n">
+      <c r="G278" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H278" s="31" t="inlineStr">
+      <c r="H278" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I278" s="31" t="inlineStr"/>
+      <c r="I278" s="32" t="inlineStr"/>
       <c r="J278" s="8" t="n"/>
-      <c r="K278" s="8" t="n"/>
+      <c r="K278" s="34" t="n">
+        <v>680</v>
+      </c>
       <c r="L278" s="8" t="n"/>
       <c r="M278" s="8" t="n"/>
       <c r="N278" s="8" t="n"/>
@@ -11863,23 +12264,25 @@
       <c r="F279" s="8" t="n">
         <v>9816</v>
       </c>
-      <c r="G279" s="30" t="n">
+      <c r="G279" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H279" s="31" t="inlineStr">
+      <c r="H279" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I279" s="31" t="inlineStr">
+      <c r="I279" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J279" s="32" t="n">
+      <c r="J279" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K279" s="8" t="n"/>
+      <c r="K279" s="34" t="n">
+        <v>9816</v>
+      </c>
       <c r="L279" s="8" t="n"/>
       <c r="M279" s="8" t="n"/>
       <c r="N279" s="8" t="n"/>
@@ -11943,19 +12346,21 @@
       <c r="F281" s="8" t="n">
         <v>1504</v>
       </c>
-      <c r="G281" s="29" t="n">
+      <c r="G281" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H281" s="31" t="inlineStr">
+      <c r="H281" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I281" s="31" t="inlineStr"/>
-      <c r="J281" s="32" t="n">
+      <c r="I281" s="32" t="inlineStr"/>
+      <c r="J281" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K281" s="8" t="n"/>
+      <c r="K281" s="34" t="n">
+        <v>1504</v>
+      </c>
       <c r="L281" s="8" t="n"/>
       <c r="M281" s="8" t="n"/>
       <c r="N281" s="8" t="n"/>
@@ -11985,17 +12390,19 @@
       <c r="F282" s="8" t="n">
         <v>304</v>
       </c>
-      <c r="G282" s="29" t="n">
+      <c r="G282" s="30" t="n">
         <v>45842</v>
       </c>
-      <c r="H282" s="31" t="inlineStr">
+      <c r="H282" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I282" s="31" t="inlineStr"/>
+      <c r="I282" s="32" t="inlineStr"/>
       <c r="J282" s="8" t="n"/>
-      <c r="K282" s="8" t="n"/>
+      <c r="K282" s="34" t="n">
+        <v>304</v>
+      </c>
       <c r="L282" s="8" t="n"/>
       <c r="M282" s="8" t="n"/>
       <c r="N282" s="8" t="n"/>
@@ -12025,17 +12432,19 @@
       <c r="F283" s="8" t="n">
         <v>1342</v>
       </c>
-      <c r="G283" s="30" t="n">
+      <c r="G283" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H283" s="31" t="inlineStr">
+      <c r="H283" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I283" s="31" t="inlineStr"/>
+      <c r="I283" s="32" t="inlineStr"/>
       <c r="J283" s="8" t="n"/>
-      <c r="K283" s="8" t="n"/>
+      <c r="K283" s="34" t="n">
+        <v>1342</v>
+      </c>
       <c r="L283" s="8" t="n"/>
       <c r="M283" s="8" t="n"/>
       <c r="N283" s="8" t="n"/>
@@ -12065,17 +12474,19 @@
       <c r="F284" s="8" t="n">
         <v>4316</v>
       </c>
-      <c r="G284" s="29" t="n">
+      <c r="G284" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H284" s="31" t="inlineStr">
+      <c r="H284" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I284" s="31" t="inlineStr"/>
+      <c r="I284" s="32" t="inlineStr"/>
       <c r="J284" s="8" t="n"/>
-      <c r="K284" s="8" t="n"/>
+      <c r="K284" s="34" t="n">
+        <v>4316</v>
+      </c>
       <c r="L284" s="8" t="n"/>
       <c r="M284" s="8" t="n"/>
       <c r="N284" s="8" t="n"/>
@@ -12105,21 +12516,23 @@
       <c r="F285" s="8" t="n">
         <v>4020</v>
       </c>
-      <c r="G285" s="30" t="n">
+      <c r="G285" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H285" s="31" t="inlineStr">
+      <c r="H285" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I285" s="31" t="inlineStr">
+      <c r="I285" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J285" s="8" t="n"/>
-      <c r="K285" s="8" t="n"/>
+      <c r="K285" s="34" t="n">
+        <v>4020</v>
+      </c>
       <c r="L285" s="8" t="n"/>
       <c r="M285" s="8" t="n"/>
       <c r="N285" s="8" t="n"/>
@@ -12285,19 +12698,21 @@
       <c r="F290" s="8" t="n">
         <v>1522</v>
       </c>
-      <c r="G290" s="29" t="n">
+      <c r="G290" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H290" s="31" t="inlineStr">
+      <c r="H290" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I290" s="31" t="inlineStr"/>
-      <c r="J290" s="32" t="n">
+      <c r="I290" s="32" t="inlineStr"/>
+      <c r="J290" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K290" s="8" t="n"/>
+      <c r="K290" s="34" t="n">
+        <v>1522</v>
+      </c>
       <c r="L290" s="8" t="n"/>
       <c r="M290" s="8" t="n"/>
       <c r="N290" s="8" t="n"/>
@@ -12327,17 +12742,19 @@
       <c r="F291" s="8" t="n">
         <v>1793</v>
       </c>
-      <c r="G291" s="30" t="n">
+      <c r="G291" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H291" s="31" t="inlineStr">
+      <c r="H291" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I291" s="31" t="inlineStr"/>
+      <c r="I291" s="32" t="inlineStr"/>
       <c r="J291" s="8" t="n"/>
-      <c r="K291" s="8" t="n"/>
+      <c r="K291" s="34" t="n">
+        <v>1793</v>
+      </c>
       <c r="L291" s="8" t="n"/>
       <c r="M291" s="8" t="n"/>
       <c r="N291" s="8" t="n"/>
@@ -12367,21 +12784,23 @@
       <c r="F292" s="8" t="n">
         <v>6084</v>
       </c>
-      <c r="G292" s="30" t="n">
+      <c r="G292" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H292" s="31" t="inlineStr">
+      <c r="H292" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I292" s="31" t="inlineStr">
+      <c r="I292" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J292" s="8" t="n"/>
-      <c r="K292" s="8" t="n"/>
+      <c r="K292" s="34" t="n">
+        <v>6084</v>
+      </c>
       <c r="L292" s="8" t="n"/>
       <c r="M292" s="8" t="n"/>
       <c r="N292" s="8" t="n"/>
@@ -12411,21 +12830,23 @@
       <c r="F293" s="8" t="n">
         <v>239</v>
       </c>
-      <c r="G293" s="30" t="n">
+      <c r="G293" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H293" s="31" t="inlineStr">
+      <c r="H293" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I293" s="31" t="inlineStr">
+      <c r="I293" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J293" s="8" t="n"/>
-      <c r="K293" s="8" t="n"/>
+      <c r="K293" s="34" t="n">
+        <v>239</v>
+      </c>
       <c r="L293" s="8" t="n"/>
       <c r="M293" s="8" t="n"/>
       <c r="N293" s="8" t="n"/>
@@ -12455,21 +12876,23 @@
       <c r="F294" s="8" t="n">
         <v>5423</v>
       </c>
-      <c r="G294" s="30" t="n">
+      <c r="G294" s="31" t="n">
         <v>45855</v>
       </c>
-      <c r="H294" s="31" t="inlineStr">
+      <c r="H294" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I294" s="31" t="inlineStr">
+      <c r="I294" s="32" t="inlineStr">
         <is>
           <t>002486</t>
         </is>
       </c>
       <c r="J294" s="8" t="n"/>
-      <c r="K294" s="8" t="n"/>
+      <c r="K294" s="34" t="n">
+        <v>5419</v>
+      </c>
       <c r="L294" s="8" t="n"/>
       <c r="M294" s="8" t="n"/>
       <c r="N294" s="8" t="n"/>
@@ -12499,19 +12922,21 @@
       <c r="F295" s="8" t="n">
         <v>2320</v>
       </c>
-      <c r="G295" s="29" t="n">
+      <c r="G295" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H295" s="31" t="inlineStr">
+      <c r="H295" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I295" s="31" t="inlineStr"/>
-      <c r="J295" s="32" t="n">
+      <c r="I295" s="32" t="inlineStr"/>
+      <c r="J295" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K295" s="8" t="n"/>
+      <c r="K295" s="34" t="n">
+        <v>2320</v>
+      </c>
       <c r="L295" s="8" t="n"/>
       <c r="M295" s="8" t="n"/>
       <c r="N295" s="8" t="n"/>
@@ -12541,17 +12966,19 @@
       <c r="F296" s="8" t="n">
         <v>779</v>
       </c>
-      <c r="G296" s="29" t="n">
+      <c r="G296" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H296" s="31" t="inlineStr">
+      <c r="H296" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I296" s="31" t="inlineStr"/>
+      <c r="I296" s="32" t="inlineStr"/>
       <c r="J296" s="8" t="n"/>
-      <c r="K296" s="8" t="n"/>
+      <c r="K296" s="34" t="n">
+        <v>779</v>
+      </c>
       <c r="L296" s="8" t="n"/>
       <c r="M296" s="8" t="n"/>
       <c r="N296" s="8" t="n"/>
@@ -12581,21 +13008,23 @@
       <c r="F297" s="8" t="n">
         <v>4614</v>
       </c>
-      <c r="G297" s="30" t="n">
+      <c r="G297" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H297" s="31" t="inlineStr">
+      <c r="H297" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I297" s="31" t="inlineStr">
+      <c r="I297" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J297" s="8" t="n"/>
-      <c r="K297" s="8" t="n"/>
+      <c r="K297" s="34" t="n">
+        <v>4614</v>
+      </c>
       <c r="L297" s="8" t="n"/>
       <c r="M297" s="8" t="n"/>
       <c r="N297" s="8" t="n"/>
@@ -12625,17 +13054,19 @@
       <c r="F298" s="8" t="n">
         <v>2365</v>
       </c>
-      <c r="G298" s="30" t="n">
+      <c r="G298" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H298" s="31" t="inlineStr">
+      <c r="H298" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I298" s="31" t="inlineStr"/>
+      <c r="I298" s="32" t="inlineStr"/>
       <c r="J298" s="8" t="n"/>
-      <c r="K298" s="8" t="n"/>
+      <c r="K298" s="34" t="n">
+        <v>2365</v>
+      </c>
       <c r="L298" s="8" t="n"/>
       <c r="M298" s="8" t="n"/>
       <c r="N298" s="8" t="n"/>
@@ -12699,19 +13130,21 @@
       <c r="F300" s="8" t="n">
         <v>3045</v>
       </c>
-      <c r="G300" s="29" t="n">
+      <c r="G300" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H300" s="31" t="inlineStr">
+      <c r="H300" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I300" s="31" t="inlineStr"/>
-      <c r="J300" s="32" t="n">
+      <c r="I300" s="32" t="inlineStr"/>
+      <c r="J300" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K300" s="8" t="n"/>
+      <c r="K300" s="34" t="n">
+        <v>3045</v>
+      </c>
       <c r="L300" s="8" t="n"/>
       <c r="M300" s="8" t="n"/>
       <c r="N300" s="8" t="n"/>
@@ -12843,17 +13276,19 @@
       <c r="F304" s="8" t="n">
         <v>1124</v>
       </c>
-      <c r="G304" s="30" t="n">
+      <c r="G304" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H304" s="31" t="inlineStr">
+      <c r="H304" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I304" s="31" t="inlineStr"/>
+      <c r="I304" s="32" t="inlineStr"/>
       <c r="J304" s="8" t="n"/>
-      <c r="K304" s="8" t="n"/>
+      <c r="K304" s="34" t="n">
+        <v>1124</v>
+      </c>
       <c r="L304" s="8" t="n"/>
       <c r="M304" s="8" t="n"/>
       <c r="N304" s="8" t="n"/>
@@ -12883,19 +13318,21 @@
       <c r="F305" s="8" t="n">
         <v>319</v>
       </c>
-      <c r="G305" s="29" t="n">
+      <c r="G305" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H305" s="31" t="inlineStr">
+      <c r="H305" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I305" s="31" t="inlineStr"/>
-      <c r="J305" s="32" t="n">
+      <c r="I305" s="32" t="inlineStr"/>
+      <c r="J305" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K305" s="8" t="n"/>
+      <c r="K305" s="34" t="n">
+        <v>319</v>
+      </c>
       <c r="L305" s="8" t="n"/>
       <c r="M305" s="8" t="n"/>
       <c r="N305" s="8" t="n"/>
@@ -12925,17 +13362,19 @@
       <c r="F306" s="8" t="n">
         <v>1480</v>
       </c>
-      <c r="G306" s="29" t="n">
+      <c r="G306" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H306" s="31" t="inlineStr">
+      <c r="H306" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I306" s="31" t="inlineStr"/>
+      <c r="I306" s="32" t="inlineStr"/>
       <c r="J306" s="8" t="n"/>
-      <c r="K306" s="8" t="n"/>
+      <c r="K306" s="34" t="n">
+        <v>1480</v>
+      </c>
       <c r="L306" s="8" t="n"/>
       <c r="M306" s="8" t="n"/>
       <c r="N306" s="8" t="n"/>
@@ -12965,17 +13404,19 @@
       <c r="F307" s="8" t="n">
         <v>295</v>
       </c>
-      <c r="G307" s="29" t="n">
+      <c r="G307" s="30" t="n">
         <v>45852</v>
       </c>
-      <c r="H307" s="31" t="inlineStr">
+      <c r="H307" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I307" s="31" t="inlineStr"/>
+      <c r="I307" s="32" t="inlineStr"/>
       <c r="J307" s="8" t="n"/>
-      <c r="K307" s="8" t="n"/>
+      <c r="K307" s="34" t="n">
+        <v>295</v>
+      </c>
       <c r="L307" s="8" t="n"/>
       <c r="M307" s="8" t="n"/>
       <c r="N307" s="8" t="n"/>
@@ -13005,21 +13446,23 @@
       <c r="F308" s="8" t="n">
         <v>3108</v>
       </c>
-      <c r="G308" s="30" t="n">
+      <c r="G308" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H308" s="31" t="inlineStr">
+      <c r="H308" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I308" s="31" t="inlineStr">
+      <c r="I308" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J308" s="8" t="n"/>
-      <c r="K308" s="8" t="n"/>
+      <c r="K308" s="34" t="n">
+        <v>3108</v>
+      </c>
       <c r="L308" s="8" t="n"/>
       <c r="M308" s="8" t="n"/>
       <c r="N308" s="8" t="n"/>
@@ -13049,21 +13492,23 @@
       <c r="F309" s="8" t="n">
         <v>346</v>
       </c>
-      <c r="G309" s="30" t="n">
+      <c r="G309" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H309" s="31" t="inlineStr">
+      <c r="H309" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I309" s="31" t="inlineStr">
+      <c r="I309" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J309" s="8" t="n"/>
-      <c r="K309" s="8" t="n"/>
+      <c r="K309" s="34" t="n">
+        <v>346</v>
+      </c>
       <c r="L309" s="8" t="n"/>
       <c r="M309" s="8" t="n"/>
       <c r="N309" s="8" t="n"/>
@@ -13093,21 +13538,23 @@
       <c r="F310" s="8" t="n">
         <v>913</v>
       </c>
-      <c r="G310" s="30" t="n">
+      <c r="G310" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H310" s="31" t="inlineStr">
+      <c r="H310" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I310" s="31" t="inlineStr">
+      <c r="I310" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J310" s="8" t="n"/>
-      <c r="K310" s="8" t="n"/>
+      <c r="K310" s="34" t="n">
+        <v>913</v>
+      </c>
       <c r="L310" s="8" t="n"/>
       <c r="M310" s="8" t="n"/>
       <c r="N310" s="8" t="n"/>
@@ -13137,21 +13584,23 @@
       <c r="F311" s="8" t="n">
         <v>950</v>
       </c>
-      <c r="G311" s="30" t="n">
+      <c r="G311" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H311" s="31" t="inlineStr">
+      <c r="H311" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I311" s="31" t="inlineStr">
+      <c r="I311" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J311" s="8" t="n"/>
-      <c r="K311" s="8" t="n"/>
+      <c r="K311" s="34" t="n">
+        <v>950</v>
+      </c>
       <c r="L311" s="8" t="n"/>
       <c r="M311" s="8" t="n"/>
       <c r="N311" s="8" t="n"/>
@@ -13181,17 +13630,19 @@
       <c r="F312" s="8" t="n">
         <v>578</v>
       </c>
-      <c r="G312" s="30" t="n">
+      <c r="G312" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H312" s="31" t="inlineStr">
+      <c r="H312" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I312" s="31" t="inlineStr"/>
+      <c r="I312" s="32" t="inlineStr"/>
       <c r="J312" s="8" t="n"/>
-      <c r="K312" s="8" t="n"/>
+      <c r="K312" s="34" t="n">
+        <v>578</v>
+      </c>
       <c r="L312" s="8" t="n"/>
       <c r="M312" s="8" t="n"/>
       <c r="N312" s="8" t="n"/>
@@ -13221,17 +13672,19 @@
       <c r="F313" s="8" t="n">
         <v>754</v>
       </c>
-      <c r="G313" s="29" t="n">
+      <c r="G313" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H313" s="31" t="inlineStr">
+      <c r="H313" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I313" s="31" t="inlineStr"/>
+      <c r="I313" s="32" t="inlineStr"/>
       <c r="J313" s="8" t="n"/>
-      <c r="K313" s="8" t="n"/>
+      <c r="K313" s="34" t="n">
+        <v>754</v>
+      </c>
       <c r="L313" s="8" t="n"/>
       <c r="M313" s="8" t="n"/>
       <c r="N313" s="8" t="n"/>
@@ -13261,17 +13714,19 @@
       <c r="F314" s="8" t="n">
         <v>551</v>
       </c>
-      <c r="G314" s="29" t="n">
+      <c r="G314" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H314" s="31" t="inlineStr">
+      <c r="H314" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I314" s="31" t="inlineStr"/>
+      <c r="I314" s="32" t="inlineStr"/>
       <c r="J314" s="8" t="n"/>
-      <c r="K314" s="8" t="n"/>
+      <c r="K314" s="34" t="n">
+        <v>551</v>
+      </c>
       <c r="L314" s="8" t="n"/>
       <c r="M314" s="8" t="n"/>
       <c r="N314" s="8" t="n"/>
@@ -13301,21 +13756,23 @@
       <c r="F315" s="8" t="n">
         <v>573</v>
       </c>
-      <c r="G315" s="30" t="n">
+      <c r="G315" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H315" s="31" t="inlineStr">
+      <c r="H315" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I315" s="31" t="inlineStr">
+      <c r="I315" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J315" s="8" t="n"/>
-      <c r="K315" s="8" t="n"/>
+      <c r="K315" s="34" t="n">
+        <v>573</v>
+      </c>
       <c r="L315" s="8" t="n"/>
       <c r="M315" s="8" t="n"/>
       <c r="N315" s="8" t="n"/>
@@ -13345,21 +13802,23 @@
       <c r="F316" s="8" t="n">
         <v>1356</v>
       </c>
-      <c r="G316" s="30" t="n">
+      <c r="G316" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H316" s="31" t="inlineStr">
+      <c r="H316" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I316" s="31" t="inlineStr">
+      <c r="I316" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J316" s="8" t="n"/>
-      <c r="K316" s="8" t="n"/>
+      <c r="K316" s="34" t="n">
+        <v>1356</v>
+      </c>
       <c r="L316" s="8" t="n"/>
       <c r="M316" s="8" t="n"/>
       <c r="N316" s="8" t="n"/>
@@ -13389,19 +13848,21 @@
       <c r="F317" s="8" t="n">
         <v>7367</v>
       </c>
-      <c r="G317" s="29" t="n">
+      <c r="G317" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H317" s="31" t="inlineStr">
+      <c r="H317" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I317" s="31" t="inlineStr"/>
-      <c r="J317" s="32" t="n">
+      <c r="I317" s="32" t="inlineStr"/>
+      <c r="J317" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K317" s="8" t="n"/>
+      <c r="K317" s="34" t="n">
+        <v>7367</v>
+      </c>
       <c r="L317" s="8" t="n"/>
       <c r="M317" s="8" t="n"/>
       <c r="N317" s="8" t="n"/>
@@ -13567,21 +14028,23 @@
       <c r="F322" s="8" t="n">
         <v>560</v>
       </c>
-      <c r="G322" s="30" t="n">
+      <c r="G322" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H322" s="31" t="inlineStr">
+      <c r="H322" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I322" s="31" t="inlineStr">
+      <c r="I322" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J322" s="8" t="n"/>
-      <c r="K322" s="8" t="n"/>
+      <c r="K322" s="34" t="n">
+        <v>560</v>
+      </c>
       <c r="L322" s="8" t="n"/>
       <c r="M322" s="8" t="n"/>
       <c r="N322" s="8" t="n"/>
@@ -13645,17 +14108,19 @@
       <c r="F324" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="G324" s="29" t="n">
+      <c r="G324" s="30" t="n">
         <v>45852</v>
       </c>
-      <c r="H324" s="31" t="inlineStr">
+      <c r="H324" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I324" s="31" t="inlineStr"/>
+      <c r="I324" s="32" t="inlineStr"/>
       <c r="J324" s="8" t="n"/>
-      <c r="K324" s="8" t="n"/>
+      <c r="K324" s="34" t="n">
+        <v>146</v>
+      </c>
       <c r="L324" s="8" t="n"/>
       <c r="M324" s="8" t="n"/>
       <c r="N324" s="8" t="n"/>
@@ -13719,21 +14184,23 @@
       <c r="F326" s="8" t="n">
         <v>1362</v>
       </c>
-      <c r="G326" s="30" t="n">
+      <c r="G326" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H326" s="31" t="inlineStr">
+      <c r="H326" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I326" s="31" t="inlineStr">
+      <c r="I326" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J326" s="8" t="n"/>
-      <c r="K326" s="8" t="n"/>
+      <c r="K326" s="34" t="n">
+        <v>1362</v>
+      </c>
       <c r="L326" s="8" t="n"/>
       <c r="M326" s="8" t="n"/>
       <c r="N326" s="8" t="n"/>
@@ -13763,23 +14230,25 @@
       <c r="F327" s="8" t="n">
         <v>5700</v>
       </c>
-      <c r="G327" s="30" t="n">
+      <c r="G327" s="31" t="n">
         <v>45828</v>
       </c>
-      <c r="H327" s="31" t="inlineStr">
+      <c r="H327" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I327" s="31" t="inlineStr">
+      <c r="I327" s="32" t="inlineStr">
         <is>
           <t>002384</t>
         </is>
       </c>
-      <c r="J327" s="32" t="n">
+      <c r="J327" s="33" t="n">
         <v>25000</v>
       </c>
-      <c r="K327" s="8" t="n"/>
+      <c r="K327" s="34" t="n">
+        <v>1434</v>
+      </c>
       <c r="L327" s="8" t="n"/>
       <c r="M327" s="8" t="n"/>
       <c r="N327" s="8" t="n"/>
@@ -13809,17 +14278,19 @@
       <c r="F328" s="8" t="n">
         <v>5275</v>
       </c>
-      <c r="G328" s="30" t="n">
+      <c r="G328" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H328" s="31" t="inlineStr">
+      <c r="H328" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I328" s="31" t="inlineStr"/>
+      <c r="I328" s="32" t="inlineStr"/>
       <c r="J328" s="8" t="n"/>
-      <c r="K328" s="8" t="n"/>
+      <c r="K328" s="34" t="n">
+        <v>5275</v>
+      </c>
       <c r="L328" s="8" t="n"/>
       <c r="M328" s="8" t="n"/>
       <c r="N328" s="8" t="n"/>
@@ -13849,17 +14320,19 @@
       <c r="F329" s="8" t="n">
         <v>4190</v>
       </c>
-      <c r="G329" s="29" t="n">
+      <c r="G329" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H329" s="31" t="inlineStr">
+      <c r="H329" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I329" s="31" t="inlineStr"/>
+      <c r="I329" s="32" t="inlineStr"/>
       <c r="J329" s="8" t="n"/>
-      <c r="K329" s="8" t="n"/>
+      <c r="K329" s="34" t="n">
+        <v>4190</v>
+      </c>
       <c r="L329" s="8" t="n"/>
       <c r="M329" s="8" t="n"/>
       <c r="N329" s="8" t="n"/>
@@ -13889,17 +14362,19 @@
       <c r="F330" s="8" t="n">
         <v>7556</v>
       </c>
-      <c r="G330" s="30" t="n">
+      <c r="G330" s="31" t="n">
         <v>45872</v>
       </c>
-      <c r="H330" s="31" t="inlineStr">
+      <c r="H330" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I330" s="31" t="inlineStr"/>
+      <c r="I330" s="32" t="inlineStr"/>
       <c r="J330" s="8" t="n"/>
-      <c r="K330" s="8" t="n"/>
+      <c r="K330" s="34" t="n">
+        <v>7556</v>
+      </c>
       <c r="L330" s="8" t="n"/>
       <c r="M330" s="8" t="n"/>
       <c r="N330" s="8" t="n"/>
@@ -14099,23 +14574,25 @@
       <c r="F336" s="8" t="n">
         <v>3047</v>
       </c>
-      <c r="G336" s="30" t="n">
+      <c r="G336" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H336" s="31" t="inlineStr">
+      <c r="H336" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I336" s="31" t="inlineStr">
+      <c r="I336" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J336" s="32" t="n">
+      <c r="J336" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K336" s="8" t="n"/>
+      <c r="K336" s="34" t="n">
+        <v>3047</v>
+      </c>
       <c r="L336" s="8" t="n"/>
       <c r="M336" s="8" t="n"/>
       <c r="N336" s="8" t="n"/>
@@ -14145,17 +14622,19 @@
       <c r="F337" s="8" t="n">
         <v>6798</v>
       </c>
-      <c r="G337" s="30" t="n">
+      <c r="G337" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H337" s="31" t="inlineStr">
+      <c r="H337" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I337" s="31" t="inlineStr"/>
+      <c r="I337" s="32" t="inlineStr"/>
       <c r="J337" s="8" t="n"/>
-      <c r="K337" s="8" t="n"/>
+      <c r="K337" s="34" t="n">
+        <v>6798</v>
+      </c>
       <c r="L337" s="8" t="n"/>
       <c r="M337" s="8" t="n"/>
       <c r="N337" s="8" t="n"/>
@@ -14185,21 +14664,23 @@
       <c r="F338" s="8" t="n">
         <v>359</v>
       </c>
-      <c r="G338" s="30" t="n">
+      <c r="G338" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H338" s="31" t="inlineStr">
+      <c r="H338" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I338" s="31" t="inlineStr">
+      <c r="I338" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J338" s="8" t="n"/>
-      <c r="K338" s="8" t="n"/>
+      <c r="K338" s="34" t="n">
+        <v>359</v>
+      </c>
       <c r="L338" s="8" t="n"/>
       <c r="M338" s="8" t="n"/>
       <c r="N338" s="8" t="n"/>
@@ -14229,17 +14710,19 @@
       <c r="F339" s="8" t="n">
         <v>2097</v>
       </c>
-      <c r="G339" s="29" t="n">
+      <c r="G339" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H339" s="31" t="inlineStr">
+      <c r="H339" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I339" s="31" t="inlineStr"/>
+      <c r="I339" s="32" t="inlineStr"/>
       <c r="J339" s="8" t="n"/>
-      <c r="K339" s="8" t="n"/>
+      <c r="K339" s="34" t="n">
+        <v>2097</v>
+      </c>
       <c r="L339" s="8" t="n"/>
       <c r="M339" s="8" t="n"/>
       <c r="N339" s="8" t="n"/>
@@ -14337,21 +14820,23 @@
       <c r="F342" s="8" t="n">
         <v>3006</v>
       </c>
-      <c r="G342" s="30" t="n">
+      <c r="G342" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H342" s="31" t="inlineStr">
+      <c r="H342" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I342" s="31" t="inlineStr">
+      <c r="I342" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J342" s="8" t="n"/>
-      <c r="K342" s="8" t="n"/>
+      <c r="K342" s="34" t="n">
+        <v>3006</v>
+      </c>
       <c r="L342" s="8" t="n"/>
       <c r="M342" s="8" t="n"/>
       <c r="N342" s="8" t="n"/>
@@ -14381,19 +14866,21 @@
       <c r="F343" s="8" t="n">
         <v>3479</v>
       </c>
-      <c r="G343" s="29" t="n">
+      <c r="G343" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H343" s="31" t="inlineStr">
+      <c r="H343" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I343" s="31" t="inlineStr"/>
-      <c r="J343" s="32" t="n">
+      <c r="I343" s="32" t="inlineStr"/>
+      <c r="J343" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K343" s="8" t="n"/>
+      <c r="K343" s="34" t="n">
+        <v>3479</v>
+      </c>
       <c r="L343" s="8" t="n"/>
       <c r="M343" s="8" t="n"/>
       <c r="N343" s="8" t="n"/>
@@ -14559,21 +15046,23 @@
       <c r="F348" s="8" t="n">
         <v>1158</v>
       </c>
-      <c r="G348" s="30" t="n">
+      <c r="G348" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H348" s="31" t="inlineStr">
+      <c r="H348" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I348" s="31" t="inlineStr">
+      <c r="I348" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J348" s="8" t="n"/>
-      <c r="K348" s="8" t="n"/>
+      <c r="K348" s="34" t="n">
+        <v>1158</v>
+      </c>
       <c r="L348" s="8" t="n"/>
       <c r="M348" s="8" t="n"/>
       <c r="N348" s="8" t="n"/>
@@ -14603,19 +15092,21 @@
       <c r="F349" s="8" t="n">
         <v>982</v>
       </c>
-      <c r="G349" s="29" t="n">
+      <c r="G349" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H349" s="31" t="inlineStr">
+      <c r="H349" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I349" s="31" t="inlineStr"/>
-      <c r="J349" s="32" t="n">
+      <c r="I349" s="32" t="inlineStr"/>
+      <c r="J349" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K349" s="8" t="n"/>
+      <c r="K349" s="34" t="n">
+        <v>982</v>
+      </c>
       <c r="L349" s="8" t="n"/>
       <c r="M349" s="8" t="n"/>
       <c r="N349" s="8" t="n"/>
@@ -14679,21 +15170,23 @@
       <c r="F351" s="8" t="n">
         <v>2471</v>
       </c>
-      <c r="G351" s="30" t="n">
+      <c r="G351" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H351" s="31" t="inlineStr">
+      <c r="H351" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I351" s="31" t="inlineStr">
+      <c r="I351" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J351" s="8" t="n"/>
-      <c r="K351" s="8" t="n"/>
+      <c r="K351" s="34" t="n">
+        <v>2471</v>
+      </c>
       <c r="L351" s="8" t="n"/>
       <c r="M351" s="8" t="n"/>
       <c r="N351" s="8" t="n"/>
@@ -14723,17 +15216,19 @@
       <c r="F352" s="8" t="n">
         <v>2695</v>
       </c>
-      <c r="G352" s="29" t="n">
+      <c r="G352" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H352" s="31" t="inlineStr">
+      <c r="H352" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I352" s="31" t="inlineStr"/>
+      <c r="I352" s="32" t="inlineStr"/>
       <c r="J352" s="8" t="n"/>
-      <c r="K352" s="8" t="n"/>
+      <c r="K352" s="34" t="n">
+        <v>2695</v>
+      </c>
       <c r="L352" s="8" t="n"/>
       <c r="M352" s="8" t="n"/>
       <c r="N352" s="8" t="n"/>
@@ -14899,17 +15394,19 @@
       <c r="F357" s="8" t="n">
         <v>933</v>
       </c>
-      <c r="G357" s="29" t="n">
+      <c r="G357" s="30" t="n">
         <v>45852</v>
       </c>
-      <c r="H357" s="31" t="inlineStr">
+      <c r="H357" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I357" s="31" t="inlineStr"/>
+      <c r="I357" s="32" t="inlineStr"/>
       <c r="J357" s="8" t="n"/>
-      <c r="K357" s="8" t="n"/>
+      <c r="K357" s="34" t="n">
+        <v>933</v>
+      </c>
       <c r="L357" s="8" t="n"/>
       <c r="M357" s="8" t="n"/>
       <c r="N357" s="8" t="n"/>
@@ -14939,17 +15436,19 @@
       <c r="F358" s="8" t="n">
         <v>1269</v>
       </c>
-      <c r="G358" s="29" t="n">
+      <c r="G358" s="30" t="n">
         <v>45852</v>
       </c>
-      <c r="H358" s="31" t="inlineStr">
+      <c r="H358" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I358" s="31" t="inlineStr"/>
+      <c r="I358" s="32" t="inlineStr"/>
       <c r="J358" s="8" t="n"/>
-      <c r="K358" s="8" t="n"/>
+      <c r="K358" s="34" t="n">
+        <v>1269</v>
+      </c>
       <c r="L358" s="8" t="n"/>
       <c r="M358" s="8" t="n"/>
       <c r="N358" s="8" t="n"/>
@@ -14979,17 +15478,19 @@
       <c r="F359" s="8" t="n">
         <v>525</v>
       </c>
-      <c r="G359" s="30" t="n">
+      <c r="G359" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H359" s="31" t="inlineStr">
+      <c r="H359" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I359" s="31" t="inlineStr"/>
+      <c r="I359" s="32" t="inlineStr"/>
       <c r="J359" s="8" t="n"/>
-      <c r="K359" s="8" t="n"/>
+      <c r="K359" s="34" t="n">
+        <v>525</v>
+      </c>
       <c r="L359" s="8" t="n"/>
       <c r="M359" s="8" t="n"/>
       <c r="N359" s="8" t="n"/>
@@ -15019,17 +15520,19 @@
       <c r="F360" s="8" t="n">
         <v>1804</v>
       </c>
-      <c r="G360" s="29" t="n">
+      <c r="G360" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H360" s="31" t="inlineStr">
+      <c r="H360" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I360" s="31" t="inlineStr"/>
+      <c r="I360" s="32" t="inlineStr"/>
       <c r="J360" s="8" t="n"/>
-      <c r="K360" s="8" t="n"/>
+      <c r="K360" s="34" t="n">
+        <v>1804</v>
+      </c>
       <c r="L360" s="8" t="n"/>
       <c r="M360" s="8" t="n"/>
       <c r="N360" s="8" t="n"/>
@@ -15093,21 +15596,23 @@
       <c r="F362" s="8" t="n">
         <v>1704</v>
       </c>
-      <c r="G362" s="30" t="n">
+      <c r="G362" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H362" s="31" t="inlineStr">
+      <c r="H362" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I362" s="31" t="inlineStr">
+      <c r="I362" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J362" s="8" t="n"/>
-      <c r="K362" s="8" t="n"/>
+      <c r="K362" s="34" t="n">
+        <v>1704</v>
+      </c>
       <c r="L362" s="8" t="n"/>
       <c r="M362" s="8" t="n"/>
       <c r="N362" s="8" t="n"/>
@@ -15137,21 +15642,23 @@
       <c r="F363" s="8" t="n">
         <v>818</v>
       </c>
-      <c r="G363" s="30" t="n">
+      <c r="G363" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H363" s="31" t="inlineStr">
+      <c r="H363" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I363" s="31" t="inlineStr">
+      <c r="I363" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J363" s="8" t="n"/>
-      <c r="K363" s="8" t="n"/>
+      <c r="K363" s="34" t="n">
+        <v>818</v>
+      </c>
       <c r="L363" s="8" t="n"/>
       <c r="M363" s="8" t="n"/>
       <c r="N363" s="8" t="n"/>
@@ -15317,17 +15824,19 @@
       <c r="F368" s="8" t="n">
         <v>1187</v>
       </c>
-      <c r="G368" s="29" t="n">
+      <c r="G368" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H368" s="31" t="inlineStr">
+      <c r="H368" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I368" s="31" t="inlineStr"/>
+      <c r="I368" s="32" t="inlineStr"/>
       <c r="J368" s="8" t="n"/>
-      <c r="K368" s="8" t="n"/>
+      <c r="K368" s="34" t="n">
+        <v>1187</v>
+      </c>
       <c r="L368" s="8" t="n"/>
       <c r="M368" s="8" t="n"/>
       <c r="N368" s="8" t="n"/>
@@ -15357,17 +15866,19 @@
       <c r="F369" s="8" t="n">
         <v>977</v>
       </c>
-      <c r="G369" s="30" t="n">
+      <c r="G369" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H369" s="31" t="inlineStr">
+      <c r="H369" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I369" s="31" t="inlineStr"/>
+      <c r="I369" s="32" t="inlineStr"/>
       <c r="J369" s="8" t="n"/>
-      <c r="K369" s="8" t="n"/>
+      <c r="K369" s="34" t="n">
+        <v>977</v>
+      </c>
       <c r="L369" s="8" t="n"/>
       <c r="M369" s="8" t="n"/>
       <c r="N369" s="8" t="n"/>
@@ -15397,17 +15908,19 @@
       <c r="F370" s="8" t="n">
         <v>566</v>
       </c>
-      <c r="G370" s="29" t="n">
+      <c r="G370" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H370" s="31" t="inlineStr">
+      <c r="H370" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I370" s="31" t="inlineStr"/>
+      <c r="I370" s="32" t="inlineStr"/>
       <c r="J370" s="8" t="n"/>
-      <c r="K370" s="8" t="n"/>
+      <c r="K370" s="34" t="n">
+        <v>566</v>
+      </c>
       <c r="L370" s="8" t="n"/>
       <c r="M370" s="8" t="n"/>
       <c r="N370" s="8" t="n"/>
@@ -15437,21 +15950,23 @@
       <c r="F371" s="8" t="n">
         <v>1506</v>
       </c>
-      <c r="G371" s="30" t="n">
+      <c r="G371" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H371" s="31" t="inlineStr">
+      <c r="H371" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I371" s="31" t="inlineStr">
+      <c r="I371" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J371" s="8" t="n"/>
-      <c r="K371" s="8" t="n"/>
+      <c r="K371" s="34" t="n">
+        <v>1506</v>
+      </c>
       <c r="L371" s="8" t="n"/>
       <c r="M371" s="8" t="n"/>
       <c r="N371" s="8" t="n"/>
@@ -15481,23 +15996,25 @@
       <c r="F372" s="8" t="n">
         <v>467</v>
       </c>
-      <c r="G372" s="30" t="n">
+      <c r="G372" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H372" s="31" t="inlineStr">
+      <c r="H372" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I372" s="31" t="inlineStr">
+      <c r="I372" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J372" s="32" t="n">
+      <c r="J372" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K372" s="8" t="n"/>
+      <c r="K372" s="34" t="n">
+        <v>467</v>
+      </c>
       <c r="L372" s="8" t="n"/>
       <c r="M372" s="8" t="n"/>
       <c r="N372" s="8" t="n"/>
@@ -15527,21 +16044,23 @@
       <c r="F373" s="8" t="n">
         <v>437</v>
       </c>
-      <c r="G373" s="30" t="n">
+      <c r="G373" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H373" s="31" t="inlineStr">
+      <c r="H373" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I373" s="31" t="inlineStr">
+      <c r="I373" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J373" s="8" t="n"/>
-      <c r="K373" s="8" t="n"/>
+      <c r="K373" s="34" t="n">
+        <v>437</v>
+      </c>
       <c r="L373" s="8" t="n"/>
       <c r="M373" s="8" t="n"/>
       <c r="N373" s="8" t="n"/>
@@ -15571,19 +16090,21 @@
       <c r="F374" s="8" t="n">
         <v>154</v>
       </c>
-      <c r="G374" s="29" t="n">
+      <c r="G374" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H374" s="31" t="inlineStr">
+      <c r="H374" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I374" s="31" t="inlineStr"/>
-      <c r="J374" s="32" t="n">
+      <c r="I374" s="32" t="inlineStr"/>
+      <c r="J374" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K374" s="8" t="n"/>
+      <c r="K374" s="34" t="n">
+        <v>154</v>
+      </c>
       <c r="L374" s="8" t="n"/>
       <c r="M374" s="8" t="n"/>
       <c r="N374" s="8" t="n"/>
@@ -15613,23 +16134,25 @@
       <c r="F375" s="8" t="n">
         <v>1003</v>
       </c>
-      <c r="G375" s="30" t="n">
+      <c r="G375" s="31" t="n">
         <v>45885</v>
       </c>
-      <c r="H375" s="31" t="inlineStr">
+      <c r="H375" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I375" s="31" t="inlineStr">
+      <c r="I375" s="32" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J375" s="32" t="n">
+      <c r="J375" s="33" t="n">
         <v>9492</v>
       </c>
-      <c r="K375" s="8" t="n"/>
+      <c r="K375" s="34" t="n">
+        <v>93</v>
+      </c>
       <c r="L375" s="8" t="n"/>
       <c r="M375" s="8" t="n"/>
       <c r="N375" s="8" t="n"/>
@@ -15727,17 +16250,19 @@
       <c r="F378" s="8" t="n">
         <v>218</v>
       </c>
-      <c r="G378" s="29" t="n">
+      <c r="G378" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H378" s="31" t="inlineStr">
+      <c r="H378" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I378" s="31" t="inlineStr"/>
+      <c r="I378" s="32" t="inlineStr"/>
       <c r="J378" s="8" t="n"/>
-      <c r="K378" s="8" t="n"/>
+      <c r="K378" s="34" t="n">
+        <v>218</v>
+      </c>
       <c r="L378" s="8" t="n"/>
       <c r="M378" s="8" t="n"/>
       <c r="N378" s="8" t="n"/>
@@ -15767,19 +16292,21 @@
       <c r="F379" s="8" t="n">
         <v>2804</v>
       </c>
-      <c r="G379" s="29" t="n">
+      <c r="G379" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H379" s="31" t="inlineStr">
+      <c r="H379" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I379" s="31" t="inlineStr"/>
-      <c r="J379" s="32" t="n">
+      <c r="I379" s="32" t="inlineStr"/>
+      <c r="J379" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K379" s="8" t="n"/>
+      <c r="K379" s="34" t="n">
+        <v>2804</v>
+      </c>
       <c r="L379" s="8" t="n"/>
       <c r="M379" s="8" t="n"/>
       <c r="N379" s="8" t="n"/>
@@ -15809,21 +16336,23 @@
       <c r="F380" s="8" t="n">
         <v>4137</v>
       </c>
-      <c r="G380" s="30" t="n">
+      <c r="G380" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H380" s="31" t="inlineStr">
+      <c r="H380" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I380" s="31" t="inlineStr">
+      <c r="I380" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J380" s="8" t="n"/>
-      <c r="K380" s="8" t="n"/>
+      <c r="K380" s="34" t="n">
+        <v>4137</v>
+      </c>
       <c r="L380" s="8" t="n"/>
       <c r="M380" s="8" t="n"/>
       <c r="N380" s="8" t="n"/>
@@ -16091,21 +16620,23 @@
       <c r="F388" s="8" t="n">
         <v>537</v>
       </c>
-      <c r="G388" s="30" t="n">
+      <c r="G388" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H388" s="31" t="inlineStr">
+      <c r="H388" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I388" s="31" t="inlineStr">
+      <c r="I388" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J388" s="8" t="n"/>
-      <c r="K388" s="8" t="n"/>
+      <c r="K388" s="34" t="n">
+        <v>537</v>
+      </c>
       <c r="L388" s="8" t="n"/>
       <c r="M388" s="8" t="n"/>
       <c r="N388" s="8" t="n"/>
@@ -16135,17 +16666,19 @@
       <c r="F389" s="8" t="n">
         <v>549</v>
       </c>
-      <c r="G389" s="29" t="n">
+      <c r="G389" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H389" s="31" t="inlineStr">
+      <c r="H389" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I389" s="31" t="inlineStr"/>
+      <c r="I389" s="32" t="inlineStr"/>
       <c r="J389" s="8" t="n"/>
-      <c r="K389" s="8" t="n"/>
+      <c r="K389" s="34" t="n">
+        <v>549</v>
+      </c>
       <c r="L389" s="8" t="n"/>
       <c r="M389" s="8" t="n"/>
       <c r="N389" s="8" t="n"/>
@@ -16209,21 +16742,23 @@
       <c r="F391" s="8" t="n">
         <v>3890</v>
       </c>
-      <c r="G391" s="30" t="n">
+      <c r="G391" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H391" s="31" t="inlineStr">
+      <c r="H391" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I391" s="31" t="inlineStr">
+      <c r="I391" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J391" s="8" t="n"/>
-      <c r="K391" s="8" t="n"/>
+      <c r="K391" s="34" t="n">
+        <v>3890</v>
+      </c>
       <c r="L391" s="8" t="n"/>
       <c r="M391" s="8" t="n"/>
       <c r="N391" s="8" t="n"/>
@@ -16253,19 +16788,21 @@
       <c r="F392" s="8" t="n">
         <v>1383</v>
       </c>
-      <c r="G392" s="29" t="n">
+      <c r="G392" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H392" s="31" t="inlineStr">
+      <c r="H392" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I392" s="31" t="inlineStr"/>
-      <c r="J392" s="32" t="n">
+      <c r="I392" s="32" t="inlineStr"/>
+      <c r="J392" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K392" s="8" t="n"/>
+      <c r="K392" s="34" t="n">
+        <v>1383</v>
+      </c>
       <c r="L392" s="8" t="n"/>
       <c r="M392" s="8" t="n"/>
       <c r="N392" s="8" t="n"/>
@@ -16533,21 +17070,23 @@
       <c r="F400" s="8" t="n">
         <v>187</v>
       </c>
-      <c r="G400" s="30" t="n">
+      <c r="G400" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H400" s="31" t="inlineStr">
+      <c r="H400" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I400" s="31" t="inlineStr">
+      <c r="I400" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J400" s="8" t="n"/>
-      <c r="K400" s="8" t="n"/>
+      <c r="K400" s="34" t="n">
+        <v>187</v>
+      </c>
       <c r="L400" s="8" t="n"/>
       <c r="M400" s="8" t="n"/>
       <c r="N400" s="8" t="n"/>
@@ -16577,21 +17116,23 @@
       <c r="F401" s="8" t="n">
         <v>373</v>
       </c>
-      <c r="G401" s="30" t="n">
+      <c r="G401" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H401" s="31" t="inlineStr">
+      <c r="H401" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I401" s="31" t="inlineStr">
+      <c r="I401" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J401" s="8" t="n"/>
-      <c r="K401" s="8" t="n"/>
+      <c r="K401" s="34" t="n">
+        <v>373</v>
+      </c>
       <c r="L401" s="8" t="n"/>
       <c r="M401" s="8" t="n"/>
       <c r="N401" s="8" t="n"/>
@@ -16621,19 +17162,21 @@
       <c r="F402" s="8" t="n">
         <v>1702</v>
       </c>
-      <c r="G402" s="29" t="n">
+      <c r="G402" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H402" s="31" t="inlineStr">
+      <c r="H402" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I402" s="31" t="inlineStr"/>
-      <c r="J402" s="32" t="n">
+      <c r="I402" s="32" t="inlineStr"/>
+      <c r="J402" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K402" s="8" t="n"/>
+      <c r="K402" s="34" t="n">
+        <v>1702</v>
+      </c>
       <c r="L402" s="8" t="n"/>
       <c r="M402" s="8" t="n"/>
       <c r="N402" s="8" t="n"/>
@@ -16663,23 +17206,25 @@
       <c r="F403" s="8" t="n">
         <v>326</v>
       </c>
-      <c r="G403" s="30" t="n">
+      <c r="G403" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H403" s="31" t="inlineStr">
+      <c r="H403" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I403" s="31" t="inlineStr">
+      <c r="I403" s="32" t="inlineStr">
         <is>
           <t>002566</t>
         </is>
       </c>
-      <c r="J403" s="32" t="n">
+      <c r="J403" s="33" t="n">
         <v>35999</v>
       </c>
-      <c r="K403" s="8" t="n"/>
+      <c r="K403" s="34" t="n">
+        <v>2446</v>
+      </c>
       <c r="L403" s="8" t="n"/>
       <c r="M403" s="8" t="n"/>
       <c r="N403" s="8" t="n"/>
@@ -16709,21 +17254,23 @@
       <c r="F404" s="8" t="n">
         <v>3451</v>
       </c>
-      <c r="G404" s="30" t="n">
+      <c r="G404" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H404" s="31" t="inlineStr">
+      <c r="H404" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I404" s="31" t="inlineStr">
+      <c r="I404" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J404" s="8" t="n"/>
-      <c r="K404" s="8" t="n"/>
+      <c r="K404" s="34" t="n">
+        <v>3451</v>
+      </c>
       <c r="L404" s="8" t="n"/>
       <c r="M404" s="8" t="n"/>
       <c r="N404" s="8" t="n"/>
@@ -16787,17 +17334,19 @@
       <c r="F406" s="8" t="n">
         <v>572</v>
       </c>
-      <c r="G406" s="30" t="n">
+      <c r="G406" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H406" s="31" t="inlineStr">
+      <c r="H406" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I406" s="31" t="inlineStr"/>
+      <c r="I406" s="32" t="inlineStr"/>
       <c r="J406" s="8" t="n"/>
-      <c r="K406" s="8" t="n"/>
+      <c r="K406" s="34" t="n">
+        <v>572</v>
+      </c>
       <c r="L406" s="8" t="n"/>
       <c r="M406" s="8" t="n"/>
       <c r="N406" s="8" t="n"/>
@@ -16827,17 +17376,19 @@
       <c r="F407" s="8" t="n">
         <v>1361</v>
       </c>
-      <c r="G407" s="29" t="n">
+      <c r="G407" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H407" s="31" t="inlineStr">
+      <c r="H407" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I407" s="31" t="inlineStr"/>
+      <c r="I407" s="32" t="inlineStr"/>
       <c r="J407" s="8" t="n"/>
-      <c r="K407" s="8" t="n"/>
+      <c r="K407" s="34" t="n">
+        <v>1361</v>
+      </c>
       <c r="L407" s="8" t="n"/>
       <c r="M407" s="8" t="n"/>
       <c r="N407" s="8" t="n"/>
@@ -16935,21 +17486,23 @@
       <c r="F410" s="8" t="n">
         <v>1328</v>
       </c>
-      <c r="G410" s="29" t="n">
+      <c r="G410" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H410" s="31" t="inlineStr">
+      <c r="H410" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I410" s="31" t="inlineStr">
+      <c r="I410" s="32" t="inlineStr">
         <is>
           <t>002558</t>
         </is>
       </c>
       <c r="J410" s="8" t="n"/>
-      <c r="K410" s="8" t="n"/>
+      <c r="K410" s="34" t="n">
+        <v>1328</v>
+      </c>
       <c r="L410" s="8" t="n"/>
       <c r="M410" s="8" t="n"/>
       <c r="N410" s="8" t="n"/>
@@ -16979,21 +17532,23 @@
       <c r="F411" s="8" t="n">
         <v>9819</v>
       </c>
-      <c r="G411" s="30" t="n">
+      <c r="G411" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H411" s="31" t="inlineStr">
+      <c r="H411" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I411" s="31" t="inlineStr">
+      <c r="I411" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J411" s="8" t="n"/>
-      <c r="K411" s="8" t="n"/>
+      <c r="K411" s="34" t="n">
+        <v>9819</v>
+      </c>
       <c r="L411" s="8" t="n"/>
       <c r="M411" s="8" t="n"/>
       <c r="N411" s="8" t="n"/>
@@ -17057,17 +17612,19 @@
       <c r="F413" s="8" t="n">
         <v>2485</v>
       </c>
-      <c r="G413" s="30" t="n">
+      <c r="G413" s="31" t="n">
         <v>45872</v>
       </c>
-      <c r="H413" s="31" t="inlineStr">
+      <c r="H413" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I413" s="31" t="inlineStr"/>
+      <c r="I413" s="32" t="inlineStr"/>
       <c r="J413" s="8" t="n"/>
-      <c r="K413" s="8" t="n"/>
+      <c r="K413" s="34" t="n">
+        <v>2485</v>
+      </c>
       <c r="L413" s="8" t="n"/>
       <c r="M413" s="8" t="n"/>
       <c r="N413" s="8" t="n"/>
@@ -17097,21 +17654,23 @@
       <c r="F414" s="8" t="n">
         <v>8436</v>
       </c>
-      <c r="G414" s="30" t="n">
+      <c r="G414" s="31" t="n">
         <v>45915</v>
       </c>
-      <c r="H414" s="31" t="inlineStr">
+      <c r="H414" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I414" s="31" t="inlineStr">
+      <c r="I414" s="32" t="inlineStr">
         <is>
           <t>002617</t>
         </is>
       </c>
       <c r="J414" s="8" t="n"/>
-      <c r="K414" s="8" t="n"/>
+      <c r="K414" s="34" t="n">
+        <v>8436</v>
+      </c>
       <c r="L414" s="8" t="n"/>
       <c r="M414" s="8" t="n"/>
       <c r="N414" s="8" t="n"/>
@@ -17209,21 +17768,23 @@
       <c r="F417" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="G417" s="30" t="n">
+      <c r="G417" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H417" s="31" t="inlineStr">
+      <c r="H417" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I417" s="31" t="inlineStr">
+      <c r="I417" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J417" s="8" t="n"/>
-      <c r="K417" s="8" t="n"/>
+      <c r="K417" s="34" t="n">
+        <v>260</v>
+      </c>
       <c r="L417" s="8" t="n"/>
       <c r="M417" s="8" t="n"/>
       <c r="N417" s="8" t="n"/>
@@ -17253,19 +17814,21 @@
       <c r="F418" s="8" t="n">
         <v>1038</v>
       </c>
-      <c r="G418" s="29" t="n">
+      <c r="G418" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H418" s="31" t="inlineStr">
+      <c r="H418" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I418" s="31" t="inlineStr"/>
-      <c r="J418" s="32" t="n">
+      <c r="I418" s="32" t="inlineStr"/>
+      <c r="J418" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K418" s="8" t="n"/>
+      <c r="K418" s="34" t="n">
+        <v>1038</v>
+      </c>
       <c r="L418" s="8" t="n"/>
       <c r="M418" s="8" t="n"/>
       <c r="N418" s="8" t="n"/>
@@ -17295,17 +17858,19 @@
       <c r="F419" s="8" t="n">
         <v>3323</v>
       </c>
-      <c r="G419" s="30" t="n">
+      <c r="G419" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H419" s="31" t="inlineStr">
+      <c r="H419" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I419" s="31" t="inlineStr"/>
+      <c r="I419" s="32" t="inlineStr"/>
       <c r="J419" s="8" t="n"/>
-      <c r="K419" s="8" t="n"/>
+      <c r="K419" s="34" t="n">
+        <v>3323</v>
+      </c>
       <c r="L419" s="8" t="n"/>
       <c r="M419" s="8" t="n"/>
       <c r="N419" s="8" t="n"/>
@@ -17369,21 +17934,23 @@
       <c r="F421" s="8" t="n">
         <v>3005</v>
       </c>
-      <c r="G421" s="30" t="n">
+      <c r="G421" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H421" s="31" t="inlineStr">
+      <c r="H421" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I421" s="31" t="inlineStr">
+      <c r="I421" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J421" s="8" t="n"/>
-      <c r="K421" s="8" t="n"/>
+      <c r="K421" s="34" t="n">
+        <v>3005</v>
+      </c>
       <c r="L421" s="8" t="n"/>
       <c r="M421" s="8" t="n"/>
       <c r="N421" s="8" t="n"/>
@@ -17413,17 +17980,19 @@
       <c r="F422" s="8" t="n">
         <v>4104</v>
       </c>
-      <c r="G422" s="29" t="n">
+      <c r="G422" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H422" s="31" t="inlineStr">
+      <c r="H422" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I422" s="31" t="inlineStr"/>
+      <c r="I422" s="32" t="inlineStr"/>
       <c r="J422" s="8" t="n"/>
-      <c r="K422" s="8" t="n"/>
+      <c r="K422" s="34" t="n">
+        <v>4104</v>
+      </c>
       <c r="L422" s="8" t="n"/>
       <c r="M422" s="8" t="n"/>
       <c r="N422" s="8" t="n"/>
@@ -17657,21 +18226,23 @@
       <c r="F429" s="8" t="n">
         <v>2932</v>
       </c>
-      <c r="G429" s="30" t="n">
+      <c r="G429" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H429" s="31" t="inlineStr">
+      <c r="H429" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I429" s="31" t="inlineStr">
+      <c r="I429" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J429" s="8" t="n"/>
-      <c r="K429" s="8" t="n"/>
+      <c r="K429" s="34" t="n">
+        <v>2932</v>
+      </c>
       <c r="L429" s="8" t="n"/>
       <c r="M429" s="8" t="n"/>
       <c r="N429" s="8" t="n"/>
@@ -17701,21 +18272,23 @@
       <c r="F430" s="8" t="n">
         <v>1053</v>
       </c>
-      <c r="G430" s="30" t="n">
+      <c r="G430" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H430" s="31" t="inlineStr">
+      <c r="H430" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I430" s="31" t="inlineStr">
+      <c r="I430" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J430" s="8" t="n"/>
-      <c r="K430" s="8" t="n"/>
+      <c r="K430" s="34" t="n">
+        <v>1053</v>
+      </c>
       <c r="L430" s="8" t="n"/>
       <c r="M430" s="8" t="n"/>
       <c r="N430" s="8" t="n"/>
@@ -17745,19 +18318,21 @@
       <c r="F431" s="8" t="n">
         <v>1814</v>
       </c>
-      <c r="G431" s="29" t="n">
+      <c r="G431" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H431" s="31" t="inlineStr">
+      <c r="H431" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I431" s="31" t="inlineStr"/>
-      <c r="J431" s="32" t="n">
+      <c r="I431" s="32" t="inlineStr"/>
+      <c r="J431" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K431" s="8" t="n"/>
+      <c r="K431" s="34" t="n">
+        <v>1814</v>
+      </c>
       <c r="L431" s="8" t="n"/>
       <c r="M431" s="8" t="n"/>
       <c r="N431" s="8" t="n"/>
@@ -17957,17 +18532,19 @@
       <c r="F437" s="8" t="n">
         <v>1070</v>
       </c>
-      <c r="G437" s="29" t="n">
+      <c r="G437" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H437" s="31" t="inlineStr">
+      <c r="H437" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I437" s="31" t="inlineStr"/>
+      <c r="I437" s="32" t="inlineStr"/>
       <c r="J437" s="8" t="n"/>
-      <c r="K437" s="8" t="n"/>
+      <c r="K437" s="34" t="n">
+        <v>1070</v>
+      </c>
       <c r="L437" s="8" t="n"/>
       <c r="M437" s="8" t="n"/>
       <c r="N437" s="8" t="n"/>
@@ -17997,17 +18574,19 @@
       <c r="F438" s="8" t="n">
         <v>1649</v>
       </c>
-      <c r="G438" s="30" t="n">
+      <c r="G438" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H438" s="31" t="inlineStr">
+      <c r="H438" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I438" s="31" t="inlineStr"/>
+      <c r="I438" s="32" t="inlineStr"/>
       <c r="J438" s="8" t="n"/>
-      <c r="K438" s="8" t="n"/>
+      <c r="K438" s="34" t="n">
+        <v>1649</v>
+      </c>
       <c r="L438" s="8" t="n"/>
       <c r="M438" s="8" t="n"/>
       <c r="N438" s="8" t="n"/>
@@ -18241,17 +18820,19 @@
       <c r="F445" s="8" t="n">
         <v>3693</v>
       </c>
-      <c r="G445" s="30" t="n">
+      <c r="G445" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H445" s="31" t="inlineStr">
+      <c r="H445" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I445" s="31" t="inlineStr"/>
+      <c r="I445" s="32" t="inlineStr"/>
       <c r="J445" s="8" t="n"/>
-      <c r="K445" s="8" t="n"/>
+      <c r="K445" s="34" t="n">
+        <v>3693</v>
+      </c>
       <c r="L445" s="8" t="n"/>
       <c r="M445" s="8" t="n"/>
       <c r="N445" s="8" t="n"/>
@@ -18281,21 +18862,23 @@
       <c r="F446" s="8" t="n">
         <v>827</v>
       </c>
-      <c r="G446" s="30" t="n">
+      <c r="G446" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H446" s="31" t="inlineStr">
+      <c r="H446" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I446" s="31" t="inlineStr">
+      <c r="I446" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J446" s="8" t="n"/>
-      <c r="K446" s="8" t="n"/>
+      <c r="K446" s="34" t="n">
+        <v>827</v>
+      </c>
       <c r="L446" s="8" t="n"/>
       <c r="M446" s="8" t="n"/>
       <c r="N446" s="8" t="n"/>
@@ -18359,17 +18942,19 @@
       <c r="F448" s="8" t="n">
         <v>697</v>
       </c>
-      <c r="G448" s="29" t="n">
+      <c r="G448" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H448" s="31" t="inlineStr">
+      <c r="H448" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I448" s="31" t="inlineStr"/>
+      <c r="I448" s="32" t="inlineStr"/>
       <c r="J448" s="8" t="n"/>
-      <c r="K448" s="8" t="n"/>
+      <c r="K448" s="34" t="n">
+        <v>697</v>
+      </c>
       <c r="L448" s="8" t="n"/>
       <c r="M448" s="8" t="n"/>
       <c r="N448" s="8" t="n"/>
@@ -18399,19 +18984,21 @@
       <c r="F449" s="8" t="n">
         <v>3664</v>
       </c>
-      <c r="G449" s="29" t="n">
+      <c r="G449" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H449" s="31" t="inlineStr">
+      <c r="H449" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I449" s="31" t="inlineStr"/>
-      <c r="J449" s="32" t="n">
+      <c r="I449" s="32" t="inlineStr"/>
+      <c r="J449" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K449" s="8" t="n"/>
+      <c r="K449" s="34" t="n">
+        <v>3664</v>
+      </c>
       <c r="L449" s="8" t="n"/>
       <c r="M449" s="8" t="n"/>
       <c r="N449" s="8" t="n"/>
@@ -18475,21 +19062,23 @@
       <c r="F451" s="8" t="n">
         <v>220</v>
       </c>
-      <c r="G451" s="30" t="n">
+      <c r="G451" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H451" s="31" t="inlineStr">
+      <c r="H451" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I451" s="31" t="inlineStr">
+      <c r="I451" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J451" s="8" t="n"/>
-      <c r="K451" s="8" t="n"/>
+      <c r="K451" s="34" t="n">
+        <v>220</v>
+      </c>
       <c r="L451" s="8" t="n"/>
       <c r="M451" s="8" t="n"/>
       <c r="N451" s="8" t="n"/>
@@ -18519,17 +19108,19 @@
       <c r="F452" s="8" t="n">
         <v>219</v>
       </c>
-      <c r="G452" s="30" t="n">
+      <c r="G452" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H452" s="31" t="inlineStr">
+      <c r="H452" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I452" s="31" t="inlineStr"/>
+      <c r="I452" s="32" t="inlineStr"/>
       <c r="J452" s="8" t="n"/>
-      <c r="K452" s="8" t="n"/>
+      <c r="K452" s="34" t="n">
+        <v>219</v>
+      </c>
       <c r="L452" s="8" t="n"/>
       <c r="M452" s="8" t="n"/>
       <c r="N452" s="8" t="n"/>
@@ -18559,19 +19150,21 @@
       <c r="F453" s="8" t="n">
         <v>543</v>
       </c>
-      <c r="G453" s="29" t="n">
+      <c r="G453" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H453" s="31" t="inlineStr">
+      <c r="H453" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I453" s="31" t="inlineStr"/>
-      <c r="J453" s="32" t="n">
+      <c r="I453" s="32" t="inlineStr"/>
+      <c r="J453" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K453" s="8" t="n"/>
+      <c r="K453" s="34" t="n">
+        <v>543</v>
+      </c>
       <c r="L453" s="8" t="n"/>
       <c r="M453" s="8" t="n"/>
       <c r="N453" s="8" t="n"/>
@@ -18601,21 +19194,23 @@
       <c r="F454" s="8" t="n">
         <v>3788</v>
       </c>
-      <c r="G454" s="30" t="n">
+      <c r="G454" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H454" s="31" t="inlineStr">
+      <c r="H454" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I454" s="31" t="inlineStr">
+      <c r="I454" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J454" s="8" t="n"/>
-      <c r="K454" s="8" t="n"/>
+      <c r="K454" s="34" t="n">
+        <v>3788</v>
+      </c>
       <c r="L454" s="8" t="n"/>
       <c r="M454" s="8" t="n"/>
       <c r="N454" s="8" t="n"/>
@@ -18815,21 +19410,23 @@
       <c r="F460" s="8" t="n">
         <v>687</v>
       </c>
-      <c r="G460" s="30" t="n">
+      <c r="G460" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H460" s="31" t="inlineStr">
+      <c r="H460" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I460" s="31" t="inlineStr">
+      <c r="I460" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J460" s="8" t="n"/>
-      <c r="K460" s="8" t="n"/>
+      <c r="K460" s="34" t="n">
+        <v>687</v>
+      </c>
       <c r="L460" s="8" t="n"/>
       <c r="M460" s="8" t="n"/>
       <c r="N460" s="8" t="n"/>
@@ -18859,17 +19456,19 @@
       <c r="F461" s="8" t="n">
         <v>2403</v>
       </c>
-      <c r="G461" s="29" t="n">
+      <c r="G461" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H461" s="31" t="inlineStr">
+      <c r="H461" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I461" s="31" t="inlineStr"/>
+      <c r="I461" s="32" t="inlineStr"/>
       <c r="J461" s="8" t="n"/>
-      <c r="K461" s="8" t="n"/>
+      <c r="K461" s="34" t="n">
+        <v>2403</v>
+      </c>
       <c r="L461" s="8" t="n"/>
       <c r="M461" s="8" t="n"/>
       <c r="N461" s="8" t="n"/>
@@ -18899,21 +19498,23 @@
       <c r="F462" s="8" t="n">
         <v>871</v>
       </c>
-      <c r="G462" s="30" t="n">
+      <c r="G462" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H462" s="31" t="inlineStr">
+      <c r="H462" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I462" s="31" t="inlineStr">
+      <c r="I462" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J462" s="8" t="n"/>
-      <c r="K462" s="8" t="n"/>
+      <c r="K462" s="34" t="n">
+        <v>871</v>
+      </c>
       <c r="L462" s="8" t="n"/>
       <c r="M462" s="8" t="n"/>
       <c r="N462" s="8" t="n"/>
@@ -18943,21 +19544,23 @@
       <c r="F463" s="8" t="n">
         <v>1214</v>
       </c>
-      <c r="G463" s="30" t="n">
+      <c r="G463" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H463" s="31" t="inlineStr">
+      <c r="H463" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I463" s="31" t="inlineStr">
+      <c r="I463" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J463" s="8" t="n"/>
-      <c r="K463" s="8" t="n"/>
+      <c r="K463" s="34" t="n">
+        <v>1214</v>
+      </c>
       <c r="L463" s="8" t="n"/>
       <c r="M463" s="8" t="n"/>
       <c r="N463" s="8" t="n"/>
@@ -18987,17 +19590,19 @@
       <c r="F464" s="8" t="n">
         <v>7696</v>
       </c>
-      <c r="G464" s="30" t="n">
+      <c r="G464" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H464" s="31" t="inlineStr">
+      <c r="H464" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I464" s="31" t="inlineStr"/>
+      <c r="I464" s="32" t="inlineStr"/>
       <c r="J464" s="8" t="n"/>
-      <c r="K464" s="8" t="n"/>
+      <c r="K464" s="34" t="n">
+        <v>7696</v>
+      </c>
       <c r="L464" s="8" t="n"/>
       <c r="M464" s="8" t="n"/>
       <c r="N464" s="8" t="n"/>
@@ -19027,21 +19632,23 @@
       <c r="F465" s="8" t="n">
         <v>897</v>
       </c>
-      <c r="G465" s="30" t="n">
+      <c r="G465" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H465" s="31" t="inlineStr">
+      <c r="H465" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I465" s="31" t="inlineStr">
+      <c r="I465" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J465" s="8" t="n"/>
-      <c r="K465" s="8" t="n"/>
+      <c r="K465" s="34" t="n">
+        <v>897</v>
+      </c>
       <c r="L465" s="8" t="n"/>
       <c r="M465" s="8" t="n"/>
       <c r="N465" s="8" t="n"/>
@@ -19241,19 +19848,21 @@
       <c r="F471" s="8" t="n">
         <v>406</v>
       </c>
-      <c r="G471" s="29" t="n">
+      <c r="G471" s="30" t="n">
         <v>45883</v>
       </c>
-      <c r="H471" s="31" t="inlineStr">
+      <c r="H471" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I471" s="31" t="inlineStr"/>
-      <c r="J471" s="32" t="n">
+      <c r="I471" s="32" t="inlineStr"/>
+      <c r="J471" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="K471" s="8" t="n"/>
+      <c r="K471" s="34" t="n">
+        <v>406</v>
+      </c>
       <c r="L471" s="8" t="n"/>
       <c r="M471" s="8" t="n"/>
       <c r="N471" s="8" t="n"/>
@@ -19283,17 +19892,19 @@
       <c r="F472" s="8" t="n">
         <v>1242</v>
       </c>
-      <c r="G472" s="30" t="n">
+      <c r="G472" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H472" s="31" t="inlineStr">
+      <c r="H472" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I472" s="31" t="inlineStr"/>
+      <c r="I472" s="32" t="inlineStr"/>
       <c r="J472" s="8" t="n"/>
-      <c r="K472" s="8" t="n"/>
+      <c r="K472" s="34" t="n">
+        <v>1242</v>
+      </c>
       <c r="L472" s="8" t="n"/>
       <c r="M472" s="8" t="n"/>
       <c r="N472" s="8" t="n"/>
@@ -19323,21 +19934,23 @@
       <c r="F473" s="8" t="n">
         <v>319</v>
       </c>
-      <c r="G473" s="30" t="n">
+      <c r="G473" s="31" t="n">
         <v>45894</v>
       </c>
-      <c r="H473" s="31" t="inlineStr">
+      <c r="H473" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I473" s="31" t="inlineStr">
+      <c r="I473" s="32" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
       </c>
       <c r="J473" s="8" t="n"/>
-      <c r="K473" s="8" t="n"/>
+      <c r="K473" s="34" t="n">
+        <v>319</v>
+      </c>
       <c r="L473" s="8" t="n"/>
       <c r="M473" s="8" t="n"/>
       <c r="N473" s="8" t="n"/>
@@ -19367,21 +19980,23 @@
       <c r="F474" s="8" t="n">
         <v>3918</v>
       </c>
-      <c r="G474" s="30" t="n">
+      <c r="G474" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H474" s="31" t="inlineStr">
+      <c r="H474" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I474" s="31" t="inlineStr">
+      <c r="I474" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J474" s="8" t="n"/>
-      <c r="K474" s="8" t="n"/>
+      <c r="K474" s="34" t="n">
+        <v>3918</v>
+      </c>
       <c r="L474" s="8" t="n"/>
       <c r="M474" s="8" t="n"/>
       <c r="N474" s="8" t="n"/>
@@ -19411,17 +20026,19 @@
       <c r="F475" s="8" t="n">
         <v>1178</v>
       </c>
-      <c r="G475" s="29" t="n">
+      <c r="G475" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H475" s="31" t="inlineStr">
+      <c r="H475" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I475" s="31" t="inlineStr"/>
+      <c r="I475" s="32" t="inlineStr"/>
       <c r="J475" s="8" t="n"/>
-      <c r="K475" s="8" t="n"/>
+      <c r="K475" s="34" t="n">
+        <v>1178</v>
+      </c>
       <c r="L475" s="8" t="n"/>
       <c r="M475" s="8" t="n"/>
       <c r="N475" s="8" t="n"/>
@@ -19485,21 +20102,23 @@
       <c r="F477" s="8" t="n">
         <v>850</v>
       </c>
-      <c r="G477" s="30" t="n">
+      <c r="G477" s="31" t="n">
         <v>45899</v>
       </c>
-      <c r="H477" s="31" t="inlineStr">
+      <c r="H477" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I477" s="31" t="inlineStr">
+      <c r="I477" s="32" t="inlineStr">
         <is>
           <t>002585</t>
         </is>
       </c>
       <c r="J477" s="8" t="n"/>
-      <c r="K477" s="8" t="n"/>
+      <c r="K477" s="34" t="n">
+        <v>837</v>
+      </c>
       <c r="L477" s="8" t="n"/>
       <c r="M477" s="8" t="n"/>
       <c r="N477" s="8" t="n"/>
@@ -19563,17 +20182,19 @@
       <c r="F479" s="8" t="n">
         <v>1297</v>
       </c>
-      <c r="G479" s="30" t="n">
+      <c r="G479" s="31" t="n">
         <v>45870</v>
       </c>
-      <c r="H479" s="31" t="inlineStr">
+      <c r="H479" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I479" s="31" t="inlineStr"/>
+      <c r="I479" s="32" t="inlineStr"/>
       <c r="J479" s="8" t="n"/>
-      <c r="K479" s="8" t="n"/>
+      <c r="K479" s="34" t="n">
+        <v>1297</v>
+      </c>
       <c r="L479" s="8" t="n"/>
       <c r="M479" s="8" t="n"/>
       <c r="N479" s="8" t="n"/>
@@ -19603,17 +20224,19 @@
       <c r="F480" s="8" t="n">
         <v>866</v>
       </c>
-      <c r="G480" s="29" t="n">
+      <c r="G480" s="30" t="n">
         <v>45875</v>
       </c>
-      <c r="H480" s="31" t="inlineStr">
+      <c r="H480" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I480" s="31" t="inlineStr"/>
+      <c r="I480" s="32" t="inlineStr"/>
       <c r="J480" s="8" t="n"/>
-      <c r="K480" s="8" t="n"/>
+      <c r="K480" s="34" t="n">
+        <v>866</v>
+      </c>
       <c r="L480" s="8" t="n"/>
       <c r="M480" s="8" t="n"/>
       <c r="N480" s="8" t="n"/>
@@ -19643,21 +20266,23 @@
       <c r="F481" s="8" t="n">
         <v>4306</v>
       </c>
-      <c r="G481" s="30" t="n">
+      <c r="G481" s="31" t="n">
         <v>45925</v>
       </c>
-      <c r="H481" s="31" t="inlineStr">
+      <c r="H481" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I481" s="31" t="inlineStr">
+      <c r="I481" s="32" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
       </c>
       <c r="J481" s="8" t="n"/>
-      <c r="K481" s="8" t="n"/>
+      <c r="K481" s="34" t="n">
+        <v>4306</v>
+      </c>
       <c r="L481" s="8" t="n"/>
       <c r="M481" s="8" t="n"/>
       <c r="N481" s="8" t="n"/>
@@ -19755,21 +20380,23 @@
       <c r="F484" s="8" t="n">
         <v>990</v>
       </c>
-      <c r="G484" s="30" t="n">
+      <c r="G484" s="31" t="n">
         <v>45879</v>
       </c>
-      <c r="H484" s="31" t="inlineStr">
+      <c r="H484" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I484" s="31" t="inlineStr">
+      <c r="I484" s="32" t="inlineStr">
         <is>
           <t>002561</t>
         </is>
       </c>
       <c r="J484" s="8" t="n"/>
-      <c r="K484" s="8" t="n"/>
+      <c r="K484" s="34" t="n">
+        <v>990</v>
+      </c>
       <c r="L484" s="8" t="n"/>
       <c r="M484" s="8" t="n"/>
       <c r="N484" s="8" t="n"/>
@@ -19901,17 +20528,19 @@
       <c r="F488" s="8" t="n">
         <v>4088</v>
       </c>
-      <c r="G488" s="30" t="n">
+      <c r="G488" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H488" s="31" t="inlineStr">
+      <c r="H488" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I488" s="31" t="inlineStr"/>
+      <c r="I488" s="32" t="inlineStr"/>
       <c r="J488" s="8" t="n"/>
-      <c r="K488" s="8" t="n"/>
+      <c r="K488" s="34" t="n">
+        <v>4088</v>
+      </c>
       <c r="L488" s="8" t="n"/>
       <c r="M488" s="8" t="n"/>
       <c r="N488" s="8" t="n"/>
@@ -20145,17 +20774,19 @@
       <c r="F495" s="8" t="n">
         <v>975</v>
       </c>
-      <c r="G495" s="30" t="n">
+      <c r="G495" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H495" s="31" t="inlineStr">
+      <c r="H495" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I495" s="31" t="inlineStr"/>
+      <c r="I495" s="32" t="inlineStr"/>
       <c r="J495" s="8" t="n"/>
-      <c r="K495" s="8" t="n"/>
+      <c r="K495" s="34" t="n">
+        <v>975</v>
+      </c>
       <c r="L495" s="8" t="n"/>
       <c r="M495" s="8" t="n"/>
       <c r="N495" s="8" t="n"/>
@@ -20253,17 +20884,19 @@
       <c r="F498" s="8" t="n">
         <v>584</v>
       </c>
-      <c r="G498" s="30" t="n">
+      <c r="G498" s="31" t="n">
         <v>45872</v>
       </c>
-      <c r="H498" s="31" t="inlineStr">
+      <c r="H498" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I498" s="31" t="inlineStr"/>
+      <c r="I498" s="32" t="inlineStr"/>
       <c r="J498" s="8" t="n"/>
-      <c r="K498" s="8" t="n"/>
+      <c r="K498" s="34" t="n">
+        <v>584</v>
+      </c>
       <c r="L498" s="8" t="n"/>
       <c r="M498" s="8" t="n"/>
       <c r="N498" s="8" t="n"/>
@@ -20531,17 +21164,19 @@
       <c r="F506" s="8" t="n">
         <v>2038</v>
       </c>
-      <c r="G506" s="30" t="n">
+      <c r="G506" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H506" s="31" t="inlineStr">
+      <c r="H506" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I506" s="31" t="inlineStr"/>
+      <c r="I506" s="32" t="inlineStr"/>
       <c r="J506" s="8" t="n"/>
-      <c r="K506" s="8" t="n"/>
+      <c r="K506" s="34" t="n">
+        <v>2038</v>
+      </c>
       <c r="L506" s="8" t="n"/>
       <c r="M506" s="8" t="n"/>
       <c r="N506" s="8" t="n"/>
@@ -20843,17 +21478,19 @@
       <c r="F515" s="8" t="n">
         <v>3209</v>
       </c>
-      <c r="G515" s="30" t="n">
+      <c r="G515" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H515" s="31" t="inlineStr">
+      <c r="H515" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I515" s="31" t="inlineStr"/>
+      <c r="I515" s="32" t="inlineStr"/>
       <c r="J515" s="8" t="n"/>
-      <c r="K515" s="8" t="n"/>
+      <c r="K515" s="34" t="n">
+        <v>3209</v>
+      </c>
       <c r="L515" s="8" t="n"/>
       <c r="M515" s="8" t="n"/>
       <c r="N515" s="8" t="n"/>
@@ -21087,17 +21724,19 @@
       <c r="F522" s="8" t="n">
         <v>6518</v>
       </c>
-      <c r="G522" s="30" t="n">
+      <c r="G522" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H522" s="31" t="inlineStr">
+      <c r="H522" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I522" s="31" t="inlineStr"/>
+      <c r="I522" s="32" t="inlineStr"/>
       <c r="J522" s="8" t="n"/>
-      <c r="K522" s="8" t="n"/>
+      <c r="K522" s="34" t="n">
+        <v>6518</v>
+      </c>
       <c r="L522" s="8" t="n"/>
       <c r="M522" s="8" t="n"/>
       <c r="N522" s="8" t="n"/>
@@ -21671,17 +22310,19 @@
       <c r="F539" s="8" t="n">
         <v>193</v>
       </c>
-      <c r="G539" s="30" t="n">
+      <c r="G539" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H539" s="31" t="inlineStr">
+      <c r="H539" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I539" s="31" t="inlineStr"/>
+      <c r="I539" s="32" t="inlineStr"/>
       <c r="J539" s="8" t="n"/>
-      <c r="K539" s="8" t="n"/>
+      <c r="K539" s="34" t="n">
+        <v>193</v>
+      </c>
       <c r="L539" s="8" t="n"/>
       <c r="M539" s="8" t="n"/>
       <c r="N539" s="8" t="n"/>
@@ -21847,17 +22488,19 @@
       <c r="F544" s="8" t="n">
         <v>392</v>
       </c>
-      <c r="G544" s="30" t="n">
+      <c r="G544" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H544" s="31" t="inlineStr">
+      <c r="H544" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I544" s="31" t="inlineStr"/>
+      <c r="I544" s="32" t="inlineStr"/>
       <c r="J544" s="8" t="n"/>
-      <c r="K544" s="8" t="n"/>
+      <c r="K544" s="34" t="n">
+        <v>392</v>
+      </c>
       <c r="L544" s="8" t="n"/>
       <c r="M544" s="8" t="n"/>
       <c r="N544" s="8" t="n"/>
@@ -22159,17 +22802,19 @@
       <c r="F553" s="8" t="n">
         <v>2086</v>
       </c>
-      <c r="G553" s="30" t="n">
+      <c r="G553" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H553" s="31" t="inlineStr">
+      <c r="H553" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I553" s="31" t="inlineStr"/>
+      <c r="I553" s="32" t="inlineStr"/>
       <c r="J553" s="8" t="n"/>
-      <c r="K553" s="8" t="n"/>
+      <c r="K553" s="34" t="n">
+        <v>2086</v>
+      </c>
       <c r="L553" s="8" t="n"/>
       <c r="M553" s="8" t="n"/>
       <c r="N553" s="8" t="n"/>
@@ -22471,17 +23116,19 @@
       <c r="F562" s="8" t="n">
         <v>1167</v>
       </c>
-      <c r="G562" s="30" t="n">
+      <c r="G562" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H562" s="31" t="inlineStr">
+      <c r="H562" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I562" s="31" t="inlineStr"/>
+      <c r="I562" s="32" t="inlineStr"/>
       <c r="J562" s="8" t="n"/>
-      <c r="K562" s="8" t="n"/>
+      <c r="K562" s="34" t="n">
+        <v>1167</v>
+      </c>
       <c r="L562" s="8" t="n"/>
       <c r="M562" s="8" t="n"/>
       <c r="N562" s="8" t="n"/>
@@ -22715,17 +23362,19 @@
       <c r="F569" s="8" t="n">
         <v>832</v>
       </c>
-      <c r="G569" s="30" t="n">
+      <c r="G569" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H569" s="31" t="inlineStr">
+      <c r="H569" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I569" s="31" t="inlineStr"/>
+      <c r="I569" s="32" t="inlineStr"/>
       <c r="J569" s="8" t="n"/>
-      <c r="K569" s="8" t="n"/>
+      <c r="K569" s="34" t="n">
+        <v>832</v>
+      </c>
       <c r="L569" s="8" t="n"/>
       <c r="M569" s="8" t="n"/>
       <c r="N569" s="8" t="n"/>
@@ -23163,17 +23812,19 @@
       <c r="F582" s="8" t="n">
         <v>7116</v>
       </c>
-      <c r="G582" s="30" t="n">
+      <c r="G582" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H582" s="31" t="inlineStr">
+      <c r="H582" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I582" s="31" t="inlineStr"/>
+      <c r="I582" s="32" t="inlineStr"/>
       <c r="J582" s="8" t="n"/>
-      <c r="K582" s="8" t="n"/>
+      <c r="K582" s="34" t="n">
+        <v>7116</v>
+      </c>
       <c r="L582" s="8" t="n"/>
       <c r="M582" s="8" t="n"/>
       <c r="N582" s="8" t="n"/>
@@ -23679,17 +24330,19 @@
       <c r="F597" s="8" t="n">
         <v>5597</v>
       </c>
-      <c r="G597" s="30" t="n">
+      <c r="G597" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H597" s="31" t="inlineStr">
+      <c r="H597" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I597" s="31" t="inlineStr"/>
+      <c r="I597" s="32" t="inlineStr"/>
       <c r="J597" s="8" t="n"/>
-      <c r="K597" s="8" t="n"/>
+      <c r="K597" s="34" t="n">
+        <v>5597</v>
+      </c>
       <c r="L597" s="8" t="n"/>
       <c r="M597" s="8" t="n"/>
       <c r="N597" s="8" t="n"/>
@@ -23923,17 +24576,19 @@
       <c r="F604" s="8" t="n">
         <v>270</v>
       </c>
-      <c r="G604" s="30" t="n">
+      <c r="G604" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H604" s="31" t="inlineStr">
+      <c r="H604" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I604" s="31" t="inlineStr"/>
+      <c r="I604" s="32" t="inlineStr"/>
       <c r="J604" s="8" t="n"/>
-      <c r="K604" s="8" t="n"/>
+      <c r="K604" s="34" t="n">
+        <v>270</v>
+      </c>
       <c r="L604" s="8" t="n"/>
       <c r="M604" s="8" t="n"/>
       <c r="N604" s="8" t="n"/>
@@ -24133,17 +24788,19 @@
       <c r="F610" s="8" t="n">
         <v>5786</v>
       </c>
-      <c r="G610" s="30" t="n">
+      <c r="G610" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H610" s="31" t="inlineStr">
+      <c r="H610" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I610" s="31" t="inlineStr"/>
+      <c r="I610" s="32" t="inlineStr"/>
       <c r="J610" s="8" t="n"/>
-      <c r="K610" s="8" t="n"/>
+      <c r="K610" s="34" t="n">
+        <v>5786</v>
+      </c>
       <c r="L610" s="8" t="n"/>
       <c r="M610" s="8" t="n"/>
       <c r="N610" s="8" t="n"/>
@@ -24615,21 +25272,23 @@
       <c r="F624" s="8" t="n">
         <v>6054</v>
       </c>
-      <c r="G624" s="30" t="n">
+      <c r="G624" s="31" t="n">
         <v>45915</v>
       </c>
-      <c r="H624" s="31" t="inlineStr">
+      <c r="H624" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I624" s="31" t="inlineStr">
+      <c r="I624" s="32" t="inlineStr">
         <is>
           <t>002617</t>
         </is>
       </c>
       <c r="J624" s="8" t="n"/>
-      <c r="K624" s="8" t="n"/>
+      <c r="K624" s="34" t="n">
+        <v>6054</v>
+      </c>
       <c r="L624" s="8" t="n"/>
       <c r="M624" s="8" t="n"/>
       <c r="N624" s="8" t="n"/>
@@ -24897,17 +25556,19 @@
       <c r="F632" s="8" t="n">
         <v>2743</v>
       </c>
-      <c r="G632" s="30" t="n">
+      <c r="G632" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H632" s="31" t="inlineStr">
+      <c r="H632" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I632" s="31" t="inlineStr"/>
+      <c r="I632" s="32" t="inlineStr"/>
       <c r="J632" s="8" t="n"/>
-      <c r="K632" s="8" t="n"/>
+      <c r="K632" s="34" t="n">
+        <v>2743</v>
+      </c>
       <c r="L632" s="8" t="n"/>
       <c r="M632" s="8" t="n"/>
       <c r="N632" s="8" t="n"/>
@@ -24971,17 +25632,19 @@
       <c r="F634" s="8" t="n">
         <v>2381</v>
       </c>
-      <c r="G634" s="30" t="n">
+      <c r="G634" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H634" s="31" t="inlineStr">
+      <c r="H634" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I634" s="31" t="inlineStr"/>
+      <c r="I634" s="32" t="inlineStr"/>
       <c r="J634" s="8" t="n"/>
-      <c r="K634" s="8" t="n"/>
+      <c r="K634" s="34" t="n">
+        <v>2381</v>
+      </c>
       <c r="L634" s="8" t="n"/>
       <c r="M634" s="8" t="n"/>
       <c r="N634" s="8" t="n"/>
@@ -25623,17 +26286,19 @@
       <c r="F653" s="8" t="n">
         <v>422</v>
       </c>
-      <c r="G653" s="30" t="n">
+      <c r="G653" s="31" t="n">
         <v>45902</v>
       </c>
-      <c r="H653" s="31" t="inlineStr">
+      <c r="H653" s="32" t="inlineStr">
         <is>
           <t>GPAY</t>
         </is>
       </c>
-      <c r="I653" s="31" t="inlineStr"/>
+      <c r="I653" s="32" t="inlineStr"/>
       <c r="J653" s="8" t="n"/>
-      <c r="K653" s="8" t="n"/>
+      <c r="K653" s="34" t="n">
+        <v>422</v>
+      </c>
       <c r="L653" s="8" t="n"/>
       <c r="M653" s="8" t="n"/>
       <c r="N653" s="8" t="n"/>
@@ -27805,17 +28470,19 @@
       <c r="F717" s="8" t="n">
         <v>2009</v>
       </c>
-      <c r="G717" s="31" t="n"/>
-      <c r="H717" s="31" t="inlineStr">
+      <c r="G717" s="32" t="n"/>
+      <c r="H717" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I717" s="31" t="inlineStr"/>
-      <c r="J717" s="32" t="n">
+      <c r="I717" s="32" t="inlineStr"/>
+      <c r="J717" s="33" t="n">
         <v>3884</v>
       </c>
-      <c r="K717" s="8" t="n"/>
+      <c r="K717" s="34" t="n">
+        <v>3884</v>
+      </c>
       <c r="L717" s="8" t="n"/>
       <c r="M717" s="8" t="n"/>
       <c r="N717" s="8" t="n"/>
@@ -29341,23 +30008,25 @@
       <c r="F762" s="8" t="n">
         <v>1086</v>
       </c>
-      <c r="G762" s="29" t="n">
+      <c r="G762" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H762" s="31" t="inlineStr">
+      <c r="H762" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I762" s="31" t="inlineStr">
+      <c r="I762" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J762" s="32" t="n">
+      <c r="J762" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K762" s="8" t="n"/>
+      <c r="K762" s="34" t="n">
+        <v>13738</v>
+      </c>
       <c r="L762" s="8" t="n"/>
       <c r="M762" s="8" t="n"/>
       <c r="N762" s="8" t="n"/>
@@ -30407,23 +31076,25 @@
       <c r="F793" s="8" t="n">
         <v>2587</v>
       </c>
-      <c r="G793" s="29" t="n">
+      <c r="G793" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H793" s="31" t="inlineStr">
+      <c r="H793" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I793" s="31" t="inlineStr">
+      <c r="I793" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J793" s="32" t="n">
+      <c r="J793" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K793" s="8" t="n"/>
+      <c r="K793" s="34" t="n">
+        <v>8869</v>
+      </c>
       <c r="L793" s="8" t="n"/>
       <c r="M793" s="8" t="n"/>
       <c r="N793" s="8" t="n"/>
@@ -30589,17 +31260,19 @@
       <c r="F798" s="8" t="n">
         <v>3354</v>
       </c>
-      <c r="G798" s="31" t="n"/>
-      <c r="H798" s="31" t="inlineStr">
+      <c r="G798" s="32" t="n"/>
+      <c r="H798" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I798" s="31" t="inlineStr"/>
-      <c r="J798" s="32" t="n">
+      <c r="I798" s="32" t="inlineStr"/>
+      <c r="J798" s="33" t="n">
         <v>68712</v>
       </c>
-      <c r="K798" s="8" t="n"/>
+      <c r="K798" s="34" t="n">
+        <v>15048</v>
+      </c>
       <c r="L798" s="8" t="n"/>
       <c r="M798" s="8" t="n"/>
       <c r="N798" s="8" t="n"/>
@@ -31037,23 +31710,25 @@
       <c r="F811" s="8" t="n">
         <v>808</v>
       </c>
-      <c r="G811" s="29" t="n">
+      <c r="G811" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H811" s="31" t="inlineStr">
+      <c r="H811" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I811" s="31" t="inlineStr">
+      <c r="I811" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J811" s="32" t="n">
+      <c r="J811" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K811" s="8" t="n"/>
+      <c r="K811" s="34" t="n">
+        <v>9151</v>
+      </c>
       <c r="L811" s="8" t="n"/>
       <c r="M811" s="8" t="n"/>
       <c r="N811" s="8" t="n"/>
@@ -31491,23 +32166,25 @@
       <c r="F824" s="8" t="n">
         <v>1689</v>
       </c>
-      <c r="G824" s="29" t="n">
+      <c r="G824" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H824" s="31" t="inlineStr">
+      <c r="H824" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I824" s="31" t="inlineStr">
+      <c r="I824" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J824" s="32" t="n">
+      <c r="J824" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K824" s="8" t="n"/>
+      <c r="K824" s="34" t="n">
+        <v>2355</v>
+      </c>
       <c r="L824" s="8" t="n"/>
       <c r="M824" s="8" t="n"/>
       <c r="N824" s="8" t="n"/>
@@ -32453,23 +33130,25 @@
       <c r="F852" s="11" t="n">
         <v>45934</v>
       </c>
-      <c r="G852" s="29" t="n">
+      <c r="G852" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H852" s="31" t="inlineStr">
+      <c r="H852" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I852" s="31" t="inlineStr">
+      <c r="I852" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J852" s="32" t="n">
+      <c r="J852" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K852" s="8" t="n"/>
+      <c r="K852" s="34" t="n">
+        <v>3812</v>
+      </c>
       <c r="L852" s="8" t="n"/>
       <c r="M852" s="11" t="n"/>
       <c r="N852" s="8" t="n"/>
@@ -33455,23 +34134,25 @@
         <v>6054</v>
       </c>
       <c r="F885" s="8" t="n"/>
-      <c r="G885" s="29" t="n">
+      <c r="G885" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H885" s="31" t="inlineStr">
+      <c r="H885" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I885" s="31" t="inlineStr">
+      <c r="I885" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J885" s="32" t="n">
+      <c r="J885" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K885" s="8" t="n"/>
+      <c r="K885" s="34" t="n">
+        <v>2162</v>
+      </c>
       <c r="L885" s="8" t="n"/>
       <c r="M885" s="8" t="n"/>
       <c r="N885" s="8" t="n"/>
@@ -34187,23 +34868,25 @@
         <v>10130</v>
       </c>
       <c r="F909" s="8" t="n"/>
-      <c r="G909" s="29" t="n">
+      <c r="G909" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H909" s="31" t="inlineStr">
+      <c r="H909" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I909" s="31" t="inlineStr">
+      <c r="I909" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J909" s="32" t="n">
+      <c r="J909" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K909" s="8" t="n"/>
+      <c r="K909" s="34" t="n">
+        <v>5659</v>
+      </c>
       <c r="L909" s="8" t="n"/>
       <c r="M909" s="8" t="n"/>
       <c r="N909" s="8" t="n"/>
@@ -34439,23 +35122,25 @@
         <v>1597</v>
       </c>
       <c r="F917" s="8" t="n"/>
-      <c r="G917" s="29" t="n">
+      <c r="G917" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H917" s="31" t="inlineStr">
+      <c r="H917" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I917" s="31" t="inlineStr">
+      <c r="I917" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J917" s="32" t="n">
+      <c r="J917" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K917" s="8" t="n"/>
+      <c r="K917" s="34" t="n">
+        <v>349</v>
+      </c>
       <c r="L917" s="8" t="n"/>
       <c r="M917" s="8" t="n"/>
       <c r="N917" s="8" t="n"/>
@@ -34631,23 +35316,25 @@
         <v>600</v>
       </c>
       <c r="F923" s="8" t="n"/>
-      <c r="G923" s="29" t="n">
+      <c r="G923" s="30" t="n">
         <v>45894</v>
       </c>
-      <c r="H923" s="31" t="inlineStr">
+      <c r="H923" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I923" s="31" t="inlineStr">
+      <c r="I923" s="32" t="inlineStr">
         <is>
           <t>002566</t>
         </is>
       </c>
-      <c r="J923" s="32" t="n">
+      <c r="J923" s="33" t="n">
         <v>35999</v>
       </c>
-      <c r="K923" s="8" t="n"/>
+      <c r="K923" s="34" t="n">
+        <v>20294</v>
+      </c>
       <c r="L923" s="8" t="n"/>
       <c r="M923" s="8" t="n"/>
       <c r="N923" s="8" t="n"/>
@@ -34673,23 +35360,25 @@
         <v>325</v>
       </c>
       <c r="F924" s="8" t="n"/>
-      <c r="G924" s="29" t="n">
+      <c r="G924" s="30" t="n">
         <v>45894</v>
       </c>
-      <c r="H924" s="31" t="inlineStr">
+      <c r="H924" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I924" s="31" t="inlineStr">
+      <c r="I924" s="32" t="inlineStr">
         <is>
           <t>002566</t>
         </is>
       </c>
-      <c r="J924" s="32" t="n">
+      <c r="J924" s="33" t="n">
         <v>35999</v>
       </c>
-      <c r="K924" s="8" t="n"/>
+      <c r="K924" s="34" t="n">
+        <v>11561</v>
+      </c>
       <c r="L924" s="8" t="n"/>
       <c r="M924" s="8" t="n"/>
       <c r="N924" s="8" t="n"/>
@@ -35045,17 +35734,19 @@
         <v>1306</v>
       </c>
       <c r="F936" s="8" t="n"/>
-      <c r="G936" s="31" t="n"/>
-      <c r="H936" s="31" t="inlineStr">
+      <c r="G936" s="32" t="n"/>
+      <c r="H936" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I936" s="31" t="inlineStr"/>
-      <c r="J936" s="32" t="n">
+      <c r="I936" s="32" t="inlineStr"/>
+      <c r="J936" s="33" t="n">
         <v>68712</v>
       </c>
-      <c r="K936" s="8" t="n"/>
+      <c r="K936" s="34" t="n">
+        <v>6314</v>
+      </c>
       <c r="L936" s="8" t="n"/>
       <c r="M936" s="8" t="n"/>
       <c r="N936" s="8" t="n"/>
@@ -35081,17 +35772,19 @@
         <v>23909</v>
       </c>
       <c r="F937" s="8" t="n"/>
-      <c r="G937" s="31" t="n"/>
-      <c r="H937" s="31" t="inlineStr">
+      <c r="G937" s="32" t="n"/>
+      <c r="H937" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I937" s="31" t="inlineStr"/>
-      <c r="J937" s="32" t="n">
+      <c r="I937" s="32" t="inlineStr"/>
+      <c r="J937" s="33" t="n">
         <v>68712</v>
       </c>
-      <c r="K937" s="8" t="n"/>
+      <c r="K937" s="34" t="n">
+        <v>959</v>
+      </c>
       <c r="L937" s="8" t="n"/>
       <c r="M937" s="8" t="n"/>
       <c r="N937" s="8" t="n"/>
@@ -35297,23 +35990,25 @@
         <v>168</v>
       </c>
       <c r="F944" s="8" t="n"/>
-      <c r="G944" s="29" t="n">
+      <c r="G944" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H944" s="31" t="inlineStr">
+      <c r="H944" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I944" s="31" t="inlineStr">
+      <c r="I944" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J944" s="32" t="n">
+      <c r="J944" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K944" s="8" t="n"/>
+      <c r="K944" s="34" t="n">
+        <v>5670</v>
+      </c>
       <c r="L944" s="8" t="n"/>
       <c r="M944" s="8" t="n"/>
       <c r="N944" s="8" t="n"/>
@@ -37529,23 +38224,25 @@
         <v>3369</v>
       </c>
       <c r="F1018" s="8" t="n"/>
-      <c r="G1018" s="29" t="n">
+      <c r="G1018" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H1018" s="31" t="inlineStr">
+      <c r="H1018" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I1018" s="31" t="inlineStr">
+      <c r="I1018" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J1018" s="32" t="n">
+      <c r="J1018" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K1018" s="8" t="n"/>
+      <c r="K1018" s="34" t="n">
+        <v>12245</v>
+      </c>
       <c r="L1018" s="8" t="n"/>
       <c r="M1018" s="8" t="n"/>
       <c r="N1018" s="8" t="n"/>
@@ -37631,23 +38328,25 @@
         <v>310</v>
       </c>
       <c r="F1021" s="8" t="n"/>
-      <c r="G1021" s="29" t="n">
+      <c r="G1021" s="30" t="n">
         <v>45817</v>
       </c>
-      <c r="H1021" s="31" t="inlineStr">
+      <c r="H1021" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I1021" s="31" t="inlineStr">
+      <c r="I1021" s="32" t="inlineStr">
         <is>
           <t>002419</t>
         </is>
       </c>
-      <c r="J1021" s="32" t="n">
+      <c r="J1021" s="33" t="n">
         <v>70582</v>
       </c>
-      <c r="K1021" s="8" t="n"/>
+      <c r="K1021" s="34" t="n">
+        <v>1110</v>
+      </c>
       <c r="L1021" s="8" t="n"/>
       <c r="M1021" s="8" t="n"/>
       <c r="N1021" s="8" t="n"/>
@@ -37893,14 +38592,14 @@
       <c r="N1029" s="12" t="n"/>
     </row>
     <row r="1030" ht="15" customHeight="1" thickBot="1">
-      <c r="A1030" s="36" t="inlineStr">
+      <c r="A1030" s="39" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B1030" s="37" t="n"/>
-      <c r="C1030" s="37" t="n"/>
-      <c r="D1030" s="38" t="n"/>
+      <c r="B1030" s="40" t="n"/>
+      <c r="C1030" s="40" t="n"/>
+      <c r="D1030" s="41" t="n"/>
       <c r="E1030" s="23">
         <f>SUM(E852:E1029)</f>
         <v/>

--- a/System_Puchase.xlsx
+++ b/System_Puchase.xlsx
@@ -43,7 +43,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
         <bgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -270,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
@@ -320,10 +332,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1386,7 +1400,9 @@
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
+      <c r="M13" s="35" t="n">
+        <v>3746</v>
+      </c>
       <c r="N13" s="8" t="n"/>
     </row>
     <row r="14">
@@ -1556,7 +1572,9 @@
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
+      <c r="M17" s="35" t="n">
+        <v>3417</v>
+      </c>
       <c r="N17" s="8" t="n"/>
     </row>
     <row r="18">
@@ -1590,7 +1608,9 @@
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
+      <c r="M18" s="35" t="n">
+        <v>1550</v>
+      </c>
       <c r="N18" s="8" t="n"/>
     </row>
     <row r="19">
@@ -1624,7 +1644,9 @@
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
+      <c r="M19" s="35" t="n">
+        <v>2298</v>
+      </c>
       <c r="N19" s="8" t="n"/>
     </row>
     <row r="20">
@@ -1838,7 +1860,9 @@
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
+      <c r="M24" s="35" t="n">
+        <v>3721</v>
+      </c>
       <c r="N24" s="8" t="n"/>
     </row>
     <row r="25">
@@ -1872,7 +1896,9 @@
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
-      <c r="M25" s="8" t="n"/>
+      <c r="M25" s="35" t="n">
+        <v>11835</v>
+      </c>
       <c r="N25" s="8" t="n"/>
     </row>
     <row r="26">
@@ -1900,21 +1926,21 @@
       <c r="F26" s="12" t="n">
         <v>3567</v>
       </c>
-      <c r="G26" s="35" t="n">
+      <c r="G26" s="36" t="n">
         <v>45868</v>
       </c>
-      <c r="H26" s="35" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I26" s="36" t="inlineStr">
+      <c r="I26" s="37" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
       </c>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="37" t="n">
+      <c r="K26" s="38" t="n">
         <v>3567</v>
       </c>
       <c r="L26" s="12" t="n"/>
@@ -1959,7 +1985,7 @@
           <t>002562</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n">
+      <c r="J27" s="39" t="n">
         <v>9492</v>
       </c>
       <c r="K27" s="29" t="n">
@@ -2000,7 +2026,9 @@
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
+      <c r="M28" s="35" t="n">
+        <v>4074</v>
+      </c>
       <c r="N28" s="8" t="n"/>
     </row>
     <row r="29">
@@ -2082,7 +2110,9 @@
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="n"/>
-      <c r="M30" s="8" t="n"/>
+      <c r="M30" s="35" t="n">
+        <v>3309</v>
+      </c>
       <c r="N30" s="8" t="n"/>
     </row>
     <row r="31">
@@ -2116,7 +2146,9 @@
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="8" t="n"/>
-      <c r="M31" s="8" t="n"/>
+      <c r="M31" s="35" t="n">
+        <v>170</v>
+      </c>
       <c r="N31" s="8" t="n"/>
     </row>
     <row r="32">
@@ -3284,7 +3316,9 @@
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
-      <c r="M58" s="8" t="n"/>
+      <c r="M58" s="35" t="n">
+        <v>4166</v>
+      </c>
       <c r="N58" s="8" t="n"/>
     </row>
     <row r="59">
@@ -3318,7 +3352,9 @@
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
-      <c r="M59" s="8" t="n"/>
+      <c r="M59" s="35" t="n">
+        <v>6665</v>
+      </c>
       <c r="N59" s="8" t="n"/>
     </row>
     <row r="60">
@@ -3352,7 +3388,9 @@
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
-      <c r="M60" s="8" t="n"/>
+      <c r="M60" s="35" t="n">
+        <v>5628</v>
+      </c>
       <c r="N60" s="8" t="n"/>
     </row>
     <row r="61">
@@ -3386,7 +3424,9 @@
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
-      <c r="M61" s="8" t="n"/>
+      <c r="M61" s="35" t="n">
+        <v>4336</v>
+      </c>
       <c r="N61" s="8" t="n"/>
     </row>
     <row r="62">
@@ -3420,7 +3460,9 @@
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
-      <c r="M62" s="8" t="n"/>
+      <c r="M62" s="35" t="n">
+        <v>2105</v>
+      </c>
       <c r="N62" s="8" t="n"/>
     </row>
     <row r="63">
@@ -3542,7 +3584,9 @@
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
-      <c r="M65" s="8" t="n"/>
+      <c r="M65" s="35" t="n">
+        <v>2937</v>
+      </c>
       <c r="N65" s="8" t="n"/>
     </row>
     <row r="66">
@@ -3576,7 +3620,9 @@
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
-      <c r="M66" s="8" t="n"/>
+      <c r="M66" s="35" t="n">
+        <v>9091</v>
+      </c>
       <c r="N66" s="8" t="n"/>
     </row>
     <row r="67">
@@ -3702,7 +3748,9 @@
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8" t="n"/>
+      <c r="M69" s="35" t="n">
+        <v>3604</v>
+      </c>
       <c r="N69" s="8" t="n"/>
     </row>
     <row r="70">
@@ -3736,7 +3784,9 @@
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
-      <c r="M70" s="8" t="n"/>
+      <c r="M70" s="35" t="n">
+        <v>1102</v>
+      </c>
       <c r="N70" s="8" t="n"/>
     </row>
     <row r="71">
@@ -3980,7 +4030,9 @@
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
-      <c r="M76" s="8" t="n"/>
+      <c r="M76" s="35" t="n">
+        <v>20026</v>
+      </c>
       <c r="N76" s="8" t="n"/>
     </row>
     <row r="77">
@@ -4060,7 +4112,9 @@
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
-      <c r="M78" s="8" t="n"/>
+      <c r="M78" s="35" t="n">
+        <v>2221</v>
+      </c>
       <c r="N78" s="8" t="n"/>
     </row>
     <row r="79">
@@ -4094,7 +4148,9 @@
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
-      <c r="M79" s="8" t="n"/>
+      <c r="M79" s="35" t="n">
+        <v>5450</v>
+      </c>
       <c r="N79" s="8" t="n"/>
     </row>
     <row r="80">
@@ -4220,7 +4276,9 @@
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
-      <c r="M82" s="8" t="n"/>
+      <c r="M82" s="35" t="n">
+        <v>1296</v>
+      </c>
       <c r="N82" s="8" t="n"/>
     </row>
     <row r="83">
@@ -4254,7 +4312,9 @@
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
-      <c r="M83" s="8" t="n"/>
+      <c r="M83" s="35" t="n">
+        <v>992</v>
+      </c>
       <c r="N83" s="8" t="n"/>
     </row>
     <row r="84">
@@ -4334,7 +4394,9 @@
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
-      <c r="M85" s="8" t="n"/>
+      <c r="M85" s="35" t="n">
+        <v>5040</v>
+      </c>
       <c r="N85" s="8" t="n"/>
     </row>
     <row r="86">
@@ -4368,7 +4430,9 @@
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
-      <c r="M86" s="8" t="n"/>
+      <c r="M86" s="35" t="n">
+        <v>1260</v>
+      </c>
       <c r="N86" s="8" t="n"/>
     </row>
     <row r="87">
@@ -4664,7 +4728,9 @@
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8" t="n"/>
+      <c r="M93" s="35" t="n">
+        <v>1557</v>
+      </c>
       <c r="N93" s="8" t="n"/>
     </row>
     <row r="94">
@@ -4698,7 +4764,9 @@
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
-      <c r="M94" s="8" t="n"/>
+      <c r="M94" s="35" t="n">
+        <v>2305</v>
+      </c>
       <c r="N94" s="8" t="n"/>
     </row>
     <row r="95">
@@ -4732,7 +4800,9 @@
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
-      <c r="M95" s="8" t="n"/>
+      <c r="M95" s="35" t="n">
+        <v>964</v>
+      </c>
       <c r="N95" s="8" t="n"/>
     </row>
     <row r="96">
@@ -5116,7 +5186,9 @@
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
-      <c r="M104" s="8" t="n"/>
+      <c r="M104" s="35" t="n">
+        <v>1630</v>
+      </c>
       <c r="N104" s="8" t="n"/>
     </row>
     <row r="105">
@@ -5242,7 +5314,9 @@
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
-      <c r="M107" s="8" t="n"/>
+      <c r="M107" s="35" t="n">
+        <v>1370</v>
+      </c>
       <c r="N107" s="8" t="n"/>
     </row>
     <row r="108">
@@ -5368,7 +5442,9 @@
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
-      <c r="M110" s="8" t="n"/>
+      <c r="M110" s="35" t="n">
+        <v>624</v>
+      </c>
       <c r="N110" s="8" t="n"/>
     </row>
     <row r="111">
@@ -5750,7 +5826,9 @@
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
-      <c r="M119" s="8" t="n"/>
+      <c r="M119" s="35" t="n">
+        <v>4115</v>
+      </c>
       <c r="N119" s="8" t="n"/>
     </row>
     <row r="120">
@@ -5830,7 +5908,9 @@
       <c r="J121" s="8" t="n"/>
       <c r="K121" s="8" t="n"/>
       <c r="L121" s="8" t="n"/>
-      <c r="M121" s="8" t="n"/>
+      <c r="M121" s="35" t="n">
+        <v>4522</v>
+      </c>
       <c r="N121" s="8" t="n"/>
     </row>
     <row r="122">
@@ -5864,7 +5944,9 @@
       <c r="J122" s="8" t="n"/>
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
-      <c r="M122" s="8" t="n"/>
+      <c r="M122" s="35" t="n">
+        <v>708</v>
+      </c>
       <c r="N122" s="8" t="n"/>
     </row>
     <row r="123">
@@ -5898,7 +5980,9 @@
       <c r="J123" s="8" t="n"/>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
-      <c r="M123" s="8" t="n"/>
+      <c r="M123" s="35" t="n">
+        <v>149</v>
+      </c>
       <c r="N123" s="8" t="n"/>
     </row>
     <row r="124">
@@ -5932,7 +6016,9 @@
       <c r="J124" s="8" t="n"/>
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
-      <c r="M124" s="8" t="n"/>
+      <c r="M124" s="35" t="n">
+        <v>1775</v>
+      </c>
       <c r="N124" s="8" t="n"/>
     </row>
     <row r="125">
@@ -5966,7 +6052,9 @@
       <c r="J125" s="8" t="n"/>
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
-      <c r="M125" s="8" t="n"/>
+      <c r="M125" s="35" t="n">
+        <v>744</v>
+      </c>
       <c r="N125" s="8" t="n"/>
     </row>
     <row r="126">
@@ -6000,7 +6088,9 @@
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
-      <c r="M126" s="8" t="n"/>
+      <c r="M126" s="35" t="n">
+        <v>1053</v>
+      </c>
       <c r="N126" s="8" t="n"/>
     </row>
     <row r="127">
@@ -6034,7 +6124,9 @@
       <c r="J127" s="8" t="n"/>
       <c r="K127" s="8" t="n"/>
       <c r="L127" s="8" t="n"/>
-      <c r="M127" s="8" t="n"/>
+      <c r="M127" s="35" t="n">
+        <v>138</v>
+      </c>
       <c r="N127" s="8" t="n"/>
     </row>
     <row r="128">
@@ -6068,7 +6160,9 @@
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
-      <c r="M128" s="8" t="n"/>
+      <c r="M128" s="35" t="n">
+        <v>2503</v>
+      </c>
       <c r="N128" s="8" t="n"/>
     </row>
     <row r="129">
@@ -6408,7 +6502,9 @@
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
-      <c r="M136" s="8" t="n"/>
+      <c r="M136" s="35" t="n">
+        <v>1594</v>
+      </c>
       <c r="N136" s="8" t="n"/>
     </row>
     <row r="137">
@@ -6490,7 +6586,9 @@
       <c r="J138" s="8" t="n"/>
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
-      <c r="M138" s="8" t="n"/>
+      <c r="M138" s="35" t="n">
+        <v>1242</v>
+      </c>
       <c r="N138" s="8" t="n"/>
     </row>
     <row r="139">
@@ -7054,7 +7152,9 @@
       <c r="J151" s="8" t="n"/>
       <c r="K151" s="8" t="n"/>
       <c r="L151" s="8" t="n"/>
-      <c r="M151" s="8" t="n"/>
+      <c r="M151" s="35" t="n">
+        <v>420</v>
+      </c>
       <c r="N151" s="8" t="n"/>
     </row>
     <row r="152">
@@ -7134,7 +7234,9 @@
       <c r="J153" s="8" t="n"/>
       <c r="K153" s="8" t="n"/>
       <c r="L153" s="8" t="n"/>
-      <c r="M153" s="8" t="n"/>
+      <c r="M153" s="35" t="n">
+        <v>2645</v>
+      </c>
       <c r="N153" s="8" t="n"/>
     </row>
     <row r="154">
@@ -7168,7 +7270,9 @@
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
-      <c r="M154" s="8" t="n"/>
+      <c r="M154" s="35" t="n">
+        <v>2937</v>
+      </c>
       <c r="N154" s="8" t="n"/>
     </row>
     <row r="155">
@@ -7504,7 +7608,9 @@
       <c r="J162" s="8" t="n"/>
       <c r="K162" s="8" t="n"/>
       <c r="L162" s="8" t="n"/>
-      <c r="M162" s="8" t="n"/>
+      <c r="M162" s="35" t="n">
+        <v>11006</v>
+      </c>
       <c r="N162" s="8" t="n"/>
     </row>
     <row r="163">
@@ -7538,7 +7644,9 @@
       <c r="J163" s="8" t="n"/>
       <c r="K163" s="8" t="n"/>
       <c r="L163" s="8" t="n"/>
-      <c r="M163" s="8" t="n"/>
+      <c r="M163" s="35" t="n">
+        <v>11542</v>
+      </c>
       <c r="N163" s="8" t="n"/>
     </row>
     <row r="164">
@@ -7572,7 +7680,9 @@
       <c r="J164" s="8" t="n"/>
       <c r="K164" s="8" t="n"/>
       <c r="L164" s="8" t="n"/>
-      <c r="M164" s="8" t="n"/>
+      <c r="M164" s="35" t="n">
+        <v>5185</v>
+      </c>
       <c r="N164" s="8" t="n"/>
     </row>
     <row r="165">
@@ -7606,7 +7716,9 @@
       <c r="J165" s="8" t="n"/>
       <c r="K165" s="8" t="n"/>
       <c r="L165" s="8" t="n"/>
-      <c r="M165" s="8" t="n"/>
+      <c r="M165" s="35" t="n">
+        <v>7645</v>
+      </c>
       <c r="N165" s="8" t="n"/>
     </row>
     <row r="166">
@@ -7640,7 +7752,9 @@
       <c r="J166" s="8" t="n"/>
       <c r="K166" s="8" t="n"/>
       <c r="L166" s="8" t="n"/>
-      <c r="M166" s="8" t="n"/>
+      <c r="M166" s="35" t="n">
+        <v>1070</v>
+      </c>
       <c r="N166" s="8" t="n"/>
     </row>
     <row r="167">
@@ -8022,7 +8136,9 @@
       <c r="J175" s="8" t="n"/>
       <c r="K175" s="8" t="n"/>
       <c r="L175" s="8" t="n"/>
-      <c r="M175" s="8" t="n"/>
+      <c r="M175" s="35" t="n">
+        <v>3771</v>
+      </c>
       <c r="N175" s="8" t="n"/>
     </row>
     <row r="176">
@@ -8192,7 +8308,9 @@
       <c r="J179" s="8" t="n"/>
       <c r="K179" s="8" t="n"/>
       <c r="L179" s="8" t="n"/>
-      <c r="M179" s="8" t="n"/>
+      <c r="M179" s="35" t="n">
+        <v>4200</v>
+      </c>
       <c r="N179" s="8" t="n"/>
     </row>
     <row r="180">
@@ -8226,7 +8344,9 @@
       <c r="J180" s="8" t="n"/>
       <c r="K180" s="8" t="n"/>
       <c r="L180" s="8" t="n"/>
-      <c r="M180" s="8" t="n"/>
+      <c r="M180" s="35" t="n">
+        <v>14379</v>
+      </c>
       <c r="N180" s="8" t="n"/>
     </row>
     <row r="181">
@@ -8260,7 +8380,9 @@
       <c r="J181" s="8" t="n"/>
       <c r="K181" s="8" t="n"/>
       <c r="L181" s="8" t="n"/>
-      <c r="M181" s="8" t="n"/>
+      <c r="M181" s="35" t="n">
+        <v>8349</v>
+      </c>
       <c r="N181" s="8" t="n"/>
     </row>
     <row r="182">
@@ -8294,7 +8416,9 @@
       <c r="J182" s="8" t="n"/>
       <c r="K182" s="8" t="n"/>
       <c r="L182" s="8" t="n"/>
-      <c r="M182" s="8" t="n"/>
+      <c r="M182" s="35" t="n">
+        <v>2216</v>
+      </c>
       <c r="N182" s="8" t="n"/>
     </row>
     <row r="183">
@@ -8550,7 +8674,9 @@
       <c r="J188" s="8" t="n"/>
       <c r="K188" s="8" t="n"/>
       <c r="L188" s="8" t="n"/>
-      <c r="M188" s="8" t="n"/>
+      <c r="M188" s="35" t="n">
+        <v>2015</v>
+      </c>
       <c r="N188" s="8" t="n"/>
     </row>
     <row r="189">
@@ -8630,7 +8756,9 @@
       <c r="J190" s="8" t="n"/>
       <c r="K190" s="8" t="n"/>
       <c r="L190" s="8" t="n"/>
-      <c r="M190" s="8" t="n"/>
+      <c r="M190" s="35" t="n">
+        <v>3130</v>
+      </c>
       <c r="N190" s="8" t="n"/>
     </row>
     <row r="191">
@@ -8966,7 +9094,9 @@
       <c r="J198" s="8" t="n"/>
       <c r="K198" s="8" t="n"/>
       <c r="L198" s="8" t="n"/>
-      <c r="M198" s="8" t="n"/>
+      <c r="M198" s="35" t="n">
+        <v>2984</v>
+      </c>
       <c r="N198" s="8" t="n"/>
     </row>
     <row r="199">
@@ -9000,7 +9130,9 @@
       <c r="J199" s="8" t="n"/>
       <c r="K199" s="8" t="n"/>
       <c r="L199" s="8" t="n"/>
-      <c r="M199" s="8" t="n"/>
+      <c r="M199" s="35" t="n">
+        <v>4839</v>
+      </c>
       <c r="N199" s="8" t="n"/>
     </row>
     <row r="200">
@@ -9252,7 +9384,9 @@
       <c r="J205" s="8" t="n"/>
       <c r="K205" s="8" t="n"/>
       <c r="L205" s="8" t="n"/>
-      <c r="M205" s="8" t="n"/>
+      <c r="M205" s="35" t="n">
+        <v>1458</v>
+      </c>
       <c r="N205" s="8" t="n"/>
     </row>
     <row r="206">
@@ -9636,7 +9770,9 @@
       <c r="J214" s="8" t="n"/>
       <c r="K214" s="8" t="n"/>
       <c r="L214" s="8" t="n"/>
-      <c r="M214" s="8" t="n"/>
+      <c r="M214" s="35" t="n">
+        <v>3464</v>
+      </c>
       <c r="N214" s="8" t="n"/>
     </row>
     <row r="215">
@@ -9670,7 +9806,9 @@
       <c r="J215" s="8" t="n"/>
       <c r="K215" s="8" t="n"/>
       <c r="L215" s="8" t="n"/>
-      <c r="M215" s="8" t="n"/>
+      <c r="M215" s="35" t="n">
+        <v>1630</v>
+      </c>
       <c r="N215" s="8" t="n"/>
     </row>
     <row r="216">
@@ -9704,7 +9842,9 @@
       <c r="J216" s="8" t="n"/>
       <c r="K216" s="8" t="n"/>
       <c r="L216" s="8" t="n"/>
-      <c r="M216" s="8" t="n"/>
+      <c r="M216" s="35" t="n">
+        <v>4300</v>
+      </c>
       <c r="N216" s="8" t="n"/>
     </row>
     <row r="217">
@@ -9738,7 +9878,9 @@
       <c r="J217" s="8" t="n"/>
       <c r="K217" s="8" t="n"/>
       <c r="L217" s="8" t="n"/>
-      <c r="M217" s="8" t="n"/>
+      <c r="M217" s="35" t="n">
+        <v>1068</v>
+      </c>
       <c r="N217" s="8" t="n"/>
     </row>
     <row r="218">
@@ -10032,7 +10174,9 @@
       <c r="J224" s="8" t="n"/>
       <c r="K224" s="8" t="n"/>
       <c r="L224" s="8" t="n"/>
-      <c r="M224" s="8" t="n"/>
+      <c r="M224" s="35" t="n">
+        <v>1756</v>
+      </c>
       <c r="N224" s="8" t="n"/>
     </row>
     <row r="225">
@@ -10066,7 +10210,9 @@
       <c r="J225" s="8" t="n"/>
       <c r="K225" s="8" t="n"/>
       <c r="L225" s="8" t="n"/>
-      <c r="M225" s="8" t="n"/>
+      <c r="M225" s="35" t="n">
+        <v>2925</v>
+      </c>
       <c r="N225" s="8" t="n"/>
     </row>
     <row r="226">
@@ -10100,7 +10246,9 @@
       <c r="J226" s="8" t="n"/>
       <c r="K226" s="8" t="n"/>
       <c r="L226" s="8" t="n"/>
-      <c r="M226" s="8" t="n"/>
+      <c r="M226" s="35" t="n">
+        <v>1325</v>
+      </c>
       <c r="N226" s="8" t="n"/>
     </row>
     <row r="227">
@@ -10134,7 +10282,9 @@
       <c r="J227" s="8" t="n"/>
       <c r="K227" s="8" t="n"/>
       <c r="L227" s="8" t="n"/>
-      <c r="M227" s="8" t="n"/>
+      <c r="M227" s="35" t="n">
+        <v>967</v>
+      </c>
       <c r="N227" s="8" t="n"/>
     </row>
     <row r="228">
@@ -10168,7 +10318,9 @@
       <c r="J228" s="8" t="n"/>
       <c r="K228" s="8" t="n"/>
       <c r="L228" s="8" t="n"/>
-      <c r="M228" s="8" t="n"/>
+      <c r="M228" s="35" t="n">
+        <v>6986</v>
+      </c>
       <c r="N228" s="8" t="n"/>
     </row>
     <row r="229">
@@ -10202,7 +10354,9 @@
       <c r="J229" s="8" t="n"/>
       <c r="K229" s="8" t="n"/>
       <c r="L229" s="8" t="n"/>
-      <c r="M229" s="8" t="n"/>
+      <c r="M229" s="35" t="n">
+        <v>7565</v>
+      </c>
       <c r="N229" s="8" t="n"/>
     </row>
     <row r="230">
@@ -10450,7 +10604,9 @@
       <c r="J235" s="8" t="n"/>
       <c r="K235" s="8" t="n"/>
       <c r="L235" s="8" t="n"/>
-      <c r="M235" s="8" t="n"/>
+      <c r="M235" s="35" t="n">
+        <v>6285</v>
+      </c>
       <c r="N235" s="8" t="n"/>
     </row>
     <row r="236">
@@ -11174,7 +11330,9 @@
       <c r="J252" s="8" t="n"/>
       <c r="K252" s="8" t="n"/>
       <c r="L252" s="8" t="n"/>
-      <c r="M252" s="8" t="n"/>
+      <c r="M252" s="35" t="n">
+        <v>420</v>
+      </c>
       <c r="N252" s="8" t="n"/>
     </row>
     <row r="253">
@@ -11202,21 +11360,21 @@
       <c r="F253" s="12" t="n">
         <v>4733</v>
       </c>
-      <c r="G253" s="35" t="n">
+      <c r="G253" s="36" t="n">
         <v>45915</v>
       </c>
-      <c r="H253" s="35" t="inlineStr">
+      <c r="H253" s="36" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I253" s="36" t="inlineStr">
+      <c r="I253" s="37" t="inlineStr">
         <is>
           <t>002617</t>
         </is>
       </c>
       <c r="J253" s="12" t="n"/>
-      <c r="K253" s="37" t="n">
+      <c r="K253" s="38" t="n">
         <v>4733</v>
       </c>
       <c r="L253" s="12" t="n"/>
@@ -11254,7 +11412,9 @@
       <c r="J254" s="8" t="n"/>
       <c r="K254" s="8" t="n"/>
       <c r="L254" s="8" t="n"/>
-      <c r="M254" s="8" t="n"/>
+      <c r="M254" s="35" t="n">
+        <v>2107</v>
+      </c>
       <c r="N254" s="8" t="n"/>
     </row>
     <row r="255">
@@ -11288,7 +11448,9 @@
       <c r="J255" s="8" t="n"/>
       <c r="K255" s="8" t="n"/>
       <c r="L255" s="8" t="n"/>
-      <c r="M255" s="8" t="n"/>
+      <c r="M255" s="35" t="n">
+        <v>4283</v>
+      </c>
       <c r="N255" s="8" t="n"/>
     </row>
     <row r="256">
@@ -11322,7 +11484,9 @@
       <c r="J256" s="8" t="n"/>
       <c r="K256" s="8" t="n"/>
       <c r="L256" s="8" t="n"/>
-      <c r="M256" s="8" t="n"/>
+      <c r="M256" s="35" t="n">
+        <v>4132</v>
+      </c>
       <c r="N256" s="8" t="n"/>
     </row>
     <row r="257">
@@ -11356,7 +11520,9 @@
       <c r="J257" s="8" t="n"/>
       <c r="K257" s="8" t="n"/>
       <c r="L257" s="8" t="n"/>
-      <c r="M257" s="8" t="n"/>
+      <c r="M257" s="35" t="n">
+        <v>17393</v>
+      </c>
       <c r="N257" s="8" t="n"/>
     </row>
     <row r="258">
@@ -11740,7 +11906,9 @@
       <c r="J266" s="8" t="n"/>
       <c r="K266" s="8" t="n"/>
       <c r="L266" s="8" t="n"/>
-      <c r="M266" s="8" t="n"/>
+      <c r="M266" s="35" t="n">
+        <v>1062</v>
+      </c>
       <c r="N266" s="8" t="n"/>
     </row>
     <row r="267">
@@ -11774,7 +11942,9 @@
       <c r="J267" s="8" t="n"/>
       <c r="K267" s="8" t="n"/>
       <c r="L267" s="8" t="n"/>
-      <c r="M267" s="8" t="n"/>
+      <c r="M267" s="35" t="n">
+        <v>612</v>
+      </c>
       <c r="N267" s="8" t="n"/>
     </row>
     <row r="268">
@@ -11946,7 +12116,9 @@
       <c r="J271" s="8" t="n"/>
       <c r="K271" s="8" t="n"/>
       <c r="L271" s="8" t="n"/>
-      <c r="M271" s="8" t="n"/>
+      <c r="M271" s="35" t="n">
+        <v>6878</v>
+      </c>
       <c r="N271" s="8" t="n"/>
     </row>
     <row r="272">
@@ -11980,7 +12152,9 @@
       <c r="J272" s="8" t="n"/>
       <c r="K272" s="8" t="n"/>
       <c r="L272" s="8" t="n"/>
-      <c r="M272" s="8" t="n"/>
+      <c r="M272" s="35" t="n">
+        <v>3669</v>
+      </c>
       <c r="N272" s="8" t="n"/>
     </row>
     <row r="273">
@@ -12060,7 +12234,9 @@
       <c r="J274" s="8" t="n"/>
       <c r="K274" s="8" t="n"/>
       <c r="L274" s="8" t="n"/>
-      <c r="M274" s="8" t="n"/>
+      <c r="M274" s="35" t="n">
+        <v>1172</v>
+      </c>
       <c r="N274" s="8" t="n"/>
     </row>
     <row r="275">
@@ -12318,7 +12494,9 @@
       <c r="J280" s="8" t="n"/>
       <c r="K280" s="8" t="n"/>
       <c r="L280" s="8" t="n"/>
-      <c r="M280" s="8" t="n"/>
+      <c r="M280" s="35" t="n">
+        <v>8447</v>
+      </c>
       <c r="N280" s="8" t="n"/>
     </row>
     <row r="281">
@@ -12568,7 +12746,9 @@
       <c r="J286" s="8" t="n"/>
       <c r="K286" s="8" t="n"/>
       <c r="L286" s="8" t="n"/>
-      <c r="M286" s="8" t="n"/>
+      <c r="M286" s="35" t="n">
+        <v>2773</v>
+      </c>
       <c r="N286" s="8" t="n"/>
     </row>
     <row r="287">
@@ -12602,7 +12782,9 @@
       <c r="J287" s="8" t="n"/>
       <c r="K287" s="8" t="n"/>
       <c r="L287" s="8" t="n"/>
-      <c r="M287" s="8" t="n"/>
+      <c r="M287" s="35" t="n">
+        <v>3362</v>
+      </c>
       <c r="N287" s="8" t="n"/>
     </row>
     <row r="288">
@@ -12636,7 +12818,9 @@
       <c r="J288" s="8" t="n"/>
       <c r="K288" s="8" t="n"/>
       <c r="L288" s="8" t="n"/>
-      <c r="M288" s="8" t="n"/>
+      <c r="M288" s="35" t="n">
+        <v>1403</v>
+      </c>
       <c r="N288" s="8" t="n"/>
     </row>
     <row r="289">
@@ -12670,7 +12854,9 @@
       <c r="J289" s="8" t="n"/>
       <c r="K289" s="8" t="n"/>
       <c r="L289" s="8" t="n"/>
-      <c r="M289" s="8" t="n"/>
+      <c r="M289" s="35" t="n">
+        <v>1380</v>
+      </c>
       <c r="N289" s="8" t="n"/>
     </row>
     <row r="290">
@@ -13102,7 +13288,9 @@
       <c r="J299" s="8" t="n"/>
       <c r="K299" s="8" t="n"/>
       <c r="L299" s="8" t="n"/>
-      <c r="M299" s="8" t="n"/>
+      <c r="M299" s="35" t="n">
+        <v>679</v>
+      </c>
       <c r="N299" s="8" t="n"/>
     </row>
     <row r="300">
@@ -13180,7 +13368,9 @@
       <c r="J301" s="8" t="n"/>
       <c r="K301" s="8" t="n"/>
       <c r="L301" s="8" t="n"/>
-      <c r="M301" s="8" t="n"/>
+      <c r="M301" s="35" t="n">
+        <v>3787</v>
+      </c>
       <c r="N301" s="8" t="n"/>
     </row>
     <row r="302">
@@ -13214,7 +13404,9 @@
       <c r="J302" s="8" t="n"/>
       <c r="K302" s="8" t="n"/>
       <c r="L302" s="8" t="n"/>
-      <c r="M302" s="8" t="n"/>
+      <c r="M302" s="35" t="n">
+        <v>4037</v>
+      </c>
       <c r="N302" s="8" t="n"/>
     </row>
     <row r="303">
@@ -13248,7 +13440,9 @@
       <c r="J303" s="8" t="n"/>
       <c r="K303" s="8" t="n"/>
       <c r="L303" s="8" t="n"/>
-      <c r="M303" s="8" t="n"/>
+      <c r="M303" s="35" t="n">
+        <v>3391</v>
+      </c>
       <c r="N303" s="8" t="n"/>
     </row>
     <row r="304">
@@ -13898,7 +14092,9 @@
       <c r="J318" s="8" t="n"/>
       <c r="K318" s="8" t="n"/>
       <c r="L318" s="8" t="n"/>
-      <c r="M318" s="8" t="n"/>
+      <c r="M318" s="35" t="n">
+        <v>775</v>
+      </c>
       <c r="N318" s="8" t="n"/>
     </row>
     <row r="319">
@@ -13932,7 +14128,9 @@
       <c r="J319" s="8" t="n"/>
       <c r="K319" s="8" t="n"/>
       <c r="L319" s="8" t="n"/>
-      <c r="M319" s="8" t="n"/>
+      <c r="M319" s="35" t="n">
+        <v>676</v>
+      </c>
       <c r="N319" s="8" t="n"/>
     </row>
     <row r="320">
@@ -13966,7 +14164,9 @@
       <c r="J320" s="8" t="n"/>
       <c r="K320" s="8" t="n"/>
       <c r="L320" s="8" t="n"/>
-      <c r="M320" s="8" t="n"/>
+      <c r="M320" s="35" t="n">
+        <v>2713</v>
+      </c>
       <c r="N320" s="8" t="n"/>
     </row>
     <row r="321">
@@ -14000,7 +14200,9 @@
       <c r="J321" s="8" t="n"/>
       <c r="K321" s="8" t="n"/>
       <c r="L321" s="8" t="n"/>
-      <c r="M321" s="8" t="n"/>
+      <c r="M321" s="35" t="n">
+        <v>2294</v>
+      </c>
       <c r="N321" s="8" t="n"/>
     </row>
     <row r="322">
@@ -14080,7 +14282,9 @@
       <c r="J323" s="8" t="n"/>
       <c r="K323" s="8" t="n"/>
       <c r="L323" s="8" t="n"/>
-      <c r="M323" s="8" t="n"/>
+      <c r="M323" s="35" t="n">
+        <v>2090</v>
+      </c>
       <c r="N323" s="8" t="n"/>
     </row>
     <row r="324">
@@ -14156,7 +14360,9 @@
       <c r="J325" s="8" t="n"/>
       <c r="K325" s="8" t="n"/>
       <c r="L325" s="8" t="n"/>
-      <c r="M325" s="8" t="n"/>
+      <c r="M325" s="35" t="n">
+        <v>456</v>
+      </c>
       <c r="N325" s="8" t="n"/>
     </row>
     <row r="326">
@@ -14250,7 +14456,9 @@
         <v>1434</v>
       </c>
       <c r="L327" s="8" t="n"/>
-      <c r="M327" s="8" t="n"/>
+      <c r="M327" s="40" t="n">
+        <v>18993</v>
+      </c>
       <c r="N327" s="8" t="n"/>
     </row>
     <row r="328">
@@ -14410,7 +14618,9 @@
       <c r="J331" s="8" t="n"/>
       <c r="K331" s="8" t="n"/>
       <c r="L331" s="8" t="n"/>
-      <c r="M331" s="8" t="n"/>
+      <c r="M331" s="35" t="n">
+        <v>643</v>
+      </c>
       <c r="N331" s="8" t="n"/>
     </row>
     <row r="332">
@@ -14444,7 +14654,9 @@
       <c r="J332" s="8" t="n"/>
       <c r="K332" s="8" t="n"/>
       <c r="L332" s="8" t="n"/>
-      <c r="M332" s="8" t="n"/>
+      <c r="M332" s="35" t="n">
+        <v>1128</v>
+      </c>
       <c r="N332" s="8" t="n"/>
     </row>
     <row r="333">
@@ -14478,7 +14690,9 @@
       <c r="J333" s="8" t="n"/>
       <c r="K333" s="8" t="n"/>
       <c r="L333" s="8" t="n"/>
-      <c r="M333" s="8" t="n"/>
+      <c r="M333" s="35" t="n">
+        <v>2006</v>
+      </c>
       <c r="N333" s="8" t="n"/>
     </row>
     <row r="334">
@@ -14512,7 +14726,9 @@
       <c r="J334" s="8" t="n"/>
       <c r="K334" s="8" t="n"/>
       <c r="L334" s="8" t="n"/>
-      <c r="M334" s="8" t="n"/>
+      <c r="M334" s="35" t="n">
+        <v>4142</v>
+      </c>
       <c r="N334" s="8" t="n"/>
     </row>
     <row r="335">
@@ -14546,7 +14762,9 @@
       <c r="J335" s="8" t="n"/>
       <c r="K335" s="8" t="n"/>
       <c r="L335" s="8" t="n"/>
-      <c r="M335" s="8" t="n"/>
+      <c r="M335" s="35" t="n">
+        <v>2746</v>
+      </c>
       <c r="N335" s="8" t="n"/>
     </row>
     <row r="336">
@@ -14758,7 +14976,9 @@
       <c r="J340" s="8" t="n"/>
       <c r="K340" s="8" t="n"/>
       <c r="L340" s="8" t="n"/>
-      <c r="M340" s="8" t="n"/>
+      <c r="M340" s="35" t="n">
+        <v>1338</v>
+      </c>
       <c r="N340" s="8" t="n"/>
     </row>
     <row r="341">
@@ -14792,7 +15012,9 @@
       <c r="J341" s="8" t="n"/>
       <c r="K341" s="8" t="n"/>
       <c r="L341" s="8" t="n"/>
-      <c r="M341" s="8" t="n"/>
+      <c r="M341" s="35" t="n">
+        <v>1900</v>
+      </c>
       <c r="N341" s="8" t="n"/>
     </row>
     <row r="342">
@@ -14916,7 +15138,9 @@
       <c r="J344" s="8" t="n"/>
       <c r="K344" s="8" t="n"/>
       <c r="L344" s="8" t="n"/>
-      <c r="M344" s="8" t="n"/>
+      <c r="M344" s="35" t="n">
+        <v>2126</v>
+      </c>
       <c r="N344" s="8" t="n"/>
     </row>
     <row r="345">
@@ -14950,7 +15174,9 @@
       <c r="J345" s="8" t="n"/>
       <c r="K345" s="8" t="n"/>
       <c r="L345" s="8" t="n"/>
-      <c r="M345" s="8" t="n"/>
+      <c r="M345" s="35" t="n">
+        <v>1629</v>
+      </c>
       <c r="N345" s="8" t="n"/>
     </row>
     <row r="346">
@@ -14984,7 +15210,9 @@
       <c r="J346" s="8" t="n"/>
       <c r="K346" s="8" t="n"/>
       <c r="L346" s="8" t="n"/>
-      <c r="M346" s="8" t="n"/>
+      <c r="M346" s="35" t="n">
+        <v>5654</v>
+      </c>
       <c r="N346" s="8" t="n"/>
     </row>
     <row r="347">
@@ -15018,7 +15246,9 @@
       <c r="J347" s="8" t="n"/>
       <c r="K347" s="8" t="n"/>
       <c r="L347" s="8" t="n"/>
-      <c r="M347" s="8" t="n"/>
+      <c r="M347" s="35" t="n">
+        <v>2129</v>
+      </c>
       <c r="N347" s="8" t="n"/>
     </row>
     <row r="348">
@@ -15142,7 +15372,9 @@
       <c r="J350" s="8" t="n"/>
       <c r="K350" s="8" t="n"/>
       <c r="L350" s="8" t="n"/>
-      <c r="M350" s="8" t="n"/>
+      <c r="M350" s="35" t="n">
+        <v>23811</v>
+      </c>
       <c r="N350" s="8" t="n"/>
     </row>
     <row r="351">
@@ -15264,7 +15496,9 @@
       <c r="J353" s="8" t="n"/>
       <c r="K353" s="8" t="n"/>
       <c r="L353" s="8" t="n"/>
-      <c r="M353" s="8" t="n"/>
+      <c r="M353" s="35" t="n">
+        <v>3212</v>
+      </c>
       <c r="N353" s="8" t="n"/>
     </row>
     <row r="354">
@@ -15298,7 +15532,9 @@
       <c r="J354" s="8" t="n"/>
       <c r="K354" s="8" t="n"/>
       <c r="L354" s="8" t="n"/>
-      <c r="M354" s="8" t="n"/>
+      <c r="M354" s="35" t="n">
+        <v>3715</v>
+      </c>
       <c r="N354" s="8" t="n"/>
     </row>
     <row r="355">
@@ -15332,7 +15568,9 @@
       <c r="J355" s="8" t="n"/>
       <c r="K355" s="8" t="n"/>
       <c r="L355" s="8" t="n"/>
-      <c r="M355" s="8" t="n"/>
+      <c r="M355" s="35" t="n">
+        <v>1298</v>
+      </c>
       <c r="N355" s="8" t="n"/>
     </row>
     <row r="356">
@@ -15366,7 +15604,9 @@
       <c r="J356" s="8" t="n"/>
       <c r="K356" s="8" t="n"/>
       <c r="L356" s="8" t="n"/>
-      <c r="M356" s="8" t="n"/>
+      <c r="M356" s="35" t="n">
+        <v>12135</v>
+      </c>
       <c r="N356" s="8" t="n"/>
     </row>
     <row r="357">
@@ -15568,7 +15808,9 @@
       <c r="J361" s="8" t="n"/>
       <c r="K361" s="8" t="n"/>
       <c r="L361" s="8" t="n"/>
-      <c r="M361" s="8" t="n"/>
+      <c r="M361" s="35" t="n">
+        <v>1609</v>
+      </c>
       <c r="N361" s="8" t="n"/>
     </row>
     <row r="362">
@@ -15694,7 +15936,9 @@
       <c r="J364" s="8" t="n"/>
       <c r="K364" s="8" t="n"/>
       <c r="L364" s="8" t="n"/>
-      <c r="M364" s="8" t="n"/>
+      <c r="M364" s="35" t="n">
+        <v>8588</v>
+      </c>
       <c r="N364" s="8" t="n"/>
     </row>
     <row r="365">
@@ -15728,7 +15972,9 @@
       <c r="J365" s="8" t="n"/>
       <c r="K365" s="8" t="n"/>
       <c r="L365" s="8" t="n"/>
-      <c r="M365" s="8" t="n"/>
+      <c r="M365" s="35" t="n">
+        <v>1550</v>
+      </c>
       <c r="N365" s="8" t="n"/>
     </row>
     <row r="366">
@@ -15762,7 +16008,9 @@
       <c r="J366" s="8" t="n"/>
       <c r="K366" s="8" t="n"/>
       <c r="L366" s="8" t="n"/>
-      <c r="M366" s="8" t="n"/>
+      <c r="M366" s="35" t="n">
+        <v>1942</v>
+      </c>
       <c r="N366" s="8" t="n"/>
     </row>
     <row r="367">
@@ -15796,7 +16044,9 @@
       <c r="J367" s="8" t="n"/>
       <c r="K367" s="8" t="n"/>
       <c r="L367" s="8" t="n"/>
-      <c r="M367" s="8" t="n"/>
+      <c r="M367" s="35" t="n">
+        <v>4311</v>
+      </c>
       <c r="N367" s="8" t="n"/>
     </row>
     <row r="368">
@@ -16154,7 +16404,9 @@
         <v>93</v>
       </c>
       <c r="L375" s="8" t="n"/>
-      <c r="M375" s="8" t="n"/>
+      <c r="M375" s="40" t="n">
+        <v>910</v>
+      </c>
       <c r="N375" s="8" t="n"/>
     </row>
     <row r="376">
@@ -16188,7 +16440,9 @@
       <c r="J376" s="8" t="n"/>
       <c r="K376" s="8" t="n"/>
       <c r="L376" s="8" t="n"/>
-      <c r="M376" s="8" t="n"/>
+      <c r="M376" s="35" t="n">
+        <v>185</v>
+      </c>
       <c r="N376" s="8" t="n"/>
     </row>
     <row r="377">
@@ -16222,7 +16476,9 @@
       <c r="J377" s="8" t="n"/>
       <c r="K377" s="8" t="n"/>
       <c r="L377" s="8" t="n"/>
-      <c r="M377" s="8" t="n"/>
+      <c r="M377" s="35" t="n">
+        <v>763</v>
+      </c>
       <c r="N377" s="8" t="n"/>
     </row>
     <row r="378">
@@ -16388,7 +16644,9 @@
       <c r="J381" s="8" t="n"/>
       <c r="K381" s="8" t="n"/>
       <c r="L381" s="8" t="n"/>
-      <c r="M381" s="8" t="n"/>
+      <c r="M381" s="35" t="n">
+        <v>6090</v>
+      </c>
       <c r="N381" s="8" t="n"/>
     </row>
     <row r="382">
@@ -16422,7 +16680,9 @@
       <c r="J382" s="8" t="n"/>
       <c r="K382" s="8" t="n"/>
       <c r="L382" s="8" t="n"/>
-      <c r="M382" s="8" t="n"/>
+      <c r="M382" s="35" t="n">
+        <v>5364</v>
+      </c>
       <c r="N382" s="8" t="n"/>
     </row>
     <row r="383">
@@ -16456,7 +16716,9 @@
       <c r="J383" s="8" t="n"/>
       <c r="K383" s="8" t="n"/>
       <c r="L383" s="8" t="n"/>
-      <c r="M383" s="8" t="n"/>
+      <c r="M383" s="35" t="n">
+        <v>6610</v>
+      </c>
       <c r="N383" s="8" t="n"/>
     </row>
     <row r="384">
@@ -16490,7 +16752,9 @@
       <c r="J384" s="8" t="n"/>
       <c r="K384" s="8" t="n"/>
       <c r="L384" s="8" t="n"/>
-      <c r="M384" s="8" t="n"/>
+      <c r="M384" s="35" t="n">
+        <v>2800</v>
+      </c>
       <c r="N384" s="8" t="n"/>
     </row>
     <row r="385">
@@ -16524,7 +16788,9 @@
       <c r="J385" s="8" t="n"/>
       <c r="K385" s="8" t="n"/>
       <c r="L385" s="8" t="n"/>
-      <c r="M385" s="8" t="n"/>
+      <c r="M385" s="35" t="n">
+        <v>5696</v>
+      </c>
       <c r="N385" s="8" t="n"/>
     </row>
     <row r="386">
@@ -16558,7 +16824,9 @@
       <c r="J386" s="8" t="n"/>
       <c r="K386" s="8" t="n"/>
       <c r="L386" s="8" t="n"/>
-      <c r="M386" s="8" t="n"/>
+      <c r="M386" s="35" t="n">
+        <v>1500</v>
+      </c>
       <c r="N386" s="8" t="n"/>
     </row>
     <row r="387">
@@ -16592,7 +16860,9 @@
       <c r="J387" s="8" t="n"/>
       <c r="K387" s="8" t="n"/>
       <c r="L387" s="8" t="n"/>
-      <c r="M387" s="8" t="n"/>
+      <c r="M387" s="35" t="n">
+        <v>594</v>
+      </c>
       <c r="N387" s="8" t="n"/>
     </row>
     <row r="388">
@@ -16714,7 +16984,9 @@
       <c r="J390" s="8" t="n"/>
       <c r="K390" s="8" t="n"/>
       <c r="L390" s="8" t="n"/>
-      <c r="M390" s="8" t="n"/>
+      <c r="M390" s="35" t="n">
+        <v>1414</v>
+      </c>
       <c r="N390" s="8" t="n"/>
     </row>
     <row r="391">
@@ -16838,7 +17110,9 @@
       <c r="J393" s="8" t="n"/>
       <c r="K393" s="8" t="n"/>
       <c r="L393" s="8" t="n"/>
-      <c r="M393" s="8" t="n"/>
+      <c r="M393" s="35" t="n">
+        <v>1417</v>
+      </c>
       <c r="N393" s="8" t="n"/>
     </row>
     <row r="394">
@@ -16872,7 +17146,9 @@
       <c r="J394" s="8" t="n"/>
       <c r="K394" s="8" t="n"/>
       <c r="L394" s="8" t="n"/>
-      <c r="M394" s="8" t="n"/>
+      <c r="M394" s="35" t="n">
+        <v>1861</v>
+      </c>
       <c r="N394" s="8" t="n"/>
     </row>
     <row r="395">
@@ -16906,7 +17182,9 @@
       <c r="J395" s="8" t="n"/>
       <c r="K395" s="8" t="n"/>
       <c r="L395" s="8" t="n"/>
-      <c r="M395" s="8" t="n"/>
+      <c r="M395" s="35" t="n">
+        <v>630</v>
+      </c>
       <c r="N395" s="8" t="n"/>
     </row>
     <row r="396">
@@ -16940,7 +17218,9 @@
       <c r="J396" s="8" t="n"/>
       <c r="K396" s="8" t="n"/>
       <c r="L396" s="8" t="n"/>
-      <c r="M396" s="8" t="n"/>
+      <c r="M396" s="35" t="n">
+        <v>3246</v>
+      </c>
       <c r="N396" s="8" t="n"/>
     </row>
     <row r="397">
@@ -16974,7 +17254,9 @@
       <c r="J397" s="8" t="n"/>
       <c r="K397" s="8" t="n"/>
       <c r="L397" s="8" t="n"/>
-      <c r="M397" s="8" t="n"/>
+      <c r="M397" s="35" t="n">
+        <v>11856</v>
+      </c>
       <c r="N397" s="8" t="n"/>
     </row>
     <row r="398">
@@ -17008,7 +17290,9 @@
       <c r="J398" s="8" t="n"/>
       <c r="K398" s="8" t="n"/>
       <c r="L398" s="8" t="n"/>
-      <c r="M398" s="8" t="n"/>
+      <c r="M398" s="35" t="n">
+        <v>2394</v>
+      </c>
       <c r="N398" s="8" t="n"/>
     </row>
     <row r="399">
@@ -17042,7 +17326,9 @@
       <c r="J399" s="8" t="n"/>
       <c r="K399" s="8" t="n"/>
       <c r="L399" s="8" t="n"/>
-      <c r="M399" s="8" t="n"/>
+      <c r="M399" s="35" t="n">
+        <v>4170</v>
+      </c>
       <c r="N399" s="8" t="n"/>
     </row>
     <row r="400">
@@ -17306,7 +17592,9 @@
       <c r="J405" s="8" t="n"/>
       <c r="K405" s="8" t="n"/>
       <c r="L405" s="8" t="n"/>
-      <c r="M405" s="8" t="n"/>
+      <c r="M405" s="35" t="n">
+        <v>577</v>
+      </c>
       <c r="N405" s="8" t="n"/>
     </row>
     <row r="406">
@@ -17424,7 +17712,9 @@
       <c r="J408" s="8" t="n"/>
       <c r="K408" s="8" t="n"/>
       <c r="L408" s="8" t="n"/>
-      <c r="M408" s="8" t="n"/>
+      <c r="M408" s="35" t="n">
+        <v>3262</v>
+      </c>
       <c r="N408" s="8" t="n"/>
     </row>
     <row r="409">
@@ -17458,7 +17748,9 @@
       <c r="J409" s="8" t="n"/>
       <c r="K409" s="8" t="n"/>
       <c r="L409" s="8" t="n"/>
-      <c r="M409" s="8" t="n"/>
+      <c r="M409" s="35" t="n">
+        <v>3528</v>
+      </c>
       <c r="N409" s="8" t="n"/>
     </row>
     <row r="410">
@@ -17584,7 +17876,9 @@
       <c r="J412" s="8" t="n"/>
       <c r="K412" s="8" t="n"/>
       <c r="L412" s="8" t="n"/>
-      <c r="M412" s="8" t="n"/>
+      <c r="M412" s="35" t="n">
+        <v>4330</v>
+      </c>
       <c r="N412" s="8" t="n"/>
     </row>
     <row r="413">
@@ -17706,7 +18000,9 @@
       <c r="J415" s="8" t="n"/>
       <c r="K415" s="8" t="n"/>
       <c r="L415" s="8" t="n"/>
-      <c r="M415" s="8" t="n"/>
+      <c r="M415" s="35" t="n">
+        <v>5880</v>
+      </c>
       <c r="N415" s="8" t="n"/>
     </row>
     <row r="416">
@@ -17740,7 +18036,9 @@
       <c r="J416" s="8" t="n"/>
       <c r="K416" s="8" t="n"/>
       <c r="L416" s="8" t="n"/>
-      <c r="M416" s="8" t="n"/>
+      <c r="M416" s="35" t="n">
+        <v>1239</v>
+      </c>
       <c r="N416" s="8" t="n"/>
     </row>
     <row r="417">
@@ -17906,7 +18204,9 @@
       <c r="J420" s="8" t="n"/>
       <c r="K420" s="8" t="n"/>
       <c r="L420" s="8" t="n"/>
-      <c r="M420" s="8" t="n"/>
+      <c r="M420" s="35" t="n">
+        <v>26460</v>
+      </c>
       <c r="N420" s="8" t="n"/>
     </row>
     <row r="421">
@@ -18028,7 +18328,9 @@
       <c r="J423" s="8" t="n"/>
       <c r="K423" s="8" t="n"/>
       <c r="L423" s="8" t="n"/>
-      <c r="M423" s="8" t="n"/>
+      <c r="M423" s="35" t="n">
+        <v>645</v>
+      </c>
       <c r="N423" s="8" t="n"/>
     </row>
     <row r="424">
@@ -18062,7 +18364,9 @@
       <c r="J424" s="8" t="n"/>
       <c r="K424" s="8" t="n"/>
       <c r="L424" s="8" t="n"/>
-      <c r="M424" s="8" t="n"/>
+      <c r="M424" s="35" t="n">
+        <v>1139</v>
+      </c>
       <c r="N424" s="8" t="n"/>
     </row>
     <row r="425">
@@ -18096,7 +18400,9 @@
       <c r="J425" s="8" t="n"/>
       <c r="K425" s="8" t="n"/>
       <c r="L425" s="8" t="n"/>
-      <c r="M425" s="8" t="n"/>
+      <c r="M425" s="35" t="n">
+        <v>1060</v>
+      </c>
       <c r="N425" s="8" t="n"/>
     </row>
     <row r="426">
@@ -18130,7 +18436,9 @@
       <c r="J426" s="8" t="n"/>
       <c r="K426" s="8" t="n"/>
       <c r="L426" s="8" t="n"/>
-      <c r="M426" s="8" t="n"/>
+      <c r="M426" s="35" t="n">
+        <v>5522</v>
+      </c>
       <c r="N426" s="8" t="n"/>
     </row>
     <row r="427">
@@ -18164,7 +18472,9 @@
       <c r="J427" s="8" t="n"/>
       <c r="K427" s="8" t="n"/>
       <c r="L427" s="8" t="n"/>
-      <c r="M427" s="8" t="n"/>
+      <c r="M427" s="35" t="n">
+        <v>4050</v>
+      </c>
       <c r="N427" s="8" t="n"/>
     </row>
     <row r="428">
@@ -18198,7 +18508,9 @@
       <c r="J428" s="8" t="n"/>
       <c r="K428" s="8" t="n"/>
       <c r="L428" s="8" t="n"/>
-      <c r="M428" s="8" t="n"/>
+      <c r="M428" s="35" t="n">
+        <v>3988</v>
+      </c>
       <c r="N428" s="8" t="n"/>
     </row>
     <row r="429">
@@ -18368,7 +18680,9 @@
       <c r="J432" s="8" t="n"/>
       <c r="K432" s="8" t="n"/>
       <c r="L432" s="8" t="n"/>
-      <c r="M432" s="8" t="n"/>
+      <c r="M432" s="35" t="n">
+        <v>473</v>
+      </c>
       <c r="N432" s="8" t="n"/>
     </row>
     <row r="433">
@@ -18402,7 +18716,9 @@
       <c r="J433" s="8" t="n"/>
       <c r="K433" s="8" t="n"/>
       <c r="L433" s="8" t="n"/>
-      <c r="M433" s="8" t="n"/>
+      <c r="M433" s="35" t="n">
+        <v>12845</v>
+      </c>
       <c r="N433" s="8" t="n"/>
     </row>
     <row r="434">
@@ -18436,7 +18752,9 @@
       <c r="J434" s="8" t="n"/>
       <c r="K434" s="8" t="n"/>
       <c r="L434" s="8" t="n"/>
-      <c r="M434" s="8" t="n"/>
+      <c r="M434" s="35" t="n">
+        <v>4416</v>
+      </c>
       <c r="N434" s="8" t="n"/>
     </row>
     <row r="435">
@@ -18470,7 +18788,9 @@
       <c r="J435" s="8" t="n"/>
       <c r="K435" s="8" t="n"/>
       <c r="L435" s="8" t="n"/>
-      <c r="M435" s="8" t="n"/>
+      <c r="M435" s="35" t="n">
+        <v>7391</v>
+      </c>
       <c r="N435" s="8" t="n"/>
     </row>
     <row r="436">
@@ -18504,7 +18824,9 @@
       <c r="J436" s="8" t="n"/>
       <c r="K436" s="8" t="n"/>
       <c r="L436" s="8" t="n"/>
-      <c r="M436" s="8" t="n"/>
+      <c r="M436" s="35" t="n">
+        <v>14442</v>
+      </c>
       <c r="N436" s="8" t="n"/>
     </row>
     <row r="437">
@@ -18622,7 +18944,9 @@
       <c r="J439" s="8" t="n"/>
       <c r="K439" s="8" t="n"/>
       <c r="L439" s="8" t="n"/>
-      <c r="M439" s="8" t="n"/>
+      <c r="M439" s="35" t="n">
+        <v>5326</v>
+      </c>
       <c r="N439" s="8" t="n"/>
     </row>
     <row r="440">
@@ -18656,7 +18980,9 @@
       <c r="J440" s="8" t="n"/>
       <c r="K440" s="8" t="n"/>
       <c r="L440" s="8" t="n"/>
-      <c r="M440" s="8" t="n"/>
+      <c r="M440" s="35" t="n">
+        <v>218</v>
+      </c>
       <c r="N440" s="8" t="n"/>
     </row>
     <row r="441">
@@ -18690,7 +19016,9 @@
       <c r="J441" s="8" t="n"/>
       <c r="K441" s="8" t="n"/>
       <c r="L441" s="8" t="n"/>
-      <c r="M441" s="8" t="n"/>
+      <c r="M441" s="35" t="n">
+        <v>3020</v>
+      </c>
       <c r="N441" s="8" t="n"/>
     </row>
     <row r="442">
@@ -18724,7 +19052,9 @@
       <c r="J442" s="8" t="n"/>
       <c r="K442" s="8" t="n"/>
       <c r="L442" s="8" t="n"/>
-      <c r="M442" s="8" t="n"/>
+      <c r="M442" s="35" t="n">
+        <v>2439</v>
+      </c>
       <c r="N442" s="8" t="n"/>
     </row>
     <row r="443">
@@ -18758,7 +19088,9 @@
       <c r="J443" s="8" t="n"/>
       <c r="K443" s="8" t="n"/>
       <c r="L443" s="8" t="n"/>
-      <c r="M443" s="8" t="n"/>
+      <c r="M443" s="35" t="n">
+        <v>1880</v>
+      </c>
       <c r="N443" s="8" t="n"/>
     </row>
     <row r="444">
@@ -18792,7 +19124,9 @@
       <c r="J444" s="8" t="n"/>
       <c r="K444" s="8" t="n"/>
       <c r="L444" s="8" t="n"/>
-      <c r="M444" s="8" t="n"/>
+      <c r="M444" s="35" t="n">
+        <v>697</v>
+      </c>
       <c r="N444" s="8" t="n"/>
     </row>
     <row r="445">
@@ -18914,7 +19248,9 @@
       <c r="J447" s="8" t="n"/>
       <c r="K447" s="8" t="n"/>
       <c r="L447" s="8" t="n"/>
-      <c r="M447" s="8" t="n"/>
+      <c r="M447" s="35" t="n">
+        <v>2060</v>
+      </c>
       <c r="N447" s="8" t="n"/>
     </row>
     <row r="448">
@@ -19034,7 +19370,9 @@
       <c r="J450" s="8" t="n"/>
       <c r="K450" s="8" t="n"/>
       <c r="L450" s="8" t="n"/>
-      <c r="M450" s="8" t="n"/>
+      <c r="M450" s="35" t="n">
+        <v>1749</v>
+      </c>
       <c r="N450" s="8" t="n"/>
     </row>
     <row r="451">
@@ -19246,7 +19584,9 @@
       <c r="J455" s="8" t="n"/>
       <c r="K455" s="8" t="n"/>
       <c r="L455" s="8" t="n"/>
-      <c r="M455" s="8" t="n"/>
+      <c r="M455" s="35" t="n">
+        <v>5183</v>
+      </c>
       <c r="N455" s="8" t="n"/>
     </row>
     <row r="456">
@@ -19280,7 +19620,9 @@
       <c r="J456" s="8" t="n"/>
       <c r="K456" s="8" t="n"/>
       <c r="L456" s="8" t="n"/>
-      <c r="M456" s="8" t="n"/>
+      <c r="M456" s="35" t="n">
+        <v>4509</v>
+      </c>
       <c r="N456" s="8" t="n"/>
     </row>
     <row r="457">
@@ -19314,7 +19656,9 @@
       <c r="J457" s="8" t="n"/>
       <c r="K457" s="8" t="n"/>
       <c r="L457" s="8" t="n"/>
-      <c r="M457" s="8" t="n"/>
+      <c r="M457" s="35" t="n">
+        <v>2720</v>
+      </c>
       <c r="N457" s="8" t="n"/>
     </row>
     <row r="458">
@@ -19348,7 +19692,9 @@
       <c r="J458" s="8" t="n"/>
       <c r="K458" s="8" t="n"/>
       <c r="L458" s="8" t="n"/>
-      <c r="M458" s="8" t="n"/>
+      <c r="M458" s="35" t="n">
+        <v>1796</v>
+      </c>
       <c r="N458" s="8" t="n"/>
     </row>
     <row r="459">
@@ -19382,7 +19728,9 @@
       <c r="J459" s="8" t="n"/>
       <c r="K459" s="8" t="n"/>
       <c r="L459" s="8" t="n"/>
-      <c r="M459" s="8" t="n"/>
+      <c r="M459" s="35" t="n">
+        <v>1575</v>
+      </c>
       <c r="N459" s="8" t="n"/>
     </row>
     <row r="460">
@@ -19684,7 +20032,9 @@
       <c r="J466" s="8" t="n"/>
       <c r="K466" s="8" t="n"/>
       <c r="L466" s="8" t="n"/>
-      <c r="M466" s="8" t="n"/>
+      <c r="M466" s="35" t="n">
+        <v>5756</v>
+      </c>
       <c r="N466" s="8" t="n"/>
     </row>
     <row r="467">
@@ -19718,7 +20068,9 @@
       <c r="J467" s="8" t="n"/>
       <c r="K467" s="8" t="n"/>
       <c r="L467" s="8" t="n"/>
-      <c r="M467" s="8" t="n"/>
+      <c r="M467" s="35" t="n">
+        <v>908</v>
+      </c>
       <c r="N467" s="8" t="n"/>
     </row>
     <row r="468">
@@ -19752,7 +20104,9 @@
       <c r="J468" s="8" t="n"/>
       <c r="K468" s="8" t="n"/>
       <c r="L468" s="8" t="n"/>
-      <c r="M468" s="8" t="n"/>
+      <c r="M468" s="35" t="n">
+        <v>3015</v>
+      </c>
       <c r="N468" s="8" t="n"/>
     </row>
     <row r="469">
@@ -19786,7 +20140,9 @@
       <c r="J469" s="8" t="n"/>
       <c r="K469" s="8" t="n"/>
       <c r="L469" s="8" t="n"/>
-      <c r="M469" s="8" t="n"/>
+      <c r="M469" s="35" t="n">
+        <v>8605</v>
+      </c>
       <c r="N469" s="8" t="n"/>
     </row>
     <row r="470">
@@ -19820,7 +20176,9 @@
       <c r="J470" s="8" t="n"/>
       <c r="K470" s="8" t="n"/>
       <c r="L470" s="8" t="n"/>
-      <c r="M470" s="8" t="n"/>
+      <c r="M470" s="35" t="n">
+        <v>2420</v>
+      </c>
       <c r="N470" s="8" t="n"/>
     </row>
     <row r="471">
@@ -20074,7 +20432,9 @@
       <c r="J476" s="8" t="n"/>
       <c r="K476" s="8" t="n"/>
       <c r="L476" s="8" t="n"/>
-      <c r="M476" s="8" t="n"/>
+      <c r="M476" s="35" t="n">
+        <v>13158</v>
+      </c>
       <c r="N476" s="8" t="n"/>
     </row>
     <row r="477">
@@ -20154,7 +20514,9 @@
       <c r="J478" s="8" t="n"/>
       <c r="K478" s="8" t="n"/>
       <c r="L478" s="8" t="n"/>
-      <c r="M478" s="8" t="n"/>
+      <c r="M478" s="35" t="n">
+        <v>1073</v>
+      </c>
       <c r="N478" s="8" t="n"/>
     </row>
     <row r="479">
@@ -20318,7 +20680,9 @@
       <c r="J482" s="8" t="n"/>
       <c r="K482" s="8" t="n"/>
       <c r="L482" s="8" t="n"/>
-      <c r="M482" s="8" t="n"/>
+      <c r="M482" s="35" t="n">
+        <v>1088</v>
+      </c>
       <c r="N482" s="8" t="n"/>
     </row>
     <row r="483">
@@ -20352,7 +20716,9 @@
       <c r="J483" s="8" t="n"/>
       <c r="K483" s="8" t="n"/>
       <c r="L483" s="8" t="n"/>
-      <c r="M483" s="8" t="n"/>
+      <c r="M483" s="35" t="n">
+        <v>1591</v>
+      </c>
       <c r="N483" s="8" t="n"/>
     </row>
     <row r="484">
@@ -20432,7 +20798,9 @@
       <c r="J485" s="8" t="n"/>
       <c r="K485" s="8" t="n"/>
       <c r="L485" s="8" t="n"/>
-      <c r="M485" s="8" t="n"/>
+      <c r="M485" s="35" t="n">
+        <v>4586</v>
+      </c>
       <c r="N485" s="8" t="n"/>
     </row>
     <row r="486">
@@ -20466,7 +20834,9 @@
       <c r="J486" s="8" t="n"/>
       <c r="K486" s="8" t="n"/>
       <c r="L486" s="8" t="n"/>
-      <c r="M486" s="8" t="n"/>
+      <c r="M486" s="35" t="n">
+        <v>479</v>
+      </c>
       <c r="N486" s="8" t="n"/>
     </row>
     <row r="487">
@@ -20500,7 +20870,9 @@
       <c r="J487" s="8" t="n"/>
       <c r="K487" s="8" t="n"/>
       <c r="L487" s="8" t="n"/>
-      <c r="M487" s="8" t="n"/>
+      <c r="M487" s="35" t="n">
+        <v>250</v>
+      </c>
       <c r="N487" s="8" t="n"/>
     </row>
     <row r="488">
@@ -20576,7 +20948,9 @@
       <c r="J489" s="8" t="n"/>
       <c r="K489" s="8" t="n"/>
       <c r="L489" s="8" t="n"/>
-      <c r="M489" s="8" t="n"/>
+      <c r="M489" s="35" t="n">
+        <v>4881</v>
+      </c>
       <c r="N489" s="8" t="n"/>
     </row>
     <row r="490">
@@ -20610,7 +20984,9 @@
       <c r="J490" s="8" t="n"/>
       <c r="K490" s="8" t="n"/>
       <c r="L490" s="8" t="n"/>
-      <c r="M490" s="8" t="n"/>
+      <c r="M490" s="35" t="n">
+        <v>2230</v>
+      </c>
       <c r="N490" s="8" t="n"/>
     </row>
     <row r="491">
@@ -20644,7 +21020,9 @@
       <c r="J491" s="8" t="n"/>
       <c r="K491" s="8" t="n"/>
       <c r="L491" s="8" t="n"/>
-      <c r="M491" s="8" t="n"/>
+      <c r="M491" s="35" t="n">
+        <v>4592</v>
+      </c>
       <c r="N491" s="8" t="n"/>
     </row>
     <row r="492">
@@ -20678,7 +21056,9 @@
       <c r="J492" s="8" t="n"/>
       <c r="K492" s="8" t="n"/>
       <c r="L492" s="8" t="n"/>
-      <c r="M492" s="8" t="n"/>
+      <c r="M492" s="35" t="n">
+        <v>1913</v>
+      </c>
       <c r="N492" s="8" t="n"/>
     </row>
     <row r="493">
@@ -20712,7 +21092,9 @@
       <c r="J493" s="8" t="n"/>
       <c r="K493" s="8" t="n"/>
       <c r="L493" s="8" t="n"/>
-      <c r="M493" s="8" t="n"/>
+      <c r="M493" s="35" t="n">
+        <v>3141</v>
+      </c>
       <c r="N493" s="8" t="n"/>
     </row>
     <row r="494">
@@ -20746,7 +21128,9 @@
       <c r="J494" s="8" t="n"/>
       <c r="K494" s="8" t="n"/>
       <c r="L494" s="8" t="n"/>
-      <c r="M494" s="8" t="n"/>
+      <c r="M494" s="35" t="n">
+        <v>982</v>
+      </c>
       <c r="N494" s="8" t="n"/>
     </row>
     <row r="495">
@@ -20822,7 +21206,9 @@
       <c r="J496" s="8" t="n"/>
       <c r="K496" s="8" t="n"/>
       <c r="L496" s="8" t="n"/>
-      <c r="M496" s="8" t="n"/>
+      <c r="M496" s="35" t="n">
+        <v>4494</v>
+      </c>
       <c r="N496" s="8" t="n"/>
     </row>
     <row r="497">
@@ -20856,7 +21242,9 @@
       <c r="J497" s="8" t="n"/>
       <c r="K497" s="8" t="n"/>
       <c r="L497" s="8" t="n"/>
-      <c r="M497" s="8" t="n"/>
+      <c r="M497" s="35" t="n">
+        <v>1599</v>
+      </c>
       <c r="N497" s="8" t="n"/>
     </row>
     <row r="498">
@@ -20932,7 +21320,9 @@
       <c r="J499" s="8" t="n"/>
       <c r="K499" s="8" t="n"/>
       <c r="L499" s="8" t="n"/>
-      <c r="M499" s="8" t="n"/>
+      <c r="M499" s="35" t="n">
+        <v>899</v>
+      </c>
       <c r="N499" s="8" t="n"/>
     </row>
     <row r="500">
@@ -20966,7 +21356,9 @@
       <c r="J500" s="8" t="n"/>
       <c r="K500" s="8" t="n"/>
       <c r="L500" s="8" t="n"/>
-      <c r="M500" s="8" t="n"/>
+      <c r="M500" s="35" t="n">
+        <v>1220</v>
+      </c>
       <c r="N500" s="8" t="n"/>
     </row>
     <row r="501">
@@ -21000,7 +21392,9 @@
       <c r="J501" s="8" t="n"/>
       <c r="K501" s="8" t="n"/>
       <c r="L501" s="8" t="n"/>
-      <c r="M501" s="8" t="n"/>
+      <c r="M501" s="35" t="n">
+        <v>5007</v>
+      </c>
       <c r="N501" s="8" t="n"/>
     </row>
     <row r="502">
@@ -21034,7 +21428,9 @@
       <c r="J502" s="8" t="n"/>
       <c r="K502" s="8" t="n"/>
       <c r="L502" s="8" t="n"/>
-      <c r="M502" s="8" t="n"/>
+      <c r="M502" s="35" t="n">
+        <v>12656</v>
+      </c>
       <c r="N502" s="8" t="n"/>
     </row>
     <row r="503">
@@ -21068,7 +21464,9 @@
       <c r="J503" s="8" t="n"/>
       <c r="K503" s="8" t="n"/>
       <c r="L503" s="8" t="n"/>
-      <c r="M503" s="8" t="n"/>
+      <c r="M503" s="35" t="n">
+        <v>5359</v>
+      </c>
       <c r="N503" s="8" t="n"/>
     </row>
     <row r="504">
@@ -21102,7 +21500,9 @@
       <c r="J504" s="8" t="n"/>
       <c r="K504" s="8" t="n"/>
       <c r="L504" s="8" t="n"/>
-      <c r="M504" s="8" t="n"/>
+      <c r="M504" s="35" t="n">
+        <v>3961</v>
+      </c>
       <c r="N504" s="8" t="n"/>
     </row>
     <row r="505">
@@ -21136,7 +21536,9 @@
       <c r="J505" s="8" t="n"/>
       <c r="K505" s="8" t="n"/>
       <c r="L505" s="8" t="n"/>
-      <c r="M505" s="8" t="n"/>
+      <c r="M505" s="35" t="n">
+        <v>1615</v>
+      </c>
       <c r="N505" s="8" t="n"/>
     </row>
     <row r="506">
@@ -21212,7 +21614,9 @@
       <c r="J507" s="8" t="n"/>
       <c r="K507" s="8" t="n"/>
       <c r="L507" s="8" t="n"/>
-      <c r="M507" s="8" t="n"/>
+      <c r="M507" s="35" t="n">
+        <v>274</v>
+      </c>
       <c r="N507" s="8" t="n"/>
     </row>
     <row r="508">
@@ -21246,7 +21650,9 @@
       <c r="J508" s="8" t="n"/>
       <c r="K508" s="8" t="n"/>
       <c r="L508" s="8" t="n"/>
-      <c r="M508" s="8" t="n"/>
+      <c r="M508" s="35" t="n">
+        <v>1108</v>
+      </c>
       <c r="N508" s="8" t="n"/>
     </row>
     <row r="509">
@@ -21280,7 +21686,9 @@
       <c r="J509" s="8" t="n"/>
       <c r="K509" s="8" t="n"/>
       <c r="L509" s="8" t="n"/>
-      <c r="M509" s="8" t="n"/>
+      <c r="M509" s="35" t="n">
+        <v>279</v>
+      </c>
       <c r="N509" s="8" t="n"/>
     </row>
     <row r="510">
@@ -21314,7 +21722,9 @@
       <c r="J510" s="8" t="n"/>
       <c r="K510" s="8" t="n"/>
       <c r="L510" s="8" t="n"/>
-      <c r="M510" s="8" t="n"/>
+      <c r="M510" s="35" t="n">
+        <v>496</v>
+      </c>
       <c r="N510" s="8" t="n"/>
     </row>
     <row r="511">
@@ -21348,7 +21758,9 @@
       <c r="J511" s="8" t="n"/>
       <c r="K511" s="8" t="n"/>
       <c r="L511" s="8" t="n"/>
-      <c r="M511" s="8" t="n"/>
+      <c r="M511" s="35" t="n">
+        <v>2880</v>
+      </c>
       <c r="N511" s="8" t="n"/>
     </row>
     <row r="512">
@@ -21382,7 +21794,9 @@
       <c r="J512" s="8" t="n"/>
       <c r="K512" s="8" t="n"/>
       <c r="L512" s="8" t="n"/>
-      <c r="M512" s="8" t="n"/>
+      <c r="M512" s="35" t="n">
+        <v>8414</v>
+      </c>
       <c r="N512" s="8" t="n"/>
     </row>
     <row r="513">
@@ -21416,7 +21830,9 @@
       <c r="J513" s="8" t="n"/>
       <c r="K513" s="8" t="n"/>
       <c r="L513" s="8" t="n"/>
-      <c r="M513" s="8" t="n"/>
+      <c r="M513" s="35" t="n">
+        <v>456</v>
+      </c>
       <c r="N513" s="8" t="n"/>
     </row>
     <row r="514">
@@ -21450,7 +21866,9 @@
       <c r="J514" s="8" t="n"/>
       <c r="K514" s="8" t="n"/>
       <c r="L514" s="8" t="n"/>
-      <c r="M514" s="8" t="n"/>
+      <c r="M514" s="35" t="n">
+        <v>2736</v>
+      </c>
       <c r="N514" s="8" t="n"/>
     </row>
     <row r="515">
@@ -21526,7 +21944,9 @@
       <c r="J516" s="8" t="n"/>
       <c r="K516" s="8" t="n"/>
       <c r="L516" s="8" t="n"/>
-      <c r="M516" s="8" t="n"/>
+      <c r="M516" s="35" t="n">
+        <v>3475</v>
+      </c>
       <c r="N516" s="8" t="n"/>
     </row>
     <row r="517">
@@ -21560,7 +21980,9 @@
       <c r="J517" s="8" t="n"/>
       <c r="K517" s="8" t="n"/>
       <c r="L517" s="8" t="n"/>
-      <c r="M517" s="8" t="n"/>
+      <c r="M517" s="35" t="n">
+        <v>12647</v>
+      </c>
       <c r="N517" s="8" t="n"/>
     </row>
     <row r="518">
@@ -21594,7 +22016,9 @@
       <c r="J518" s="8" t="n"/>
       <c r="K518" s="8" t="n"/>
       <c r="L518" s="8" t="n"/>
-      <c r="M518" s="8" t="n"/>
+      <c r="M518" s="35" t="n">
+        <v>2</v>
+      </c>
       <c r="N518" s="8" t="n"/>
     </row>
     <row r="519">
@@ -21628,7 +22052,9 @@
       <c r="J519" s="8" t="n"/>
       <c r="K519" s="8" t="n"/>
       <c r="L519" s="8" t="n"/>
-      <c r="M519" s="8" t="n"/>
+      <c r="M519" s="35" t="n">
+        <v>7016</v>
+      </c>
       <c r="N519" s="8" t="n"/>
     </row>
     <row r="520">
@@ -21662,7 +22088,9 @@
       <c r="J520" s="8" t="n"/>
       <c r="K520" s="8" t="n"/>
       <c r="L520" s="8" t="n"/>
-      <c r="M520" s="8" t="n"/>
+      <c r="M520" s="35" t="n">
+        <v>4213</v>
+      </c>
       <c r="N520" s="8" t="n"/>
     </row>
     <row r="521">
@@ -21696,7 +22124,9 @@
       <c r="J521" s="8" t="n"/>
       <c r="K521" s="8" t="n"/>
       <c r="L521" s="8" t="n"/>
-      <c r="M521" s="8" t="n"/>
+      <c r="M521" s="35" t="n">
+        <v>3395</v>
+      </c>
       <c r="N521" s="8" t="n"/>
     </row>
     <row r="522">
@@ -21772,7 +22202,9 @@
       <c r="J523" s="8" t="n"/>
       <c r="K523" s="8" t="n"/>
       <c r="L523" s="8" t="n"/>
-      <c r="M523" s="8" t="n"/>
+      <c r="M523" s="35" t="n">
+        <v>587</v>
+      </c>
       <c r="N523" s="8" t="n"/>
     </row>
     <row r="524">
@@ -21806,7 +22238,9 @@
       <c r="J524" s="8" t="n"/>
       <c r="K524" s="8" t="n"/>
       <c r="L524" s="8" t="n"/>
-      <c r="M524" s="8" t="n"/>
+      <c r="M524" s="35" t="n">
+        <v>4596</v>
+      </c>
       <c r="N524" s="8" t="n"/>
     </row>
     <row r="525">
@@ -21840,7 +22274,9 @@
       <c r="J525" s="8" t="n"/>
       <c r="K525" s="8" t="n"/>
       <c r="L525" s="8" t="n"/>
-      <c r="M525" s="8" t="n"/>
+      <c r="M525" s="35" t="n">
+        <v>8733</v>
+      </c>
       <c r="N525" s="8" t="n"/>
     </row>
     <row r="526">
@@ -21874,7 +22310,9 @@
       <c r="J526" s="8" t="n"/>
       <c r="K526" s="8" t="n"/>
       <c r="L526" s="8" t="n"/>
-      <c r="M526" s="8" t="n"/>
+      <c r="M526" s="35" t="n">
+        <v>3166</v>
+      </c>
       <c r="N526" s="8" t="n"/>
     </row>
     <row r="527">
@@ -21908,7 +22346,9 @@
       <c r="J527" s="8" t="n"/>
       <c r="K527" s="8" t="n"/>
       <c r="L527" s="8" t="n"/>
-      <c r="M527" s="8" t="n"/>
+      <c r="M527" s="35" t="n">
+        <v>2821</v>
+      </c>
       <c r="N527" s="8" t="n"/>
     </row>
     <row r="528">
@@ -21942,7 +22382,9 @@
       <c r="J528" s="8" t="n"/>
       <c r="K528" s="8" t="n"/>
       <c r="L528" s="8" t="n"/>
-      <c r="M528" s="8" t="n"/>
+      <c r="M528" s="35" t="n">
+        <v>10328</v>
+      </c>
       <c r="N528" s="8" t="n"/>
     </row>
     <row r="529">
@@ -21976,7 +22418,9 @@
       <c r="J529" s="8" t="n"/>
       <c r="K529" s="8" t="n"/>
       <c r="L529" s="8" t="n"/>
-      <c r="M529" s="8" t="n"/>
+      <c r="M529" s="35" t="n">
+        <v>2061</v>
+      </c>
       <c r="N529" s="8" t="n"/>
     </row>
     <row r="530">
@@ -22010,7 +22454,9 @@
       <c r="J530" s="8" t="n"/>
       <c r="K530" s="8" t="n"/>
       <c r="L530" s="8" t="n"/>
-      <c r="M530" s="8" t="n"/>
+      <c r="M530" s="35" t="n">
+        <v>1121</v>
+      </c>
       <c r="N530" s="8" t="n"/>
     </row>
     <row r="531">
@@ -22044,7 +22490,9 @@
       <c r="J531" s="8" t="n"/>
       <c r="K531" s="8" t="n"/>
       <c r="L531" s="8" t="n"/>
-      <c r="M531" s="8" t="n"/>
+      <c r="M531" s="35" t="n">
+        <v>1550</v>
+      </c>
       <c r="N531" s="8" t="n"/>
     </row>
     <row r="532">
@@ -22078,7 +22526,9 @@
       <c r="J532" s="8" t="n"/>
       <c r="K532" s="8" t="n"/>
       <c r="L532" s="8" t="n"/>
-      <c r="M532" s="8" t="n"/>
+      <c r="M532" s="35" t="n">
+        <v>7317</v>
+      </c>
       <c r="N532" s="8" t="n"/>
     </row>
     <row r="533">
@@ -22112,7 +22562,9 @@
       <c r="J533" s="8" t="n"/>
       <c r="K533" s="8" t="n"/>
       <c r="L533" s="8" t="n"/>
-      <c r="M533" s="8" t="n"/>
+      <c r="M533" s="35" t="n">
+        <v>5784</v>
+      </c>
       <c r="N533" s="8" t="n"/>
     </row>
     <row r="534">
@@ -22146,7 +22598,9 @@
       <c r="J534" s="8" t="n"/>
       <c r="K534" s="8" t="n"/>
       <c r="L534" s="8" t="n"/>
-      <c r="M534" s="8" t="n"/>
+      <c r="M534" s="35" t="n">
+        <v>1838</v>
+      </c>
       <c r="N534" s="8" t="n"/>
     </row>
     <row r="535">
@@ -22180,7 +22634,9 @@
       <c r="J535" s="8" t="n"/>
       <c r="K535" s="8" t="n"/>
       <c r="L535" s="8" t="n"/>
-      <c r="M535" s="8" t="n"/>
+      <c r="M535" s="35" t="n">
+        <v>2992</v>
+      </c>
       <c r="N535" s="8" t="n"/>
     </row>
     <row r="536">
@@ -22214,7 +22670,9 @@
       <c r="J536" s="8" t="n"/>
       <c r="K536" s="8" t="n"/>
       <c r="L536" s="8" t="n"/>
-      <c r="M536" s="8" t="n"/>
+      <c r="M536" s="35" t="n">
+        <v>1383</v>
+      </c>
       <c r="N536" s="8" t="n"/>
     </row>
     <row r="537">
@@ -22248,7 +22706,9 @@
       <c r="J537" s="8" t="n"/>
       <c r="K537" s="8" t="n"/>
       <c r="L537" s="8" t="n"/>
-      <c r="M537" s="8" t="n"/>
+      <c r="M537" s="35" t="n">
+        <v>1837</v>
+      </c>
       <c r="N537" s="8" t="n"/>
     </row>
     <row r="538">
@@ -22282,7 +22742,9 @@
       <c r="J538" s="8" t="n"/>
       <c r="K538" s="8" t="n"/>
       <c r="L538" s="8" t="n"/>
-      <c r="M538" s="8" t="n"/>
+      <c r="M538" s="35" t="n">
+        <v>570</v>
+      </c>
       <c r="N538" s="8" t="n"/>
     </row>
     <row r="539">
@@ -22358,7 +22820,9 @@
       <c r="J540" s="8" t="n"/>
       <c r="K540" s="8" t="n"/>
       <c r="L540" s="8" t="n"/>
-      <c r="M540" s="8" t="n"/>
+      <c r="M540" s="35" t="n">
+        <v>3560</v>
+      </c>
       <c r="N540" s="8" t="n"/>
     </row>
     <row r="541">
@@ -22392,7 +22856,9 @@
       <c r="J541" s="8" t="n"/>
       <c r="K541" s="8" t="n"/>
       <c r="L541" s="8" t="n"/>
-      <c r="M541" s="8" t="n"/>
+      <c r="M541" s="35" t="n">
+        <v>2442</v>
+      </c>
       <c r="N541" s="8" t="n"/>
     </row>
     <row r="542">
@@ -22426,7 +22892,9 @@
       <c r="J542" s="8" t="n"/>
       <c r="K542" s="8" t="n"/>
       <c r="L542" s="8" t="n"/>
-      <c r="M542" s="8" t="n"/>
+      <c r="M542" s="35" t="n">
+        <v>298</v>
+      </c>
       <c r="N542" s="8" t="n"/>
     </row>
     <row r="543">
@@ -22460,7 +22928,9 @@
       <c r="J543" s="8" t="n"/>
       <c r="K543" s="8" t="n"/>
       <c r="L543" s="8" t="n"/>
-      <c r="M543" s="8" t="n"/>
+      <c r="M543" s="35" t="n">
+        <v>1076</v>
+      </c>
       <c r="N543" s="8" t="n"/>
     </row>
     <row r="544">
@@ -22536,7 +23006,9 @@
       <c r="J545" s="8" t="n"/>
       <c r="K545" s="8" t="n"/>
       <c r="L545" s="8" t="n"/>
-      <c r="M545" s="8" t="n"/>
+      <c r="M545" s="35" t="n">
+        <v>209</v>
+      </c>
       <c r="N545" s="8" t="n"/>
     </row>
     <row r="546">
@@ -22570,7 +23042,9 @@
       <c r="J546" s="8" t="n"/>
       <c r="K546" s="8" t="n"/>
       <c r="L546" s="8" t="n"/>
-      <c r="M546" s="8" t="n"/>
+      <c r="M546" s="35" t="n">
+        <v>2648</v>
+      </c>
       <c r="N546" s="8" t="n"/>
     </row>
     <row r="547">
@@ -22604,7 +23078,9 @@
       <c r="J547" s="8" t="n"/>
       <c r="K547" s="8" t="n"/>
       <c r="L547" s="8" t="n"/>
-      <c r="M547" s="8" t="n"/>
+      <c r="M547" s="35" t="n">
+        <v>1323</v>
+      </c>
       <c r="N547" s="8" t="n"/>
     </row>
     <row r="548">
@@ -22638,7 +23114,9 @@
       <c r="J548" s="8" t="n"/>
       <c r="K548" s="8" t="n"/>
       <c r="L548" s="8" t="n"/>
-      <c r="M548" s="8" t="n"/>
+      <c r="M548" s="35" t="n">
+        <v>1104</v>
+      </c>
       <c r="N548" s="8" t="n"/>
     </row>
     <row r="549">
@@ -22672,7 +23150,9 @@
       <c r="J549" s="8" t="n"/>
       <c r="K549" s="8" t="n"/>
       <c r="L549" s="8" t="n"/>
-      <c r="M549" s="8" t="n"/>
+      <c r="M549" s="35" t="n">
+        <v>954</v>
+      </c>
       <c r="N549" s="8" t="n"/>
     </row>
     <row r="550">
@@ -22706,7 +23186,9 @@
       <c r="J550" s="8" t="n"/>
       <c r="K550" s="8" t="n"/>
       <c r="L550" s="8" t="n"/>
-      <c r="M550" s="8" t="n"/>
+      <c r="M550" s="35" t="n">
+        <v>768</v>
+      </c>
       <c r="N550" s="8" t="n"/>
     </row>
     <row r="551">
@@ -22740,7 +23222,9 @@
       <c r="J551" s="8" t="n"/>
       <c r="K551" s="8" t="n"/>
       <c r="L551" s="8" t="n"/>
-      <c r="M551" s="8" t="n"/>
+      <c r="M551" s="35" t="n">
+        <v>383</v>
+      </c>
       <c r="N551" s="8" t="n"/>
     </row>
     <row r="552">
@@ -22774,7 +23258,9 @@
       <c r="J552" s="8" t="n"/>
       <c r="K552" s="8" t="n"/>
       <c r="L552" s="8" t="n"/>
-      <c r="M552" s="8" t="n"/>
+      <c r="M552" s="35" t="n">
+        <v>714</v>
+      </c>
       <c r="N552" s="8" t="n"/>
     </row>
     <row r="553">
@@ -22850,7 +23336,9 @@
       <c r="J554" s="8" t="n"/>
       <c r="K554" s="8" t="n"/>
       <c r="L554" s="8" t="n"/>
-      <c r="M554" s="8" t="n"/>
+      <c r="M554" s="35" t="n">
+        <v>2476</v>
+      </c>
       <c r="N554" s="8" t="n"/>
     </row>
     <row r="555">
@@ -22884,7 +23372,9 @@
       <c r="J555" s="8" t="n"/>
       <c r="K555" s="8" t="n"/>
       <c r="L555" s="8" t="n"/>
-      <c r="M555" s="8" t="n"/>
+      <c r="M555" s="35" t="n">
+        <v>1500</v>
+      </c>
       <c r="N555" s="8" t="n"/>
     </row>
     <row r="556">
@@ -22918,7 +23408,9 @@
       <c r="J556" s="8" t="n"/>
       <c r="K556" s="8" t="n"/>
       <c r="L556" s="8" t="n"/>
-      <c r="M556" s="8" t="n"/>
+      <c r="M556" s="35" t="n">
+        <v>8917</v>
+      </c>
       <c r="N556" s="8" t="n"/>
     </row>
     <row r="557">
@@ -22952,7 +23444,9 @@
       <c r="J557" s="8" t="n"/>
       <c r="K557" s="8" t="n"/>
       <c r="L557" s="8" t="n"/>
-      <c r="M557" s="8" t="n"/>
+      <c r="M557" s="35" t="n">
+        <v>1444</v>
+      </c>
       <c r="N557" s="8" t="n"/>
     </row>
     <row r="558">
@@ -22986,7 +23480,9 @@
       <c r="J558" s="8" t="n"/>
       <c r="K558" s="8" t="n"/>
       <c r="L558" s="8" t="n"/>
-      <c r="M558" s="8" t="n"/>
+      <c r="M558" s="35" t="n">
+        <v>889</v>
+      </c>
       <c r="N558" s="8" t="n"/>
     </row>
     <row r="559">
@@ -23020,7 +23516,9 @@
       <c r="J559" s="8" t="n"/>
       <c r="K559" s="8" t="n"/>
       <c r="L559" s="8" t="n"/>
-      <c r="M559" s="8" t="n"/>
+      <c r="M559" s="35" t="n">
+        <v>573</v>
+      </c>
       <c r="N559" s="8" t="n"/>
     </row>
     <row r="560">
@@ -23054,7 +23552,9 @@
       <c r="J560" s="8" t="n"/>
       <c r="K560" s="8" t="n"/>
       <c r="L560" s="8" t="n"/>
-      <c r="M560" s="8" t="n"/>
+      <c r="M560" s="35" t="n">
+        <v>3526</v>
+      </c>
       <c r="N560" s="8" t="n"/>
     </row>
     <row r="561">
@@ -23088,7 +23588,9 @@
       <c r="J561" s="8" t="n"/>
       <c r="K561" s="8" t="n"/>
       <c r="L561" s="8" t="n"/>
-      <c r="M561" s="8" t="n"/>
+      <c r="M561" s="35" t="n">
+        <v>1595</v>
+      </c>
       <c r="N561" s="8" t="n"/>
     </row>
     <row r="562">
@@ -23164,7 +23666,9 @@
       <c r="J563" s="8" t="n"/>
       <c r="K563" s="8" t="n"/>
       <c r="L563" s="8" t="n"/>
-      <c r="M563" s="8" t="n"/>
+      <c r="M563" s="35" t="n">
+        <v>2703</v>
+      </c>
       <c r="N563" s="8" t="n"/>
     </row>
     <row r="564">
@@ -23198,7 +23702,9 @@
       <c r="J564" s="8" t="n"/>
       <c r="K564" s="8" t="n"/>
       <c r="L564" s="8" t="n"/>
-      <c r="M564" s="8" t="n"/>
+      <c r="M564" s="35" t="n">
+        <v>6835</v>
+      </c>
       <c r="N564" s="8" t="n"/>
     </row>
     <row r="565">
@@ -23232,7 +23738,9 @@
       <c r="J565" s="8" t="n"/>
       <c r="K565" s="8" t="n"/>
       <c r="L565" s="8" t="n"/>
-      <c r="M565" s="8" t="n"/>
+      <c r="M565" s="35" t="n">
+        <v>6653</v>
+      </c>
       <c r="N565" s="8" t="n"/>
     </row>
     <row r="566">
@@ -23266,7 +23774,9 @@
       <c r="J566" s="8" t="n"/>
       <c r="K566" s="8" t="n"/>
       <c r="L566" s="8" t="n"/>
-      <c r="M566" s="8" t="n"/>
+      <c r="M566" s="35" t="n">
+        <v>2996</v>
+      </c>
       <c r="N566" s="8" t="n"/>
     </row>
     <row r="567">
@@ -23300,7 +23810,9 @@
       <c r="J567" s="8" t="n"/>
       <c r="K567" s="8" t="n"/>
       <c r="L567" s="8" t="n"/>
-      <c r="M567" s="8" t="n"/>
+      <c r="M567" s="35" t="n">
+        <v>20217</v>
+      </c>
       <c r="N567" s="8" t="n"/>
     </row>
     <row r="568">
@@ -23334,7 +23846,9 @@
       <c r="J568" s="8" t="n"/>
       <c r="K568" s="8" t="n"/>
       <c r="L568" s="8" t="n"/>
-      <c r="M568" s="8" t="n"/>
+      <c r="M568" s="35" t="n">
+        <v>737</v>
+      </c>
       <c r="N568" s="8" t="n"/>
     </row>
     <row r="569">
@@ -23410,7 +23924,9 @@
       <c r="J570" s="8" t="n"/>
       <c r="K570" s="8" t="n"/>
       <c r="L570" s="8" t="n"/>
-      <c r="M570" s="8" t="n"/>
+      <c r="M570" s="35" t="n">
+        <v>1372</v>
+      </c>
       <c r="N570" s="8" t="n"/>
     </row>
     <row r="571">
@@ -23444,7 +23960,9 @@
       <c r="J571" s="8" t="n"/>
       <c r="K571" s="8" t="n"/>
       <c r="L571" s="8" t="n"/>
-      <c r="M571" s="8" t="n"/>
+      <c r="M571" s="35" t="n">
+        <v>5442</v>
+      </c>
       <c r="N571" s="8" t="n"/>
     </row>
     <row r="572">
@@ -23478,7 +23996,9 @@
       <c r="J572" s="8" t="n"/>
       <c r="K572" s="8" t="n"/>
       <c r="L572" s="8" t="n"/>
-      <c r="M572" s="8" t="n"/>
+      <c r="M572" s="35" t="n">
+        <v>1512</v>
+      </c>
       <c r="N572" s="8" t="n"/>
     </row>
     <row r="573">
@@ -23512,7 +24032,9 @@
       <c r="J573" s="8" t="n"/>
       <c r="K573" s="8" t="n"/>
       <c r="L573" s="8" t="n"/>
-      <c r="M573" s="8" t="n"/>
+      <c r="M573" s="35" t="n">
+        <v>10103</v>
+      </c>
       <c r="N573" s="8" t="n"/>
     </row>
     <row r="574">
@@ -23546,7 +24068,9 @@
       <c r="J574" s="8" t="n"/>
       <c r="K574" s="8" t="n"/>
       <c r="L574" s="8" t="n"/>
-      <c r="M574" s="8" t="n"/>
+      <c r="M574" s="35" t="n">
+        <v>2812</v>
+      </c>
       <c r="N574" s="8" t="n"/>
     </row>
     <row r="575">
@@ -23580,7 +24104,9 @@
       <c r="J575" s="8" t="n"/>
       <c r="K575" s="8" t="n"/>
       <c r="L575" s="8" t="n"/>
-      <c r="M575" s="8" t="n"/>
+      <c r="M575" s="35" t="n">
+        <v>3876</v>
+      </c>
       <c r="N575" s="8" t="n"/>
     </row>
     <row r="576">
@@ -23614,7 +24140,9 @@
       <c r="J576" s="8" t="n"/>
       <c r="K576" s="8" t="n"/>
       <c r="L576" s="8" t="n"/>
-      <c r="M576" s="8" t="n"/>
+      <c r="M576" s="35" t="n">
+        <v>1288</v>
+      </c>
       <c r="N576" s="8" t="n"/>
     </row>
     <row r="577">
@@ -23648,7 +24176,9 @@
       <c r="J577" s="8" t="n"/>
       <c r="K577" s="8" t="n"/>
       <c r="L577" s="8" t="n"/>
-      <c r="M577" s="8" t="n"/>
+      <c r="M577" s="35" t="n">
+        <v>2442</v>
+      </c>
       <c r="N577" s="8" t="n"/>
     </row>
     <row r="578">
@@ -23682,7 +24212,9 @@
       <c r="J578" s="8" t="n"/>
       <c r="K578" s="8" t="n"/>
       <c r="L578" s="8" t="n"/>
-      <c r="M578" s="8" t="n"/>
+      <c r="M578" s="35" t="n">
+        <v>4002</v>
+      </c>
       <c r="N578" s="8" t="n"/>
     </row>
     <row r="579">
@@ -23716,7 +24248,9 @@
       <c r="J579" s="8" t="n"/>
       <c r="K579" s="8" t="n"/>
       <c r="L579" s="8" t="n"/>
-      <c r="M579" s="8" t="n"/>
+      <c r="M579" s="35" t="n">
+        <v>963</v>
+      </c>
       <c r="N579" s="8" t="n"/>
     </row>
     <row r="580">
@@ -23750,7 +24284,9 @@
       <c r="J580" s="8" t="n"/>
       <c r="K580" s="8" t="n"/>
       <c r="L580" s="8" t="n"/>
-      <c r="M580" s="8" t="n"/>
+      <c r="M580" s="35" t="n">
+        <v>1514</v>
+      </c>
       <c r="N580" s="8" t="n"/>
     </row>
     <row r="581">
@@ -23784,7 +24320,9 @@
       <c r="J581" s="8" t="n"/>
       <c r="K581" s="8" t="n"/>
       <c r="L581" s="8" t="n"/>
-      <c r="M581" s="8" t="n"/>
+      <c r="M581" s="35" t="n">
+        <v>3558</v>
+      </c>
       <c r="N581" s="8" t="n"/>
     </row>
     <row r="582">
@@ -23860,7 +24398,9 @@
       <c r="J583" s="8" t="n"/>
       <c r="K583" s="8" t="n"/>
       <c r="L583" s="8" t="n"/>
-      <c r="M583" s="8" t="n"/>
+      <c r="M583" s="35" t="n">
+        <v>2647</v>
+      </c>
       <c r="N583" s="8" t="n"/>
     </row>
     <row r="584">
@@ -23894,7 +24434,9 @@
       <c r="J584" s="8" t="n"/>
       <c r="K584" s="8" t="n"/>
       <c r="L584" s="8" t="n"/>
-      <c r="M584" s="8" t="n"/>
+      <c r="M584" s="35" t="n">
+        <v>1546</v>
+      </c>
       <c r="N584" s="8" t="n"/>
     </row>
     <row r="585">
@@ -23928,7 +24470,9 @@
       <c r="J585" s="8" t="n"/>
       <c r="K585" s="8" t="n"/>
       <c r="L585" s="8" t="n"/>
-      <c r="M585" s="8" t="n"/>
+      <c r="M585" s="35" t="n">
+        <v>4776</v>
+      </c>
       <c r="N585" s="8" t="n"/>
     </row>
     <row r="586">
@@ -23962,7 +24506,9 @@
       <c r="J586" s="8" t="n"/>
       <c r="K586" s="8" t="n"/>
       <c r="L586" s="8" t="n"/>
-      <c r="M586" s="8" t="n"/>
+      <c r="M586" s="35" t="n">
+        <v>1500</v>
+      </c>
       <c r="N586" s="8" t="n"/>
     </row>
     <row r="587">
@@ -23996,7 +24542,9 @@
       <c r="J587" s="8" t="n"/>
       <c r="K587" s="8" t="n"/>
       <c r="L587" s="8" t="n"/>
-      <c r="M587" s="8" t="n"/>
+      <c r="M587" s="35" t="n">
+        <v>2717</v>
+      </c>
       <c r="N587" s="8" t="n"/>
     </row>
     <row r="588">
@@ -24030,7 +24578,9 @@
       <c r="J588" s="8" t="n"/>
       <c r="K588" s="8" t="n"/>
       <c r="L588" s="8" t="n"/>
-      <c r="M588" s="8" t="n"/>
+      <c r="M588" s="35" t="n">
+        <v>1970</v>
+      </c>
       <c r="N588" s="8" t="n"/>
     </row>
     <row r="589">
@@ -24064,7 +24614,9 @@
       <c r="J589" s="8" t="n"/>
       <c r="K589" s="8" t="n"/>
       <c r="L589" s="8" t="n"/>
-      <c r="M589" s="8" t="n"/>
+      <c r="M589" s="35" t="n">
+        <v>2554</v>
+      </c>
       <c r="N589" s="8" t="n"/>
     </row>
     <row r="590">
@@ -24098,7 +24650,9 @@
       <c r="J590" s="8" t="n"/>
       <c r="K590" s="8" t="n"/>
       <c r="L590" s="8" t="n"/>
-      <c r="M590" s="8" t="n"/>
+      <c r="M590" s="35" t="n">
+        <v>582</v>
+      </c>
       <c r="N590" s="8" t="n"/>
     </row>
     <row r="591">
@@ -24132,7 +24686,9 @@
       <c r="J591" s="8" t="n"/>
       <c r="K591" s="8" t="n"/>
       <c r="L591" s="8" t="n"/>
-      <c r="M591" s="8" t="n"/>
+      <c r="M591" s="35" t="n">
+        <v>1651</v>
+      </c>
       <c r="N591" s="8" t="n"/>
     </row>
     <row r="592">
@@ -24166,7 +24722,9 @@
       <c r="J592" s="8" t="n"/>
       <c r="K592" s="8" t="n"/>
       <c r="L592" s="8" t="n"/>
-      <c r="M592" s="8" t="n"/>
+      <c r="M592" s="35" t="n">
+        <v>1722</v>
+      </c>
       <c r="N592" s="8" t="n"/>
     </row>
     <row r="593">
@@ -24200,7 +24758,9 @@
       <c r="J593" s="8" t="n"/>
       <c r="K593" s="8" t="n"/>
       <c r="L593" s="8" t="n"/>
-      <c r="M593" s="8" t="n"/>
+      <c r="M593" s="35" t="n">
+        <v>10411</v>
+      </c>
       <c r="N593" s="8" t="n"/>
     </row>
     <row r="594">
@@ -24234,7 +24794,9 @@
       <c r="J594" s="8" t="n"/>
       <c r="K594" s="8" t="n"/>
       <c r="L594" s="8" t="n"/>
-      <c r="M594" s="8" t="n"/>
+      <c r="M594" s="35" t="n">
+        <v>728</v>
+      </c>
       <c r="N594" s="8" t="n"/>
     </row>
     <row r="595">
@@ -24268,7 +24830,9 @@
       <c r="J595" s="8" t="n"/>
       <c r="K595" s="8" t="n"/>
       <c r="L595" s="8" t="n"/>
-      <c r="M595" s="8" t="n"/>
+      <c r="M595" s="35" t="n">
+        <v>4807</v>
+      </c>
       <c r="N595" s="8" t="n"/>
     </row>
     <row r="596">
@@ -24302,7 +24866,9 @@
       <c r="J596" s="8" t="n"/>
       <c r="K596" s="8" t="n"/>
       <c r="L596" s="8" t="n"/>
-      <c r="M596" s="8" t="n"/>
+      <c r="M596" s="35" t="n">
+        <v>1016</v>
+      </c>
       <c r="N596" s="8" t="n"/>
     </row>
     <row r="597">
@@ -24378,7 +24944,9 @@
       <c r="J598" s="8" t="n"/>
       <c r="K598" s="8" t="n"/>
       <c r="L598" s="8" t="n"/>
-      <c r="M598" s="8" t="n"/>
+      <c r="M598" s="35" t="n">
+        <v>1363</v>
+      </c>
       <c r="N598" s="8" t="n"/>
     </row>
     <row r="599">
@@ -24412,7 +24980,9 @@
       <c r="J599" s="8" t="n"/>
       <c r="K599" s="8" t="n"/>
       <c r="L599" s="8" t="n"/>
-      <c r="M599" s="8" t="n"/>
+      <c r="M599" s="35" t="n">
+        <v>3567</v>
+      </c>
       <c r="N599" s="8" t="n"/>
     </row>
     <row r="600">
@@ -24446,7 +25016,9 @@
       <c r="J600" s="8" t="n"/>
       <c r="K600" s="8" t="n"/>
       <c r="L600" s="8" t="n"/>
-      <c r="M600" s="8" t="n"/>
+      <c r="M600" s="35" t="n">
+        <v>1086</v>
+      </c>
       <c r="N600" s="8" t="n"/>
     </row>
     <row r="601">
@@ -24480,7 +25052,9 @@
       <c r="J601" s="8" t="n"/>
       <c r="K601" s="8" t="n"/>
       <c r="L601" s="8" t="n"/>
-      <c r="M601" s="8" t="n"/>
+      <c r="M601" s="35" t="n">
+        <v>2720</v>
+      </c>
       <c r="N601" s="8" t="n"/>
     </row>
     <row r="602">
@@ -24514,7 +25088,9 @@
       <c r="J602" s="8" t="n"/>
       <c r="K602" s="8" t="n"/>
       <c r="L602" s="8" t="n"/>
-      <c r="M602" s="8" t="n"/>
+      <c r="M602" s="35" t="n">
+        <v>595</v>
+      </c>
       <c r="N602" s="8" t="n"/>
     </row>
     <row r="603">
@@ -24548,7 +25124,9 @@
       <c r="J603" s="8" t="n"/>
       <c r="K603" s="8" t="n"/>
       <c r="L603" s="8" t="n"/>
-      <c r="M603" s="8" t="n"/>
+      <c r="M603" s="35" t="n">
+        <v>14128</v>
+      </c>
       <c r="N603" s="8" t="n"/>
     </row>
     <row r="604">
@@ -24624,7 +25202,9 @@
       <c r="J605" s="8" t="n"/>
       <c r="K605" s="8" t="n"/>
       <c r="L605" s="8" t="n"/>
-      <c r="M605" s="8" t="n"/>
+      <c r="M605" s="35" t="n">
+        <v>233</v>
+      </c>
       <c r="N605" s="8" t="n"/>
     </row>
     <row r="606">
@@ -24658,7 +25238,9 @@
       <c r="J606" s="8" t="n"/>
       <c r="K606" s="8" t="n"/>
       <c r="L606" s="8" t="n"/>
-      <c r="M606" s="8" t="n"/>
+      <c r="M606" s="35" t="n">
+        <v>1628</v>
+      </c>
       <c r="N606" s="8" t="n"/>
     </row>
     <row r="607">
@@ -24692,7 +25274,9 @@
       <c r="J607" s="8" t="n"/>
       <c r="K607" s="8" t="n"/>
       <c r="L607" s="8" t="n"/>
-      <c r="M607" s="8" t="n"/>
+      <c r="M607" s="35" t="n">
+        <v>137</v>
+      </c>
       <c r="N607" s="8" t="n"/>
     </row>
     <row r="608">
@@ -24726,7 +25310,9 @@
       <c r="J608" s="8" t="n"/>
       <c r="K608" s="8" t="n"/>
       <c r="L608" s="8" t="n"/>
-      <c r="M608" s="8" t="n"/>
+      <c r="M608" s="35" t="n">
+        <v>3436</v>
+      </c>
       <c r="N608" s="8" t="n"/>
     </row>
     <row r="609">
@@ -24760,7 +25346,9 @@
       <c r="J609" s="8" t="n"/>
       <c r="K609" s="16" t="n"/>
       <c r="L609" s="8" t="n"/>
-      <c r="M609" s="8" t="n"/>
+      <c r="M609" s="35" t="n">
+        <v>5772</v>
+      </c>
       <c r="N609" s="8" t="n"/>
     </row>
     <row r="610">
@@ -24836,7 +25424,9 @@
       <c r="J611" s="8" t="n"/>
       <c r="K611" s="8" t="n"/>
       <c r="L611" s="8" t="n"/>
-      <c r="M611" s="8" t="n"/>
+      <c r="M611" s="35" t="n">
+        <v>7330</v>
+      </c>
       <c r="N611" s="8" t="n"/>
     </row>
     <row r="612">
@@ -24870,7 +25460,9 @@
       <c r="J612" s="8" t="n"/>
       <c r="K612" s="8" t="n"/>
       <c r="L612" s="8" t="n"/>
-      <c r="M612" s="8" t="n"/>
+      <c r="M612" s="35" t="n">
+        <v>2141</v>
+      </c>
       <c r="N612" s="8" t="n"/>
     </row>
     <row r="613">
@@ -24904,7 +25496,9 @@
       <c r="J613" s="8" t="n"/>
       <c r="K613" s="8" t="n"/>
       <c r="L613" s="8" t="n"/>
-      <c r="M613" s="8" t="n"/>
+      <c r="M613" s="35" t="n">
+        <v>7657</v>
+      </c>
       <c r="N613" s="8" t="n"/>
     </row>
     <row r="614">
@@ -24938,7 +25532,9 @@
       <c r="J614" s="8" t="n"/>
       <c r="K614" s="8" t="n"/>
       <c r="L614" s="8" t="n"/>
-      <c r="M614" s="8" t="n"/>
+      <c r="M614" s="35" t="n">
+        <v>3456</v>
+      </c>
       <c r="N614" s="8" t="n"/>
     </row>
     <row r="615">
@@ -24972,7 +25568,9 @@
       <c r="J615" s="8" t="n"/>
       <c r="K615" s="8" t="n"/>
       <c r="L615" s="8" t="n"/>
-      <c r="M615" s="8" t="n"/>
+      <c r="M615" s="35" t="n">
+        <v>2600</v>
+      </c>
       <c r="N615" s="8" t="n"/>
     </row>
     <row r="616">
@@ -25006,7 +25604,9 @@
       <c r="J616" s="8" t="n"/>
       <c r="K616" s="8" t="n"/>
       <c r="L616" s="8" t="n"/>
-      <c r="M616" s="8" t="n"/>
+      <c r="M616" s="35" t="n">
+        <v>2260</v>
+      </c>
       <c r="N616" s="8" t="n"/>
     </row>
     <row r="617">
@@ -25040,7 +25640,9 @@
       <c r="J617" s="8" t="n"/>
       <c r="K617" s="8" t="n"/>
       <c r="L617" s="8" t="n"/>
-      <c r="M617" s="8" t="n"/>
+      <c r="M617" s="35" t="n">
+        <v>2703</v>
+      </c>
       <c r="N617" s="8" t="n"/>
     </row>
     <row r="618">
@@ -25074,7 +25676,9 @@
       <c r="J618" s="8" t="n"/>
       <c r="K618" s="8" t="n"/>
       <c r="L618" s="8" t="n"/>
-      <c r="M618" s="8" t="n"/>
+      <c r="M618" s="35" t="n">
+        <v>10052</v>
+      </c>
       <c r="N618" s="8" t="n"/>
     </row>
     <row r="619">
@@ -25108,7 +25712,9 @@
       <c r="J619" s="8" t="n"/>
       <c r="K619" s="8" t="n"/>
       <c r="L619" s="8" t="n"/>
-      <c r="M619" s="8" t="n"/>
+      <c r="M619" s="35" t="n">
+        <v>2403</v>
+      </c>
       <c r="N619" s="8" t="n"/>
     </row>
     <row r="620">
@@ -25142,7 +25748,9 @@
       <c r="J620" s="8" t="n"/>
       <c r="K620" s="8" t="n"/>
       <c r="L620" s="8" t="n"/>
-      <c r="M620" s="8" t="n"/>
+      <c r="M620" s="35" t="n">
+        <v>496</v>
+      </c>
       <c r="N620" s="8" t="n"/>
     </row>
     <row r="621">
@@ -25176,7 +25784,9 @@
       <c r="J621" s="8" t="n"/>
       <c r="K621" s="8" t="n"/>
       <c r="L621" s="8" t="n"/>
-      <c r="M621" s="8" t="n"/>
+      <c r="M621" s="35" t="n">
+        <v>2873</v>
+      </c>
       <c r="N621" s="8" t="n"/>
     </row>
     <row r="622">
@@ -25210,7 +25820,9 @@
       <c r="J622" s="8" t="n"/>
       <c r="K622" s="8" t="n"/>
       <c r="L622" s="8" t="n"/>
-      <c r="M622" s="8" t="n"/>
+      <c r="M622" s="35" t="n">
+        <v>590</v>
+      </c>
       <c r="N622" s="8" t="n"/>
     </row>
     <row r="623">
@@ -25244,7 +25856,9 @@
       <c r="J623" s="8" t="n"/>
       <c r="K623" s="8" t="n"/>
       <c r="L623" s="8" t="n"/>
-      <c r="M623" s="8" t="n"/>
+      <c r="M623" s="35" t="n">
+        <v>992</v>
+      </c>
       <c r="N623" s="8" t="n"/>
     </row>
     <row r="624">
@@ -25324,7 +25938,9 @@
       <c r="J625" s="8" t="n"/>
       <c r="K625" s="8" t="n"/>
       <c r="L625" s="8" t="n"/>
-      <c r="M625" s="8" t="n"/>
+      <c r="M625" s="35" t="n">
+        <v>2045</v>
+      </c>
       <c r="N625" s="8" t="n"/>
     </row>
     <row r="626">
@@ -25358,7 +25974,9 @@
       <c r="J626" s="8" t="n"/>
       <c r="K626" s="8" t="n"/>
       <c r="L626" s="8" t="n"/>
-      <c r="M626" s="8" t="n"/>
+      <c r="M626" s="35" t="n">
+        <v>5145</v>
+      </c>
       <c r="N626" s="8" t="n"/>
     </row>
     <row r="627">
@@ -25392,7 +26010,9 @@
       <c r="J627" s="8" t="n"/>
       <c r="K627" s="8" t="n"/>
       <c r="L627" s="8" t="n"/>
-      <c r="M627" s="8" t="n"/>
+      <c r="M627" s="35" t="n">
+        <v>6755</v>
+      </c>
       <c r="N627" s="8" t="n"/>
     </row>
     <row r="628">
@@ -25426,7 +26046,9 @@
       <c r="J628" s="8" t="n"/>
       <c r="K628" s="8" t="n"/>
       <c r="L628" s="8" t="n"/>
-      <c r="M628" s="8" t="n"/>
+      <c r="M628" s="35" t="n">
+        <v>4560</v>
+      </c>
       <c r="N628" s="8" t="n"/>
     </row>
     <row r="629">
@@ -25460,7 +26082,9 @@
       <c r="J629" s="8" t="n"/>
       <c r="K629" s="8" t="n"/>
       <c r="L629" s="8" t="n"/>
-      <c r="M629" s="8" t="n"/>
+      <c r="M629" s="35" t="n">
+        <v>4525</v>
+      </c>
       <c r="N629" s="8" t="n"/>
     </row>
     <row r="630">
@@ -25494,7 +26118,9 @@
       <c r="J630" s="8" t="n"/>
       <c r="K630" s="8" t="n"/>
       <c r="L630" s="8" t="n"/>
-      <c r="M630" s="8" t="n"/>
+      <c r="M630" s="35" t="n">
+        <v>9337</v>
+      </c>
       <c r="N630" s="8" t="n"/>
     </row>
     <row r="631">
@@ -25528,7 +26154,9 @@
       <c r="J631" s="8" t="n"/>
       <c r="K631" s="8" t="n"/>
       <c r="L631" s="8" t="n"/>
-      <c r="M631" s="8" t="n"/>
+      <c r="M631" s="35" t="n">
+        <v>446</v>
+      </c>
       <c r="N631" s="8" t="n"/>
     </row>
     <row r="632">
@@ -25604,7 +26232,9 @@
       <c r="J633" s="8" t="n"/>
       <c r="K633" s="8" t="n"/>
       <c r="L633" s="8" t="n"/>
-      <c r="M633" s="8" t="n"/>
+      <c r="M633" s="35" t="n">
+        <v>2283</v>
+      </c>
       <c r="N633" s="8" t="n"/>
     </row>
     <row r="634">
@@ -25680,7 +26310,9 @@
       <c r="J635" s="8" t="n"/>
       <c r="K635" s="8" t="n"/>
       <c r="L635" s="8" t="n"/>
-      <c r="M635" s="8" t="n"/>
+      <c r="M635" s="35" t="n">
+        <v>602</v>
+      </c>
       <c r="N635" s="8" t="n"/>
     </row>
     <row r="636">
@@ -25714,7 +26346,9 @@
       <c r="J636" s="8" t="n"/>
       <c r="K636" s="8" t="n"/>
       <c r="L636" s="8" t="n"/>
-      <c r="M636" s="8" t="n"/>
+      <c r="M636" s="35" t="n">
+        <v>3431</v>
+      </c>
       <c r="N636" s="8" t="n"/>
     </row>
     <row r="637">
@@ -25748,7 +26382,9 @@
       <c r="J637" s="8" t="n"/>
       <c r="K637" s="8" t="n"/>
       <c r="L637" s="8" t="n"/>
-      <c r="M637" s="8" t="n"/>
+      <c r="M637" s="35" t="n">
+        <v>6242</v>
+      </c>
       <c r="N637" s="8" t="n"/>
     </row>
     <row r="638">
@@ -25782,7 +26418,9 @@
       <c r="J638" s="8" t="n"/>
       <c r="K638" s="8" t="n"/>
       <c r="L638" s="8" t="n"/>
-      <c r="M638" s="8" t="n"/>
+      <c r="M638" s="35" t="n">
+        <v>1404</v>
+      </c>
       <c r="N638" s="8" t="n"/>
     </row>
     <row r="639">
@@ -25816,7 +26454,9 @@
       <c r="J639" s="8" t="n"/>
       <c r="K639" s="8" t="n"/>
       <c r="L639" s="8" t="n"/>
-      <c r="M639" s="8" t="n"/>
+      <c r="M639" s="35" t="n">
+        <v>4596</v>
+      </c>
       <c r="N639" s="8" t="n"/>
     </row>
     <row r="640">
@@ -25850,7 +26490,9 @@
       <c r="J640" s="8" t="n"/>
       <c r="K640" s="8" t="n"/>
       <c r="L640" s="8" t="n"/>
-      <c r="M640" s="8" t="n"/>
+      <c r="M640" s="35" t="n">
+        <v>1663</v>
+      </c>
       <c r="N640" s="8" t="n"/>
     </row>
     <row r="641">
@@ -25884,7 +26526,9 @@
       <c r="J641" s="8" t="n"/>
       <c r="K641" s="8" t="n"/>
       <c r="L641" s="8" t="n"/>
-      <c r="M641" s="8" t="n"/>
+      <c r="M641" s="35" t="n">
+        <v>608</v>
+      </c>
       <c r="N641" s="8" t="n"/>
     </row>
     <row r="642">
@@ -25918,7 +26562,9 @@
       <c r="J642" s="8" t="n"/>
       <c r="K642" s="8" t="n"/>
       <c r="L642" s="8" t="n"/>
-      <c r="M642" s="8" t="n"/>
+      <c r="M642" s="35" t="n">
+        <v>820</v>
+      </c>
       <c r="N642" s="8" t="n"/>
     </row>
     <row r="643">
@@ -25952,7 +26598,9 @@
       <c r="J643" s="8" t="n"/>
       <c r="K643" s="8" t="n"/>
       <c r="L643" s="8" t="n"/>
-      <c r="M643" s="8" t="n"/>
+      <c r="M643" s="35" t="n">
+        <v>3868</v>
+      </c>
       <c r="N643" s="8" t="n"/>
     </row>
     <row r="644">
@@ -25986,7 +26634,9 @@
       <c r="J644" s="8" t="n"/>
       <c r="K644" s="8" t="n"/>
       <c r="L644" s="8" t="n"/>
-      <c r="M644" s="8" t="n"/>
+      <c r="M644" s="35" t="n">
+        <v>9774</v>
+      </c>
       <c r="N644" s="8" t="n"/>
     </row>
     <row r="645">
@@ -26020,7 +26670,9 @@
       <c r="J645" s="8" t="n"/>
       <c r="K645" s="8" t="n"/>
       <c r="L645" s="8" t="n"/>
-      <c r="M645" s="8" t="n"/>
+      <c r="M645" s="35" t="n">
+        <v>5400</v>
+      </c>
       <c r="N645" s="8" t="n"/>
     </row>
     <row r="646">
@@ -26054,7 +26706,9 @@
       <c r="J646" s="8" t="n"/>
       <c r="K646" s="8" t="n"/>
       <c r="L646" s="8" t="n"/>
-      <c r="M646" s="8" t="n"/>
+      <c r="M646" s="35" t="n">
+        <v>12439</v>
+      </c>
       <c r="N646" s="8" t="n"/>
     </row>
     <row r="647">
@@ -26088,7 +26742,9 @@
       <c r="J647" s="8" t="n"/>
       <c r="K647" s="8" t="n"/>
       <c r="L647" s="8" t="n"/>
-      <c r="M647" s="8" t="n"/>
+      <c r="M647" s="35" t="n">
+        <v>9190</v>
+      </c>
       <c r="N647" s="8" t="n"/>
     </row>
     <row r="648">
@@ -26122,7 +26778,9 @@
       <c r="J648" s="8" t="n"/>
       <c r="K648" s="8" t="n"/>
       <c r="L648" s="8" t="n"/>
-      <c r="M648" s="8" t="n"/>
+      <c r="M648" s="35" t="n">
+        <v>3654</v>
+      </c>
       <c r="N648" s="8" t="n"/>
     </row>
     <row r="649">
@@ -26156,7 +26814,9 @@
       <c r="J649" s="8" t="n"/>
       <c r="K649" s="8" t="n"/>
       <c r="L649" s="8" t="n"/>
-      <c r="M649" s="8" t="n"/>
+      <c r="M649" s="35" t="n">
+        <v>13642</v>
+      </c>
       <c r="N649" s="8" t="n"/>
     </row>
     <row r="650">
@@ -26190,7 +26850,9 @@
       <c r="J650" s="8" t="n"/>
       <c r="K650" s="8" t="n"/>
       <c r="L650" s="8" t="n"/>
-      <c r="M650" s="8" t="n"/>
+      <c r="M650" s="35" t="n">
+        <v>636</v>
+      </c>
       <c r="N650" s="8" t="n"/>
     </row>
     <row r="651">
@@ -26224,7 +26886,9 @@
       <c r="J651" s="8" t="n"/>
       <c r="K651" s="8" t="n"/>
       <c r="L651" s="8" t="n"/>
-      <c r="M651" s="8" t="n"/>
+      <c r="M651" s="35" t="n">
+        <v>138</v>
+      </c>
       <c r="N651" s="8" t="n"/>
     </row>
     <row r="652">
@@ -26258,7 +26922,9 @@
       <c r="J652" s="8" t="n"/>
       <c r="K652" s="8" t="n"/>
       <c r="L652" s="8" t="n"/>
-      <c r="M652" s="8" t="n"/>
+      <c r="M652" s="35" t="n">
+        <v>1111</v>
+      </c>
       <c r="N652" s="8" t="n"/>
     </row>
     <row r="653">
@@ -26334,7 +27000,9 @@
       <c r="J654" s="8" t="n"/>
       <c r="K654" s="8" t="n"/>
       <c r="L654" s="8" t="n"/>
-      <c r="M654" s="8" t="n"/>
+      <c r="M654" s="35" t="n">
+        <v>20229</v>
+      </c>
       <c r="N654" s="8" t="n"/>
     </row>
     <row r="655">
@@ -26368,7 +27036,9 @@
       <c r="J655" s="8" t="n"/>
       <c r="K655" s="8" t="n"/>
       <c r="L655" s="8" t="n"/>
-      <c r="M655" s="8" t="n"/>
+      <c r="M655" s="35" t="n">
+        <v>1021</v>
+      </c>
       <c r="N655" s="8" t="n"/>
     </row>
     <row r="656">
@@ -26402,7 +27072,9 @@
       <c r="J656" s="8" t="n"/>
       <c r="K656" s="8" t="n"/>
       <c r="L656" s="8" t="n"/>
-      <c r="M656" s="8" t="n"/>
+      <c r="M656" s="35" t="n">
+        <v>4076</v>
+      </c>
       <c r="N656" s="8" t="n"/>
     </row>
     <row r="657">
@@ -26436,7 +27108,9 @@
       <c r="J657" s="8" t="n"/>
       <c r="K657" s="8" t="n"/>
       <c r="L657" s="8" t="n"/>
-      <c r="M657" s="8" t="n"/>
+      <c r="M657" s="35" t="n">
+        <v>1404</v>
+      </c>
       <c r="N657" s="8" t="n"/>
     </row>
     <row r="658">
@@ -26470,7 +27144,9 @@
       <c r="J658" s="8" t="n"/>
       <c r="K658" s="8" t="n"/>
       <c r="L658" s="8" t="n"/>
-      <c r="M658" s="8" t="n"/>
+      <c r="M658" s="35" t="n">
+        <v>2263</v>
+      </c>
       <c r="N658" s="8" t="n"/>
     </row>
     <row r="659">
@@ -26504,7 +27180,9 @@
       <c r="J659" s="8" t="n"/>
       <c r="K659" s="8" t="n"/>
       <c r="L659" s="8" t="n"/>
-      <c r="M659" s="8" t="n"/>
+      <c r="M659" s="35" t="n">
+        <v>4593</v>
+      </c>
       <c r="N659" s="8" t="n"/>
     </row>
     <row r="660">
@@ -26538,7 +27216,9 @@
       <c r="J660" s="8" t="n"/>
       <c r="K660" s="8" t="n"/>
       <c r="L660" s="8" t="n"/>
-      <c r="M660" s="8" t="n"/>
+      <c r="M660" s="35" t="n">
+        <v>908</v>
+      </c>
       <c r="N660" s="8" t="n"/>
     </row>
     <row r="661">
@@ -26572,7 +27252,9 @@
       <c r="J661" s="8" t="n"/>
       <c r="K661" s="8" t="n"/>
       <c r="L661" s="8" t="n"/>
-      <c r="M661" s="8" t="n"/>
+      <c r="M661" s="35" t="n">
+        <v>7247</v>
+      </c>
       <c r="N661" s="8" t="n"/>
     </row>
     <row r="662">
@@ -26606,7 +27288,9 @@
       <c r="J662" s="8" t="n"/>
       <c r="K662" s="8" t="n"/>
       <c r="L662" s="8" t="n"/>
-      <c r="M662" s="8" t="n"/>
+      <c r="M662" s="35" t="n">
+        <v>1849</v>
+      </c>
       <c r="N662" s="8" t="n"/>
     </row>
     <row r="663">
@@ -26640,7 +27324,9 @@
       <c r="J663" s="8" t="n"/>
       <c r="K663" s="8" t="n"/>
       <c r="L663" s="8" t="n"/>
-      <c r="M663" s="8" t="n"/>
+      <c r="M663" s="35" t="n">
+        <v>1180</v>
+      </c>
       <c r="N663" s="8" t="n"/>
     </row>
     <row r="664">
@@ -26674,7 +27360,9 @@
       <c r="J664" s="8" t="n"/>
       <c r="K664" s="8" t="n"/>
       <c r="L664" s="8" t="n"/>
-      <c r="M664" s="8" t="n"/>
+      <c r="M664" s="35" t="n">
+        <v>2892</v>
+      </c>
       <c r="N664" s="8" t="n"/>
     </row>
     <row r="665">
@@ -26708,7 +27396,9 @@
       <c r="J665" s="8" t="n"/>
       <c r="K665" s="8" t="n"/>
       <c r="L665" s="8" t="n"/>
-      <c r="M665" s="8" t="n"/>
+      <c r="M665" s="35" t="n">
+        <v>786</v>
+      </c>
       <c r="N665" s="8" t="n"/>
     </row>
     <row r="666">
@@ -26742,7 +27432,9 @@
       <c r="J666" s="8" t="n"/>
       <c r="K666" s="8" t="n"/>
       <c r="L666" s="8" t="n"/>
-      <c r="M666" s="8" t="n"/>
+      <c r="M666" s="35" t="n">
+        <v>3533</v>
+      </c>
       <c r="N666" s="8" t="n"/>
     </row>
     <row r="667">
@@ -26776,7 +27468,9 @@
       <c r="J667" s="8" t="n"/>
       <c r="K667" s="8" t="n"/>
       <c r="L667" s="8" t="n"/>
-      <c r="M667" s="8" t="n"/>
+      <c r="M667" s="35" t="n">
+        <v>1644</v>
+      </c>
       <c r="N667" s="8" t="n"/>
     </row>
     <row r="668">
@@ -26810,7 +27504,9 @@
       <c r="J668" s="8" t="n"/>
       <c r="K668" s="8" t="n"/>
       <c r="L668" s="8" t="n"/>
-      <c r="M668" s="8" t="n"/>
+      <c r="M668" s="35" t="n">
+        <v>1239</v>
+      </c>
       <c r="N668" s="8" t="n"/>
     </row>
     <row r="669">
@@ -26844,7 +27540,9 @@
       <c r="J669" s="8" t="n"/>
       <c r="K669" s="8" t="n"/>
       <c r="L669" s="8" t="n"/>
-      <c r="M669" s="8" t="n"/>
+      <c r="M669" s="35" t="n">
+        <v>5904</v>
+      </c>
       <c r="N669" s="8" t="n"/>
     </row>
     <row r="670">
@@ -26878,7 +27576,9 @@
       <c r="J670" s="8" t="n"/>
       <c r="K670" s="11" t="n"/>
       <c r="L670" s="8" t="n"/>
-      <c r="M670" s="8" t="n"/>
+      <c r="M670" s="35" t="n">
+        <v>7650</v>
+      </c>
       <c r="N670" s="8" t="n"/>
     </row>
     <row r="671">
@@ -26912,7 +27612,9 @@
       <c r="J671" s="8" t="n"/>
       <c r="K671" s="8" t="n"/>
       <c r="L671" s="8" t="n"/>
-      <c r="M671" s="8" t="n"/>
+      <c r="M671" s="35" t="n">
+        <v>1112</v>
+      </c>
       <c r="N671" s="8" t="n"/>
     </row>
     <row r="672">
@@ -26946,7 +27648,9 @@
       <c r="J672" s="8" t="n"/>
       <c r="K672" s="8" t="n"/>
       <c r="L672" s="8" t="n"/>
-      <c r="M672" s="8" t="n"/>
+      <c r="M672" s="35" t="n">
+        <v>280</v>
+      </c>
       <c r="N672" s="8" t="n"/>
     </row>
     <row r="673">
@@ -26980,7 +27684,9 @@
       <c r="J673" s="8" t="n"/>
       <c r="K673" s="8" t="n"/>
       <c r="L673" s="8" t="n"/>
-      <c r="M673" s="8" t="n"/>
+      <c r="M673" s="35" t="n">
+        <v>1458</v>
+      </c>
       <c r="N673" s="8" t="n"/>
     </row>
     <row r="674">
@@ -27014,7 +27720,9 @@
       <c r="J674" s="8" t="n"/>
       <c r="K674" s="8" t="n"/>
       <c r="L674" s="8" t="n"/>
-      <c r="M674" s="8" t="n"/>
+      <c r="M674" s="35" t="n">
+        <v>528</v>
+      </c>
       <c r="N674" s="8" t="n"/>
     </row>
     <row r="675">
@@ -27048,7 +27756,9 @@
       <c r="J675" s="8" t="n"/>
       <c r="K675" s="8" t="n"/>
       <c r="L675" s="8" t="n"/>
-      <c r="M675" s="8" t="n"/>
+      <c r="M675" s="35" t="n">
+        <v>708</v>
+      </c>
       <c r="N675" s="8" t="n"/>
     </row>
     <row r="676">
@@ -27082,7 +27792,9 @@
       <c r="J676" s="8" t="n"/>
       <c r="K676" s="8" t="n"/>
       <c r="L676" s="8" t="n"/>
-      <c r="M676" s="8" t="n"/>
+      <c r="M676" s="35" t="n">
+        <v>540</v>
+      </c>
       <c r="N676" s="8" t="n"/>
     </row>
     <row r="677">
@@ -27116,7 +27828,9 @@
       <c r="J677" s="8" t="n"/>
       <c r="K677" s="8" t="n"/>
       <c r="L677" s="8" t="n"/>
-      <c r="M677" s="8" t="n"/>
+      <c r="M677" s="35" t="n">
+        <v>2784</v>
+      </c>
       <c r="N677" s="8" t="n"/>
     </row>
     <row r="678">
@@ -27150,7 +27864,9 @@
       <c r="J678" s="8" t="n"/>
       <c r="K678" s="8" t="n"/>
       <c r="L678" s="8" t="n"/>
-      <c r="M678" s="8" t="n"/>
+      <c r="M678" s="35" t="n">
+        <v>473</v>
+      </c>
       <c r="N678" s="8" t="n"/>
     </row>
     <row r="679">
@@ -27184,7 +27900,9 @@
       <c r="J679" s="8" t="n"/>
       <c r="K679" s="8" t="n"/>
       <c r="L679" s="8" t="n"/>
-      <c r="M679" s="8" t="n"/>
+      <c r="M679" s="35" t="n">
+        <v>927</v>
+      </c>
       <c r="N679" s="8" t="n"/>
     </row>
     <row r="680">
@@ -27218,7 +27936,9 @@
       <c r="J680" s="8" t="n"/>
       <c r="K680" s="8" t="n"/>
       <c r="L680" s="8" t="n"/>
-      <c r="M680" s="8" t="n"/>
+      <c r="M680" s="35" t="n">
+        <v>3855</v>
+      </c>
       <c r="N680" s="8" t="n"/>
     </row>
     <row r="681">
@@ -27252,7 +27972,9 @@
       <c r="J681" s="8" t="n"/>
       <c r="K681" s="11" t="n"/>
       <c r="L681" s="8" t="n"/>
-      <c r="M681" s="8" t="n"/>
+      <c r="M681" s="35" t="n">
+        <v>2195</v>
+      </c>
       <c r="N681" s="8" t="n"/>
     </row>
     <row r="682">
@@ -27286,7 +28008,9 @@
       <c r="J682" s="8" t="n"/>
       <c r="K682" s="8" t="n"/>
       <c r="L682" s="8" t="n"/>
-      <c r="M682" s="8" t="n"/>
+      <c r="M682" s="35" t="n">
+        <v>1375</v>
+      </c>
       <c r="N682" s="8" t="n"/>
     </row>
     <row r="683">
@@ -27320,7 +28044,9 @@
       <c r="J683" s="8" t="n"/>
       <c r="K683" s="8" t="n"/>
       <c r="L683" s="8" t="n"/>
-      <c r="M683" s="8" t="n"/>
+      <c r="M683" s="35" t="n">
+        <v>400</v>
+      </c>
       <c r="N683" s="8" t="n"/>
     </row>
     <row r="684">
@@ -27354,7 +28080,9 @@
       <c r="J684" s="8" t="n"/>
       <c r="K684" s="8" t="n"/>
       <c r="L684" s="8" t="n"/>
-      <c r="M684" s="8" t="n"/>
+      <c r="M684" s="35" t="n">
+        <v>415</v>
+      </c>
       <c r="N684" s="8" t="n"/>
     </row>
     <row r="685">
@@ -27388,7 +28116,9 @@
       <c r="J685" s="8" t="n"/>
       <c r="K685" s="8" t="n"/>
       <c r="L685" s="8" t="n"/>
-      <c r="M685" s="8" t="n"/>
+      <c r="M685" s="35" t="n">
+        <v>457</v>
+      </c>
       <c r="N685" s="8" t="n"/>
     </row>
     <row r="686">
@@ -27422,7 +28152,9 @@
       <c r="J686" s="8" t="n"/>
       <c r="K686" s="8" t="n"/>
       <c r="L686" s="8" t="n"/>
-      <c r="M686" s="8" t="n"/>
+      <c r="M686" s="35" t="n">
+        <v>223</v>
+      </c>
       <c r="N686" s="8" t="n"/>
     </row>
     <row r="687">
@@ -27456,7 +28188,9 @@
       <c r="J687" s="8" t="n"/>
       <c r="K687" s="8" t="n"/>
       <c r="L687" s="8" t="n"/>
-      <c r="M687" s="8" t="n"/>
+      <c r="M687" s="35" t="n">
+        <v>2424</v>
+      </c>
       <c r="N687" s="8" t="n"/>
     </row>
     <row r="688">
@@ -27490,7 +28224,9 @@
       <c r="J688" s="8" t="n"/>
       <c r="K688" s="8" t="n"/>
       <c r="L688" s="8" t="n"/>
-      <c r="M688" s="8" t="n"/>
+      <c r="M688" s="35" t="n">
+        <v>760</v>
+      </c>
       <c r="N688" s="8" t="n"/>
     </row>
     <row r="689">
@@ -27524,7 +28260,9 @@
       <c r="J689" s="8" t="n"/>
       <c r="K689" s="8" t="n"/>
       <c r="L689" s="8" t="n"/>
-      <c r="M689" s="8" t="n"/>
+      <c r="M689" s="35" t="n">
+        <v>1016</v>
+      </c>
       <c r="N689" s="8" t="n"/>
     </row>
     <row r="690">
@@ -27558,7 +28296,9 @@
       <c r="J690" s="8" t="n"/>
       <c r="K690" s="8" t="n"/>
       <c r="L690" s="8" t="n"/>
-      <c r="M690" s="8" t="n"/>
+      <c r="M690" s="35" t="n">
+        <v>2452</v>
+      </c>
       <c r="N690" s="8" t="n"/>
     </row>
     <row r="691">
@@ -27592,7 +28332,9 @@
       <c r="J691" s="8" t="n"/>
       <c r="K691" s="8" t="n"/>
       <c r="L691" s="8" t="n"/>
-      <c r="M691" s="8" t="n"/>
+      <c r="M691" s="35" t="n">
+        <v>198</v>
+      </c>
       <c r="N691" s="8" t="n"/>
     </row>
     <row r="692">
@@ -27626,7 +28368,9 @@
       <c r="J692" s="8" t="n"/>
       <c r="K692" s="8" t="n"/>
       <c r="L692" s="8" t="n"/>
-      <c r="M692" s="8" t="n"/>
+      <c r="M692" s="35" t="n">
+        <v>443</v>
+      </c>
       <c r="N692" s="8" t="n"/>
     </row>
     <row r="693">
@@ -27660,7 +28404,9 @@
       <c r="J693" s="8" t="n"/>
       <c r="K693" s="8" t="n"/>
       <c r="L693" s="8" t="n"/>
-      <c r="M693" s="8" t="n"/>
+      <c r="M693" s="35" t="n">
+        <v>1725</v>
+      </c>
       <c r="N693" s="8" t="n"/>
     </row>
     <row r="694">
@@ -27694,7 +28440,9 @@
       <c r="J694" s="8" t="n"/>
       <c r="K694" s="8" t="n"/>
       <c r="L694" s="8" t="n"/>
-      <c r="M694" s="8" t="n"/>
+      <c r="M694" s="35" t="n">
+        <v>4827</v>
+      </c>
       <c r="N694" s="8" t="n"/>
     </row>
     <row r="695">
@@ -27728,7 +28476,9 @@
       <c r="J695" s="8" t="n"/>
       <c r="K695" s="8" t="n"/>
       <c r="L695" s="8" t="n"/>
-      <c r="M695" s="8" t="n"/>
+      <c r="M695" s="35" t="n">
+        <v>2253</v>
+      </c>
       <c r="N695" s="8" t="n"/>
     </row>
     <row r="696">
@@ -27762,7 +28512,9 @@
       <c r="J696" s="8" t="n"/>
       <c r="K696" s="8" t="n"/>
       <c r="L696" s="17" t="n"/>
-      <c r="M696" s="8" t="n"/>
+      <c r="M696" s="35" t="n">
+        <v>249</v>
+      </c>
       <c r="N696" s="8" t="n"/>
     </row>
     <row r="697">
@@ -27796,7 +28548,9 @@
       <c r="J697" s="8" t="n"/>
       <c r="K697" s="8" t="n"/>
       <c r="L697" s="8" t="n"/>
-      <c r="M697" s="8" t="n"/>
+      <c r="M697" s="35" t="n">
+        <v>3257</v>
+      </c>
       <c r="N697" s="8" t="n"/>
     </row>
     <row r="698">
@@ -27830,7 +28584,9 @@
       <c r="J698" s="8" t="n"/>
       <c r="K698" s="8" t="n"/>
       <c r="L698" s="8" t="n"/>
-      <c r="M698" s="8" t="n"/>
+      <c r="M698" s="35" t="n">
+        <v>2827</v>
+      </c>
       <c r="N698" s="8" t="n"/>
     </row>
     <row r="699">
@@ -27864,7 +28620,9 @@
       <c r="J699" s="8" t="n"/>
       <c r="K699" s="8" t="n"/>
       <c r="L699" s="8" t="n"/>
-      <c r="M699" s="8" t="n"/>
+      <c r="M699" s="35" t="n">
+        <v>1930</v>
+      </c>
       <c r="N699" s="8" t="n"/>
     </row>
     <row r="700">
@@ -27898,7 +28656,9 @@
       <c r="J700" s="8" t="n"/>
       <c r="K700" s="8" t="n"/>
       <c r="L700" s="8" t="n"/>
-      <c r="M700" s="8" t="n"/>
+      <c r="M700" s="35" t="n">
+        <v>161</v>
+      </c>
       <c r="N700" s="8" t="n"/>
     </row>
     <row r="701">
@@ -27932,7 +28692,9 @@
       <c r="J701" s="8" t="n"/>
       <c r="K701" s="8" t="n"/>
       <c r="L701" s="8" t="n"/>
-      <c r="M701" s="8" t="n"/>
+      <c r="M701" s="35" t="n">
+        <v>2810</v>
+      </c>
       <c r="N701" s="8" t="n"/>
     </row>
     <row r="702">
@@ -27966,7 +28728,9 @@
       <c r="J702" s="8" t="n"/>
       <c r="K702" s="8" t="n"/>
       <c r="L702" s="8" t="n"/>
-      <c r="M702" s="8" t="n"/>
+      <c r="M702" s="35" t="n">
+        <v>340</v>
+      </c>
       <c r="N702" s="8" t="n"/>
     </row>
     <row r="703">
@@ -28000,7 +28764,9 @@
       <c r="J703" s="8" t="n"/>
       <c r="K703" s="8" t="n"/>
       <c r="L703" s="8" t="n"/>
-      <c r="M703" s="8" t="n"/>
+      <c r="M703" s="35" t="n">
+        <v>3644</v>
+      </c>
       <c r="N703" s="8" t="n"/>
     </row>
     <row r="704">
@@ -28034,7 +28800,9 @@
       <c r="J704" s="8" t="n"/>
       <c r="K704" s="8" t="n"/>
       <c r="L704" s="8" t="n"/>
-      <c r="M704" s="8" t="n"/>
+      <c r="M704" s="35" t="n">
+        <v>425</v>
+      </c>
       <c r="N704" s="8" t="n"/>
     </row>
     <row r="705">
@@ -28068,7 +28836,9 @@
       <c r="J705" s="8" t="n"/>
       <c r="K705" s="8" t="n"/>
       <c r="L705" s="8" t="n"/>
-      <c r="M705" s="8" t="n"/>
+      <c r="M705" s="35" t="n">
+        <v>5545</v>
+      </c>
       <c r="N705" s="8" t="n"/>
     </row>
     <row r="706">
@@ -28102,7 +28872,9 @@
       <c r="J706" s="8" t="n"/>
       <c r="K706" s="8" t="n"/>
       <c r="L706" s="8" t="n"/>
-      <c r="M706" s="8" t="n"/>
+      <c r="M706" s="35" t="n">
+        <v>996</v>
+      </c>
       <c r="N706" s="8" t="n"/>
     </row>
     <row r="707">
@@ -28136,7 +28908,9 @@
       <c r="J707" s="8" t="n"/>
       <c r="K707" s="8" t="n"/>
       <c r="L707" s="8" t="n"/>
-      <c r="M707" s="8" t="n"/>
+      <c r="M707" s="35" t="n">
+        <v>1544</v>
+      </c>
       <c r="N707" s="8" t="n"/>
     </row>
     <row r="708">
@@ -28170,7 +28944,9 @@
       <c r="J708" s="8" t="n"/>
       <c r="K708" s="8" t="n"/>
       <c r="L708" s="8" t="n"/>
-      <c r="M708" s="8" t="n"/>
+      <c r="M708" s="35" t="n">
+        <v>12818</v>
+      </c>
       <c r="N708" s="8" t="n"/>
     </row>
     <row r="709">
@@ -28204,7 +28980,9 @@
       <c r="J709" s="8" t="n"/>
       <c r="K709" s="8" t="n"/>
       <c r="L709" s="8" t="n"/>
-      <c r="M709" s="8" t="n"/>
+      <c r="M709" s="35" t="n">
+        <v>2922</v>
+      </c>
       <c r="N709" s="8" t="n"/>
     </row>
     <row r="710">
@@ -28238,7 +29016,9 @@
       <c r="J710" s="8" t="n"/>
       <c r="K710" s="8" t="n"/>
       <c r="L710" s="8" t="n"/>
-      <c r="M710" s="8" t="n"/>
+      <c r="M710" s="35" t="n">
+        <v>4077</v>
+      </c>
       <c r="N710" s="8" t="n"/>
     </row>
     <row r="711">
@@ -28272,7 +29052,9 @@
       <c r="J711" s="8" t="n"/>
       <c r="K711" s="8" t="n"/>
       <c r="L711" s="8" t="n"/>
-      <c r="M711" s="8" t="n"/>
+      <c r="M711" s="35" t="n">
+        <v>240</v>
+      </c>
       <c r="N711" s="8" t="n"/>
     </row>
     <row r="712">
@@ -28306,7 +29088,9 @@
       <c r="J712" s="8" t="n"/>
       <c r="K712" s="8" t="n"/>
       <c r="L712" s="8" t="n"/>
-      <c r="M712" s="8" t="n"/>
+      <c r="M712" s="35" t="n">
+        <v>1728</v>
+      </c>
       <c r="N712" s="8" t="n"/>
     </row>
     <row r="713">
@@ -28340,7 +29124,9 @@
       <c r="J713" s="8" t="n"/>
       <c r="K713" s="8" t="n"/>
       <c r="L713" s="8" t="n"/>
-      <c r="M713" s="8" t="n"/>
+      <c r="M713" s="35" t="n">
+        <v>695</v>
+      </c>
       <c r="N713" s="8" t="n"/>
     </row>
     <row r="714">
@@ -28374,7 +29160,9 @@
       <c r="J714" s="8" t="n"/>
       <c r="K714" s="8" t="n"/>
       <c r="L714" s="8" t="n"/>
-      <c r="M714" s="8" t="n"/>
+      <c r="M714" s="35" t="n">
+        <v>200</v>
+      </c>
       <c r="N714" s="8" t="n"/>
     </row>
     <row r="715">
@@ -28408,7 +29196,9 @@
       <c r="J715" s="8" t="n"/>
       <c r="K715" s="8" t="n"/>
       <c r="L715" s="8" t="n"/>
-      <c r="M715" s="8" t="n"/>
+      <c r="M715" s="35" t="n">
+        <v>493</v>
+      </c>
       <c r="N715" s="8" t="n"/>
     </row>
     <row r="716">
@@ -28442,7 +29232,9 @@
       <c r="J716" s="8" t="n"/>
       <c r="K716" s="8" t="n"/>
       <c r="L716" s="8" t="n"/>
-      <c r="M716" s="8" t="n"/>
+      <c r="M716" s="35" t="n">
+        <v>1036</v>
+      </c>
       <c r="N716" s="8" t="n"/>
     </row>
     <row r="717">
@@ -28518,7 +29310,9 @@
       <c r="J718" s="8" t="n"/>
       <c r="K718" s="8" t="n"/>
       <c r="L718" s="8" t="n"/>
-      <c r="M718" s="8" t="n"/>
+      <c r="M718" s="35" t="n">
+        <v>530</v>
+      </c>
       <c r="N718" s="8" t="n"/>
     </row>
     <row r="719">
@@ -28552,7 +29346,9 @@
       <c r="J719" s="8" t="n"/>
       <c r="K719" s="8" t="n"/>
       <c r="L719" s="8" t="n"/>
-      <c r="M719" s="8" t="n"/>
+      <c r="M719" s="35" t="n">
+        <v>1329</v>
+      </c>
       <c r="N719" s="8" t="n"/>
     </row>
     <row r="720">
@@ -28586,7 +29382,9 @@
       <c r="J720" s="8" t="n"/>
       <c r="K720" s="8" t="n"/>
       <c r="L720" s="8" t="n"/>
-      <c r="M720" s="8" t="n"/>
+      <c r="M720" s="35" t="n">
+        <v>280</v>
+      </c>
       <c r="N720" s="8" t="n"/>
     </row>
     <row r="721">
@@ -28620,7 +29418,9 @@
       <c r="J721" s="8" t="n"/>
       <c r="K721" s="8" t="n"/>
       <c r="L721" s="17" t="n"/>
-      <c r="M721" s="8" t="n"/>
+      <c r="M721" s="35" t="n">
+        <v>4123</v>
+      </c>
       <c r="N721" s="8" t="n"/>
     </row>
     <row r="722">
@@ -28654,7 +29454,9 @@
       <c r="J722" s="8" t="n"/>
       <c r="K722" s="8" t="n"/>
       <c r="L722" s="17" t="n"/>
-      <c r="M722" s="8" t="n"/>
+      <c r="M722" s="35" t="n">
+        <v>784</v>
+      </c>
       <c r="N722" s="8" t="n"/>
     </row>
     <row r="723">
@@ -28688,7 +29490,9 @@
       <c r="J723" s="8" t="n"/>
       <c r="K723" s="8" t="n"/>
       <c r="L723" s="8" t="n"/>
-      <c r="M723" s="8" t="n"/>
+      <c r="M723" s="35" t="n">
+        <v>1262</v>
+      </c>
       <c r="N723" s="8" t="n"/>
     </row>
     <row r="724">
@@ -28722,7 +29526,9 @@
       <c r="J724" s="8" t="n"/>
       <c r="K724" s="8" t="n"/>
       <c r="L724" s="8" t="n"/>
-      <c r="M724" s="8" t="n"/>
+      <c r="M724" s="35" t="n">
+        <v>263</v>
+      </c>
       <c r="N724" s="8" t="n"/>
     </row>
     <row r="725">
@@ -28756,7 +29562,9 @@
       <c r="J725" s="8" t="n"/>
       <c r="K725" s="8" t="n"/>
       <c r="L725" s="8" t="n"/>
-      <c r="M725" s="8" t="n"/>
+      <c r="M725" s="35" t="n">
+        <v>4795</v>
+      </c>
       <c r="N725" s="8" t="n"/>
     </row>
     <row r="726">
@@ -28790,7 +29598,9 @@
       <c r="J726" s="8" t="n"/>
       <c r="K726" s="8" t="n"/>
       <c r="L726" s="17" t="n"/>
-      <c r="M726" s="8" t="n"/>
+      <c r="M726" s="35" t="n">
+        <v>289</v>
+      </c>
       <c r="N726" s="8" t="n"/>
     </row>
     <row r="727">
@@ -28824,7 +29634,9 @@
       <c r="J727" s="8" t="n"/>
       <c r="K727" s="8" t="n"/>
       <c r="L727" s="8" t="n"/>
-      <c r="M727" s="8" t="n"/>
+      <c r="M727" s="35" t="n">
+        <v>252</v>
+      </c>
       <c r="N727" s="8" t="n"/>
     </row>
     <row r="728">
@@ -28858,7 +29670,9 @@
       <c r="J728" s="8" t="n"/>
       <c r="K728" s="8" t="n"/>
       <c r="L728" s="8" t="n"/>
-      <c r="M728" s="8" t="n"/>
+      <c r="M728" s="35" t="n">
+        <v>773</v>
+      </c>
       <c r="N728" s="8" t="n"/>
     </row>
     <row r="729">
@@ -28892,7 +29706,9 @@
       <c r="J729" s="8" t="n"/>
       <c r="K729" s="8" t="n"/>
       <c r="L729" s="8" t="n"/>
-      <c r="M729" s="8" t="n"/>
+      <c r="M729" s="35" t="n">
+        <v>2398</v>
+      </c>
       <c r="N729" s="8" t="n"/>
     </row>
     <row r="730">
@@ -28926,7 +29742,9 @@
       <c r="J730" s="8" t="n"/>
       <c r="K730" s="8" t="n"/>
       <c r="L730" s="8" t="n"/>
-      <c r="M730" s="8" t="n"/>
+      <c r="M730" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="N730" s="8" t="n"/>
     </row>
     <row r="731">
@@ -28960,7 +29778,9 @@
       <c r="J731" s="8" t="n"/>
       <c r="K731" s="8" t="n"/>
       <c r="L731" s="8" t="n"/>
-      <c r="M731" s="8" t="n"/>
+      <c r="M731" s="35" t="n">
+        <v>296</v>
+      </c>
       <c r="N731" s="8" t="n"/>
     </row>
     <row r="732">
@@ -28994,7 +29814,9 @@
       <c r="J732" s="8" t="n"/>
       <c r="K732" s="8" t="n"/>
       <c r="L732" s="8" t="n"/>
-      <c r="M732" s="8" t="n"/>
+      <c r="M732" s="35" t="n">
+        <v>242</v>
+      </c>
       <c r="N732" s="8" t="n"/>
     </row>
     <row r="733">
@@ -29028,7 +29850,9 @@
       <c r="J733" s="8" t="n"/>
       <c r="K733" s="8" t="n"/>
       <c r="L733" s="8" t="n"/>
-      <c r="M733" s="8" t="n"/>
+      <c r="M733" s="35" t="n">
+        <v>596</v>
+      </c>
       <c r="N733" s="8" t="n"/>
     </row>
     <row r="734">
@@ -29062,7 +29886,9 @@
       <c r="J734" s="8" t="n"/>
       <c r="K734" s="8" t="n"/>
       <c r="L734" s="8" t="n"/>
-      <c r="M734" s="8" t="n"/>
+      <c r="M734" s="35" t="n">
+        <v>330</v>
+      </c>
       <c r="N734" s="8" t="n"/>
     </row>
     <row r="735">
@@ -29096,7 +29922,9 @@
       <c r="J735" s="8" t="n"/>
       <c r="K735" s="8" t="n"/>
       <c r="L735" s="8" t="n"/>
-      <c r="M735" s="8" t="n"/>
+      <c r="M735" s="35" t="n">
+        <v>213</v>
+      </c>
       <c r="N735" s="8" t="n"/>
     </row>
     <row r="736">
@@ -29130,7 +29958,9 @@
       <c r="J736" s="8" t="n"/>
       <c r="K736" s="8" t="n"/>
       <c r="L736" s="8" t="n"/>
-      <c r="M736" s="8" t="n"/>
+      <c r="M736" s="35" t="n">
+        <v>2218</v>
+      </c>
       <c r="N736" s="8" t="n"/>
     </row>
     <row r="737">
@@ -29164,7 +29994,9 @@
       <c r="J737" s="8" t="n"/>
       <c r="K737" s="8" t="n"/>
       <c r="L737" s="8" t="n"/>
-      <c r="M737" s="8" t="n"/>
+      <c r="M737" s="35" t="n">
+        <v>2144</v>
+      </c>
       <c r="N737" s="8" t="n"/>
     </row>
     <row r="738">
@@ -29198,7 +30030,9 @@
       <c r="J738" s="8" t="n"/>
       <c r="K738" s="8" t="n"/>
       <c r="L738" s="8" t="n"/>
-      <c r="M738" s="8" t="n"/>
+      <c r="M738" s="35" t="n">
+        <v>1167</v>
+      </c>
       <c r="N738" s="8" t="n"/>
     </row>
     <row r="739">
@@ -29232,7 +30066,9 @@
       <c r="J739" s="8" t="n"/>
       <c r="K739" s="8" t="n"/>
       <c r="L739" s="8" t="n"/>
-      <c r="M739" s="8" t="n"/>
+      <c r="M739" s="35" t="n">
+        <v>480</v>
+      </c>
       <c r="N739" s="8" t="n"/>
     </row>
     <row r="740">
@@ -29266,7 +30102,9 @@
       <c r="J740" s="8" t="n"/>
       <c r="K740" s="8" t="n"/>
       <c r="L740" s="8" t="n"/>
-      <c r="M740" s="8" t="n"/>
+      <c r="M740" s="35" t="n">
+        <v>1512</v>
+      </c>
       <c r="N740" s="8" t="n"/>
     </row>
     <row r="741">
@@ -29300,7 +30138,9 @@
       <c r="J741" s="8" t="n"/>
       <c r="K741" s="8" t="n"/>
       <c r="L741" s="8" t="n"/>
-      <c r="M741" s="8" t="n"/>
+      <c r="M741" s="35" t="n">
+        <v>1862</v>
+      </c>
       <c r="N741" s="8" t="n"/>
     </row>
     <row r="742">
@@ -29334,7 +30174,9 @@
       <c r="J742" s="8" t="n"/>
       <c r="K742" s="8" t="n"/>
       <c r="L742" s="8" t="n"/>
-      <c r="M742" s="8" t="n"/>
+      <c r="M742" s="35" t="n">
+        <v>2837</v>
+      </c>
       <c r="N742" s="8" t="n"/>
     </row>
     <row r="743">
@@ -29368,7 +30210,9 @@
       <c r="J743" s="8" t="n"/>
       <c r="K743" s="8" t="n"/>
       <c r="L743" s="8" t="n"/>
-      <c r="M743" s="8" t="n"/>
+      <c r="M743" s="35" t="n">
+        <v>4010</v>
+      </c>
       <c r="N743" s="8" t="n"/>
     </row>
     <row r="744">
@@ -29402,7 +30246,9 @@
       <c r="J744" s="8" t="n"/>
       <c r="K744" s="8" t="n"/>
       <c r="L744" s="8" t="n"/>
-      <c r="M744" s="8" t="n"/>
+      <c r="M744" s="35" t="n">
+        <v>12541</v>
+      </c>
       <c r="N744" s="8" t="n"/>
     </row>
     <row r="745">
@@ -29436,7 +30282,9 @@
       <c r="J745" s="8" t="n"/>
       <c r="K745" s="8" t="n"/>
       <c r="L745" s="8" t="n"/>
-      <c r="M745" s="8" t="n"/>
+      <c r="M745" s="35" t="n">
+        <v>476</v>
+      </c>
       <c r="N745" s="8" t="n"/>
     </row>
     <row r="746">
@@ -29470,7 +30318,9 @@
       <c r="J746" s="8" t="n"/>
       <c r="K746" s="8" t="n"/>
       <c r="L746" s="8" t="n"/>
-      <c r="M746" s="8" t="n"/>
+      <c r="M746" s="35" t="n">
+        <v>374</v>
+      </c>
       <c r="N746" s="8" t="n"/>
     </row>
     <row r="747">
@@ -29504,7 +30354,9 @@
       <c r="J747" s="8" t="n"/>
       <c r="K747" s="8" t="n"/>
       <c r="L747" s="8" t="n"/>
-      <c r="M747" s="8" t="n"/>
+      <c r="M747" s="35" t="n">
+        <v>2116</v>
+      </c>
       <c r="N747" s="8" t="n"/>
     </row>
     <row r="748">
@@ -29538,7 +30390,9 @@
       <c r="J748" s="8" t="n"/>
       <c r="K748" s="8" t="n"/>
       <c r="L748" s="8" t="n"/>
-      <c r="M748" s="8" t="n"/>
+      <c r="M748" s="35" t="n">
+        <v>1277</v>
+      </c>
       <c r="N748" s="8" t="n"/>
     </row>
     <row r="749">
@@ -29572,7 +30426,9 @@
       <c r="J749" s="8" t="n"/>
       <c r="K749" s="8" t="n"/>
       <c r="L749" s="8" t="n"/>
-      <c r="M749" s="8" t="n"/>
+      <c r="M749" s="35" t="n">
+        <v>1113</v>
+      </c>
       <c r="N749" s="8" t="n"/>
     </row>
     <row r="750">
@@ -29606,7 +30462,9 @@
       <c r="J750" s="8" t="n"/>
       <c r="K750" s="8" t="n"/>
       <c r="L750" s="8" t="n"/>
-      <c r="M750" s="8" t="n"/>
+      <c r="M750" s="35" t="n">
+        <v>1736</v>
+      </c>
       <c r="N750" s="8" t="n"/>
     </row>
     <row r="751">
@@ -29640,7 +30498,9 @@
       <c r="J751" s="8" t="n"/>
       <c r="K751" s="8" t="n"/>
       <c r="L751" s="8" t="n"/>
-      <c r="M751" s="8" t="n"/>
+      <c r="M751" s="35" t="n">
+        <v>2039</v>
+      </c>
       <c r="N751" s="8" t="n"/>
     </row>
     <row r="752">
@@ -29674,7 +30534,9 @@
       <c r="J752" s="8" t="n"/>
       <c r="K752" s="8" t="n"/>
       <c r="L752" s="8" t="n"/>
-      <c r="M752" s="8" t="n"/>
+      <c r="M752" s="35" t="n">
+        <v>473</v>
+      </c>
       <c r="N752" s="8" t="n"/>
     </row>
     <row r="753">
@@ -29708,7 +30570,9 @@
       <c r="J753" s="8" t="n"/>
       <c r="K753" s="8" t="n"/>
       <c r="L753" s="8" t="n"/>
-      <c r="M753" s="8" t="n"/>
+      <c r="M753" s="35" t="n">
+        <v>667</v>
+      </c>
       <c r="N753" s="8" t="n"/>
     </row>
     <row r="754">
@@ -29742,7 +30606,9 @@
       <c r="J754" s="8" t="n"/>
       <c r="K754" s="8" t="n"/>
       <c r="L754" s="8" t="n"/>
-      <c r="M754" s="8" t="n"/>
+      <c r="M754" s="35" t="n">
+        <v>1502</v>
+      </c>
       <c r="N754" s="8" t="n"/>
     </row>
     <row r="755">
@@ -29776,7 +30642,9 @@
       <c r="J755" s="8" t="n"/>
       <c r="K755" s="8" t="n"/>
       <c r="L755" s="8" t="n"/>
-      <c r="M755" s="8" t="n"/>
+      <c r="M755" s="35" t="n">
+        <v>540</v>
+      </c>
       <c r="N755" s="8" t="n"/>
     </row>
     <row r="756">
@@ -29810,7 +30678,9 @@
       <c r="J756" s="8" t="n"/>
       <c r="K756" s="8" t="n"/>
       <c r="L756" s="8" t="n"/>
-      <c r="M756" s="8" t="n"/>
+      <c r="M756" s="35" t="n">
+        <v>254</v>
+      </c>
       <c r="N756" s="8" t="n"/>
     </row>
     <row r="757">
@@ -29844,7 +30714,9 @@
       <c r="J757" s="8" t="n"/>
       <c r="K757" s="8" t="n"/>
       <c r="L757" s="8" t="n"/>
-      <c r="M757" s="8" t="n"/>
+      <c r="M757" s="35" t="n">
+        <v>295</v>
+      </c>
       <c r="N757" s="8" t="n"/>
     </row>
     <row r="758">
@@ -29878,7 +30750,9 @@
       <c r="J758" s="8" t="n"/>
       <c r="K758" s="8" t="n"/>
       <c r="L758" s="18" t="n"/>
-      <c r="M758" s="8" t="n"/>
+      <c r="M758" s="35" t="n">
+        <v>570</v>
+      </c>
       <c r="N758" s="8" t="n"/>
     </row>
     <row r="759">
@@ -29912,7 +30786,9 @@
       <c r="J759" s="8" t="n"/>
       <c r="K759" s="8" t="n"/>
       <c r="L759" s="8" t="n"/>
-      <c r="M759" s="8" t="n"/>
+      <c r="M759" s="35" t="n">
+        <v>413</v>
+      </c>
       <c r="N759" s="8" t="n"/>
     </row>
     <row r="760">
@@ -29946,7 +30822,9 @@
       <c r="J760" s="8" t="n"/>
       <c r="K760" s="8" t="n"/>
       <c r="L760" s="8" t="n"/>
-      <c r="M760" s="8" t="n"/>
+      <c r="M760" s="35" t="n">
+        <v>504</v>
+      </c>
       <c r="N760" s="8" t="n"/>
     </row>
     <row r="761">
@@ -29980,7 +30858,9 @@
       <c r="J761" s="8" t="n"/>
       <c r="K761" s="8" t="n"/>
       <c r="L761" s="8" t="n"/>
-      <c r="M761" s="8" t="n"/>
+      <c r="M761" s="35" t="n">
+        <v>1801</v>
+      </c>
       <c r="N761" s="8" t="n"/>
     </row>
     <row r="762">
@@ -30062,7 +30942,9 @@
       <c r="J763" s="8" t="n"/>
       <c r="K763" s="8" t="n"/>
       <c r="L763" s="8" t="n"/>
-      <c r="M763" s="8" t="n"/>
+      <c r="M763" s="35" t="n">
+        <v>3257</v>
+      </c>
       <c r="N763" s="8" t="n"/>
     </row>
     <row r="764">
@@ -30096,7 +30978,9 @@
       <c r="J764" s="8" t="n"/>
       <c r="K764" s="8" t="n"/>
       <c r="L764" s="8" t="n"/>
-      <c r="M764" s="8" t="n"/>
+      <c r="M764" s="35" t="n">
+        <v>4410</v>
+      </c>
       <c r="N764" s="8" t="n"/>
     </row>
     <row r="765">
@@ -30130,7 +31014,9 @@
       <c r="J765" s="8" t="n"/>
       <c r="K765" s="8" t="n"/>
       <c r="L765" s="8" t="n"/>
-      <c r="M765" s="8" t="n"/>
+      <c r="M765" s="35" t="n">
+        <v>243</v>
+      </c>
       <c r="N765" s="8" t="n"/>
     </row>
     <row r="766">
@@ -30164,7 +31050,9 @@
       <c r="J766" s="8" t="n"/>
       <c r="K766" s="8" t="n"/>
       <c r="L766" s="8" t="n"/>
-      <c r="M766" s="8" t="n"/>
+      <c r="M766" s="35" t="n">
+        <v>328</v>
+      </c>
       <c r="N766" s="8" t="n"/>
     </row>
     <row r="767">
@@ -30198,7 +31086,9 @@
       <c r="J767" s="8" t="n"/>
       <c r="K767" s="8" t="n"/>
       <c r="L767" s="8" t="n"/>
-      <c r="M767" s="8" t="n"/>
+      <c r="M767" s="35" t="n">
+        <v>1550</v>
+      </c>
       <c r="N767" s="8" t="n"/>
     </row>
     <row r="768">
@@ -30232,7 +31122,9 @@
       <c r="J768" s="8" t="n"/>
       <c r="K768" s="8" t="n"/>
       <c r="L768" s="8" t="n"/>
-      <c r="M768" s="8" t="n"/>
+      <c r="M768" s="35" t="n">
+        <v>927</v>
+      </c>
       <c r="N768" s="8" t="n"/>
     </row>
     <row r="769">
@@ -30266,7 +31158,9 @@
       <c r="J769" s="8" t="n"/>
       <c r="K769" s="8" t="n"/>
       <c r="L769" s="8" t="n"/>
-      <c r="M769" s="8" t="n"/>
+      <c r="M769" s="35" t="n">
+        <v>1838</v>
+      </c>
       <c r="N769" s="8" t="n"/>
     </row>
     <row r="770">
@@ -30300,7 +31194,9 @@
       <c r="J770" s="8" t="n"/>
       <c r="K770" s="8" t="n"/>
       <c r="L770" s="8" t="n"/>
-      <c r="M770" s="8" t="n"/>
+      <c r="M770" s="35" t="n">
+        <v>360</v>
+      </c>
       <c r="N770" s="8" t="n"/>
     </row>
     <row r="771">
@@ -30334,7 +31230,9 @@
       <c r="J771" s="8" t="n"/>
       <c r="K771" s="8" t="n"/>
       <c r="L771" s="8" t="n"/>
-      <c r="M771" s="8" t="n"/>
+      <c r="M771" s="35" t="n">
+        <v>2484</v>
+      </c>
       <c r="N771" s="8" t="n"/>
     </row>
     <row r="772">
@@ -30368,7 +31266,9 @@
       <c r="J772" s="8" t="n"/>
       <c r="K772" s="8" t="n"/>
       <c r="L772" s="8" t="n"/>
-      <c r="M772" s="8" t="n"/>
+      <c r="M772" s="35" t="n">
+        <v>463</v>
+      </c>
       <c r="N772" s="8" t="n"/>
     </row>
     <row r="773">
@@ -30402,7 +31302,9 @@
       <c r="J773" s="8" t="n"/>
       <c r="K773" s="8" t="n"/>
       <c r="L773" s="8" t="n"/>
-      <c r="M773" s="8" t="n"/>
+      <c r="M773" s="35" t="n">
+        <v>418</v>
+      </c>
       <c r="N773" s="8" t="n"/>
     </row>
     <row r="774">
@@ -30436,7 +31338,9 @@
       <c r="J774" s="8" t="n"/>
       <c r="K774" s="8" t="n"/>
       <c r="L774" s="8" t="n"/>
-      <c r="M774" s="8" t="n"/>
+      <c r="M774" s="35" t="n">
+        <v>564</v>
+      </c>
       <c r="N774" s="8" t="n"/>
     </row>
     <row r="775">
@@ -30470,7 +31374,9 @@
       <c r="J775" s="8" t="n"/>
       <c r="K775" s="8" t="n"/>
       <c r="L775" s="18" t="n"/>
-      <c r="M775" s="8" t="n"/>
+      <c r="M775" s="35" t="n">
+        <v>1795</v>
+      </c>
       <c r="N775" s="8" t="n"/>
     </row>
     <row r="776">
@@ -30504,7 +31410,9 @@
       <c r="J776" s="8" t="n"/>
       <c r="K776" s="8" t="n"/>
       <c r="L776" s="8" t="n"/>
-      <c r="M776" s="8" t="n"/>
+      <c r="M776" s="35" t="n">
+        <v>1265</v>
+      </c>
       <c r="N776" s="8" t="n"/>
     </row>
     <row r="777">
@@ -30538,7 +31446,9 @@
       <c r="J777" s="8" t="n"/>
       <c r="K777" s="8" t="n"/>
       <c r="L777" s="8" t="n"/>
-      <c r="M777" s="8" t="n"/>
+      <c r="M777" s="35" t="n">
+        <v>3781</v>
+      </c>
       <c r="N777" s="8" t="n"/>
     </row>
     <row r="778">
@@ -30572,7 +31482,9 @@
       <c r="J778" s="8" t="n"/>
       <c r="K778" s="8" t="n"/>
       <c r="L778" s="8" t="n"/>
-      <c r="M778" s="8" t="n"/>
+      <c r="M778" s="35" t="n">
+        <v>5623</v>
+      </c>
       <c r="N778" s="8" t="n"/>
     </row>
     <row r="779">
@@ -30606,7 +31518,9 @@
       <c r="J779" s="8" t="n"/>
       <c r="K779" s="8" t="n"/>
       <c r="L779" s="8" t="n"/>
-      <c r="M779" s="8" t="n"/>
+      <c r="M779" s="35" t="n">
+        <v>3102</v>
+      </c>
       <c r="N779" s="8" t="n"/>
     </row>
     <row r="780">
@@ -30640,7 +31554,9 @@
       <c r="J780" s="8" t="n"/>
       <c r="K780" s="8" t="n"/>
       <c r="L780" s="8" t="n"/>
-      <c r="M780" s="8" t="n"/>
+      <c r="M780" s="35" t="n">
+        <v>1200</v>
+      </c>
       <c r="N780" s="8" t="n"/>
     </row>
     <row r="781">
@@ -30674,7 +31590,9 @@
       <c r="J781" s="8" t="n"/>
       <c r="K781" s="8" t="n"/>
       <c r="L781" s="8" t="n"/>
-      <c r="M781" s="8" t="n"/>
+      <c r="M781" s="35" t="n">
+        <v>481</v>
+      </c>
       <c r="N781" s="8" t="n"/>
     </row>
     <row r="782">
@@ -30708,7 +31626,9 @@
       <c r="J782" s="8" t="n"/>
       <c r="K782" s="8" t="n"/>
       <c r="L782" s="8" t="n"/>
-      <c r="M782" s="8" t="n"/>
+      <c r="M782" s="35" t="n">
+        <v>672</v>
+      </c>
       <c r="N782" s="8" t="n"/>
     </row>
     <row r="783">
@@ -30742,7 +31662,9 @@
       <c r="J783" s="8" t="n"/>
       <c r="K783" s="8" t="n"/>
       <c r="L783" s="8" t="n"/>
-      <c r="M783" s="8" t="n"/>
+      <c r="M783" s="35" t="n">
+        <v>1220</v>
+      </c>
       <c r="N783" s="8" t="n"/>
     </row>
     <row r="784">
@@ -30776,7 +31698,9 @@
       <c r="J784" s="8" t="n"/>
       <c r="K784" s="8" t="n"/>
       <c r="L784" s="8" t="n"/>
-      <c r="M784" s="8" t="n"/>
+      <c r="M784" s="35" t="n">
+        <v>4801</v>
+      </c>
       <c r="N784" s="8" t="n"/>
     </row>
     <row r="785">
@@ -30810,7 +31734,9 @@
       <c r="J785" s="8" t="n"/>
       <c r="K785" s="8" t="n"/>
       <c r="L785" s="8" t="n"/>
-      <c r="M785" s="8" t="n"/>
+      <c r="M785" s="35" t="n">
+        <v>3571</v>
+      </c>
       <c r="N785" s="8" t="n"/>
     </row>
     <row r="786">
@@ -30844,7 +31770,9 @@
       <c r="J786" s="8" t="n"/>
       <c r="K786" s="8" t="n"/>
       <c r="L786" s="8" t="n"/>
-      <c r="M786" s="8" t="n"/>
+      <c r="M786" s="35" t="n">
+        <v>413</v>
+      </c>
       <c r="N786" s="8" t="n"/>
     </row>
     <row r="787">
@@ -30878,7 +31806,9 @@
       <c r="J787" s="8" t="n"/>
       <c r="K787" s="8" t="n"/>
       <c r="L787" s="8" t="n"/>
-      <c r="M787" s="8" t="n"/>
+      <c r="M787" s="35" t="n">
+        <v>2621</v>
+      </c>
       <c r="N787" s="8" t="n"/>
     </row>
     <row r="788">
@@ -30912,7 +31842,9 @@
       <c r="J788" s="8" t="n"/>
       <c r="K788" s="8" t="n"/>
       <c r="L788" s="8" t="n"/>
-      <c r="M788" s="8" t="n"/>
+      <c r="M788" s="35" t="n">
+        <v>830</v>
+      </c>
       <c r="N788" s="8" t="n"/>
     </row>
     <row r="789">
@@ -30946,7 +31878,9 @@
       <c r="J789" s="8" t="n"/>
       <c r="K789" s="8" t="n"/>
       <c r="L789" s="8" t="n"/>
-      <c r="M789" s="8" t="n"/>
+      <c r="M789" s="35" t="n">
+        <v>1714</v>
+      </c>
       <c r="N789" s="8" t="n"/>
     </row>
     <row r="790">
@@ -30980,7 +31914,9 @@
       <c r="J790" s="8" t="n"/>
       <c r="K790" s="8" t="n"/>
       <c r="L790" s="8" t="n"/>
-      <c r="M790" s="8" t="n"/>
+      <c r="M790" s="35" t="n">
+        <v>549</v>
+      </c>
       <c r="N790" s="8" t="n"/>
     </row>
     <row r="791">
@@ -31014,7 +31950,9 @@
       <c r="J791" s="8" t="n"/>
       <c r="K791" s="8" t="n"/>
       <c r="L791" s="8" t="n"/>
-      <c r="M791" s="8" t="n"/>
+      <c r="M791" s="35" t="n">
+        <v>189</v>
+      </c>
       <c r="N791" s="8" t="n"/>
     </row>
     <row r="792">
@@ -31048,7 +31986,9 @@
       <c r="J792" s="8" t="n"/>
       <c r="K792" s="8" t="n"/>
       <c r="L792" s="8" t="n"/>
-      <c r="M792" s="8" t="n"/>
+      <c r="M792" s="35" t="n">
+        <v>782</v>
+      </c>
       <c r="N792" s="8" t="n"/>
     </row>
     <row r="793">
@@ -31130,7 +32070,9 @@
       <c r="J794" s="8" t="n"/>
       <c r="K794" s="8" t="n"/>
       <c r="L794" s="8" t="n"/>
-      <c r="M794" s="8" t="n"/>
+      <c r="M794" s="35" t="n">
+        <v>3074</v>
+      </c>
       <c r="N794" s="8" t="n"/>
     </row>
     <row r="795">
@@ -31164,7 +32106,9 @@
       <c r="J795" s="8" t="n"/>
       <c r="K795" s="8" t="n"/>
       <c r="L795" s="8" t="n"/>
-      <c r="M795" s="8" t="n"/>
+      <c r="M795" s="35" t="n">
+        <v>1404</v>
+      </c>
       <c r="N795" s="8" t="n"/>
     </row>
     <row r="796">
@@ -31198,7 +32142,9 @@
       <c r="J796" s="8" t="n"/>
       <c r="K796" s="8" t="n"/>
       <c r="L796" s="8" t="n"/>
-      <c r="M796" s="8" t="n"/>
+      <c r="M796" s="35" t="n">
+        <v>7336</v>
+      </c>
       <c r="N796" s="8" t="n"/>
     </row>
     <row r="797">
@@ -31232,7 +32178,9 @@
       <c r="J797" s="8" t="n"/>
       <c r="K797" s="8" t="n"/>
       <c r="L797" s="8" t="n"/>
-      <c r="M797" s="8" t="n"/>
+      <c r="M797" s="35" t="n">
+        <v>146</v>
+      </c>
       <c r="N797" s="8" t="n"/>
     </row>
     <row r="798">
@@ -31308,7 +32256,9 @@
       <c r="J799" s="8" t="n"/>
       <c r="K799" s="8" t="n"/>
       <c r="L799" s="8" t="n"/>
-      <c r="M799" s="8" t="n"/>
+      <c r="M799" s="35" t="n">
+        <v>1108</v>
+      </c>
       <c r="N799" s="8" t="n"/>
     </row>
     <row r="800">
@@ -31342,7 +32292,9 @@
       <c r="J800" s="8" t="n"/>
       <c r="K800" s="8" t="n"/>
       <c r="L800" s="8" t="n"/>
-      <c r="M800" s="8" t="n"/>
+      <c r="M800" s="35" t="n">
+        <v>2547</v>
+      </c>
       <c r="N800" s="8" t="n"/>
     </row>
     <row r="801">
@@ -31376,7 +32328,9 @@
       <c r="J801" s="8" t="n"/>
       <c r="K801" s="8" t="n"/>
       <c r="L801" s="18" t="n"/>
-      <c r="M801" s="8" t="n"/>
+      <c r="M801" s="35" t="n">
+        <v>637</v>
+      </c>
       <c r="N801" s="8" t="n"/>
     </row>
     <row r="802">
@@ -31410,7 +32364,9 @@
       <c r="J802" s="8" t="n"/>
       <c r="K802" s="8" t="n"/>
       <c r="L802" s="18" t="n"/>
-      <c r="M802" s="8" t="n"/>
+      <c r="M802" s="35" t="n">
+        <v>1645</v>
+      </c>
       <c r="N802" s="8" t="n"/>
     </row>
     <row r="803">
@@ -31444,7 +32400,9 @@
       <c r="J803" s="8" t="n"/>
       <c r="K803" s="8" t="n"/>
       <c r="L803" s="18" t="n"/>
-      <c r="M803" s="8" t="n"/>
+      <c r="M803" s="35" t="n">
+        <v>3790</v>
+      </c>
       <c r="N803" s="8" t="n"/>
     </row>
     <row r="804">
@@ -31478,7 +32436,9 @@
       <c r="J804" s="8" t="n"/>
       <c r="K804" s="8" t="n"/>
       <c r="L804" s="8" t="n"/>
-      <c r="M804" s="8" t="n"/>
+      <c r="M804" s="35" t="n">
+        <v>574</v>
+      </c>
       <c r="N804" s="8" t="n"/>
     </row>
     <row r="805">
@@ -31512,7 +32472,9 @@
       <c r="J805" s="8" t="n"/>
       <c r="K805" s="8" t="n"/>
       <c r="L805" s="8" t="n"/>
-      <c r="M805" s="8" t="n"/>
+      <c r="M805" s="35" t="n">
+        <v>5277</v>
+      </c>
       <c r="N805" s="8" t="n"/>
     </row>
     <row r="806">
@@ -31546,7 +32508,9 @@
       <c r="J806" s="8" t="n"/>
       <c r="K806" s="8" t="n"/>
       <c r="L806" s="8" t="n"/>
-      <c r="M806" s="8" t="n"/>
+      <c r="M806" s="35" t="n">
+        <v>2918</v>
+      </c>
       <c r="N806" s="8" t="n"/>
     </row>
     <row r="807">
@@ -31580,7 +32544,9 @@
       <c r="J807" s="8" t="n"/>
       <c r="K807" s="8" t="n"/>
       <c r="L807" s="8" t="n"/>
-      <c r="M807" s="8" t="n"/>
+      <c r="M807" s="35" t="n">
+        <v>6925</v>
+      </c>
       <c r="N807" s="8" t="n"/>
     </row>
     <row r="808">
@@ -31614,7 +32580,9 @@
       <c r="J808" s="8" t="n"/>
       <c r="K808" s="8" t="n"/>
       <c r="L808" s="18" t="n"/>
-      <c r="M808" s="8" t="n"/>
+      <c r="M808" s="35" t="n">
+        <v>2969</v>
+      </c>
       <c r="N808" s="8" t="n"/>
     </row>
     <row r="809">
@@ -31648,7 +32616,9 @@
       <c r="J809" s="8" t="n"/>
       <c r="K809" s="8" t="n"/>
       <c r="L809" s="8" t="n"/>
-      <c r="M809" s="8" t="n"/>
+      <c r="M809" s="35" t="n">
+        <v>242</v>
+      </c>
       <c r="N809" s="8" t="n"/>
     </row>
     <row r="810">
@@ -31682,7 +32652,9 @@
       <c r="J810" s="8" t="n"/>
       <c r="K810" s="8" t="n"/>
       <c r="L810" s="8" t="n"/>
-      <c r="M810" s="8" t="n"/>
+      <c r="M810" s="35" t="n">
+        <v>989</v>
+      </c>
       <c r="N810" s="8" t="n"/>
     </row>
     <row r="811">
@@ -31764,7 +32736,9 @@
       <c r="J812" s="8" t="n"/>
       <c r="K812" s="8" t="n"/>
       <c r="L812" s="8" t="n"/>
-      <c r="M812" s="8" t="n"/>
+      <c r="M812" s="35" t="n">
+        <v>1908</v>
+      </c>
       <c r="N812" s="8" t="n"/>
     </row>
     <row r="813">
@@ -31798,7 +32772,9 @@
       <c r="J813" s="8" t="n"/>
       <c r="K813" s="8" t="n"/>
       <c r="L813" s="8" t="n"/>
-      <c r="M813" s="8" t="n"/>
+      <c r="M813" s="35" t="n">
+        <v>1015</v>
+      </c>
       <c r="N813" s="8" t="n"/>
     </row>
     <row r="814">
@@ -31832,7 +32808,9 @@
       <c r="J814" s="8" t="n"/>
       <c r="K814" s="8" t="n"/>
       <c r="L814" s="8" t="n"/>
-      <c r="M814" s="8" t="n"/>
+      <c r="M814" s="35" t="n">
+        <v>1590</v>
+      </c>
       <c r="N814" s="8" t="n"/>
     </row>
     <row r="815">
@@ -31866,7 +32844,9 @@
       <c r="J815" s="8" t="n"/>
       <c r="K815" s="8" t="n"/>
       <c r="L815" s="8" t="n"/>
-      <c r="M815" s="8" t="n"/>
+      <c r="M815" s="35" t="n">
+        <v>925</v>
+      </c>
       <c r="N815" s="8" t="n"/>
     </row>
     <row r="816">
@@ -31900,7 +32880,9 @@
       <c r="J816" s="8" t="n"/>
       <c r="K816" s="8" t="n"/>
       <c r="L816" s="8" t="n"/>
-      <c r="M816" s="8" t="n"/>
+      <c r="M816" s="35" t="n">
+        <v>2653</v>
+      </c>
       <c r="N816" s="8" t="n"/>
     </row>
     <row r="817">
@@ -31934,7 +32916,9 @@
       <c r="J817" s="8" t="n"/>
       <c r="K817" s="8" t="n"/>
       <c r="L817" s="8" t="n"/>
-      <c r="M817" s="8" t="n"/>
+      <c r="M817" s="35" t="n">
+        <v>141</v>
+      </c>
       <c r="N817" s="8" t="n"/>
     </row>
     <row r="818">
@@ -31968,7 +32952,9 @@
       <c r="J818" s="8" t="n"/>
       <c r="K818" s="8" t="n"/>
       <c r="L818" s="8" t="n"/>
-      <c r="M818" s="8" t="n"/>
+      <c r="M818" s="35" t="n">
+        <v>3563</v>
+      </c>
       <c r="N818" s="8" t="n"/>
     </row>
     <row r="819">
@@ -32002,7 +32988,9 @@
       <c r="J819" s="8" t="n"/>
       <c r="K819" s="8" t="n"/>
       <c r="L819" s="8" t="n"/>
-      <c r="M819" s="8" t="n"/>
+      <c r="M819" s="35" t="n">
+        <v>134</v>
+      </c>
       <c r="N819" s="8" t="n"/>
     </row>
     <row r="820">
@@ -32036,7 +33024,9 @@
       <c r="J820" s="8" t="n"/>
       <c r="K820" s="8" t="n"/>
       <c r="L820" s="8" t="n"/>
-      <c r="M820" s="8" t="n"/>
+      <c r="M820" s="35" t="n">
+        <v>331</v>
+      </c>
       <c r="N820" s="8" t="n"/>
     </row>
     <row r="821">
@@ -32070,7 +33060,9 @@
       <c r="J821" s="8" t="n"/>
       <c r="K821" s="8" t="n"/>
       <c r="L821" s="8" t="n"/>
-      <c r="M821" s="8" t="n"/>
+      <c r="M821" s="35" t="n">
+        <v>217</v>
+      </c>
       <c r="N821" s="8" t="n"/>
     </row>
     <row r="822">
@@ -32104,7 +33096,9 @@
       <c r="J822" s="8" t="n"/>
       <c r="K822" s="8" t="n"/>
       <c r="L822" s="8" t="n"/>
-      <c r="M822" s="8" t="n"/>
+      <c r="M822" s="35" t="n">
+        <v>566</v>
+      </c>
       <c r="N822" s="8" t="n"/>
     </row>
     <row r="823">
@@ -32138,7 +33132,9 @@
       <c r="J823" s="8" t="n"/>
       <c r="K823" s="8" t="n"/>
       <c r="L823" s="8" t="n"/>
-      <c r="M823" s="8" t="n"/>
+      <c r="M823" s="35" t="n">
+        <v>2896</v>
+      </c>
       <c r="N823" s="8" t="n"/>
     </row>
     <row r="824">
@@ -32220,7 +33216,9 @@
       <c r="J825" s="8" t="n"/>
       <c r="K825" s="8" t="n"/>
       <c r="L825" s="8" t="n"/>
-      <c r="M825" s="8" t="n"/>
+      <c r="M825" s="35" t="n">
+        <v>174</v>
+      </c>
       <c r="N825" s="8" t="n"/>
     </row>
     <row r="826">
@@ -32254,7 +33252,9 @@
       <c r="J826" s="8" t="n"/>
       <c r="K826" s="8" t="n"/>
       <c r="L826" s="8" t="n"/>
-      <c r="M826" s="8" t="n"/>
+      <c r="M826" s="35" t="n">
+        <v>1042</v>
+      </c>
       <c r="N826" s="8" t="n"/>
     </row>
     <row r="827">
@@ -32288,7 +33288,9 @@
       <c r="J827" s="8" t="n"/>
       <c r="K827" s="8" t="n"/>
       <c r="L827" s="8" t="n"/>
-      <c r="M827" s="8" t="n"/>
+      <c r="M827" s="35" t="n">
+        <v>1296</v>
+      </c>
       <c r="N827" s="8" t="n"/>
     </row>
     <row r="828">
@@ -32322,7 +33324,9 @@
       <c r="J828" s="8" t="n"/>
       <c r="K828" s="8" t="n"/>
       <c r="L828" s="8" t="n"/>
-      <c r="M828" s="8" t="n"/>
+      <c r="M828" s="35" t="n">
+        <v>167</v>
+      </c>
       <c r="N828" s="8" t="n"/>
     </row>
     <row r="829">
@@ -32356,7 +33360,9 @@
       <c r="J829" s="8" t="n"/>
       <c r="K829" s="8" t="n"/>
       <c r="L829" s="8" t="n"/>
-      <c r="M829" s="8" t="n"/>
+      <c r="M829" s="35" t="n">
+        <v>962</v>
+      </c>
       <c r="N829" s="8" t="n"/>
     </row>
     <row r="830">
@@ -32390,7 +33396,9 @@
       <c r="J830" s="8" t="n"/>
       <c r="K830" s="8" t="n"/>
       <c r="L830" s="8" t="n"/>
-      <c r="M830" s="8" t="n"/>
+      <c r="M830" s="35" t="n">
+        <v>1636</v>
+      </c>
       <c r="N830" s="8" t="n"/>
     </row>
     <row r="831">
@@ -32424,7 +33432,9 @@
       <c r="J831" s="8" t="n"/>
       <c r="K831" s="8" t="n"/>
       <c r="L831" s="8" t="n"/>
-      <c r="M831" s="8" t="n"/>
+      <c r="M831" s="35" t="n">
+        <v>192</v>
+      </c>
       <c r="N831" s="8" t="n"/>
     </row>
     <row r="832">
@@ -32458,7 +33468,9 @@
       <c r="J832" s="8" t="n"/>
       <c r="K832" s="8" t="n"/>
       <c r="L832" s="8" t="n"/>
-      <c r="M832" s="8" t="n"/>
+      <c r="M832" s="35" t="n">
+        <v>723</v>
+      </c>
       <c r="N832" s="8" t="n"/>
     </row>
     <row r="833">
@@ -32492,7 +33504,9 @@
       <c r="J833" s="8" t="n"/>
       <c r="K833" s="8" t="n"/>
       <c r="L833" s="18" t="n"/>
-      <c r="M833" s="8" t="n"/>
+      <c r="M833" s="35" t="n">
+        <v>859</v>
+      </c>
       <c r="N833" s="8" t="n"/>
     </row>
     <row r="834">
@@ -32526,7 +33540,9 @@
       <c r="J834" s="8" t="n"/>
       <c r="K834" s="8" t="n"/>
       <c r="L834" s="19" t="n"/>
-      <c r="M834" s="8" t="n"/>
+      <c r="M834" s="35" t="n">
+        <v>590</v>
+      </c>
       <c r="N834" s="8" t="n"/>
     </row>
     <row r="835">
@@ -32560,7 +33576,9 @@
       <c r="J835" s="8" t="n"/>
       <c r="K835" s="8" t="n"/>
       <c r="L835" s="19" t="n"/>
-      <c r="M835" s="8" t="n"/>
+      <c r="M835" s="35" t="n">
+        <v>1097</v>
+      </c>
       <c r="N835" s="8" t="n"/>
     </row>
     <row r="836">
@@ -32594,7 +33612,9 @@
       <c r="J836" s="8" t="n"/>
       <c r="K836" s="8" t="n"/>
       <c r="L836" s="8" t="n"/>
-      <c r="M836" s="8" t="n"/>
+      <c r="M836" s="35" t="n">
+        <v>539</v>
+      </c>
       <c r="N836" s="8" t="n"/>
     </row>
     <row r="837">
@@ -32628,7 +33648,9 @@
       <c r="J837" s="8" t="n"/>
       <c r="K837" s="8" t="n"/>
       <c r="L837" s="8" t="n"/>
-      <c r="M837" s="8" t="n"/>
+      <c r="M837" s="35" t="n">
+        <v>1171</v>
+      </c>
       <c r="N837" s="8" t="n"/>
     </row>
     <row r="838">
@@ -32662,7 +33684,9 @@
       <c r="J838" s="8" t="n"/>
       <c r="K838" s="8" t="n"/>
       <c r="L838" s="8" t="n"/>
-      <c r="M838" s="8" t="n"/>
+      <c r="M838" s="35" t="n">
+        <v>147</v>
+      </c>
       <c r="N838" s="8" t="n"/>
     </row>
     <row r="839">
@@ -32696,7 +33720,9 @@
       <c r="J839" s="8" t="n"/>
       <c r="K839" s="8" t="n"/>
       <c r="L839" s="8" t="n"/>
-      <c r="M839" s="8" t="n"/>
+      <c r="M839" s="35" t="n">
+        <v>1059</v>
+      </c>
       <c r="N839" s="8" t="n"/>
     </row>
     <row r="840">
@@ -32730,7 +33756,9 @@
       <c r="J840" s="8" t="n"/>
       <c r="K840" s="8" t="n"/>
       <c r="L840" s="8" t="n"/>
-      <c r="M840" s="8" t="n"/>
+      <c r="M840" s="35" t="n">
+        <v>1667</v>
+      </c>
       <c r="N840" s="8" t="n"/>
     </row>
     <row r="841">
@@ -32764,7 +33792,9 @@
       <c r="J841" s="8" t="n"/>
       <c r="K841" s="8" t="n"/>
       <c r="L841" s="8" t="n"/>
-      <c r="M841" s="8" t="n"/>
+      <c r="M841" s="35" t="n">
+        <v>4176</v>
+      </c>
       <c r="N841" s="8" t="n"/>
     </row>
     <row r="842">
@@ -32798,7 +33828,9 @@
       <c r="J842" s="8" t="n"/>
       <c r="K842" s="8" t="n"/>
       <c r="L842" s="8" t="n"/>
-      <c r="M842" s="8" t="n"/>
+      <c r="M842" s="35" t="n">
+        <v>1693</v>
+      </c>
       <c r="N842" s="8" t="n"/>
     </row>
     <row r="843">
@@ -32832,7 +33864,9 @@
       <c r="J843" s="8" t="n"/>
       <c r="K843" s="8" t="n"/>
       <c r="L843" s="8" t="n"/>
-      <c r="M843" s="8" t="n"/>
+      <c r="M843" s="35" t="n">
+        <v>1037</v>
+      </c>
       <c r="N843" s="8" t="n"/>
     </row>
     <row r="844">
@@ -32866,7 +33900,9 @@
       <c r="J844" s="8" t="n"/>
       <c r="K844" s="8" t="n"/>
       <c r="L844" s="8" t="n"/>
-      <c r="M844" s="8" t="n"/>
+      <c r="M844" s="35" t="n">
+        <v>6356</v>
+      </c>
       <c r="N844" s="8" t="n"/>
     </row>
     <row r="845">
@@ -32900,7 +33936,9 @@
       <c r="J845" s="8" t="n"/>
       <c r="K845" s="8" t="n"/>
       <c r="L845" s="8" t="n"/>
-      <c r="M845" s="8" t="n"/>
+      <c r="M845" s="35" t="n">
+        <v>460</v>
+      </c>
       <c r="N845" s="8" t="n"/>
     </row>
     <row r="846">
@@ -32934,7 +33972,9 @@
       <c r="J846" s="8" t="n"/>
       <c r="K846" s="8" t="n"/>
       <c r="L846" s="8" t="n"/>
-      <c r="M846" s="8" t="n"/>
+      <c r="M846" s="35" t="n">
+        <v>250</v>
+      </c>
       <c r="N846" s="8" t="n"/>
     </row>
     <row r="847">
@@ -32968,7 +34008,9 @@
       <c r="J847" s="8" t="n"/>
       <c r="K847" s="8" t="n"/>
       <c r="L847" s="8" t="n"/>
-      <c r="M847" s="8" t="n"/>
+      <c r="M847" s="35" t="n">
+        <v>1792</v>
+      </c>
       <c r="N847" s="8" t="n"/>
     </row>
     <row r="848">
@@ -33002,7 +34044,9 @@
       <c r="J848" s="8" t="n"/>
       <c r="K848" s="8" t="n"/>
       <c r="L848" s="19" t="n"/>
-      <c r="M848" s="8" t="n"/>
+      <c r="M848" s="35" t="n">
+        <v>1314</v>
+      </c>
       <c r="N848" s="8" t="n"/>
     </row>
     <row r="849">
@@ -33036,7 +34080,9 @@
       <c r="J849" s="8" t="n"/>
       <c r="K849" s="8" t="n"/>
       <c r="L849" s="8" t="n"/>
-      <c r="M849" s="8" t="n"/>
+      <c r="M849" s="35" t="n">
+        <v>9548</v>
+      </c>
       <c r="N849" s="8" t="n"/>
     </row>
     <row r="850">
@@ -33070,7 +34116,9 @@
       <c r="J850" s="8" t="n"/>
       <c r="K850" s="8" t="n"/>
       <c r="L850" s="8" t="n"/>
-      <c r="M850" s="8" t="n"/>
+      <c r="M850" s="35" t="n">
+        <v>1266</v>
+      </c>
       <c r="N850" s="8" t="n"/>
     </row>
     <row r="851">
@@ -33104,7 +34152,9 @@
       <c r="J851" s="8" t="n"/>
       <c r="K851" s="8" t="n"/>
       <c r="L851" s="8" t="n"/>
-      <c r="M851" s="8" t="n"/>
+      <c r="M851" s="35" t="n">
+        <v>7770</v>
+      </c>
       <c r="N851" s="8" t="n"/>
     </row>
     <row r="852">
@@ -38592,14 +39642,14 @@
       <c r="N1029" s="12" t="n"/>
     </row>
     <row r="1030" ht="15" customHeight="1" thickBot="1">
-      <c r="A1030" s="39" t="inlineStr">
+      <c r="A1030" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B1030" s="40" t="n"/>
-      <c r="C1030" s="40" t="n"/>
-      <c r="D1030" s="41" t="n"/>
+      <c r="B1030" s="42" t="n"/>
+      <c r="C1030" s="42" t="n"/>
+      <c r="D1030" s="43" t="n"/>
       <c r="E1030" s="23">
         <f>SUM(E852:E1029)</f>
         <v/>

--- a/System_Puchase.xlsx
+++ b/System_Puchase.xlsx
@@ -43,7 +43,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
         <bgColor rgb="00FFD966"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -282,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
@@ -332,12 +326,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1400,9 +1393,7 @@
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
-      <c r="M13" s="35" t="n">
-        <v>3746</v>
-      </c>
+      <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n"/>
     </row>
     <row r="14">
@@ -1572,9 +1563,7 @@
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
-      <c r="M17" s="35" t="n">
-        <v>3417</v>
-      </c>
+      <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n"/>
     </row>
     <row r="18">
@@ -1608,9 +1597,7 @@
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
-      <c r="M18" s="35" t="n">
-        <v>1550</v>
-      </c>
+      <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n"/>
     </row>
     <row r="19">
@@ -1644,9 +1631,7 @@
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
-      <c r="M19" s="35" t="n">
-        <v>2298</v>
-      </c>
+      <c r="M19" s="8" t="n"/>
       <c r="N19" s="8" t="n"/>
     </row>
     <row r="20">
@@ -1860,9 +1845,7 @@
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
-      <c r="M24" s="35" t="n">
-        <v>3721</v>
-      </c>
+      <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
     </row>
     <row r="25">
@@ -1896,9 +1879,7 @@
       <c r="J25" s="8" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
-      <c r="M25" s="35" t="n">
-        <v>11835</v>
-      </c>
+      <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n"/>
     </row>
     <row r="26">
@@ -1926,21 +1907,21 @@
       <c r="F26" s="12" t="n">
         <v>3567</v>
       </c>
-      <c r="G26" s="36" t="n">
+      <c r="G26" s="35" t="n">
         <v>45868</v>
       </c>
-      <c r="H26" s="36" t="inlineStr">
+      <c r="H26" s="35" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I26" s="37" t="inlineStr">
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
       </c>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="38" t="n">
+      <c r="K26" s="37" t="n">
         <v>3567</v>
       </c>
       <c r="L26" s="12" t="n"/>
@@ -1985,7 +1966,7 @@
           <t>002562</t>
         </is>
       </c>
-      <c r="J27" s="39" t="n">
+      <c r="J27" s="38" t="n">
         <v>9492</v>
       </c>
       <c r="K27" s="29" t="n">
@@ -2026,9 +2007,7 @@
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
-      <c r="M28" s="35" t="n">
-        <v>4074</v>
-      </c>
+      <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n"/>
     </row>
     <row r="29">
@@ -2110,9 +2089,7 @@
       <c r="J30" s="8" t="n"/>
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="n"/>
-      <c r="M30" s="35" t="n">
-        <v>3309</v>
-      </c>
+      <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n"/>
     </row>
     <row r="31">
@@ -2146,9 +2123,7 @@
       <c r="J31" s="8" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="8" t="n"/>
-      <c r="M31" s="35" t="n">
-        <v>170</v>
-      </c>
+      <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
     </row>
     <row r="32">
@@ -3316,9 +3291,7 @@
       <c r="J58" s="8" t="n"/>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
-      <c r="M58" s="35" t="n">
-        <v>4166</v>
-      </c>
+      <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n"/>
     </row>
     <row r="59">
@@ -3352,9 +3325,7 @@
       <c r="J59" s="8" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
-      <c r="M59" s="35" t="n">
-        <v>6665</v>
-      </c>
+      <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n"/>
     </row>
     <row r="60">
@@ -3388,9 +3359,7 @@
       <c r="J60" s="8" t="n"/>
       <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
-      <c r="M60" s="35" t="n">
-        <v>5628</v>
-      </c>
+      <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n"/>
     </row>
     <row r="61">
@@ -3424,9 +3393,7 @@
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
-      <c r="M61" s="35" t="n">
-        <v>4336</v>
-      </c>
+      <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n"/>
     </row>
     <row r="62">
@@ -3460,9 +3427,7 @@
       <c r="J62" s="8" t="n"/>
       <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
-      <c r="M62" s="35" t="n">
-        <v>2105</v>
-      </c>
+      <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n"/>
     </row>
     <row r="63">
@@ -3584,9 +3549,7 @@
       <c r="J65" s="8" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
-      <c r="M65" s="35" t="n">
-        <v>2937</v>
-      </c>
+      <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n"/>
     </row>
     <row r="66">
@@ -3620,9 +3583,7 @@
       <c r="J66" s="8" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
-      <c r="M66" s="35" t="n">
-        <v>9091</v>
-      </c>
+      <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n"/>
     </row>
     <row r="67">
@@ -3748,9 +3709,7 @@
       <c r="J69" s="8" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
-      <c r="M69" s="35" t="n">
-        <v>3604</v>
-      </c>
+      <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n"/>
     </row>
     <row r="70">
@@ -3784,9 +3743,7 @@
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
-      <c r="M70" s="35" t="n">
-        <v>1102</v>
-      </c>
+      <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n"/>
     </row>
     <row r="71">
@@ -4030,9 +3987,7 @@
       <c r="J76" s="8" t="n"/>
       <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
-      <c r="M76" s="35" t="n">
-        <v>20026</v>
-      </c>
+      <c r="M76" s="8" t="n"/>
       <c r="N76" s="8" t="n"/>
     </row>
     <row r="77">
@@ -4112,9 +4067,7 @@
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
-      <c r="M78" s="35" t="n">
-        <v>2221</v>
-      </c>
+      <c r="M78" s="8" t="n"/>
       <c r="N78" s="8" t="n"/>
     </row>
     <row r="79">
@@ -4148,9 +4101,7 @@
       <c r="J79" s="8" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
-      <c r="M79" s="35" t="n">
-        <v>5450</v>
-      </c>
+      <c r="M79" s="8" t="n"/>
       <c r="N79" s="8" t="n"/>
     </row>
     <row r="80">
@@ -4276,9 +4227,7 @@
       <c r="J82" s="8" t="n"/>
       <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
-      <c r="M82" s="35" t="n">
-        <v>1296</v>
-      </c>
+      <c r="M82" s="8" t="n"/>
       <c r="N82" s="8" t="n"/>
     </row>
     <row r="83">
@@ -4312,9 +4261,7 @@
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
-      <c r="M83" s="35" t="n">
-        <v>992</v>
-      </c>
+      <c r="M83" s="8" t="n"/>
       <c r="N83" s="8" t="n"/>
     </row>
     <row r="84">
@@ -4394,9 +4341,7 @@
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
-      <c r="M85" s="35" t="n">
-        <v>5040</v>
-      </c>
+      <c r="M85" s="8" t="n"/>
       <c r="N85" s="8" t="n"/>
     </row>
     <row r="86">
@@ -4430,9 +4375,7 @@
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
-      <c r="M86" s="35" t="n">
-        <v>1260</v>
-      </c>
+      <c r="M86" s="8" t="n"/>
       <c r="N86" s="8" t="n"/>
     </row>
     <row r="87">
@@ -4728,9 +4671,7 @@
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
-      <c r="M93" s="35" t="n">
-        <v>1557</v>
-      </c>
+      <c r="M93" s="8" t="n"/>
       <c r="N93" s="8" t="n"/>
     </row>
     <row r="94">
@@ -4764,9 +4705,7 @@
       <c r="J94" s="8" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
-      <c r="M94" s="35" t="n">
-        <v>2305</v>
-      </c>
+      <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n"/>
     </row>
     <row r="95">
@@ -4800,9 +4739,7 @@
       <c r="J95" s="8" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
-      <c r="M95" s="35" t="n">
-        <v>964</v>
-      </c>
+      <c r="M95" s="8" t="n"/>
       <c r="N95" s="8" t="n"/>
     </row>
     <row r="96">
@@ -5186,9 +5123,7 @@
       <c r="J104" s="8" t="n"/>
       <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
-      <c r="M104" s="35" t="n">
-        <v>1630</v>
-      </c>
+      <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n"/>
     </row>
     <row r="105">
@@ -5314,9 +5249,7 @@
       <c r="J107" s="8" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
-      <c r="M107" s="35" t="n">
-        <v>1370</v>
-      </c>
+      <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n"/>
     </row>
     <row r="108">
@@ -5442,9 +5375,7 @@
       <c r="J110" s="8" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
-      <c r="M110" s="35" t="n">
-        <v>624</v>
-      </c>
+      <c r="M110" s="8" t="n"/>
       <c r="N110" s="8" t="n"/>
     </row>
     <row r="111">
@@ -5826,9 +5757,7 @@
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
-      <c r="M119" s="35" t="n">
-        <v>4115</v>
-      </c>
+      <c r="M119" s="8" t="n"/>
       <c r="N119" s="8" t="n"/>
     </row>
     <row r="120">
@@ -5908,9 +5837,7 @@
       <c r="J121" s="8" t="n"/>
       <c r="K121" s="8" t="n"/>
       <c r="L121" s="8" t="n"/>
-      <c r="M121" s="35" t="n">
-        <v>4522</v>
-      </c>
+      <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n"/>
     </row>
     <row r="122">
@@ -5944,9 +5871,7 @@
       <c r="J122" s="8" t="n"/>
       <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
-      <c r="M122" s="35" t="n">
-        <v>708</v>
-      </c>
+      <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n"/>
     </row>
     <row r="123">
@@ -5980,9 +5905,7 @@
       <c r="J123" s="8" t="n"/>
       <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
-      <c r="M123" s="35" t="n">
-        <v>149</v>
-      </c>
+      <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n"/>
     </row>
     <row r="124">
@@ -6016,9 +5939,7 @@
       <c r="J124" s="8" t="n"/>
       <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
-      <c r="M124" s="35" t="n">
-        <v>1775</v>
-      </c>
+      <c r="M124" s="8" t="n"/>
       <c r="N124" s="8" t="n"/>
     </row>
     <row r="125">
@@ -6052,9 +5973,7 @@
       <c r="J125" s="8" t="n"/>
       <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
-      <c r="M125" s="35" t="n">
-        <v>744</v>
-      </c>
+      <c r="M125" s="8" t="n"/>
       <c r="N125" s="8" t="n"/>
     </row>
     <row r="126">
@@ -6088,9 +6007,7 @@
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
-      <c r="M126" s="35" t="n">
-        <v>1053</v>
-      </c>
+      <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n"/>
     </row>
     <row r="127">
@@ -6124,9 +6041,7 @@
       <c r="J127" s="8" t="n"/>
       <c r="K127" s="8" t="n"/>
       <c r="L127" s="8" t="n"/>
-      <c r="M127" s="35" t="n">
-        <v>138</v>
-      </c>
+      <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n"/>
     </row>
     <row r="128">
@@ -6160,9 +6075,7 @@
       <c r="J128" s="8" t="n"/>
       <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
-      <c r="M128" s="35" t="n">
-        <v>2503</v>
-      </c>
+      <c r="M128" s="8" t="n"/>
       <c r="N128" s="8" t="n"/>
     </row>
     <row r="129">
@@ -6502,9 +6415,7 @@
       <c r="J136" s="8" t="n"/>
       <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
-      <c r="M136" s="35" t="n">
-        <v>1594</v>
-      </c>
+      <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n"/>
     </row>
     <row r="137">
@@ -6533,7 +6444,7 @@
         <v>5071</v>
       </c>
       <c r="G137" s="31" t="n">
-        <v>45828</v>
+        <v>45899</v>
       </c>
       <c r="H137" s="31" t="inlineStr">
         <is>
@@ -6542,14 +6453,12 @@
       </c>
       <c r="I137" s="32" t="inlineStr">
         <is>
-          <t>002384</t>
-        </is>
-      </c>
-      <c r="J137" s="33" t="n">
-        <v>25000</v>
-      </c>
+          <t>002585</t>
+        </is>
+      </c>
+      <c r="J137" s="8" t="n"/>
       <c r="K137" s="34" t="n">
-        <v>272</v>
+        <v>5071</v>
       </c>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
@@ -6586,9 +6495,7 @@
       <c r="J138" s="8" t="n"/>
       <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
-      <c r="M138" s="35" t="n">
-        <v>1242</v>
-      </c>
+      <c r="M138" s="8" t="n"/>
       <c r="N138" s="8" t="n"/>
     </row>
     <row r="139">
@@ -6751,23 +6658,17 @@
         <v>1752</v>
       </c>
       <c r="G142" s="30" t="n">
-        <v>45828</v>
+        <v>45822</v>
       </c>
       <c r="H142" s="32" t="inlineStr">
         <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I142" s="32" t="inlineStr">
-        <is>
-          <t>002384</t>
-        </is>
-      </c>
-      <c r="J142" s="33" t="n">
-        <v>25000</v>
-      </c>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I142" s="32" t="inlineStr"/>
+      <c r="J142" s="8" t="n"/>
       <c r="K142" s="34" t="n">
-        <v>6593</v>
+        <v>1752</v>
       </c>
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
@@ -7152,9 +7053,7 @@
       <c r="J151" s="8" t="n"/>
       <c r="K151" s="8" t="n"/>
       <c r="L151" s="8" t="n"/>
-      <c r="M151" s="35" t="n">
-        <v>420</v>
-      </c>
+      <c r="M151" s="8" t="n"/>
       <c r="N151" s="8" t="n"/>
     </row>
     <row r="152">
@@ -7234,9 +7133,7 @@
       <c r="J153" s="8" t="n"/>
       <c r="K153" s="8" t="n"/>
       <c r="L153" s="8" t="n"/>
-      <c r="M153" s="35" t="n">
-        <v>2645</v>
-      </c>
+      <c r="M153" s="8" t="n"/>
       <c r="N153" s="8" t="n"/>
     </row>
     <row r="154">
@@ -7270,9 +7167,7 @@
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
-      <c r="M154" s="35" t="n">
-        <v>2937</v>
-      </c>
+      <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n"/>
     </row>
     <row r="155">
@@ -7608,9 +7503,7 @@
       <c r="J162" s="8" t="n"/>
       <c r="K162" s="8" t="n"/>
       <c r="L162" s="8" t="n"/>
-      <c r="M162" s="35" t="n">
-        <v>11006</v>
-      </c>
+      <c r="M162" s="8" t="n"/>
       <c r="N162" s="8" t="n"/>
     </row>
     <row r="163">
@@ -7644,9 +7537,7 @@
       <c r="J163" s="8" t="n"/>
       <c r="K163" s="8" t="n"/>
       <c r="L163" s="8" t="n"/>
-      <c r="M163" s="35" t="n">
-        <v>11542</v>
-      </c>
+      <c r="M163" s="8" t="n"/>
       <c r="N163" s="8" t="n"/>
     </row>
     <row r="164">
@@ -7680,9 +7571,7 @@
       <c r="J164" s="8" t="n"/>
       <c r="K164" s="8" t="n"/>
       <c r="L164" s="8" t="n"/>
-      <c r="M164" s="35" t="n">
-        <v>5185</v>
-      </c>
+      <c r="M164" s="8" t="n"/>
       <c r="N164" s="8" t="n"/>
     </row>
     <row r="165">
@@ -7716,9 +7605,7 @@
       <c r="J165" s="8" t="n"/>
       <c r="K165" s="8" t="n"/>
       <c r="L165" s="8" t="n"/>
-      <c r="M165" s="35" t="n">
-        <v>7645</v>
-      </c>
+      <c r="M165" s="8" t="n"/>
       <c r="N165" s="8" t="n"/>
     </row>
     <row r="166">
@@ -7752,9 +7639,7 @@
       <c r="J166" s="8" t="n"/>
       <c r="K166" s="8" t="n"/>
       <c r="L166" s="8" t="n"/>
-      <c r="M166" s="35" t="n">
-        <v>1070</v>
-      </c>
+      <c r="M166" s="8" t="n"/>
       <c r="N166" s="8" t="n"/>
     </row>
     <row r="167">
@@ -8136,9 +8021,7 @@
       <c r="J175" s="8" t="n"/>
       <c r="K175" s="8" t="n"/>
       <c r="L175" s="8" t="n"/>
-      <c r="M175" s="35" t="n">
-        <v>3771</v>
-      </c>
+      <c r="M175" s="8" t="n"/>
       <c r="N175" s="8" t="n"/>
     </row>
     <row r="176">
@@ -8308,9 +8191,7 @@
       <c r="J179" s="8" t="n"/>
       <c r="K179" s="8" t="n"/>
       <c r="L179" s="8" t="n"/>
-      <c r="M179" s="35" t="n">
-        <v>4200</v>
-      </c>
+      <c r="M179" s="8" t="n"/>
       <c r="N179" s="8" t="n"/>
     </row>
     <row r="180">
@@ -8344,9 +8225,7 @@
       <c r="J180" s="8" t="n"/>
       <c r="K180" s="8" t="n"/>
       <c r="L180" s="8" t="n"/>
-      <c r="M180" s="35" t="n">
-        <v>14379</v>
-      </c>
+      <c r="M180" s="8" t="n"/>
       <c r="N180" s="8" t="n"/>
     </row>
     <row r="181">
@@ -8380,9 +8259,7 @@
       <c r="J181" s="8" t="n"/>
       <c r="K181" s="8" t="n"/>
       <c r="L181" s="8" t="n"/>
-      <c r="M181" s="35" t="n">
-        <v>8349</v>
-      </c>
+      <c r="M181" s="8" t="n"/>
       <c r="N181" s="8" t="n"/>
     </row>
     <row r="182">
@@ -8416,9 +8293,7 @@
       <c r="J182" s="8" t="n"/>
       <c r="K182" s="8" t="n"/>
       <c r="L182" s="8" t="n"/>
-      <c r="M182" s="35" t="n">
-        <v>2216</v>
-      </c>
+      <c r="M182" s="8" t="n"/>
       <c r="N182" s="8" t="n"/>
     </row>
     <row r="183">
@@ -8674,9 +8549,7 @@
       <c r="J188" s="8" t="n"/>
       <c r="K188" s="8" t="n"/>
       <c r="L188" s="8" t="n"/>
-      <c r="M188" s="35" t="n">
-        <v>2015</v>
-      </c>
+      <c r="M188" s="8" t="n"/>
       <c r="N188" s="8" t="n"/>
     </row>
     <row r="189">
@@ -8756,9 +8629,7 @@
       <c r="J190" s="8" t="n"/>
       <c r="K190" s="8" t="n"/>
       <c r="L190" s="8" t="n"/>
-      <c r="M190" s="35" t="n">
-        <v>3130</v>
-      </c>
+      <c r="M190" s="8" t="n"/>
       <c r="N190" s="8" t="n"/>
     </row>
     <row r="191">
@@ -9094,9 +8965,7 @@
       <c r="J198" s="8" t="n"/>
       <c r="K198" s="8" t="n"/>
       <c r="L198" s="8" t="n"/>
-      <c r="M198" s="35" t="n">
-        <v>2984</v>
-      </c>
+      <c r="M198" s="8" t="n"/>
       <c r="N198" s="8" t="n"/>
     </row>
     <row r="199">
@@ -9130,9 +8999,7 @@
       <c r="J199" s="8" t="n"/>
       <c r="K199" s="8" t="n"/>
       <c r="L199" s="8" t="n"/>
-      <c r="M199" s="35" t="n">
-        <v>4839</v>
-      </c>
+      <c r="M199" s="8" t="n"/>
       <c r="N199" s="8" t="n"/>
     </row>
     <row r="200">
@@ -9384,9 +9251,7 @@
       <c r="J205" s="8" t="n"/>
       <c r="K205" s="8" t="n"/>
       <c r="L205" s="8" t="n"/>
-      <c r="M205" s="35" t="n">
-        <v>1458</v>
-      </c>
+      <c r="M205" s="8" t="n"/>
       <c r="N205" s="8" t="n"/>
     </row>
     <row r="206">
@@ -9770,9 +9635,7 @@
       <c r="J214" s="8" t="n"/>
       <c r="K214" s="8" t="n"/>
       <c r="L214" s="8" t="n"/>
-      <c r="M214" s="35" t="n">
-        <v>3464</v>
-      </c>
+      <c r="M214" s="8" t="n"/>
       <c r="N214" s="8" t="n"/>
     </row>
     <row r="215">
@@ -9806,9 +9669,7 @@
       <c r="J215" s="8" t="n"/>
       <c r="K215" s="8" t="n"/>
       <c r="L215" s="8" t="n"/>
-      <c r="M215" s="35" t="n">
-        <v>1630</v>
-      </c>
+      <c r="M215" s="8" t="n"/>
       <c r="N215" s="8" t="n"/>
     </row>
     <row r="216">
@@ -9842,9 +9703,7 @@
       <c r="J216" s="8" t="n"/>
       <c r="K216" s="8" t="n"/>
       <c r="L216" s="8" t="n"/>
-      <c r="M216" s="35" t="n">
-        <v>4300</v>
-      </c>
+      <c r="M216" s="8" t="n"/>
       <c r="N216" s="8" t="n"/>
     </row>
     <row r="217">
@@ -9878,9 +9737,7 @@
       <c r="J217" s="8" t="n"/>
       <c r="K217" s="8" t="n"/>
       <c r="L217" s="8" t="n"/>
-      <c r="M217" s="35" t="n">
-        <v>1068</v>
-      </c>
+      <c r="M217" s="8" t="n"/>
       <c r="N217" s="8" t="n"/>
     </row>
     <row r="218">
@@ -10174,9 +10031,7 @@
       <c r="J224" s="8" t="n"/>
       <c r="K224" s="8" t="n"/>
       <c r="L224" s="8" t="n"/>
-      <c r="M224" s="35" t="n">
-        <v>1756</v>
-      </c>
+      <c r="M224" s="8" t="n"/>
       <c r="N224" s="8" t="n"/>
     </row>
     <row r="225">
@@ -10210,9 +10065,7 @@
       <c r="J225" s="8" t="n"/>
       <c r="K225" s="8" t="n"/>
       <c r="L225" s="8" t="n"/>
-      <c r="M225" s="35" t="n">
-        <v>2925</v>
-      </c>
+      <c r="M225" s="8" t="n"/>
       <c r="N225" s="8" t="n"/>
     </row>
     <row r="226">
@@ -10246,9 +10099,7 @@
       <c r="J226" s="8" t="n"/>
       <c r="K226" s="8" t="n"/>
       <c r="L226" s="8" t="n"/>
-      <c r="M226" s="35" t="n">
-        <v>1325</v>
-      </c>
+      <c r="M226" s="8" t="n"/>
       <c r="N226" s="8" t="n"/>
     </row>
     <row r="227">
@@ -10282,9 +10133,7 @@
       <c r="J227" s="8" t="n"/>
       <c r="K227" s="8" t="n"/>
       <c r="L227" s="8" t="n"/>
-      <c r="M227" s="35" t="n">
-        <v>967</v>
-      </c>
+      <c r="M227" s="8" t="n"/>
       <c r="N227" s="8" t="n"/>
     </row>
     <row r="228">
@@ -10318,9 +10167,7 @@
       <c r="J228" s="8" t="n"/>
       <c r="K228" s="8" t="n"/>
       <c r="L228" s="8" t="n"/>
-      <c r="M228" s="35" t="n">
-        <v>6986</v>
-      </c>
+      <c r="M228" s="8" t="n"/>
       <c r="N228" s="8" t="n"/>
     </row>
     <row r="229">
@@ -10354,9 +10201,7 @@
       <c r="J229" s="8" t="n"/>
       <c r="K229" s="8" t="n"/>
       <c r="L229" s="8" t="n"/>
-      <c r="M229" s="35" t="n">
-        <v>7565</v>
-      </c>
+      <c r="M229" s="8" t="n"/>
       <c r="N229" s="8" t="n"/>
     </row>
     <row r="230">
@@ -10604,9 +10449,7 @@
       <c r="J235" s="8" t="n"/>
       <c r="K235" s="8" t="n"/>
       <c r="L235" s="8" t="n"/>
-      <c r="M235" s="35" t="n">
-        <v>6285</v>
-      </c>
+      <c r="M235" s="8" t="n"/>
       <c r="N235" s="8" t="n"/>
     </row>
     <row r="236">
@@ -11330,9 +11173,7 @@
       <c r="J252" s="8" t="n"/>
       <c r="K252" s="8" t="n"/>
       <c r="L252" s="8" t="n"/>
-      <c r="M252" s="35" t="n">
-        <v>420</v>
-      </c>
+      <c r="M252" s="8" t="n"/>
       <c r="N252" s="8" t="n"/>
     </row>
     <row r="253">
@@ -11360,21 +11201,21 @@
       <c r="F253" s="12" t="n">
         <v>4733</v>
       </c>
-      <c r="G253" s="36" t="n">
+      <c r="G253" s="35" t="n">
         <v>45915</v>
       </c>
-      <c r="H253" s="36" t="inlineStr">
+      <c r="H253" s="35" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I253" s="37" t="inlineStr">
+      <c r="I253" s="36" t="inlineStr">
         <is>
           <t>002617</t>
         </is>
       </c>
       <c r="J253" s="12" t="n"/>
-      <c r="K253" s="38" t="n">
+      <c r="K253" s="37" t="n">
         <v>4733</v>
       </c>
       <c r="L253" s="12" t="n"/>
@@ -11412,9 +11253,7 @@
       <c r="J254" s="8" t="n"/>
       <c r="K254" s="8" t="n"/>
       <c r="L254" s="8" t="n"/>
-      <c r="M254" s="35" t="n">
-        <v>2107</v>
-      </c>
+      <c r="M254" s="8" t="n"/>
       <c r="N254" s="8" t="n"/>
     </row>
     <row r="255">
@@ -11448,9 +11287,7 @@
       <c r="J255" s="8" t="n"/>
       <c r="K255" s="8" t="n"/>
       <c r="L255" s="8" t="n"/>
-      <c r="M255" s="35" t="n">
-        <v>4283</v>
-      </c>
+      <c r="M255" s="8" t="n"/>
       <c r="N255" s="8" t="n"/>
     </row>
     <row r="256">
@@ -11484,9 +11321,7 @@
       <c r="J256" s="8" t="n"/>
       <c r="K256" s="8" t="n"/>
       <c r="L256" s="8" t="n"/>
-      <c r="M256" s="35" t="n">
-        <v>4132</v>
-      </c>
+      <c r="M256" s="8" t="n"/>
       <c r="N256" s="8" t="n"/>
     </row>
     <row r="257">
@@ -11520,9 +11355,7 @@
       <c r="J257" s="8" t="n"/>
       <c r="K257" s="8" t="n"/>
       <c r="L257" s="8" t="n"/>
-      <c r="M257" s="35" t="n">
-        <v>17393</v>
-      </c>
+      <c r="M257" s="8" t="n"/>
       <c r="N257" s="8" t="n"/>
     </row>
     <row r="258">
@@ -11906,9 +11739,7 @@
       <c r="J266" s="8" t="n"/>
       <c r="K266" s="8" t="n"/>
       <c r="L266" s="8" t="n"/>
-      <c r="M266" s="35" t="n">
-        <v>1062</v>
-      </c>
+      <c r="M266" s="8" t="n"/>
       <c r="N266" s="8" t="n"/>
     </row>
     <row r="267">
@@ -11942,9 +11773,7 @@
       <c r="J267" s="8" t="n"/>
       <c r="K267" s="8" t="n"/>
       <c r="L267" s="8" t="n"/>
-      <c r="M267" s="35" t="n">
-        <v>612</v>
-      </c>
+      <c r="M267" s="8" t="n"/>
       <c r="N267" s="8" t="n"/>
     </row>
     <row r="268">
@@ -12116,9 +11945,7 @@
       <c r="J271" s="8" t="n"/>
       <c r="K271" s="8" t="n"/>
       <c r="L271" s="8" t="n"/>
-      <c r="M271" s="35" t="n">
-        <v>6878</v>
-      </c>
+      <c r="M271" s="8" t="n"/>
       <c r="N271" s="8" t="n"/>
     </row>
     <row r="272">
@@ -12152,9 +11979,7 @@
       <c r="J272" s="8" t="n"/>
       <c r="K272" s="8" t="n"/>
       <c r="L272" s="8" t="n"/>
-      <c r="M272" s="35" t="n">
-        <v>3669</v>
-      </c>
+      <c r="M272" s="8" t="n"/>
       <c r="N272" s="8" t="n"/>
     </row>
     <row r="273">
@@ -12234,9 +12059,7 @@
       <c r="J274" s="8" t="n"/>
       <c r="K274" s="8" t="n"/>
       <c r="L274" s="8" t="n"/>
-      <c r="M274" s="35" t="n">
-        <v>1172</v>
-      </c>
+      <c r="M274" s="8" t="n"/>
       <c r="N274" s="8" t="n"/>
     </row>
     <row r="275">
@@ -12494,9 +12317,7 @@
       <c r="J280" s="8" t="n"/>
       <c r="K280" s="8" t="n"/>
       <c r="L280" s="8" t="n"/>
-      <c r="M280" s="35" t="n">
-        <v>8447</v>
-      </c>
+      <c r="M280" s="8" t="n"/>
       <c r="N280" s="8" t="n"/>
     </row>
     <row r="281">
@@ -12746,9 +12567,7 @@
       <c r="J286" s="8" t="n"/>
       <c r="K286" s="8" t="n"/>
       <c r="L286" s="8" t="n"/>
-      <c r="M286" s="35" t="n">
-        <v>2773</v>
-      </c>
+      <c r="M286" s="8" t="n"/>
       <c r="N286" s="8" t="n"/>
     </row>
     <row r="287">
@@ -12782,9 +12601,7 @@
       <c r="J287" s="8" t="n"/>
       <c r="K287" s="8" t="n"/>
       <c r="L287" s="8" t="n"/>
-      <c r="M287" s="35" t="n">
-        <v>3362</v>
-      </c>
+      <c r="M287" s="8" t="n"/>
       <c r="N287" s="8" t="n"/>
     </row>
     <row r="288">
@@ -12818,9 +12635,7 @@
       <c r="J288" s="8" t="n"/>
       <c r="K288" s="8" t="n"/>
       <c r="L288" s="8" t="n"/>
-      <c r="M288" s="35" t="n">
-        <v>1403</v>
-      </c>
+      <c r="M288" s="8" t="n"/>
       <c r="N288" s="8" t="n"/>
     </row>
     <row r="289">
@@ -12854,9 +12669,7 @@
       <c r="J289" s="8" t="n"/>
       <c r="K289" s="8" t="n"/>
       <c r="L289" s="8" t="n"/>
-      <c r="M289" s="35" t="n">
-        <v>1380</v>
-      </c>
+      <c r="M289" s="8" t="n"/>
       <c r="N289" s="8" t="n"/>
     </row>
     <row r="290">
@@ -13288,9 +13101,7 @@
       <c r="J299" s="8" t="n"/>
       <c r="K299" s="8" t="n"/>
       <c r="L299" s="8" t="n"/>
-      <c r="M299" s="35" t="n">
-        <v>679</v>
-      </c>
+      <c r="M299" s="8" t="n"/>
       <c r="N299" s="8" t="n"/>
     </row>
     <row r="300">
@@ -13368,9 +13179,7 @@
       <c r="J301" s="8" t="n"/>
       <c r="K301" s="8" t="n"/>
       <c r="L301" s="8" t="n"/>
-      <c r="M301" s="35" t="n">
-        <v>3787</v>
-      </c>
+      <c r="M301" s="8" t="n"/>
       <c r="N301" s="8" t="n"/>
     </row>
     <row r="302">
@@ -13404,9 +13213,7 @@
       <c r="J302" s="8" t="n"/>
       <c r="K302" s="8" t="n"/>
       <c r="L302" s="8" t="n"/>
-      <c r="M302" s="35" t="n">
-        <v>4037</v>
-      </c>
+      <c r="M302" s="8" t="n"/>
       <c r="N302" s="8" t="n"/>
     </row>
     <row r="303">
@@ -13440,9 +13247,7 @@
       <c r="J303" s="8" t="n"/>
       <c r="K303" s="8" t="n"/>
       <c r="L303" s="8" t="n"/>
-      <c r="M303" s="35" t="n">
-        <v>3391</v>
-      </c>
+      <c r="M303" s="8" t="n"/>
       <c r="N303" s="8" t="n"/>
     </row>
     <row r="304">
@@ -14092,9 +13897,7 @@
       <c r="J318" s="8" t="n"/>
       <c r="K318" s="8" t="n"/>
       <c r="L318" s="8" t="n"/>
-      <c r="M318" s="35" t="n">
-        <v>775</v>
-      </c>
+      <c r="M318" s="8" t="n"/>
       <c r="N318" s="8" t="n"/>
     </row>
     <row r="319">
@@ -14128,9 +13931,7 @@
       <c r="J319" s="8" t="n"/>
       <c r="K319" s="8" t="n"/>
       <c r="L319" s="8" t="n"/>
-      <c r="M319" s="35" t="n">
-        <v>676</v>
-      </c>
+      <c r="M319" s="8" t="n"/>
       <c r="N319" s="8" t="n"/>
     </row>
     <row r="320">
@@ -14164,9 +13965,7 @@
       <c r="J320" s="8" t="n"/>
       <c r="K320" s="8" t="n"/>
       <c r="L320" s="8" t="n"/>
-      <c r="M320" s="35" t="n">
-        <v>2713</v>
-      </c>
+      <c r="M320" s="8" t="n"/>
       <c r="N320" s="8" t="n"/>
     </row>
     <row r="321">
@@ -14200,9 +13999,7 @@
       <c r="J321" s="8" t="n"/>
       <c r="K321" s="8" t="n"/>
       <c r="L321" s="8" t="n"/>
-      <c r="M321" s="35" t="n">
-        <v>2294</v>
-      </c>
+      <c r="M321" s="8" t="n"/>
       <c r="N321" s="8" t="n"/>
     </row>
     <row r="322">
@@ -14282,9 +14079,7 @@
       <c r="J323" s="8" t="n"/>
       <c r="K323" s="8" t="n"/>
       <c r="L323" s="8" t="n"/>
-      <c r="M323" s="35" t="n">
-        <v>2090</v>
-      </c>
+      <c r="M323" s="8" t="n"/>
       <c r="N323" s="8" t="n"/>
     </row>
     <row r="324">
@@ -14360,9 +14155,7 @@
       <c r="J325" s="8" t="n"/>
       <c r="K325" s="8" t="n"/>
       <c r="L325" s="8" t="n"/>
-      <c r="M325" s="35" t="n">
-        <v>456</v>
-      </c>
+      <c r="M325" s="8" t="n"/>
       <c r="N325" s="8" t="n"/>
     </row>
     <row r="326">
@@ -14437,7 +14230,7 @@
         <v>5700</v>
       </c>
       <c r="G327" s="31" t="n">
-        <v>45828</v>
+        <v>45925</v>
       </c>
       <c r="H327" s="32" t="inlineStr">
         <is>
@@ -14446,19 +14239,15 @@
       </c>
       <c r="I327" s="32" t="inlineStr">
         <is>
-          <t>002384</t>
-        </is>
-      </c>
-      <c r="J327" s="33" t="n">
-        <v>25000</v>
-      </c>
+          <t>002613</t>
+        </is>
+      </c>
+      <c r="J327" s="8" t="n"/>
       <c r="K327" s="34" t="n">
-        <v>1434</v>
+        <v>5700</v>
       </c>
       <c r="L327" s="8" t="n"/>
-      <c r="M327" s="40" t="n">
-        <v>18993</v>
-      </c>
+      <c r="M327" s="8" t="n"/>
       <c r="N327" s="8" t="n"/>
     </row>
     <row r="328">
@@ -14618,9 +14407,7 @@
       <c r="J331" s="8" t="n"/>
       <c r="K331" s="8" t="n"/>
       <c r="L331" s="8" t="n"/>
-      <c r="M331" s="35" t="n">
-        <v>643</v>
-      </c>
+      <c r="M331" s="8" t="n"/>
       <c r="N331" s="8" t="n"/>
     </row>
     <row r="332">
@@ -14654,9 +14441,7 @@
       <c r="J332" s="8" t="n"/>
       <c r="K332" s="8" t="n"/>
       <c r="L332" s="8" t="n"/>
-      <c r="M332" s="35" t="n">
-        <v>1128</v>
-      </c>
+      <c r="M332" s="8" t="n"/>
       <c r="N332" s="8" t="n"/>
     </row>
     <row r="333">
@@ -14690,9 +14475,7 @@
       <c r="J333" s="8" t="n"/>
       <c r="K333" s="8" t="n"/>
       <c r="L333" s="8" t="n"/>
-      <c r="M333" s="35" t="n">
-        <v>2006</v>
-      </c>
+      <c r="M333" s="8" t="n"/>
       <c r="N333" s="8" t="n"/>
     </row>
     <row r="334">
@@ -14726,9 +14509,7 @@
       <c r="J334" s="8" t="n"/>
       <c r="K334" s="8" t="n"/>
       <c r="L334" s="8" t="n"/>
-      <c r="M334" s="35" t="n">
-        <v>4142</v>
-      </c>
+      <c r="M334" s="8" t="n"/>
       <c r="N334" s="8" t="n"/>
     </row>
     <row r="335">
@@ -14762,9 +14543,7 @@
       <c r="J335" s="8" t="n"/>
       <c r="K335" s="8" t="n"/>
       <c r="L335" s="8" t="n"/>
-      <c r="M335" s="35" t="n">
-        <v>2746</v>
-      </c>
+      <c r="M335" s="8" t="n"/>
       <c r="N335" s="8" t="n"/>
     </row>
     <row r="336">
@@ -14976,9 +14755,7 @@
       <c r="J340" s="8" t="n"/>
       <c r="K340" s="8" t="n"/>
       <c r="L340" s="8" t="n"/>
-      <c r="M340" s="35" t="n">
-        <v>1338</v>
-      </c>
+      <c r="M340" s="8" t="n"/>
       <c r="N340" s="8" t="n"/>
     </row>
     <row r="341">
@@ -15012,9 +14789,7 @@
       <c r="J341" s="8" t="n"/>
       <c r="K341" s="8" t="n"/>
       <c r="L341" s="8" t="n"/>
-      <c r="M341" s="35" t="n">
-        <v>1900</v>
-      </c>
+      <c r="M341" s="8" t="n"/>
       <c r="N341" s="8" t="n"/>
     </row>
     <row r="342">
@@ -15138,9 +14913,7 @@
       <c r="J344" s="8" t="n"/>
       <c r="K344" s="8" t="n"/>
       <c r="L344" s="8" t="n"/>
-      <c r="M344" s="35" t="n">
-        <v>2126</v>
-      </c>
+      <c r="M344" s="8" t="n"/>
       <c r="N344" s="8" t="n"/>
     </row>
     <row r="345">
@@ -15174,9 +14947,7 @@
       <c r="J345" s="8" t="n"/>
       <c r="K345" s="8" t="n"/>
       <c r="L345" s="8" t="n"/>
-      <c r="M345" s="35" t="n">
-        <v>1629</v>
-      </c>
+      <c r="M345" s="8" t="n"/>
       <c r="N345" s="8" t="n"/>
     </row>
     <row r="346">
@@ -15210,9 +14981,7 @@
       <c r="J346" s="8" t="n"/>
       <c r="K346" s="8" t="n"/>
       <c r="L346" s="8" t="n"/>
-      <c r="M346" s="35" t="n">
-        <v>5654</v>
-      </c>
+      <c r="M346" s="8" t="n"/>
       <c r="N346" s="8" t="n"/>
     </row>
     <row r="347">
@@ -15246,9 +15015,7 @@
       <c r="J347" s="8" t="n"/>
       <c r="K347" s="8" t="n"/>
       <c r="L347" s="8" t="n"/>
-      <c r="M347" s="35" t="n">
-        <v>2129</v>
-      </c>
+      <c r="M347" s="8" t="n"/>
       <c r="N347" s="8" t="n"/>
     </row>
     <row r="348">
@@ -15372,9 +15139,7 @@
       <c r="J350" s="8" t="n"/>
       <c r="K350" s="8" t="n"/>
       <c r="L350" s="8" t="n"/>
-      <c r="M350" s="35" t="n">
-        <v>23811</v>
-      </c>
+      <c r="M350" s="8" t="n"/>
       <c r="N350" s="8" t="n"/>
     </row>
     <row r="351">
@@ -15496,9 +15261,7 @@
       <c r="J353" s="8" t="n"/>
       <c r="K353" s="8" t="n"/>
       <c r="L353" s="8" t="n"/>
-      <c r="M353" s="35" t="n">
-        <v>3212</v>
-      </c>
+      <c r="M353" s="8" t="n"/>
       <c r="N353" s="8" t="n"/>
     </row>
     <row r="354">
@@ -15532,9 +15295,7 @@
       <c r="J354" s="8" t="n"/>
       <c r="K354" s="8" t="n"/>
       <c r="L354" s="8" t="n"/>
-      <c r="M354" s="35" t="n">
-        <v>3715</v>
-      </c>
+      <c r="M354" s="8" t="n"/>
       <c r="N354" s="8" t="n"/>
     </row>
     <row r="355">
@@ -15568,9 +15329,7 @@
       <c r="J355" s="8" t="n"/>
       <c r="K355" s="8" t="n"/>
       <c r="L355" s="8" t="n"/>
-      <c r="M355" s="35" t="n">
-        <v>1298</v>
-      </c>
+      <c r="M355" s="8" t="n"/>
       <c r="N355" s="8" t="n"/>
     </row>
     <row r="356">
@@ -15604,9 +15363,7 @@
       <c r="J356" s="8" t="n"/>
       <c r="K356" s="8" t="n"/>
       <c r="L356" s="8" t="n"/>
-      <c r="M356" s="35" t="n">
-        <v>12135</v>
-      </c>
+      <c r="M356" s="8" t="n"/>
       <c r="N356" s="8" t="n"/>
     </row>
     <row r="357">
@@ -15808,9 +15565,7 @@
       <c r="J361" s="8" t="n"/>
       <c r="K361" s="8" t="n"/>
       <c r="L361" s="8" t="n"/>
-      <c r="M361" s="35" t="n">
-        <v>1609</v>
-      </c>
+      <c r="M361" s="8" t="n"/>
       <c r="N361" s="8" t="n"/>
     </row>
     <row r="362">
@@ -15936,9 +15691,7 @@
       <c r="J364" s="8" t="n"/>
       <c r="K364" s="8" t="n"/>
       <c r="L364" s="8" t="n"/>
-      <c r="M364" s="35" t="n">
-        <v>8588</v>
-      </c>
+      <c r="M364" s="8" t="n"/>
       <c r="N364" s="8" t="n"/>
     </row>
     <row r="365">
@@ -15972,9 +15725,7 @@
       <c r="J365" s="8" t="n"/>
       <c r="K365" s="8" t="n"/>
       <c r="L365" s="8" t="n"/>
-      <c r="M365" s="35" t="n">
-        <v>1550</v>
-      </c>
+      <c r="M365" s="8" t="n"/>
       <c r="N365" s="8" t="n"/>
     </row>
     <row r="366">
@@ -16008,9 +15759,7 @@
       <c r="J366" s="8" t="n"/>
       <c r="K366" s="8" t="n"/>
       <c r="L366" s="8" t="n"/>
-      <c r="M366" s="35" t="n">
-        <v>1942</v>
-      </c>
+      <c r="M366" s="8" t="n"/>
       <c r="N366" s="8" t="n"/>
     </row>
     <row r="367">
@@ -16044,9 +15793,7 @@
       <c r="J367" s="8" t="n"/>
       <c r="K367" s="8" t="n"/>
       <c r="L367" s="8" t="n"/>
-      <c r="M367" s="35" t="n">
-        <v>4311</v>
-      </c>
+      <c r="M367" s="8" t="n"/>
       <c r="N367" s="8" t="n"/>
     </row>
     <row r="368">
@@ -16404,7 +16151,7 @@
         <v>93</v>
       </c>
       <c r="L375" s="8" t="n"/>
-      <c r="M375" s="40" t="n">
+      <c r="M375" s="39" t="n">
         <v>910</v>
       </c>
       <c r="N375" s="8" t="n"/>
@@ -16440,9 +16187,7 @@
       <c r="J376" s="8" t="n"/>
       <c r="K376" s="8" t="n"/>
       <c r="L376" s="8" t="n"/>
-      <c r="M376" s="35" t="n">
-        <v>185</v>
-      </c>
+      <c r="M376" s="8" t="n"/>
       <c r="N376" s="8" t="n"/>
     </row>
     <row r="377">
@@ -16476,9 +16221,7 @@
       <c r="J377" s="8" t="n"/>
       <c r="K377" s="8" t="n"/>
       <c r="L377" s="8" t="n"/>
-      <c r="M377" s="35" t="n">
-        <v>763</v>
-      </c>
+      <c r="M377" s="8" t="n"/>
       <c r="N377" s="8" t="n"/>
     </row>
     <row r="378">
@@ -16644,9 +16387,7 @@
       <c r="J381" s="8" t="n"/>
       <c r="K381" s="8" t="n"/>
       <c r="L381" s="8" t="n"/>
-      <c r="M381" s="35" t="n">
-        <v>6090</v>
-      </c>
+      <c r="M381" s="8" t="n"/>
       <c r="N381" s="8" t="n"/>
     </row>
     <row r="382">
@@ -16680,9 +16421,7 @@
       <c r="J382" s="8" t="n"/>
       <c r="K382" s="8" t="n"/>
       <c r="L382" s="8" t="n"/>
-      <c r="M382" s="35" t="n">
-        <v>5364</v>
-      </c>
+      <c r="M382" s="8" t="n"/>
       <c r="N382" s="8" t="n"/>
     </row>
     <row r="383">
@@ -16716,9 +16455,7 @@
       <c r="J383" s="8" t="n"/>
       <c r="K383" s="8" t="n"/>
       <c r="L383" s="8" t="n"/>
-      <c r="M383" s="35" t="n">
-        <v>6610</v>
-      </c>
+      <c r="M383" s="8" t="n"/>
       <c r="N383" s="8" t="n"/>
     </row>
     <row r="384">
@@ -16752,9 +16489,7 @@
       <c r="J384" s="8" t="n"/>
       <c r="K384" s="8" t="n"/>
       <c r="L384" s="8" t="n"/>
-      <c r="M384" s="35" t="n">
-        <v>2800</v>
-      </c>
+      <c r="M384" s="8" t="n"/>
       <c r="N384" s="8" t="n"/>
     </row>
     <row r="385">
@@ -16788,9 +16523,7 @@
       <c r="J385" s="8" t="n"/>
       <c r="K385" s="8" t="n"/>
       <c r="L385" s="8" t="n"/>
-      <c r="M385" s="35" t="n">
-        <v>5696</v>
-      </c>
+      <c r="M385" s="8" t="n"/>
       <c r="N385" s="8" t="n"/>
     </row>
     <row r="386">
@@ -16824,9 +16557,7 @@
       <c r="J386" s="8" t="n"/>
       <c r="K386" s="8" t="n"/>
       <c r="L386" s="8" t="n"/>
-      <c r="M386" s="35" t="n">
-        <v>1500</v>
-      </c>
+      <c r="M386" s="8" t="n"/>
       <c r="N386" s="8" t="n"/>
     </row>
     <row r="387">
@@ -16860,9 +16591,7 @@
       <c r="J387" s="8" t="n"/>
       <c r="K387" s="8" t="n"/>
       <c r="L387" s="8" t="n"/>
-      <c r="M387" s="35" t="n">
-        <v>594</v>
-      </c>
+      <c r="M387" s="8" t="n"/>
       <c r="N387" s="8" t="n"/>
     </row>
     <row r="388">
@@ -16984,9 +16713,7 @@
       <c r="J390" s="8" t="n"/>
       <c r="K390" s="8" t="n"/>
       <c r="L390" s="8" t="n"/>
-      <c r="M390" s="35" t="n">
-        <v>1414</v>
-      </c>
+      <c r="M390" s="8" t="n"/>
       <c r="N390" s="8" t="n"/>
     </row>
     <row r="391">
@@ -17110,9 +16837,7 @@
       <c r="J393" s="8" t="n"/>
       <c r="K393" s="8" t="n"/>
       <c r="L393" s="8" t="n"/>
-      <c r="M393" s="35" t="n">
-        <v>1417</v>
-      </c>
+      <c r="M393" s="8" t="n"/>
       <c r="N393" s="8" t="n"/>
     </row>
     <row r="394">
@@ -17146,9 +16871,7 @@
       <c r="J394" s="8" t="n"/>
       <c r="K394" s="8" t="n"/>
       <c r="L394" s="8" t="n"/>
-      <c r="M394" s="35" t="n">
-        <v>1861</v>
-      </c>
+      <c r="M394" s="8" t="n"/>
       <c r="N394" s="8" t="n"/>
     </row>
     <row r="395">
@@ -17182,9 +16905,7 @@
       <c r="J395" s="8" t="n"/>
       <c r="K395" s="8" t="n"/>
       <c r="L395" s="8" t="n"/>
-      <c r="M395" s="35" t="n">
-        <v>630</v>
-      </c>
+      <c r="M395" s="8" t="n"/>
       <c r="N395" s="8" t="n"/>
     </row>
     <row r="396">
@@ -17218,9 +16939,7 @@
       <c r="J396" s="8" t="n"/>
       <c r="K396" s="8" t="n"/>
       <c r="L396" s="8" t="n"/>
-      <c r="M396" s="35" t="n">
-        <v>3246</v>
-      </c>
+      <c r="M396" s="8" t="n"/>
       <c r="N396" s="8" t="n"/>
     </row>
     <row r="397">
@@ -17254,9 +16973,7 @@
       <c r="J397" s="8" t="n"/>
       <c r="K397" s="8" t="n"/>
       <c r="L397" s="8" t="n"/>
-      <c r="M397" s="35" t="n">
-        <v>11856</v>
-      </c>
+      <c r="M397" s="8" t="n"/>
       <c r="N397" s="8" t="n"/>
     </row>
     <row r="398">
@@ -17290,9 +17007,7 @@
       <c r="J398" s="8" t="n"/>
       <c r="K398" s="8" t="n"/>
       <c r="L398" s="8" t="n"/>
-      <c r="M398" s="35" t="n">
-        <v>2394</v>
-      </c>
+      <c r="M398" s="8" t="n"/>
       <c r="N398" s="8" t="n"/>
     </row>
     <row r="399">
@@ -17326,9 +17041,7 @@
       <c r="J399" s="8" t="n"/>
       <c r="K399" s="8" t="n"/>
       <c r="L399" s="8" t="n"/>
-      <c r="M399" s="35" t="n">
-        <v>4170</v>
-      </c>
+      <c r="M399" s="8" t="n"/>
       <c r="N399" s="8" t="n"/>
     </row>
     <row r="400">
@@ -17493,7 +17206,7 @@
         <v>326</v>
       </c>
       <c r="G403" s="31" t="n">
-        <v>45894</v>
+        <v>45925</v>
       </c>
       <c r="H403" s="32" t="inlineStr">
         <is>
@@ -17502,14 +17215,12 @@
       </c>
       <c r="I403" s="32" t="inlineStr">
         <is>
-          <t>002566</t>
-        </is>
-      </c>
-      <c r="J403" s="33" t="n">
-        <v>35999</v>
-      </c>
+          <t>002613</t>
+        </is>
+      </c>
+      <c r="J403" s="8" t="n"/>
       <c r="K403" s="34" t="n">
-        <v>2446</v>
+        <v>326</v>
       </c>
       <c r="L403" s="8" t="n"/>
       <c r="M403" s="8" t="n"/>
@@ -17592,9 +17303,7 @@
       <c r="J405" s="8" t="n"/>
       <c r="K405" s="8" t="n"/>
       <c r="L405" s="8" t="n"/>
-      <c r="M405" s="35" t="n">
-        <v>577</v>
-      </c>
+      <c r="M405" s="8" t="n"/>
       <c r="N405" s="8" t="n"/>
     </row>
     <row r="406">
@@ -17712,9 +17421,7 @@
       <c r="J408" s="8" t="n"/>
       <c r="K408" s="8" t="n"/>
       <c r="L408" s="8" t="n"/>
-      <c r="M408" s="35" t="n">
-        <v>3262</v>
-      </c>
+      <c r="M408" s="8" t="n"/>
       <c r="N408" s="8" t="n"/>
     </row>
     <row r="409">
@@ -17748,9 +17455,7 @@
       <c r="J409" s="8" t="n"/>
       <c r="K409" s="8" t="n"/>
       <c r="L409" s="8" t="n"/>
-      <c r="M409" s="35" t="n">
-        <v>3528</v>
-      </c>
+      <c r="M409" s="8" t="n"/>
       <c r="N409" s="8" t="n"/>
     </row>
     <row r="410">
@@ -17876,9 +17581,7 @@
       <c r="J412" s="8" t="n"/>
       <c r="K412" s="8" t="n"/>
       <c r="L412" s="8" t="n"/>
-      <c r="M412" s="35" t="n">
-        <v>4330</v>
-      </c>
+      <c r="M412" s="8" t="n"/>
       <c r="N412" s="8" t="n"/>
     </row>
     <row r="413">
@@ -18000,9 +17703,7 @@
       <c r="J415" s="8" t="n"/>
       <c r="K415" s="8" t="n"/>
       <c r="L415" s="8" t="n"/>
-      <c r="M415" s="35" t="n">
-        <v>5880</v>
-      </c>
+      <c r="M415" s="8" t="n"/>
       <c r="N415" s="8" t="n"/>
     </row>
     <row r="416">
@@ -18036,9 +17737,7 @@
       <c r="J416" s="8" t="n"/>
       <c r="K416" s="8" t="n"/>
       <c r="L416" s="8" t="n"/>
-      <c r="M416" s="35" t="n">
-        <v>1239</v>
-      </c>
+      <c r="M416" s="8" t="n"/>
       <c r="N416" s="8" t="n"/>
     </row>
     <row r="417">
@@ -18204,9 +17903,7 @@
       <c r="J420" s="8" t="n"/>
       <c r="K420" s="8" t="n"/>
       <c r="L420" s="8" t="n"/>
-      <c r="M420" s="35" t="n">
-        <v>26460</v>
-      </c>
+      <c r="M420" s="8" t="n"/>
       <c r="N420" s="8" t="n"/>
     </row>
     <row r="421">
@@ -18328,9 +18025,7 @@
       <c r="J423" s="8" t="n"/>
       <c r="K423" s="8" t="n"/>
       <c r="L423" s="8" t="n"/>
-      <c r="M423" s="35" t="n">
-        <v>645</v>
-      </c>
+      <c r="M423" s="8" t="n"/>
       <c r="N423" s="8" t="n"/>
     </row>
     <row r="424">
@@ -18364,9 +18059,7 @@
       <c r="J424" s="8" t="n"/>
       <c r="K424" s="8" t="n"/>
       <c r="L424" s="8" t="n"/>
-      <c r="M424" s="35" t="n">
-        <v>1139</v>
-      </c>
+      <c r="M424" s="8" t="n"/>
       <c r="N424" s="8" t="n"/>
     </row>
     <row r="425">
@@ -18400,9 +18093,7 @@
       <c r="J425" s="8" t="n"/>
       <c r="K425" s="8" t="n"/>
       <c r="L425" s="8" t="n"/>
-      <c r="M425" s="35" t="n">
-        <v>1060</v>
-      </c>
+      <c r="M425" s="8" t="n"/>
       <c r="N425" s="8" t="n"/>
     </row>
     <row r="426">
@@ -18436,9 +18127,7 @@
       <c r="J426" s="8" t="n"/>
       <c r="K426" s="8" t="n"/>
       <c r="L426" s="8" t="n"/>
-      <c r="M426" s="35" t="n">
-        <v>5522</v>
-      </c>
+      <c r="M426" s="8" t="n"/>
       <c r="N426" s="8" t="n"/>
     </row>
     <row r="427">
@@ -18472,9 +18161,7 @@
       <c r="J427" s="8" t="n"/>
       <c r="K427" s="8" t="n"/>
       <c r="L427" s="8" t="n"/>
-      <c r="M427" s="35" t="n">
-        <v>4050</v>
-      </c>
+      <c r="M427" s="8" t="n"/>
       <c r="N427" s="8" t="n"/>
     </row>
     <row r="428">
@@ -18508,9 +18195,7 @@
       <c r="J428" s="8" t="n"/>
       <c r="K428" s="8" t="n"/>
       <c r="L428" s="8" t="n"/>
-      <c r="M428" s="35" t="n">
-        <v>3988</v>
-      </c>
+      <c r="M428" s="8" t="n"/>
       <c r="N428" s="8" t="n"/>
     </row>
     <row r="429">
@@ -18680,9 +18365,7 @@
       <c r="J432" s="8" t="n"/>
       <c r="K432" s="8" t="n"/>
       <c r="L432" s="8" t="n"/>
-      <c r="M432" s="35" t="n">
-        <v>473</v>
-      </c>
+      <c r="M432" s="8" t="n"/>
       <c r="N432" s="8" t="n"/>
     </row>
     <row r="433">
@@ -18716,9 +18399,7 @@
       <c r="J433" s="8" t="n"/>
       <c r="K433" s="8" t="n"/>
       <c r="L433" s="8" t="n"/>
-      <c r="M433" s="35" t="n">
-        <v>12845</v>
-      </c>
+      <c r="M433" s="8" t="n"/>
       <c r="N433" s="8" t="n"/>
     </row>
     <row r="434">
@@ -18752,9 +18433,7 @@
       <c r="J434" s="8" t="n"/>
       <c r="K434" s="8" t="n"/>
       <c r="L434" s="8" t="n"/>
-      <c r="M434" s="35" t="n">
-        <v>4416</v>
-      </c>
+      <c r="M434" s="8" t="n"/>
       <c r="N434" s="8" t="n"/>
     </row>
     <row r="435">
@@ -18788,9 +18467,7 @@
       <c r="J435" s="8" t="n"/>
       <c r="K435" s="8" t="n"/>
       <c r="L435" s="8" t="n"/>
-      <c r="M435" s="35" t="n">
-        <v>7391</v>
-      </c>
+      <c r="M435" s="8" t="n"/>
       <c r="N435" s="8" t="n"/>
     </row>
     <row r="436">
@@ -18824,9 +18501,7 @@
       <c r="J436" s="8" t="n"/>
       <c r="K436" s="8" t="n"/>
       <c r="L436" s="8" t="n"/>
-      <c r="M436" s="35" t="n">
-        <v>14442</v>
-      </c>
+      <c r="M436" s="8" t="n"/>
       <c r="N436" s="8" t="n"/>
     </row>
     <row r="437">
@@ -18944,9 +18619,7 @@
       <c r="J439" s="8" t="n"/>
       <c r="K439" s="8" t="n"/>
       <c r="L439" s="8" t="n"/>
-      <c r="M439" s="35" t="n">
-        <v>5326</v>
-      </c>
+      <c r="M439" s="8" t="n"/>
       <c r="N439" s="8" t="n"/>
     </row>
     <row r="440">
@@ -18980,9 +18653,7 @@
       <c r="J440" s="8" t="n"/>
       <c r="K440" s="8" t="n"/>
       <c r="L440" s="8" t="n"/>
-      <c r="M440" s="35" t="n">
-        <v>218</v>
-      </c>
+      <c r="M440" s="8" t="n"/>
       <c r="N440" s="8" t="n"/>
     </row>
     <row r="441">
@@ -19016,9 +18687,7 @@
       <c r="J441" s="8" t="n"/>
       <c r="K441" s="8" t="n"/>
       <c r="L441" s="8" t="n"/>
-      <c r="M441" s="35" t="n">
-        <v>3020</v>
-      </c>
+      <c r="M441" s="8" t="n"/>
       <c r="N441" s="8" t="n"/>
     </row>
     <row r="442">
@@ -19052,9 +18721,7 @@
       <c r="J442" s="8" t="n"/>
       <c r="K442" s="8" t="n"/>
       <c r="L442" s="8" t="n"/>
-      <c r="M442" s="35" t="n">
-        <v>2439</v>
-      </c>
+      <c r="M442" s="8" t="n"/>
       <c r="N442" s="8" t="n"/>
     </row>
     <row r="443">
@@ -19088,9 +18755,7 @@
       <c r="J443" s="8" t="n"/>
       <c r="K443" s="8" t="n"/>
       <c r="L443" s="8" t="n"/>
-      <c r="M443" s="35" t="n">
-        <v>1880</v>
-      </c>
+      <c r="M443" s="8" t="n"/>
       <c r="N443" s="8" t="n"/>
     </row>
     <row r="444">
@@ -19124,9 +18789,7 @@
       <c r="J444" s="8" t="n"/>
       <c r="K444" s="8" t="n"/>
       <c r="L444" s="8" t="n"/>
-      <c r="M444" s="35" t="n">
-        <v>697</v>
-      </c>
+      <c r="M444" s="8" t="n"/>
       <c r="N444" s="8" t="n"/>
     </row>
     <row r="445">
@@ -19248,9 +18911,7 @@
       <c r="J447" s="8" t="n"/>
       <c r="K447" s="8" t="n"/>
       <c r="L447" s="8" t="n"/>
-      <c r="M447" s="35" t="n">
-        <v>2060</v>
-      </c>
+      <c r="M447" s="8" t="n"/>
       <c r="N447" s="8" t="n"/>
     </row>
     <row r="448">
@@ -19370,9 +19031,7 @@
       <c r="J450" s="8" t="n"/>
       <c r="K450" s="8" t="n"/>
       <c r="L450" s="8" t="n"/>
-      <c r="M450" s="35" t="n">
-        <v>1749</v>
-      </c>
+      <c r="M450" s="8" t="n"/>
       <c r="N450" s="8" t="n"/>
     </row>
     <row r="451">
@@ -19584,9 +19243,7 @@
       <c r="J455" s="8" t="n"/>
       <c r="K455" s="8" t="n"/>
       <c r="L455" s="8" t="n"/>
-      <c r="M455" s="35" t="n">
-        <v>5183</v>
-      </c>
+      <c r="M455" s="8" t="n"/>
       <c r="N455" s="8" t="n"/>
     </row>
     <row r="456">
@@ -19620,9 +19277,7 @@
       <c r="J456" s="8" t="n"/>
       <c r="K456" s="8" t="n"/>
       <c r="L456" s="8" t="n"/>
-      <c r="M456" s="35" t="n">
-        <v>4509</v>
-      </c>
+      <c r="M456" s="8" t="n"/>
       <c r="N456" s="8" t="n"/>
     </row>
     <row r="457">
@@ -19656,9 +19311,7 @@
       <c r="J457" s="8" t="n"/>
       <c r="K457" s="8" t="n"/>
       <c r="L457" s="8" t="n"/>
-      <c r="M457" s="35" t="n">
-        <v>2720</v>
-      </c>
+      <c r="M457" s="8" t="n"/>
       <c r="N457" s="8" t="n"/>
     </row>
     <row r="458">
@@ -19692,9 +19345,7 @@
       <c r="J458" s="8" t="n"/>
       <c r="K458" s="8" t="n"/>
       <c r="L458" s="8" t="n"/>
-      <c r="M458" s="35" t="n">
-        <v>1796</v>
-      </c>
+      <c r="M458" s="8" t="n"/>
       <c r="N458" s="8" t="n"/>
     </row>
     <row r="459">
@@ -19728,9 +19379,7 @@
       <c r="J459" s="8" t="n"/>
       <c r="K459" s="8" t="n"/>
       <c r="L459" s="8" t="n"/>
-      <c r="M459" s="35" t="n">
-        <v>1575</v>
-      </c>
+      <c r="M459" s="8" t="n"/>
       <c r="N459" s="8" t="n"/>
     </row>
     <row r="460">
@@ -20032,9 +19681,7 @@
       <c r="J466" s="8" t="n"/>
       <c r="K466" s="8" t="n"/>
       <c r="L466" s="8" t="n"/>
-      <c r="M466" s="35" t="n">
-        <v>5756</v>
-      </c>
+      <c r="M466" s="8" t="n"/>
       <c r="N466" s="8" t="n"/>
     </row>
     <row r="467">
@@ -20068,9 +19715,7 @@
       <c r="J467" s="8" t="n"/>
       <c r="K467" s="8" t="n"/>
       <c r="L467" s="8" t="n"/>
-      <c r="M467" s="35" t="n">
-        <v>908</v>
-      </c>
+      <c r="M467" s="8" t="n"/>
       <c r="N467" s="8" t="n"/>
     </row>
     <row r="468">
@@ -20104,9 +19749,7 @@
       <c r="J468" s="8" t="n"/>
       <c r="K468" s="8" t="n"/>
       <c r="L468" s="8" t="n"/>
-      <c r="M468" s="35" t="n">
-        <v>3015</v>
-      </c>
+      <c r="M468" s="8" t="n"/>
       <c r="N468" s="8" t="n"/>
     </row>
     <row r="469">
@@ -20140,9 +19783,7 @@
       <c r="J469" s="8" t="n"/>
       <c r="K469" s="8" t="n"/>
       <c r="L469" s="8" t="n"/>
-      <c r="M469" s="35" t="n">
-        <v>8605</v>
-      </c>
+      <c r="M469" s="8" t="n"/>
       <c r="N469" s="8" t="n"/>
     </row>
     <row r="470">
@@ -20176,9 +19817,7 @@
       <c r="J470" s="8" t="n"/>
       <c r="K470" s="8" t="n"/>
       <c r="L470" s="8" t="n"/>
-      <c r="M470" s="35" t="n">
-        <v>2420</v>
-      </c>
+      <c r="M470" s="8" t="n"/>
       <c r="N470" s="8" t="n"/>
     </row>
     <row r="471">
@@ -20432,9 +20071,7 @@
       <c r="J476" s="8" t="n"/>
       <c r="K476" s="8" t="n"/>
       <c r="L476" s="8" t="n"/>
-      <c r="M476" s="35" t="n">
-        <v>13158</v>
-      </c>
+      <c r="M476" s="8" t="n"/>
       <c r="N476" s="8" t="n"/>
     </row>
     <row r="477">
@@ -20514,9 +20151,7 @@
       <c r="J478" s="8" t="n"/>
       <c r="K478" s="8" t="n"/>
       <c r="L478" s="8" t="n"/>
-      <c r="M478" s="35" t="n">
-        <v>1073</v>
-      </c>
+      <c r="M478" s="8" t="n"/>
       <c r="N478" s="8" t="n"/>
     </row>
     <row r="479">
@@ -20680,9 +20315,7 @@
       <c r="J482" s="8" t="n"/>
       <c r="K482" s="8" t="n"/>
       <c r="L482" s="8" t="n"/>
-      <c r="M482" s="35" t="n">
-        <v>1088</v>
-      </c>
+      <c r="M482" s="8" t="n"/>
       <c r="N482" s="8" t="n"/>
     </row>
     <row r="483">
@@ -20716,9 +20349,7 @@
       <c r="J483" s="8" t="n"/>
       <c r="K483" s="8" t="n"/>
       <c r="L483" s="8" t="n"/>
-      <c r="M483" s="35" t="n">
-        <v>1591</v>
-      </c>
+      <c r="M483" s="8" t="n"/>
       <c r="N483" s="8" t="n"/>
     </row>
     <row r="484">
@@ -20798,9 +20429,7 @@
       <c r="J485" s="8" t="n"/>
       <c r="K485" s="8" t="n"/>
       <c r="L485" s="8" t="n"/>
-      <c r="M485" s="35" t="n">
-        <v>4586</v>
-      </c>
+      <c r="M485" s="8" t="n"/>
       <c r="N485" s="8" t="n"/>
     </row>
     <row r="486">
@@ -20834,9 +20463,7 @@
       <c r="J486" s="8" t="n"/>
       <c r="K486" s="8" t="n"/>
       <c r="L486" s="8" t="n"/>
-      <c r="M486" s="35" t="n">
-        <v>479</v>
-      </c>
+      <c r="M486" s="8" t="n"/>
       <c r="N486" s="8" t="n"/>
     </row>
     <row r="487">
@@ -20870,9 +20497,7 @@
       <c r="J487" s="8" t="n"/>
       <c r="K487" s="8" t="n"/>
       <c r="L487" s="8" t="n"/>
-      <c r="M487" s="35" t="n">
-        <v>250</v>
-      </c>
+      <c r="M487" s="8" t="n"/>
       <c r="N487" s="8" t="n"/>
     </row>
     <row r="488">
@@ -20948,9 +20573,7 @@
       <c r="J489" s="8" t="n"/>
       <c r="K489" s="8" t="n"/>
       <c r="L489" s="8" t="n"/>
-      <c r="M489" s="35" t="n">
-        <v>4881</v>
-      </c>
+      <c r="M489" s="8" t="n"/>
       <c r="N489" s="8" t="n"/>
     </row>
     <row r="490">
@@ -20984,9 +20607,7 @@
       <c r="J490" s="8" t="n"/>
       <c r="K490" s="8" t="n"/>
       <c r="L490" s="8" t="n"/>
-      <c r="M490" s="35" t="n">
-        <v>2230</v>
-      </c>
+      <c r="M490" s="8" t="n"/>
       <c r="N490" s="8" t="n"/>
     </row>
     <row r="491">
@@ -21020,9 +20641,7 @@
       <c r="J491" s="8" t="n"/>
       <c r="K491" s="8" t="n"/>
       <c r="L491" s="8" t="n"/>
-      <c r="M491" s="35" t="n">
-        <v>4592</v>
-      </c>
+      <c r="M491" s="8" t="n"/>
       <c r="N491" s="8" t="n"/>
     </row>
     <row r="492">
@@ -21056,9 +20675,7 @@
       <c r="J492" s="8" t="n"/>
       <c r="K492" s="8" t="n"/>
       <c r="L492" s="8" t="n"/>
-      <c r="M492" s="35" t="n">
-        <v>1913</v>
-      </c>
+      <c r="M492" s="8" t="n"/>
       <c r="N492" s="8" t="n"/>
     </row>
     <row r="493">
@@ -21092,9 +20709,7 @@
       <c r="J493" s="8" t="n"/>
       <c r="K493" s="8" t="n"/>
       <c r="L493" s="8" t="n"/>
-      <c r="M493" s="35" t="n">
-        <v>3141</v>
-      </c>
+      <c r="M493" s="8" t="n"/>
       <c r="N493" s="8" t="n"/>
     </row>
     <row r="494">
@@ -21128,9 +20743,7 @@
       <c r="J494" s="8" t="n"/>
       <c r="K494" s="8" t="n"/>
       <c r="L494" s="8" t="n"/>
-      <c r="M494" s="35" t="n">
-        <v>982</v>
-      </c>
+      <c r="M494" s="8" t="n"/>
       <c r="N494" s="8" t="n"/>
     </row>
     <row r="495">
@@ -21206,9 +20819,7 @@
       <c r="J496" s="8" t="n"/>
       <c r="K496" s="8" t="n"/>
       <c r="L496" s="8" t="n"/>
-      <c r="M496" s="35" t="n">
-        <v>4494</v>
-      </c>
+      <c r="M496" s="8" t="n"/>
       <c r="N496" s="8" t="n"/>
     </row>
     <row r="497">
@@ -21242,9 +20853,7 @@
       <c r="J497" s="8" t="n"/>
       <c r="K497" s="8" t="n"/>
       <c r="L497" s="8" t="n"/>
-      <c r="M497" s="35" t="n">
-        <v>1599</v>
-      </c>
+      <c r="M497" s="8" t="n"/>
       <c r="N497" s="8" t="n"/>
     </row>
     <row r="498">
@@ -21320,9 +20929,7 @@
       <c r="J499" s="8" t="n"/>
       <c r="K499" s="8" t="n"/>
       <c r="L499" s="8" t="n"/>
-      <c r="M499" s="35" t="n">
-        <v>899</v>
-      </c>
+      <c r="M499" s="8" t="n"/>
       <c r="N499" s="8" t="n"/>
     </row>
     <row r="500">
@@ -21356,9 +20963,7 @@
       <c r="J500" s="8" t="n"/>
       <c r="K500" s="8" t="n"/>
       <c r="L500" s="8" t="n"/>
-      <c r="M500" s="35" t="n">
-        <v>1220</v>
-      </c>
+      <c r="M500" s="8" t="n"/>
       <c r="N500" s="8" t="n"/>
     </row>
     <row r="501">
@@ -21392,9 +20997,7 @@
       <c r="J501" s="8" t="n"/>
       <c r="K501" s="8" t="n"/>
       <c r="L501" s="8" t="n"/>
-      <c r="M501" s="35" t="n">
-        <v>5007</v>
-      </c>
+      <c r="M501" s="8" t="n"/>
       <c r="N501" s="8" t="n"/>
     </row>
     <row r="502">
@@ -21428,9 +21031,7 @@
       <c r="J502" s="8" t="n"/>
       <c r="K502" s="8" t="n"/>
       <c r="L502" s="8" t="n"/>
-      <c r="M502" s="35" t="n">
-        <v>12656</v>
-      </c>
+      <c r="M502" s="8" t="n"/>
       <c r="N502" s="8" t="n"/>
     </row>
     <row r="503">
@@ -21464,9 +21065,7 @@
       <c r="J503" s="8" t="n"/>
       <c r="K503" s="8" t="n"/>
       <c r="L503" s="8" t="n"/>
-      <c r="M503" s="35" t="n">
-        <v>5359</v>
-      </c>
+      <c r="M503" s="8" t="n"/>
       <c r="N503" s="8" t="n"/>
     </row>
     <row r="504">
@@ -21500,9 +21099,7 @@
       <c r="J504" s="8" t="n"/>
       <c r="K504" s="8" t="n"/>
       <c r="L504" s="8" t="n"/>
-      <c r="M504" s="35" t="n">
-        <v>3961</v>
-      </c>
+      <c r="M504" s="8" t="n"/>
       <c r="N504" s="8" t="n"/>
     </row>
     <row r="505">
@@ -21536,9 +21133,7 @@
       <c r="J505" s="8" t="n"/>
       <c r="K505" s="8" t="n"/>
       <c r="L505" s="8" t="n"/>
-      <c r="M505" s="35" t="n">
-        <v>1615</v>
-      </c>
+      <c r="M505" s="8" t="n"/>
       <c r="N505" s="8" t="n"/>
     </row>
     <row r="506">
@@ -21614,9 +21209,7 @@
       <c r="J507" s="8" t="n"/>
       <c r="K507" s="8" t="n"/>
       <c r="L507" s="8" t="n"/>
-      <c r="M507" s="35" t="n">
-        <v>274</v>
-      </c>
+      <c r="M507" s="8" t="n"/>
       <c r="N507" s="8" t="n"/>
     </row>
     <row r="508">
@@ -21650,9 +21243,7 @@
       <c r="J508" s="8" t="n"/>
       <c r="K508" s="8" t="n"/>
       <c r="L508" s="8" t="n"/>
-      <c r="M508" s="35" t="n">
-        <v>1108</v>
-      </c>
+      <c r="M508" s="8" t="n"/>
       <c r="N508" s="8" t="n"/>
     </row>
     <row r="509">
@@ -21686,9 +21277,7 @@
       <c r="J509" s="8" t="n"/>
       <c r="K509" s="8" t="n"/>
       <c r="L509" s="8" t="n"/>
-      <c r="M509" s="35" t="n">
-        <v>279</v>
-      </c>
+      <c r="M509" s="8" t="n"/>
       <c r="N509" s="8" t="n"/>
     </row>
     <row r="510">
@@ -21722,9 +21311,7 @@
       <c r="J510" s="8" t="n"/>
       <c r="K510" s="8" t="n"/>
       <c r="L510" s="8" t="n"/>
-      <c r="M510" s="35" t="n">
-        <v>496</v>
-      </c>
+      <c r="M510" s="8" t="n"/>
       <c r="N510" s="8" t="n"/>
     </row>
     <row r="511">
@@ -21758,9 +21345,7 @@
       <c r="J511" s="8" t="n"/>
       <c r="K511" s="8" t="n"/>
       <c r="L511" s="8" t="n"/>
-      <c r="M511" s="35" t="n">
-        <v>2880</v>
-      </c>
+      <c r="M511" s="8" t="n"/>
       <c r="N511" s="8" t="n"/>
     </row>
     <row r="512">
@@ -21794,9 +21379,7 @@
       <c r="J512" s="8" t="n"/>
       <c r="K512" s="8" t="n"/>
       <c r="L512" s="8" t="n"/>
-      <c r="M512" s="35" t="n">
-        <v>8414</v>
-      </c>
+      <c r="M512" s="8" t="n"/>
       <c r="N512" s="8" t="n"/>
     </row>
     <row r="513">
@@ -21830,9 +21413,7 @@
       <c r="J513" s="8" t="n"/>
       <c r="K513" s="8" t="n"/>
       <c r="L513" s="8" t="n"/>
-      <c r="M513" s="35" t="n">
-        <v>456</v>
-      </c>
+      <c r="M513" s="8" t="n"/>
       <c r="N513" s="8" t="n"/>
     </row>
     <row r="514">
@@ -21866,9 +21447,7 @@
       <c r="J514" s="8" t="n"/>
       <c r="K514" s="8" t="n"/>
       <c r="L514" s="8" t="n"/>
-      <c r="M514" s="35" t="n">
-        <v>2736</v>
-      </c>
+      <c r="M514" s="8" t="n"/>
       <c r="N514" s="8" t="n"/>
     </row>
     <row r="515">
@@ -21944,9 +21523,7 @@
       <c r="J516" s="8" t="n"/>
       <c r="K516" s="8" t="n"/>
       <c r="L516" s="8" t="n"/>
-      <c r="M516" s="35" t="n">
-        <v>3475</v>
-      </c>
+      <c r="M516" s="8" t="n"/>
       <c r="N516" s="8" t="n"/>
     </row>
     <row r="517">
@@ -21980,9 +21557,7 @@
       <c r="J517" s="8" t="n"/>
       <c r="K517" s="8" t="n"/>
       <c r="L517" s="8" t="n"/>
-      <c r="M517" s="35" t="n">
-        <v>12647</v>
-      </c>
+      <c r="M517" s="8" t="n"/>
       <c r="N517" s="8" t="n"/>
     </row>
     <row r="518">
@@ -22016,9 +21591,7 @@
       <c r="J518" s="8" t="n"/>
       <c r="K518" s="8" t="n"/>
       <c r="L518" s="8" t="n"/>
-      <c r="M518" s="35" t="n">
-        <v>2</v>
-      </c>
+      <c r="M518" s="8" t="n"/>
       <c r="N518" s="8" t="n"/>
     </row>
     <row r="519">
@@ -22052,9 +21625,7 @@
       <c r="J519" s="8" t="n"/>
       <c r="K519" s="8" t="n"/>
       <c r="L519" s="8" t="n"/>
-      <c r="M519" s="35" t="n">
-        <v>7016</v>
-      </c>
+      <c r="M519" s="8" t="n"/>
       <c r="N519" s="8" t="n"/>
     </row>
     <row r="520">
@@ -22088,9 +21659,7 @@
       <c r="J520" s="8" t="n"/>
       <c r="K520" s="8" t="n"/>
       <c r="L520" s="8" t="n"/>
-      <c r="M520" s="35" t="n">
-        <v>4213</v>
-      </c>
+      <c r="M520" s="8" t="n"/>
       <c r="N520" s="8" t="n"/>
     </row>
     <row r="521">
@@ -22124,9 +21693,7 @@
       <c r="J521" s="8" t="n"/>
       <c r="K521" s="8" t="n"/>
       <c r="L521" s="8" t="n"/>
-      <c r="M521" s="35" t="n">
-        <v>3395</v>
-      </c>
+      <c r="M521" s="8" t="n"/>
       <c r="N521" s="8" t="n"/>
     </row>
     <row r="522">
@@ -22202,9 +21769,7 @@
       <c r="J523" s="8" t="n"/>
       <c r="K523" s="8" t="n"/>
       <c r="L523" s="8" t="n"/>
-      <c r="M523" s="35" t="n">
-        <v>587</v>
-      </c>
+      <c r="M523" s="8" t="n"/>
       <c r="N523" s="8" t="n"/>
     </row>
     <row r="524">
@@ -22238,9 +21803,7 @@
       <c r="J524" s="8" t="n"/>
       <c r="K524" s="8" t="n"/>
       <c r="L524" s="8" t="n"/>
-      <c r="M524" s="35" t="n">
-        <v>4596</v>
-      </c>
+      <c r="M524" s="8" t="n"/>
       <c r="N524" s="8" t="n"/>
     </row>
     <row r="525">
@@ -22274,9 +21837,7 @@
       <c r="J525" s="8" t="n"/>
       <c r="K525" s="8" t="n"/>
       <c r="L525" s="8" t="n"/>
-      <c r="M525" s="35" t="n">
-        <v>8733</v>
-      </c>
+      <c r="M525" s="8" t="n"/>
       <c r="N525" s="8" t="n"/>
     </row>
     <row r="526">
@@ -22310,9 +21871,7 @@
       <c r="J526" s="8" t="n"/>
       <c r="K526" s="8" t="n"/>
       <c r="L526" s="8" t="n"/>
-      <c r="M526" s="35" t="n">
-        <v>3166</v>
-      </c>
+      <c r="M526" s="8" t="n"/>
       <c r="N526" s="8" t="n"/>
     </row>
     <row r="527">
@@ -22346,9 +21905,7 @@
       <c r="J527" s="8" t="n"/>
       <c r="K527" s="8" t="n"/>
       <c r="L527" s="8" t="n"/>
-      <c r="M527" s="35" t="n">
-        <v>2821</v>
-      </c>
+      <c r="M527" s="8" t="n"/>
       <c r="N527" s="8" t="n"/>
     </row>
     <row r="528">
@@ -22382,9 +21939,7 @@
       <c r="J528" s="8" t="n"/>
       <c r="K528" s="8" t="n"/>
       <c r="L528" s="8" t="n"/>
-      <c r="M528" s="35" t="n">
-        <v>10328</v>
-      </c>
+      <c r="M528" s="8" t="n"/>
       <c r="N528" s="8" t="n"/>
     </row>
     <row r="529">
@@ -22418,9 +21973,7 @@
       <c r="J529" s="8" t="n"/>
       <c r="K529" s="8" t="n"/>
       <c r="L529" s="8" t="n"/>
-      <c r="M529" s="35" t="n">
-        <v>2061</v>
-      </c>
+      <c r="M529" s="8" t="n"/>
       <c r="N529" s="8" t="n"/>
     </row>
     <row r="530">
@@ -22454,9 +22007,7 @@
       <c r="J530" s="8" t="n"/>
       <c r="K530" s="8" t="n"/>
       <c r="L530" s="8" t="n"/>
-      <c r="M530" s="35" t="n">
-        <v>1121</v>
-      </c>
+      <c r="M530" s="8" t="n"/>
       <c r="N530" s="8" t="n"/>
     </row>
     <row r="531">
@@ -22490,9 +22041,7 @@
       <c r="J531" s="8" t="n"/>
       <c r="K531" s="8" t="n"/>
       <c r="L531" s="8" t="n"/>
-      <c r="M531" s="35" t="n">
-        <v>1550</v>
-      </c>
+      <c r="M531" s="8" t="n"/>
       <c r="N531" s="8" t="n"/>
     </row>
     <row r="532">
@@ -22526,9 +22075,7 @@
       <c r="J532" s="8" t="n"/>
       <c r="K532" s="8" t="n"/>
       <c r="L532" s="8" t="n"/>
-      <c r="M532" s="35" t="n">
-        <v>7317</v>
-      </c>
+      <c r="M532" s="8" t="n"/>
       <c r="N532" s="8" t="n"/>
     </row>
     <row r="533">
@@ -22562,9 +22109,7 @@
       <c r="J533" s="8" t="n"/>
       <c r="K533" s="8" t="n"/>
       <c r="L533" s="8" t="n"/>
-      <c r="M533" s="35" t="n">
-        <v>5784</v>
-      </c>
+      <c r="M533" s="8" t="n"/>
       <c r="N533" s="8" t="n"/>
     </row>
     <row r="534">
@@ -22598,9 +22143,7 @@
       <c r="J534" s="8" t="n"/>
       <c r="K534" s="8" t="n"/>
       <c r="L534" s="8" t="n"/>
-      <c r="M534" s="35" t="n">
-        <v>1838</v>
-      </c>
+      <c r="M534" s="8" t="n"/>
       <c r="N534" s="8" t="n"/>
     </row>
     <row r="535">
@@ -22634,9 +22177,7 @@
       <c r="J535" s="8" t="n"/>
       <c r="K535" s="8" t="n"/>
       <c r="L535" s="8" t="n"/>
-      <c r="M535" s="35" t="n">
-        <v>2992</v>
-      </c>
+      <c r="M535" s="8" t="n"/>
       <c r="N535" s="8" t="n"/>
     </row>
     <row r="536">
@@ -22670,9 +22211,7 @@
       <c r="J536" s="8" t="n"/>
       <c r="K536" s="8" t="n"/>
       <c r="L536" s="8" t="n"/>
-      <c r="M536" s="35" t="n">
-        <v>1383</v>
-      </c>
+      <c r="M536" s="8" t="n"/>
       <c r="N536" s="8" t="n"/>
     </row>
     <row r="537">
@@ -22706,9 +22245,7 @@
       <c r="J537" s="8" t="n"/>
       <c r="K537" s="8" t="n"/>
       <c r="L537" s="8" t="n"/>
-      <c r="M537" s="35" t="n">
-        <v>1837</v>
-      </c>
+      <c r="M537" s="8" t="n"/>
       <c r="N537" s="8" t="n"/>
     </row>
     <row r="538">
@@ -22742,9 +22279,7 @@
       <c r="J538" s="8" t="n"/>
       <c r="K538" s="8" t="n"/>
       <c r="L538" s="8" t="n"/>
-      <c r="M538" s="35" t="n">
-        <v>570</v>
-      </c>
+      <c r="M538" s="8" t="n"/>
       <c r="N538" s="8" t="n"/>
     </row>
     <row r="539">
@@ -22820,9 +22355,7 @@
       <c r="J540" s="8" t="n"/>
       <c r="K540" s="8" t="n"/>
       <c r="L540" s="8" t="n"/>
-      <c r="M540" s="35" t="n">
-        <v>3560</v>
-      </c>
+      <c r="M540" s="8" t="n"/>
       <c r="N540" s="8" t="n"/>
     </row>
     <row r="541">
@@ -22856,9 +22389,7 @@
       <c r="J541" s="8" t="n"/>
       <c r="K541" s="8" t="n"/>
       <c r="L541" s="8" t="n"/>
-      <c r="M541" s="35" t="n">
-        <v>2442</v>
-      </c>
+      <c r="M541" s="8" t="n"/>
       <c r="N541" s="8" t="n"/>
     </row>
     <row r="542">
@@ -22892,9 +22423,7 @@
       <c r="J542" s="8" t="n"/>
       <c r="K542" s="8" t="n"/>
       <c r="L542" s="8" t="n"/>
-      <c r="M542" s="35" t="n">
-        <v>298</v>
-      </c>
+      <c r="M542" s="8" t="n"/>
       <c r="N542" s="8" t="n"/>
     </row>
     <row r="543">
@@ -22928,9 +22457,7 @@
       <c r="J543" s="8" t="n"/>
       <c r="K543" s="8" t="n"/>
       <c r="L543" s="8" t="n"/>
-      <c r="M543" s="35" t="n">
-        <v>1076</v>
-      </c>
+      <c r="M543" s="8" t="n"/>
       <c r="N543" s="8" t="n"/>
     </row>
     <row r="544">
@@ -23006,9 +22533,7 @@
       <c r="J545" s="8" t="n"/>
       <c r="K545" s="8" t="n"/>
       <c r="L545" s="8" t="n"/>
-      <c r="M545" s="35" t="n">
-        <v>209</v>
-      </c>
+      <c r="M545" s="8" t="n"/>
       <c r="N545" s="8" t="n"/>
     </row>
     <row r="546">
@@ -23042,9 +22567,7 @@
       <c r="J546" s="8" t="n"/>
       <c r="K546" s="8" t="n"/>
       <c r="L546" s="8" t="n"/>
-      <c r="M546" s="35" t="n">
-        <v>2648</v>
-      </c>
+      <c r="M546" s="8" t="n"/>
       <c r="N546" s="8" t="n"/>
     </row>
     <row r="547">
@@ -23078,9 +22601,7 @@
       <c r="J547" s="8" t="n"/>
       <c r="K547" s="8" t="n"/>
       <c r="L547" s="8" t="n"/>
-      <c r="M547" s="35" t="n">
-        <v>1323</v>
-      </c>
+      <c r="M547" s="8" t="n"/>
       <c r="N547" s="8" t="n"/>
     </row>
     <row r="548">
@@ -23114,9 +22635,7 @@
       <c r="J548" s="8" t="n"/>
       <c r="K548" s="8" t="n"/>
       <c r="L548" s="8" t="n"/>
-      <c r="M548" s="35" t="n">
-        <v>1104</v>
-      </c>
+      <c r="M548" s="8" t="n"/>
       <c r="N548" s="8" t="n"/>
     </row>
     <row r="549">
@@ -23150,9 +22669,7 @@
       <c r="J549" s="8" t="n"/>
       <c r="K549" s="8" t="n"/>
       <c r="L549" s="8" t="n"/>
-      <c r="M549" s="35" t="n">
-        <v>954</v>
-      </c>
+      <c r="M549" s="8" t="n"/>
       <c r="N549" s="8" t="n"/>
     </row>
     <row r="550">
@@ -23186,9 +22703,7 @@
       <c r="J550" s="8" t="n"/>
       <c r="K550" s="8" t="n"/>
       <c r="L550" s="8" t="n"/>
-      <c r="M550" s="35" t="n">
-        <v>768</v>
-      </c>
+      <c r="M550" s="8" t="n"/>
       <c r="N550" s="8" t="n"/>
     </row>
     <row r="551">
@@ -23222,9 +22737,7 @@
       <c r="J551" s="8" t="n"/>
       <c r="K551" s="8" t="n"/>
       <c r="L551" s="8" t="n"/>
-      <c r="M551" s="35" t="n">
-        <v>383</v>
-      </c>
+      <c r="M551" s="8" t="n"/>
       <c r="N551" s="8" t="n"/>
     </row>
     <row r="552">
@@ -23258,9 +22771,7 @@
       <c r="J552" s="8" t="n"/>
       <c r="K552" s="8" t="n"/>
       <c r="L552" s="8" t="n"/>
-      <c r="M552" s="35" t="n">
-        <v>714</v>
-      </c>
+      <c r="M552" s="8" t="n"/>
       <c r="N552" s="8" t="n"/>
     </row>
     <row r="553">
@@ -23336,9 +22847,7 @@
       <c r="J554" s="8" t="n"/>
       <c r="K554" s="8" t="n"/>
       <c r="L554" s="8" t="n"/>
-      <c r="M554" s="35" t="n">
-        <v>2476</v>
-      </c>
+      <c r="M554" s="8" t="n"/>
       <c r="N554" s="8" t="n"/>
     </row>
     <row r="555">
@@ -23372,9 +22881,7 @@
       <c r="J555" s="8" t="n"/>
       <c r="K555" s="8" t="n"/>
       <c r="L555" s="8" t="n"/>
-      <c r="M555" s="35" t="n">
-        <v>1500</v>
-      </c>
+      <c r="M555" s="8" t="n"/>
       <c r="N555" s="8" t="n"/>
     </row>
     <row r="556">
@@ -23408,9 +22915,7 @@
       <c r="J556" s="8" t="n"/>
       <c r="K556" s="8" t="n"/>
       <c r="L556" s="8" t="n"/>
-      <c r="M556" s="35" t="n">
-        <v>8917</v>
-      </c>
+      <c r="M556" s="8" t="n"/>
       <c r="N556" s="8" t="n"/>
     </row>
     <row r="557">
@@ -23444,9 +22949,7 @@
       <c r="J557" s="8" t="n"/>
       <c r="K557" s="8" t="n"/>
       <c r="L557" s="8" t="n"/>
-      <c r="M557" s="35" t="n">
-        <v>1444</v>
-      </c>
+      <c r="M557" s="8" t="n"/>
       <c r="N557" s="8" t="n"/>
     </row>
     <row r="558">
@@ -23480,9 +22983,7 @@
       <c r="J558" s="8" t="n"/>
       <c r="K558" s="8" t="n"/>
       <c r="L558" s="8" t="n"/>
-      <c r="M558" s="35" t="n">
-        <v>889</v>
-      </c>
+      <c r="M558" s="8" t="n"/>
       <c r="N558" s="8" t="n"/>
     </row>
     <row r="559">
@@ -23516,9 +23017,7 @@
       <c r="J559" s="8" t="n"/>
       <c r="K559" s="8" t="n"/>
       <c r="L559" s="8" t="n"/>
-      <c r="M559" s="35" t="n">
-        <v>573</v>
-      </c>
+      <c r="M559" s="8" t="n"/>
       <c r="N559" s="8" t="n"/>
     </row>
     <row r="560">
@@ -23552,9 +23051,7 @@
       <c r="J560" s="8" t="n"/>
       <c r="K560" s="8" t="n"/>
       <c r="L560" s="8" t="n"/>
-      <c r="M560" s="35" t="n">
-        <v>3526</v>
-      </c>
+      <c r="M560" s="8" t="n"/>
       <c r="N560" s="8" t="n"/>
     </row>
     <row r="561">
@@ -23588,9 +23085,7 @@
       <c r="J561" s="8" t="n"/>
       <c r="K561" s="8" t="n"/>
       <c r="L561" s="8" t="n"/>
-      <c r="M561" s="35" t="n">
-        <v>1595</v>
-      </c>
+      <c r="M561" s="8" t="n"/>
       <c r="N561" s="8" t="n"/>
     </row>
     <row r="562">
@@ -23666,9 +23161,7 @@
       <c r="J563" s="8" t="n"/>
       <c r="K563" s="8" t="n"/>
       <c r="L563" s="8" t="n"/>
-      <c r="M563" s="35" t="n">
-        <v>2703</v>
-      </c>
+      <c r="M563" s="8" t="n"/>
       <c r="N563" s="8" t="n"/>
     </row>
     <row r="564">
@@ -23702,9 +23195,7 @@
       <c r="J564" s="8" t="n"/>
       <c r="K564" s="8" t="n"/>
       <c r="L564" s="8" t="n"/>
-      <c r="M564" s="35" t="n">
-        <v>6835</v>
-      </c>
+      <c r="M564" s="8" t="n"/>
       <c r="N564" s="8" t="n"/>
     </row>
     <row r="565">
@@ -23738,9 +23229,7 @@
       <c r="J565" s="8" t="n"/>
       <c r="K565" s="8" t="n"/>
       <c r="L565" s="8" t="n"/>
-      <c r="M565" s="35" t="n">
-        <v>6653</v>
-      </c>
+      <c r="M565" s="8" t="n"/>
       <c r="N565" s="8" t="n"/>
     </row>
     <row r="566">
@@ -23774,9 +23263,7 @@
       <c r="J566" s="8" t="n"/>
       <c r="K566" s="8" t="n"/>
       <c r="L566" s="8" t="n"/>
-      <c r="M566" s="35" t="n">
-        <v>2996</v>
-      </c>
+      <c r="M566" s="8" t="n"/>
       <c r="N566" s="8" t="n"/>
     </row>
     <row r="567">
@@ -23810,9 +23297,7 @@
       <c r="J567" s="8" t="n"/>
       <c r="K567" s="8" t="n"/>
       <c r="L567" s="8" t="n"/>
-      <c r="M567" s="35" t="n">
-        <v>20217</v>
-      </c>
+      <c r="M567" s="8" t="n"/>
       <c r="N567" s="8" t="n"/>
     </row>
     <row r="568">
@@ -23846,9 +23331,7 @@
       <c r="J568" s="8" t="n"/>
       <c r="K568" s="8" t="n"/>
       <c r="L568" s="8" t="n"/>
-      <c r="M568" s="35" t="n">
-        <v>737</v>
-      </c>
+      <c r="M568" s="8" t="n"/>
       <c r="N568" s="8" t="n"/>
     </row>
     <row r="569">
@@ -23924,9 +23407,7 @@
       <c r="J570" s="8" t="n"/>
       <c r="K570" s="8" t="n"/>
       <c r="L570" s="8" t="n"/>
-      <c r="M570" s="35" t="n">
-        <v>1372</v>
-      </c>
+      <c r="M570" s="8" t="n"/>
       <c r="N570" s="8" t="n"/>
     </row>
     <row r="571">
@@ -23960,9 +23441,7 @@
       <c r="J571" s="8" t="n"/>
       <c r="K571" s="8" t="n"/>
       <c r="L571" s="8" t="n"/>
-      <c r="M571" s="35" t="n">
-        <v>5442</v>
-      </c>
+      <c r="M571" s="8" t="n"/>
       <c r="N571" s="8" t="n"/>
     </row>
     <row r="572">
@@ -23996,9 +23475,7 @@
       <c r="J572" s="8" t="n"/>
       <c r="K572" s="8" t="n"/>
       <c r="L572" s="8" t="n"/>
-      <c r="M572" s="35" t="n">
-        <v>1512</v>
-      </c>
+      <c r="M572" s="8" t="n"/>
       <c r="N572" s="8" t="n"/>
     </row>
     <row r="573">
@@ -24032,9 +23509,7 @@
       <c r="J573" s="8" t="n"/>
       <c r="K573" s="8" t="n"/>
       <c r="L573" s="8" t="n"/>
-      <c r="M573" s="35" t="n">
-        <v>10103</v>
-      </c>
+      <c r="M573" s="8" t="n"/>
       <c r="N573" s="8" t="n"/>
     </row>
     <row r="574">
@@ -24068,9 +23543,7 @@
       <c r="J574" s="8" t="n"/>
       <c r="K574" s="8" t="n"/>
       <c r="L574" s="8" t="n"/>
-      <c r="M574" s="35" t="n">
-        <v>2812</v>
-      </c>
+      <c r="M574" s="8" t="n"/>
       <c r="N574" s="8" t="n"/>
     </row>
     <row r="575">
@@ -24104,9 +23577,7 @@
       <c r="J575" s="8" t="n"/>
       <c r="K575" s="8" t="n"/>
       <c r="L575" s="8" t="n"/>
-      <c r="M575" s="35" t="n">
-        <v>3876</v>
-      </c>
+      <c r="M575" s="8" t="n"/>
       <c r="N575" s="8" t="n"/>
     </row>
     <row r="576">
@@ -24140,9 +23611,7 @@
       <c r="J576" s="8" t="n"/>
       <c r="K576" s="8" t="n"/>
       <c r="L576" s="8" t="n"/>
-      <c r="M576" s="35" t="n">
-        <v>1288</v>
-      </c>
+      <c r="M576" s="8" t="n"/>
       <c r="N576" s="8" t="n"/>
     </row>
     <row r="577">
@@ -24176,9 +23645,7 @@
       <c r="J577" s="8" t="n"/>
       <c r="K577" s="8" t="n"/>
       <c r="L577" s="8" t="n"/>
-      <c r="M577" s="35" t="n">
-        <v>2442</v>
-      </c>
+      <c r="M577" s="8" t="n"/>
       <c r="N577" s="8" t="n"/>
     </row>
     <row r="578">
@@ -24212,9 +23679,7 @@
       <c r="J578" s="8" t="n"/>
       <c r="K578" s="8" t="n"/>
       <c r="L578" s="8" t="n"/>
-      <c r="M578" s="35" t="n">
-        <v>4002</v>
-      </c>
+      <c r="M578" s="8" t="n"/>
       <c r="N578" s="8" t="n"/>
     </row>
     <row r="579">
@@ -24248,9 +23713,7 @@
       <c r="J579" s="8" t="n"/>
       <c r="K579" s="8" t="n"/>
       <c r="L579" s="8" t="n"/>
-      <c r="M579" s="35" t="n">
-        <v>963</v>
-      </c>
+      <c r="M579" s="8" t="n"/>
       <c r="N579" s="8" t="n"/>
     </row>
     <row r="580">
@@ -24284,9 +23747,7 @@
       <c r="J580" s="8" t="n"/>
       <c r="K580" s="8" t="n"/>
       <c r="L580" s="8" t="n"/>
-      <c r="M580" s="35" t="n">
-        <v>1514</v>
-      </c>
+      <c r="M580" s="8" t="n"/>
       <c r="N580" s="8" t="n"/>
     </row>
     <row r="581">
@@ -24320,9 +23781,7 @@
       <c r="J581" s="8" t="n"/>
       <c r="K581" s="8" t="n"/>
       <c r="L581" s="8" t="n"/>
-      <c r="M581" s="35" t="n">
-        <v>3558</v>
-      </c>
+      <c r="M581" s="8" t="n"/>
       <c r="N581" s="8" t="n"/>
     </row>
     <row r="582">
@@ -24398,9 +23857,7 @@
       <c r="J583" s="8" t="n"/>
       <c r="K583" s="8" t="n"/>
       <c r="L583" s="8" t="n"/>
-      <c r="M583" s="35" t="n">
-        <v>2647</v>
-      </c>
+      <c r="M583" s="8" t="n"/>
       <c r="N583" s="8" t="n"/>
     </row>
     <row r="584">
@@ -24434,9 +23891,7 @@
       <c r="J584" s="8" t="n"/>
       <c r="K584" s="8" t="n"/>
       <c r="L584" s="8" t="n"/>
-      <c r="M584" s="35" t="n">
-        <v>1546</v>
-      </c>
+      <c r="M584" s="8" t="n"/>
       <c r="N584" s="8" t="n"/>
     </row>
     <row r="585">
@@ -24470,9 +23925,7 @@
       <c r="J585" s="8" t="n"/>
       <c r="K585" s="8" t="n"/>
       <c r="L585" s="8" t="n"/>
-      <c r="M585" s="35" t="n">
-        <v>4776</v>
-      </c>
+      <c r="M585" s="8" t="n"/>
       <c r="N585" s="8" t="n"/>
     </row>
     <row r="586">
@@ -24506,9 +23959,7 @@
       <c r="J586" s="8" t="n"/>
       <c r="K586" s="8" t="n"/>
       <c r="L586" s="8" t="n"/>
-      <c r="M586" s="35" t="n">
-        <v>1500</v>
-      </c>
+      <c r="M586" s="8" t="n"/>
       <c r="N586" s="8" t="n"/>
     </row>
     <row r="587">
@@ -24542,9 +23993,7 @@
       <c r="J587" s="8" t="n"/>
       <c r="K587" s="8" t="n"/>
       <c r="L587" s="8" t="n"/>
-      <c r="M587" s="35" t="n">
-        <v>2717</v>
-      </c>
+      <c r="M587" s="8" t="n"/>
       <c r="N587" s="8" t="n"/>
     </row>
     <row r="588">
@@ -24578,9 +24027,7 @@
       <c r="J588" s="8" t="n"/>
       <c r="K588" s="8" t="n"/>
       <c r="L588" s="8" t="n"/>
-      <c r="M588" s="35" t="n">
-        <v>1970</v>
-      </c>
+      <c r="M588" s="8" t="n"/>
       <c r="N588" s="8" t="n"/>
     </row>
     <row r="589">
@@ -24614,9 +24061,7 @@
       <c r="J589" s="8" t="n"/>
       <c r="K589" s="8" t="n"/>
       <c r="L589" s="8" t="n"/>
-      <c r="M589" s="35" t="n">
-        <v>2554</v>
-      </c>
+      <c r="M589" s="8" t="n"/>
       <c r="N589" s="8" t="n"/>
     </row>
     <row r="590">
@@ -24650,9 +24095,7 @@
       <c r="J590" s="8" t="n"/>
       <c r="K590" s="8" t="n"/>
       <c r="L590" s="8" t="n"/>
-      <c r="M590" s="35" t="n">
-        <v>582</v>
-      </c>
+      <c r="M590" s="8" t="n"/>
       <c r="N590" s="8" t="n"/>
     </row>
     <row r="591">
@@ -24686,9 +24129,7 @@
       <c r="J591" s="8" t="n"/>
       <c r="K591" s="8" t="n"/>
       <c r="L591" s="8" t="n"/>
-      <c r="M591" s="35" t="n">
-        <v>1651</v>
-      </c>
+      <c r="M591" s="8" t="n"/>
       <c r="N591" s="8" t="n"/>
     </row>
     <row r="592">
@@ -24722,9 +24163,7 @@
       <c r="J592" s="8" t="n"/>
       <c r="K592" s="8" t="n"/>
       <c r="L592" s="8" t="n"/>
-      <c r="M592" s="35" t="n">
-        <v>1722</v>
-      </c>
+      <c r="M592" s="8" t="n"/>
       <c r="N592" s="8" t="n"/>
     </row>
     <row r="593">
@@ -24758,9 +24197,7 @@
       <c r="J593" s="8" t="n"/>
       <c r="K593" s="8" t="n"/>
       <c r="L593" s="8" t="n"/>
-      <c r="M593" s="35" t="n">
-        <v>10411</v>
-      </c>
+      <c r="M593" s="8" t="n"/>
       <c r="N593" s="8" t="n"/>
     </row>
     <row r="594">
@@ -24794,9 +24231,7 @@
       <c r="J594" s="8" t="n"/>
       <c r="K594" s="8" t="n"/>
       <c r="L594" s="8" t="n"/>
-      <c r="M594" s="35" t="n">
-        <v>728</v>
-      </c>
+      <c r="M594" s="8" t="n"/>
       <c r="N594" s="8" t="n"/>
     </row>
     <row r="595">
@@ -24830,9 +24265,7 @@
       <c r="J595" s="8" t="n"/>
       <c r="K595" s="8" t="n"/>
       <c r="L595" s="8" t="n"/>
-      <c r="M595" s="35" t="n">
-        <v>4807</v>
-      </c>
+      <c r="M595" s="8" t="n"/>
       <c r="N595" s="8" t="n"/>
     </row>
     <row r="596">
@@ -24866,9 +24299,7 @@
       <c r="J596" s="8" t="n"/>
       <c r="K596" s="8" t="n"/>
       <c r="L596" s="8" t="n"/>
-      <c r="M596" s="35" t="n">
-        <v>1016</v>
-      </c>
+      <c r="M596" s="8" t="n"/>
       <c r="N596" s="8" t="n"/>
     </row>
     <row r="597">
@@ -24944,9 +24375,7 @@
       <c r="J598" s="8" t="n"/>
       <c r="K598" s="8" t="n"/>
       <c r="L598" s="8" t="n"/>
-      <c r="M598" s="35" t="n">
-        <v>1363</v>
-      </c>
+      <c r="M598" s="8" t="n"/>
       <c r="N598" s="8" t="n"/>
     </row>
     <row r="599">
@@ -24980,9 +24409,7 @@
       <c r="J599" s="8" t="n"/>
       <c r="K599" s="8" t="n"/>
       <c r="L599" s="8" t="n"/>
-      <c r="M599" s="35" t="n">
-        <v>3567</v>
-      </c>
+      <c r="M599" s="8" t="n"/>
       <c r="N599" s="8" t="n"/>
     </row>
     <row r="600">
@@ -25016,9 +24443,7 @@
       <c r="J600" s="8" t="n"/>
       <c r="K600" s="8" t="n"/>
       <c r="L600" s="8" t="n"/>
-      <c r="M600" s="35" t="n">
-        <v>1086</v>
-      </c>
+      <c r="M600" s="8" t="n"/>
       <c r="N600" s="8" t="n"/>
     </row>
     <row r="601">
@@ -25052,9 +24477,7 @@
       <c r="J601" s="8" t="n"/>
       <c r="K601" s="8" t="n"/>
       <c r="L601" s="8" t="n"/>
-      <c r="M601" s="35" t="n">
-        <v>2720</v>
-      </c>
+      <c r="M601" s="8" t="n"/>
       <c r="N601" s="8" t="n"/>
     </row>
     <row r="602">
@@ -25088,9 +24511,7 @@
       <c r="J602" s="8" t="n"/>
       <c r="K602" s="8" t="n"/>
       <c r="L602" s="8" t="n"/>
-      <c r="M602" s="35" t="n">
-        <v>595</v>
-      </c>
+      <c r="M602" s="8" t="n"/>
       <c r="N602" s="8" t="n"/>
     </row>
     <row r="603">
@@ -25124,9 +24545,7 @@
       <c r="J603" s="8" t="n"/>
       <c r="K603" s="8" t="n"/>
       <c r="L603" s="8" t="n"/>
-      <c r="M603" s="35" t="n">
-        <v>14128</v>
-      </c>
+      <c r="M603" s="8" t="n"/>
       <c r="N603" s="8" t="n"/>
     </row>
     <row r="604">
@@ -25202,9 +24621,7 @@
       <c r="J605" s="8" t="n"/>
       <c r="K605" s="8" t="n"/>
       <c r="L605" s="8" t="n"/>
-      <c r="M605" s="35" t="n">
-        <v>233</v>
-      </c>
+      <c r="M605" s="8" t="n"/>
       <c r="N605" s="8" t="n"/>
     </row>
     <row r="606">
@@ -25238,9 +24655,7 @@
       <c r="J606" s="8" t="n"/>
       <c r="K606" s="8" t="n"/>
       <c r="L606" s="8" t="n"/>
-      <c r="M606" s="35" t="n">
-        <v>1628</v>
-      </c>
+      <c r="M606" s="8" t="n"/>
       <c r="N606" s="8" t="n"/>
     </row>
     <row r="607">
@@ -25274,9 +24689,7 @@
       <c r="J607" s="8" t="n"/>
       <c r="K607" s="8" t="n"/>
       <c r="L607" s="8" t="n"/>
-      <c r="M607" s="35" t="n">
-        <v>137</v>
-      </c>
+      <c r="M607" s="8" t="n"/>
       <c r="N607" s="8" t="n"/>
     </row>
     <row r="608">
@@ -25310,9 +24723,7 @@
       <c r="J608" s="8" t="n"/>
       <c r="K608" s="8" t="n"/>
       <c r="L608" s="8" t="n"/>
-      <c r="M608" s="35" t="n">
-        <v>3436</v>
-      </c>
+      <c r="M608" s="8" t="n"/>
       <c r="N608" s="8" t="n"/>
     </row>
     <row r="609">
@@ -25346,9 +24757,7 @@
       <c r="J609" s="8" t="n"/>
       <c r="K609" s="16" t="n"/>
       <c r="L609" s="8" t="n"/>
-      <c r="M609" s="35" t="n">
-        <v>5772</v>
-      </c>
+      <c r="M609" s="8" t="n"/>
       <c r="N609" s="8" t="n"/>
     </row>
     <row r="610">
@@ -25424,9 +24833,7 @@
       <c r="J611" s="8" t="n"/>
       <c r="K611" s="8" t="n"/>
       <c r="L611" s="8" t="n"/>
-      <c r="M611" s="35" t="n">
-        <v>7330</v>
-      </c>
+      <c r="M611" s="8" t="n"/>
       <c r="N611" s="8" t="n"/>
     </row>
     <row r="612">
@@ -25460,9 +24867,7 @@
       <c r="J612" s="8" t="n"/>
       <c r="K612" s="8" t="n"/>
       <c r="L612" s="8" t="n"/>
-      <c r="M612" s="35" t="n">
-        <v>2141</v>
-      </c>
+      <c r="M612" s="8" t="n"/>
       <c r="N612" s="8" t="n"/>
     </row>
     <row r="613">
@@ -25496,9 +24901,7 @@
       <c r="J613" s="8" t="n"/>
       <c r="K613" s="8" t="n"/>
       <c r="L613" s="8" t="n"/>
-      <c r="M613" s="35" t="n">
-        <v>7657</v>
-      </c>
+      <c r="M613" s="8" t="n"/>
       <c r="N613" s="8" t="n"/>
     </row>
     <row r="614">
@@ -25532,9 +24935,7 @@
       <c r="J614" s="8" t="n"/>
       <c r="K614" s="8" t="n"/>
       <c r="L614" s="8" t="n"/>
-      <c r="M614" s="35" t="n">
-        <v>3456</v>
-      </c>
+      <c r="M614" s="8" t="n"/>
       <c r="N614" s="8" t="n"/>
     </row>
     <row r="615">
@@ -25568,9 +24969,7 @@
       <c r="J615" s="8" t="n"/>
       <c r="K615" s="8" t="n"/>
       <c r="L615" s="8" t="n"/>
-      <c r="M615" s="35" t="n">
-        <v>2600</v>
-      </c>
+      <c r="M615" s="8" t="n"/>
       <c r="N615" s="8" t="n"/>
     </row>
     <row r="616">
@@ -25604,9 +25003,7 @@
       <c r="J616" s="8" t="n"/>
       <c r="K616" s="8" t="n"/>
       <c r="L616" s="8" t="n"/>
-      <c r="M616" s="35" t="n">
-        <v>2260</v>
-      </c>
+      <c r="M616" s="8" t="n"/>
       <c r="N616" s="8" t="n"/>
     </row>
     <row r="617">
@@ -25640,9 +25037,7 @@
       <c r="J617" s="8" t="n"/>
       <c r="K617" s="8" t="n"/>
       <c r="L617" s="8" t="n"/>
-      <c r="M617" s="35" t="n">
-        <v>2703</v>
-      </c>
+      <c r="M617" s="8" t="n"/>
       <c r="N617" s="8" t="n"/>
     </row>
     <row r="618">
@@ -25676,9 +25071,7 @@
       <c r="J618" s="8" t="n"/>
       <c r="K618" s="8" t="n"/>
       <c r="L618" s="8" t="n"/>
-      <c r="M618" s="35" t="n">
-        <v>10052</v>
-      </c>
+      <c r="M618" s="8" t="n"/>
       <c r="N618" s="8" t="n"/>
     </row>
     <row r="619">
@@ -25712,9 +25105,7 @@
       <c r="J619" s="8" t="n"/>
       <c r="K619" s="8" t="n"/>
       <c r="L619" s="8" t="n"/>
-      <c r="M619" s="35" t="n">
-        <v>2403</v>
-      </c>
+      <c r="M619" s="8" t="n"/>
       <c r="N619" s="8" t="n"/>
     </row>
     <row r="620">
@@ -25748,9 +25139,7 @@
       <c r="J620" s="8" t="n"/>
       <c r="K620" s="8" t="n"/>
       <c r="L620" s="8" t="n"/>
-      <c r="M620" s="35" t="n">
-        <v>496</v>
-      </c>
+      <c r="M620" s="8" t="n"/>
       <c r="N620" s="8" t="n"/>
     </row>
     <row r="621">
@@ -25784,9 +25173,7 @@
       <c r="J621" s="8" t="n"/>
       <c r="K621" s="8" t="n"/>
       <c r="L621" s="8" t="n"/>
-      <c r="M621" s="35" t="n">
-        <v>2873</v>
-      </c>
+      <c r="M621" s="8" t="n"/>
       <c r="N621" s="8" t="n"/>
     </row>
     <row r="622">
@@ -25820,9 +25207,7 @@
       <c r="J622" s="8" t="n"/>
       <c r="K622" s="8" t="n"/>
       <c r="L622" s="8" t="n"/>
-      <c r="M622" s="35" t="n">
-        <v>590</v>
-      </c>
+      <c r="M622" s="8" t="n"/>
       <c r="N622" s="8" t="n"/>
     </row>
     <row r="623">
@@ -25856,9 +25241,7 @@
       <c r="J623" s="8" t="n"/>
       <c r="K623" s="8" t="n"/>
       <c r="L623" s="8" t="n"/>
-      <c r="M623" s="35" t="n">
-        <v>992</v>
-      </c>
+      <c r="M623" s="8" t="n"/>
       <c r="N623" s="8" t="n"/>
     </row>
     <row r="624">
@@ -25938,9 +25321,7 @@
       <c r="J625" s="8" t="n"/>
       <c r="K625" s="8" t="n"/>
       <c r="L625" s="8" t="n"/>
-      <c r="M625" s="35" t="n">
-        <v>2045</v>
-      </c>
+      <c r="M625" s="8" t="n"/>
       <c r="N625" s="8" t="n"/>
     </row>
     <row r="626">
@@ -25974,9 +25355,7 @@
       <c r="J626" s="8" t="n"/>
       <c r="K626" s="8" t="n"/>
       <c r="L626" s="8" t="n"/>
-      <c r="M626" s="35" t="n">
-        <v>5145</v>
-      </c>
+      <c r="M626" s="8" t="n"/>
       <c r="N626" s="8" t="n"/>
     </row>
     <row r="627">
@@ -26010,9 +25389,7 @@
       <c r="J627" s="8" t="n"/>
       <c r="K627" s="8" t="n"/>
       <c r="L627" s="8" t="n"/>
-      <c r="M627" s="35" t="n">
-        <v>6755</v>
-      </c>
+      <c r="M627" s="8" t="n"/>
       <c r="N627" s="8" t="n"/>
     </row>
     <row r="628">
@@ -26046,9 +25423,7 @@
       <c r="J628" s="8" t="n"/>
       <c r="K628" s="8" t="n"/>
       <c r="L628" s="8" t="n"/>
-      <c r="M628" s="35" t="n">
-        <v>4560</v>
-      </c>
+      <c r="M628" s="8" t="n"/>
       <c r="N628" s="8" t="n"/>
     </row>
     <row r="629">
@@ -26082,9 +25457,7 @@
       <c r="J629" s="8" t="n"/>
       <c r="K629" s="8" t="n"/>
       <c r="L629" s="8" t="n"/>
-      <c r="M629" s="35" t="n">
-        <v>4525</v>
-      </c>
+      <c r="M629" s="8" t="n"/>
       <c r="N629" s="8" t="n"/>
     </row>
     <row r="630">
@@ -26118,9 +25491,7 @@
       <c r="J630" s="8" t="n"/>
       <c r="K630" s="8" t="n"/>
       <c r="L630" s="8" t="n"/>
-      <c r="M630" s="35" t="n">
-        <v>9337</v>
-      </c>
+      <c r="M630" s="8" t="n"/>
       <c r="N630" s="8" t="n"/>
     </row>
     <row r="631">
@@ -26154,9 +25525,7 @@
       <c r="J631" s="8" t="n"/>
       <c r="K631" s="8" t="n"/>
       <c r="L631" s="8" t="n"/>
-      <c r="M631" s="35" t="n">
-        <v>446</v>
-      </c>
+      <c r="M631" s="8" t="n"/>
       <c r="N631" s="8" t="n"/>
     </row>
     <row r="632">
@@ -26232,9 +25601,7 @@
       <c r="J633" s="8" t="n"/>
       <c r="K633" s="8" t="n"/>
       <c r="L633" s="8" t="n"/>
-      <c r="M633" s="35" t="n">
-        <v>2283</v>
-      </c>
+      <c r="M633" s="8" t="n"/>
       <c r="N633" s="8" t="n"/>
     </row>
     <row r="634">
@@ -26310,9 +25677,7 @@
       <c r="J635" s="8" t="n"/>
       <c r="K635" s="8" t="n"/>
       <c r="L635" s="8" t="n"/>
-      <c r="M635" s="35" t="n">
-        <v>602</v>
-      </c>
+      <c r="M635" s="8" t="n"/>
       <c r="N635" s="8" t="n"/>
     </row>
     <row r="636">
@@ -26346,9 +25711,7 @@
       <c r="J636" s="8" t="n"/>
       <c r="K636" s="8" t="n"/>
       <c r="L636" s="8" t="n"/>
-      <c r="M636" s="35" t="n">
-        <v>3431</v>
-      </c>
+      <c r="M636" s="8" t="n"/>
       <c r="N636" s="8" t="n"/>
     </row>
     <row r="637">
@@ -26382,9 +25745,7 @@
       <c r="J637" s="8" t="n"/>
       <c r="K637" s="8" t="n"/>
       <c r="L637" s="8" t="n"/>
-      <c r="M637" s="35" t="n">
-        <v>6242</v>
-      </c>
+      <c r="M637" s="8" t="n"/>
       <c r="N637" s="8" t="n"/>
     </row>
     <row r="638">
@@ -26418,9 +25779,7 @@
       <c r="J638" s="8" t="n"/>
       <c r="K638" s="8" t="n"/>
       <c r="L638" s="8" t="n"/>
-      <c r="M638" s="35" t="n">
-        <v>1404</v>
-      </c>
+      <c r="M638" s="8" t="n"/>
       <c r="N638" s="8" t="n"/>
     </row>
     <row r="639">
@@ -26454,9 +25813,7 @@
       <c r="J639" s="8" t="n"/>
       <c r="K639" s="8" t="n"/>
       <c r="L639" s="8" t="n"/>
-      <c r="M639" s="35" t="n">
-        <v>4596</v>
-      </c>
+      <c r="M639" s="8" t="n"/>
       <c r="N639" s="8" t="n"/>
     </row>
     <row r="640">
@@ -26490,9 +25847,7 @@
       <c r="J640" s="8" t="n"/>
       <c r="K640" s="8" t="n"/>
       <c r="L640" s="8" t="n"/>
-      <c r="M640" s="35" t="n">
-        <v>1663</v>
-      </c>
+      <c r="M640" s="8" t="n"/>
       <c r="N640" s="8" t="n"/>
     </row>
     <row r="641">
@@ -26526,9 +25881,7 @@
       <c r="J641" s="8" t="n"/>
       <c r="K641" s="8" t="n"/>
       <c r="L641" s="8" t="n"/>
-      <c r="M641" s="35" t="n">
-        <v>608</v>
-      </c>
+      <c r="M641" s="8" t="n"/>
       <c r="N641" s="8" t="n"/>
     </row>
     <row r="642">
@@ -26562,9 +25915,7 @@
       <c r="J642" s="8" t="n"/>
       <c r="K642" s="8" t="n"/>
       <c r="L642" s="8" t="n"/>
-      <c r="M642" s="35" t="n">
-        <v>820</v>
-      </c>
+      <c r="M642" s="8" t="n"/>
       <c r="N642" s="8" t="n"/>
     </row>
     <row r="643">
@@ -26598,9 +25949,7 @@
       <c r="J643" s="8" t="n"/>
       <c r="K643" s="8" t="n"/>
       <c r="L643" s="8" t="n"/>
-      <c r="M643" s="35" t="n">
-        <v>3868</v>
-      </c>
+      <c r="M643" s="8" t="n"/>
       <c r="N643" s="8" t="n"/>
     </row>
     <row r="644">
@@ -26634,9 +25983,7 @@
       <c r="J644" s="8" t="n"/>
       <c r="K644" s="8" t="n"/>
       <c r="L644" s="8" t="n"/>
-      <c r="M644" s="35" t="n">
-        <v>9774</v>
-      </c>
+      <c r="M644" s="8" t="n"/>
       <c r="N644" s="8" t="n"/>
     </row>
     <row r="645">
@@ -26670,9 +26017,7 @@
       <c r="J645" s="8" t="n"/>
       <c r="K645" s="8" t="n"/>
       <c r="L645" s="8" t="n"/>
-      <c r="M645" s="35" t="n">
-        <v>5400</v>
-      </c>
+      <c r="M645" s="8" t="n"/>
       <c r="N645" s="8" t="n"/>
     </row>
     <row r="646">
@@ -26706,9 +26051,7 @@
       <c r="J646" s="8" t="n"/>
       <c r="K646" s="8" t="n"/>
       <c r="L646" s="8" t="n"/>
-      <c r="M646" s="35" t="n">
-        <v>12439</v>
-      </c>
+      <c r="M646" s="8" t="n"/>
       <c r="N646" s="8" t="n"/>
     </row>
     <row r="647">
@@ -26742,9 +26085,7 @@
       <c r="J647" s="8" t="n"/>
       <c r="K647" s="8" t="n"/>
       <c r="L647" s="8" t="n"/>
-      <c r="M647" s="35" t="n">
-        <v>9190</v>
-      </c>
+      <c r="M647" s="8" t="n"/>
       <c r="N647" s="8" t="n"/>
     </row>
     <row r="648">
@@ -26778,9 +26119,7 @@
       <c r="J648" s="8" t="n"/>
       <c r="K648" s="8" t="n"/>
       <c r="L648" s="8" t="n"/>
-      <c r="M648" s="35" t="n">
-        <v>3654</v>
-      </c>
+      <c r="M648" s="8" t="n"/>
       <c r="N648" s="8" t="n"/>
     </row>
     <row r="649">
@@ -26814,9 +26153,7 @@
       <c r="J649" s="8" t="n"/>
       <c r="K649" s="8" t="n"/>
       <c r="L649" s="8" t="n"/>
-      <c r="M649" s="35" t="n">
-        <v>13642</v>
-      </c>
+      <c r="M649" s="8" t="n"/>
       <c r="N649" s="8" t="n"/>
     </row>
     <row r="650">
@@ -26850,9 +26187,7 @@
       <c r="J650" s="8" t="n"/>
       <c r="K650" s="8" t="n"/>
       <c r="L650" s="8" t="n"/>
-      <c r="M650" s="35" t="n">
-        <v>636</v>
-      </c>
+      <c r="M650" s="8" t="n"/>
       <c r="N650" s="8" t="n"/>
     </row>
     <row r="651">
@@ -26886,9 +26221,7 @@
       <c r="J651" s="8" t="n"/>
       <c r="K651" s="8" t="n"/>
       <c r="L651" s="8" t="n"/>
-      <c r="M651" s="35" t="n">
-        <v>138</v>
-      </c>
+      <c r="M651" s="8" t="n"/>
       <c r="N651" s="8" t="n"/>
     </row>
     <row r="652">
@@ -26922,9 +26255,7 @@
       <c r="J652" s="8" t="n"/>
       <c r="K652" s="8" t="n"/>
       <c r="L652" s="8" t="n"/>
-      <c r="M652" s="35" t="n">
-        <v>1111</v>
-      </c>
+      <c r="M652" s="8" t="n"/>
       <c r="N652" s="8" t="n"/>
     </row>
     <row r="653">
@@ -27000,9 +26331,7 @@
       <c r="J654" s="8" t="n"/>
       <c r="K654" s="8" t="n"/>
       <c r="L654" s="8" t="n"/>
-      <c r="M654" s="35" t="n">
-        <v>20229</v>
-      </c>
+      <c r="M654" s="8" t="n"/>
       <c r="N654" s="8" t="n"/>
     </row>
     <row r="655">
@@ -27036,9 +26365,7 @@
       <c r="J655" s="8" t="n"/>
       <c r="K655" s="8" t="n"/>
       <c r="L655" s="8" t="n"/>
-      <c r="M655" s="35" t="n">
-        <v>1021</v>
-      </c>
+      <c r="M655" s="8" t="n"/>
       <c r="N655" s="8" t="n"/>
     </row>
     <row r="656">
@@ -27072,9 +26399,7 @@
       <c r="J656" s="8" t="n"/>
       <c r="K656" s="8" t="n"/>
       <c r="L656" s="8" t="n"/>
-      <c r="M656" s="35" t="n">
-        <v>4076</v>
-      </c>
+      <c r="M656" s="8" t="n"/>
       <c r="N656" s="8" t="n"/>
     </row>
     <row r="657">
@@ -27108,9 +26433,7 @@
       <c r="J657" s="8" t="n"/>
       <c r="K657" s="8" t="n"/>
       <c r="L657" s="8" t="n"/>
-      <c r="M657" s="35" t="n">
-        <v>1404</v>
-      </c>
+      <c r="M657" s="8" t="n"/>
       <c r="N657" s="8" t="n"/>
     </row>
     <row r="658">
@@ -27144,9 +26467,7 @@
       <c r="J658" s="8" t="n"/>
       <c r="K658" s="8" t="n"/>
       <c r="L658" s="8" t="n"/>
-      <c r="M658" s="35" t="n">
-        <v>2263</v>
-      </c>
+      <c r="M658" s="8" t="n"/>
       <c r="N658" s="8" t="n"/>
     </row>
     <row r="659">
@@ -27180,9 +26501,7 @@
       <c r="J659" s="8" t="n"/>
       <c r="K659" s="8" t="n"/>
       <c r="L659" s="8" t="n"/>
-      <c r="M659" s="35" t="n">
-        <v>4593</v>
-      </c>
+      <c r="M659" s="8" t="n"/>
       <c r="N659" s="8" t="n"/>
     </row>
     <row r="660">
@@ -27216,9 +26535,7 @@
       <c r="J660" s="8" t="n"/>
       <c r="K660" s="8" t="n"/>
       <c r="L660" s="8" t="n"/>
-      <c r="M660" s="35" t="n">
-        <v>908</v>
-      </c>
+      <c r="M660" s="8" t="n"/>
       <c r="N660" s="8" t="n"/>
     </row>
     <row r="661">
@@ -27252,9 +26569,7 @@
       <c r="J661" s="8" t="n"/>
       <c r="K661" s="8" t="n"/>
       <c r="L661" s="8" t="n"/>
-      <c r="M661" s="35" t="n">
-        <v>7247</v>
-      </c>
+      <c r="M661" s="8" t="n"/>
       <c r="N661" s="8" t="n"/>
     </row>
     <row r="662">
@@ -27288,9 +26603,7 @@
       <c r="J662" s="8" t="n"/>
       <c r="K662" s="8" t="n"/>
       <c r="L662" s="8" t="n"/>
-      <c r="M662" s="35" t="n">
-        <v>1849</v>
-      </c>
+      <c r="M662" s="8" t="n"/>
       <c r="N662" s="8" t="n"/>
     </row>
     <row r="663">
@@ -27324,9 +26637,7 @@
       <c r="J663" s="8" t="n"/>
       <c r="K663" s="8" t="n"/>
       <c r="L663" s="8" t="n"/>
-      <c r="M663" s="35" t="n">
-        <v>1180</v>
-      </c>
+      <c r="M663" s="8" t="n"/>
       <c r="N663" s="8" t="n"/>
     </row>
     <row r="664">
@@ -27360,9 +26671,7 @@
       <c r="J664" s="8" t="n"/>
       <c r="K664" s="8" t="n"/>
       <c r="L664" s="8" t="n"/>
-      <c r="M664" s="35" t="n">
-        <v>2892</v>
-      </c>
+      <c r="M664" s="8" t="n"/>
       <c r="N664" s="8" t="n"/>
     </row>
     <row r="665">
@@ -27396,9 +26705,7 @@
       <c r="J665" s="8" t="n"/>
       <c r="K665" s="8" t="n"/>
       <c r="L665" s="8" t="n"/>
-      <c r="M665" s="35" t="n">
-        <v>786</v>
-      </c>
+      <c r="M665" s="8" t="n"/>
       <c r="N665" s="8" t="n"/>
     </row>
     <row r="666">
@@ -27432,9 +26739,7 @@
       <c r="J666" s="8" t="n"/>
       <c r="K666" s="8" t="n"/>
       <c r="L666" s="8" t="n"/>
-      <c r="M666" s="35" t="n">
-        <v>3533</v>
-      </c>
+      <c r="M666" s="8" t="n"/>
       <c r="N666" s="8" t="n"/>
     </row>
     <row r="667">
@@ -27468,9 +26773,7 @@
       <c r="J667" s="8" t="n"/>
       <c r="K667" s="8" t="n"/>
       <c r="L667" s="8" t="n"/>
-      <c r="M667" s="35" t="n">
-        <v>1644</v>
-      </c>
+      <c r="M667" s="8" t="n"/>
       <c r="N667" s="8" t="n"/>
     </row>
     <row r="668">
@@ -27504,9 +26807,7 @@
       <c r="J668" s="8" t="n"/>
       <c r="K668" s="8" t="n"/>
       <c r="L668" s="8" t="n"/>
-      <c r="M668" s="35" t="n">
-        <v>1239</v>
-      </c>
+      <c r="M668" s="8" t="n"/>
       <c r="N668" s="8" t="n"/>
     </row>
     <row r="669">
@@ -27540,9 +26841,7 @@
       <c r="J669" s="8" t="n"/>
       <c r="K669" s="8" t="n"/>
       <c r="L669" s="8" t="n"/>
-      <c r="M669" s="35" t="n">
-        <v>5904</v>
-      </c>
+      <c r="M669" s="8" t="n"/>
       <c r="N669" s="8" t="n"/>
     </row>
     <row r="670">
@@ -27576,9 +26875,7 @@
       <c r="J670" s="8" t="n"/>
       <c r="K670" s="11" t="n"/>
       <c r="L670" s="8" t="n"/>
-      <c r="M670" s="35" t="n">
-        <v>7650</v>
-      </c>
+      <c r="M670" s="8" t="n"/>
       <c r="N670" s="8" t="n"/>
     </row>
     <row r="671">
@@ -27612,9 +26909,7 @@
       <c r="J671" s="8" t="n"/>
       <c r="K671" s="8" t="n"/>
       <c r="L671" s="8" t="n"/>
-      <c r="M671" s="35" t="n">
-        <v>1112</v>
-      </c>
+      <c r="M671" s="8" t="n"/>
       <c r="N671" s="8" t="n"/>
     </row>
     <row r="672">
@@ -27648,9 +26943,7 @@
       <c r="J672" s="8" t="n"/>
       <c r="K672" s="8" t="n"/>
       <c r="L672" s="8" t="n"/>
-      <c r="M672" s="35" t="n">
-        <v>280</v>
-      </c>
+      <c r="M672" s="8" t="n"/>
       <c r="N672" s="8" t="n"/>
     </row>
     <row r="673">
@@ -27684,9 +26977,7 @@
       <c r="J673" s="8" t="n"/>
       <c r="K673" s="8" t="n"/>
       <c r="L673" s="8" t="n"/>
-      <c r="M673" s="35" t="n">
-        <v>1458</v>
-      </c>
+      <c r="M673" s="8" t="n"/>
       <c r="N673" s="8" t="n"/>
     </row>
     <row r="674">
@@ -27720,9 +27011,7 @@
       <c r="J674" s="8" t="n"/>
       <c r="K674" s="8" t="n"/>
       <c r="L674" s="8" t="n"/>
-      <c r="M674" s="35" t="n">
-        <v>528</v>
-      </c>
+      <c r="M674" s="8" t="n"/>
       <c r="N674" s="8" t="n"/>
     </row>
     <row r="675">
@@ -27756,9 +27045,7 @@
       <c r="J675" s="8" t="n"/>
       <c r="K675" s="8" t="n"/>
       <c r="L675" s="8" t="n"/>
-      <c r="M675" s="35" t="n">
-        <v>708</v>
-      </c>
+      <c r="M675" s="8" t="n"/>
       <c r="N675" s="8" t="n"/>
     </row>
     <row r="676">
@@ -27792,9 +27079,7 @@
       <c r="J676" s="8" t="n"/>
       <c r="K676" s="8" t="n"/>
       <c r="L676" s="8" t="n"/>
-      <c r="M676" s="35" t="n">
-        <v>540</v>
-      </c>
+      <c r="M676" s="8" t="n"/>
       <c r="N676" s="8" t="n"/>
     </row>
     <row r="677">
@@ -27828,9 +27113,7 @@
       <c r="J677" s="8" t="n"/>
       <c r="K677" s="8" t="n"/>
       <c r="L677" s="8" t="n"/>
-      <c r="M677" s="35" t="n">
-        <v>2784</v>
-      </c>
+      <c r="M677" s="8" t="n"/>
       <c r="N677" s="8" t="n"/>
     </row>
     <row r="678">
@@ -27864,9 +27147,7 @@
       <c r="J678" s="8" t="n"/>
       <c r="K678" s="8" t="n"/>
       <c r="L678" s="8" t="n"/>
-      <c r="M678" s="35" t="n">
-        <v>473</v>
-      </c>
+      <c r="M678" s="8" t="n"/>
       <c r="N678" s="8" t="n"/>
     </row>
     <row r="679">
@@ -27900,9 +27181,7 @@
       <c r="J679" s="8" t="n"/>
       <c r="K679" s="8" t="n"/>
       <c r="L679" s="8" t="n"/>
-      <c r="M679" s="35" t="n">
-        <v>927</v>
-      </c>
+      <c r="M679" s="8" t="n"/>
       <c r="N679" s="8" t="n"/>
     </row>
     <row r="680">
@@ -27936,9 +27215,7 @@
       <c r="J680" s="8" t="n"/>
       <c r="K680" s="8" t="n"/>
       <c r="L680" s="8" t="n"/>
-      <c r="M680" s="35" t="n">
-        <v>3855</v>
-      </c>
+      <c r="M680" s="8" t="n"/>
       <c r="N680" s="8" t="n"/>
     </row>
     <row r="681">
@@ -27972,9 +27249,7 @@
       <c r="J681" s="8" t="n"/>
       <c r="K681" s="11" t="n"/>
       <c r="L681" s="8" t="n"/>
-      <c r="M681" s="35" t="n">
-        <v>2195</v>
-      </c>
+      <c r="M681" s="8" t="n"/>
       <c r="N681" s="8" t="n"/>
     </row>
     <row r="682">
@@ -28008,9 +27283,7 @@
       <c r="J682" s="8" t="n"/>
       <c r="K682" s="8" t="n"/>
       <c r="L682" s="8" t="n"/>
-      <c r="M682" s="35" t="n">
-        <v>1375</v>
-      </c>
+      <c r="M682" s="8" t="n"/>
       <c r="N682" s="8" t="n"/>
     </row>
     <row r="683">
@@ -28044,9 +27317,7 @@
       <c r="J683" s="8" t="n"/>
       <c r="K683" s="8" t="n"/>
       <c r="L683" s="8" t="n"/>
-      <c r="M683" s="35" t="n">
-        <v>400</v>
-      </c>
+      <c r="M683" s="8" t="n"/>
       <c r="N683" s="8" t="n"/>
     </row>
     <row r="684">
@@ -28080,9 +27351,7 @@
       <c r="J684" s="8" t="n"/>
       <c r="K684" s="8" t="n"/>
       <c r="L684" s="8" t="n"/>
-      <c r="M684" s="35" t="n">
-        <v>415</v>
-      </c>
+      <c r="M684" s="8" t="n"/>
       <c r="N684" s="8" t="n"/>
     </row>
     <row r="685">
@@ -28116,9 +27385,7 @@
       <c r="J685" s="8" t="n"/>
       <c r="K685" s="8" t="n"/>
       <c r="L685" s="8" t="n"/>
-      <c r="M685" s="35" t="n">
-        <v>457</v>
-      </c>
+      <c r="M685" s="8" t="n"/>
       <c r="N685" s="8" t="n"/>
     </row>
     <row r="686">
@@ -28152,9 +27419,7 @@
       <c r="J686" s="8" t="n"/>
       <c r="K686" s="8" t="n"/>
       <c r="L686" s="8" t="n"/>
-      <c r="M686" s="35" t="n">
-        <v>223</v>
-      </c>
+      <c r="M686" s="8" t="n"/>
       <c r="N686" s="8" t="n"/>
     </row>
     <row r="687">
@@ -28188,9 +27453,7 @@
       <c r="J687" s="8" t="n"/>
       <c r="K687" s="8" t="n"/>
       <c r="L687" s="8" t="n"/>
-      <c r="M687" s="35" t="n">
-        <v>2424</v>
-      </c>
+      <c r="M687" s="8" t="n"/>
       <c r="N687" s="8" t="n"/>
     </row>
     <row r="688">
@@ -28224,9 +27487,7 @@
       <c r="J688" s="8" t="n"/>
       <c r="K688" s="8" t="n"/>
       <c r="L688" s="8" t="n"/>
-      <c r="M688" s="35" t="n">
-        <v>760</v>
-      </c>
+      <c r="M688" s="8" t="n"/>
       <c r="N688" s="8" t="n"/>
     </row>
     <row r="689">
@@ -28260,9 +27521,7 @@
       <c r="J689" s="8" t="n"/>
       <c r="K689" s="8" t="n"/>
       <c r="L689" s="8" t="n"/>
-      <c r="M689" s="35" t="n">
-        <v>1016</v>
-      </c>
+      <c r="M689" s="8" t="n"/>
       <c r="N689" s="8" t="n"/>
     </row>
     <row r="690">
@@ -28296,9 +27555,7 @@
       <c r="J690" s="8" t="n"/>
       <c r="K690" s="8" t="n"/>
       <c r="L690" s="8" t="n"/>
-      <c r="M690" s="35" t="n">
-        <v>2452</v>
-      </c>
+      <c r="M690" s="8" t="n"/>
       <c r="N690" s="8" t="n"/>
     </row>
     <row r="691">
@@ -28332,9 +27589,7 @@
       <c r="J691" s="8" t="n"/>
       <c r="K691" s="8" t="n"/>
       <c r="L691" s="8" t="n"/>
-      <c r="M691" s="35" t="n">
-        <v>198</v>
-      </c>
+      <c r="M691" s="8" t="n"/>
       <c r="N691" s="8" t="n"/>
     </row>
     <row r="692">
@@ -28368,9 +27623,7 @@
       <c r="J692" s="8" t="n"/>
       <c r="K692" s="8" t="n"/>
       <c r="L692" s="8" t="n"/>
-      <c r="M692" s="35" t="n">
-        <v>443</v>
-      </c>
+      <c r="M692" s="8" t="n"/>
       <c r="N692" s="8" t="n"/>
     </row>
     <row r="693">
@@ -28404,9 +27657,7 @@
       <c r="J693" s="8" t="n"/>
       <c r="K693" s="8" t="n"/>
       <c r="L693" s="8" t="n"/>
-      <c r="M693" s="35" t="n">
-        <v>1725</v>
-      </c>
+      <c r="M693" s="8" t="n"/>
       <c r="N693" s="8" t="n"/>
     </row>
     <row r="694">
@@ -28440,9 +27691,7 @@
       <c r="J694" s="8" t="n"/>
       <c r="K694" s="8" t="n"/>
       <c r="L694" s="8" t="n"/>
-      <c r="M694" s="35" t="n">
-        <v>4827</v>
-      </c>
+      <c r="M694" s="8" t="n"/>
       <c r="N694" s="8" t="n"/>
     </row>
     <row r="695">
@@ -28476,9 +27725,7 @@
       <c r="J695" s="8" t="n"/>
       <c r="K695" s="8" t="n"/>
       <c r="L695" s="8" t="n"/>
-      <c r="M695" s="35" t="n">
-        <v>2253</v>
-      </c>
+      <c r="M695" s="8" t="n"/>
       <c r="N695" s="8" t="n"/>
     </row>
     <row r="696">
@@ -28512,9 +27759,7 @@
       <c r="J696" s="8" t="n"/>
       <c r="K696" s="8" t="n"/>
       <c r="L696" s="17" t="n"/>
-      <c r="M696" s="35" t="n">
-        <v>249</v>
-      </c>
+      <c r="M696" s="8" t="n"/>
       <c r="N696" s="8" t="n"/>
     </row>
     <row r="697">
@@ -28548,9 +27793,7 @@
       <c r="J697" s="8" t="n"/>
       <c r="K697" s="8" t="n"/>
       <c r="L697" s="8" t="n"/>
-      <c r="M697" s="35" t="n">
-        <v>3257</v>
-      </c>
+      <c r="M697" s="8" t="n"/>
       <c r="N697" s="8" t="n"/>
     </row>
     <row r="698">
@@ -28584,9 +27827,7 @@
       <c r="J698" s="8" t="n"/>
       <c r="K698" s="8" t="n"/>
       <c r="L698" s="8" t="n"/>
-      <c r="M698" s="35" t="n">
-        <v>2827</v>
-      </c>
+      <c r="M698" s="8" t="n"/>
       <c r="N698" s="8" t="n"/>
     </row>
     <row r="699">
@@ -28620,9 +27861,7 @@
       <c r="J699" s="8" t="n"/>
       <c r="K699" s="8" t="n"/>
       <c r="L699" s="8" t="n"/>
-      <c r="M699" s="35" t="n">
-        <v>1930</v>
-      </c>
+      <c r="M699" s="8" t="n"/>
       <c r="N699" s="8" t="n"/>
     </row>
     <row r="700">
@@ -28656,9 +27895,7 @@
       <c r="J700" s="8" t="n"/>
       <c r="K700" s="8" t="n"/>
       <c r="L700" s="8" t="n"/>
-      <c r="M700" s="35" t="n">
-        <v>161</v>
-      </c>
+      <c r="M700" s="8" t="n"/>
       <c r="N700" s="8" t="n"/>
     </row>
     <row r="701">
@@ -28692,9 +27929,7 @@
       <c r="J701" s="8" t="n"/>
       <c r="K701" s="8" t="n"/>
       <c r="L701" s="8" t="n"/>
-      <c r="M701" s="35" t="n">
-        <v>2810</v>
-      </c>
+      <c r="M701" s="8" t="n"/>
       <c r="N701" s="8" t="n"/>
     </row>
     <row r="702">
@@ -28728,9 +27963,7 @@
       <c r="J702" s="8" t="n"/>
       <c r="K702" s="8" t="n"/>
       <c r="L702" s="8" t="n"/>
-      <c r="M702" s="35" t="n">
-        <v>340</v>
-      </c>
+      <c r="M702" s="8" t="n"/>
       <c r="N702" s="8" t="n"/>
     </row>
     <row r="703">
@@ -28764,9 +27997,7 @@
       <c r="J703" s="8" t="n"/>
       <c r="K703" s="8" t="n"/>
       <c r="L703" s="8" t="n"/>
-      <c r="M703" s="35" t="n">
-        <v>3644</v>
-      </c>
+      <c r="M703" s="8" t="n"/>
       <c r="N703" s="8" t="n"/>
     </row>
     <row r="704">
@@ -28800,9 +28031,7 @@
       <c r="J704" s="8" t="n"/>
       <c r="K704" s="8" t="n"/>
       <c r="L704" s="8" t="n"/>
-      <c r="M704" s="35" t="n">
-        <v>425</v>
-      </c>
+      <c r="M704" s="8" t="n"/>
       <c r="N704" s="8" t="n"/>
     </row>
     <row r="705">
@@ -28836,9 +28065,7 @@
       <c r="J705" s="8" t="n"/>
       <c r="K705" s="8" t="n"/>
       <c r="L705" s="8" t="n"/>
-      <c r="M705" s="35" t="n">
-        <v>5545</v>
-      </c>
+      <c r="M705" s="8" t="n"/>
       <c r="N705" s="8" t="n"/>
     </row>
     <row r="706">
@@ -28872,9 +28099,7 @@
       <c r="J706" s="8" t="n"/>
       <c r="K706" s="8" t="n"/>
       <c r="L706" s="8" t="n"/>
-      <c r="M706" s="35" t="n">
-        <v>996</v>
-      </c>
+      <c r="M706" s="8" t="n"/>
       <c r="N706" s="8" t="n"/>
     </row>
     <row r="707">
@@ -28908,9 +28133,7 @@
       <c r="J707" s="8" t="n"/>
       <c r="K707" s="8" t="n"/>
       <c r="L707" s="8" t="n"/>
-      <c r="M707" s="35" t="n">
-        <v>1544</v>
-      </c>
+      <c r="M707" s="8" t="n"/>
       <c r="N707" s="8" t="n"/>
     </row>
     <row r="708">
@@ -28944,9 +28167,7 @@
       <c r="J708" s="8" t="n"/>
       <c r="K708" s="8" t="n"/>
       <c r="L708" s="8" t="n"/>
-      <c r="M708" s="35" t="n">
-        <v>12818</v>
-      </c>
+      <c r="M708" s="8" t="n"/>
       <c r="N708" s="8" t="n"/>
     </row>
     <row r="709">
@@ -28980,9 +28201,7 @@
       <c r="J709" s="8" t="n"/>
       <c r="K709" s="8" t="n"/>
       <c r="L709" s="8" t="n"/>
-      <c r="M709" s="35" t="n">
-        <v>2922</v>
-      </c>
+      <c r="M709" s="8" t="n"/>
       <c r="N709" s="8" t="n"/>
     </row>
     <row r="710">
@@ -29016,9 +28235,7 @@
       <c r="J710" s="8" t="n"/>
       <c r="K710" s="8" t="n"/>
       <c r="L710" s="8" t="n"/>
-      <c r="M710" s="35" t="n">
-        <v>4077</v>
-      </c>
+      <c r="M710" s="8" t="n"/>
       <c r="N710" s="8" t="n"/>
     </row>
     <row r="711">
@@ -29052,9 +28269,7 @@
       <c r="J711" s="8" t="n"/>
       <c r="K711" s="8" t="n"/>
       <c r="L711" s="8" t="n"/>
-      <c r="M711" s="35" t="n">
-        <v>240</v>
-      </c>
+      <c r="M711" s="8" t="n"/>
       <c r="N711" s="8" t="n"/>
     </row>
     <row r="712">
@@ -29088,9 +28303,7 @@
       <c r="J712" s="8" t="n"/>
       <c r="K712" s="8" t="n"/>
       <c r="L712" s="8" t="n"/>
-      <c r="M712" s="35" t="n">
-        <v>1728</v>
-      </c>
+      <c r="M712" s="8" t="n"/>
       <c r="N712" s="8" t="n"/>
     </row>
     <row r="713">
@@ -29124,9 +28337,7 @@
       <c r="J713" s="8" t="n"/>
       <c r="K713" s="8" t="n"/>
       <c r="L713" s="8" t="n"/>
-      <c r="M713" s="35" t="n">
-        <v>695</v>
-      </c>
+      <c r="M713" s="8" t="n"/>
       <c r="N713" s="8" t="n"/>
     </row>
     <row r="714">
@@ -29160,9 +28371,7 @@
       <c r="J714" s="8" t="n"/>
       <c r="K714" s="8" t="n"/>
       <c r="L714" s="8" t="n"/>
-      <c r="M714" s="35" t="n">
-        <v>200</v>
-      </c>
+      <c r="M714" s="8" t="n"/>
       <c r="N714" s="8" t="n"/>
     </row>
     <row r="715">
@@ -29196,9 +28405,7 @@
       <c r="J715" s="8" t="n"/>
       <c r="K715" s="8" t="n"/>
       <c r="L715" s="8" t="n"/>
-      <c r="M715" s="35" t="n">
-        <v>493</v>
-      </c>
+      <c r="M715" s="8" t="n"/>
       <c r="N715" s="8" t="n"/>
     </row>
     <row r="716">
@@ -29232,9 +28439,7 @@
       <c r="J716" s="8" t="n"/>
       <c r="K716" s="8" t="n"/>
       <c r="L716" s="8" t="n"/>
-      <c r="M716" s="35" t="n">
-        <v>1036</v>
-      </c>
+      <c r="M716" s="8" t="n"/>
       <c r="N716" s="8" t="n"/>
     </row>
     <row r="717">
@@ -29262,19 +28467,11 @@
       <c r="F717" s="8" t="n">
         <v>2009</v>
       </c>
-      <c r="G717" s="32" t="n"/>
-      <c r="H717" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I717" s="32" t="inlineStr"/>
-      <c r="J717" s="33" t="n">
-        <v>3884</v>
-      </c>
-      <c r="K717" s="34" t="n">
-        <v>3884</v>
-      </c>
+      <c r="G717" s="8" t="n"/>
+      <c r="H717" s="8" t="n"/>
+      <c r="I717" s="8" t="n"/>
+      <c r="J717" s="8" t="n"/>
+      <c r="K717" s="8" t="n"/>
       <c r="L717" s="8" t="n"/>
       <c r="M717" s="8" t="n"/>
       <c r="N717" s="8" t="n"/>
@@ -29310,9 +28507,7 @@
       <c r="J718" s="8" t="n"/>
       <c r="K718" s="8" t="n"/>
       <c r="L718" s="8" t="n"/>
-      <c r="M718" s="35" t="n">
-        <v>530</v>
-      </c>
+      <c r="M718" s="8" t="n"/>
       <c r="N718" s="8" t="n"/>
     </row>
     <row r="719">
@@ -29346,9 +28541,7 @@
       <c r="J719" s="8" t="n"/>
       <c r="K719" s="8" t="n"/>
       <c r="L719" s="8" t="n"/>
-      <c r="M719" s="35" t="n">
-        <v>1329</v>
-      </c>
+      <c r="M719" s="8" t="n"/>
       <c r="N719" s="8" t="n"/>
     </row>
     <row r="720">
@@ -29382,9 +28575,7 @@
       <c r="J720" s="8" t="n"/>
       <c r="K720" s="8" t="n"/>
       <c r="L720" s="8" t="n"/>
-      <c r="M720" s="35" t="n">
-        <v>280</v>
-      </c>
+      <c r="M720" s="8" t="n"/>
       <c r="N720" s="8" t="n"/>
     </row>
     <row r="721">
@@ -29418,9 +28609,7 @@
       <c r="J721" s="8" t="n"/>
       <c r="K721" s="8" t="n"/>
       <c r="L721" s="17" t="n"/>
-      <c r="M721" s="35" t="n">
-        <v>4123</v>
-      </c>
+      <c r="M721" s="8" t="n"/>
       <c r="N721" s="8" t="n"/>
     </row>
     <row r="722">
@@ -29454,9 +28643,7 @@
       <c r="J722" s="8" t="n"/>
       <c r="K722" s="8" t="n"/>
       <c r="L722" s="17" t="n"/>
-      <c r="M722" s="35" t="n">
-        <v>784</v>
-      </c>
+      <c r="M722" s="8" t="n"/>
       <c r="N722" s="8" t="n"/>
     </row>
     <row r="723">
@@ -29490,9 +28677,7 @@
       <c r="J723" s="8" t="n"/>
       <c r="K723" s="8" t="n"/>
       <c r="L723" s="8" t="n"/>
-      <c r="M723" s="35" t="n">
-        <v>1262</v>
-      </c>
+      <c r="M723" s="8" t="n"/>
       <c r="N723" s="8" t="n"/>
     </row>
     <row r="724">
@@ -29526,9 +28711,7 @@
       <c r="J724" s="8" t="n"/>
       <c r="K724" s="8" t="n"/>
       <c r="L724" s="8" t="n"/>
-      <c r="M724" s="35" t="n">
-        <v>263</v>
-      </c>
+      <c r="M724" s="8" t="n"/>
       <c r="N724" s="8" t="n"/>
     </row>
     <row r="725">
@@ -29562,9 +28745,7 @@
       <c r="J725" s="8" t="n"/>
       <c r="K725" s="8" t="n"/>
       <c r="L725" s="8" t="n"/>
-      <c r="M725" s="35" t="n">
-        <v>4795</v>
-      </c>
+      <c r="M725" s="8" t="n"/>
       <c r="N725" s="8" t="n"/>
     </row>
     <row r="726">
@@ -29598,9 +28779,7 @@
       <c r="J726" s="8" t="n"/>
       <c r="K726" s="8" t="n"/>
       <c r="L726" s="17" t="n"/>
-      <c r="M726" s="35" t="n">
-        <v>289</v>
-      </c>
+      <c r="M726" s="8" t="n"/>
       <c r="N726" s="8" t="n"/>
     </row>
     <row r="727">
@@ -29634,9 +28813,7 @@
       <c r="J727" s="8" t="n"/>
       <c r="K727" s="8" t="n"/>
       <c r="L727" s="8" t="n"/>
-      <c r="M727" s="35" t="n">
-        <v>252</v>
-      </c>
+      <c r="M727" s="8" t="n"/>
       <c r="N727" s="8" t="n"/>
     </row>
     <row r="728">
@@ -29670,9 +28847,7 @@
       <c r="J728" s="8" t="n"/>
       <c r="K728" s="8" t="n"/>
       <c r="L728" s="8" t="n"/>
-      <c r="M728" s="35" t="n">
-        <v>773</v>
-      </c>
+      <c r="M728" s="8" t="n"/>
       <c r="N728" s="8" t="n"/>
     </row>
     <row r="729">
@@ -29706,9 +28881,7 @@
       <c r="J729" s="8" t="n"/>
       <c r="K729" s="8" t="n"/>
       <c r="L729" s="8" t="n"/>
-      <c r="M729" s="35" t="n">
-        <v>2398</v>
-      </c>
+      <c r="M729" s="8" t="n"/>
       <c r="N729" s="8" t="n"/>
     </row>
     <row r="730">
@@ -29742,9 +28915,7 @@
       <c r="J730" s="8" t="n"/>
       <c r="K730" s="8" t="n"/>
       <c r="L730" s="8" t="n"/>
-      <c r="M730" s="35" t="n">
-        <v>1</v>
-      </c>
+      <c r="M730" s="8" t="n"/>
       <c r="N730" s="8" t="n"/>
     </row>
     <row r="731">
@@ -29778,9 +28949,7 @@
       <c r="J731" s="8" t="n"/>
       <c r="K731" s="8" t="n"/>
       <c r="L731" s="8" t="n"/>
-      <c r="M731" s="35" t="n">
-        <v>296</v>
-      </c>
+      <c r="M731" s="8" t="n"/>
       <c r="N731" s="8" t="n"/>
     </row>
     <row r="732">
@@ -29814,9 +28983,7 @@
       <c r="J732" s="8" t="n"/>
       <c r="K732" s="8" t="n"/>
       <c r="L732" s="8" t="n"/>
-      <c r="M732" s="35" t="n">
-        <v>242</v>
-      </c>
+      <c r="M732" s="8" t="n"/>
       <c r="N732" s="8" t="n"/>
     </row>
     <row r="733">
@@ -29850,9 +29017,7 @@
       <c r="J733" s="8" t="n"/>
       <c r="K733" s="8" t="n"/>
       <c r="L733" s="8" t="n"/>
-      <c r="M733" s="35" t="n">
-        <v>596</v>
-      </c>
+      <c r="M733" s="8" t="n"/>
       <c r="N733" s="8" t="n"/>
     </row>
     <row r="734">
@@ -29886,9 +29051,7 @@
       <c r="J734" s="8" t="n"/>
       <c r="K734" s="8" t="n"/>
       <c r="L734" s="8" t="n"/>
-      <c r="M734" s="35" t="n">
-        <v>330</v>
-      </c>
+      <c r="M734" s="8" t="n"/>
       <c r="N734" s="8" t="n"/>
     </row>
     <row r="735">
@@ -29922,9 +29085,7 @@
       <c r="J735" s="8" t="n"/>
       <c r="K735" s="8" t="n"/>
       <c r="L735" s="8" t="n"/>
-      <c r="M735" s="35" t="n">
-        <v>213</v>
-      </c>
+      <c r="M735" s="8" t="n"/>
       <c r="N735" s="8" t="n"/>
     </row>
     <row r="736">
@@ -29958,9 +29119,7 @@
       <c r="J736" s="8" t="n"/>
       <c r="K736" s="8" t="n"/>
       <c r="L736" s="8" t="n"/>
-      <c r="M736" s="35" t="n">
-        <v>2218</v>
-      </c>
+      <c r="M736" s="8" t="n"/>
       <c r="N736" s="8" t="n"/>
     </row>
     <row r="737">
@@ -29994,9 +29153,7 @@
       <c r="J737" s="8" t="n"/>
       <c r="K737" s="8" t="n"/>
       <c r="L737" s="8" t="n"/>
-      <c r="M737" s="35" t="n">
-        <v>2144</v>
-      </c>
+      <c r="M737" s="8" t="n"/>
       <c r="N737" s="8" t="n"/>
     </row>
     <row r="738">
@@ -30030,9 +29187,7 @@
       <c r="J738" s="8" t="n"/>
       <c r="K738" s="8" t="n"/>
       <c r="L738" s="8" t="n"/>
-      <c r="M738" s="35" t="n">
-        <v>1167</v>
-      </c>
+      <c r="M738" s="8" t="n"/>
       <c r="N738" s="8" t="n"/>
     </row>
     <row r="739">
@@ -30066,9 +29221,7 @@
       <c r="J739" s="8" t="n"/>
       <c r="K739" s="8" t="n"/>
       <c r="L739" s="8" t="n"/>
-      <c r="M739" s="35" t="n">
-        <v>480</v>
-      </c>
+      <c r="M739" s="8" t="n"/>
       <c r="N739" s="8" t="n"/>
     </row>
     <row r="740">
@@ -30102,9 +29255,7 @@
       <c r="J740" s="8" t="n"/>
       <c r="K740" s="8" t="n"/>
       <c r="L740" s="8" t="n"/>
-      <c r="M740" s="35" t="n">
-        <v>1512</v>
-      </c>
+      <c r="M740" s="8" t="n"/>
       <c r="N740" s="8" t="n"/>
     </row>
     <row r="741">
@@ -30138,9 +29289,7 @@
       <c r="J741" s="8" t="n"/>
       <c r="K741" s="8" t="n"/>
       <c r="L741" s="8" t="n"/>
-      <c r="M741" s="35" t="n">
-        <v>1862</v>
-      </c>
+      <c r="M741" s="8" t="n"/>
       <c r="N741" s="8" t="n"/>
     </row>
     <row r="742">
@@ -30174,9 +29323,7 @@
       <c r="J742" s="8" t="n"/>
       <c r="K742" s="8" t="n"/>
       <c r="L742" s="8" t="n"/>
-      <c r="M742" s="35" t="n">
-        <v>2837</v>
-      </c>
+      <c r="M742" s="8" t="n"/>
       <c r="N742" s="8" t="n"/>
     </row>
     <row r="743">
@@ -30210,9 +29357,7 @@
       <c r="J743" s="8" t="n"/>
       <c r="K743" s="8" t="n"/>
       <c r="L743" s="8" t="n"/>
-      <c r="M743" s="35" t="n">
-        <v>4010</v>
-      </c>
+      <c r="M743" s="8" t="n"/>
       <c r="N743" s="8" t="n"/>
     </row>
     <row r="744">
@@ -30246,9 +29391,7 @@
       <c r="J744" s="8" t="n"/>
       <c r="K744" s="8" t="n"/>
       <c r="L744" s="8" t="n"/>
-      <c r="M744" s="35" t="n">
-        <v>12541</v>
-      </c>
+      <c r="M744" s="8" t="n"/>
       <c r="N744" s="8" t="n"/>
     </row>
     <row r="745">
@@ -30282,9 +29425,7 @@
       <c r="J745" s="8" t="n"/>
       <c r="K745" s="8" t="n"/>
       <c r="L745" s="8" t="n"/>
-      <c r="M745" s="35" t="n">
-        <v>476</v>
-      </c>
+      <c r="M745" s="8" t="n"/>
       <c r="N745" s="8" t="n"/>
     </row>
     <row r="746">
@@ -30318,9 +29459,7 @@
       <c r="J746" s="8" t="n"/>
       <c r="K746" s="8" t="n"/>
       <c r="L746" s="8" t="n"/>
-      <c r="M746" s="35" t="n">
-        <v>374</v>
-      </c>
+      <c r="M746" s="8" t="n"/>
       <c r="N746" s="8" t="n"/>
     </row>
     <row r="747">
@@ -30354,9 +29493,7 @@
       <c r="J747" s="8" t="n"/>
       <c r="K747" s="8" t="n"/>
       <c r="L747" s="8" t="n"/>
-      <c r="M747" s="35" t="n">
-        <v>2116</v>
-      </c>
+      <c r="M747" s="8" t="n"/>
       <c r="N747" s="8" t="n"/>
     </row>
     <row r="748">
@@ -30390,9 +29527,7 @@
       <c r="J748" s="8" t="n"/>
       <c r="K748" s="8" t="n"/>
       <c r="L748" s="8" t="n"/>
-      <c r="M748" s="35" t="n">
-        <v>1277</v>
-      </c>
+      <c r="M748" s="8" t="n"/>
       <c r="N748" s="8" t="n"/>
     </row>
     <row r="749">
@@ -30426,9 +29561,7 @@
       <c r="J749" s="8" t="n"/>
       <c r="K749" s="8" t="n"/>
       <c r="L749" s="8" t="n"/>
-      <c r="M749" s="35" t="n">
-        <v>1113</v>
-      </c>
+      <c r="M749" s="8" t="n"/>
       <c r="N749" s="8" t="n"/>
     </row>
     <row r="750">
@@ -30462,9 +29595,7 @@
       <c r="J750" s="8" t="n"/>
       <c r="K750" s="8" t="n"/>
       <c r="L750" s="8" t="n"/>
-      <c r="M750" s="35" t="n">
-        <v>1736</v>
-      </c>
+      <c r="M750" s="8" t="n"/>
       <c r="N750" s="8" t="n"/>
     </row>
     <row r="751">
@@ -30498,9 +29629,7 @@
       <c r="J751" s="8" t="n"/>
       <c r="K751" s="8" t="n"/>
       <c r="L751" s="8" t="n"/>
-      <c r="M751" s="35" t="n">
-        <v>2039</v>
-      </c>
+      <c r="M751" s="8" t="n"/>
       <c r="N751" s="8" t="n"/>
     </row>
     <row r="752">
@@ -30534,9 +29663,7 @@
       <c r="J752" s="8" t="n"/>
       <c r="K752" s="8" t="n"/>
       <c r="L752" s="8" t="n"/>
-      <c r="M752" s="35" t="n">
-        <v>473</v>
-      </c>
+      <c r="M752" s="8" t="n"/>
       <c r="N752" s="8" t="n"/>
     </row>
     <row r="753">
@@ -30570,9 +29697,7 @@
       <c r="J753" s="8" t="n"/>
       <c r="K753" s="8" t="n"/>
       <c r="L753" s="8" t="n"/>
-      <c r="M753" s="35" t="n">
-        <v>667</v>
-      </c>
+      <c r="M753" s="8" t="n"/>
       <c r="N753" s="8" t="n"/>
     </row>
     <row r="754">
@@ -30606,9 +29731,7 @@
       <c r="J754" s="8" t="n"/>
       <c r="K754" s="8" t="n"/>
       <c r="L754" s="8" t="n"/>
-      <c r="M754" s="35" t="n">
-        <v>1502</v>
-      </c>
+      <c r="M754" s="8" t="n"/>
       <c r="N754" s="8" t="n"/>
     </row>
     <row r="755">
@@ -30642,9 +29765,7 @@
       <c r="J755" s="8" t="n"/>
       <c r="K755" s="8" t="n"/>
       <c r="L755" s="8" t="n"/>
-      <c r="M755" s="35" t="n">
-        <v>540</v>
-      </c>
+      <c r="M755" s="8" t="n"/>
       <c r="N755" s="8" t="n"/>
     </row>
     <row r="756">
@@ -30678,9 +29799,7 @@
       <c r="J756" s="8" t="n"/>
       <c r="K756" s="8" t="n"/>
       <c r="L756" s="8" t="n"/>
-      <c r="M756" s="35" t="n">
-        <v>254</v>
-      </c>
+      <c r="M756" s="8" t="n"/>
       <c r="N756" s="8" t="n"/>
     </row>
     <row r="757">
@@ -30714,9 +29833,7 @@
       <c r="J757" s="8" t="n"/>
       <c r="K757" s="8" t="n"/>
       <c r="L757" s="8" t="n"/>
-      <c r="M757" s="35" t="n">
-        <v>295</v>
-      </c>
+      <c r="M757" s="8" t="n"/>
       <c r="N757" s="8" t="n"/>
     </row>
     <row r="758">
@@ -30750,9 +29867,7 @@
       <c r="J758" s="8" t="n"/>
       <c r="K758" s="8" t="n"/>
       <c r="L758" s="18" t="n"/>
-      <c r="M758" s="35" t="n">
-        <v>570</v>
-      </c>
+      <c r="M758" s="8" t="n"/>
       <c r="N758" s="8" t="n"/>
     </row>
     <row r="759">
@@ -30786,9 +29901,7 @@
       <c r="J759" s="8" t="n"/>
       <c r="K759" s="8" t="n"/>
       <c r="L759" s="8" t="n"/>
-      <c r="M759" s="35" t="n">
-        <v>413</v>
-      </c>
+      <c r="M759" s="8" t="n"/>
       <c r="N759" s="8" t="n"/>
     </row>
     <row r="760">
@@ -30822,9 +29935,7 @@
       <c r="J760" s="8" t="n"/>
       <c r="K760" s="8" t="n"/>
       <c r="L760" s="8" t="n"/>
-      <c r="M760" s="35" t="n">
-        <v>504</v>
-      </c>
+      <c r="M760" s="8" t="n"/>
       <c r="N760" s="8" t="n"/>
     </row>
     <row r="761">
@@ -30858,9 +29969,7 @@
       <c r="J761" s="8" t="n"/>
       <c r="K761" s="8" t="n"/>
       <c r="L761" s="8" t="n"/>
-      <c r="M761" s="35" t="n">
-        <v>1801</v>
-      </c>
+      <c r="M761" s="8" t="n"/>
       <c r="N761" s="8" t="n"/>
     </row>
     <row r="762">
@@ -30888,25 +29997,11 @@
       <c r="F762" s="8" t="n">
         <v>1086</v>
       </c>
-      <c r="G762" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H762" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I762" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J762" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K762" s="34" t="n">
-        <v>13738</v>
-      </c>
+      <c r="G762" s="8" t="n"/>
+      <c r="H762" s="8" t="n"/>
+      <c r="I762" s="8" t="n"/>
+      <c r="J762" s="8" t="n"/>
+      <c r="K762" s="8" t="n"/>
       <c r="L762" s="8" t="n"/>
       <c r="M762" s="8" t="n"/>
       <c r="N762" s="8" t="n"/>
@@ -30942,9 +30037,7 @@
       <c r="J763" s="8" t="n"/>
       <c r="K763" s="8" t="n"/>
       <c r="L763" s="8" t="n"/>
-      <c r="M763" s="35" t="n">
-        <v>3257</v>
-      </c>
+      <c r="M763" s="8" t="n"/>
       <c r="N763" s="8" t="n"/>
     </row>
     <row r="764">
@@ -30978,9 +30071,7 @@
       <c r="J764" s="8" t="n"/>
       <c r="K764" s="8" t="n"/>
       <c r="L764" s="8" t="n"/>
-      <c r="M764" s="35" t="n">
-        <v>4410</v>
-      </c>
+      <c r="M764" s="8" t="n"/>
       <c r="N764" s="8" t="n"/>
     </row>
     <row r="765">
@@ -31014,9 +30105,7 @@
       <c r="J765" s="8" t="n"/>
       <c r="K765" s="8" t="n"/>
       <c r="L765" s="8" t="n"/>
-      <c r="M765" s="35" t="n">
-        <v>243</v>
-      </c>
+      <c r="M765" s="8" t="n"/>
       <c r="N765" s="8" t="n"/>
     </row>
     <row r="766">
@@ -31050,9 +30139,7 @@
       <c r="J766" s="8" t="n"/>
       <c r="K766" s="8" t="n"/>
       <c r="L766" s="8" t="n"/>
-      <c r="M766" s="35" t="n">
-        <v>328</v>
-      </c>
+      <c r="M766" s="8" t="n"/>
       <c r="N766" s="8" t="n"/>
     </row>
     <row r="767">
@@ -31086,9 +30173,7 @@
       <c r="J767" s="8" t="n"/>
       <c r="K767" s="8" t="n"/>
       <c r="L767" s="8" t="n"/>
-      <c r="M767" s="35" t="n">
-        <v>1550</v>
-      </c>
+      <c r="M767" s="8" t="n"/>
       <c r="N767" s="8" t="n"/>
     </row>
     <row r="768">
@@ -31122,9 +30207,7 @@
       <c r="J768" s="8" t="n"/>
       <c r="K768" s="8" t="n"/>
       <c r="L768" s="8" t="n"/>
-      <c r="M768" s="35" t="n">
-        <v>927</v>
-      </c>
+      <c r="M768" s="8" t="n"/>
       <c r="N768" s="8" t="n"/>
     </row>
     <row r="769">
@@ -31158,9 +30241,7 @@
       <c r="J769" s="8" t="n"/>
       <c r="K769" s="8" t="n"/>
       <c r="L769" s="8" t="n"/>
-      <c r="M769" s="35" t="n">
-        <v>1838</v>
-      </c>
+      <c r="M769" s="8" t="n"/>
       <c r="N769" s="8" t="n"/>
     </row>
     <row r="770">
@@ -31194,9 +30275,7 @@
       <c r="J770" s="8" t="n"/>
       <c r="K770" s="8" t="n"/>
       <c r="L770" s="8" t="n"/>
-      <c r="M770" s="35" t="n">
-        <v>360</v>
-      </c>
+      <c r="M770" s="8" t="n"/>
       <c r="N770" s="8" t="n"/>
     </row>
     <row r="771">
@@ -31230,9 +30309,7 @@
       <c r="J771" s="8" t="n"/>
       <c r="K771" s="8" t="n"/>
       <c r="L771" s="8" t="n"/>
-      <c r="M771" s="35" t="n">
-        <v>2484</v>
-      </c>
+      <c r="M771" s="8" t="n"/>
       <c r="N771" s="8" t="n"/>
     </row>
     <row r="772">
@@ -31266,9 +30343,7 @@
       <c r="J772" s="8" t="n"/>
       <c r="K772" s="8" t="n"/>
       <c r="L772" s="8" t="n"/>
-      <c r="M772" s="35" t="n">
-        <v>463</v>
-      </c>
+      <c r="M772" s="8" t="n"/>
       <c r="N772" s="8" t="n"/>
     </row>
     <row r="773">
@@ -31302,9 +30377,7 @@
       <c r="J773" s="8" t="n"/>
       <c r="K773" s="8" t="n"/>
       <c r="L773" s="8" t="n"/>
-      <c r="M773" s="35" t="n">
-        <v>418</v>
-      </c>
+      <c r="M773" s="8" t="n"/>
       <c r="N773" s="8" t="n"/>
     </row>
     <row r="774">
@@ -31338,9 +30411,7 @@
       <c r="J774" s="8" t="n"/>
       <c r="K774" s="8" t="n"/>
       <c r="L774" s="8" t="n"/>
-      <c r="M774" s="35" t="n">
-        <v>564</v>
-      </c>
+      <c r="M774" s="8" t="n"/>
       <c r="N774" s="8" t="n"/>
     </row>
     <row r="775">
@@ -31374,9 +30445,7 @@
       <c r="J775" s="8" t="n"/>
       <c r="K775" s="8" t="n"/>
       <c r="L775" s="18" t="n"/>
-      <c r="M775" s="35" t="n">
-        <v>1795</v>
-      </c>
+      <c r="M775" s="8" t="n"/>
       <c r="N775" s="8" t="n"/>
     </row>
     <row r="776">
@@ -31410,9 +30479,7 @@
       <c r="J776" s="8" t="n"/>
       <c r="K776" s="8" t="n"/>
       <c r="L776" s="8" t="n"/>
-      <c r="M776" s="35" t="n">
-        <v>1265</v>
-      </c>
+      <c r="M776" s="8" t="n"/>
       <c r="N776" s="8" t="n"/>
     </row>
     <row r="777">
@@ -31446,9 +30513,7 @@
       <c r="J777" s="8" t="n"/>
       <c r="K777" s="8" t="n"/>
       <c r="L777" s="8" t="n"/>
-      <c r="M777" s="35" t="n">
-        <v>3781</v>
-      </c>
+      <c r="M777" s="8" t="n"/>
       <c r="N777" s="8" t="n"/>
     </row>
     <row r="778">
@@ -31482,9 +30547,7 @@
       <c r="J778" s="8" t="n"/>
       <c r="K778" s="8" t="n"/>
       <c r="L778" s="8" t="n"/>
-      <c r="M778" s="35" t="n">
-        <v>5623</v>
-      </c>
+      <c r="M778" s="8" t="n"/>
       <c r="N778" s="8" t="n"/>
     </row>
     <row r="779">
@@ -31518,9 +30581,7 @@
       <c r="J779" s="8" t="n"/>
       <c r="K779" s="8" t="n"/>
       <c r="L779" s="8" t="n"/>
-      <c r="M779" s="35" t="n">
-        <v>3102</v>
-      </c>
+      <c r="M779" s="8" t="n"/>
       <c r="N779" s="8" t="n"/>
     </row>
     <row r="780">
@@ -31554,9 +30615,7 @@
       <c r="J780" s="8" t="n"/>
       <c r="K780" s="8" t="n"/>
       <c r="L780" s="8" t="n"/>
-      <c r="M780" s="35" t="n">
-        <v>1200</v>
-      </c>
+      <c r="M780" s="8" t="n"/>
       <c r="N780" s="8" t="n"/>
     </row>
     <row r="781">
@@ -31590,9 +30649,7 @@
       <c r="J781" s="8" t="n"/>
       <c r="K781" s="8" t="n"/>
       <c r="L781" s="8" t="n"/>
-      <c r="M781" s="35" t="n">
-        <v>481</v>
-      </c>
+      <c r="M781" s="8" t="n"/>
       <c r="N781" s="8" t="n"/>
     </row>
     <row r="782">
@@ -31626,9 +30683,7 @@
       <c r="J782" s="8" t="n"/>
       <c r="K782" s="8" t="n"/>
       <c r="L782" s="8" t="n"/>
-      <c r="M782" s="35" t="n">
-        <v>672</v>
-      </c>
+      <c r="M782" s="8" t="n"/>
       <c r="N782" s="8" t="n"/>
     </row>
     <row r="783">
@@ -31662,9 +30717,7 @@
       <c r="J783" s="8" t="n"/>
       <c r="K783" s="8" t="n"/>
       <c r="L783" s="8" t="n"/>
-      <c r="M783" s="35" t="n">
-        <v>1220</v>
-      </c>
+      <c r="M783" s="8" t="n"/>
       <c r="N783" s="8" t="n"/>
     </row>
     <row r="784">
@@ -31698,9 +30751,7 @@
       <c r="J784" s="8" t="n"/>
       <c r="K784" s="8" t="n"/>
       <c r="L784" s="8" t="n"/>
-      <c r="M784" s="35" t="n">
-        <v>4801</v>
-      </c>
+      <c r="M784" s="8" t="n"/>
       <c r="N784" s="8" t="n"/>
     </row>
     <row r="785">
@@ -31734,9 +30785,7 @@
       <c r="J785" s="8" t="n"/>
       <c r="K785" s="8" t="n"/>
       <c r="L785" s="8" t="n"/>
-      <c r="M785" s="35" t="n">
-        <v>3571</v>
-      </c>
+      <c r="M785" s="8" t="n"/>
       <c r="N785" s="8" t="n"/>
     </row>
     <row r="786">
@@ -31770,9 +30819,7 @@
       <c r="J786" s="8" t="n"/>
       <c r="K786" s="8" t="n"/>
       <c r="L786" s="8" t="n"/>
-      <c r="M786" s="35" t="n">
-        <v>413</v>
-      </c>
+      <c r="M786" s="8" t="n"/>
       <c r="N786" s="8" t="n"/>
     </row>
     <row r="787">
@@ -31806,9 +30853,7 @@
       <c r="J787" s="8" t="n"/>
       <c r="K787" s="8" t="n"/>
       <c r="L787" s="8" t="n"/>
-      <c r="M787" s="35" t="n">
-        <v>2621</v>
-      </c>
+      <c r="M787" s="8" t="n"/>
       <c r="N787" s="8" t="n"/>
     </row>
     <row r="788">
@@ -31842,9 +30887,7 @@
       <c r="J788" s="8" t="n"/>
       <c r="K788" s="8" t="n"/>
       <c r="L788" s="8" t="n"/>
-      <c r="M788" s="35" t="n">
-        <v>830</v>
-      </c>
+      <c r="M788" s="8" t="n"/>
       <c r="N788" s="8" t="n"/>
     </row>
     <row r="789">
@@ -31878,9 +30921,7 @@
       <c r="J789" s="8" t="n"/>
       <c r="K789" s="8" t="n"/>
       <c r="L789" s="8" t="n"/>
-      <c r="M789" s="35" t="n">
-        <v>1714</v>
-      </c>
+      <c r="M789" s="8" t="n"/>
       <c r="N789" s="8" t="n"/>
     </row>
     <row r="790">
@@ -31914,9 +30955,7 @@
       <c r="J790" s="8" t="n"/>
       <c r="K790" s="8" t="n"/>
       <c r="L790" s="8" t="n"/>
-      <c r="M790" s="35" t="n">
-        <v>549</v>
-      </c>
+      <c r="M790" s="8" t="n"/>
       <c r="N790" s="8" t="n"/>
     </row>
     <row r="791">
@@ -31950,9 +30989,7 @@
       <c r="J791" s="8" t="n"/>
       <c r="K791" s="8" t="n"/>
       <c r="L791" s="8" t="n"/>
-      <c r="M791" s="35" t="n">
-        <v>189</v>
-      </c>
+      <c r="M791" s="8" t="n"/>
       <c r="N791" s="8" t="n"/>
     </row>
     <row r="792">
@@ -31986,9 +31023,7 @@
       <c r="J792" s="8" t="n"/>
       <c r="K792" s="8" t="n"/>
       <c r="L792" s="8" t="n"/>
-      <c r="M792" s="35" t="n">
-        <v>782</v>
-      </c>
+      <c r="M792" s="8" t="n"/>
       <c r="N792" s="8" t="n"/>
     </row>
     <row r="793">
@@ -32016,25 +31051,11 @@
       <c r="F793" s="8" t="n">
         <v>2587</v>
       </c>
-      <c r="G793" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H793" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I793" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J793" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K793" s="34" t="n">
-        <v>8869</v>
-      </c>
+      <c r="G793" s="8" t="n"/>
+      <c r="H793" s="8" t="n"/>
+      <c r="I793" s="8" t="n"/>
+      <c r="J793" s="8" t="n"/>
+      <c r="K793" s="8" t="n"/>
       <c r="L793" s="8" t="n"/>
       <c r="M793" s="8" t="n"/>
       <c r="N793" s="8" t="n"/>
@@ -32070,9 +31091,7 @@
       <c r="J794" s="8" t="n"/>
       <c r="K794" s="8" t="n"/>
       <c r="L794" s="8" t="n"/>
-      <c r="M794" s="35" t="n">
-        <v>3074</v>
-      </c>
+      <c r="M794" s="8" t="n"/>
       <c r="N794" s="8" t="n"/>
     </row>
     <row r="795">
@@ -32106,9 +31125,7 @@
       <c r="J795" s="8" t="n"/>
       <c r="K795" s="8" t="n"/>
       <c r="L795" s="8" t="n"/>
-      <c r="M795" s="35" t="n">
-        <v>1404</v>
-      </c>
+      <c r="M795" s="8" t="n"/>
       <c r="N795" s="8" t="n"/>
     </row>
     <row r="796">
@@ -32142,9 +31159,7 @@
       <c r="J796" s="8" t="n"/>
       <c r="K796" s="8" t="n"/>
       <c r="L796" s="8" t="n"/>
-      <c r="M796" s="35" t="n">
-        <v>7336</v>
-      </c>
+      <c r="M796" s="8" t="n"/>
       <c r="N796" s="8" t="n"/>
     </row>
     <row r="797">
@@ -32178,9 +31193,7 @@
       <c r="J797" s="8" t="n"/>
       <c r="K797" s="8" t="n"/>
       <c r="L797" s="8" t="n"/>
-      <c r="M797" s="35" t="n">
-        <v>146</v>
-      </c>
+      <c r="M797" s="8" t="n"/>
       <c r="N797" s="8" t="n"/>
     </row>
     <row r="798">
@@ -32208,19 +31221,11 @@
       <c r="F798" s="8" t="n">
         <v>3354</v>
       </c>
-      <c r="G798" s="32" t="n"/>
-      <c r="H798" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I798" s="32" t="inlineStr"/>
-      <c r="J798" s="33" t="n">
-        <v>68712</v>
-      </c>
-      <c r="K798" s="34" t="n">
-        <v>15048</v>
-      </c>
+      <c r="G798" s="8" t="n"/>
+      <c r="H798" s="8" t="n"/>
+      <c r="I798" s="8" t="n"/>
+      <c r="J798" s="8" t="n"/>
+      <c r="K798" s="8" t="n"/>
       <c r="L798" s="8" t="n"/>
       <c r="M798" s="8" t="n"/>
       <c r="N798" s="8" t="n"/>
@@ -32256,9 +31261,7 @@
       <c r="J799" s="8" t="n"/>
       <c r="K799" s="8" t="n"/>
       <c r="L799" s="8" t="n"/>
-      <c r="M799" s="35" t="n">
-        <v>1108</v>
-      </c>
+      <c r="M799" s="8" t="n"/>
       <c r="N799" s="8" t="n"/>
     </row>
     <row r="800">
@@ -32292,9 +31295,7 @@
       <c r="J800" s="8" t="n"/>
       <c r="K800" s="8" t="n"/>
       <c r="L800" s="8" t="n"/>
-      <c r="M800" s="35" t="n">
-        <v>2547</v>
-      </c>
+      <c r="M800" s="8" t="n"/>
       <c r="N800" s="8" t="n"/>
     </row>
     <row r="801">
@@ -32328,9 +31329,7 @@
       <c r="J801" s="8" t="n"/>
       <c r="K801" s="8" t="n"/>
       <c r="L801" s="18" t="n"/>
-      <c r="M801" s="35" t="n">
-        <v>637</v>
-      </c>
+      <c r="M801" s="8" t="n"/>
       <c r="N801" s="8" t="n"/>
     </row>
     <row r="802">
@@ -32364,9 +31363,7 @@
       <c r="J802" s="8" t="n"/>
       <c r="K802" s="8" t="n"/>
       <c r="L802" s="18" t="n"/>
-      <c r="M802" s="35" t="n">
-        <v>1645</v>
-      </c>
+      <c r="M802" s="8" t="n"/>
       <c r="N802" s="8" t="n"/>
     </row>
     <row r="803">
@@ -32400,9 +31397,7 @@
       <c r="J803" s="8" t="n"/>
       <c r="K803" s="8" t="n"/>
       <c r="L803" s="18" t="n"/>
-      <c r="M803" s="35" t="n">
-        <v>3790</v>
-      </c>
+      <c r="M803" s="8" t="n"/>
       <c r="N803" s="8" t="n"/>
     </row>
     <row r="804">
@@ -32436,9 +31431,7 @@
       <c r="J804" s="8" t="n"/>
       <c r="K804" s="8" t="n"/>
       <c r="L804" s="8" t="n"/>
-      <c r="M804" s="35" t="n">
-        <v>574</v>
-      </c>
+      <c r="M804" s="8" t="n"/>
       <c r="N804" s="8" t="n"/>
     </row>
     <row r="805">
@@ -32472,9 +31465,7 @@
       <c r="J805" s="8" t="n"/>
       <c r="K805" s="8" t="n"/>
       <c r="L805" s="8" t="n"/>
-      <c r="M805" s="35" t="n">
-        <v>5277</v>
-      </c>
+      <c r="M805" s="8" t="n"/>
       <c r="N805" s="8" t="n"/>
     </row>
     <row r="806">
@@ -32508,9 +31499,7 @@
       <c r="J806" s="8" t="n"/>
       <c r="K806" s="8" t="n"/>
       <c r="L806" s="8" t="n"/>
-      <c r="M806" s="35" t="n">
-        <v>2918</v>
-      </c>
+      <c r="M806" s="8" t="n"/>
       <c r="N806" s="8" t="n"/>
     </row>
     <row r="807">
@@ -32544,9 +31533,7 @@
       <c r="J807" s="8" t="n"/>
       <c r="K807" s="8" t="n"/>
       <c r="L807" s="8" t="n"/>
-      <c r="M807" s="35" t="n">
-        <v>6925</v>
-      </c>
+      <c r="M807" s="8" t="n"/>
       <c r="N807" s="8" t="n"/>
     </row>
     <row r="808">
@@ -32580,9 +31567,7 @@
       <c r="J808" s="8" t="n"/>
       <c r="K808" s="8" t="n"/>
       <c r="L808" s="18" t="n"/>
-      <c r="M808" s="35" t="n">
-        <v>2969</v>
-      </c>
+      <c r="M808" s="8" t="n"/>
       <c r="N808" s="8" t="n"/>
     </row>
     <row r="809">
@@ -32616,9 +31601,7 @@
       <c r="J809" s="8" t="n"/>
       <c r="K809" s="8" t="n"/>
       <c r="L809" s="8" t="n"/>
-      <c r="M809" s="35" t="n">
-        <v>242</v>
-      </c>
+      <c r="M809" s="8" t="n"/>
       <c r="N809" s="8" t="n"/>
     </row>
     <row r="810">
@@ -32652,9 +31635,7 @@
       <c r="J810" s="8" t="n"/>
       <c r="K810" s="8" t="n"/>
       <c r="L810" s="8" t="n"/>
-      <c r="M810" s="35" t="n">
-        <v>989</v>
-      </c>
+      <c r="M810" s="8" t="n"/>
       <c r="N810" s="8" t="n"/>
     </row>
     <row r="811">
@@ -32682,25 +31663,11 @@
       <c r="F811" s="8" t="n">
         <v>808</v>
       </c>
-      <c r="G811" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H811" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I811" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J811" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K811" s="34" t="n">
-        <v>9151</v>
-      </c>
+      <c r="G811" s="8" t="n"/>
+      <c r="H811" s="8" t="n"/>
+      <c r="I811" s="8" t="n"/>
+      <c r="J811" s="8" t="n"/>
+      <c r="K811" s="8" t="n"/>
       <c r="L811" s="8" t="n"/>
       <c r="M811" s="8" t="n"/>
       <c r="N811" s="8" t="n"/>
@@ -32736,9 +31703,7 @@
       <c r="J812" s="8" t="n"/>
       <c r="K812" s="8" t="n"/>
       <c r="L812" s="8" t="n"/>
-      <c r="M812" s="35" t="n">
-        <v>1908</v>
-      </c>
+      <c r="M812" s="8" t="n"/>
       <c r="N812" s="8" t="n"/>
     </row>
     <row r="813">
@@ -32772,9 +31737,7 @@
       <c r="J813" s="8" t="n"/>
       <c r="K813" s="8" t="n"/>
       <c r="L813" s="8" t="n"/>
-      <c r="M813" s="35" t="n">
-        <v>1015</v>
-      </c>
+      <c r="M813" s="8" t="n"/>
       <c r="N813" s="8" t="n"/>
     </row>
     <row r="814">
@@ -32808,9 +31771,7 @@
       <c r="J814" s="8" t="n"/>
       <c r="K814" s="8" t="n"/>
       <c r="L814" s="8" t="n"/>
-      <c r="M814" s="35" t="n">
-        <v>1590</v>
-      </c>
+      <c r="M814" s="8" t="n"/>
       <c r="N814" s="8" t="n"/>
     </row>
     <row r="815">
@@ -32844,9 +31805,7 @@
       <c r="J815" s="8" t="n"/>
       <c r="K815" s="8" t="n"/>
       <c r="L815" s="8" t="n"/>
-      <c r="M815" s="35" t="n">
-        <v>925</v>
-      </c>
+      <c r="M815" s="8" t="n"/>
       <c r="N815" s="8" t="n"/>
     </row>
     <row r="816">
@@ -32880,9 +31839,7 @@
       <c r="J816" s="8" t="n"/>
       <c r="K816" s="8" t="n"/>
       <c r="L816" s="8" t="n"/>
-      <c r="M816" s="35" t="n">
-        <v>2653</v>
-      </c>
+      <c r="M816" s="8" t="n"/>
       <c r="N816" s="8" t="n"/>
     </row>
     <row r="817">
@@ -32916,9 +31873,7 @@
       <c r="J817" s="8" t="n"/>
       <c r="K817" s="8" t="n"/>
       <c r="L817" s="8" t="n"/>
-      <c r="M817" s="35" t="n">
-        <v>141</v>
-      </c>
+      <c r="M817" s="8" t="n"/>
       <c r="N817" s="8" t="n"/>
     </row>
     <row r="818">
@@ -32952,9 +31907,7 @@
       <c r="J818" s="8" t="n"/>
       <c r="K818" s="8" t="n"/>
       <c r="L818" s="8" t="n"/>
-      <c r="M818" s="35" t="n">
-        <v>3563</v>
-      </c>
+      <c r="M818" s="8" t="n"/>
       <c r="N818" s="8" t="n"/>
     </row>
     <row r="819">
@@ -32988,9 +31941,7 @@
       <c r="J819" s="8" t="n"/>
       <c r="K819" s="8" t="n"/>
       <c r="L819" s="8" t="n"/>
-      <c r="M819" s="35" t="n">
-        <v>134</v>
-      </c>
+      <c r="M819" s="8" t="n"/>
       <c r="N819" s="8" t="n"/>
     </row>
     <row r="820">
@@ -33024,9 +31975,7 @@
       <c r="J820" s="8" t="n"/>
       <c r="K820" s="8" t="n"/>
       <c r="L820" s="8" t="n"/>
-      <c r="M820" s="35" t="n">
-        <v>331</v>
-      </c>
+      <c r="M820" s="8" t="n"/>
       <c r="N820" s="8" t="n"/>
     </row>
     <row r="821">
@@ -33060,9 +32009,7 @@
       <c r="J821" s="8" t="n"/>
       <c r="K821" s="8" t="n"/>
       <c r="L821" s="8" t="n"/>
-      <c r="M821" s="35" t="n">
-        <v>217</v>
-      </c>
+      <c r="M821" s="8" t="n"/>
       <c r="N821" s="8" t="n"/>
     </row>
     <row r="822">
@@ -33096,9 +32043,7 @@
       <c r="J822" s="8" t="n"/>
       <c r="K822" s="8" t="n"/>
       <c r="L822" s="8" t="n"/>
-      <c r="M822" s="35" t="n">
-        <v>566</v>
-      </c>
+      <c r="M822" s="8" t="n"/>
       <c r="N822" s="8" t="n"/>
     </row>
     <row r="823">
@@ -33132,9 +32077,7 @@
       <c r="J823" s="8" t="n"/>
       <c r="K823" s="8" t="n"/>
       <c r="L823" s="8" t="n"/>
-      <c r="M823" s="35" t="n">
-        <v>2896</v>
-      </c>
+      <c r="M823" s="8" t="n"/>
       <c r="N823" s="8" t="n"/>
     </row>
     <row r="824">
@@ -33162,25 +32105,11 @@
       <c r="F824" s="8" t="n">
         <v>1689</v>
       </c>
-      <c r="G824" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H824" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I824" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J824" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K824" s="34" t="n">
-        <v>2355</v>
-      </c>
+      <c r="G824" s="8" t="n"/>
+      <c r="H824" s="8" t="n"/>
+      <c r="I824" s="8" t="n"/>
+      <c r="J824" s="8" t="n"/>
+      <c r="K824" s="8" t="n"/>
       <c r="L824" s="8" t="n"/>
       <c r="M824" s="8" t="n"/>
       <c r="N824" s="8" t="n"/>
@@ -33216,9 +32145,7 @@
       <c r="J825" s="8" t="n"/>
       <c r="K825" s="8" t="n"/>
       <c r="L825" s="8" t="n"/>
-      <c r="M825" s="35" t="n">
-        <v>174</v>
-      </c>
+      <c r="M825" s="8" t="n"/>
       <c r="N825" s="8" t="n"/>
     </row>
     <row r="826">
@@ -33252,9 +32179,7 @@
       <c r="J826" s="8" t="n"/>
       <c r="K826" s="8" t="n"/>
       <c r="L826" s="8" t="n"/>
-      <c r="M826" s="35" t="n">
-        <v>1042</v>
-      </c>
+      <c r="M826" s="8" t="n"/>
       <c r="N826" s="8" t="n"/>
     </row>
     <row r="827">
@@ -33288,9 +32213,7 @@
       <c r="J827" s="8" t="n"/>
       <c r="K827" s="8" t="n"/>
       <c r="L827" s="8" t="n"/>
-      <c r="M827" s="35" t="n">
-        <v>1296</v>
-      </c>
+      <c r="M827" s="8" t="n"/>
       <c r="N827" s="8" t="n"/>
     </row>
     <row r="828">
@@ -33324,9 +32247,7 @@
       <c r="J828" s="8" t="n"/>
       <c r="K828" s="8" t="n"/>
       <c r="L828" s="8" t="n"/>
-      <c r="M828" s="35" t="n">
-        <v>167</v>
-      </c>
+      <c r="M828" s="8" t="n"/>
       <c r="N828" s="8" t="n"/>
     </row>
     <row r="829">
@@ -33360,9 +32281,7 @@
       <c r="J829" s="8" t="n"/>
       <c r="K829" s="8" t="n"/>
       <c r="L829" s="8" t="n"/>
-      <c r="M829" s="35" t="n">
-        <v>962</v>
-      </c>
+      <c r="M829" s="8" t="n"/>
       <c r="N829" s="8" t="n"/>
     </row>
     <row r="830">
@@ -33396,9 +32315,7 @@
       <c r="J830" s="8" t="n"/>
       <c r="K830" s="8" t="n"/>
       <c r="L830" s="8" t="n"/>
-      <c r="M830" s="35" t="n">
-        <v>1636</v>
-      </c>
+      <c r="M830" s="8" t="n"/>
       <c r="N830" s="8" t="n"/>
     </row>
     <row r="831">
@@ -33432,9 +32349,7 @@
       <c r="J831" s="8" t="n"/>
       <c r="K831" s="8" t="n"/>
       <c r="L831" s="8" t="n"/>
-      <c r="M831" s="35" t="n">
-        <v>192</v>
-      </c>
+      <c r="M831" s="8" t="n"/>
       <c r="N831" s="8" t="n"/>
     </row>
     <row r="832">
@@ -33468,9 +32383,7 @@
       <c r="J832" s="8" t="n"/>
       <c r="K832" s="8" t="n"/>
       <c r="L832" s="8" t="n"/>
-      <c r="M832" s="35" t="n">
-        <v>723</v>
-      </c>
+      <c r="M832" s="8" t="n"/>
       <c r="N832" s="8" t="n"/>
     </row>
     <row r="833">
@@ -33504,9 +32417,7 @@
       <c r="J833" s="8" t="n"/>
       <c r="K833" s="8" t="n"/>
       <c r="L833" s="18" t="n"/>
-      <c r="M833" s="35" t="n">
-        <v>859</v>
-      </c>
+      <c r="M833" s="8" t="n"/>
       <c r="N833" s="8" t="n"/>
     </row>
     <row r="834">
@@ -33540,9 +32451,7 @@
       <c r="J834" s="8" t="n"/>
       <c r="K834" s="8" t="n"/>
       <c r="L834" s="19" t="n"/>
-      <c r="M834" s="35" t="n">
-        <v>590</v>
-      </c>
+      <c r="M834" s="8" t="n"/>
       <c r="N834" s="8" t="n"/>
     </row>
     <row r="835">
@@ -33576,9 +32485,7 @@
       <c r="J835" s="8" t="n"/>
       <c r="K835" s="8" t="n"/>
       <c r="L835" s="19" t="n"/>
-      <c r="M835" s="35" t="n">
-        <v>1097</v>
-      </c>
+      <c r="M835" s="8" t="n"/>
       <c r="N835" s="8" t="n"/>
     </row>
     <row r="836">
@@ -33612,9 +32519,7 @@
       <c r="J836" s="8" t="n"/>
       <c r="K836" s="8" t="n"/>
       <c r="L836" s="8" t="n"/>
-      <c r="M836" s="35" t="n">
-        <v>539</v>
-      </c>
+      <c r="M836" s="8" t="n"/>
       <c r="N836" s="8" t="n"/>
     </row>
     <row r="837">
@@ -33648,9 +32553,7 @@
       <c r="J837" s="8" t="n"/>
       <c r="K837" s="8" t="n"/>
       <c r="L837" s="8" t="n"/>
-      <c r="M837" s="35" t="n">
-        <v>1171</v>
-      </c>
+      <c r="M837" s="8" t="n"/>
       <c r="N837" s="8" t="n"/>
     </row>
     <row r="838">
@@ -33684,9 +32587,7 @@
       <c r="J838" s="8" t="n"/>
       <c r="K838" s="8" t="n"/>
       <c r="L838" s="8" t="n"/>
-      <c r="M838" s="35" t="n">
-        <v>147</v>
-      </c>
+      <c r="M838" s="8" t="n"/>
       <c r="N838" s="8" t="n"/>
     </row>
     <row r="839">
@@ -33720,9 +32621,7 @@
       <c r="J839" s="8" t="n"/>
       <c r="K839" s="8" t="n"/>
       <c r="L839" s="8" t="n"/>
-      <c r="M839" s="35" t="n">
-        <v>1059</v>
-      </c>
+      <c r="M839" s="8" t="n"/>
       <c r="N839" s="8" t="n"/>
     </row>
     <row r="840">
@@ -33756,9 +32655,7 @@
       <c r="J840" s="8" t="n"/>
       <c r="K840" s="8" t="n"/>
       <c r="L840" s="8" t="n"/>
-      <c r="M840" s="35" t="n">
-        <v>1667</v>
-      </c>
+      <c r="M840" s="8" t="n"/>
       <c r="N840" s="8" t="n"/>
     </row>
     <row r="841">
@@ -33792,9 +32689,7 @@
       <c r="J841" s="8" t="n"/>
       <c r="K841" s="8" t="n"/>
       <c r="L841" s="8" t="n"/>
-      <c r="M841" s="35" t="n">
-        <v>4176</v>
-      </c>
+      <c r="M841" s="8" t="n"/>
       <c r="N841" s="8" t="n"/>
     </row>
     <row r="842">
@@ -33828,9 +32723,7 @@
       <c r="J842" s="8" t="n"/>
       <c r="K842" s="8" t="n"/>
       <c r="L842" s="8" t="n"/>
-      <c r="M842" s="35" t="n">
-        <v>1693</v>
-      </c>
+      <c r="M842" s="8" t="n"/>
       <c r="N842" s="8" t="n"/>
     </row>
     <row r="843">
@@ -33864,9 +32757,7 @@
       <c r="J843" s="8" t="n"/>
       <c r="K843" s="8" t="n"/>
       <c r="L843" s="8" t="n"/>
-      <c r="M843" s="35" t="n">
-        <v>1037</v>
-      </c>
+      <c r="M843" s="8" t="n"/>
       <c r="N843" s="8" t="n"/>
     </row>
     <row r="844">
@@ -33900,9 +32791,7 @@
       <c r="J844" s="8" t="n"/>
       <c r="K844" s="8" t="n"/>
       <c r="L844" s="8" t="n"/>
-      <c r="M844" s="35" t="n">
-        <v>6356</v>
-      </c>
+      <c r="M844" s="8" t="n"/>
       <c r="N844" s="8" t="n"/>
     </row>
     <row r="845">
@@ -33936,9 +32825,7 @@
       <c r="J845" s="8" t="n"/>
       <c r="K845" s="8" t="n"/>
       <c r="L845" s="8" t="n"/>
-      <c r="M845" s="35" t="n">
-        <v>460</v>
-      </c>
+      <c r="M845" s="8" t="n"/>
       <c r="N845" s="8" t="n"/>
     </row>
     <row r="846">
@@ -33972,9 +32859,7 @@
       <c r="J846" s="8" t="n"/>
       <c r="K846" s="8" t="n"/>
       <c r="L846" s="8" t="n"/>
-      <c r="M846" s="35" t="n">
-        <v>250</v>
-      </c>
+      <c r="M846" s="8" t="n"/>
       <c r="N846" s="8" t="n"/>
     </row>
     <row r="847">
@@ -34008,9 +32893,7 @@
       <c r="J847" s="8" t="n"/>
       <c r="K847" s="8" t="n"/>
       <c r="L847" s="8" t="n"/>
-      <c r="M847" s="35" t="n">
-        <v>1792</v>
-      </c>
+      <c r="M847" s="8" t="n"/>
       <c r="N847" s="8" t="n"/>
     </row>
     <row r="848">
@@ -34044,9 +32927,7 @@
       <c r="J848" s="8" t="n"/>
       <c r="K848" s="8" t="n"/>
       <c r="L848" s="19" t="n"/>
-      <c r="M848" s="35" t="n">
-        <v>1314</v>
-      </c>
+      <c r="M848" s="8" t="n"/>
       <c r="N848" s="8" t="n"/>
     </row>
     <row r="849">
@@ -34080,9 +32961,7 @@
       <c r="J849" s="8" t="n"/>
       <c r="K849" s="8" t="n"/>
       <c r="L849" s="8" t="n"/>
-      <c r="M849" s="35" t="n">
-        <v>9548</v>
-      </c>
+      <c r="M849" s="8" t="n"/>
       <c r="N849" s="8" t="n"/>
     </row>
     <row r="850">
@@ -34116,9 +32995,7 @@
       <c r="J850" s="8" t="n"/>
       <c r="K850" s="8" t="n"/>
       <c r="L850" s="8" t="n"/>
-      <c r="M850" s="35" t="n">
-        <v>1266</v>
-      </c>
+      <c r="M850" s="8" t="n"/>
       <c r="N850" s="8" t="n"/>
     </row>
     <row r="851">
@@ -34152,9 +33029,7 @@
       <c r="J851" s="8" t="n"/>
       <c r="K851" s="8" t="n"/>
       <c r="L851" s="8" t="n"/>
-      <c r="M851" s="35" t="n">
-        <v>7770</v>
-      </c>
+      <c r="M851" s="8" t="n"/>
       <c r="N851" s="8" t="n"/>
     </row>
     <row r="852">
@@ -34180,25 +33055,11 @@
       <c r="F852" s="11" t="n">
         <v>45934</v>
       </c>
-      <c r="G852" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H852" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I852" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J852" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K852" s="34" t="n">
-        <v>3812</v>
-      </c>
+      <c r="G852" s="8" t="n"/>
+      <c r="H852" s="8" t="n"/>
+      <c r="I852" s="8" t="n"/>
+      <c r="J852" s="8" t="n"/>
+      <c r="K852" s="8" t="n"/>
       <c r="L852" s="8" t="n"/>
       <c r="M852" s="11" t="n"/>
       <c r="N852" s="8" t="n"/>
@@ -35184,25 +34045,11 @@
         <v>6054</v>
       </c>
       <c r="F885" s="8" t="n"/>
-      <c r="G885" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H885" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I885" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J885" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K885" s="34" t="n">
-        <v>2162</v>
-      </c>
+      <c r="G885" s="8" t="n"/>
+      <c r="H885" s="8" t="n"/>
+      <c r="I885" s="8" t="n"/>
+      <c r="J885" s="8" t="n"/>
+      <c r="K885" s="8" t="n"/>
       <c r="L885" s="8" t="n"/>
       <c r="M885" s="8" t="n"/>
       <c r="N885" s="8" t="n"/>
@@ -35918,25 +34765,11 @@
         <v>10130</v>
       </c>
       <c r="F909" s="8" t="n"/>
-      <c r="G909" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H909" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I909" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J909" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K909" s="34" t="n">
-        <v>5659</v>
-      </c>
+      <c r="G909" s="8" t="n"/>
+      <c r="H909" s="8" t="n"/>
+      <c r="I909" s="8" t="n"/>
+      <c r="J909" s="8" t="n"/>
+      <c r="K909" s="8" t="n"/>
       <c r="L909" s="8" t="n"/>
       <c r="M909" s="8" t="n"/>
       <c r="N909" s="8" t="n"/>
@@ -36172,25 +35005,11 @@
         <v>1597</v>
       </c>
       <c r="F917" s="8" t="n"/>
-      <c r="G917" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H917" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I917" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J917" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K917" s="34" t="n">
-        <v>349</v>
-      </c>
+      <c r="G917" s="8" t="n"/>
+      <c r="H917" s="8" t="n"/>
+      <c r="I917" s="8" t="n"/>
+      <c r="J917" s="8" t="n"/>
+      <c r="K917" s="8" t="n"/>
       <c r="L917" s="8" t="n"/>
       <c r="M917" s="8" t="n"/>
       <c r="N917" s="8" t="n"/>
@@ -36366,25 +35185,11 @@
         <v>600</v>
       </c>
       <c r="F923" s="8" t="n"/>
-      <c r="G923" s="30" t="n">
-        <v>45894</v>
-      </c>
-      <c r="H923" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I923" s="32" t="inlineStr">
-        <is>
-          <t>002566</t>
-        </is>
-      </c>
-      <c r="J923" s="33" t="n">
-        <v>35999</v>
-      </c>
-      <c r="K923" s="34" t="n">
-        <v>20294</v>
-      </c>
+      <c r="G923" s="8" t="n"/>
+      <c r="H923" s="8" t="n"/>
+      <c r="I923" s="8" t="n"/>
+      <c r="J923" s="8" t="n"/>
+      <c r="K923" s="8" t="n"/>
       <c r="L923" s="8" t="n"/>
       <c r="M923" s="8" t="n"/>
       <c r="N923" s="8" t="n"/>
@@ -36410,25 +35215,11 @@
         <v>325</v>
       </c>
       <c r="F924" s="8" t="n"/>
-      <c r="G924" s="30" t="n">
-        <v>45894</v>
-      </c>
-      <c r="H924" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I924" s="32" t="inlineStr">
-        <is>
-          <t>002566</t>
-        </is>
-      </c>
-      <c r="J924" s="33" t="n">
-        <v>35999</v>
-      </c>
-      <c r="K924" s="34" t="n">
-        <v>11561</v>
-      </c>
+      <c r="G924" s="8" t="n"/>
+      <c r="H924" s="8" t="n"/>
+      <c r="I924" s="8" t="n"/>
+      <c r="J924" s="8" t="n"/>
+      <c r="K924" s="8" t="n"/>
       <c r="L924" s="8" t="n"/>
       <c r="M924" s="8" t="n"/>
       <c r="N924" s="8" t="n"/>
@@ -36784,19 +35575,11 @@
         <v>1306</v>
       </c>
       <c r="F936" s="8" t="n"/>
-      <c r="G936" s="32" t="n"/>
-      <c r="H936" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I936" s="32" t="inlineStr"/>
-      <c r="J936" s="33" t="n">
-        <v>68712</v>
-      </c>
-      <c r="K936" s="34" t="n">
-        <v>6314</v>
-      </c>
+      <c r="G936" s="8" t="n"/>
+      <c r="H936" s="8" t="n"/>
+      <c r="I936" s="8" t="n"/>
+      <c r="J936" s="8" t="n"/>
+      <c r="K936" s="8" t="n"/>
       <c r="L936" s="8" t="n"/>
       <c r="M936" s="8" t="n"/>
       <c r="N936" s="8" t="n"/>
@@ -36822,19 +35605,11 @@
         <v>23909</v>
       </c>
       <c r="F937" s="8" t="n"/>
-      <c r="G937" s="32" t="n"/>
-      <c r="H937" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I937" s="32" t="inlineStr"/>
-      <c r="J937" s="33" t="n">
-        <v>68712</v>
-      </c>
-      <c r="K937" s="34" t="n">
-        <v>959</v>
-      </c>
+      <c r="G937" s="8" t="n"/>
+      <c r="H937" s="8" t="n"/>
+      <c r="I937" s="8" t="n"/>
+      <c r="J937" s="8" t="n"/>
+      <c r="K937" s="8" t="n"/>
       <c r="L937" s="8" t="n"/>
       <c r="M937" s="8" t="n"/>
       <c r="N937" s="8" t="n"/>
@@ -37040,25 +35815,11 @@
         <v>168</v>
       </c>
       <c r="F944" s="8" t="n"/>
-      <c r="G944" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H944" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I944" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J944" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K944" s="34" t="n">
-        <v>5670</v>
-      </c>
+      <c r="G944" s="8" t="n"/>
+      <c r="H944" s="8" t="n"/>
+      <c r="I944" s="8" t="n"/>
+      <c r="J944" s="8" t="n"/>
+      <c r="K944" s="8" t="n"/>
       <c r="L944" s="8" t="n"/>
       <c r="M944" s="8" t="n"/>
       <c r="N944" s="8" t="n"/>
@@ -39274,25 +38035,11 @@
         <v>3369</v>
       </c>
       <c r="F1018" s="8" t="n"/>
-      <c r="G1018" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H1018" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I1018" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J1018" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K1018" s="34" t="n">
-        <v>12245</v>
-      </c>
+      <c r="G1018" s="8" t="n"/>
+      <c r="H1018" s="8" t="n"/>
+      <c r="I1018" s="8" t="n"/>
+      <c r="J1018" s="8" t="n"/>
+      <c r="K1018" s="8" t="n"/>
       <c r="L1018" s="8" t="n"/>
       <c r="M1018" s="8" t="n"/>
       <c r="N1018" s="8" t="n"/>
@@ -39378,25 +38125,11 @@
         <v>310</v>
       </c>
       <c r="F1021" s="8" t="n"/>
-      <c r="G1021" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H1021" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I1021" s="32" t="inlineStr">
-        <is>
-          <t>002419</t>
-        </is>
-      </c>
-      <c r="J1021" s="33" t="n">
-        <v>70582</v>
-      </c>
-      <c r="K1021" s="34" t="n">
-        <v>1110</v>
-      </c>
+      <c r="G1021" s="8" t="n"/>
+      <c r="H1021" s="8" t="n"/>
+      <c r="I1021" s="8" t="n"/>
+      <c r="J1021" s="8" t="n"/>
+      <c r="K1021" s="8" t="n"/>
       <c r="L1021" s="8" t="n"/>
       <c r="M1021" s="8" t="n"/>
       <c r="N1021" s="8" t="n"/>
@@ -39642,14 +38375,14 @@
       <c r="N1029" s="12" t="n"/>
     </row>
     <row r="1030" ht="15" customHeight="1" thickBot="1">
-      <c r="A1030" s="41" t="inlineStr">
+      <c r="A1030" s="40" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B1030" s="42" t="n"/>
-      <c r="C1030" s="42" t="n"/>
-      <c r="D1030" s="43" t="n"/>
+      <c r="B1030" s="41" t="n"/>
+      <c r="C1030" s="41" t="n"/>
+      <c r="D1030" s="42" t="n"/>
       <c r="E1030" s="23">
         <f>SUM(E852:E1029)</f>
         <v/>

--- a/System_Puchase.xlsx
+++ b/System_Puchase.xlsx
@@ -88,8 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -276,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
@@ -321,16 +321,17 @@
     <xf numFmtId="16" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -927,23 +928,17 @@
       <c r="F3" s="8" t="n">
         <v>463</v>
       </c>
-      <c r="G3" s="30" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I3" s="32" t="inlineStr"/>
-      <c r="J3" s="33" t="n">
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="30" t="n">
         <v>16897</v>
       </c>
-      <c r="K3" s="34" t="n">
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="31" t="n">
         <v>463</v>
       </c>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8" t="n"/>
       <c r="N3" s="8" t="n"/>
     </row>
     <row r="4">
@@ -971,15 +966,15 @@
       <c r="F4" s="8" t="n">
         <v>1193</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -1017,20 +1012,20 @@
       <c r="F5" s="8" t="n">
         <v>341</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H5" s="31" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J5" s="33" t="n">
+      <c r="J5" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K5" s="34" t="n">
@@ -1065,23 +1060,17 @@
       <c r="F6" s="8" t="n">
         <v>1099</v>
       </c>
-      <c r="G6" s="31" t="n">
-        <v>45808</v>
-      </c>
-      <c r="H6" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I6" s="32" t="inlineStr"/>
-      <c r="J6" s="33" t="n">
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="30" t="n">
         <v>23923</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="31" t="n">
         <v>1099</v>
       </c>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n"/>
     </row>
     <row r="7">
@@ -1109,23 +1098,17 @@
       <c r="F7" s="8" t="n">
         <v>1138</v>
       </c>
-      <c r="G7" s="30" t="n">
-        <v>45833</v>
-      </c>
-      <c r="H7" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I7" s="32" t="inlineStr"/>
-      <c r="J7" s="33" t="n">
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="30" t="n">
         <v>52145</v>
       </c>
-      <c r="K7" s="34" t="n">
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="31" t="n">
         <v>1138</v>
       </c>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
     </row>
     <row r="8">
@@ -1153,15 +1136,15 @@
       <c r="F8" s="8" t="n">
         <v>1693</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="32" t="n">
         <v>45818</v>
       </c>
-      <c r="H8" s="31" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>002402</t>
         </is>
@@ -1199,20 +1182,20 @@
       <c r="F9" s="8" t="n">
         <v>576</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="35" t="n">
         <v>45853</v>
       </c>
-      <c r="H9" s="31" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>002491</t>
         </is>
       </c>
-      <c r="J9" s="33" t="n">
+      <c r="J9" s="30" t="n">
         <v>27994</v>
       </c>
       <c r="K9" s="34" t="n">
@@ -1247,20 +1230,20 @@
       <c r="F10" s="8" t="n">
         <v>167</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="35" t="n">
         <v>45832</v>
       </c>
-      <c r="H10" s="31" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>002457</t>
         </is>
       </c>
-      <c r="J10" s="33" t="n">
+      <c r="J10" s="30" t="n">
         <v>26866</v>
       </c>
       <c r="K10" s="34" t="n">
@@ -1295,20 +1278,20 @@
       <c r="F11" s="8" t="n">
         <v>274</v>
       </c>
-      <c r="G11" s="31" t="n">
+      <c r="G11" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H11" s="31" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J11" s="33" t="n">
+      <c r="J11" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K11" s="34" t="n">
@@ -1343,23 +1326,17 @@
       <c r="F12" s="8" t="n">
         <v>5551</v>
       </c>
-      <c r="G12" s="31" t="n">
-        <v>45808</v>
-      </c>
-      <c r="H12" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I12" s="32" t="inlineStr"/>
-      <c r="J12" s="33" t="n">
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="30" t="n">
         <v>23923</v>
       </c>
-      <c r="K12" s="34" t="n">
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="31" t="n">
         <v>5551</v>
       </c>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
     </row>
     <row r="13">
@@ -1421,23 +1398,17 @@
       <c r="F14" s="8" t="n">
         <v>2228</v>
       </c>
-      <c r="G14" s="30" t="n">
-        <v>45833</v>
-      </c>
-      <c r="H14" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I14" s="32" t="inlineStr"/>
-      <c r="J14" s="33" t="n">
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="30" t="n">
         <v>52145</v>
       </c>
-      <c r="K14" s="34" t="n">
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="31" t="n">
         <v>2228</v>
       </c>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
     </row>
     <row r="15">
@@ -1465,15 +1436,15 @@
       <c r="F15" s="8" t="n">
         <v>7873</v>
       </c>
-      <c r="G15" s="31" t="n">
+      <c r="G15" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H15" s="31" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -1511,15 +1482,15 @@
       <c r="F16" s="8" t="n">
         <v>13488</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="35" t="n">
         <v>45827</v>
       </c>
-      <c r="H16" s="31" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>002429</t>
         </is>
@@ -1659,15 +1630,15 @@
       <c r="F20" s="8" t="n">
         <v>458</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H20" s="31" t="inlineStr">
+      <c r="H20" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I20" s="32" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -1705,23 +1676,17 @@
       <c r="F21" s="8" t="n">
         <v>623</v>
       </c>
-      <c r="G21" s="31" t="n">
-        <v>45808</v>
-      </c>
-      <c r="H21" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I21" s="32" t="inlineStr"/>
-      <c r="J21" s="33" t="n">
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="30" t="n">
         <v>23923</v>
       </c>
-      <c r="K21" s="34" t="n">
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="31" t="n">
         <v>623</v>
       </c>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
     </row>
     <row r="22">
@@ -1749,15 +1714,15 @@
       <c r="F22" s="8" t="n">
         <v>5224</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H22" s="31" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I22" s="32" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -1795,23 +1760,17 @@
       <c r="F23" s="8" t="n">
         <v>356</v>
       </c>
-      <c r="G23" s="30" t="n">
-        <v>45808</v>
-      </c>
-      <c r="H23" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I23" s="32" t="inlineStr"/>
-      <c r="J23" s="33" t="n">
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="30" t="n">
         <v>3193</v>
       </c>
-      <c r="K23" s="34" t="n">
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="31" t="n">
         <v>356</v>
       </c>
-      <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n"/>
     </row>
     <row r="24">
@@ -1907,21 +1866,21 @@
       <c r="F26" s="12" t="n">
         <v>3567</v>
       </c>
-      <c r="G26" s="35" t="n">
+      <c r="G26" s="36" t="n">
         <v>45868</v>
       </c>
-      <c r="H26" s="35" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I26" s="36" t="inlineStr">
+      <c r="I26" s="37" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
       </c>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="37" t="n">
+      <c r="K26" s="38" t="n">
         <v>3567</v>
       </c>
       <c r="L26" s="12" t="n"/>
@@ -1966,7 +1925,7 @@
           <t>002562</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n">
+      <c r="J27" s="39" t="n">
         <v>9492</v>
       </c>
       <c r="K27" s="29" t="n">
@@ -2035,20 +1994,20 @@
       <c r="F29" s="8" t="n">
         <v>907</v>
       </c>
-      <c r="G29" s="31" t="n">
+      <c r="G29" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H29" s="31" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J29" s="33" t="n">
+      <c r="J29" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K29" s="34" t="n">
@@ -2151,15 +2110,15 @@
       <c r="F32" s="8" t="n">
         <v>609</v>
       </c>
-      <c r="G32" s="31" t="n">
+      <c r="G32" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H32" s="31" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I32" s="32" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -2197,21 +2156,15 @@
       <c r="F33" s="8" t="n">
         <v>1197</v>
       </c>
-      <c r="G33" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H33" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I33" s="32" t="inlineStr"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
-      <c r="K33" s="34" t="n">
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="31" t="n">
         <v>1197</v>
       </c>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n"/>
     </row>
     <row r="34">
@@ -2239,15 +2192,15 @@
       <c r="F34" s="8" t="n">
         <v>2451</v>
       </c>
-      <c r="G34" s="31" t="n">
+      <c r="G34" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H34" s="31" t="inlineStr">
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I34" s="32" t="inlineStr">
+      <c r="I34" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -2285,25 +2238,15 @@
       <c r="F35" s="8" t="n">
         <v>4898</v>
       </c>
-      <c r="G35" s="31" t="n">
-        <v>45826</v>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I35" s="32" t="inlineStr">
-        <is>
-          <t>002438</t>
-        </is>
-      </c>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="8" t="n"/>
       <c r="J35" s="8" t="n"/>
-      <c r="K35" s="34" t="n">
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="31" t="n">
         <v>4898</v>
       </c>
-      <c r="L35" s="8" t="n"/>
-      <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n"/>
     </row>
     <row r="36">
@@ -2331,21 +2274,15 @@
       <c r="F36" s="8" t="n">
         <v>1417</v>
       </c>
-      <c r="G36" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H36" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I36" s="32" t="inlineStr"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="8" t="n"/>
       <c r="J36" s="8" t="n"/>
-      <c r="K36" s="34" t="n">
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="31" t="n">
         <v>1417</v>
       </c>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n"/>
     </row>
     <row r="37">
@@ -2373,15 +2310,15 @@
       <c r="F37" s="8" t="n">
         <v>799</v>
       </c>
-      <c r="G37" s="31" t="n">
+      <c r="G37" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H37" s="31" t="inlineStr">
+      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I37" s="32" t="inlineStr">
+      <c r="I37" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -2419,21 +2356,15 @@
       <c r="F38" s="8" t="n">
         <v>547</v>
       </c>
-      <c r="G38" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H38" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I38" s="32" t="inlineStr"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
       <c r="J38" s="8" t="n"/>
-      <c r="K38" s="34" t="n">
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="31" t="n">
         <v>547</v>
       </c>
-      <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n"/>
     </row>
     <row r="39">
@@ -2461,15 +2392,15 @@
       <c r="F39" s="8" t="n">
         <v>531</v>
       </c>
-      <c r="G39" s="31" t="n">
+      <c r="G39" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H39" s="31" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I39" s="32" t="inlineStr">
+      <c r="I39" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -2507,21 +2438,15 @@
       <c r="F40" s="8" t="n">
         <v>1986</v>
       </c>
-      <c r="G40" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H40" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I40" s="32" t="inlineStr"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
       <c r="J40" s="8" t="n"/>
-      <c r="K40" s="34" t="n">
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="31" t="n">
         <v>1986</v>
       </c>
-      <c r="L40" s="8" t="n"/>
-      <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n"/>
     </row>
     <row r="41">
@@ -2549,21 +2474,15 @@
       <c r="F41" s="8" t="n">
         <v>5294</v>
       </c>
-      <c r="G41" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H41" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I41" s="32" t="inlineStr"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="8" t="n"/>
       <c r="J41" s="8" t="n"/>
-      <c r="K41" s="34" t="n">
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="31" t="n">
         <v>5294</v>
       </c>
-      <c r="L41" s="8" t="n"/>
-      <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n"/>
     </row>
     <row r="42">
@@ -2591,15 +2510,15 @@
       <c r="F42" s="8" t="n">
         <v>433</v>
       </c>
-      <c r="G42" s="31" t="n">
+      <c r="G42" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H42" s="31" t="inlineStr">
+      <c r="H42" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I42" s="32" t="inlineStr">
+      <c r="I42" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -2637,21 +2556,15 @@
       <c r="F43" s="8" t="n">
         <v>1048</v>
       </c>
-      <c r="G43" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H43" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I43" s="32" t="inlineStr"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
-      <c r="K43" s="34" t="n">
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="31" t="n">
         <v>1048</v>
       </c>
-      <c r="L43" s="8" t="n"/>
-      <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n"/>
     </row>
     <row r="44">
@@ -2679,21 +2592,15 @@
       <c r="F44" s="8" t="n">
         <v>634</v>
       </c>
-      <c r="G44" s="30" t="n">
-        <v>45811</v>
-      </c>
-      <c r="H44" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I44" s="32" t="inlineStr"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="n"/>
-      <c r="K44" s="34" t="n">
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="31" t="n">
         <v>634</v>
       </c>
-      <c r="L44" s="8" t="n"/>
-      <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n"/>
     </row>
     <row r="45">
@@ -2721,15 +2628,15 @@
       <c r="F45" s="8" t="n">
         <v>3083</v>
       </c>
-      <c r="G45" s="31" t="n">
+      <c r="G45" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H45" s="31" t="inlineStr">
+      <c r="H45" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I45" s="32" t="inlineStr">
+      <c r="I45" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -2767,21 +2674,15 @@
       <c r="F46" s="8" t="n">
         <v>504</v>
       </c>
-      <c r="G46" s="31" t="n">
-        <v>45872</v>
-      </c>
-      <c r="H46" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I46" s="32" t="inlineStr"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="8" t="n"/>
       <c r="J46" s="8" t="n"/>
-      <c r="K46" s="34" t="n">
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
+      <c r="M46" s="31" t="n">
         <v>504</v>
       </c>
-      <c r="L46" s="8" t="n"/>
-      <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n"/>
     </row>
     <row r="47">
@@ -2809,21 +2710,15 @@
       <c r="F47" s="8" t="n">
         <v>1443</v>
       </c>
-      <c r="G47" s="30" t="n">
-        <v>45821</v>
-      </c>
-      <c r="H47" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I47" s="32" t="inlineStr"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
       <c r="J47" s="8" t="n"/>
-      <c r="K47" s="34" t="n">
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="31" t="n">
         <v>1443</v>
       </c>
-      <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n"/>
     </row>
     <row r="48">
@@ -2851,21 +2746,15 @@
       <c r="F48" s="8" t="n">
         <v>2071</v>
       </c>
-      <c r="G48" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H48" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I48" s="32" t="inlineStr"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
       <c r="J48" s="8" t="n"/>
-      <c r="K48" s="34" t="n">
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="31" t="n">
         <v>2071</v>
       </c>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n"/>
     </row>
     <row r="49">
@@ -2893,21 +2782,15 @@
       <c r="F49" s="8" t="n">
         <v>339</v>
       </c>
-      <c r="G49" s="30" t="n">
-        <v>45812</v>
-      </c>
-      <c r="H49" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I49" s="32" t="inlineStr"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n"/>
-      <c r="K49" s="34" t="n">
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="31" t="n">
         <v>339</v>
       </c>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n"/>
     </row>
     <row r="50">
@@ -2935,21 +2818,15 @@
       <c r="F50" s="8" t="n">
         <v>437</v>
       </c>
-      <c r="G50" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H50" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I50" s="32" t="inlineStr"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n"/>
-      <c r="K50" s="34" t="n">
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="31" t="n">
         <v>437</v>
       </c>
-      <c r="L50" s="8" t="n"/>
-      <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
     </row>
     <row r="51">
@@ -2977,15 +2854,15 @@
       <c r="F51" s="8" t="n">
         <v>6324</v>
       </c>
-      <c r="G51" s="31" t="n">
+      <c r="G51" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H51" s="31" t="inlineStr">
+      <c r="H51" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I51" s="32" t="inlineStr">
+      <c r="I51" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -3023,20 +2900,20 @@
       <c r="F52" s="8" t="n">
         <v>3372</v>
       </c>
-      <c r="G52" s="31" t="n">
+      <c r="G52" s="32" t="n">
         <v>45837</v>
       </c>
-      <c r="H52" s="31" t="inlineStr">
+      <c r="H52" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I52" s="32" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
         <is>
           <t>002463</t>
         </is>
       </c>
-      <c r="J52" s="33" t="n">
+      <c r="J52" s="30" t="n">
         <v>11958</v>
       </c>
       <c r="K52" s="34" t="n">
@@ -3071,21 +2948,15 @@
       <c r="F53" s="8" t="n">
         <v>1197</v>
       </c>
-      <c r="G53" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H53" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I53" s="32" t="inlineStr"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
       <c r="J53" s="8" t="n"/>
-      <c r="K53" s="34" t="n">
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="31" t="n">
         <v>1197</v>
       </c>
-      <c r="L53" s="8" t="n"/>
-      <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n"/>
     </row>
     <row r="54">
@@ -3113,21 +2984,15 @@
       <c r="F54" s="8" t="n">
         <v>2178</v>
       </c>
-      <c r="G54" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H54" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I54" s="32" t="inlineStr"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="n"/>
-      <c r="K54" s="34" t="n">
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="31" t="n">
         <v>2178</v>
       </c>
-      <c r="L54" s="8" t="n"/>
-      <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n"/>
     </row>
     <row r="55">
@@ -3155,15 +3020,15 @@
       <c r="F55" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="G55" s="31" t="n">
+      <c r="G55" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H55" s="31" t="inlineStr">
+      <c r="H55" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I55" s="32" t="inlineStr">
+      <c r="I55" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -3201,21 +3066,15 @@
       <c r="F56" s="8" t="n">
         <v>2296</v>
       </c>
-      <c r="G56" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H56" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I56" s="32" t="inlineStr"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="n"/>
-      <c r="K56" s="34" t="n">
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="31" t="n">
         <v>2296</v>
       </c>
-      <c r="L56" s="8" t="n"/>
-      <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
     </row>
     <row r="57">
@@ -3243,21 +3102,15 @@
       <c r="F57" s="8" t="n">
         <v>1796</v>
       </c>
-      <c r="G57" s="30" t="n">
-        <v>45819</v>
-      </c>
-      <c r="H57" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I57" s="32" t="inlineStr"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n"/>
-      <c r="K57" s="34" t="n">
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="31" t="n">
         <v>1796</v>
       </c>
-      <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n"/>
     </row>
     <row r="58">
@@ -3455,15 +3308,15 @@
       <c r="F63" s="8" t="n">
         <v>4577</v>
       </c>
-      <c r="G63" s="31" t="n">
+      <c r="G63" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H63" s="31" t="inlineStr">
+      <c r="H63" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I63" s="32" t="inlineStr">
+      <c r="I63" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -3501,21 +3354,15 @@
       <c r="F64" s="8" t="n">
         <v>9499</v>
       </c>
-      <c r="G64" s="31" t="n">
-        <v>45854</v>
-      </c>
-      <c r="H64" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr"/>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="11" t="n"/>
+      <c r="I64" s="8" t="n"/>
       <c r="J64" s="8" t="n"/>
-      <c r="K64" s="34" t="n">
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="31" t="n">
         <v>9499</v>
       </c>
-      <c r="L64" s="8" t="n"/>
-      <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
     </row>
     <row r="65">
@@ -3611,15 +3458,15 @@
       <c r="F67" s="8" t="n">
         <v>985</v>
       </c>
-      <c r="G67" s="31" t="n">
+      <c r="G67" s="32" t="n">
         <v>45823</v>
       </c>
-      <c r="H67" s="31" t="inlineStr">
+      <c r="H67" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
+      <c r="I67" s="33" t="inlineStr">
         <is>
           <t>002421</t>
         </is>
@@ -3657,15 +3504,15 @@
       <c r="F68" s="8" t="n">
         <v>4806</v>
       </c>
-      <c r="G68" s="31" t="n">
+      <c r="G68" s="32" t="n">
         <v>45823</v>
       </c>
-      <c r="H68" s="31" t="inlineStr">
+      <c r="H68" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I68" s="32" t="inlineStr">
+      <c r="I68" s="33" t="inlineStr">
         <is>
           <t>002421</t>
         </is>
@@ -3771,21 +3618,15 @@
       <c r="F71" s="8" t="n">
         <v>2169</v>
       </c>
-      <c r="G71" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H71" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="11" t="n"/>
+      <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
-      <c r="K71" s="34" t="n">
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="31" t="n">
         <v>2169</v>
       </c>
-      <c r="L71" s="8" t="n"/>
-      <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n"/>
     </row>
     <row r="72">
@@ -3813,21 +3654,15 @@
       <c r="F72" s="8" t="n">
         <v>5939</v>
       </c>
-      <c r="G72" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H72" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="11" t="n"/>
+      <c r="I72" s="8" t="n"/>
       <c r="J72" s="8" t="n"/>
-      <c r="K72" s="34" t="n">
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="8" t="n"/>
+      <c r="M72" s="31" t="n">
         <v>5939</v>
       </c>
-      <c r="L72" s="8" t="n"/>
-      <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n"/>
     </row>
     <row r="73">
@@ -3855,21 +3690,15 @@
       <c r="F73" s="8" t="n">
         <v>4565</v>
       </c>
-      <c r="G73" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H73" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n"/>
-      <c r="K73" s="34" t="n">
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="31" t="n">
         <v>4565</v>
       </c>
-      <c r="L73" s="8" t="n"/>
-      <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n"/>
     </row>
     <row r="74">
@@ -3897,21 +3726,15 @@
       <c r="F74" s="8" t="n">
         <v>3925</v>
       </c>
-      <c r="G74" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H74" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
+      <c r="G74" s="8" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="8" t="n"/>
       <c r="J74" s="8" t="n"/>
-      <c r="K74" s="34" t="n">
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n"/>
+      <c r="M74" s="31" t="n">
         <v>3925</v>
       </c>
-      <c r="L74" s="8" t="n"/>
-      <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n"/>
     </row>
     <row r="75">
@@ -3939,21 +3762,15 @@
       <c r="F75" s="8" t="n">
         <v>8180</v>
       </c>
-      <c r="G75" s="30" t="n">
-        <v>45817</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
       <c r="J75" s="8" t="n"/>
-      <c r="K75" s="34" t="n">
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="31" t="n">
         <v>8180</v>
       </c>
-      <c r="L75" s="8" t="n"/>
-      <c r="M75" s="8" t="n"/>
       <c r="N75" s="8" t="n"/>
     </row>
     <row r="76">
@@ -4015,25 +3832,15 @@
       <c r="F77" s="8" t="n">
         <v>8872</v>
       </c>
-      <c r="G77" s="31" t="n">
-        <v>45825</v>
-      </c>
-      <c r="H77" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>002425</t>
-        </is>
-      </c>
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="11" t="n"/>
+      <c r="I77" s="8" t="n"/>
       <c r="J77" s="8" t="n"/>
-      <c r="K77" s="34" t="n">
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="31" t="n">
         <v>8872</v>
       </c>
-      <c r="L77" s="8" t="n"/>
-      <c r="M77" s="8" t="n"/>
       <c r="N77" s="8" t="n"/>
     </row>
     <row r="78">
@@ -4129,25 +3936,15 @@
       <c r="F80" s="8" t="n">
         <v>5056</v>
       </c>
-      <c r="G80" s="31" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H80" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr">
-        <is>
-          <t>002458</t>
-        </is>
-      </c>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="11" t="n"/>
+      <c r="I80" s="8" t="n"/>
       <c r="J80" s="8" t="n"/>
-      <c r="K80" s="34" t="n">
-        <v>5055</v>
-      </c>
+      <c r="K80" s="8" t="n"/>
       <c r="L80" s="8" t="n"/>
-      <c r="M80" s="8" t="n"/>
+      <c r="M80" s="31" t="n">
+        <v>5056</v>
+      </c>
       <c r="N80" s="8" t="n"/>
     </row>
     <row r="81">
@@ -4175,15 +3972,15 @@
       <c r="F81" s="8" t="n">
         <v>12192</v>
       </c>
-      <c r="G81" s="31" t="n">
+      <c r="G81" s="32" t="n">
         <v>45835</v>
       </c>
-      <c r="H81" s="31" t="inlineStr">
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr">
+      <c r="I81" s="33" t="inlineStr">
         <is>
           <t>002459</t>
         </is>
@@ -4289,25 +4086,15 @@
       <c r="F84" s="8" t="n">
         <v>699</v>
       </c>
-      <c r="G84" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H84" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I84" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="11" t="n"/>
+      <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
-      <c r="K84" s="34" t="n">
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="n"/>
+      <c r="M84" s="31" t="n">
         <v>699</v>
       </c>
-      <c r="L84" s="8" t="n"/>
-      <c r="M84" s="8" t="n"/>
       <c r="N84" s="8" t="n"/>
     </row>
     <row r="85">
@@ -4403,20 +4190,20 @@
       <c r="F87" s="8" t="n">
         <v>604</v>
       </c>
-      <c r="G87" s="31" t="n">
+      <c r="G87" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H87" s="31" t="inlineStr">
+      <c r="H87" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I87" s="32" t="inlineStr">
+      <c r="I87" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J87" s="33" t="n">
+      <c r="J87" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K87" s="34" t="n">
@@ -4451,21 +4238,15 @@
       <c r="F88" s="8" t="n">
         <v>1934</v>
       </c>
-      <c r="G88" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H88" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I88" s="32" t="inlineStr"/>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="8" t="n"/>
       <c r="J88" s="8" t="n"/>
-      <c r="K88" s="34" t="n">
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="31" t="n">
         <v>1934</v>
       </c>
-      <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
       <c r="N88" s="8" t="n"/>
     </row>
     <row r="89">
@@ -4493,21 +4274,15 @@
       <c r="F89" s="8" t="n">
         <v>5387</v>
       </c>
-      <c r="G89" s="31" t="n">
-        <v>45821</v>
-      </c>
-      <c r="H89" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I89" s="32" t="inlineStr"/>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="11" t="n"/>
+      <c r="I89" s="8" t="n"/>
       <c r="J89" s="8" t="n"/>
-      <c r="K89" s="34" t="n">
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="31" t="n">
         <v>5387</v>
       </c>
-      <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
       <c r="N89" s="8" t="n"/>
     </row>
     <row r="90">
@@ -4535,21 +4310,15 @@
       <c r="F90" s="8" t="n">
         <v>701</v>
       </c>
-      <c r="G90" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H90" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I90" s="32" t="inlineStr"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
-      <c r="K90" s="34" t="n">
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="31" t="n">
         <v>701</v>
       </c>
-      <c r="L90" s="8" t="n"/>
-      <c r="M90" s="8" t="n"/>
       <c r="N90" s="8" t="n"/>
     </row>
     <row r="91">
@@ -4577,21 +4346,15 @@
       <c r="F91" s="8" t="n">
         <v>1092</v>
       </c>
-      <c r="G91" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H91" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I91" s="32" t="inlineStr"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="11" t="n"/>
+      <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
-      <c r="K91" s="34" t="n">
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="31" t="n">
         <v>1092</v>
       </c>
-      <c r="L91" s="8" t="n"/>
-      <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n"/>
     </row>
     <row r="92">
@@ -4619,15 +4382,15 @@
       <c r="F92" s="8" t="n">
         <v>1245</v>
       </c>
-      <c r="G92" s="31" t="n">
+      <c r="G92" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H92" s="31" t="inlineStr">
+      <c r="H92" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I92" s="32" t="inlineStr">
+      <c r="I92" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -4767,21 +4530,15 @@
       <c r="F96" s="8" t="n">
         <v>515</v>
       </c>
-      <c r="G96" s="30" t="n">
-        <v>45819</v>
-      </c>
-      <c r="H96" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I96" s="32" t="inlineStr"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
       <c r="J96" s="8" t="n"/>
-      <c r="K96" s="34" t="n">
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="31" t="n">
         <v>515</v>
       </c>
-      <c r="L96" s="8" t="n"/>
-      <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n"/>
     </row>
     <row r="97">
@@ -4809,21 +4566,15 @@
       <c r="F97" s="8" t="n">
         <v>352</v>
       </c>
-      <c r="G97" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H97" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I97" s="32" t="inlineStr"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="11" t="n"/>
+      <c r="I97" s="8" t="n"/>
       <c r="J97" s="8" t="n"/>
-      <c r="K97" s="34" t="n">
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="31" t="n">
         <v>352</v>
       </c>
-      <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n"/>
     </row>
     <row r="98">
@@ -4851,21 +4602,15 @@
       <c r="F98" s="8" t="n">
         <v>715</v>
       </c>
-      <c r="G98" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H98" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I98" s="32" t="inlineStr"/>
+      <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
       <c r="J98" s="8" t="n"/>
-      <c r="K98" s="34" t="n">
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
+      <c r="M98" s="31" t="n">
         <v>715</v>
       </c>
-      <c r="L98" s="8" t="n"/>
-      <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n"/>
     </row>
     <row r="99">
@@ -4893,21 +4638,15 @@
       <c r="F99" s="8" t="n">
         <v>1736</v>
       </c>
-      <c r="G99" s="30" t="n">
-        <v>45819</v>
-      </c>
-      <c r="H99" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I99" s="32" t="inlineStr"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
-      <c r="K99" s="34" t="n">
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="31" t="n">
         <v>1736</v>
       </c>
-      <c r="L99" s="8" t="n"/>
-      <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n"/>
     </row>
     <row r="100">
@@ -4935,15 +4674,15 @@
       <c r="F100" s="8" t="n">
         <v>648</v>
       </c>
-      <c r="G100" s="31" t="n">
+      <c r="G100" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H100" s="31" t="inlineStr">
+      <c r="H100" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I100" s="32" t="inlineStr">
+      <c r="I100" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -4981,15 +4720,15 @@
       <c r="F101" s="8" t="n">
         <v>334</v>
       </c>
-      <c r="G101" s="31" t="n">
+      <c r="G101" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H101" s="31" t="inlineStr">
+      <c r="H101" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I101" s="32" t="inlineStr">
+      <c r="I101" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -5027,20 +4766,20 @@
       <c r="F102" s="8" t="n">
         <v>313</v>
       </c>
-      <c r="G102" s="31" t="n">
+      <c r="G102" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H102" s="31" t="inlineStr">
+      <c r="H102" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I102" s="32" t="inlineStr">
+      <c r="I102" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J102" s="33" t="n">
+      <c r="J102" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K102" s="34" t="n">
@@ -5075,21 +4814,15 @@
       <c r="F103" s="8" t="n">
         <v>2486</v>
       </c>
-      <c r="G103" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H103" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I103" s="32" t="inlineStr"/>
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="11" t="n"/>
+      <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n"/>
-      <c r="K103" s="34" t="n">
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="8" t="n"/>
+      <c r="M103" s="31" t="n">
         <v>2486</v>
       </c>
-      <c r="L103" s="8" t="n"/>
-      <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n"/>
     </row>
     <row r="104">
@@ -5151,15 +4884,15 @@
       <c r="F105" s="8" t="n">
         <v>2959</v>
       </c>
-      <c r="G105" s="31" t="n">
+      <c r="G105" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H105" s="31" t="inlineStr">
+      <c r="H105" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I105" s="32" t="inlineStr">
+      <c r="I105" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -5197,15 +4930,15 @@
       <c r="F106" s="8" t="n">
         <v>2820</v>
       </c>
-      <c r="G106" s="31" t="n">
+      <c r="G106" s="32" t="n">
         <v>45868</v>
       </c>
-      <c r="H106" s="31" t="inlineStr">
+      <c r="H106" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I106" s="32" t="inlineStr">
+      <c r="I106" s="33" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
@@ -5277,25 +5010,15 @@
       <c r="F108" s="8" t="n">
         <v>2002</v>
       </c>
-      <c r="G108" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H108" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I108" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G108" s="11" t="n"/>
+      <c r="H108" s="11" t="n"/>
+      <c r="I108" s="8" t="n"/>
       <c r="J108" s="8" t="n"/>
-      <c r="K108" s="34" t="n">
+      <c r="K108" s="8" t="n"/>
+      <c r="L108" s="8" t="n"/>
+      <c r="M108" s="31" t="n">
         <v>2002</v>
       </c>
-      <c r="L108" s="8" t="n"/>
-      <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n"/>
     </row>
     <row r="109">
@@ -5323,15 +5046,15 @@
       <c r="F109" s="8" t="n">
         <v>9280</v>
       </c>
-      <c r="G109" s="31" t="n">
+      <c r="G109" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H109" s="31" t="inlineStr">
+      <c r="H109" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I109" s="32" t="inlineStr">
+      <c r="I109" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -5403,21 +5126,15 @@
       <c r="F111" s="8" t="n">
         <v>391</v>
       </c>
-      <c r="G111" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H111" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I111" s="32" t="inlineStr"/>
+      <c r="G111" s="11" t="n"/>
+      <c r="H111" s="11" t="n"/>
+      <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n"/>
-      <c r="K111" s="34" t="n">
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="8" t="n"/>
+      <c r="M111" s="31" t="n">
         <v>391</v>
       </c>
-      <c r="L111" s="8" t="n"/>
-      <c r="M111" s="8" t="n"/>
       <c r="N111" s="8" t="n"/>
     </row>
     <row r="112">
@@ -5445,15 +5162,15 @@
       <c r="F112" s="8" t="n">
         <v>582</v>
       </c>
-      <c r="G112" s="31" t="n">
+      <c r="G112" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H112" s="31" t="inlineStr">
+      <c r="H112" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I112" s="32" t="inlineStr">
+      <c r="I112" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -5491,21 +5208,15 @@
       <c r="F113" s="8" t="n">
         <v>818</v>
       </c>
-      <c r="G113" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H113" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I113" s="32" t="inlineStr"/>
+      <c r="G113" s="11" t="n"/>
+      <c r="H113" s="11" t="n"/>
+      <c r="I113" s="8" t="n"/>
       <c r="J113" s="8" t="n"/>
-      <c r="K113" s="34" t="n">
+      <c r="K113" s="8" t="n"/>
+      <c r="L113" s="8" t="n"/>
+      <c r="M113" s="31" t="n">
         <v>818</v>
       </c>
-      <c r="L113" s="8" t="n"/>
-      <c r="M113" s="8" t="n"/>
       <c r="N113" s="8" t="n"/>
     </row>
     <row r="114">
@@ -5533,21 +5244,15 @@
       <c r="F114" s="8" t="n">
         <v>666</v>
       </c>
-      <c r="G114" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H114" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I114" s="32" t="inlineStr"/>
+      <c r="G114" s="8" t="n"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
       <c r="J114" s="8" t="n"/>
-      <c r="K114" s="34" t="n">
+      <c r="K114" s="8" t="n"/>
+      <c r="L114" s="8" t="n"/>
+      <c r="M114" s="31" t="n">
         <v>666</v>
       </c>
-      <c r="L114" s="8" t="n"/>
-      <c r="M114" s="8" t="n"/>
       <c r="N114" s="8" t="n"/>
     </row>
     <row r="115">
@@ -5575,15 +5280,15 @@
       <c r="F115" s="8" t="n">
         <v>1133</v>
       </c>
-      <c r="G115" s="31" t="n">
+      <c r="G115" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H115" s="31" t="inlineStr">
+      <c r="H115" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I115" s="32" t="inlineStr">
+      <c r="I115" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -5621,21 +5326,15 @@
       <c r="F116" s="8" t="n">
         <v>262</v>
       </c>
-      <c r="G116" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H116" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I116" s="32" t="inlineStr"/>
+      <c r="G116" s="11" t="n"/>
+      <c r="H116" s="11" t="n"/>
+      <c r="I116" s="8" t="n"/>
       <c r="J116" s="8" t="n"/>
-      <c r="K116" s="34" t="n">
+      <c r="K116" s="8" t="n"/>
+      <c r="L116" s="8" t="n"/>
+      <c r="M116" s="31" t="n">
         <v>262</v>
       </c>
-      <c r="L116" s="8" t="n"/>
-      <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n"/>
     </row>
     <row r="117">
@@ -5663,15 +5362,15 @@
       <c r="F117" s="8" t="n">
         <v>1385</v>
       </c>
-      <c r="G117" s="31" t="n">
+      <c r="G117" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H117" s="31" t="inlineStr">
+      <c r="H117" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I117" s="32" t="inlineStr">
+      <c r="I117" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -5709,21 +5408,15 @@
       <c r="F118" s="8" t="n">
         <v>2297</v>
       </c>
-      <c r="G118" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H118" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I118" s="32" t="inlineStr"/>
+      <c r="G118" s="8" t="n"/>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="8" t="n"/>
       <c r="J118" s="8" t="n"/>
-      <c r="K118" s="34" t="n">
+      <c r="K118" s="8" t="n"/>
+      <c r="L118" s="8" t="n"/>
+      <c r="M118" s="31" t="n">
         <v>2297</v>
       </c>
-      <c r="L118" s="8" t="n"/>
-      <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n"/>
     </row>
     <row r="119">
@@ -5785,25 +5478,15 @@
       <c r="F120" s="8" t="n">
         <v>3600</v>
       </c>
-      <c r="G120" s="31" t="n">
-        <v>45826</v>
-      </c>
-      <c r="H120" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I120" s="32" t="inlineStr">
-        <is>
-          <t>002438</t>
-        </is>
-      </c>
+      <c r="G120" s="11" t="n"/>
+      <c r="H120" s="11" t="n"/>
+      <c r="I120" s="8" t="n"/>
       <c r="J120" s="8" t="n"/>
-      <c r="K120" s="34" t="n">
+      <c r="K120" s="8" t="n"/>
+      <c r="L120" s="8" t="n"/>
+      <c r="M120" s="31" t="n">
         <v>3600</v>
       </c>
-      <c r="L120" s="8" t="n"/>
-      <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n"/>
     </row>
     <row r="121">
@@ -6103,21 +5786,15 @@
       <c r="F129" s="8" t="n">
         <v>8737</v>
       </c>
-      <c r="G129" s="30" t="n">
-        <v>45829</v>
-      </c>
-      <c r="H129" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I129" s="32" t="inlineStr"/>
+      <c r="G129" s="8" t="n"/>
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="8" t="n"/>
       <c r="J129" s="8" t="n"/>
-      <c r="K129" s="34" t="n">
+      <c r="K129" s="8" t="n"/>
+      <c r="L129" s="8" t="n"/>
+      <c r="M129" s="31" t="n">
         <v>8737</v>
       </c>
-      <c r="L129" s="8" t="n"/>
-      <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n"/>
     </row>
     <row r="130">
@@ -6145,21 +5822,15 @@
       <c r="F130" s="8" t="n">
         <v>1511</v>
       </c>
-      <c r="G130" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H130" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I130" s="32" t="inlineStr"/>
+      <c r="G130" s="11" t="n"/>
+      <c r="H130" s="11" t="n"/>
+      <c r="I130" s="8" t="n"/>
       <c r="J130" s="8" t="n"/>
-      <c r="K130" s="34" t="n">
+      <c r="K130" s="8" t="n"/>
+      <c r="L130" s="8" t="n"/>
+      <c r="M130" s="31" t="n">
         <v>1511</v>
       </c>
-      <c r="L130" s="8" t="n"/>
-      <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n"/>
     </row>
     <row r="131">
@@ -6187,21 +5858,15 @@
       <c r="F131" s="8" t="n">
         <v>759</v>
       </c>
-      <c r="G131" s="30" t="n">
-        <v>45820</v>
-      </c>
-      <c r="H131" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I131" s="32" t="inlineStr"/>
+      <c r="G131" s="8" t="n"/>
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="8" t="n"/>
       <c r="J131" s="8" t="n"/>
-      <c r="K131" s="34" t="n">
+      <c r="K131" s="8" t="n"/>
+      <c r="L131" s="8" t="n"/>
+      <c r="M131" s="31" t="n">
         <v>759</v>
       </c>
-      <c r="L131" s="8" t="n"/>
-      <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n"/>
     </row>
     <row r="132">
@@ -6229,15 +5894,15 @@
       <c r="F132" s="8" t="n">
         <v>1711</v>
       </c>
-      <c r="G132" s="31" t="n">
+      <c r="G132" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H132" s="31" t="inlineStr">
+      <c r="H132" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I132" s="32" t="inlineStr">
+      <c r="I132" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -6275,25 +5940,15 @@
       <c r="F133" s="8" t="n">
         <v>159</v>
       </c>
-      <c r="G133" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H133" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I133" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G133" s="11" t="n"/>
+      <c r="H133" s="11" t="n"/>
+      <c r="I133" s="8" t="n"/>
       <c r="J133" s="8" t="n"/>
-      <c r="K133" s="34" t="n">
+      <c r="K133" s="8" t="n"/>
+      <c r="L133" s="8" t="n"/>
+      <c r="M133" s="31" t="n">
         <v>159</v>
       </c>
-      <c r="L133" s="8" t="n"/>
-      <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n"/>
     </row>
     <row r="134">
@@ -6321,21 +5976,15 @@
       <c r="F134" s="8" t="n">
         <v>1487</v>
       </c>
-      <c r="G134" s="30" t="n">
-        <v>45834</v>
-      </c>
-      <c r="H134" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I134" s="32" t="inlineStr"/>
+      <c r="G134" s="8" t="n"/>
+      <c r="H134" s="8" t="n"/>
+      <c r="I134" s="8" t="n"/>
       <c r="J134" s="8" t="n"/>
-      <c r="K134" s="34" t="n">
+      <c r="K134" s="8" t="n"/>
+      <c r="L134" s="8" t="n"/>
+      <c r="M134" s="31" t="n">
         <v>1487</v>
       </c>
-      <c r="L134" s="8" t="n"/>
-      <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n"/>
     </row>
     <row r="135">
@@ -6363,15 +6012,15 @@
       <c r="F135" s="8" t="n">
         <v>3654</v>
       </c>
-      <c r="G135" s="31" t="n">
+      <c r="G135" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H135" s="31" t="inlineStr">
+      <c r="H135" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I135" s="32" t="inlineStr">
+      <c r="I135" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -6443,25 +6092,15 @@
       <c r="F137" s="8" t="n">
         <v>5071</v>
       </c>
-      <c r="G137" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H137" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I137" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G137" s="11" t="n"/>
+      <c r="H137" s="11" t="n"/>
+      <c r="I137" s="8" t="n"/>
       <c r="J137" s="8" t="n"/>
-      <c r="K137" s="34" t="n">
+      <c r="K137" s="8" t="n"/>
+      <c r="L137" s="8" t="n"/>
+      <c r="M137" s="31" t="n">
         <v>5071</v>
       </c>
-      <c r="L137" s="8" t="n"/>
-      <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n"/>
     </row>
     <row r="138">
@@ -6523,25 +6162,15 @@
       <c r="F139" s="8" t="n">
         <v>5617</v>
       </c>
-      <c r="G139" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H139" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I139" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G139" s="11" t="n"/>
+      <c r="H139" s="11" t="n"/>
+      <c r="I139" s="8" t="n"/>
       <c r="J139" s="8" t="n"/>
-      <c r="K139" s="34" t="n">
+      <c r="K139" s="8" t="n"/>
+      <c r="L139" s="8" t="n"/>
+      <c r="M139" s="31" t="n">
         <v>5617</v>
       </c>
-      <c r="L139" s="8" t="n"/>
-      <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n"/>
     </row>
     <row r="140">
@@ -6569,25 +6198,15 @@
       <c r="F140" s="8" t="n">
         <v>6371</v>
       </c>
-      <c r="G140" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H140" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I140" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G140" s="11" t="n"/>
+      <c r="H140" s="11" t="n"/>
+      <c r="I140" s="8" t="n"/>
       <c r="J140" s="8" t="n"/>
-      <c r="K140" s="34" t="n">
+      <c r="K140" s="8" t="n"/>
+      <c r="L140" s="8" t="n"/>
+      <c r="M140" s="31" t="n">
         <v>6371</v>
       </c>
-      <c r="L140" s="8" t="n"/>
-      <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n"/>
     </row>
     <row r="141">
@@ -6615,21 +6234,15 @@
       <c r="F141" s="8" t="n">
         <v>1168</v>
       </c>
-      <c r="G141" s="30" t="n">
-        <v>45822</v>
-      </c>
-      <c r="H141" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I141" s="32" t="inlineStr"/>
+      <c r="G141" s="8" t="n"/>
+      <c r="H141" s="8" t="n"/>
+      <c r="I141" s="8" t="n"/>
       <c r="J141" s="8" t="n"/>
-      <c r="K141" s="34" t="n">
+      <c r="K141" s="8" t="n"/>
+      <c r="L141" s="8" t="n"/>
+      <c r="M141" s="31" t="n">
         <v>1168</v>
       </c>
-      <c r="L141" s="8" t="n"/>
-      <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n"/>
     </row>
     <row r="142">
@@ -6657,21 +6270,15 @@
       <c r="F142" s="8" t="n">
         <v>1752</v>
       </c>
-      <c r="G142" s="30" t="n">
-        <v>45822</v>
-      </c>
-      <c r="H142" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I142" s="32" t="inlineStr"/>
+      <c r="G142" s="8" t="n"/>
+      <c r="H142" s="8" t="n"/>
+      <c r="I142" s="8" t="n"/>
       <c r="J142" s="8" t="n"/>
-      <c r="K142" s="34" t="n">
+      <c r="K142" s="8" t="n"/>
+      <c r="L142" s="8" t="n"/>
+      <c r="M142" s="31" t="n">
         <v>1752</v>
       </c>
-      <c r="L142" s="8" t="n"/>
-      <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n"/>
     </row>
     <row r="143">
@@ -6699,21 +6306,15 @@
       <c r="F143" s="8" t="n">
         <v>697</v>
       </c>
-      <c r="G143" s="30" t="n">
-        <v>45829</v>
-      </c>
-      <c r="H143" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I143" s="32" t="inlineStr"/>
+      <c r="G143" s="8" t="n"/>
+      <c r="H143" s="8" t="n"/>
+      <c r="I143" s="8" t="n"/>
       <c r="J143" s="8" t="n"/>
-      <c r="K143" s="34" t="n">
+      <c r="K143" s="8" t="n"/>
+      <c r="L143" s="8" t="n"/>
+      <c r="M143" s="31" t="n">
         <v>697</v>
       </c>
-      <c r="L143" s="8" t="n"/>
-      <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n"/>
     </row>
     <row r="144">
@@ -6741,21 +6342,15 @@
       <c r="F144" s="8" t="n">
         <v>2312</v>
       </c>
-      <c r="G144" s="30" t="n">
-        <v>45829</v>
-      </c>
-      <c r="H144" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I144" s="32" t="inlineStr"/>
+      <c r="G144" s="8" t="n"/>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="8" t="n"/>
       <c r="J144" s="8" t="n"/>
-      <c r="K144" s="34" t="n">
-        <v>2042</v>
-      </c>
+      <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
-      <c r="M144" s="8" t="n"/>
+      <c r="M144" s="31" t="n">
+        <v>2312</v>
+      </c>
       <c r="N144" s="8" t="n"/>
     </row>
     <row r="145">
@@ -6783,25 +6378,15 @@
       <c r="F145" s="8" t="n">
         <v>593</v>
       </c>
-      <c r="G145" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H145" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I145" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G145" s="11" t="n"/>
+      <c r="H145" s="11" t="n"/>
+      <c r="I145" s="8" t="n"/>
       <c r="J145" s="8" t="n"/>
-      <c r="K145" s="34" t="n">
+      <c r="K145" s="8" t="n"/>
+      <c r="L145" s="8" t="n"/>
+      <c r="M145" s="31" t="n">
         <v>593</v>
       </c>
-      <c r="L145" s="8" t="n"/>
-      <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n"/>
     </row>
     <row r="146">
@@ -6829,15 +6414,15 @@
       <c r="F146" s="8" t="n">
         <v>6008</v>
       </c>
-      <c r="G146" s="31" t="n">
+      <c r="G146" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H146" s="31" t="inlineStr">
+      <c r="H146" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I146" s="32" t="inlineStr">
+      <c r="I146" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -6875,21 +6460,15 @@
       <c r="F147" s="8" t="n">
         <v>515</v>
       </c>
-      <c r="G147" s="30" t="n">
-        <v>45827</v>
-      </c>
-      <c r="H147" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I147" s="32" t="inlineStr"/>
+      <c r="G147" s="8" t="n"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
-      <c r="K147" s="34" t="n">
+      <c r="K147" s="8" t="n"/>
+      <c r="L147" s="8" t="n"/>
+      <c r="M147" s="31" t="n">
         <v>515</v>
       </c>
-      <c r="L147" s="8" t="n"/>
-      <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n"/>
     </row>
     <row r="148">
@@ -6917,15 +6496,15 @@
       <c r="F148" s="8" t="n">
         <v>1753</v>
       </c>
-      <c r="G148" s="31" t="n">
+      <c r="G148" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H148" s="31" t="inlineStr">
+      <c r="H148" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I148" s="32" t="inlineStr">
+      <c r="I148" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -6963,21 +6542,15 @@
       <c r="F149" s="8" t="n">
         <v>796</v>
       </c>
-      <c r="G149" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H149" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I149" s="32" t="inlineStr"/>
+      <c r="G149" s="8" t="n"/>
+      <c r="H149" s="8" t="n"/>
+      <c r="I149" s="8" t="n"/>
       <c r="J149" s="8" t="n"/>
-      <c r="K149" s="34" t="n">
+      <c r="K149" s="8" t="n"/>
+      <c r="L149" s="8" t="n"/>
+      <c r="M149" s="31" t="n">
         <v>796</v>
       </c>
-      <c r="L149" s="8" t="n"/>
-      <c r="M149" s="8" t="n"/>
       <c r="N149" s="8" t="n"/>
     </row>
     <row r="150">
@@ -7005,21 +6578,15 @@
       <c r="F150" s="8" t="n">
         <v>862</v>
       </c>
-      <c r="G150" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H150" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I150" s="32" t="inlineStr"/>
+      <c r="G150" s="11" t="n"/>
+      <c r="H150" s="11" t="n"/>
+      <c r="I150" s="8" t="n"/>
       <c r="J150" s="8" t="n"/>
-      <c r="K150" s="34" t="n">
+      <c r="K150" s="8" t="n"/>
+      <c r="L150" s="8" t="n"/>
+      <c r="M150" s="31" t="n">
         <v>862</v>
       </c>
-      <c r="L150" s="8" t="n"/>
-      <c r="M150" s="8" t="n"/>
       <c r="N150" s="8" t="n"/>
     </row>
     <row r="151">
@@ -7081,15 +6648,15 @@
       <c r="F152" s="8" t="n">
         <v>1714</v>
       </c>
-      <c r="G152" s="31" t="n">
+      <c r="G152" s="32" t="n">
         <v>45835</v>
       </c>
-      <c r="H152" s="31" t="inlineStr">
+      <c r="H152" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I152" s="32" t="inlineStr">
+      <c r="I152" s="33" t="inlineStr">
         <is>
           <t>002459</t>
         </is>
@@ -7195,15 +6762,15 @@
       <c r="F155" s="8" t="n">
         <v>4358</v>
       </c>
-      <c r="G155" s="31" t="n">
+      <c r="G155" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H155" s="31" t="inlineStr">
+      <c r="H155" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I155" s="32" t="inlineStr">
+      <c r="I155" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -7241,21 +6808,15 @@
       <c r="F156" s="8" t="n">
         <v>3717</v>
       </c>
-      <c r="G156" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H156" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I156" s="32" t="inlineStr"/>
+      <c r="G156" s="11" t="n"/>
+      <c r="H156" s="11" t="n"/>
+      <c r="I156" s="8" t="n"/>
       <c r="J156" s="8" t="n"/>
-      <c r="K156" s="34" t="n">
+      <c r="K156" s="8" t="n"/>
+      <c r="L156" s="8" t="n"/>
+      <c r="M156" s="31" t="n">
         <v>3717</v>
       </c>
-      <c r="L156" s="8" t="n"/>
-      <c r="M156" s="8" t="n"/>
       <c r="N156" s="8" t="n"/>
     </row>
     <row r="157">
@@ -7283,21 +6844,15 @@
       <c r="F157" s="8" t="n">
         <v>738</v>
       </c>
-      <c r="G157" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H157" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I157" s="32" t="inlineStr"/>
+      <c r="G157" s="8" t="n"/>
+      <c r="H157" s="8" t="n"/>
+      <c r="I157" s="8" t="n"/>
       <c r="J157" s="8" t="n"/>
-      <c r="K157" s="34" t="n">
+      <c r="K157" s="8" t="n"/>
+      <c r="L157" s="8" t="n"/>
+      <c r="M157" s="31" t="n">
         <v>738</v>
       </c>
-      <c r="L157" s="8" t="n"/>
-      <c r="M157" s="8" t="n"/>
       <c r="N157" s="8" t="n"/>
     </row>
     <row r="158">
@@ -7325,21 +6880,15 @@
       <c r="F158" s="8" t="n">
         <v>785</v>
       </c>
-      <c r="G158" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H158" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I158" s="32" t="inlineStr"/>
+      <c r="G158" s="8" t="n"/>
+      <c r="H158" s="8" t="n"/>
+      <c r="I158" s="8" t="n"/>
       <c r="J158" s="8" t="n"/>
-      <c r="K158" s="34" t="n">
+      <c r="K158" s="8" t="n"/>
+      <c r="L158" s="8" t="n"/>
+      <c r="M158" s="31" t="n">
         <v>785</v>
       </c>
-      <c r="L158" s="8" t="n"/>
-      <c r="M158" s="8" t="n"/>
       <c r="N158" s="8" t="n"/>
     </row>
     <row r="159">
@@ -7367,15 +6916,15 @@
       <c r="F159" s="8" t="n">
         <v>396</v>
       </c>
-      <c r="G159" s="31" t="n">
+      <c r="G159" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H159" s="31" t="inlineStr">
+      <c r="H159" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I159" s="32" t="inlineStr">
+      <c r="I159" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -7413,21 +6962,15 @@
       <c r="F160" s="8" t="n">
         <v>2364</v>
       </c>
-      <c r="G160" s="30" t="n">
-        <v>45827</v>
-      </c>
-      <c r="H160" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I160" s="32" t="inlineStr"/>
+      <c r="G160" s="8" t="n"/>
+      <c r="H160" s="8" t="n"/>
+      <c r="I160" s="8" t="n"/>
       <c r="J160" s="8" t="n"/>
-      <c r="K160" s="34" t="n">
+      <c r="K160" s="8" t="n"/>
+      <c r="L160" s="8" t="n"/>
+      <c r="M160" s="31" t="n">
         <v>2364</v>
       </c>
-      <c r="L160" s="8" t="n"/>
-      <c r="M160" s="8" t="n"/>
       <c r="N160" s="8" t="n"/>
     </row>
     <row r="161">
@@ -7455,21 +6998,15 @@
       <c r="F161" s="8" t="n">
         <v>5124</v>
       </c>
-      <c r="G161" s="30" t="n">
-        <v>45825</v>
-      </c>
-      <c r="H161" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I161" s="32" t="inlineStr"/>
+      <c r="G161" s="8" t="n"/>
+      <c r="H161" s="8" t="n"/>
+      <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n"/>
-      <c r="K161" s="34" t="n">
-        <v>5122</v>
-      </c>
+      <c r="K161" s="8" t="n"/>
       <c r="L161" s="8" t="n"/>
-      <c r="M161" s="8" t="n"/>
+      <c r="M161" s="31" t="n">
+        <v>5124</v>
+      </c>
       <c r="N161" s="8" t="n"/>
     </row>
     <row r="162">
@@ -7667,25 +7204,15 @@
       <c r="F167" s="8" t="n">
         <v>3590</v>
       </c>
-      <c r="G167" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H167" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I167" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G167" s="11" t="n"/>
+      <c r="H167" s="11" t="n"/>
+      <c r="I167" s="8" t="n"/>
       <c r="J167" s="8" t="n"/>
-      <c r="K167" s="34" t="n">
+      <c r="K167" s="8" t="n"/>
+      <c r="L167" s="8" t="n"/>
+      <c r="M167" s="31" t="n">
         <v>3590</v>
       </c>
-      <c r="L167" s="8" t="n"/>
-      <c r="M167" s="8" t="n"/>
       <c r="N167" s="8" t="n"/>
     </row>
     <row r="168">
@@ -7713,15 +7240,15 @@
       <c r="F168" s="8" t="n">
         <v>7709</v>
       </c>
-      <c r="G168" s="31" t="n">
+      <c r="G168" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H168" s="31" t="inlineStr">
+      <c r="H168" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I168" s="32" t="inlineStr">
+      <c r="I168" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -7759,21 +7286,15 @@
       <c r="F169" s="8" t="n">
         <v>5281</v>
       </c>
-      <c r="G169" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H169" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I169" s="32" t="inlineStr"/>
+      <c r="G169" s="8" t="n"/>
+      <c r="H169" s="8" t="n"/>
+      <c r="I169" s="8" t="n"/>
       <c r="J169" s="8" t="n"/>
-      <c r="K169" s="34" t="n">
+      <c r="K169" s="8" t="n"/>
+      <c r="L169" s="8" t="n"/>
+      <c r="M169" s="31" t="n">
         <v>5281</v>
       </c>
-      <c r="L169" s="8" t="n"/>
-      <c r="M169" s="8" t="n"/>
       <c r="N169" s="8" t="n"/>
     </row>
     <row r="170">
@@ -7801,21 +7322,15 @@
       <c r="F170" s="8" t="n">
         <v>943</v>
       </c>
-      <c r="G170" s="31" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H170" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I170" s="32" t="inlineStr"/>
+      <c r="G170" s="11" t="n"/>
+      <c r="H170" s="11" t="n"/>
+      <c r="I170" s="8" t="n"/>
       <c r="J170" s="8" t="n"/>
-      <c r="K170" s="34" t="n">
+      <c r="K170" s="8" t="n"/>
+      <c r="L170" s="8" t="n"/>
+      <c r="M170" s="31" t="n">
         <v>943</v>
       </c>
-      <c r="L170" s="8" t="n"/>
-      <c r="M170" s="8" t="n"/>
       <c r="N170" s="8" t="n"/>
     </row>
     <row r="171">
@@ -7843,21 +7358,15 @@
       <c r="F171" s="8" t="n">
         <v>423</v>
       </c>
-      <c r="G171" s="30" t="n">
-        <v>45827</v>
-      </c>
-      <c r="H171" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I171" s="32" t="inlineStr"/>
+      <c r="G171" s="8" t="n"/>
+      <c r="H171" s="8" t="n"/>
+      <c r="I171" s="8" t="n"/>
       <c r="J171" s="8" t="n"/>
-      <c r="K171" s="34" t="n">
+      <c r="K171" s="8" t="n"/>
+      <c r="L171" s="8" t="n"/>
+      <c r="M171" s="31" t="n">
         <v>423</v>
       </c>
-      <c r="L171" s="8" t="n"/>
-      <c r="M171" s="8" t="n"/>
       <c r="N171" s="8" t="n"/>
     </row>
     <row r="172">
@@ -7885,15 +7394,15 @@
       <c r="F172" s="8" t="n">
         <v>520</v>
       </c>
-      <c r="G172" s="31" t="n">
+      <c r="G172" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H172" s="31" t="inlineStr">
+      <c r="H172" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I172" s="32" t="inlineStr">
+      <c r="I172" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -7931,21 +7440,15 @@
       <c r="F173" s="8" t="n">
         <v>320</v>
       </c>
-      <c r="G173" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H173" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I173" s="32" t="inlineStr"/>
+      <c r="G173" s="11" t="n"/>
+      <c r="H173" s="11" t="n"/>
+      <c r="I173" s="8" t="n"/>
       <c r="J173" s="8" t="n"/>
-      <c r="K173" s="34" t="n">
+      <c r="K173" s="8" t="n"/>
+      <c r="L173" s="8" t="n"/>
+      <c r="M173" s="31" t="n">
         <v>320</v>
       </c>
-      <c r="L173" s="8" t="n"/>
-      <c r="M173" s="8" t="n"/>
       <c r="N173" s="8" t="n"/>
     </row>
     <row r="174">
@@ -7973,21 +7476,15 @@
       <c r="F174" s="8" t="n">
         <v>178</v>
       </c>
-      <c r="G174" s="30" t="n">
-        <v>45839</v>
-      </c>
-      <c r="H174" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I174" s="32" t="inlineStr"/>
+      <c r="G174" s="8" t="n"/>
+      <c r="H174" s="8" t="n"/>
+      <c r="I174" s="8" t="n"/>
       <c r="J174" s="8" t="n"/>
-      <c r="K174" s="34" t="n">
+      <c r="K174" s="8" t="n"/>
+      <c r="L174" s="8" t="n"/>
+      <c r="M174" s="31" t="n">
         <v>178</v>
       </c>
-      <c r="L174" s="8" t="n"/>
-      <c r="M174" s="8" t="n"/>
       <c r="N174" s="8" t="n"/>
     </row>
     <row r="175">
@@ -8049,21 +7546,15 @@
       <c r="F176" s="8" t="n">
         <v>8610</v>
       </c>
-      <c r="G176" s="30" t="n">
-        <v>45829</v>
-      </c>
-      <c r="H176" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I176" s="32" t="inlineStr"/>
+      <c r="G176" s="8" t="n"/>
+      <c r="H176" s="8" t="n"/>
+      <c r="I176" s="8" t="n"/>
       <c r="J176" s="8" t="n"/>
-      <c r="K176" s="34" t="n">
+      <c r="K176" s="8" t="n"/>
+      <c r="L176" s="8" t="n"/>
+      <c r="M176" s="31" t="n">
         <v>8610</v>
       </c>
-      <c r="L176" s="8" t="n"/>
-      <c r="M176" s="8" t="n"/>
       <c r="N176" s="8" t="n"/>
     </row>
     <row r="177">
@@ -8091,20 +7582,20 @@
       <c r="F177" s="8" t="n">
         <v>7197</v>
       </c>
-      <c r="G177" s="31" t="n">
+      <c r="G177" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H177" s="31" t="inlineStr">
+      <c r="H177" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I177" s="32" t="inlineStr">
+      <c r="I177" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J177" s="33" t="n">
+      <c r="J177" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K177" s="34" t="n">
@@ -8139,15 +7630,15 @@
       <c r="F178" s="8" t="n">
         <v>21179</v>
       </c>
-      <c r="G178" s="31" t="n">
+      <c r="G178" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H178" s="31" t="inlineStr">
+      <c r="H178" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I178" s="32" t="inlineStr">
+      <c r="I178" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -8321,21 +7812,15 @@
       <c r="F183" s="8" t="n">
         <v>628</v>
       </c>
-      <c r="G183" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H183" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I183" s="32" t="inlineStr"/>
+      <c r="G183" s="8" t="n"/>
+      <c r="H183" s="8" t="n"/>
+      <c r="I183" s="8" t="n"/>
       <c r="J183" s="8" t="n"/>
-      <c r="K183" s="34" t="n">
+      <c r="K183" s="8" t="n"/>
+      <c r="L183" s="8" t="n"/>
+      <c r="M183" s="31" t="n">
         <v>628</v>
       </c>
-      <c r="L183" s="8" t="n"/>
-      <c r="M183" s="8" t="n"/>
       <c r="N183" s="8" t="n"/>
     </row>
     <row r="184">
@@ -8363,15 +7848,15 @@
       <c r="F184" s="8" t="n">
         <v>5965</v>
       </c>
-      <c r="G184" s="31" t="n">
+      <c r="G184" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H184" s="31" t="inlineStr">
+      <c r="H184" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I184" s="32" t="inlineStr">
+      <c r="I184" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -8409,15 +7894,15 @@
       <c r="F185" s="8" t="n">
         <v>2312</v>
       </c>
-      <c r="G185" s="31" t="n">
+      <c r="G185" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H185" s="31" t="inlineStr">
+      <c r="H185" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I185" s="32" t="inlineStr">
+      <c r="I185" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -8455,21 +7940,15 @@
       <c r="F186" s="8" t="n">
         <v>1596</v>
       </c>
-      <c r="G186" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H186" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I186" s="32" t="inlineStr"/>
+      <c r="G186" s="11" t="n"/>
+      <c r="H186" s="11" t="n"/>
+      <c r="I186" s="8" t="n"/>
       <c r="J186" s="8" t="n"/>
-      <c r="K186" s="34" t="n">
+      <c r="K186" s="8" t="n"/>
+      <c r="L186" s="8" t="n"/>
+      <c r="M186" s="31" t="n">
         <v>1596</v>
       </c>
-      <c r="L186" s="8" t="n"/>
-      <c r="M186" s="8" t="n"/>
       <c r="N186" s="8" t="n"/>
     </row>
     <row r="187">
@@ -8497,25 +7976,15 @@
       <c r="F187" s="8" t="n">
         <v>186</v>
       </c>
-      <c r="G187" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H187" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I187" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G187" s="11" t="n"/>
+      <c r="H187" s="11" t="n"/>
+      <c r="I187" s="8" t="n"/>
       <c r="J187" s="8" t="n"/>
-      <c r="K187" s="34" t="n">
+      <c r="K187" s="8" t="n"/>
+      <c r="L187" s="8" t="n"/>
+      <c r="M187" s="31" t="n">
         <v>186</v>
       </c>
-      <c r="L187" s="8" t="n"/>
-      <c r="M187" s="8" t="n"/>
       <c r="N187" s="8" t="n"/>
     </row>
     <row r="188">
@@ -8577,15 +8046,15 @@
       <c r="F189" s="8" t="n">
         <v>2657</v>
       </c>
-      <c r="G189" s="31" t="n">
+      <c r="G189" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H189" s="31" t="inlineStr">
+      <c r="H189" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I189" s="32" t="inlineStr">
+      <c r="I189" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -8657,15 +8126,15 @@
       <c r="F191" s="8" t="n">
         <v>1047</v>
       </c>
-      <c r="G191" s="31" t="n">
+      <c r="G191" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H191" s="31" t="inlineStr">
+      <c r="H191" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I191" s="32" t="inlineStr">
+      <c r="I191" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -8703,21 +8172,15 @@
       <c r="F192" s="8" t="n">
         <v>2157</v>
       </c>
-      <c r="G192" s="30" t="n">
-        <v>45831</v>
-      </c>
-      <c r="H192" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I192" s="32" t="inlineStr"/>
+      <c r="G192" s="8" t="n"/>
+      <c r="H192" s="8" t="n"/>
+      <c r="I192" s="8" t="n"/>
       <c r="J192" s="8" t="n"/>
-      <c r="K192" s="34" t="n">
+      <c r="K192" s="8" t="n"/>
+      <c r="L192" s="8" t="n"/>
+      <c r="M192" s="31" t="n">
         <v>2157</v>
       </c>
-      <c r="L192" s="8" t="n"/>
-      <c r="M192" s="8" t="n"/>
       <c r="N192" s="8" t="n"/>
     </row>
     <row r="193">
@@ -8745,21 +8208,15 @@
       <c r="F193" s="8" t="n">
         <v>684</v>
       </c>
-      <c r="G193" s="30" t="n">
-        <v>45831</v>
-      </c>
-      <c r="H193" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I193" s="32" t="inlineStr"/>
+      <c r="G193" s="8" t="n"/>
+      <c r="H193" s="8" t="n"/>
+      <c r="I193" s="8" t="n"/>
       <c r="J193" s="8" t="n"/>
-      <c r="K193" s="34" t="n">
+      <c r="K193" s="8" t="n"/>
+      <c r="L193" s="8" t="n"/>
+      <c r="M193" s="31" t="n">
         <v>684</v>
       </c>
-      <c r="L193" s="8" t="n"/>
-      <c r="M193" s="8" t="n"/>
       <c r="N193" s="8" t="n"/>
     </row>
     <row r="194">
@@ -8787,21 +8244,15 @@
       <c r="F194" s="8" t="n">
         <v>2333</v>
       </c>
-      <c r="G194" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H194" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I194" s="32" t="inlineStr"/>
+      <c r="G194" s="8" t="n"/>
+      <c r="H194" s="8" t="n"/>
+      <c r="I194" s="8" t="n"/>
       <c r="J194" s="8" t="n"/>
-      <c r="K194" s="34" t="n">
+      <c r="K194" s="8" t="n"/>
+      <c r="L194" s="8" t="n"/>
+      <c r="M194" s="31" t="n">
         <v>2333</v>
       </c>
-      <c r="L194" s="8" t="n"/>
-      <c r="M194" s="8" t="n"/>
       <c r="N194" s="8" t="n"/>
     </row>
     <row r="195">
@@ -8829,21 +8280,15 @@
       <c r="F195" s="8" t="n">
         <v>2669</v>
       </c>
-      <c r="G195" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H195" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I195" s="32" t="inlineStr"/>
+      <c r="G195" s="11" t="n"/>
+      <c r="H195" s="11" t="n"/>
+      <c r="I195" s="8" t="n"/>
       <c r="J195" s="8" t="n"/>
-      <c r="K195" s="34" t="n">
+      <c r="K195" s="8" t="n"/>
+      <c r="L195" s="8" t="n"/>
+      <c r="M195" s="31" t="n">
         <v>2669</v>
       </c>
-      <c r="L195" s="8" t="n"/>
-      <c r="M195" s="8" t="n"/>
       <c r="N195" s="8" t="n"/>
     </row>
     <row r="196">
@@ -8871,21 +8316,15 @@
       <c r="F196" s="8" t="n">
         <v>196</v>
       </c>
-      <c r="G196" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H196" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I196" s="32" t="inlineStr"/>
+      <c r="G196" s="11" t="n"/>
+      <c r="H196" s="11" t="n"/>
+      <c r="I196" s="8" t="n"/>
       <c r="J196" s="8" t="n"/>
-      <c r="K196" s="34" t="n">
+      <c r="K196" s="8" t="n"/>
+      <c r="L196" s="8" t="n"/>
+      <c r="M196" s="31" t="n">
         <v>196</v>
       </c>
-      <c r="L196" s="8" t="n"/>
-      <c r="M196" s="8" t="n"/>
       <c r="N196" s="8" t="n"/>
     </row>
     <row r="197">
@@ -8913,15 +8352,15 @@
       <c r="F197" s="8" t="n">
         <v>799</v>
       </c>
-      <c r="G197" s="31" t="n">
+      <c r="G197" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H197" s="31" t="inlineStr">
+      <c r="H197" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I197" s="32" t="inlineStr">
+      <c r="I197" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -9027,21 +8466,15 @@
       <c r="F200" s="8" t="n">
         <v>1140</v>
       </c>
-      <c r="G200" s="30" t="n">
-        <v>45832</v>
-      </c>
-      <c r="H200" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I200" s="32" t="inlineStr"/>
+      <c r="G200" s="8" t="n"/>
+      <c r="H200" s="8" t="n"/>
+      <c r="I200" s="8" t="n"/>
       <c r="J200" s="8" t="n"/>
-      <c r="K200" s="34" t="n">
+      <c r="K200" s="8" t="n"/>
+      <c r="L200" s="8" t="n"/>
+      <c r="M200" s="31" t="n">
         <v>1140</v>
       </c>
-      <c r="L200" s="8" t="n"/>
-      <c r="M200" s="8" t="n"/>
       <c r="N200" s="8" t="n"/>
     </row>
     <row r="201">
@@ -9069,15 +8502,15 @@
       <c r="F201" s="8" t="n">
         <v>4991</v>
       </c>
-      <c r="G201" s="31" t="n">
+      <c r="G201" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H201" s="31" t="inlineStr">
+      <c r="H201" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I201" s="32" t="inlineStr">
+      <c r="I201" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -9115,21 +8548,15 @@
       <c r="F202" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="G202" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H202" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I202" s="32" t="inlineStr"/>
+      <c r="G202" s="11" t="n"/>
+      <c r="H202" s="11" t="n"/>
+      <c r="I202" s="8" t="n"/>
       <c r="J202" s="8" t="n"/>
-      <c r="K202" s="34" t="n">
+      <c r="K202" s="8" t="n"/>
+      <c r="L202" s="8" t="n"/>
+      <c r="M202" s="31" t="n">
         <v>500</v>
       </c>
-      <c r="L202" s="8" t="n"/>
-      <c r="M202" s="8" t="n"/>
       <c r="N202" s="8" t="n"/>
     </row>
     <row r="203">
@@ -9157,15 +8584,15 @@
       <c r="F203" s="8" t="n">
         <v>357</v>
       </c>
-      <c r="G203" s="31" t="n">
+      <c r="G203" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H203" s="31" t="inlineStr">
+      <c r="H203" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I203" s="32" t="inlineStr">
+      <c r="I203" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -9203,21 +8630,15 @@
       <c r="F204" s="8" t="n">
         <v>1382</v>
       </c>
-      <c r="G204" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H204" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I204" s="32" t="inlineStr"/>
+      <c r="G204" s="8" t="n"/>
+      <c r="H204" s="8" t="n"/>
+      <c r="I204" s="8" t="n"/>
       <c r="J204" s="8" t="n"/>
-      <c r="K204" s="34" t="n">
+      <c r="K204" s="8" t="n"/>
+      <c r="L204" s="8" t="n"/>
+      <c r="M204" s="31" t="n">
         <v>1382</v>
       </c>
-      <c r="L204" s="8" t="n"/>
-      <c r="M204" s="8" t="n"/>
       <c r="N204" s="8" t="n"/>
     </row>
     <row r="205">
@@ -9279,21 +8700,15 @@
       <c r="F206" s="8" t="n">
         <v>2401</v>
       </c>
-      <c r="G206" s="31" t="n">
-        <v>45836</v>
-      </c>
-      <c r="H206" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I206" s="32" t="inlineStr"/>
+      <c r="G206" s="11" t="n"/>
+      <c r="H206" s="11" t="n"/>
+      <c r="I206" s="8" t="n"/>
       <c r="J206" s="8" t="n"/>
-      <c r="K206" s="34" t="n">
+      <c r="K206" s="8" t="n"/>
+      <c r="L206" s="8" t="n"/>
+      <c r="M206" s="31" t="n">
         <v>2401</v>
       </c>
-      <c r="L206" s="8" t="n"/>
-      <c r="M206" s="8" t="n"/>
       <c r="N206" s="8" t="n"/>
     </row>
     <row r="207">
@@ -9321,25 +8736,15 @@
       <c r="F207" s="8" t="n">
         <v>724</v>
       </c>
-      <c r="G207" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H207" s="31" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I207" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G207" s="11" t="n"/>
+      <c r="H207" s="11" t="n"/>
+      <c r="I207" s="8" t="n"/>
       <c r="J207" s="8" t="n"/>
-      <c r="K207" s="34" t="n">
+      <c r="K207" s="8" t="n"/>
+      <c r="L207" s="8" t="n"/>
+      <c r="M207" s="31" t="n">
         <v>724</v>
       </c>
-      <c r="L207" s="8" t="n"/>
-      <c r="M207" s="8" t="n"/>
       <c r="N207" s="8" t="n"/>
     </row>
     <row r="208">
@@ -9367,15 +8772,15 @@
       <c r="F208" s="8" t="n">
         <v>4730</v>
       </c>
-      <c r="G208" s="31" t="n">
+      <c r="G208" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H208" s="31" t="inlineStr">
+      <c r="H208" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I208" s="32" t="inlineStr">
+      <c r="I208" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -9413,21 +8818,15 @@
       <c r="F209" s="8" t="n">
         <v>1287</v>
       </c>
-      <c r="G209" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H209" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I209" s="32" t="inlineStr"/>
+      <c r="G209" s="8" t="n"/>
+      <c r="H209" s="8" t="n"/>
+      <c r="I209" s="8" t="n"/>
       <c r="J209" s="8" t="n"/>
-      <c r="K209" s="34" t="n">
+      <c r="K209" s="8" t="n"/>
+      <c r="L209" s="8" t="n"/>
+      <c r="M209" s="31" t="n">
         <v>1287</v>
       </c>
-      <c r="L209" s="8" t="n"/>
-      <c r="M209" s="8" t="n"/>
       <c r="N209" s="8" t="n"/>
     </row>
     <row r="210">
@@ -9455,21 +8854,15 @@
       <c r="F210" s="8" t="n">
         <v>2121</v>
       </c>
-      <c r="G210" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H210" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I210" s="32" t="inlineStr"/>
+      <c r="G210" s="11" t="n"/>
+      <c r="H210" s="11" t="n"/>
+      <c r="I210" s="8" t="n"/>
       <c r="J210" s="8" t="n"/>
-      <c r="K210" s="34" t="n">
+      <c r="K210" s="8" t="n"/>
+      <c r="L210" s="8" t="n"/>
+      <c r="M210" s="31" t="n">
         <v>2121</v>
       </c>
-      <c r="L210" s="8" t="n"/>
-      <c r="M210" s="8" t="n"/>
       <c r="N210" s="8" t="n"/>
     </row>
     <row r="211">
@@ -9497,20 +8890,20 @@
       <c r="F211" s="8" t="n">
         <v>5448</v>
       </c>
-      <c r="G211" s="31" t="n">
+      <c r="G211" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H211" s="31" t="inlineStr">
+      <c r="H211" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I211" s="32" t="inlineStr">
+      <c r="I211" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J211" s="33" t="n">
+      <c r="J211" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K211" s="34" t="n">
@@ -9545,21 +8938,15 @@
       <c r="F212" s="8" t="n">
         <v>4435</v>
       </c>
-      <c r="G212" s="30" t="n">
-        <v>45824</v>
-      </c>
-      <c r="H212" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I212" s="32" t="inlineStr"/>
+      <c r="G212" s="8" t="n"/>
+      <c r="H212" s="8" t="n"/>
+      <c r="I212" s="8" t="n"/>
       <c r="J212" s="8" t="n"/>
-      <c r="K212" s="34" t="n">
+      <c r="K212" s="8" t="n"/>
+      <c r="L212" s="8" t="n"/>
+      <c r="M212" s="31" t="n">
         <v>4435</v>
       </c>
-      <c r="L212" s="8" t="n"/>
-      <c r="M212" s="8" t="n"/>
       <c r="N212" s="8" t="n"/>
     </row>
     <row r="213">
@@ -9587,21 +8974,15 @@
       <c r="F213" s="8" t="n">
         <v>7211</v>
       </c>
-      <c r="G213" s="30" t="n">
-        <v>45833</v>
-      </c>
-      <c r="H213" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I213" s="32" t="inlineStr"/>
+      <c r="G213" s="8" t="n"/>
+      <c r="H213" s="8" t="n"/>
+      <c r="I213" s="8" t="n"/>
       <c r="J213" s="8" t="n"/>
-      <c r="K213" s="34" t="n">
-        <v>653</v>
-      </c>
+      <c r="K213" s="8" t="n"/>
       <c r="L213" s="8" t="n"/>
-      <c r="M213" s="8" t="n"/>
+      <c r="M213" s="31" t="n">
+        <v>7211</v>
+      </c>
       <c r="N213" s="8" t="n"/>
     </row>
     <row r="214">
@@ -9765,21 +9146,15 @@
       <c r="F218" s="8" t="n">
         <v>28073</v>
       </c>
-      <c r="G218" s="31" t="n">
-        <v>45854</v>
-      </c>
-      <c r="H218" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I218" s="32" t="inlineStr"/>
+      <c r="G218" s="11" t="n"/>
+      <c r="H218" s="11" t="n"/>
+      <c r="I218" s="8" t="n"/>
       <c r="J218" s="8" t="n"/>
-      <c r="K218" s="34" t="n">
+      <c r="K218" s="8" t="n"/>
+      <c r="L218" s="8" t="n"/>
+      <c r="M218" s="31" t="n">
         <v>28073</v>
       </c>
-      <c r="L218" s="8" t="n"/>
-      <c r="M218" s="8" t="n"/>
       <c r="N218" s="8" t="n"/>
     </row>
     <row r="219">
@@ -9807,21 +9182,15 @@
       <c r="F219" s="8" t="n">
         <v>855</v>
       </c>
-      <c r="G219" s="30" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H219" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I219" s="32" t="inlineStr"/>
+      <c r="G219" s="8" t="n"/>
+      <c r="H219" s="8" t="n"/>
+      <c r="I219" s="8" t="n"/>
       <c r="J219" s="8" t="n"/>
-      <c r="K219" s="34" t="n">
+      <c r="K219" s="8" t="n"/>
+      <c r="L219" s="8" t="n"/>
+      <c r="M219" s="31" t="n">
         <v>855</v>
       </c>
-      <c r="L219" s="8" t="n"/>
-      <c r="M219" s="8" t="n"/>
       <c r="N219" s="8" t="n"/>
     </row>
     <row r="220">
@@ -9849,21 +9218,15 @@
       <c r="F220" s="8" t="n">
         <v>2858</v>
       </c>
-      <c r="G220" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H220" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I220" s="32" t="inlineStr"/>
+      <c r="G220" s="8" t="n"/>
+      <c r="H220" s="8" t="n"/>
+      <c r="I220" s="8" t="n"/>
       <c r="J220" s="8" t="n"/>
-      <c r="K220" s="34" t="n">
+      <c r="K220" s="8" t="n"/>
+      <c r="L220" s="8" t="n"/>
+      <c r="M220" s="31" t="n">
         <v>2858</v>
       </c>
-      <c r="L220" s="8" t="n"/>
-      <c r="M220" s="8" t="n"/>
       <c r="N220" s="8" t="n"/>
     </row>
     <row r="221">
@@ -9891,15 +9254,15 @@
       <c r="F221" s="8" t="n">
         <v>1276</v>
       </c>
-      <c r="G221" s="31" t="n">
+      <c r="G221" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H221" s="31" t="inlineStr">
+      <c r="H221" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I221" s="32" t="inlineStr">
+      <c r="I221" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -9937,15 +9300,15 @@
       <c r="F222" s="8" t="n">
         <v>3044</v>
       </c>
-      <c r="G222" s="31" t="n">
+      <c r="G222" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H222" s="31" t="inlineStr">
+      <c r="H222" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I222" s="32" t="inlineStr">
+      <c r="I222" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -9983,21 +9346,15 @@
       <c r="F223" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="G223" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H223" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I223" s="32" t="inlineStr"/>
+      <c r="G223" s="11" t="n"/>
+      <c r="H223" s="11" t="n"/>
+      <c r="I223" s="8" t="n"/>
       <c r="J223" s="8" t="n"/>
-      <c r="K223" s="34" t="n">
+      <c r="K223" s="8" t="n"/>
+      <c r="L223" s="8" t="n"/>
+      <c r="M223" s="31" t="n">
         <v>176</v>
       </c>
-      <c r="L223" s="8" t="n"/>
-      <c r="M223" s="8" t="n"/>
       <c r="N223" s="8" t="n"/>
     </row>
     <row r="224">
@@ -10229,21 +9586,15 @@
       <c r="F230" s="8" t="n">
         <v>2098</v>
       </c>
-      <c r="G230" s="30" t="n">
-        <v>45835</v>
-      </c>
-      <c r="H230" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I230" s="32" t="inlineStr"/>
+      <c r="G230" s="8" t="n"/>
+      <c r="H230" s="8" t="n"/>
+      <c r="I230" s="8" t="n"/>
       <c r="J230" s="8" t="n"/>
-      <c r="K230" s="34" t="n">
+      <c r="K230" s="8" t="n"/>
+      <c r="L230" s="8" t="n"/>
+      <c r="M230" s="31" t="n">
         <v>2098</v>
       </c>
-      <c r="L230" s="8" t="n"/>
-      <c r="M230" s="8" t="n"/>
       <c r="N230" s="8" t="n"/>
     </row>
     <row r="231">
@@ -10271,21 +9622,15 @@
       <c r="F231" s="8" t="n">
         <v>1673</v>
       </c>
-      <c r="G231" s="30" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H231" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I231" s="32" t="inlineStr"/>
+      <c r="G231" s="8" t="n"/>
+      <c r="H231" s="8" t="n"/>
+      <c r="I231" s="8" t="n"/>
       <c r="J231" s="8" t="n"/>
-      <c r="K231" s="34" t="n">
+      <c r="K231" s="8" t="n"/>
+      <c r="L231" s="8" t="n"/>
+      <c r="M231" s="31" t="n">
         <v>1673</v>
       </c>
-      <c r="L231" s="8" t="n"/>
-      <c r="M231" s="8" t="n"/>
       <c r="N231" s="8" t="n"/>
     </row>
     <row r="232">
@@ -10313,21 +9658,15 @@
       <c r="F232" s="8" t="n">
         <v>848</v>
       </c>
-      <c r="G232" s="30" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H232" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I232" s="32" t="inlineStr"/>
+      <c r="G232" s="8" t="n"/>
+      <c r="H232" s="8" t="n"/>
+      <c r="I232" s="8" t="n"/>
       <c r="J232" s="8" t="n"/>
-      <c r="K232" s="34" t="n">
+      <c r="K232" s="8" t="n"/>
+      <c r="L232" s="8" t="n"/>
+      <c r="M232" s="31" t="n">
         <v>848</v>
       </c>
-      <c r="L232" s="8" t="n"/>
-      <c r="M232" s="8" t="n"/>
       <c r="N232" s="8" t="n"/>
     </row>
     <row r="233">
@@ -10355,21 +9694,15 @@
       <c r="F233" s="8" t="n">
         <v>1455</v>
       </c>
-      <c r="G233" s="30" t="n">
-        <v>45835</v>
-      </c>
-      <c r="H233" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I233" s="32" t="inlineStr"/>
+      <c r="G233" s="8" t="n"/>
+      <c r="H233" s="8" t="n"/>
+      <c r="I233" s="8" t="n"/>
       <c r="J233" s="8" t="n"/>
-      <c r="K233" s="34" t="n">
+      <c r="K233" s="8" t="n"/>
+      <c r="L233" s="8" t="n"/>
+      <c r="M233" s="31" t="n">
         <v>1455</v>
       </c>
-      <c r="L233" s="8" t="n"/>
-      <c r="M233" s="8" t="n"/>
       <c r="N233" s="8" t="n"/>
     </row>
     <row r="234">
@@ -10397,15 +9730,15 @@
       <c r="F234" s="8" t="n">
         <v>8252</v>
       </c>
-      <c r="G234" s="31" t="n">
+      <c r="G234" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H234" s="31" t="inlineStr">
+      <c r="H234" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I234" s="32" t="inlineStr">
+      <c r="I234" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -10477,21 +9810,15 @@
       <c r="F236" s="8" t="n">
         <v>6442</v>
       </c>
-      <c r="G236" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H236" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I236" s="32" t="inlineStr"/>
+      <c r="G236" s="11" t="n"/>
+      <c r="H236" s="11" t="n"/>
+      <c r="I236" s="8" t="n"/>
       <c r="J236" s="8" t="n"/>
-      <c r="K236" s="34" t="n">
+      <c r="K236" s="8" t="n"/>
+      <c r="L236" s="8" t="n"/>
+      <c r="M236" s="31" t="n">
         <v>6442</v>
       </c>
-      <c r="L236" s="8" t="n"/>
-      <c r="M236" s="8" t="n"/>
       <c r="N236" s="8" t="n"/>
     </row>
     <row r="237">
@@ -10519,15 +9846,15 @@
       <c r="F237" s="8" t="n">
         <v>591</v>
       </c>
-      <c r="G237" s="31" t="n">
+      <c r="G237" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H237" s="31" t="inlineStr">
+      <c r="H237" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I237" s="32" t="inlineStr">
+      <c r="I237" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -10565,21 +9892,15 @@
       <c r="F238" s="8" t="n">
         <v>376</v>
       </c>
-      <c r="G238" s="31" t="n">
-        <v>45872</v>
-      </c>
-      <c r="H238" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I238" s="32" t="inlineStr"/>
+      <c r="G238" s="11" t="n"/>
+      <c r="H238" s="11" t="n"/>
+      <c r="I238" s="8" t="n"/>
       <c r="J238" s="8" t="n"/>
-      <c r="K238" s="34" t="n">
+      <c r="K238" s="8" t="n"/>
+      <c r="L238" s="8" t="n"/>
+      <c r="M238" s="31" t="n">
         <v>376</v>
       </c>
-      <c r="L238" s="8" t="n"/>
-      <c r="M238" s="8" t="n"/>
       <c r="N238" s="8" t="n"/>
     </row>
     <row r="239">
@@ -10607,21 +9928,15 @@
       <c r="F239" s="8" t="n">
         <v>3350</v>
       </c>
-      <c r="G239" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H239" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I239" s="32" t="inlineStr"/>
+      <c r="G239" s="8" t="n"/>
+      <c r="H239" s="8" t="n"/>
+      <c r="I239" s="8" t="n"/>
       <c r="J239" s="8" t="n"/>
-      <c r="K239" s="34" t="n">
+      <c r="K239" s="8" t="n"/>
+      <c r="L239" s="8" t="n"/>
+      <c r="M239" s="31" t="n">
         <v>3350</v>
       </c>
-      <c r="L239" s="8" t="n"/>
-      <c r="M239" s="8" t="n"/>
       <c r="N239" s="8" t="n"/>
     </row>
     <row r="240">
@@ -10649,23 +9964,17 @@
       <c r="F240" s="8" t="n">
         <v>3159</v>
       </c>
-      <c r="G240" s="31" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H240" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I240" s="32" t="inlineStr"/>
-      <c r="J240" s="33" t="n">
+      <c r="G240" s="11" t="n"/>
+      <c r="H240" s="11" t="n"/>
+      <c r="I240" s="8" t="n"/>
+      <c r="J240" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K240" s="34" t="n">
+      <c r="K240" s="8" t="n"/>
+      <c r="L240" s="8" t="n"/>
+      <c r="M240" s="31" t="n">
         <v>3159</v>
       </c>
-      <c r="L240" s="8" t="n"/>
-      <c r="M240" s="8" t="n"/>
       <c r="N240" s="8" t="n"/>
     </row>
     <row r="241">
@@ -10693,21 +10002,15 @@
       <c r="F241" s="8" t="n">
         <v>851</v>
       </c>
-      <c r="G241" s="30" t="n">
-        <v>45839</v>
-      </c>
-      <c r="H241" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I241" s="32" t="inlineStr"/>
+      <c r="G241" s="8" t="n"/>
+      <c r="H241" s="8" t="n"/>
+      <c r="I241" s="8" t="n"/>
       <c r="J241" s="8" t="n"/>
-      <c r="K241" s="34" t="n">
+      <c r="K241" s="8" t="n"/>
+      <c r="L241" s="8" t="n"/>
+      <c r="M241" s="31" t="n">
         <v>851</v>
       </c>
-      <c r="L241" s="8" t="n"/>
-      <c r="M241" s="8" t="n"/>
       <c r="N241" s="8" t="n"/>
     </row>
     <row r="242">
@@ -10735,23 +10038,17 @@
       <c r="F242" s="8" t="n">
         <v>1622</v>
       </c>
-      <c r="G242" s="31" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H242" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I242" s="32" t="inlineStr"/>
-      <c r="J242" s="33" t="n">
+      <c r="G242" s="11" t="n"/>
+      <c r="H242" s="11" t="n"/>
+      <c r="I242" s="8" t="n"/>
+      <c r="J242" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K242" s="34" t="n">
+      <c r="K242" s="8" t="n"/>
+      <c r="L242" s="8" t="n"/>
+      <c r="M242" s="31" t="n">
         <v>1622</v>
       </c>
-      <c r="L242" s="8" t="n"/>
-      <c r="M242" s="8" t="n"/>
       <c r="N242" s="8" t="n"/>
     </row>
     <row r="243">
@@ -10779,23 +10076,17 @@
       <c r="F243" s="8" t="n">
         <v>2530</v>
       </c>
-      <c r="G243" s="31" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H243" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I243" s="32" t="inlineStr"/>
-      <c r="J243" s="33" t="n">
+      <c r="G243" s="11" t="n"/>
+      <c r="H243" s="11" t="n"/>
+      <c r="I243" s="8" t="n"/>
+      <c r="J243" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K243" s="34" t="n">
+      <c r="K243" s="8" t="n"/>
+      <c r="L243" s="8" t="n"/>
+      <c r="M243" s="31" t="n">
         <v>2530</v>
       </c>
-      <c r="L243" s="8" t="n"/>
-      <c r="M243" s="8" t="n"/>
       <c r="N243" s="8" t="n"/>
     </row>
     <row r="244">
@@ -10823,15 +10114,15 @@
       <c r="F244" s="8" t="n">
         <v>238</v>
       </c>
-      <c r="G244" s="31" t="n">
+      <c r="G244" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H244" s="31" t="inlineStr">
+      <c r="H244" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I244" s="32" t="inlineStr">
+      <c r="I244" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -10869,21 +10160,15 @@
       <c r="F245" s="8" t="n">
         <v>1966</v>
       </c>
-      <c r="G245" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H245" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I245" s="32" t="inlineStr"/>
+      <c r="G245" s="8" t="n"/>
+      <c r="H245" s="8" t="n"/>
+      <c r="I245" s="8" t="n"/>
       <c r="J245" s="8" t="n"/>
-      <c r="K245" s="34" t="n">
+      <c r="K245" s="8" t="n"/>
+      <c r="L245" s="8" t="n"/>
+      <c r="M245" s="31" t="n">
         <v>1966</v>
       </c>
-      <c r="L245" s="8" t="n"/>
-      <c r="M245" s="8" t="n"/>
       <c r="N245" s="8" t="n"/>
     </row>
     <row r="246">
@@ -10911,21 +10196,15 @@
       <c r="F246" s="8" t="n">
         <v>1676</v>
       </c>
-      <c r="G246" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H246" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I246" s="32" t="inlineStr"/>
+      <c r="G246" s="11" t="n"/>
+      <c r="H246" s="11" t="n"/>
+      <c r="I246" s="8" t="n"/>
       <c r="J246" s="8" t="n"/>
-      <c r="K246" s="34" t="n">
+      <c r="K246" s="8" t="n"/>
+      <c r="L246" s="8" t="n"/>
+      <c r="M246" s="31" t="n">
         <v>1676</v>
       </c>
-      <c r="L246" s="8" t="n"/>
-      <c r="M246" s="8" t="n"/>
       <c r="N246" s="8" t="n"/>
     </row>
     <row r="247">
@@ -10953,15 +10232,15 @@
       <c r="F247" s="8" t="n">
         <v>2424</v>
       </c>
-      <c r="G247" s="31" t="n">
+      <c r="G247" s="32" t="n">
         <v>45912</v>
       </c>
-      <c r="H247" s="31" t="inlineStr">
+      <c r="H247" s="32" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I247" s="32" t="inlineStr">
+      <c r="I247" s="33" t="inlineStr">
         <is>
           <t>002610</t>
         </is>
@@ -10999,21 +10278,15 @@
       <c r="F248" s="8" t="n">
         <v>420</v>
       </c>
-      <c r="G248" s="31" t="n">
-        <v>45847</v>
-      </c>
-      <c r="H248" s="31" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I248" s="32" t="inlineStr"/>
+      <c r="G248" s="11" t="n"/>
+      <c r="H248" s="11" t="n"/>
+      <c r="I248" s="8" t="n"/>
       <c r="J248" s="8" t="n"/>
-      <c r="K248" s="34" t="n">
+      <c r="K248" s="8" t="n"/>
+      <c r="L248" s="8" t="n"/>
+      <c r="M248" s="31" t="n">
         <v>420</v>
       </c>
-      <c r="L248" s="8" t="n"/>
-      <c r="M248" s="8" t="n"/>
       <c r="N248" s="8" t="n"/>
     </row>
     <row r="249">
@@ -11041,21 +10314,15 @@
       <c r="F249" s="8" t="n">
         <v>768</v>
       </c>
-      <c r="G249" s="30" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H249" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I249" s="32" t="inlineStr"/>
+      <c r="G249" s="8" t="n"/>
+      <c r="H249" s="8" t="n"/>
+      <c r="I249" s="8" t="n"/>
       <c r="J249" s="8" t="n"/>
-      <c r="K249" s="34" t="n">
+      <c r="K249" s="8" t="n"/>
+      <c r="L249" s="8" t="n"/>
+      <c r="M249" s="31" t="n">
         <v>768</v>
       </c>
-      <c r="L249" s="8" t="n"/>
-      <c r="M249" s="8" t="n"/>
       <c r="N249" s="8" t="n"/>
     </row>
     <row r="250">
@@ -11083,21 +10350,15 @@
       <c r="F250" s="8" t="n">
         <v>1375</v>
       </c>
-      <c r="G250" s="30" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H250" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I250" s="32" t="inlineStr"/>
+      <c r="G250" s="8" t="n"/>
+      <c r="H250" s="8" t="n"/>
+      <c r="I250" s="8" t="n"/>
       <c r="J250" s="8" t="n"/>
-      <c r="K250" s="34" t="n">
+      <c r="K250" s="8" t="n"/>
+      <c r="L250" s="8" t="n"/>
+      <c r="M250" s="31" t="n">
         <v>1375</v>
       </c>
-      <c r="L250" s="8" t="n"/>
-      <c r="M250" s="8" t="n"/>
       <c r="N250" s="8" t="n"/>
     </row>
     <row r="251">
@@ -11125,21 +10386,15 @@
       <c r="F251" s="8" t="n">
         <v>2363</v>
       </c>
-      <c r="G251" s="30" t="n">
-        <v>45838</v>
-      </c>
-      <c r="H251" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I251" s="32" t="inlineStr"/>
+      <c r="G251" s="8" t="n"/>
+      <c r="H251" s="8" t="n"/>
+      <c r="I251" s="8" t="n"/>
       <c r="J251" s="8" t="n"/>
-      <c r="K251" s="34" t="n">
+      <c r="K251" s="8" t="n"/>
+      <c r="L251" s="8" t="n"/>
+      <c r="M251" s="31" t="n">
         <v>2363</v>
       </c>
-      <c r="L251" s="8" t="n"/>
-      <c r="M251" s="8" t="n"/>
       <c r="N251" s="8" t="n"/>
     </row>
     <row r="252">
@@ -11201,25 +10456,15 @@
       <c r="F253" s="12" t="n">
         <v>4733</v>
       </c>
-      <c r="G253" s="35" t="n">
-        <v>45915</v>
-      </c>
-      <c r="H253" s="35" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I253" s="36" t="inlineStr">
-        <is>
-          <t>002617</t>
-        </is>
-      </c>
+      <c r="G253" s="15" t="n"/>
+      <c r="H253" s="15" t="n"/>
+      <c r="I253" s="12" t="n"/>
       <c r="J253" s="12" t="n"/>
-      <c r="K253" s="37" t="n">
+      <c r="K253" s="12" t="n"/>
+      <c r="L253" s="12" t="n"/>
+      <c r="M253" s="40" t="n">
         <v>4733</v>
       </c>
-      <c r="L253" s="12" t="n"/>
-      <c r="M253" s="12" t="n"/>
       <c r="N253" s="12" t="n"/>
     </row>
     <row r="254">
@@ -11383,21 +10628,15 @@
       <c r="F258" s="8" t="n">
         <v>4413</v>
       </c>
-      <c r="G258" s="30" t="n">
-        <v>45889</v>
-      </c>
-      <c r="H258" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I258" s="32" t="inlineStr"/>
+      <c r="G258" s="8" t="n"/>
+      <c r="H258" s="8" t="n"/>
+      <c r="I258" s="8" t="n"/>
       <c r="J258" s="8" t="n"/>
-      <c r="K258" s="34" t="n">
+      <c r="K258" s="8" t="n"/>
+      <c r="L258" s="8" t="n"/>
+      <c r="M258" s="31" t="n">
         <v>4413</v>
       </c>
-      <c r="L258" s="8" t="n"/>
-      <c r="M258" s="8" t="n"/>
       <c r="N258" s="8" t="n"/>
     </row>
     <row r="259">
@@ -11425,15 +10664,15 @@
       <c r="F259" s="8" t="n">
         <v>1225</v>
       </c>
-      <c r="G259" s="31" t="n">
+      <c r="G259" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H259" s="32" t="inlineStr">
+      <c r="H259" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I259" s="32" t="inlineStr">
+      <c r="I259" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -11471,25 +10710,15 @@
       <c r="F260" s="8" t="n">
         <v>438</v>
       </c>
-      <c r="G260" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H260" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I260" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G260" s="11" t="n"/>
+      <c r="H260" s="8" t="n"/>
+      <c r="I260" s="8" t="n"/>
       <c r="J260" s="8" t="n"/>
-      <c r="K260" s="34" t="n">
+      <c r="K260" s="8" t="n"/>
+      <c r="L260" s="8" t="n"/>
+      <c r="M260" s="31" t="n">
         <v>438</v>
       </c>
-      <c r="L260" s="8" t="n"/>
-      <c r="M260" s="8" t="n"/>
       <c r="N260" s="8" t="n"/>
     </row>
     <row r="261">
@@ -11517,15 +10746,15 @@
       <c r="F261" s="8" t="n">
         <v>13176</v>
       </c>
-      <c r="G261" s="31" t="n">
+      <c r="G261" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H261" s="32" t="inlineStr">
+      <c r="H261" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I261" s="32" t="inlineStr">
+      <c r="I261" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -11563,23 +10792,17 @@
       <c r="F262" s="8" t="n">
         <v>1547</v>
       </c>
-      <c r="G262" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H262" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I262" s="32" t="inlineStr"/>
-      <c r="J262" s="33" t="n">
+      <c r="G262" s="8" t="n"/>
+      <c r="H262" s="8" t="n"/>
+      <c r="I262" s="8" t="n"/>
+      <c r="J262" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K262" s="34" t="n">
+      <c r="K262" s="8" t="n"/>
+      <c r="L262" s="8" t="n"/>
+      <c r="M262" s="31" t="n">
         <v>1547</v>
       </c>
-      <c r="L262" s="8" t="n"/>
-      <c r="M262" s="8" t="n"/>
       <c r="N262" s="8" t="n"/>
     </row>
     <row r="263">
@@ -11607,21 +10830,15 @@
       <c r="F263" s="8" t="n">
         <v>6103</v>
       </c>
-      <c r="G263" s="30" t="n">
-        <v>45839</v>
-      </c>
-      <c r="H263" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I263" s="32" t="inlineStr"/>
+      <c r="G263" s="8" t="n"/>
+      <c r="H263" s="8" t="n"/>
+      <c r="I263" s="8" t="n"/>
       <c r="J263" s="8" t="n"/>
-      <c r="K263" s="34" t="n">
-        <v>6099</v>
-      </c>
+      <c r="K263" s="8" t="n"/>
       <c r="L263" s="8" t="n"/>
-      <c r="M263" s="8" t="n"/>
+      <c r="M263" s="31" t="n">
+        <v>6103</v>
+      </c>
       <c r="N263" s="8" t="n"/>
     </row>
     <row r="264">
@@ -11649,21 +10866,15 @@
       <c r="F264" s="8" t="n">
         <v>6054</v>
       </c>
-      <c r="G264" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H264" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I264" s="32" t="inlineStr"/>
+      <c r="G264" s="8" t="n"/>
+      <c r="H264" s="8" t="n"/>
+      <c r="I264" s="8" t="n"/>
       <c r="J264" s="8" t="n"/>
-      <c r="K264" s="34" t="n">
+      <c r="K264" s="8" t="n"/>
+      <c r="L264" s="8" t="n"/>
+      <c r="M264" s="31" t="n">
         <v>6054</v>
       </c>
-      <c r="L264" s="8" t="n"/>
-      <c r="M264" s="8" t="n"/>
       <c r="N264" s="8" t="n"/>
     </row>
     <row r="265">
@@ -11691,21 +10902,15 @@
       <c r="F265" s="8" t="n">
         <v>5588</v>
       </c>
-      <c r="G265" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H265" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I265" s="32" t="inlineStr"/>
+      <c r="G265" s="11" t="n"/>
+      <c r="H265" s="8" t="n"/>
+      <c r="I265" s="8" t="n"/>
       <c r="J265" s="8" t="n"/>
-      <c r="K265" s="34" t="n">
+      <c r="K265" s="8" t="n"/>
+      <c r="L265" s="8" t="n"/>
+      <c r="M265" s="31" t="n">
         <v>5588</v>
       </c>
-      <c r="L265" s="8" t="n"/>
-      <c r="M265" s="8" t="n"/>
       <c r="N265" s="8" t="n"/>
     </row>
     <row r="266">
@@ -11801,15 +11006,15 @@
       <c r="F268" s="8" t="n">
         <v>2413</v>
       </c>
-      <c r="G268" s="31" t="n">
+      <c r="G268" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H268" s="32" t="inlineStr">
+      <c r="H268" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I268" s="32" t="inlineStr">
+      <c r="I268" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -11847,15 +11052,15 @@
       <c r="F269" s="8" t="n">
         <v>157</v>
       </c>
-      <c r="G269" s="31" t="n">
+      <c r="G269" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H269" s="32" t="inlineStr">
+      <c r="H269" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I269" s="32" t="inlineStr">
+      <c r="I269" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -11893,15 +11098,15 @@
       <c r="F270" s="8" t="n">
         <v>7482</v>
       </c>
-      <c r="G270" s="31" t="n">
+      <c r="G270" s="32" t="n">
         <v>45848</v>
       </c>
-      <c r="H270" s="32" t="inlineStr">
+      <c r="H270" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I270" s="32" t="inlineStr">
+      <c r="I270" s="33" t="inlineStr">
         <is>
           <t>002478</t>
         </is>
@@ -12007,15 +11212,15 @@
       <c r="F273" s="8" t="n">
         <v>2570</v>
       </c>
-      <c r="G273" s="31" t="n">
+      <c r="G273" s="32" t="n">
         <v>45868</v>
       </c>
-      <c r="H273" s="32" t="inlineStr">
+      <c r="H273" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I273" s="32" t="inlineStr">
+      <c r="I273" s="33" t="inlineStr">
         <is>
           <t>002511</t>
         </is>
@@ -12087,21 +11292,15 @@
       <c r="F275" s="8" t="n">
         <v>779</v>
       </c>
-      <c r="G275" s="30" t="n">
-        <v>45841</v>
-      </c>
-      <c r="H275" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I275" s="32" t="inlineStr"/>
+      <c r="G275" s="8" t="n"/>
+      <c r="H275" s="8" t="n"/>
+      <c r="I275" s="8" t="n"/>
       <c r="J275" s="8" t="n"/>
-      <c r="K275" s="34" t="n">
+      <c r="K275" s="8" t="n"/>
+      <c r="L275" s="8" t="n"/>
+      <c r="M275" s="31" t="n">
         <v>779</v>
       </c>
-      <c r="L275" s="8" t="n"/>
-      <c r="M275" s="8" t="n"/>
       <c r="N275" s="8" t="n"/>
     </row>
     <row r="276">
@@ -12129,15 +11328,15 @@
       <c r="F276" s="8" t="n">
         <v>4884</v>
       </c>
-      <c r="G276" s="31" t="n">
+      <c r="G276" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H276" s="32" t="inlineStr">
+      <c r="H276" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I276" s="32" t="inlineStr">
+      <c r="I276" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -12175,15 +11374,15 @@
       <c r="F277" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="G277" s="31" t="n">
+      <c r="G277" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H277" s="32" t="inlineStr">
+      <c r="H277" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I277" s="32" t="inlineStr">
+      <c r="I277" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -12221,21 +11420,15 @@
       <c r="F278" s="8" t="n">
         <v>680</v>
       </c>
-      <c r="G278" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H278" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I278" s="32" t="inlineStr"/>
+      <c r="G278" s="11" t="n"/>
+      <c r="H278" s="8" t="n"/>
+      <c r="I278" s="8" t="n"/>
       <c r="J278" s="8" t="n"/>
-      <c r="K278" s="34" t="n">
+      <c r="K278" s="8" t="n"/>
+      <c r="L278" s="8" t="n"/>
+      <c r="M278" s="31" t="n">
         <v>680</v>
       </c>
-      <c r="L278" s="8" t="n"/>
-      <c r="M278" s="8" t="n"/>
       <c r="N278" s="8" t="n"/>
     </row>
     <row r="279">
@@ -12263,20 +11456,20 @@
       <c r="F279" s="8" t="n">
         <v>9816</v>
       </c>
-      <c r="G279" s="31" t="n">
+      <c r="G279" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H279" s="32" t="inlineStr">
+      <c r="H279" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I279" s="32" t="inlineStr">
+      <c r="I279" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J279" s="33" t="n">
+      <c r="J279" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K279" s="34" t="n">
@@ -12345,23 +11538,17 @@
       <c r="F281" s="8" t="n">
         <v>1504</v>
       </c>
-      <c r="G281" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H281" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I281" s="32" t="inlineStr"/>
-      <c r="J281" s="33" t="n">
+      <c r="G281" s="8" t="n"/>
+      <c r="H281" s="8" t="n"/>
+      <c r="I281" s="8" t="n"/>
+      <c r="J281" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K281" s="34" t="n">
+      <c r="K281" s="8" t="n"/>
+      <c r="L281" s="8" t="n"/>
+      <c r="M281" s="31" t="n">
         <v>1504</v>
       </c>
-      <c r="L281" s="8" t="n"/>
-      <c r="M281" s="8" t="n"/>
       <c r="N281" s="8" t="n"/>
     </row>
     <row r="282">
@@ -12389,21 +11576,15 @@
       <c r="F282" s="8" t="n">
         <v>304</v>
       </c>
-      <c r="G282" s="30" t="n">
-        <v>45842</v>
-      </c>
-      <c r="H282" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I282" s="32" t="inlineStr"/>
+      <c r="G282" s="8" t="n"/>
+      <c r="H282" s="8" t="n"/>
+      <c r="I282" s="8" t="n"/>
       <c r="J282" s="8" t="n"/>
-      <c r="K282" s="34" t="n">
+      <c r="K282" s="8" t="n"/>
+      <c r="L282" s="8" t="n"/>
+      <c r="M282" s="31" t="n">
         <v>304</v>
       </c>
-      <c r="L282" s="8" t="n"/>
-      <c r="M282" s="8" t="n"/>
       <c r="N282" s="8" t="n"/>
     </row>
     <row r="283">
@@ -12431,21 +11612,15 @@
       <c r="F283" s="8" t="n">
         <v>1342</v>
       </c>
-      <c r="G283" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H283" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I283" s="32" t="inlineStr"/>
+      <c r="G283" s="11" t="n"/>
+      <c r="H283" s="8" t="n"/>
+      <c r="I283" s="8" t="n"/>
       <c r="J283" s="8" t="n"/>
-      <c r="K283" s="34" t="n">
+      <c r="K283" s="8" t="n"/>
+      <c r="L283" s="8" t="n"/>
+      <c r="M283" s="31" t="n">
         <v>1342</v>
       </c>
-      <c r="L283" s="8" t="n"/>
-      <c r="M283" s="8" t="n"/>
       <c r="N283" s="8" t="n"/>
     </row>
     <row r="284">
@@ -12473,21 +11648,15 @@
       <c r="F284" s="8" t="n">
         <v>4316</v>
       </c>
-      <c r="G284" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H284" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I284" s="32" t="inlineStr"/>
+      <c r="G284" s="8" t="n"/>
+      <c r="H284" s="8" t="n"/>
+      <c r="I284" s="8" t="n"/>
       <c r="J284" s="8" t="n"/>
-      <c r="K284" s="34" t="n">
+      <c r="K284" s="8" t="n"/>
+      <c r="L284" s="8" t="n"/>
+      <c r="M284" s="31" t="n">
         <v>4316</v>
       </c>
-      <c r="L284" s="8" t="n"/>
-      <c r="M284" s="8" t="n"/>
       <c r="N284" s="8" t="n"/>
     </row>
     <row r="285">
@@ -12515,15 +11684,15 @@
       <c r="F285" s="8" t="n">
         <v>4020</v>
       </c>
-      <c r="G285" s="31" t="n">
+      <c r="G285" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H285" s="32" t="inlineStr">
+      <c r="H285" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I285" s="32" t="inlineStr">
+      <c r="I285" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -12697,23 +11866,17 @@
       <c r="F290" s="8" t="n">
         <v>1522</v>
       </c>
-      <c r="G290" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H290" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I290" s="32" t="inlineStr"/>
-      <c r="J290" s="33" t="n">
+      <c r="G290" s="8" t="n"/>
+      <c r="H290" s="8" t="n"/>
+      <c r="I290" s="8" t="n"/>
+      <c r="J290" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K290" s="34" t="n">
+      <c r="K290" s="8" t="n"/>
+      <c r="L290" s="8" t="n"/>
+      <c r="M290" s="31" t="n">
         <v>1522</v>
       </c>
-      <c r="L290" s="8" t="n"/>
-      <c r="M290" s="8" t="n"/>
       <c r="N290" s="8" t="n"/>
     </row>
     <row r="291">
@@ -12741,21 +11904,15 @@
       <c r="F291" s="8" t="n">
         <v>1793</v>
       </c>
-      <c r="G291" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H291" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I291" s="32" t="inlineStr"/>
+      <c r="G291" s="11" t="n"/>
+      <c r="H291" s="8" t="n"/>
+      <c r="I291" s="8" t="n"/>
       <c r="J291" s="8" t="n"/>
-      <c r="K291" s="34" t="n">
+      <c r="K291" s="8" t="n"/>
+      <c r="L291" s="8" t="n"/>
+      <c r="M291" s="31" t="n">
         <v>1793</v>
       </c>
-      <c r="L291" s="8" t="n"/>
-      <c r="M291" s="8" t="n"/>
       <c r="N291" s="8" t="n"/>
     </row>
     <row r="292">
@@ -12783,15 +11940,15 @@
       <c r="F292" s="8" t="n">
         <v>6084</v>
       </c>
-      <c r="G292" s="31" t="n">
+      <c r="G292" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H292" s="32" t="inlineStr">
+      <c r="H292" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I292" s="32" t="inlineStr">
+      <c r="I292" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -12829,15 +11986,15 @@
       <c r="F293" s="8" t="n">
         <v>239</v>
       </c>
-      <c r="G293" s="31" t="n">
+      <c r="G293" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H293" s="32" t="inlineStr">
+      <c r="H293" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I293" s="32" t="inlineStr">
+      <c r="I293" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -12875,15 +12032,15 @@
       <c r="F294" s="8" t="n">
         <v>5423</v>
       </c>
-      <c r="G294" s="31" t="n">
+      <c r="G294" s="32" t="n">
         <v>45855</v>
       </c>
-      <c r="H294" s="32" t="inlineStr">
+      <c r="H294" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I294" s="32" t="inlineStr">
+      <c r="I294" s="33" t="inlineStr">
         <is>
           <t>002486</t>
         </is>
@@ -12921,23 +12078,17 @@
       <c r="F295" s="8" t="n">
         <v>2320</v>
       </c>
-      <c r="G295" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H295" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I295" s="32" t="inlineStr"/>
-      <c r="J295" s="33" t="n">
+      <c r="G295" s="8" t="n"/>
+      <c r="H295" s="8" t="n"/>
+      <c r="I295" s="8" t="n"/>
+      <c r="J295" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K295" s="34" t="n">
+      <c r="K295" s="8" t="n"/>
+      <c r="L295" s="8" t="n"/>
+      <c r="M295" s="31" t="n">
         <v>2320</v>
       </c>
-      <c r="L295" s="8" t="n"/>
-      <c r="M295" s="8" t="n"/>
       <c r="N295" s="8" t="n"/>
     </row>
     <row r="296">
@@ -12965,21 +12116,15 @@
       <c r="F296" s="8" t="n">
         <v>779</v>
       </c>
-      <c r="G296" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H296" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I296" s="32" t="inlineStr"/>
+      <c r="G296" s="8" t="n"/>
+      <c r="H296" s="8" t="n"/>
+      <c r="I296" s="8" t="n"/>
       <c r="J296" s="8" t="n"/>
-      <c r="K296" s="34" t="n">
+      <c r="K296" s="8" t="n"/>
+      <c r="L296" s="8" t="n"/>
+      <c r="M296" s="31" t="n">
         <v>779</v>
       </c>
-      <c r="L296" s="8" t="n"/>
-      <c r="M296" s="8" t="n"/>
       <c r="N296" s="8" t="n"/>
     </row>
     <row r="297">
@@ -13007,15 +12152,15 @@
       <c r="F297" s="8" t="n">
         <v>4614</v>
       </c>
-      <c r="G297" s="31" t="n">
+      <c r="G297" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H297" s="32" t="inlineStr">
+      <c r="H297" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I297" s="32" t="inlineStr">
+      <c r="I297" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -13053,21 +12198,15 @@
       <c r="F298" s="8" t="n">
         <v>2365</v>
       </c>
-      <c r="G298" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H298" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I298" s="32" t="inlineStr"/>
+      <c r="G298" s="11" t="n"/>
+      <c r="H298" s="8" t="n"/>
+      <c r="I298" s="8" t="n"/>
       <c r="J298" s="8" t="n"/>
-      <c r="K298" s="34" t="n">
+      <c r="K298" s="8" t="n"/>
+      <c r="L298" s="8" t="n"/>
+      <c r="M298" s="31" t="n">
         <v>2365</v>
       </c>
-      <c r="L298" s="8" t="n"/>
-      <c r="M298" s="8" t="n"/>
       <c r="N298" s="8" t="n"/>
     </row>
     <row r="299">
@@ -13129,23 +12268,17 @@
       <c r="F300" s="8" t="n">
         <v>3045</v>
       </c>
-      <c r="G300" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H300" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I300" s="32" t="inlineStr"/>
-      <c r="J300" s="33" t="n">
+      <c r="G300" s="8" t="n"/>
+      <c r="H300" s="8" t="n"/>
+      <c r="I300" s="8" t="n"/>
+      <c r="J300" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K300" s="34" t="n">
+      <c r="K300" s="8" t="n"/>
+      <c r="L300" s="8" t="n"/>
+      <c r="M300" s="31" t="n">
         <v>3045</v>
       </c>
-      <c r="L300" s="8" t="n"/>
-      <c r="M300" s="8" t="n"/>
       <c r="N300" s="8" t="n"/>
     </row>
     <row r="301">
@@ -13275,21 +12408,15 @@
       <c r="F304" s="8" t="n">
         <v>1124</v>
       </c>
-      <c r="G304" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H304" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I304" s="32" t="inlineStr"/>
+      <c r="G304" s="11" t="n"/>
+      <c r="H304" s="8" t="n"/>
+      <c r="I304" s="8" t="n"/>
       <c r="J304" s="8" t="n"/>
-      <c r="K304" s="34" t="n">
+      <c r="K304" s="8" t="n"/>
+      <c r="L304" s="8" t="n"/>
+      <c r="M304" s="31" t="n">
         <v>1124</v>
       </c>
-      <c r="L304" s="8" t="n"/>
-      <c r="M304" s="8" t="n"/>
       <c r="N304" s="8" t="n"/>
     </row>
     <row r="305">
@@ -13317,23 +12444,17 @@
       <c r="F305" s="8" t="n">
         <v>319</v>
       </c>
-      <c r="G305" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H305" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I305" s="32" t="inlineStr"/>
-      <c r="J305" s="33" t="n">
+      <c r="G305" s="8" t="n"/>
+      <c r="H305" s="8" t="n"/>
+      <c r="I305" s="8" t="n"/>
+      <c r="J305" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K305" s="34" t="n">
+      <c r="K305" s="8" t="n"/>
+      <c r="L305" s="8" t="n"/>
+      <c r="M305" s="31" t="n">
         <v>319</v>
       </c>
-      <c r="L305" s="8" t="n"/>
-      <c r="M305" s="8" t="n"/>
       <c r="N305" s="8" t="n"/>
     </row>
     <row r="306">
@@ -13361,21 +12482,15 @@
       <c r="F306" s="8" t="n">
         <v>1480</v>
       </c>
-      <c r="G306" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H306" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I306" s="32" t="inlineStr"/>
+      <c r="G306" s="8" t="n"/>
+      <c r="H306" s="8" t="n"/>
+      <c r="I306" s="8" t="n"/>
       <c r="J306" s="8" t="n"/>
-      <c r="K306" s="34" t="n">
+      <c r="K306" s="8" t="n"/>
+      <c r="L306" s="8" t="n"/>
+      <c r="M306" s="31" t="n">
         <v>1480</v>
       </c>
-      <c r="L306" s="8" t="n"/>
-      <c r="M306" s="8" t="n"/>
       <c r="N306" s="8" t="n"/>
     </row>
     <row r="307">
@@ -13403,21 +12518,15 @@
       <c r="F307" s="8" t="n">
         <v>295</v>
       </c>
-      <c r="G307" s="30" t="n">
-        <v>45852</v>
-      </c>
-      <c r="H307" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I307" s="32" t="inlineStr"/>
+      <c r="G307" s="8" t="n"/>
+      <c r="H307" s="8" t="n"/>
+      <c r="I307" s="8" t="n"/>
       <c r="J307" s="8" t="n"/>
-      <c r="K307" s="34" t="n">
+      <c r="K307" s="8" t="n"/>
+      <c r="L307" s="8" t="n"/>
+      <c r="M307" s="31" t="n">
         <v>295</v>
       </c>
-      <c r="L307" s="8" t="n"/>
-      <c r="M307" s="8" t="n"/>
       <c r="N307" s="8" t="n"/>
     </row>
     <row r="308">
@@ -13445,15 +12554,15 @@
       <c r="F308" s="8" t="n">
         <v>3108</v>
       </c>
-      <c r="G308" s="31" t="n">
+      <c r="G308" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H308" s="32" t="inlineStr">
+      <c r="H308" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I308" s="32" t="inlineStr">
+      <c r="I308" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -13491,15 +12600,15 @@
       <c r="F309" s="8" t="n">
         <v>346</v>
       </c>
-      <c r="G309" s="31" t="n">
+      <c r="G309" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H309" s="32" t="inlineStr">
+      <c r="H309" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I309" s="32" t="inlineStr">
+      <c r="I309" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -13537,15 +12646,15 @@
       <c r="F310" s="8" t="n">
         <v>913</v>
       </c>
-      <c r="G310" s="31" t="n">
+      <c r="G310" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H310" s="32" t="inlineStr">
+      <c r="H310" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I310" s="32" t="inlineStr">
+      <c r="I310" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -13583,15 +12692,15 @@
       <c r="F311" s="8" t="n">
         <v>950</v>
       </c>
-      <c r="G311" s="31" t="n">
+      <c r="G311" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H311" s="32" t="inlineStr">
+      <c r="H311" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I311" s="32" t="inlineStr">
+      <c r="I311" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -13629,21 +12738,15 @@
       <c r="F312" s="8" t="n">
         <v>578</v>
       </c>
-      <c r="G312" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H312" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I312" s="32" t="inlineStr"/>
+      <c r="G312" s="11" t="n"/>
+      <c r="H312" s="8" t="n"/>
+      <c r="I312" s="8" t="n"/>
       <c r="J312" s="8" t="n"/>
-      <c r="K312" s="34" t="n">
+      <c r="K312" s="8" t="n"/>
+      <c r="L312" s="8" t="n"/>
+      <c r="M312" s="31" t="n">
         <v>578</v>
       </c>
-      <c r="L312" s="8" t="n"/>
-      <c r="M312" s="8" t="n"/>
       <c r="N312" s="8" t="n"/>
     </row>
     <row r="313">
@@ -13671,21 +12774,15 @@
       <c r="F313" s="8" t="n">
         <v>754</v>
       </c>
-      <c r="G313" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H313" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I313" s="32" t="inlineStr"/>
+      <c r="G313" s="8" t="n"/>
+      <c r="H313" s="8" t="n"/>
+      <c r="I313" s="8" t="n"/>
       <c r="J313" s="8" t="n"/>
-      <c r="K313" s="34" t="n">
+      <c r="K313" s="8" t="n"/>
+      <c r="L313" s="8" t="n"/>
+      <c r="M313" s="31" t="n">
         <v>754</v>
       </c>
-      <c r="L313" s="8" t="n"/>
-      <c r="M313" s="8" t="n"/>
       <c r="N313" s="8" t="n"/>
     </row>
     <row r="314">
@@ -13713,21 +12810,15 @@
       <c r="F314" s="8" t="n">
         <v>551</v>
       </c>
-      <c r="G314" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H314" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I314" s="32" t="inlineStr"/>
+      <c r="G314" s="8" t="n"/>
+      <c r="H314" s="8" t="n"/>
+      <c r="I314" s="8" t="n"/>
       <c r="J314" s="8" t="n"/>
-      <c r="K314" s="34" t="n">
+      <c r="K314" s="8" t="n"/>
+      <c r="L314" s="8" t="n"/>
+      <c r="M314" s="31" t="n">
         <v>551</v>
       </c>
-      <c r="L314" s="8" t="n"/>
-      <c r="M314" s="8" t="n"/>
       <c r="N314" s="8" t="n"/>
     </row>
     <row r="315">
@@ -13755,15 +12846,15 @@
       <c r="F315" s="8" t="n">
         <v>573</v>
       </c>
-      <c r="G315" s="31" t="n">
+      <c r="G315" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H315" s="32" t="inlineStr">
+      <c r="H315" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I315" s="32" t="inlineStr">
+      <c r="I315" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -13801,15 +12892,15 @@
       <c r="F316" s="8" t="n">
         <v>1356</v>
       </c>
-      <c r="G316" s="31" t="n">
+      <c r="G316" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H316" s="32" t="inlineStr">
+      <c r="H316" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I316" s="32" t="inlineStr">
+      <c r="I316" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -13847,23 +12938,17 @@
       <c r="F317" s="8" t="n">
         <v>7367</v>
       </c>
-      <c r="G317" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H317" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I317" s="32" t="inlineStr"/>
-      <c r="J317" s="33" t="n">
+      <c r="G317" s="8" t="n"/>
+      <c r="H317" s="8" t="n"/>
+      <c r="I317" s="8" t="n"/>
+      <c r="J317" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K317" s="34" t="n">
+      <c r="K317" s="8" t="n"/>
+      <c r="L317" s="8" t="n"/>
+      <c r="M317" s="31" t="n">
         <v>7367</v>
       </c>
-      <c r="L317" s="8" t="n"/>
-      <c r="M317" s="8" t="n"/>
       <c r="N317" s="8" t="n"/>
     </row>
     <row r="318">
@@ -14027,15 +13112,15 @@
       <c r="F322" s="8" t="n">
         <v>560</v>
       </c>
-      <c r="G322" s="31" t="n">
+      <c r="G322" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H322" s="32" t="inlineStr">
+      <c r="H322" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I322" s="32" t="inlineStr">
+      <c r="I322" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -14107,21 +13192,15 @@
       <c r="F324" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="G324" s="30" t="n">
-        <v>45852</v>
-      </c>
-      <c r="H324" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I324" s="32" t="inlineStr"/>
+      <c r="G324" s="8" t="n"/>
+      <c r="H324" s="8" t="n"/>
+      <c r="I324" s="8" t="n"/>
       <c r="J324" s="8" t="n"/>
-      <c r="K324" s="34" t="n">
+      <c r="K324" s="8" t="n"/>
+      <c r="L324" s="8" t="n"/>
+      <c r="M324" s="31" t="n">
         <v>146</v>
       </c>
-      <c r="L324" s="8" t="n"/>
-      <c r="M324" s="8" t="n"/>
       <c r="N324" s="8" t="n"/>
     </row>
     <row r="325">
@@ -14183,25 +13262,15 @@
       <c r="F326" s="8" t="n">
         <v>1362</v>
       </c>
-      <c r="G326" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H326" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I326" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G326" s="11" t="n"/>
+      <c r="H326" s="8" t="n"/>
+      <c r="I326" s="8" t="n"/>
       <c r="J326" s="8" t="n"/>
-      <c r="K326" s="34" t="n">
+      <c r="K326" s="8" t="n"/>
+      <c r="L326" s="8" t="n"/>
+      <c r="M326" s="31" t="n">
         <v>1362</v>
       </c>
-      <c r="L326" s="8" t="n"/>
-      <c r="M326" s="8" t="n"/>
       <c r="N326" s="8" t="n"/>
     </row>
     <row r="327">
@@ -14229,15 +13298,15 @@
       <c r="F327" s="8" t="n">
         <v>5700</v>
       </c>
-      <c r="G327" s="31" t="n">
+      <c r="G327" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H327" s="32" t="inlineStr">
+      <c r="H327" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I327" s="32" t="inlineStr">
+      <c r="I327" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -14275,21 +13344,15 @@
       <c r="F328" s="8" t="n">
         <v>5275</v>
       </c>
-      <c r="G328" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H328" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I328" s="32" t="inlineStr"/>
+      <c r="G328" s="11" t="n"/>
+      <c r="H328" s="8" t="n"/>
+      <c r="I328" s="8" t="n"/>
       <c r="J328" s="8" t="n"/>
-      <c r="K328" s="34" t="n">
+      <c r="K328" s="8" t="n"/>
+      <c r="L328" s="8" t="n"/>
+      <c r="M328" s="31" t="n">
         <v>5275</v>
       </c>
-      <c r="L328" s="8" t="n"/>
-      <c r="M328" s="8" t="n"/>
       <c r="N328" s="8" t="n"/>
     </row>
     <row r="329">
@@ -14317,21 +13380,15 @@
       <c r="F329" s="8" t="n">
         <v>4190</v>
       </c>
-      <c r="G329" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H329" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I329" s="32" t="inlineStr"/>
+      <c r="G329" s="8" t="n"/>
+      <c r="H329" s="8" t="n"/>
+      <c r="I329" s="8" t="n"/>
       <c r="J329" s="8" t="n"/>
-      <c r="K329" s="34" t="n">
+      <c r="K329" s="8" t="n"/>
+      <c r="L329" s="8" t="n"/>
+      <c r="M329" s="31" t="n">
         <v>4190</v>
       </c>
-      <c r="L329" s="8" t="n"/>
-      <c r="M329" s="8" t="n"/>
       <c r="N329" s="8" t="n"/>
     </row>
     <row r="330">
@@ -14359,21 +13416,15 @@
       <c r="F330" s="8" t="n">
         <v>7556</v>
       </c>
-      <c r="G330" s="31" t="n">
-        <v>45872</v>
-      </c>
-      <c r="H330" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I330" s="32" t="inlineStr"/>
+      <c r="G330" s="11" t="n"/>
+      <c r="H330" s="8" t="n"/>
+      <c r="I330" s="8" t="n"/>
       <c r="J330" s="8" t="n"/>
-      <c r="K330" s="34" t="n">
+      <c r="K330" s="8" t="n"/>
+      <c r="L330" s="8" t="n"/>
+      <c r="M330" s="31" t="n">
         <v>7556</v>
       </c>
-      <c r="L330" s="8" t="n"/>
-      <c r="M330" s="8" t="n"/>
       <c r="N330" s="8" t="n"/>
     </row>
     <row r="331">
@@ -14571,20 +13622,20 @@
       <c r="F336" s="8" t="n">
         <v>3047</v>
       </c>
-      <c r="G336" s="31" t="n">
+      <c r="G336" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H336" s="32" t="inlineStr">
+      <c r="H336" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I336" s="32" t="inlineStr">
+      <c r="I336" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J336" s="33" t="n">
+      <c r="J336" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K336" s="34" t="n">
@@ -14619,21 +13670,15 @@
       <c r="F337" s="8" t="n">
         <v>6798</v>
       </c>
-      <c r="G337" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H337" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I337" s="32" t="inlineStr"/>
+      <c r="G337" s="11" t="n"/>
+      <c r="H337" s="8" t="n"/>
+      <c r="I337" s="8" t="n"/>
       <c r="J337" s="8" t="n"/>
-      <c r="K337" s="34" t="n">
+      <c r="K337" s="8" t="n"/>
+      <c r="L337" s="8" t="n"/>
+      <c r="M337" s="31" t="n">
         <v>6798</v>
       </c>
-      <c r="L337" s="8" t="n"/>
-      <c r="M337" s="8" t="n"/>
       <c r="N337" s="8" t="n"/>
     </row>
     <row r="338">
@@ -14661,15 +13706,15 @@
       <c r="F338" s="8" t="n">
         <v>359</v>
       </c>
-      <c r="G338" s="31" t="n">
+      <c r="G338" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H338" s="32" t="inlineStr">
+      <c r="H338" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I338" s="32" t="inlineStr">
+      <c r="I338" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -14707,21 +13752,15 @@
       <c r="F339" s="8" t="n">
         <v>2097</v>
       </c>
-      <c r="G339" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H339" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I339" s="32" t="inlineStr"/>
+      <c r="G339" s="8" t="n"/>
+      <c r="H339" s="8" t="n"/>
+      <c r="I339" s="8" t="n"/>
       <c r="J339" s="8" t="n"/>
-      <c r="K339" s="34" t="n">
+      <c r="K339" s="8" t="n"/>
+      <c r="L339" s="8" t="n"/>
+      <c r="M339" s="31" t="n">
         <v>2097</v>
       </c>
-      <c r="L339" s="8" t="n"/>
-      <c r="M339" s="8" t="n"/>
       <c r="N339" s="8" t="n"/>
     </row>
     <row r="340">
@@ -14817,15 +13856,15 @@
       <c r="F342" s="8" t="n">
         <v>3006</v>
       </c>
-      <c r="G342" s="31" t="n">
+      <c r="G342" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H342" s="32" t="inlineStr">
+      <c r="H342" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I342" s="32" t="inlineStr">
+      <c r="I342" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -14863,23 +13902,17 @@
       <c r="F343" s="8" t="n">
         <v>3479</v>
       </c>
-      <c r="G343" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H343" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I343" s="32" t="inlineStr"/>
-      <c r="J343" s="33" t="n">
+      <c r="G343" s="8" t="n"/>
+      <c r="H343" s="8" t="n"/>
+      <c r="I343" s="8" t="n"/>
+      <c r="J343" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K343" s="34" t="n">
+      <c r="K343" s="8" t="n"/>
+      <c r="L343" s="8" t="n"/>
+      <c r="M343" s="31" t="n">
         <v>3479</v>
       </c>
-      <c r="L343" s="8" t="n"/>
-      <c r="M343" s="8" t="n"/>
       <c r="N343" s="8" t="n"/>
     </row>
     <row r="344">
@@ -15043,15 +14076,15 @@
       <c r="F348" s="8" t="n">
         <v>1158</v>
       </c>
-      <c r="G348" s="31" t="n">
+      <c r="G348" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H348" s="32" t="inlineStr">
+      <c r="H348" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I348" s="32" t="inlineStr">
+      <c r="I348" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -15089,23 +14122,17 @@
       <c r="F349" s="8" t="n">
         <v>982</v>
       </c>
-      <c r="G349" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H349" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I349" s="32" t="inlineStr"/>
-      <c r="J349" s="33" t="n">
+      <c r="G349" s="8" t="n"/>
+      <c r="H349" s="8" t="n"/>
+      <c r="I349" s="8" t="n"/>
+      <c r="J349" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K349" s="34" t="n">
+      <c r="K349" s="8" t="n"/>
+      <c r="L349" s="8" t="n"/>
+      <c r="M349" s="31" t="n">
         <v>982</v>
       </c>
-      <c r="L349" s="8" t="n"/>
-      <c r="M349" s="8" t="n"/>
       <c r="N349" s="8" t="n"/>
     </row>
     <row r="350">
@@ -15167,15 +14194,15 @@
       <c r="F351" s="8" t="n">
         <v>2471</v>
       </c>
-      <c r="G351" s="31" t="n">
+      <c r="G351" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H351" s="32" t="inlineStr">
+      <c r="H351" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I351" s="32" t="inlineStr">
+      <c r="I351" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -15213,21 +14240,15 @@
       <c r="F352" s="8" t="n">
         <v>2695</v>
       </c>
-      <c r="G352" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H352" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I352" s="32" t="inlineStr"/>
+      <c r="G352" s="8" t="n"/>
+      <c r="H352" s="8" t="n"/>
+      <c r="I352" s="8" t="n"/>
       <c r="J352" s="8" t="n"/>
-      <c r="K352" s="34" t="n">
+      <c r="K352" s="8" t="n"/>
+      <c r="L352" s="8" t="n"/>
+      <c r="M352" s="31" t="n">
         <v>2695</v>
       </c>
-      <c r="L352" s="8" t="n"/>
-      <c r="M352" s="8" t="n"/>
       <c r="N352" s="8" t="n"/>
     </row>
     <row r="353">
@@ -15391,21 +14412,15 @@
       <c r="F357" s="8" t="n">
         <v>933</v>
       </c>
-      <c r="G357" s="30" t="n">
-        <v>45852</v>
-      </c>
-      <c r="H357" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I357" s="32" t="inlineStr"/>
+      <c r="G357" s="8" t="n"/>
+      <c r="H357" s="8" t="n"/>
+      <c r="I357" s="8" t="n"/>
       <c r="J357" s="8" t="n"/>
-      <c r="K357" s="34" t="n">
+      <c r="K357" s="8" t="n"/>
+      <c r="L357" s="8" t="n"/>
+      <c r="M357" s="31" t="n">
         <v>933</v>
       </c>
-      <c r="L357" s="8" t="n"/>
-      <c r="M357" s="8" t="n"/>
       <c r="N357" s="8" t="n"/>
     </row>
     <row r="358">
@@ -15433,21 +14448,15 @@
       <c r="F358" s="8" t="n">
         <v>1269</v>
       </c>
-      <c r="G358" s="30" t="n">
-        <v>45852</v>
-      </c>
-      <c r="H358" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I358" s="32" t="inlineStr"/>
+      <c r="G358" s="8" t="n"/>
+      <c r="H358" s="8" t="n"/>
+      <c r="I358" s="8" t="n"/>
       <c r="J358" s="8" t="n"/>
-      <c r="K358" s="34" t="n">
+      <c r="K358" s="8" t="n"/>
+      <c r="L358" s="8" t="n"/>
+      <c r="M358" s="31" t="n">
         <v>1269</v>
       </c>
-      <c r="L358" s="8" t="n"/>
-      <c r="M358" s="8" t="n"/>
       <c r="N358" s="8" t="n"/>
     </row>
     <row r="359">
@@ -15475,21 +14484,15 @@
       <c r="F359" s="8" t="n">
         <v>525</v>
       </c>
-      <c r="G359" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H359" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I359" s="32" t="inlineStr"/>
+      <c r="G359" s="11" t="n"/>
+      <c r="H359" s="8" t="n"/>
+      <c r="I359" s="8" t="n"/>
       <c r="J359" s="8" t="n"/>
-      <c r="K359" s="34" t="n">
+      <c r="K359" s="8" t="n"/>
+      <c r="L359" s="8" t="n"/>
+      <c r="M359" s="31" t="n">
         <v>525</v>
       </c>
-      <c r="L359" s="8" t="n"/>
-      <c r="M359" s="8" t="n"/>
       <c r="N359" s="8" t="n"/>
     </row>
     <row r="360">
@@ -15517,21 +14520,15 @@
       <c r="F360" s="8" t="n">
         <v>1804</v>
       </c>
-      <c r="G360" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H360" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I360" s="32" t="inlineStr"/>
+      <c r="G360" s="8" t="n"/>
+      <c r="H360" s="8" t="n"/>
+      <c r="I360" s="8" t="n"/>
       <c r="J360" s="8" t="n"/>
-      <c r="K360" s="34" t="n">
+      <c r="K360" s="8" t="n"/>
+      <c r="L360" s="8" t="n"/>
+      <c r="M360" s="31" t="n">
         <v>1804</v>
       </c>
-      <c r="L360" s="8" t="n"/>
-      <c r="M360" s="8" t="n"/>
       <c r="N360" s="8" t="n"/>
     </row>
     <row r="361">
@@ -15593,15 +14590,15 @@
       <c r="F362" s="8" t="n">
         <v>1704</v>
       </c>
-      <c r="G362" s="31" t="n">
+      <c r="G362" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H362" s="32" t="inlineStr">
+      <c r="H362" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I362" s="32" t="inlineStr">
+      <c r="I362" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -15639,15 +14636,15 @@
       <c r="F363" s="8" t="n">
         <v>818</v>
       </c>
-      <c r="G363" s="31" t="n">
+      <c r="G363" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H363" s="32" t="inlineStr">
+      <c r="H363" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I363" s="32" t="inlineStr">
+      <c r="I363" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -15821,21 +14818,15 @@
       <c r="F368" s="8" t="n">
         <v>1187</v>
       </c>
-      <c r="G368" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H368" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I368" s="32" t="inlineStr"/>
+      <c r="G368" s="8" t="n"/>
+      <c r="H368" s="8" t="n"/>
+      <c r="I368" s="8" t="n"/>
       <c r="J368" s="8" t="n"/>
-      <c r="K368" s="34" t="n">
+      <c r="K368" s="8" t="n"/>
+      <c r="L368" s="8" t="n"/>
+      <c r="M368" s="31" t="n">
         <v>1187</v>
       </c>
-      <c r="L368" s="8" t="n"/>
-      <c r="M368" s="8" t="n"/>
       <c r="N368" s="8" t="n"/>
     </row>
     <row r="369">
@@ -15863,21 +14854,15 @@
       <c r="F369" s="8" t="n">
         <v>977</v>
       </c>
-      <c r="G369" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H369" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I369" s="32" t="inlineStr"/>
+      <c r="G369" s="11" t="n"/>
+      <c r="H369" s="8" t="n"/>
+      <c r="I369" s="8" t="n"/>
       <c r="J369" s="8" t="n"/>
-      <c r="K369" s="34" t="n">
+      <c r="K369" s="8" t="n"/>
+      <c r="L369" s="8" t="n"/>
+      <c r="M369" s="31" t="n">
         <v>977</v>
       </c>
-      <c r="L369" s="8" t="n"/>
-      <c r="M369" s="8" t="n"/>
       <c r="N369" s="8" t="n"/>
     </row>
     <row r="370">
@@ -15905,21 +14890,15 @@
       <c r="F370" s="8" t="n">
         <v>566</v>
       </c>
-      <c r="G370" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H370" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I370" s="32" t="inlineStr"/>
+      <c r="G370" s="8" t="n"/>
+      <c r="H370" s="8" t="n"/>
+      <c r="I370" s="8" t="n"/>
       <c r="J370" s="8" t="n"/>
-      <c r="K370" s="34" t="n">
+      <c r="K370" s="8" t="n"/>
+      <c r="L370" s="8" t="n"/>
+      <c r="M370" s="31" t="n">
         <v>566</v>
       </c>
-      <c r="L370" s="8" t="n"/>
-      <c r="M370" s="8" t="n"/>
       <c r="N370" s="8" t="n"/>
     </row>
     <row r="371">
@@ -15947,15 +14926,15 @@
       <c r="F371" s="8" t="n">
         <v>1506</v>
       </c>
-      <c r="G371" s="31" t="n">
+      <c r="G371" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H371" s="32" t="inlineStr">
+      <c r="H371" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I371" s="32" t="inlineStr">
+      <c r="I371" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -15993,20 +14972,20 @@
       <c r="F372" s="8" t="n">
         <v>467</v>
       </c>
-      <c r="G372" s="31" t="n">
+      <c r="G372" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H372" s="32" t="inlineStr">
+      <c r="H372" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I372" s="32" t="inlineStr">
+      <c r="I372" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J372" s="33" t="n">
+      <c r="J372" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K372" s="34" t="n">
@@ -16041,15 +15020,15 @@
       <c r="F373" s="8" t="n">
         <v>437</v>
       </c>
-      <c r="G373" s="31" t="n">
+      <c r="G373" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H373" s="32" t="inlineStr">
+      <c r="H373" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I373" s="32" t="inlineStr">
+      <c r="I373" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -16087,23 +15066,17 @@
       <c r="F374" s="8" t="n">
         <v>154</v>
       </c>
-      <c r="G374" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H374" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I374" s="32" t="inlineStr"/>
-      <c r="J374" s="33" t="n">
+      <c r="G374" s="8" t="n"/>
+      <c r="H374" s="8" t="n"/>
+      <c r="I374" s="8" t="n"/>
+      <c r="J374" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K374" s="34" t="n">
+      <c r="K374" s="8" t="n"/>
+      <c r="L374" s="8" t="n"/>
+      <c r="M374" s="31" t="n">
         <v>154</v>
       </c>
-      <c r="L374" s="8" t="n"/>
-      <c r="M374" s="8" t="n"/>
       <c r="N374" s="8" t="n"/>
     </row>
     <row r="375">
@@ -16131,29 +15104,27 @@
       <c r="F375" s="8" t="n">
         <v>1003</v>
       </c>
-      <c r="G375" s="31" t="n">
+      <c r="G375" s="32" t="n">
         <v>45885</v>
       </c>
-      <c r="H375" s="32" t="inlineStr">
+      <c r="H375" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I375" s="32" t="inlineStr">
+      <c r="I375" s="33" t="inlineStr">
         <is>
           <t>002562</t>
         </is>
       </c>
-      <c r="J375" s="33" t="n">
+      <c r="J375" s="30" t="n">
         <v>9492</v>
       </c>
       <c r="K375" s="34" t="n">
         <v>93</v>
       </c>
       <c r="L375" s="8" t="n"/>
-      <c r="M375" s="39" t="n">
-        <v>910</v>
-      </c>
+      <c r="M375" s="8" t="n"/>
       <c r="N375" s="8" t="n"/>
     </row>
     <row r="376">
@@ -16249,21 +15220,15 @@
       <c r="F378" s="8" t="n">
         <v>218</v>
       </c>
-      <c r="G378" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H378" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I378" s="32" t="inlineStr"/>
+      <c r="G378" s="8" t="n"/>
+      <c r="H378" s="8" t="n"/>
+      <c r="I378" s="8" t="n"/>
       <c r="J378" s="8" t="n"/>
-      <c r="K378" s="34" t="n">
+      <c r="K378" s="8" t="n"/>
+      <c r="L378" s="8" t="n"/>
+      <c r="M378" s="31" t="n">
         <v>218</v>
       </c>
-      <c r="L378" s="8" t="n"/>
-      <c r="M378" s="8" t="n"/>
       <c r="N378" s="8" t="n"/>
     </row>
     <row r="379">
@@ -16291,23 +15256,17 @@
       <c r="F379" s="8" t="n">
         <v>2804</v>
       </c>
-      <c r="G379" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H379" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I379" s="32" t="inlineStr"/>
-      <c r="J379" s="33" t="n">
+      <c r="G379" s="8" t="n"/>
+      <c r="H379" s="8" t="n"/>
+      <c r="I379" s="8" t="n"/>
+      <c r="J379" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K379" s="34" t="n">
+      <c r="K379" s="8" t="n"/>
+      <c r="L379" s="8" t="n"/>
+      <c r="M379" s="31" t="n">
         <v>2804</v>
       </c>
-      <c r="L379" s="8" t="n"/>
-      <c r="M379" s="8" t="n"/>
       <c r="N379" s="8" t="n"/>
     </row>
     <row r="380">
@@ -16335,15 +15294,15 @@
       <c r="F380" s="8" t="n">
         <v>4137</v>
       </c>
-      <c r="G380" s="31" t="n">
+      <c r="G380" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H380" s="32" t="inlineStr">
+      <c r="H380" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I380" s="32" t="inlineStr">
+      <c r="I380" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -16619,15 +15578,15 @@
       <c r="F388" s="8" t="n">
         <v>537</v>
       </c>
-      <c r="G388" s="31" t="n">
+      <c r="G388" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H388" s="32" t="inlineStr">
+      <c r="H388" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I388" s="32" t="inlineStr">
+      <c r="I388" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -16665,21 +15624,15 @@
       <c r="F389" s="8" t="n">
         <v>549</v>
       </c>
-      <c r="G389" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H389" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I389" s="32" t="inlineStr"/>
+      <c r="G389" s="8" t="n"/>
+      <c r="H389" s="8" t="n"/>
+      <c r="I389" s="8" t="n"/>
       <c r="J389" s="8" t="n"/>
-      <c r="K389" s="34" t="n">
+      <c r="K389" s="8" t="n"/>
+      <c r="L389" s="8" t="n"/>
+      <c r="M389" s="31" t="n">
         <v>549</v>
       </c>
-      <c r="L389" s="8" t="n"/>
-      <c r="M389" s="8" t="n"/>
       <c r="N389" s="8" t="n"/>
     </row>
     <row r="390">
@@ -16741,25 +15694,15 @@
       <c r="F391" s="8" t="n">
         <v>3890</v>
       </c>
-      <c r="G391" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H391" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I391" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G391" s="11" t="n"/>
+      <c r="H391" s="8" t="n"/>
+      <c r="I391" s="8" t="n"/>
       <c r="J391" s="8" t="n"/>
-      <c r="K391" s="34" t="n">
+      <c r="K391" s="8" t="n"/>
+      <c r="L391" s="8" t="n"/>
+      <c r="M391" s="31" t="n">
         <v>3890</v>
       </c>
-      <c r="L391" s="8" t="n"/>
-      <c r="M391" s="8" t="n"/>
       <c r="N391" s="8" t="n"/>
     </row>
     <row r="392">
@@ -16787,23 +15730,17 @@
       <c r="F392" s="8" t="n">
         <v>1383</v>
       </c>
-      <c r="G392" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H392" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I392" s="32" t="inlineStr"/>
-      <c r="J392" s="33" t="n">
+      <c r="G392" s="8" t="n"/>
+      <c r="H392" s="8" t="n"/>
+      <c r="I392" s="8" t="n"/>
+      <c r="J392" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K392" s="34" t="n">
+      <c r="K392" s="8" t="n"/>
+      <c r="L392" s="8" t="n"/>
+      <c r="M392" s="31" t="n">
         <v>1383</v>
       </c>
-      <c r="L392" s="8" t="n"/>
-      <c r="M392" s="8" t="n"/>
       <c r="N392" s="8" t="n"/>
     </row>
     <row r="393">
@@ -17069,25 +16006,15 @@
       <c r="F400" s="8" t="n">
         <v>187</v>
       </c>
-      <c r="G400" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H400" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I400" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G400" s="11" t="n"/>
+      <c r="H400" s="8" t="n"/>
+      <c r="I400" s="8" t="n"/>
       <c r="J400" s="8" t="n"/>
-      <c r="K400" s="34" t="n">
+      <c r="K400" s="8" t="n"/>
+      <c r="L400" s="8" t="n"/>
+      <c r="M400" s="31" t="n">
         <v>187</v>
       </c>
-      <c r="L400" s="8" t="n"/>
-      <c r="M400" s="8" t="n"/>
       <c r="N400" s="8" t="n"/>
     </row>
     <row r="401">
@@ -17115,15 +16042,15 @@
       <c r="F401" s="8" t="n">
         <v>373</v>
       </c>
-      <c r="G401" s="31" t="n">
+      <c r="G401" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H401" s="32" t="inlineStr">
+      <c r="H401" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I401" s="32" t="inlineStr">
+      <c r="I401" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -17161,23 +16088,17 @@
       <c r="F402" s="8" t="n">
         <v>1702</v>
       </c>
-      <c r="G402" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H402" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I402" s="32" t="inlineStr"/>
-      <c r="J402" s="33" t="n">
+      <c r="G402" s="8" t="n"/>
+      <c r="H402" s="8" t="n"/>
+      <c r="I402" s="8" t="n"/>
+      <c r="J402" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K402" s="34" t="n">
+      <c r="K402" s="8" t="n"/>
+      <c r="L402" s="8" t="n"/>
+      <c r="M402" s="31" t="n">
         <v>1702</v>
       </c>
-      <c r="L402" s="8" t="n"/>
-      <c r="M402" s="8" t="n"/>
       <c r="N402" s="8" t="n"/>
     </row>
     <row r="403">
@@ -17205,15 +16126,15 @@
       <c r="F403" s="8" t="n">
         <v>326</v>
       </c>
-      <c r="G403" s="31" t="n">
+      <c r="G403" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H403" s="32" t="inlineStr">
+      <c r="H403" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I403" s="32" t="inlineStr">
+      <c r="I403" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -17251,15 +16172,15 @@
       <c r="F404" s="8" t="n">
         <v>3451</v>
       </c>
-      <c r="G404" s="31" t="n">
+      <c r="G404" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H404" s="32" t="inlineStr">
+      <c r="H404" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I404" s="32" t="inlineStr">
+      <c r="I404" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -17331,21 +16252,15 @@
       <c r="F406" s="8" t="n">
         <v>572</v>
       </c>
-      <c r="G406" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H406" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I406" s="32" t="inlineStr"/>
+      <c r="G406" s="11" t="n"/>
+      <c r="H406" s="8" t="n"/>
+      <c r="I406" s="8" t="n"/>
       <c r="J406" s="8" t="n"/>
-      <c r="K406" s="34" t="n">
+      <c r="K406" s="8" t="n"/>
+      <c r="L406" s="8" t="n"/>
+      <c r="M406" s="31" t="n">
         <v>572</v>
       </c>
-      <c r="L406" s="8" t="n"/>
-      <c r="M406" s="8" t="n"/>
       <c r="N406" s="8" t="n"/>
     </row>
     <row r="407">
@@ -17373,21 +16288,15 @@
       <c r="F407" s="8" t="n">
         <v>1361</v>
       </c>
-      <c r="G407" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H407" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I407" s="32" t="inlineStr"/>
+      <c r="G407" s="8" t="n"/>
+      <c r="H407" s="8" t="n"/>
+      <c r="I407" s="8" t="n"/>
       <c r="J407" s="8" t="n"/>
-      <c r="K407" s="34" t="n">
+      <c r="K407" s="8" t="n"/>
+      <c r="L407" s="8" t="n"/>
+      <c r="M407" s="31" t="n">
         <v>1361</v>
       </c>
-      <c r="L407" s="8" t="n"/>
-      <c r="M407" s="8" t="n"/>
       <c r="N407" s="8" t="n"/>
     </row>
     <row r="408">
@@ -17483,25 +16392,15 @@
       <c r="F410" s="8" t="n">
         <v>1328</v>
       </c>
-      <c r="G410" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H410" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I410" s="32" t="inlineStr">
-        <is>
-          <t>002558</t>
-        </is>
-      </c>
+      <c r="G410" s="8" t="n"/>
+      <c r="H410" s="8" t="n"/>
+      <c r="I410" s="8" t="n"/>
       <c r="J410" s="8" t="n"/>
-      <c r="K410" s="34" t="n">
+      <c r="K410" s="8" t="n"/>
+      <c r="L410" s="8" t="n"/>
+      <c r="M410" s="31" t="n">
         <v>1328</v>
       </c>
-      <c r="L410" s="8" t="n"/>
-      <c r="M410" s="8" t="n"/>
       <c r="N410" s="8" t="n"/>
     </row>
     <row r="411">
@@ -17529,15 +16428,15 @@
       <c r="F411" s="8" t="n">
         <v>9819</v>
       </c>
-      <c r="G411" s="31" t="n">
+      <c r="G411" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H411" s="32" t="inlineStr">
+      <c r="H411" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I411" s="32" t="inlineStr">
+      <c r="I411" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -17609,21 +16508,15 @@
       <c r="F413" s="8" t="n">
         <v>2485</v>
       </c>
-      <c r="G413" s="31" t="n">
-        <v>45872</v>
-      </c>
-      <c r="H413" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I413" s="32" t="inlineStr"/>
+      <c r="G413" s="11" t="n"/>
+      <c r="H413" s="8" t="n"/>
+      <c r="I413" s="8" t="n"/>
       <c r="J413" s="8" t="n"/>
-      <c r="K413" s="34" t="n">
+      <c r="K413" s="8" t="n"/>
+      <c r="L413" s="8" t="n"/>
+      <c r="M413" s="31" t="n">
         <v>2485</v>
       </c>
-      <c r="L413" s="8" t="n"/>
-      <c r="M413" s="8" t="n"/>
       <c r="N413" s="8" t="n"/>
     </row>
     <row r="414">
@@ -17651,25 +16544,15 @@
       <c r="F414" s="8" t="n">
         <v>8436</v>
       </c>
-      <c r="G414" s="31" t="n">
-        <v>45915</v>
-      </c>
-      <c r="H414" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I414" s="32" t="inlineStr">
-        <is>
-          <t>002617</t>
-        </is>
-      </c>
+      <c r="G414" s="11" t="n"/>
+      <c r="H414" s="8" t="n"/>
+      <c r="I414" s="8" t="n"/>
       <c r="J414" s="8" t="n"/>
-      <c r="K414" s="34" t="n">
+      <c r="K414" s="8" t="n"/>
+      <c r="L414" s="8" t="n"/>
+      <c r="M414" s="31" t="n">
         <v>8436</v>
       </c>
-      <c r="L414" s="8" t="n"/>
-      <c r="M414" s="8" t="n"/>
       <c r="N414" s="8" t="n"/>
     </row>
     <row r="415">
@@ -17765,15 +16648,15 @@
       <c r="F417" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="G417" s="31" t="n">
+      <c r="G417" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H417" s="32" t="inlineStr">
+      <c r="H417" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I417" s="32" t="inlineStr">
+      <c r="I417" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -17811,23 +16694,17 @@
       <c r="F418" s="8" t="n">
         <v>1038</v>
       </c>
-      <c r="G418" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H418" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I418" s="32" t="inlineStr"/>
-      <c r="J418" s="33" t="n">
+      <c r="G418" s="8" t="n"/>
+      <c r="H418" s="8" t="n"/>
+      <c r="I418" s="8" t="n"/>
+      <c r="J418" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K418" s="34" t="n">
+      <c r="K418" s="8" t="n"/>
+      <c r="L418" s="8" t="n"/>
+      <c r="M418" s="31" t="n">
         <v>1038</v>
       </c>
-      <c r="L418" s="8" t="n"/>
-      <c r="M418" s="8" t="n"/>
       <c r="N418" s="8" t="n"/>
     </row>
     <row r="419">
@@ -17855,21 +16732,15 @@
       <c r="F419" s="8" t="n">
         <v>3323</v>
       </c>
-      <c r="G419" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H419" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I419" s="32" t="inlineStr"/>
+      <c r="G419" s="11" t="n"/>
+      <c r="H419" s="8" t="n"/>
+      <c r="I419" s="8" t="n"/>
       <c r="J419" s="8" t="n"/>
-      <c r="K419" s="34" t="n">
+      <c r="K419" s="8" t="n"/>
+      <c r="L419" s="8" t="n"/>
+      <c r="M419" s="31" t="n">
         <v>3323</v>
       </c>
-      <c r="L419" s="8" t="n"/>
-      <c r="M419" s="8" t="n"/>
       <c r="N419" s="8" t="n"/>
     </row>
     <row r="420">
@@ -17931,15 +16802,15 @@
       <c r="F421" s="8" t="n">
         <v>3005</v>
       </c>
-      <c r="G421" s="31" t="n">
+      <c r="G421" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H421" s="32" t="inlineStr">
+      <c r="H421" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I421" s="32" t="inlineStr">
+      <c r="I421" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -17977,21 +16848,15 @@
       <c r="F422" s="8" t="n">
         <v>4104</v>
       </c>
-      <c r="G422" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H422" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I422" s="32" t="inlineStr"/>
+      <c r="G422" s="8" t="n"/>
+      <c r="H422" s="8" t="n"/>
+      <c r="I422" s="8" t="n"/>
       <c r="J422" s="8" t="n"/>
-      <c r="K422" s="34" t="n">
+      <c r="K422" s="8" t="n"/>
+      <c r="L422" s="8" t="n"/>
+      <c r="M422" s="31" t="n">
         <v>4104</v>
       </c>
-      <c r="L422" s="8" t="n"/>
-      <c r="M422" s="8" t="n"/>
       <c r="N422" s="8" t="n"/>
     </row>
     <row r="423">
@@ -18223,15 +17088,15 @@
       <c r="F429" s="8" t="n">
         <v>2932</v>
       </c>
-      <c r="G429" s="31" t="n">
+      <c r="G429" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H429" s="32" t="inlineStr">
+      <c r="H429" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I429" s="32" t="inlineStr">
+      <c r="I429" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -18269,15 +17134,15 @@
       <c r="F430" s="8" t="n">
         <v>1053</v>
       </c>
-      <c r="G430" s="31" t="n">
+      <c r="G430" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H430" s="32" t="inlineStr">
+      <c r="H430" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I430" s="32" t="inlineStr">
+      <c r="I430" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -18315,23 +17180,17 @@
       <c r="F431" s="8" t="n">
         <v>1814</v>
       </c>
-      <c r="G431" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H431" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I431" s="32" t="inlineStr"/>
-      <c r="J431" s="33" t="n">
+      <c r="G431" s="8" t="n"/>
+      <c r="H431" s="8" t="n"/>
+      <c r="I431" s="8" t="n"/>
+      <c r="J431" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K431" s="34" t="n">
+      <c r="K431" s="8" t="n"/>
+      <c r="L431" s="8" t="n"/>
+      <c r="M431" s="31" t="n">
         <v>1814</v>
       </c>
-      <c r="L431" s="8" t="n"/>
-      <c r="M431" s="8" t="n"/>
       <c r="N431" s="8" t="n"/>
     </row>
     <row r="432">
@@ -18529,21 +17388,15 @@
       <c r="F437" s="8" t="n">
         <v>1070</v>
       </c>
-      <c r="G437" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H437" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I437" s="32" t="inlineStr"/>
+      <c r="G437" s="8" t="n"/>
+      <c r="H437" s="8" t="n"/>
+      <c r="I437" s="8" t="n"/>
       <c r="J437" s="8" t="n"/>
-      <c r="K437" s="34" t="n">
+      <c r="K437" s="8" t="n"/>
+      <c r="L437" s="8" t="n"/>
+      <c r="M437" s="31" t="n">
         <v>1070</v>
       </c>
-      <c r="L437" s="8" t="n"/>
-      <c r="M437" s="8" t="n"/>
       <c r="N437" s="8" t="n"/>
     </row>
     <row r="438">
@@ -18571,21 +17424,15 @@
       <c r="F438" s="8" t="n">
         <v>1649</v>
       </c>
-      <c r="G438" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H438" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I438" s="32" t="inlineStr"/>
+      <c r="G438" s="11" t="n"/>
+      <c r="H438" s="8" t="n"/>
+      <c r="I438" s="8" t="n"/>
       <c r="J438" s="8" t="n"/>
-      <c r="K438" s="34" t="n">
+      <c r="K438" s="8" t="n"/>
+      <c r="L438" s="8" t="n"/>
+      <c r="M438" s="31" t="n">
         <v>1649</v>
       </c>
-      <c r="L438" s="8" t="n"/>
-      <c r="M438" s="8" t="n"/>
       <c r="N438" s="8" t="n"/>
     </row>
     <row r="439">
@@ -18817,21 +17664,15 @@
       <c r="F445" s="8" t="n">
         <v>3693</v>
       </c>
-      <c r="G445" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H445" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I445" s="32" t="inlineStr"/>
+      <c r="G445" s="11" t="n"/>
+      <c r="H445" s="8" t="n"/>
+      <c r="I445" s="8" t="n"/>
       <c r="J445" s="8" t="n"/>
-      <c r="K445" s="34" t="n">
+      <c r="K445" s="8" t="n"/>
+      <c r="L445" s="8" t="n"/>
+      <c r="M445" s="31" t="n">
         <v>3693</v>
       </c>
-      <c r="L445" s="8" t="n"/>
-      <c r="M445" s="8" t="n"/>
       <c r="N445" s="8" t="n"/>
     </row>
     <row r="446">
@@ -18859,25 +17700,15 @@
       <c r="F446" s="8" t="n">
         <v>827</v>
       </c>
-      <c r="G446" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H446" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I446" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G446" s="11" t="n"/>
+      <c r="H446" s="8" t="n"/>
+      <c r="I446" s="8" t="n"/>
       <c r="J446" s="8" t="n"/>
-      <c r="K446" s="34" t="n">
+      <c r="K446" s="8" t="n"/>
+      <c r="L446" s="8" t="n"/>
+      <c r="M446" s="31" t="n">
         <v>827</v>
       </c>
-      <c r="L446" s="8" t="n"/>
-      <c r="M446" s="8" t="n"/>
       <c r="N446" s="8" t="n"/>
     </row>
     <row r="447">
@@ -18939,21 +17770,15 @@
       <c r="F448" s="8" t="n">
         <v>697</v>
       </c>
-      <c r="G448" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H448" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I448" s="32" t="inlineStr"/>
+      <c r="G448" s="8" t="n"/>
+      <c r="H448" s="8" t="n"/>
+      <c r="I448" s="8" t="n"/>
       <c r="J448" s="8" t="n"/>
-      <c r="K448" s="34" t="n">
+      <c r="K448" s="8" t="n"/>
+      <c r="L448" s="8" t="n"/>
+      <c r="M448" s="31" t="n">
         <v>697</v>
       </c>
-      <c r="L448" s="8" t="n"/>
-      <c r="M448" s="8" t="n"/>
       <c r="N448" s="8" t="n"/>
     </row>
     <row r="449">
@@ -18981,23 +17806,17 @@
       <c r="F449" s="8" t="n">
         <v>3664</v>
       </c>
-      <c r="G449" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H449" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I449" s="32" t="inlineStr"/>
-      <c r="J449" s="33" t="n">
+      <c r="G449" s="8" t="n"/>
+      <c r="H449" s="8" t="n"/>
+      <c r="I449" s="8" t="n"/>
+      <c r="J449" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K449" s="34" t="n">
+      <c r="K449" s="8" t="n"/>
+      <c r="L449" s="8" t="n"/>
+      <c r="M449" s="31" t="n">
         <v>3664</v>
       </c>
-      <c r="L449" s="8" t="n"/>
-      <c r="M449" s="8" t="n"/>
       <c r="N449" s="8" t="n"/>
     </row>
     <row r="450">
@@ -19059,15 +17878,15 @@
       <c r="F451" s="8" t="n">
         <v>220</v>
       </c>
-      <c r="G451" s="31" t="n">
+      <c r="G451" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H451" s="32" t="inlineStr">
+      <c r="H451" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I451" s="32" t="inlineStr">
+      <c r="I451" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -19105,21 +17924,15 @@
       <c r="F452" s="8" t="n">
         <v>219</v>
       </c>
-      <c r="G452" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H452" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I452" s="32" t="inlineStr"/>
+      <c r="G452" s="11" t="n"/>
+      <c r="H452" s="8" t="n"/>
+      <c r="I452" s="8" t="n"/>
       <c r="J452" s="8" t="n"/>
-      <c r="K452" s="34" t="n">
+      <c r="K452" s="8" t="n"/>
+      <c r="L452" s="8" t="n"/>
+      <c r="M452" s="31" t="n">
         <v>219</v>
       </c>
-      <c r="L452" s="8" t="n"/>
-      <c r="M452" s="8" t="n"/>
       <c r="N452" s="8" t="n"/>
     </row>
     <row r="453">
@@ -19147,23 +17960,17 @@
       <c r="F453" s="8" t="n">
         <v>543</v>
       </c>
-      <c r="G453" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H453" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I453" s="32" t="inlineStr"/>
-      <c r="J453" s="33" t="n">
+      <c r="G453" s="8" t="n"/>
+      <c r="H453" s="8" t="n"/>
+      <c r="I453" s="8" t="n"/>
+      <c r="J453" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K453" s="34" t="n">
+      <c r="K453" s="8" t="n"/>
+      <c r="L453" s="8" t="n"/>
+      <c r="M453" s="31" t="n">
         <v>543</v>
       </c>
-      <c r="L453" s="8" t="n"/>
-      <c r="M453" s="8" t="n"/>
       <c r="N453" s="8" t="n"/>
     </row>
     <row r="454">
@@ -19191,15 +17998,15 @@
       <c r="F454" s="8" t="n">
         <v>3788</v>
       </c>
-      <c r="G454" s="31" t="n">
+      <c r="G454" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H454" s="32" t="inlineStr">
+      <c r="H454" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I454" s="32" t="inlineStr">
+      <c r="I454" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -19407,25 +18214,15 @@
       <c r="F460" s="8" t="n">
         <v>687</v>
       </c>
-      <c r="G460" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H460" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I460" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G460" s="11" t="n"/>
+      <c r="H460" s="8" t="n"/>
+      <c r="I460" s="8" t="n"/>
       <c r="J460" s="8" t="n"/>
-      <c r="K460" s="34" t="n">
+      <c r="K460" s="8" t="n"/>
+      <c r="L460" s="8" t="n"/>
+      <c r="M460" s="31" t="n">
         <v>687</v>
       </c>
-      <c r="L460" s="8" t="n"/>
-      <c r="M460" s="8" t="n"/>
       <c r="N460" s="8" t="n"/>
     </row>
     <row r="461">
@@ -19453,21 +18250,15 @@
       <c r="F461" s="8" t="n">
         <v>2403</v>
       </c>
-      <c r="G461" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H461" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I461" s="32" t="inlineStr"/>
+      <c r="G461" s="8" t="n"/>
+      <c r="H461" s="8" t="n"/>
+      <c r="I461" s="8" t="n"/>
       <c r="J461" s="8" t="n"/>
-      <c r="K461" s="34" t="n">
+      <c r="K461" s="8" t="n"/>
+      <c r="L461" s="8" t="n"/>
+      <c r="M461" s="31" t="n">
         <v>2403</v>
       </c>
-      <c r="L461" s="8" t="n"/>
-      <c r="M461" s="8" t="n"/>
       <c r="N461" s="8" t="n"/>
     </row>
     <row r="462">
@@ -19495,15 +18286,15 @@
       <c r="F462" s="8" t="n">
         <v>871</v>
       </c>
-      <c r="G462" s="31" t="n">
+      <c r="G462" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H462" s="32" t="inlineStr">
+      <c r="H462" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I462" s="32" t="inlineStr">
+      <c r="I462" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -19541,15 +18332,15 @@
       <c r="F463" s="8" t="n">
         <v>1214</v>
       </c>
-      <c r="G463" s="31" t="n">
+      <c r="G463" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H463" s="32" t="inlineStr">
+      <c r="H463" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I463" s="32" t="inlineStr">
+      <c r="I463" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -19587,21 +18378,15 @@
       <c r="F464" s="8" t="n">
         <v>7696</v>
       </c>
-      <c r="G464" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H464" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I464" s="32" t="inlineStr"/>
+      <c r="G464" s="11" t="n"/>
+      <c r="H464" s="8" t="n"/>
+      <c r="I464" s="8" t="n"/>
       <c r="J464" s="8" t="n"/>
-      <c r="K464" s="34" t="n">
+      <c r="K464" s="8" t="n"/>
+      <c r="L464" s="8" t="n"/>
+      <c r="M464" s="31" t="n">
         <v>7696</v>
       </c>
-      <c r="L464" s="8" t="n"/>
-      <c r="M464" s="8" t="n"/>
       <c r="N464" s="8" t="n"/>
     </row>
     <row r="465">
@@ -19629,15 +18414,15 @@
       <c r="F465" s="8" t="n">
         <v>897</v>
       </c>
-      <c r="G465" s="31" t="n">
+      <c r="G465" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H465" s="32" t="inlineStr">
+      <c r="H465" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I465" s="32" t="inlineStr">
+      <c r="I465" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -19845,23 +18630,17 @@
       <c r="F471" s="8" t="n">
         <v>406</v>
       </c>
-      <c r="G471" s="30" t="n">
-        <v>45883</v>
-      </c>
-      <c r="H471" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I471" s="32" t="inlineStr"/>
-      <c r="J471" s="33" t="n">
+      <c r="G471" s="8" t="n"/>
+      <c r="H471" s="8" t="n"/>
+      <c r="I471" s="8" t="n"/>
+      <c r="J471" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K471" s="34" t="n">
+      <c r="K471" s="8" t="n"/>
+      <c r="L471" s="8" t="n"/>
+      <c r="M471" s="31" t="n">
         <v>406</v>
       </c>
-      <c r="L471" s="8" t="n"/>
-      <c r="M471" s="8" t="n"/>
       <c r="N471" s="8" t="n"/>
     </row>
     <row r="472">
@@ -19889,21 +18668,15 @@
       <c r="F472" s="8" t="n">
         <v>1242</v>
       </c>
-      <c r="G472" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H472" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I472" s="32" t="inlineStr"/>
+      <c r="G472" s="11" t="n"/>
+      <c r="H472" s="8" t="n"/>
+      <c r="I472" s="8" t="n"/>
       <c r="J472" s="8" t="n"/>
-      <c r="K472" s="34" t="n">
+      <c r="K472" s="8" t="n"/>
+      <c r="L472" s="8" t="n"/>
+      <c r="M472" s="31" t="n">
         <v>1242</v>
       </c>
-      <c r="L472" s="8" t="n"/>
-      <c r="M472" s="8" t="n"/>
       <c r="N472" s="8" t="n"/>
     </row>
     <row r="473">
@@ -19931,15 +18704,15 @@
       <c r="F473" s="8" t="n">
         <v>319</v>
       </c>
-      <c r="G473" s="31" t="n">
+      <c r="G473" s="32" t="n">
         <v>45894</v>
       </c>
-      <c r="H473" s="32" t="inlineStr">
+      <c r="H473" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I473" s="32" t="inlineStr">
+      <c r="I473" s="33" t="inlineStr">
         <is>
           <t>002569</t>
         </is>
@@ -19977,15 +18750,15 @@
       <c r="F474" s="8" t="n">
         <v>3918</v>
       </c>
-      <c r="G474" s="31" t="n">
+      <c r="G474" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H474" s="32" t="inlineStr">
+      <c r="H474" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I474" s="32" t="inlineStr">
+      <c r="I474" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -20023,21 +18796,15 @@
       <c r="F475" s="8" t="n">
         <v>1178</v>
       </c>
-      <c r="G475" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H475" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I475" s="32" t="inlineStr"/>
+      <c r="G475" s="8" t="n"/>
+      <c r="H475" s="8" t="n"/>
+      <c r="I475" s="8" t="n"/>
       <c r="J475" s="8" t="n"/>
-      <c r="K475" s="34" t="n">
+      <c r="K475" s="8" t="n"/>
+      <c r="L475" s="8" t="n"/>
+      <c r="M475" s="31" t="n">
         <v>1178</v>
       </c>
-      <c r="L475" s="8" t="n"/>
-      <c r="M475" s="8" t="n"/>
       <c r="N475" s="8" t="n"/>
     </row>
     <row r="476">
@@ -20099,25 +18866,15 @@
       <c r="F477" s="8" t="n">
         <v>850</v>
       </c>
-      <c r="G477" s="31" t="n">
-        <v>45899</v>
-      </c>
-      <c r="H477" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I477" s="32" t="inlineStr">
-        <is>
-          <t>002585</t>
-        </is>
-      </c>
+      <c r="G477" s="11" t="n"/>
+      <c r="H477" s="8" t="n"/>
+      <c r="I477" s="8" t="n"/>
       <c r="J477" s="8" t="n"/>
-      <c r="K477" s="34" t="n">
-        <v>837</v>
-      </c>
+      <c r="K477" s="8" t="n"/>
       <c r="L477" s="8" t="n"/>
-      <c r="M477" s="8" t="n"/>
+      <c r="M477" s="31" t="n">
+        <v>850</v>
+      </c>
       <c r="N477" s="8" t="n"/>
     </row>
     <row r="478">
@@ -20179,21 +18936,15 @@
       <c r="F479" s="8" t="n">
         <v>1297</v>
       </c>
-      <c r="G479" s="31" t="n">
-        <v>45870</v>
-      </c>
-      <c r="H479" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I479" s="32" t="inlineStr"/>
+      <c r="G479" s="11" t="n"/>
+      <c r="H479" s="8" t="n"/>
+      <c r="I479" s="8" t="n"/>
       <c r="J479" s="8" t="n"/>
-      <c r="K479" s="34" t="n">
+      <c r="K479" s="8" t="n"/>
+      <c r="L479" s="8" t="n"/>
+      <c r="M479" s="31" t="n">
         <v>1297</v>
       </c>
-      <c r="L479" s="8" t="n"/>
-      <c r="M479" s="8" t="n"/>
       <c r="N479" s="8" t="n"/>
     </row>
     <row r="480">
@@ -20221,21 +18972,15 @@
       <c r="F480" s="8" t="n">
         <v>866</v>
       </c>
-      <c r="G480" s="30" t="n">
-        <v>45875</v>
-      </c>
-      <c r="H480" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I480" s="32" t="inlineStr"/>
+      <c r="G480" s="8" t="n"/>
+      <c r="H480" s="8" t="n"/>
+      <c r="I480" s="8" t="n"/>
       <c r="J480" s="8" t="n"/>
-      <c r="K480" s="34" t="n">
+      <c r="K480" s="8" t="n"/>
+      <c r="L480" s="8" t="n"/>
+      <c r="M480" s="31" t="n">
         <v>866</v>
       </c>
-      <c r="L480" s="8" t="n"/>
-      <c r="M480" s="8" t="n"/>
       <c r="N480" s="8" t="n"/>
     </row>
     <row r="481">
@@ -20263,15 +19008,15 @@
       <c r="F481" s="8" t="n">
         <v>4306</v>
       </c>
-      <c r="G481" s="31" t="n">
+      <c r="G481" s="32" t="n">
         <v>45925</v>
       </c>
-      <c r="H481" s="32" t="inlineStr">
+      <c r="H481" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I481" s="32" t="inlineStr">
+      <c r="I481" s="33" t="inlineStr">
         <is>
           <t>002613</t>
         </is>
@@ -20377,15 +19122,15 @@
       <c r="F484" s="8" t="n">
         <v>990</v>
       </c>
-      <c r="G484" s="31" t="n">
+      <c r="G484" s="32" t="n">
         <v>45879</v>
       </c>
-      <c r="H484" s="32" t="inlineStr">
+      <c r="H484" s="33" t="inlineStr">
         <is>
           <t>CHQ</t>
         </is>
       </c>
-      <c r="I484" s="32" t="inlineStr">
+      <c r="I484" s="33" t="inlineStr">
         <is>
           <t>002561</t>
         </is>
@@ -20525,21 +19270,15 @@
       <c r="F488" s="8" t="n">
         <v>4088</v>
       </c>
-      <c r="G488" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H488" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I488" s="32" t="inlineStr"/>
+      <c r="G488" s="11" t="n"/>
+      <c r="H488" s="8" t="n"/>
+      <c r="I488" s="8" t="n"/>
       <c r="J488" s="8" t="n"/>
-      <c r="K488" s="34" t="n">
+      <c r="K488" s="8" t="n"/>
+      <c r="L488" s="8" t="n"/>
+      <c r="M488" s="31" t="n">
         <v>4088</v>
       </c>
-      <c r="L488" s="8" t="n"/>
-      <c r="M488" s="8" t="n"/>
       <c r="N488" s="8" t="n"/>
     </row>
     <row r="489">
@@ -20771,21 +19510,15 @@
       <c r="F495" s="8" t="n">
         <v>975</v>
       </c>
-      <c r="G495" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H495" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I495" s="32" t="inlineStr"/>
+      <c r="G495" s="11" t="n"/>
+      <c r="H495" s="8" t="n"/>
+      <c r="I495" s="8" t="n"/>
       <c r="J495" s="8" t="n"/>
-      <c r="K495" s="34" t="n">
+      <c r="K495" s="8" t="n"/>
+      <c r="L495" s="8" t="n"/>
+      <c r="M495" s="31" t="n">
         <v>975</v>
       </c>
-      <c r="L495" s="8" t="n"/>
-      <c r="M495" s="8" t="n"/>
       <c r="N495" s="8" t="n"/>
     </row>
     <row r="496">
@@ -20881,21 +19614,15 @@
       <c r="F498" s="8" t="n">
         <v>584</v>
       </c>
-      <c r="G498" s="31" t="n">
-        <v>45872</v>
-      </c>
-      <c r="H498" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I498" s="32" t="inlineStr"/>
+      <c r="G498" s="11" t="n"/>
+      <c r="H498" s="8" t="n"/>
+      <c r="I498" s="8" t="n"/>
       <c r="J498" s="8" t="n"/>
-      <c r="K498" s="34" t="n">
+      <c r="K498" s="8" t="n"/>
+      <c r="L498" s="8" t="n"/>
+      <c r="M498" s="31" t="n">
         <v>584</v>
       </c>
-      <c r="L498" s="8" t="n"/>
-      <c r="M498" s="8" t="n"/>
       <c r="N498" s="8" t="n"/>
     </row>
     <row r="499">
@@ -21161,21 +19888,15 @@
       <c r="F506" s="8" t="n">
         <v>2038</v>
       </c>
-      <c r="G506" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H506" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I506" s="32" t="inlineStr"/>
+      <c r="G506" s="11" t="n"/>
+      <c r="H506" s="8" t="n"/>
+      <c r="I506" s="8" t="n"/>
       <c r="J506" s="8" t="n"/>
-      <c r="K506" s="34" t="n">
+      <c r="K506" s="8" t="n"/>
+      <c r="L506" s="8" t="n"/>
+      <c r="M506" s="31" t="n">
         <v>2038</v>
       </c>
-      <c r="L506" s="8" t="n"/>
-      <c r="M506" s="8" t="n"/>
       <c r="N506" s="8" t="n"/>
     </row>
     <row r="507">
@@ -21475,21 +20196,15 @@
       <c r="F515" s="8" t="n">
         <v>3209</v>
       </c>
-      <c r="G515" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H515" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I515" s="32" t="inlineStr"/>
+      <c r="G515" s="11" t="n"/>
+      <c r="H515" s="8" t="n"/>
+      <c r="I515" s="8" t="n"/>
       <c r="J515" s="8" t="n"/>
-      <c r="K515" s="34" t="n">
+      <c r="K515" s="8" t="n"/>
+      <c r="L515" s="8" t="n"/>
+      <c r="M515" s="31" t="n">
         <v>3209</v>
       </c>
-      <c r="L515" s="8" t="n"/>
-      <c r="M515" s="8" t="n"/>
       <c r="N515" s="8" t="n"/>
     </row>
     <row r="516">
@@ -21721,21 +20436,15 @@
       <c r="F522" s="8" t="n">
         <v>6518</v>
       </c>
-      <c r="G522" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H522" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I522" s="32" t="inlineStr"/>
+      <c r="G522" s="11" t="n"/>
+      <c r="H522" s="8" t="n"/>
+      <c r="I522" s="8" t="n"/>
       <c r="J522" s="8" t="n"/>
-      <c r="K522" s="34" t="n">
+      <c r="K522" s="8" t="n"/>
+      <c r="L522" s="8" t="n"/>
+      <c r="M522" s="31" t="n">
         <v>6518</v>
       </c>
-      <c r="L522" s="8" t="n"/>
-      <c r="M522" s="8" t="n"/>
       <c r="N522" s="8" t="n"/>
     </row>
     <row r="523">
@@ -22307,21 +21016,15 @@
       <c r="F539" s="8" t="n">
         <v>193</v>
       </c>
-      <c r="G539" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H539" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I539" s="32" t="inlineStr"/>
+      <c r="G539" s="11" t="n"/>
+      <c r="H539" s="8" t="n"/>
+      <c r="I539" s="8" t="n"/>
       <c r="J539" s="8" t="n"/>
-      <c r="K539" s="34" t="n">
+      <c r="K539" s="8" t="n"/>
+      <c r="L539" s="8" t="n"/>
+      <c r="M539" s="31" t="n">
         <v>193</v>
       </c>
-      <c r="L539" s="8" t="n"/>
-      <c r="M539" s="8" t="n"/>
       <c r="N539" s="8" t="n"/>
     </row>
     <row r="540">
@@ -22485,21 +21188,15 @@
       <c r="F544" s="8" t="n">
         <v>392</v>
       </c>
-      <c r="G544" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H544" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I544" s="32" t="inlineStr"/>
+      <c r="G544" s="11" t="n"/>
+      <c r="H544" s="8" t="n"/>
+      <c r="I544" s="8" t="n"/>
       <c r="J544" s="8" t="n"/>
-      <c r="K544" s="34" t="n">
+      <c r="K544" s="8" t="n"/>
+      <c r="L544" s="8" t="n"/>
+      <c r="M544" s="31" t="n">
         <v>392</v>
       </c>
-      <c r="L544" s="8" t="n"/>
-      <c r="M544" s="8" t="n"/>
       <c r="N544" s="8" t="n"/>
     </row>
     <row r="545">
@@ -22799,21 +21496,15 @@
       <c r="F553" s="8" t="n">
         <v>2086</v>
       </c>
-      <c r="G553" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H553" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I553" s="32" t="inlineStr"/>
+      <c r="G553" s="11" t="n"/>
+      <c r="H553" s="8" t="n"/>
+      <c r="I553" s="8" t="n"/>
       <c r="J553" s="8" t="n"/>
-      <c r="K553" s="34" t="n">
+      <c r="K553" s="8" t="n"/>
+      <c r="L553" s="8" t="n"/>
+      <c r="M553" s="31" t="n">
         <v>2086</v>
       </c>
-      <c r="L553" s="8" t="n"/>
-      <c r="M553" s="8" t="n"/>
       <c r="N553" s="8" t="n"/>
     </row>
     <row r="554">
@@ -23113,21 +21804,15 @@
       <c r="F562" s="8" t="n">
         <v>1167</v>
       </c>
-      <c r="G562" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H562" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I562" s="32" t="inlineStr"/>
+      <c r="G562" s="11" t="n"/>
+      <c r="H562" s="8" t="n"/>
+      <c r="I562" s="8" t="n"/>
       <c r="J562" s="8" t="n"/>
-      <c r="K562" s="34" t="n">
+      <c r="K562" s="8" t="n"/>
+      <c r="L562" s="8" t="n"/>
+      <c r="M562" s="31" t="n">
         <v>1167</v>
       </c>
-      <c r="L562" s="8" t="n"/>
-      <c r="M562" s="8" t="n"/>
       <c r="N562" s="8" t="n"/>
     </row>
     <row r="563">
@@ -23359,21 +22044,15 @@
       <c r="F569" s="8" t="n">
         <v>832</v>
       </c>
-      <c r="G569" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H569" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I569" s="32" t="inlineStr"/>
+      <c r="G569" s="11" t="n"/>
+      <c r="H569" s="8" t="n"/>
+      <c r="I569" s="8" t="n"/>
       <c r="J569" s="8" t="n"/>
-      <c r="K569" s="34" t="n">
+      <c r="K569" s="8" t="n"/>
+      <c r="L569" s="8" t="n"/>
+      <c r="M569" s="31" t="n">
         <v>832</v>
       </c>
-      <c r="L569" s="8" t="n"/>
-      <c r="M569" s="8" t="n"/>
       <c r="N569" s="8" t="n"/>
     </row>
     <row r="570">
@@ -23809,21 +22488,15 @@
       <c r="F582" s="8" t="n">
         <v>7116</v>
       </c>
-      <c r="G582" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H582" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I582" s="32" t="inlineStr"/>
+      <c r="G582" s="11" t="n"/>
+      <c r="H582" s="8" t="n"/>
+      <c r="I582" s="8" t="n"/>
       <c r="J582" s="8" t="n"/>
-      <c r="K582" s="34" t="n">
+      <c r="K582" s="8" t="n"/>
+      <c r="L582" s="8" t="n"/>
+      <c r="M582" s="31" t="n">
         <v>7116</v>
       </c>
-      <c r="L582" s="8" t="n"/>
-      <c r="M582" s="8" t="n"/>
       <c r="N582" s="8" t="n"/>
     </row>
     <row r="583">
@@ -24327,21 +23000,15 @@
       <c r="F597" s="8" t="n">
         <v>5597</v>
       </c>
-      <c r="G597" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H597" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I597" s="32" t="inlineStr"/>
+      <c r="G597" s="11" t="n"/>
+      <c r="H597" s="8" t="n"/>
+      <c r="I597" s="8" t="n"/>
       <c r="J597" s="8" t="n"/>
-      <c r="K597" s="34" t="n">
+      <c r="K597" s="8" t="n"/>
+      <c r="L597" s="8" t="n"/>
+      <c r="M597" s="31" t="n">
         <v>5597</v>
       </c>
-      <c r="L597" s="8" t="n"/>
-      <c r="M597" s="8" t="n"/>
       <c r="N597" s="8" t="n"/>
     </row>
     <row r="598">
@@ -24573,21 +23240,15 @@
       <c r="F604" s="8" t="n">
         <v>270</v>
       </c>
-      <c r="G604" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H604" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I604" s="32" t="inlineStr"/>
+      <c r="G604" s="11" t="n"/>
+      <c r="H604" s="8" t="n"/>
+      <c r="I604" s="8" t="n"/>
       <c r="J604" s="8" t="n"/>
-      <c r="K604" s="34" t="n">
+      <c r="K604" s="8" t="n"/>
+      <c r="L604" s="8" t="n"/>
+      <c r="M604" s="31" t="n">
         <v>270</v>
       </c>
-      <c r="L604" s="8" t="n"/>
-      <c r="M604" s="8" t="n"/>
       <c r="N604" s="8" t="n"/>
     </row>
     <row r="605">
@@ -24785,21 +23446,15 @@
       <c r="F610" s="8" t="n">
         <v>5786</v>
       </c>
-      <c r="G610" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H610" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I610" s="32" t="inlineStr"/>
+      <c r="G610" s="11" t="n"/>
+      <c r="H610" s="8" t="n"/>
+      <c r="I610" s="8" t="n"/>
       <c r="J610" s="8" t="n"/>
-      <c r="K610" s="34" t="n">
+      <c r="K610" s="8" t="n"/>
+      <c r="L610" s="8" t="n"/>
+      <c r="M610" s="31" t="n">
         <v>5786</v>
       </c>
-      <c r="L610" s="8" t="n"/>
-      <c r="M610" s="8" t="n"/>
       <c r="N610" s="8" t="n"/>
     </row>
     <row r="611">
@@ -25269,25 +23924,15 @@
       <c r="F624" s="8" t="n">
         <v>6054</v>
       </c>
-      <c r="G624" s="31" t="n">
-        <v>45915</v>
-      </c>
-      <c r="H624" s="32" t="inlineStr">
-        <is>
-          <t>CHQ</t>
-        </is>
-      </c>
-      <c r="I624" s="32" t="inlineStr">
-        <is>
-          <t>002617</t>
-        </is>
-      </c>
+      <c r="G624" s="11" t="n"/>
+      <c r="H624" s="8" t="n"/>
+      <c r="I624" s="8" t="n"/>
       <c r="J624" s="8" t="n"/>
-      <c r="K624" s="34" t="n">
+      <c r="K624" s="8" t="n"/>
+      <c r="L624" s="8" t="n"/>
+      <c r="M624" s="31" t="n">
         <v>6054</v>
       </c>
-      <c r="L624" s="8" t="n"/>
-      <c r="M624" s="8" t="n"/>
       <c r="N624" s="8" t="n"/>
     </row>
     <row r="625">
@@ -25553,21 +24198,15 @@
       <c r="F632" s="8" t="n">
         <v>2743</v>
       </c>
-      <c r="G632" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H632" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I632" s="32" t="inlineStr"/>
+      <c r="G632" s="11" t="n"/>
+      <c r="H632" s="8" t="n"/>
+      <c r="I632" s="8" t="n"/>
       <c r="J632" s="8" t="n"/>
-      <c r="K632" s="34" t="n">
+      <c r="K632" s="8" t="n"/>
+      <c r="L632" s="8" t="n"/>
+      <c r="M632" s="31" t="n">
         <v>2743</v>
       </c>
-      <c r="L632" s="8" t="n"/>
-      <c r="M632" s="8" t="n"/>
       <c r="N632" s="8" t="n"/>
     </row>
     <row r="633">
@@ -25629,21 +24268,15 @@
       <c r="F634" s="8" t="n">
         <v>2381</v>
       </c>
-      <c r="G634" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H634" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I634" s="32" t="inlineStr"/>
+      <c r="G634" s="11" t="n"/>
+      <c r="H634" s="8" t="n"/>
+      <c r="I634" s="8" t="n"/>
       <c r="J634" s="8" t="n"/>
-      <c r="K634" s="34" t="n">
+      <c r="K634" s="8" t="n"/>
+      <c r="L634" s="8" t="n"/>
+      <c r="M634" s="31" t="n">
         <v>2381</v>
       </c>
-      <c r="L634" s="8" t="n"/>
-      <c r="M634" s="8" t="n"/>
       <c r="N634" s="8" t="n"/>
     </row>
     <row r="635">
@@ -26283,21 +24916,15 @@
       <c r="F653" s="8" t="n">
         <v>422</v>
       </c>
-      <c r="G653" s="31" t="n">
-        <v>45902</v>
-      </c>
-      <c r="H653" s="32" t="inlineStr">
-        <is>
-          <t>GPAY</t>
-        </is>
-      </c>
-      <c r="I653" s="32" t="inlineStr"/>
+      <c r="G653" s="11" t="n"/>
+      <c r="H653" s="8" t="n"/>
+      <c r="I653" s="8" t="n"/>
       <c r="J653" s="8" t="n"/>
-      <c r="K653" s="34" t="n">
+      <c r="K653" s="8" t="n"/>
+      <c r="L653" s="8" t="n"/>
+      <c r="M653" s="31" t="n">
         <v>422</v>
       </c>
-      <c r="L653" s="8" t="n"/>
-      <c r="M653" s="8" t="n"/>
       <c r="N653" s="8" t="n"/>
     </row>
     <row r="654">
@@ -38375,14 +37002,14 @@
       <c r="N1029" s="12" t="n"/>
     </row>
     <row r="1030" ht="15" customHeight="1" thickBot="1">
-      <c r="A1030" s="40" t="inlineStr">
+      <c r="A1030" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B1030" s="41" t="n"/>
-      <c r="C1030" s="41" t="n"/>
-      <c r="D1030" s="42" t="n"/>
+      <c r="B1030" s="42" t="n"/>
+      <c r="C1030" s="42" t="n"/>
+      <c r="D1030" s="43" t="n"/>
       <c r="E1030" s="23">
         <f>SUM(E852:E1029)</f>
         <v/>

--- a/System_Puchase.xlsx
+++ b/System_Puchase.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -274,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
@@ -346,6 +347,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="12" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4319,9 +4321,7 @@
       <c r="J84" s="49" t="n"/>
       <c r="K84" s="49" t="n"/>
       <c r="L84" s="49" t="n"/>
-      <c r="M84" s="51" t="n">
-        <v>699</v>
-      </c>
+      <c r="M84" s="49" t="n"/>
       <c r="N84" s="49" t="n"/>
     </row>
     <row r="85">
@@ -5291,9 +5291,7 @@
       <c r="J108" s="49" t="n"/>
       <c r="K108" s="49" t="n"/>
       <c r="L108" s="49" t="n"/>
-      <c r="M108" s="51" t="n">
-        <v>2002</v>
-      </c>
+      <c r="M108" s="49" t="n"/>
       <c r="N108" s="49" t="n"/>
     </row>
     <row r="109">
@@ -6263,9 +6261,7 @@
       <c r="J133" s="49" t="n"/>
       <c r="K133" s="49" t="n"/>
       <c r="L133" s="49" t="n"/>
-      <c r="M133" s="51" t="n">
-        <v>159</v>
-      </c>
+      <c r="M133" s="49" t="n"/>
       <c r="N133" s="49" t="n"/>
     </row>
     <row r="134">
@@ -6421,9 +6417,7 @@
       <c r="J137" s="49" t="n"/>
       <c r="K137" s="49" t="n"/>
       <c r="L137" s="49" t="n"/>
-      <c r="M137" s="51" t="n">
-        <v>5071</v>
-      </c>
+      <c r="M137" s="49" t="n"/>
       <c r="N137" s="49" t="n"/>
     </row>
     <row r="138">
@@ -6491,9 +6485,7 @@
       <c r="J139" s="49" t="n"/>
       <c r="K139" s="49" t="n"/>
       <c r="L139" s="49" t="n"/>
-      <c r="M139" s="51" t="n">
-        <v>5617</v>
-      </c>
+      <c r="M139" s="49" t="n"/>
       <c r="N139" s="49" t="n"/>
     </row>
     <row r="140">
@@ -6527,9 +6519,7 @@
       <c r="J140" s="49" t="n"/>
       <c r="K140" s="49" t="n"/>
       <c r="L140" s="49" t="n"/>
-      <c r="M140" s="51" t="n">
-        <v>6371</v>
-      </c>
+      <c r="M140" s="49" t="n"/>
       <c r="N140" s="49" t="n"/>
     </row>
     <row r="141">
@@ -6719,9 +6709,7 @@
       <c r="J145" s="49" t="n"/>
       <c r="K145" s="49" t="n"/>
       <c r="L145" s="49" t="n"/>
-      <c r="M145" s="51" t="n">
-        <v>593</v>
-      </c>
+      <c r="M145" s="49" t="n"/>
       <c r="N145" s="49" t="n"/>
     </row>
     <row r="146">
@@ -7593,9 +7581,7 @@
       <c r="J167" s="49" t="n"/>
       <c r="K167" s="49" t="n"/>
       <c r="L167" s="49" t="n"/>
-      <c r="M167" s="51" t="n">
-        <v>3590</v>
-      </c>
+      <c r="M167" s="49" t="n"/>
       <c r="N167" s="49" t="n"/>
     </row>
     <row r="168">
@@ -8413,9 +8399,7 @@
       <c r="J187" s="49" t="n"/>
       <c r="K187" s="49" t="n"/>
       <c r="L187" s="49" t="n"/>
-      <c r="M187" s="51" t="n">
-        <v>186</v>
-      </c>
+      <c r="M187" s="49" t="n"/>
       <c r="N187" s="49" t="n"/>
     </row>
     <row r="188">
@@ -9227,9 +9211,7 @@
       <c r="J207" s="49" t="n"/>
       <c r="K207" s="49" t="n"/>
       <c r="L207" s="49" t="n"/>
-      <c r="M207" s="51" t="n">
-        <v>724</v>
-      </c>
+      <c r="M207" s="49" t="n"/>
       <c r="N207" s="49" t="n"/>
     </row>
     <row r="208">
@@ -11351,9 +11333,7 @@
       <c r="J260" s="49" t="n"/>
       <c r="K260" s="49" t="n"/>
       <c r="L260" s="49" t="n"/>
-      <c r="M260" s="51" t="n">
-        <v>438</v>
-      </c>
+      <c r="M260" s="49" t="n"/>
       <c r="N260" s="49" t="n"/>
     </row>
     <row r="261">
@@ -14047,9 +14027,7 @@
       <c r="J326" s="49" t="n"/>
       <c r="K326" s="49" t="n"/>
       <c r="L326" s="49" t="n"/>
-      <c r="M326" s="51" t="n">
-        <v>1362</v>
-      </c>
+      <c r="M326" s="49" t="n"/>
       <c r="N326" s="49" t="n"/>
     </row>
     <row r="327">
@@ -16593,9 +16571,7 @@
       <c r="J391" s="49" t="n"/>
       <c r="K391" s="49" t="n"/>
       <c r="L391" s="49" t="n"/>
-      <c r="M391" s="51" t="n">
-        <v>3890</v>
-      </c>
+      <c r="M391" s="49" t="n"/>
       <c r="N391" s="49" t="n"/>
     </row>
     <row r="392">
@@ -16911,9 +16887,7 @@
       <c r="J400" s="49" t="n"/>
       <c r="K400" s="49" t="n"/>
       <c r="L400" s="49" t="n"/>
-      <c r="M400" s="51" t="n">
-        <v>187</v>
-      </c>
+      <c r="M400" s="49" t="n"/>
       <c r="N400" s="49" t="n"/>
     </row>
     <row r="401">
@@ -18671,9 +18645,7 @@
       <c r="J446" s="49" t="n"/>
       <c r="K446" s="49" t="n"/>
       <c r="L446" s="49" t="n"/>
-      <c r="M446" s="51" t="n">
-        <v>827</v>
-      </c>
+      <c r="M446" s="49" t="n"/>
       <c r="N446" s="49" t="n"/>
     </row>
     <row r="447">
@@ -19209,9 +19181,7 @@
       <c r="J460" s="49" t="n"/>
       <c r="K460" s="49" t="n"/>
       <c r="L460" s="49" t="n"/>
-      <c r="M460" s="51" t="n">
-        <v>687</v>
-      </c>
+      <c r="M460" s="49" t="n"/>
       <c r="N460" s="49" t="n"/>
     </row>
     <row r="461">
@@ -19891,9 +19861,7 @@
       <c r="J477" s="49" t="n"/>
       <c r="K477" s="49" t="n"/>
       <c r="L477" s="49" t="n"/>
-      <c r="M477" s="51" t="n">
-        <v>850</v>
-      </c>
+      <c r="M477" s="49" t="n"/>
       <c r="N477" s="49" t="n"/>
     </row>
     <row r="478">
@@ -20267,11 +20235,19 @@
       <c r="F487" s="7" t="n">
         <v>250</v>
       </c>
-      <c r="G487" s="49" t="n"/>
-      <c r="H487" s="49" t="n"/>
-      <c r="I487" s="49" t="n"/>
+      <c r="G487" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H487" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I487" s="46" t="inlineStr"/>
       <c r="J487" s="49" t="n"/>
-      <c r="K487" s="49" t="n"/>
+      <c r="K487" s="48" t="n">
+        <v>250</v>
+      </c>
       <c r="L487" s="49" t="n"/>
       <c r="M487" s="49" t="n"/>
       <c r="N487" s="49" t="n"/>
@@ -20377,11 +20353,23 @@
       <c r="F490" s="7" t="n">
         <v>2230</v>
       </c>
-      <c r="G490" s="50" t="n"/>
-      <c r="H490" s="49" t="n"/>
-      <c r="I490" s="49" t="n"/>
+      <c r="G490" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H490" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I490" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J490" s="49" t="n"/>
-      <c r="K490" s="49" t="n"/>
+      <c r="K490" s="48" t="n">
+        <v>2230</v>
+      </c>
       <c r="L490" s="49" t="n"/>
       <c r="M490" s="49" t="n"/>
       <c r="N490" s="49" t="n"/>
@@ -20513,11 +20501,19 @@
       <c r="F494" s="7" t="n">
         <v>982</v>
       </c>
-      <c r="G494" s="49" t="n"/>
-      <c r="H494" s="49" t="n"/>
-      <c r="I494" s="49" t="n"/>
+      <c r="G494" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H494" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I494" s="46" t="inlineStr"/>
       <c r="J494" s="49" t="n"/>
-      <c r="K494" s="49" t="n"/>
+      <c r="K494" s="48" t="n">
+        <v>982</v>
+      </c>
       <c r="L494" s="49" t="n"/>
       <c r="M494" s="49" t="n"/>
       <c r="N494" s="49" t="n"/>
@@ -20589,11 +20585,23 @@
       <c r="F496" s="7" t="n">
         <v>4494</v>
       </c>
-      <c r="G496" s="50" t="n"/>
-      <c r="H496" s="49" t="n"/>
-      <c r="I496" s="49" t="n"/>
+      <c r="G496" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H496" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I496" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J496" s="49" t="n"/>
-      <c r="K496" s="49" t="n"/>
+      <c r="K496" s="48" t="n">
+        <v>4494</v>
+      </c>
       <c r="L496" s="49" t="n"/>
       <c r="M496" s="49" t="n"/>
       <c r="N496" s="49" t="n"/>
@@ -20869,11 +20877,23 @@
       <c r="F504" s="7" t="n">
         <v>3961</v>
       </c>
-      <c r="G504" s="50" t="n"/>
-      <c r="H504" s="49" t="n"/>
-      <c r="I504" s="49" t="n"/>
+      <c r="G504" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H504" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I504" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J504" s="49" t="n"/>
-      <c r="K504" s="49" t="n"/>
+      <c r="K504" s="48" t="n">
+        <v>3961</v>
+      </c>
       <c r="L504" s="49" t="n"/>
       <c r="M504" s="49" t="n"/>
       <c r="N504" s="49" t="n"/>
@@ -21047,11 +21067,23 @@
       <c r="F509" s="7" t="n">
         <v>279</v>
       </c>
-      <c r="G509" s="50" t="n"/>
-      <c r="H509" s="49" t="n"/>
-      <c r="I509" s="49" t="n"/>
+      <c r="G509" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H509" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I509" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J509" s="49" t="n"/>
-      <c r="K509" s="49" t="n"/>
+      <c r="K509" s="48" t="n">
+        <v>279</v>
+      </c>
       <c r="L509" s="49" t="n"/>
       <c r="M509" s="49" t="n"/>
       <c r="N509" s="49" t="n"/>
@@ -21327,11 +21359,23 @@
       <c r="F517" s="7" t="n">
         <v>12647</v>
       </c>
-      <c r="G517" s="50" t="n"/>
-      <c r="H517" s="49" t="n"/>
-      <c r="I517" s="49" t="n"/>
+      <c r="G517" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H517" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I517" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J517" s="49" t="n"/>
-      <c r="K517" s="49" t="n"/>
+      <c r="K517" s="48" t="n">
+        <v>12647</v>
+      </c>
       <c r="L517" s="49" t="n"/>
       <c r="M517" s="49" t="n"/>
       <c r="N517" s="49" t="n"/>
@@ -21429,11 +21473,23 @@
       <c r="F520" s="7" t="n">
         <v>4213</v>
       </c>
-      <c r="G520" s="50" t="n"/>
-      <c r="H520" s="49" t="n"/>
-      <c r="I520" s="49" t="n"/>
+      <c r="G520" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H520" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I520" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J520" s="49" t="n"/>
-      <c r="K520" s="49" t="n"/>
+      <c r="K520" s="48" t="n">
+        <v>4213</v>
+      </c>
       <c r="L520" s="49" t="n"/>
       <c r="M520" s="49" t="n"/>
       <c r="N520" s="49" t="n"/>
@@ -21539,11 +21595,23 @@
       <c r="F523" s="7" t="n">
         <v>587</v>
       </c>
-      <c r="G523" s="50" t="n"/>
-      <c r="H523" s="49" t="n"/>
-      <c r="I523" s="49" t="n"/>
+      <c r="G523" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H523" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I523" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J523" s="49" t="n"/>
-      <c r="K523" s="49" t="n"/>
+      <c r="K523" s="48" t="n">
+        <v>587</v>
+      </c>
       <c r="L523" s="49" t="n"/>
       <c r="M523" s="49" t="n"/>
       <c r="N523" s="49" t="n"/>
@@ -21607,11 +21675,23 @@
       <c r="F525" s="7" t="n">
         <v>8733</v>
       </c>
-      <c r="G525" s="50" t="n"/>
-      <c r="H525" s="49" t="n"/>
-      <c r="I525" s="49" t="n"/>
+      <c r="G525" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H525" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I525" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J525" s="49" t="n"/>
-      <c r="K525" s="49" t="n"/>
+      <c r="K525" s="48" t="n">
+        <v>8733</v>
+      </c>
       <c r="L525" s="49" t="n"/>
       <c r="M525" s="49" t="n"/>
       <c r="N525" s="49" t="n"/>
@@ -21811,11 +21891,23 @@
       <c r="F531" s="7" t="n">
         <v>1550</v>
       </c>
-      <c r="G531" s="50" t="n"/>
-      <c r="H531" s="49" t="n"/>
-      <c r="I531" s="49" t="n"/>
+      <c r="G531" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H531" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I531" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J531" s="49" t="n"/>
-      <c r="K531" s="49" t="n"/>
+      <c r="K531" s="48" t="n">
+        <v>1550</v>
+      </c>
       <c r="L531" s="49" t="n"/>
       <c r="M531" s="49" t="n"/>
       <c r="N531" s="49" t="n"/>
@@ -21845,11 +21937,23 @@
       <c r="F532" s="7" t="n">
         <v>7317</v>
       </c>
-      <c r="G532" s="50" t="n"/>
-      <c r="H532" s="49" t="n"/>
-      <c r="I532" s="49" t="n"/>
+      <c r="G532" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H532" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I532" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J532" s="49" t="n"/>
-      <c r="K532" s="49" t="n"/>
+      <c r="K532" s="48" t="n">
+        <v>7317</v>
+      </c>
       <c r="L532" s="49" t="n"/>
       <c r="M532" s="49" t="n"/>
       <c r="N532" s="49" t="n"/>
@@ -21913,11 +22017,19 @@
       <c r="F534" s="7" t="n">
         <v>1838</v>
       </c>
-      <c r="G534" s="49" t="n"/>
-      <c r="H534" s="49" t="n"/>
-      <c r="I534" s="49" t="n"/>
+      <c r="G534" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H534" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I534" s="46" t="inlineStr"/>
       <c r="J534" s="49" t="n"/>
-      <c r="K534" s="49" t="n"/>
+      <c r="K534" s="48" t="n">
+        <v>1838</v>
+      </c>
       <c r="L534" s="49" t="n"/>
       <c r="M534" s="49" t="n"/>
       <c r="N534" s="49" t="n"/>
@@ -22049,11 +22161,23 @@
       <c r="F538" s="7" t="n">
         <v>570</v>
       </c>
-      <c r="G538" s="50" t="n"/>
-      <c r="H538" s="49" t="n"/>
-      <c r="I538" s="49" t="n"/>
+      <c r="G538" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H538" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I538" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J538" s="49" t="n"/>
-      <c r="K538" s="49" t="n"/>
+      <c r="K538" s="48" t="n">
+        <v>570</v>
+      </c>
       <c r="L538" s="49" t="n"/>
       <c r="M538" s="49" t="n"/>
       <c r="N538" s="49" t="n"/>
@@ -22125,11 +22249,23 @@
       <c r="F540" s="7" t="n">
         <v>3560</v>
       </c>
-      <c r="G540" s="50" t="n"/>
-      <c r="H540" s="49" t="n"/>
-      <c r="I540" s="49" t="n"/>
+      <c r="G540" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H540" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I540" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J540" s="49" t="n"/>
-      <c r="K540" s="49" t="n"/>
+      <c r="K540" s="48" t="n">
+        <v>3560</v>
+      </c>
       <c r="L540" s="49" t="n"/>
       <c r="M540" s="49" t="n"/>
       <c r="N540" s="49" t="n"/>
@@ -22159,11 +22295,23 @@
       <c r="F541" s="7" t="n">
         <v>2442</v>
       </c>
-      <c r="G541" s="50" t="n"/>
-      <c r="H541" s="49" t="n"/>
-      <c r="I541" s="49" t="n"/>
+      <c r="G541" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H541" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I541" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J541" s="49" t="n"/>
-      <c r="K541" s="49" t="n"/>
+      <c r="K541" s="48" t="n">
+        <v>2442</v>
+      </c>
       <c r="L541" s="49" t="n"/>
       <c r="M541" s="49" t="n"/>
       <c r="N541" s="49" t="n"/>
@@ -22193,11 +22341,23 @@
       <c r="F542" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="G542" s="50" t="n"/>
-      <c r="H542" s="49" t="n"/>
-      <c r="I542" s="49" t="n"/>
+      <c r="G542" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H542" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I542" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J542" s="49" t="n"/>
-      <c r="K542" s="49" t="n"/>
+      <c r="K542" s="48" t="n">
+        <v>298</v>
+      </c>
       <c r="L542" s="49" t="n"/>
       <c r="M542" s="49" t="n"/>
       <c r="N542" s="49" t="n"/>
@@ -22227,11 +22387,23 @@
       <c r="F543" s="7" t="n">
         <v>1076</v>
       </c>
-      <c r="G543" s="50" t="n"/>
-      <c r="H543" s="49" t="n"/>
-      <c r="I543" s="49" t="n"/>
+      <c r="G543" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H543" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I543" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J543" s="49" t="n"/>
-      <c r="K543" s="49" t="n"/>
+      <c r="K543" s="48" t="n">
+        <v>1076</v>
+      </c>
       <c r="L543" s="49" t="n"/>
       <c r="M543" s="49" t="n"/>
       <c r="N543" s="49" t="n"/>
@@ -22405,11 +22577,23 @@
       <c r="F548" s="7" t="n">
         <v>1104</v>
       </c>
-      <c r="G548" s="50" t="n"/>
-      <c r="H548" s="49" t="n"/>
-      <c r="I548" s="49" t="n"/>
+      <c r="G548" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H548" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I548" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J548" s="49" t="n"/>
-      <c r="K548" s="49" t="n"/>
+      <c r="K548" s="48" t="n">
+        <v>1104</v>
+      </c>
       <c r="L548" s="49" t="n"/>
       <c r="M548" s="49" t="n"/>
       <c r="N548" s="49" t="n"/>
@@ -22507,11 +22691,23 @@
       <c r="F551" s="7" t="n">
         <v>383</v>
       </c>
-      <c r="G551" s="50" t="n"/>
-      <c r="H551" s="49" t="n"/>
-      <c r="I551" s="49" t="n"/>
+      <c r="G551" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H551" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I551" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J551" s="49" t="n"/>
-      <c r="K551" s="49" t="n"/>
+      <c r="K551" s="48" t="n">
+        <v>383</v>
+      </c>
       <c r="L551" s="49" t="n"/>
       <c r="M551" s="49" t="n"/>
       <c r="N551" s="49" t="n"/>
@@ -22855,11 +23051,23 @@
       <c r="F561" s="7" t="n">
         <v>1595</v>
       </c>
-      <c r="G561" s="50" t="n"/>
-      <c r="H561" s="49" t="n"/>
-      <c r="I561" s="49" t="n"/>
+      <c r="G561" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H561" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I561" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J561" s="49" t="n"/>
-      <c r="K561" s="49" t="n"/>
+      <c r="K561" s="48" t="n">
+        <v>1595</v>
+      </c>
       <c r="L561" s="49" t="n"/>
       <c r="M561" s="49" t="n"/>
       <c r="N561" s="49" t="n"/>
@@ -22931,11 +23139,19 @@
       <c r="F563" s="7" t="n">
         <v>2703</v>
       </c>
-      <c r="G563" s="49" t="n"/>
-      <c r="H563" s="49" t="n"/>
-      <c r="I563" s="49" t="n"/>
+      <c r="G563" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H563" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I563" s="46" t="inlineStr"/>
       <c r="J563" s="49" t="n"/>
-      <c r="K563" s="49" t="n"/>
+      <c r="K563" s="48" t="n">
+        <v>2703</v>
+      </c>
       <c r="L563" s="49" t="n"/>
       <c r="M563" s="49" t="n"/>
       <c r="N563" s="49" t="n"/>
@@ -23101,11 +23317,23 @@
       <c r="F568" s="7" t="n">
         <v>737</v>
       </c>
-      <c r="G568" s="50" t="n"/>
-      <c r="H568" s="49" t="n"/>
-      <c r="I568" s="49" t="n"/>
+      <c r="G568" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H568" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I568" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J568" s="49" t="n"/>
-      <c r="K568" s="49" t="n"/>
+      <c r="K568" s="48" t="n">
+        <v>737</v>
+      </c>
       <c r="L568" s="49" t="n"/>
       <c r="M568" s="49" t="n"/>
       <c r="N568" s="49" t="n"/>
@@ -23177,11 +23405,19 @@
       <c r="F570" s="7" t="n">
         <v>1372</v>
       </c>
-      <c r="G570" s="49" t="n"/>
-      <c r="H570" s="49" t="n"/>
-      <c r="I570" s="49" t="n"/>
+      <c r="G570" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H570" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I570" s="46" t="inlineStr"/>
       <c r="J570" s="49" t="n"/>
-      <c r="K570" s="49" t="n"/>
+      <c r="K570" s="48" t="n">
+        <v>1372</v>
+      </c>
       <c r="L570" s="49" t="n"/>
       <c r="M570" s="49" t="n"/>
       <c r="N570" s="49" t="n"/>
@@ -23279,11 +23515,23 @@
       <c r="F573" s="7" t="n">
         <v>10103</v>
       </c>
-      <c r="G573" s="50" t="n"/>
-      <c r="H573" s="49" t="n"/>
-      <c r="I573" s="49" t="n"/>
+      <c r="G573" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H573" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I573" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J573" s="49" t="n"/>
-      <c r="K573" s="49" t="n"/>
+      <c r="K573" s="48" t="n">
+        <v>10103</v>
+      </c>
       <c r="L573" s="49" t="n"/>
       <c r="M573" s="49" t="n"/>
       <c r="N573" s="49" t="n"/>
@@ -23381,11 +23629,23 @@
       <c r="F576" s="7" t="n">
         <v>1288</v>
       </c>
-      <c r="G576" s="50" t="n"/>
-      <c r="H576" s="49" t="n"/>
-      <c r="I576" s="49" t="n"/>
+      <c r="G576" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H576" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I576" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J576" s="49" t="n"/>
-      <c r="K576" s="49" t="n"/>
+      <c r="K576" s="48" t="n">
+        <v>1288</v>
+      </c>
       <c r="L576" s="49" t="n"/>
       <c r="M576" s="49" t="n"/>
       <c r="N576" s="49" t="n"/>
@@ -23449,11 +23709,23 @@
       <c r="F578" s="7" t="n">
         <v>4002</v>
       </c>
-      <c r="G578" s="50" t="n"/>
-      <c r="H578" s="49" t="n"/>
-      <c r="I578" s="49" t="n"/>
+      <c r="G578" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H578" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I578" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J578" s="49" t="n"/>
-      <c r="K578" s="49" t="n"/>
+      <c r="K578" s="48" t="n">
+        <v>4002</v>
+      </c>
       <c r="L578" s="49" t="n"/>
       <c r="M578" s="49" t="n"/>
       <c r="N578" s="49" t="n"/>
@@ -23517,11 +23789,19 @@
       <c r="F580" s="7" t="n">
         <v>1514</v>
       </c>
-      <c r="G580" s="49" t="n"/>
-      <c r="H580" s="49" t="n"/>
-      <c r="I580" s="49" t="n"/>
+      <c r="G580" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H580" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I580" s="46" t="inlineStr"/>
       <c r="J580" s="49" t="n"/>
-      <c r="K580" s="49" t="n"/>
+      <c r="K580" s="48" t="n">
+        <v>1514</v>
+      </c>
       <c r="L580" s="49" t="n"/>
       <c r="M580" s="49" t="n"/>
       <c r="N580" s="49" t="n"/>
@@ -23551,11 +23831,19 @@
       <c r="F581" s="7" t="n">
         <v>3558</v>
       </c>
-      <c r="G581" s="49" t="n"/>
-      <c r="H581" s="49" t="n"/>
-      <c r="I581" s="49" t="n"/>
+      <c r="G581" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H581" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I581" s="46" t="inlineStr"/>
       <c r="J581" s="49" t="n"/>
-      <c r="K581" s="49" t="n"/>
+      <c r="K581" s="48" t="n">
+        <v>3558</v>
+      </c>
       <c r="L581" s="49" t="n"/>
       <c r="M581" s="49" t="n"/>
       <c r="N581" s="49" t="n"/>
@@ -23729,11 +24017,19 @@
       <c r="F586" s="7" t="n">
         <v>1500</v>
       </c>
-      <c r="G586" s="49" t="n"/>
-      <c r="H586" s="49" t="n"/>
-      <c r="I586" s="49" t="n"/>
+      <c r="G586" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H586" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I586" s="46" t="inlineStr"/>
       <c r="J586" s="49" t="n"/>
-      <c r="K586" s="49" t="n"/>
+      <c r="K586" s="48" t="n">
+        <v>1500</v>
+      </c>
       <c r="L586" s="49" t="n"/>
       <c r="M586" s="49" t="n"/>
       <c r="N586" s="49" t="n"/>
@@ -23797,11 +24093,23 @@
       <c r="F588" s="7" t="n">
         <v>1970</v>
       </c>
-      <c r="G588" s="50" t="n"/>
-      <c r="H588" s="49" t="n"/>
-      <c r="I588" s="49" t="n"/>
+      <c r="G588" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H588" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I588" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J588" s="49" t="n"/>
-      <c r="K588" s="49" t="n"/>
+      <c r="K588" s="48" t="n">
+        <v>1970</v>
+      </c>
       <c r="L588" s="49" t="n"/>
       <c r="M588" s="49" t="n"/>
       <c r="N588" s="49" t="n"/>
@@ -23831,11 +24139,23 @@
       <c r="F589" s="7" t="n">
         <v>2554</v>
       </c>
-      <c r="G589" s="50" t="n"/>
-      <c r="H589" s="49" t="n"/>
-      <c r="I589" s="49" t="n"/>
+      <c r="G589" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H589" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I589" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J589" s="49" t="n"/>
-      <c r="K589" s="49" t="n"/>
+      <c r="K589" s="48" t="n">
+        <v>2554</v>
+      </c>
       <c r="L589" s="49" t="n"/>
       <c r="M589" s="49" t="n"/>
       <c r="N589" s="49" t="n"/>
@@ -23865,11 +24185,19 @@
       <c r="F590" s="7" t="n">
         <v>582</v>
       </c>
-      <c r="G590" s="49" t="n"/>
-      <c r="H590" s="49" t="n"/>
-      <c r="I590" s="49" t="n"/>
+      <c r="G590" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H590" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I590" s="46" t="inlineStr"/>
       <c r="J590" s="49" t="n"/>
-      <c r="K590" s="49" t="n"/>
+      <c r="K590" s="48" t="n">
+        <v>582</v>
+      </c>
       <c r="L590" s="49" t="n"/>
       <c r="M590" s="49" t="n"/>
       <c r="N590" s="49" t="n"/>
@@ -24035,11 +24363,23 @@
       <c r="F595" s="7" t="n">
         <v>4807</v>
       </c>
-      <c r="G595" s="50" t="n"/>
-      <c r="H595" s="49" t="n"/>
-      <c r="I595" s="49" t="n"/>
+      <c r="G595" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H595" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I595" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J595" s="49" t="n"/>
-      <c r="K595" s="49" t="n"/>
+      <c r="K595" s="48" t="n">
+        <v>4807</v>
+      </c>
       <c r="L595" s="49" t="n"/>
       <c r="M595" s="49" t="n"/>
       <c r="N595" s="49" t="n"/>
@@ -24069,11 +24409,19 @@
       <c r="F596" s="7" t="n">
         <v>1016</v>
       </c>
-      <c r="G596" s="49" t="n"/>
-      <c r="H596" s="49" t="n"/>
-      <c r="I596" s="49" t="n"/>
+      <c r="G596" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H596" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I596" s="46" t="inlineStr"/>
       <c r="J596" s="49" t="n"/>
-      <c r="K596" s="49" t="n"/>
+      <c r="K596" s="48" t="n">
+        <v>1016</v>
+      </c>
       <c r="L596" s="49" t="n"/>
       <c r="M596" s="49" t="n"/>
       <c r="N596" s="49" t="n"/>
@@ -24179,11 +24527,19 @@
       <c r="F599" s="7" t="n">
         <v>3567</v>
       </c>
-      <c r="G599" s="49" t="n"/>
-      <c r="H599" s="49" t="n"/>
-      <c r="I599" s="49" t="n"/>
+      <c r="G599" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H599" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I599" s="46" t="inlineStr"/>
       <c r="J599" s="49" t="n"/>
-      <c r="K599" s="49" t="n"/>
+      <c r="K599" s="48" t="n">
+        <v>3567</v>
+      </c>
       <c r="L599" s="49" t="n"/>
       <c r="M599" s="49" t="n"/>
       <c r="N599" s="49" t="n"/>
@@ -24213,11 +24569,23 @@
       <c r="F600" s="7" t="n">
         <v>1086</v>
       </c>
-      <c r="G600" s="50" t="n"/>
-      <c r="H600" s="49" t="n"/>
-      <c r="I600" s="49" t="n"/>
+      <c r="G600" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H600" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I600" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J600" s="49" t="n"/>
-      <c r="K600" s="49" t="n"/>
+      <c r="K600" s="48" t="n">
+        <v>1086</v>
+      </c>
       <c r="L600" s="49" t="n"/>
       <c r="M600" s="49" t="n"/>
       <c r="N600" s="49" t="n"/>
@@ -24391,11 +24759,23 @@
       <c r="F605" s="7" t="n">
         <v>233</v>
       </c>
-      <c r="G605" s="50" t="n"/>
-      <c r="H605" s="49" t="n"/>
-      <c r="I605" s="49" t="n"/>
+      <c r="G605" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H605" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I605" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J605" s="49" t="n"/>
-      <c r="K605" s="49" t="n"/>
+      <c r="K605" s="48" t="n">
+        <v>233</v>
+      </c>
       <c r="L605" s="49" t="n"/>
       <c r="M605" s="49" t="n"/>
       <c r="N605" s="49" t="n"/>
@@ -24425,11 +24805,19 @@
       <c r="F606" s="7" t="n">
         <v>1628</v>
       </c>
-      <c r="G606" s="49" t="n"/>
-      <c r="H606" s="49" t="n"/>
-      <c r="I606" s="49" t="n"/>
+      <c r="G606" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H606" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I606" s="46" t="inlineStr"/>
       <c r="J606" s="49" t="n"/>
-      <c r="K606" s="49" t="n"/>
+      <c r="K606" s="48" t="n">
+        <v>1628</v>
+      </c>
       <c r="L606" s="49" t="n"/>
       <c r="M606" s="49" t="n"/>
       <c r="N606" s="49" t="n"/>
@@ -24459,11 +24847,23 @@
       <c r="F607" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="G607" s="50" t="n"/>
-      <c r="H607" s="49" t="n"/>
-      <c r="I607" s="49" t="n"/>
+      <c r="G607" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H607" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I607" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J607" s="49" t="n"/>
-      <c r="K607" s="49" t="n"/>
+      <c r="K607" s="48" t="n">
+        <v>137</v>
+      </c>
       <c r="L607" s="49" t="n"/>
       <c r="M607" s="49" t="n"/>
       <c r="N607" s="49" t="n"/>
@@ -24977,11 +25377,19 @@
       <c r="F622" s="7" t="n">
         <v>590</v>
       </c>
-      <c r="G622" s="49" t="n"/>
-      <c r="H622" s="49" t="n"/>
-      <c r="I622" s="49" t="n"/>
+      <c r="G622" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H622" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I622" s="46" t="inlineStr"/>
       <c r="J622" s="49" t="n"/>
-      <c r="K622" s="49" t="n"/>
+      <c r="K622" s="48" t="n">
+        <v>590</v>
+      </c>
       <c r="L622" s="49" t="n"/>
       <c r="M622" s="49" t="n"/>
       <c r="N622" s="49" t="n"/>
@@ -25011,11 +25419,23 @@
       <c r="F623" s="7" t="n">
         <v>992</v>
       </c>
-      <c r="G623" s="50" t="n"/>
-      <c r="H623" s="49" t="n"/>
-      <c r="I623" s="49" t="n"/>
+      <c r="G623" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H623" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I623" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J623" s="49" t="n"/>
-      <c r="K623" s="49" t="n"/>
+      <c r="K623" s="48" t="n">
+        <v>992</v>
+      </c>
       <c r="L623" s="49" t="n"/>
       <c r="M623" s="49" t="n"/>
       <c r="N623" s="49" t="n"/>
@@ -25285,11 +25705,19 @@
       <c r="F631" s="7" t="n">
         <v>446</v>
       </c>
-      <c r="G631" s="49" t="n"/>
-      <c r="H631" s="49" t="n"/>
-      <c r="I631" s="49" t="n"/>
+      <c r="G631" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H631" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I631" s="46" t="inlineStr"/>
       <c r="J631" s="49" t="n"/>
-      <c r="K631" s="49" t="n"/>
+      <c r="K631" s="48" t="n">
+        <v>446</v>
+      </c>
       <c r="L631" s="49" t="n"/>
       <c r="M631" s="49" t="n"/>
       <c r="N631" s="49" t="n"/>
@@ -25361,11 +25789,19 @@
       <c r="F633" s="7" t="n">
         <v>2283</v>
       </c>
-      <c r="G633" s="49" t="n"/>
-      <c r="H633" s="49" t="n"/>
-      <c r="I633" s="49" t="n"/>
+      <c r="G633" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H633" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I633" s="46" t="inlineStr"/>
       <c r="J633" s="49" t="n"/>
-      <c r="K633" s="49" t="n"/>
+      <c r="K633" s="48" t="n">
+        <v>2283</v>
+      </c>
       <c r="L633" s="49" t="n"/>
       <c r="M633" s="49" t="n"/>
       <c r="N633" s="49" t="n"/>
@@ -25437,11 +25873,23 @@
       <c r="F635" s="7" t="n">
         <v>602</v>
       </c>
-      <c r="G635" s="50" t="n"/>
-      <c r="H635" s="49" t="n"/>
-      <c r="I635" s="49" t="n"/>
+      <c r="G635" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H635" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I635" s="46" t="inlineStr">
+        <is>
+          <t>002653</t>
+        </is>
+      </c>
       <c r="J635" s="49" t="n"/>
-      <c r="K635" s="49" t="n"/>
+      <c r="K635" s="48" t="n">
+        <v>602</v>
+      </c>
       <c r="L635" s="49" t="n"/>
       <c r="M635" s="49" t="n"/>
       <c r="N635" s="49" t="n"/>
@@ -25505,11 +25953,23 @@
       <c r="F637" s="7" t="n">
         <v>6242</v>
       </c>
-      <c r="G637" s="50" t="n"/>
-      <c r="H637" s="49" t="n"/>
-      <c r="I637" s="49" t="n"/>
+      <c r="G637" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H637" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I637" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J637" s="49" t="n"/>
-      <c r="K637" s="49" t="n"/>
+      <c r="K637" s="48" t="n">
+        <v>6242</v>
+      </c>
       <c r="L637" s="49" t="n"/>
       <c r="M637" s="49" t="n"/>
       <c r="N637" s="49" t="n"/>
@@ -25607,11 +26067,19 @@
       <c r="F640" s="7" t="n">
         <v>1663</v>
       </c>
-      <c r="G640" s="49" t="n"/>
-      <c r="H640" s="49" t="n"/>
-      <c r="I640" s="49" t="n"/>
+      <c r="G640" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H640" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I640" s="46" t="inlineStr"/>
       <c r="J640" s="49" t="n"/>
-      <c r="K640" s="49" t="n"/>
+      <c r="K640" s="48" t="n">
+        <v>1663</v>
+      </c>
       <c r="L640" s="49" t="n"/>
       <c r="M640" s="49" t="n"/>
       <c r="N640" s="49" t="n"/>
@@ -25641,11 +26109,23 @@
       <c r="F641" s="7" t="n">
         <v>608</v>
       </c>
-      <c r="G641" s="50" t="n"/>
-      <c r="H641" s="49" t="n"/>
-      <c r="I641" s="49" t="n"/>
+      <c r="G641" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H641" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I641" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J641" s="49" t="n"/>
-      <c r="K641" s="49" t="n"/>
+      <c r="K641" s="48" t="n">
+        <v>608</v>
+      </c>
       <c r="L641" s="49" t="n"/>
       <c r="M641" s="49" t="n"/>
       <c r="N641" s="49" t="n"/>
@@ -25947,11 +26427,23 @@
       <c r="F650" s="7" t="n">
         <v>636</v>
       </c>
-      <c r="G650" s="50" t="n"/>
-      <c r="H650" s="49" t="n"/>
-      <c r="I650" s="49" t="n"/>
+      <c r="G650" s="45" t="n">
+        <v>45935</v>
+      </c>
+      <c r="H650" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I650" s="46" t="inlineStr">
+        <is>
+          <t>002651</t>
+        </is>
+      </c>
       <c r="J650" s="49" t="n"/>
-      <c r="K650" s="49" t="n"/>
+      <c r="K650" s="48" t="n">
+        <v>636</v>
+      </c>
       <c r="L650" s="49" t="n"/>
       <c r="M650" s="49" t="n"/>
       <c r="N650" s="49" t="n"/>
@@ -25981,11 +26473,19 @@
       <c r="F651" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="G651" s="49" t="n"/>
-      <c r="H651" s="49" t="n"/>
-      <c r="I651" s="49" t="n"/>
+      <c r="G651" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H651" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I651" s="46" t="inlineStr"/>
       <c r="J651" s="49" t="n"/>
-      <c r="K651" s="49" t="n"/>
+      <c r="K651" s="48" t="n">
+        <v>138</v>
+      </c>
       <c r="L651" s="49" t="n"/>
       <c r="M651" s="49" t="n"/>
       <c r="N651" s="49" t="n"/>
@@ -26015,11 +26515,19 @@
       <c r="F652" s="7" t="n">
         <v>1111</v>
       </c>
-      <c r="G652" s="49" t="n"/>
-      <c r="H652" s="49" t="n"/>
-      <c r="I652" s="49" t="n"/>
+      <c r="G652" s="61" t="n">
+        <v>45927</v>
+      </c>
+      <c r="H652" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I652" s="46" t="inlineStr"/>
       <c r="J652" s="49" t="n"/>
-      <c r="K652" s="49" t="n"/>
+      <c r="K652" s="48" t="n">
+        <v>1111</v>
+      </c>
       <c r="L652" s="49" t="n"/>
       <c r="M652" s="49" t="n"/>
       <c r="N652" s="49" t="n"/>
@@ -26159,11 +26667,19 @@
       <c r="F656" s="7" t="n">
         <v>4076</v>
       </c>
-      <c r="G656" s="49" t="n"/>
-      <c r="H656" s="49" t="n"/>
-      <c r="I656" s="49" t="n"/>
+      <c r="G656" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H656" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I656" s="46" t="inlineStr"/>
       <c r="J656" s="49" t="n"/>
-      <c r="K656" s="49" t="n"/>
+      <c r="K656" s="48" t="n">
+        <v>4076</v>
+      </c>
       <c r="L656" s="49" t="n"/>
       <c r="M656" s="49" t="n"/>
       <c r="N656" s="49" t="n"/>
@@ -26397,11 +26913,23 @@
       <c r="F663" s="7" t="n">
         <v>1180</v>
       </c>
-      <c r="G663" s="50" t="n"/>
-      <c r="H663" s="49" t="n"/>
-      <c r="I663" s="49" t="n"/>
+      <c r="G663" s="45" t="n">
+        <v>45908</v>
+      </c>
+      <c r="H663" s="46" t="inlineStr">
+        <is>
+          <t>CHQ</t>
+        </is>
+      </c>
+      <c r="I663" s="46" t="inlineStr">
+        <is>
+          <t>002611</t>
+        </is>
+      </c>
       <c r="J663" s="49" t="n"/>
-      <c r="K663" s="49" t="n"/>
+      <c r="K663" s="48" t="n">
+        <v>1149</v>
+      </c>
       <c r="L663" s="49" t="n"/>
       <c r="M663" s="49" t="n"/>
       <c r="N663" s="49" t="n"/>
@@ -26601,11 +27129,19 @@
       <c r="F669" s="7" t="n">
         <v>5904</v>
       </c>
-      <c r="G669" s="49" t="n"/>
-      <c r="H669" s="49" t="n"/>
-      <c r="I669" s="49" t="n"/>
+      <c r="G669" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H669" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I669" s="46" t="inlineStr"/>
       <c r="J669" s="49" t="n"/>
-      <c r="K669" s="49" t="n"/>
+      <c r="K669" s="48" t="n">
+        <v>5904</v>
+      </c>
       <c r="L669" s="49" t="n"/>
       <c r="M669" s="49" t="n"/>
       <c r="N669" s="49" t="n"/>
@@ -26771,11 +27307,19 @@
       <c r="F674" s="7" t="n">
         <v>528</v>
       </c>
-      <c r="G674" s="49" t="n"/>
-      <c r="H674" s="49" t="n"/>
-      <c r="I674" s="49" t="n"/>
+      <c r="G674" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H674" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I674" s="46" t="inlineStr"/>
       <c r="J674" s="49" t="n"/>
-      <c r="K674" s="49" t="n"/>
+      <c r="K674" s="48" t="n">
+        <v>528</v>
+      </c>
       <c r="L674" s="49" t="n"/>
       <c r="M674" s="49" t="n"/>
       <c r="N674" s="49" t="n"/>
@@ -27145,11 +27689,19 @@
       <c r="F685" s="7" t="n">
         <v>457</v>
       </c>
-      <c r="G685" s="49" t="n"/>
-      <c r="H685" s="49" t="n"/>
-      <c r="I685" s="49" t="n"/>
+      <c r="G685" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H685" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I685" s="46" t="inlineStr"/>
       <c r="J685" s="49" t="n"/>
-      <c r="K685" s="49" t="n"/>
+      <c r="K685" s="48" t="n">
+        <v>457</v>
+      </c>
       <c r="L685" s="49" t="n"/>
       <c r="M685" s="49" t="n"/>
       <c r="N685" s="49" t="n"/>
@@ -27315,11 +27867,19 @@
       <c r="F690" s="7" t="n">
         <v>2452</v>
       </c>
-      <c r="G690" s="49" t="n"/>
-      <c r="H690" s="49" t="n"/>
-      <c r="I690" s="49" t="n"/>
+      <c r="G690" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H690" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I690" s="46" t="inlineStr"/>
       <c r="J690" s="49" t="n"/>
-      <c r="K690" s="49" t="n"/>
+      <c r="K690" s="48" t="n">
+        <v>2452</v>
+      </c>
       <c r="L690" s="49" t="n"/>
       <c r="M690" s="49" t="n"/>
       <c r="N690" s="49" t="n"/>
@@ -27553,11 +28113,19 @@
       <c r="F697" s="7" t="n">
         <v>3257</v>
       </c>
-      <c r="G697" s="49" t="n"/>
-      <c r="H697" s="49" t="n"/>
-      <c r="I697" s="49" t="n"/>
+      <c r="G697" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H697" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I697" s="46" t="inlineStr"/>
       <c r="J697" s="49" t="n"/>
-      <c r="K697" s="49" t="n"/>
+      <c r="K697" s="48" t="n">
+        <v>3257</v>
+      </c>
       <c r="L697" s="49" t="n"/>
       <c r="M697" s="49" t="n"/>
       <c r="N697" s="49" t="n"/>
@@ -27757,11 +28325,19 @@
       <c r="F703" s="7" t="n">
         <v>3644</v>
       </c>
-      <c r="G703" s="49" t="n"/>
-      <c r="H703" s="49" t="n"/>
-      <c r="I703" s="49" t="n"/>
+      <c r="G703" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H703" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I703" s="46" t="inlineStr"/>
       <c r="J703" s="49" t="n"/>
-      <c r="K703" s="49" t="n"/>
+      <c r="K703" s="48" t="n">
+        <v>3644</v>
+      </c>
       <c r="L703" s="49" t="n"/>
       <c r="M703" s="49" t="n"/>
       <c r="N703" s="49" t="n"/>
@@ -27893,11 +28469,19 @@
       <c r="F707" s="7" t="n">
         <v>1544</v>
       </c>
-      <c r="G707" s="49" t="n"/>
-      <c r="H707" s="49" t="n"/>
-      <c r="I707" s="49" t="n"/>
+      <c r="G707" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H707" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I707" s="46" t="inlineStr"/>
       <c r="J707" s="49" t="n"/>
-      <c r="K707" s="49" t="n"/>
+      <c r="K707" s="48" t="n">
+        <v>1544</v>
+      </c>
       <c r="L707" s="49" t="n"/>
       <c r="M707" s="49" t="n"/>
       <c r="N707" s="49" t="n"/>
@@ -27967,7 +28551,9 @@
       <c r="J709" s="49" t="n"/>
       <c r="K709" s="49" t="n"/>
       <c r="L709" s="49" t="n"/>
-      <c r="M709" s="49" t="n"/>
+      <c r="M709" s="51" t="n">
+        <v>2922</v>
+      </c>
       <c r="N709" s="49" t="n"/>
     </row>
     <row r="710">
@@ -28063,11 +28649,19 @@
       <c r="F712" s="7" t="n">
         <v>1728</v>
       </c>
-      <c r="G712" s="49" t="n"/>
-      <c r="H712" s="49" t="n"/>
-      <c r="I712" s="49" t="n"/>
+      <c r="G712" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H712" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I712" s="46" t="inlineStr"/>
       <c r="J712" s="49" t="n"/>
-      <c r="K712" s="49" t="n"/>
+      <c r="K712" s="48" t="n">
+        <v>1728</v>
+      </c>
       <c r="L712" s="49" t="n"/>
       <c r="M712" s="49" t="n"/>
       <c r="N712" s="49" t="n"/>
@@ -28273,7 +28867,9 @@
       <c r="J718" s="49" t="n"/>
       <c r="K718" s="49" t="n"/>
       <c r="L718" s="49" t="n"/>
-      <c r="M718" s="49" t="n"/>
+      <c r="M718" s="51" t="n">
+        <v>530</v>
+      </c>
       <c r="N718" s="49" t="n"/>
     </row>
     <row r="719">
@@ -28301,11 +28897,19 @@
       <c r="F719" s="7" t="n">
         <v>1329</v>
       </c>
-      <c r="G719" s="49" t="n"/>
-      <c r="H719" s="49" t="n"/>
-      <c r="I719" s="49" t="n"/>
+      <c r="G719" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H719" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I719" s="46" t="inlineStr"/>
       <c r="J719" s="49" t="n"/>
-      <c r="K719" s="49" t="n"/>
+      <c r="K719" s="48" t="n">
+        <v>1329</v>
+      </c>
       <c r="L719" s="49" t="n"/>
       <c r="M719" s="49" t="n"/>
       <c r="N719" s="49" t="n"/>
@@ -28477,7 +29081,9 @@
       <c r="J724" s="49" t="n"/>
       <c r="K724" s="49" t="n"/>
       <c r="L724" s="49" t="n"/>
-      <c r="M724" s="49" t="n"/>
+      <c r="M724" s="51" t="n">
+        <v>263</v>
+      </c>
       <c r="N724" s="49" t="n"/>
     </row>
     <row r="725">
@@ -28607,11 +29213,19 @@
       <c r="F728" s="7" t="n">
         <v>773</v>
       </c>
-      <c r="G728" s="49" t="n"/>
-      <c r="H728" s="49" t="n"/>
-      <c r="I728" s="49" t="n"/>
+      <c r="G728" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H728" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I728" s="46" t="inlineStr"/>
       <c r="J728" s="49" t="n"/>
-      <c r="K728" s="49" t="n"/>
+      <c r="K728" s="48" t="n">
+        <v>773</v>
+      </c>
       <c r="L728" s="49" t="n"/>
       <c r="M728" s="49" t="n"/>
       <c r="N728" s="49" t="n"/>
@@ -28715,7 +29329,9 @@
       <c r="J731" s="49" t="n"/>
       <c r="K731" s="49" t="n"/>
       <c r="L731" s="49" t="n"/>
-      <c r="M731" s="49" t="n"/>
+      <c r="M731" s="51" t="n">
+        <v>296</v>
+      </c>
       <c r="N731" s="49" t="n"/>
     </row>
     <row r="732">
@@ -28879,11 +29495,19 @@
       <c r="F736" s="7" t="n">
         <v>2218</v>
       </c>
-      <c r="G736" s="49" t="n"/>
-      <c r="H736" s="49" t="n"/>
-      <c r="I736" s="49" t="n"/>
+      <c r="G736" s="61" t="n">
+        <v>45926</v>
+      </c>
+      <c r="H736" s="46" t="inlineStr">
+        <is>
+          <t>GPAY</t>
+        </is>
+      </c>
+      <c r="I736" s="46" t="inlineStr"/>
       <c r="J736" s="49" t="n"/>
-      <c r="K736" s="49" t="n"/>
+      <c r="K736" s="48" t="n">
+        <v>2218</v>
+      </c>
       <c r="L736" s="49" t="n"/>
       <c r="M736" s="49" t="n"/>
       <c r="N736" s="49" t="n"/>
@@ -29259,7 +29883,9 @@
       <c r="J747" s="49" t="n"/>
       <c r="K747" s="49" t="n"/>
       <c r="L747" s="49" t="n"/>
-      <c r="M747" s="49" t="n"/>
+      <c r="M747" s="51" t="n">
+        <v>2116</v>
+      </c>
       <c r="N747" s="49" t="n"/>
     </row>
     <row r="748">
@@ -29497,7 +30123,9 @@
       <c r="J754" s="49" t="n"/>
       <c r="K754" s="49" t="n"/>
       <c r="L754" s="49" t="n"/>
-      <c r="M754" s="49" t="n"/>
+      <c r="M754" s="51" t="n">
+        <v>1502</v>
+      </c>
       <c r="N754" s="49" t="n"/>
     </row>
     <row r="755">
@@ -29667,7 +30295,9 @@
       <c r="J759" s="49" t="n"/>
       <c r="K759" s="49" t="n"/>
       <c r="L759" s="49" t="n"/>
-      <c r="M759" s="49" t="n"/>
+      <c r="M759" s="51" t="n">
+        <v>413</v>
+      </c>
       <c r="N759" s="49" t="n"/>
     </row>
     <row r="760">
@@ -29803,7 +30433,9 @@
       <c r="J763" s="49" t="n"/>
       <c r="K763" s="49" t="n"/>
       <c r="L763" s="49" t="n"/>
-      <c r="M763" s="49" t="n"/>
+      <c r="M763" s="51" t="n">
+        <v>3257</v>
+      </c>
       <c r="N763" s="49" t="n"/>
     </row>
     <row r="764">
@@ -30313,7 +30945,9 @@
       <c r="J778" s="49" t="n"/>
       <c r="K778" s="49" t="n"/>
       <c r="L778" s="49" t="n"/>
-      <c r="M778" s="49" t="n"/>
+      <c r="M778" s="51" t="n">
+        <v>5623</v>
+      </c>
       <c r="N778" s="49" t="n"/>
     </row>
     <row r="779">
@@ -30415,7 +31049,9 @@
       <c r="J781" s="49" t="n"/>
       <c r="K781" s="49" t="n"/>
       <c r="L781" s="49" t="n"/>
-      <c r="M781" s="49" t="n"/>
+      <c r="M781" s="51" t="n">
+        <v>481</v>
+      </c>
       <c r="N781" s="49" t="n"/>
     </row>
     <row r="782">
@@ -30551,7 +31187,9 @@
       <c r="J785" s="49" t="n"/>
       <c r="K785" s="49" t="n"/>
       <c r="L785" s="49" t="n"/>
-      <c r="M785" s="49" t="n"/>
+      <c r="M785" s="51" t="n">
+        <v>3571</v>
+      </c>
       <c r="N785" s="49" t="n"/>
     </row>
     <row r="786">
@@ -30823,7 +31461,9 @@
       <c r="J793" s="49" t="n"/>
       <c r="K793" s="49" t="n"/>
       <c r="L793" s="49" t="n"/>
-      <c r="M793" s="49" t="n"/>
+      <c r="M793" s="51" t="n">
+        <v>2587</v>
+      </c>
       <c r="N793" s="49" t="n"/>
     </row>
     <row r="794">
@@ -31197,7 +31837,9 @@
       <c r="J804" s="49" t="n"/>
       <c r="K804" s="49" t="n"/>
       <c r="L804" s="49" t="n"/>
-      <c r="M804" s="49" t="n"/>
+      <c r="M804" s="51" t="n">
+        <v>574</v>
+      </c>
       <c r="N804" s="49" t="n"/>
     </row>
     <row r="805">
@@ -31537,7 +32179,9 @@
       <c r="J814" s="49" t="n"/>
       <c r="K814" s="49" t="n"/>
       <c r="L814" s="49" t="n"/>
-      <c r="M814" s="49" t="n"/>
+      <c r="M814" s="51" t="n">
+        <v>1590</v>
+      </c>
       <c r="N814" s="49" t="n"/>
     </row>
     <row r="815">
@@ -31639,7 +32283,9 @@
       <c r="J817" s="49" t="n"/>
       <c r="K817" s="49" t="n"/>
       <c r="L817" s="49" t="n"/>
-      <c r="M817" s="49" t="n"/>
+      <c r="M817" s="51" t="n">
+        <v>141</v>
+      </c>
       <c r="N817" s="49" t="n"/>
     </row>
     <row r="818">
@@ -31877,7 +32523,9 @@
       <c r="J824" s="49" t="n"/>
       <c r="K824" s="49" t="n"/>
       <c r="L824" s="49" t="n"/>
-      <c r="M824" s="49" t="n"/>
+      <c r="M824" s="51" t="n">
+        <v>1689</v>
+      </c>
       <c r="N824" s="49" t="n"/>
     </row>
     <row r="825">
@@ -32047,7 +32695,9 @@
       <c r="J829" s="49" t="n"/>
       <c r="K829" s="49" t="n"/>
       <c r="L829" s="49" t="n"/>
-      <c r="M829" s="49" t="n"/>
+      <c r="M829" s="51" t="n">
+        <v>962</v>
+      </c>
       <c r="N829" s="49" t="n"/>
     </row>
     <row r="830">
@@ -32421,7 +33071,9 @@
       <c r="J840" s="49" t="n"/>
       <c r="K840" s="49" t="n"/>
       <c r="L840" s="49" t="n"/>
-      <c r="M840" s="49" t="n"/>
+      <c r="M840" s="51" t="n">
+        <v>1667</v>
+      </c>
       <c r="N840" s="49" t="n"/>
     </row>
     <row r="841">
@@ -32455,7 +33107,9 @@
       <c r="J841" s="49" t="n"/>
       <c r="K841" s="49" t="n"/>
       <c r="L841" s="49" t="n"/>
-      <c r="M841" s="49" t="n"/>
+      <c r="M841" s="51" t="n">
+        <v>4176</v>
+      </c>
       <c r="N841" s="49" t="n"/>
     </row>
     <row r="842">
@@ -32523,7 +33177,9 @@
       <c r="J843" s="49" t="n"/>
       <c r="K843" s="49" t="n"/>
       <c r="L843" s="49" t="n"/>
-      <c r="M843" s="49" t="n"/>
+      <c r="M843" s="51" t="n">
+        <v>1037</v>
+      </c>
       <c r="N843" s="49" t="n"/>
     </row>
     <row r="844">
@@ -32591,7 +33247,9 @@
       <c r="J845" s="49" t="n"/>
       <c r="K845" s="49" t="n"/>
       <c r="L845" s="49" t="n"/>
-      <c r="M845" s="49" t="n"/>
+      <c r="M845" s="51" t="n">
+        <v>460</v>
+      </c>
       <c r="N845" s="49" t="n"/>
     </row>
     <row r="846">
@@ -33245,7 +33903,9 @@
       <c r="J866" s="49" t="n"/>
       <c r="K866" s="49" t="n"/>
       <c r="L866" s="49" t="n"/>
-      <c r="M866" s="49" t="n"/>
+      <c r="M866" s="51" t="n">
+        <v>4177</v>
+      </c>
       <c r="N866" s="49" t="n"/>
     </row>
     <row r="867">
@@ -33275,7 +33935,9 @@
       <c r="J867" s="49" t="n"/>
       <c r="K867" s="49" t="n"/>
       <c r="L867" s="49" t="n"/>
-      <c r="M867" s="49" t="n"/>
+      <c r="M867" s="51" t="n">
+        <v>1810</v>
+      </c>
       <c r="N867" s="49" t="n"/>
     </row>
     <row r="868">
@@ -33695,7 +34357,9 @@
       <c r="J881" s="49" t="n"/>
       <c r="K881" s="49" t="n"/>
       <c r="L881" s="49" t="n"/>
-      <c r="M881" s="49" t="n"/>
+      <c r="M881" s="51" t="n">
+        <v>1389</v>
+      </c>
       <c r="N881" s="49" t="n"/>
     </row>
     <row r="882">
@@ -33785,7 +34449,9 @@
       <c r="J884" s="49" t="n"/>
       <c r="K884" s="49" t="n"/>
       <c r="L884" s="49" t="n"/>
-      <c r="M884" s="49" t="n"/>
+      <c r="M884" s="51" t="n">
+        <v>2621</v>
+      </c>
       <c r="N884" s="49" t="n"/>
     </row>
     <row r="885">
@@ -33995,7 +34661,9 @@
       <c r="J891" s="49" t="n"/>
       <c r="K891" s="49" t="n"/>
       <c r="L891" s="49" t="n"/>
-      <c r="M891" s="49" t="n"/>
+      <c r="M891" s="51" t="n">
+        <v>700</v>
+      </c>
       <c r="N891" s="49" t="n"/>
     </row>
     <row r="892">
@@ -34055,7 +34723,9 @@
       <c r="J893" s="49" t="n"/>
       <c r="K893" s="49" t="n"/>
       <c r="L893" s="49" t="n"/>
-      <c r="M893" s="49" t="n"/>
+      <c r="M893" s="51" t="n">
+        <v>800</v>
+      </c>
       <c r="N893" s="49" t="n"/>
     </row>
     <row r="894">
@@ -34445,7 +35115,9 @@
       <c r="J906" s="49" t="n"/>
       <c r="K906" s="49" t="n"/>
       <c r="L906" s="49" t="n"/>
-      <c r="M906" s="49" t="n"/>
+      <c r="M906" s="51" t="n">
+        <v>5648</v>
+      </c>
       <c r="N906" s="49" t="n"/>
     </row>
     <row r="907">
@@ -34745,7 +35417,9 @@
       <c r="J916" s="49" t="n"/>
       <c r="K916" s="49" t="n"/>
       <c r="L916" s="49" t="n"/>
-      <c r="M916" s="49" t="n"/>
+      <c r="M916" s="51" t="n">
+        <v>765</v>
+      </c>
       <c r="N916" s="49" t="n"/>
     </row>
     <row r="917">
